--- a/data/ISP.MI.xlsx
+++ b/data/ISP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="2240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="2241">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53063893318176</t>
+    <t xml:space="preserve">1.53063905239105</t>
   </si>
   <si>
     <t xml:space="preserve">ISP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56040966510773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51832008361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49265539646149</t>
+    <t xml:space="preserve">1.56040990352631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51831960678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4926552772522</t>
   </si>
   <si>
     <t xml:space="preserve">1.48752236366272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46699059009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49676156044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52447938919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48546898365021</t>
+    <t xml:space="preserve">1.46699047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49676167964935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52447950839996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48546922206879</t>
   </si>
   <si>
     <t xml:space="preserve">1.43824625015259</t>
@@ -74,73 +74,73 @@
     <t xml:space="preserve">1.36638534069061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38075757026672</t>
+    <t xml:space="preserve">1.38075733184814</t>
   </si>
   <si>
     <t xml:space="preserve">1.3047901391983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36843836307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39307653903961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35406637191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37254464626312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35919892787933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29041802883148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31505584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26988589763641</t>
+    <t xml:space="preserve">1.36843848228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39307618141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35406613349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37254452705383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35919940471649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2904177904129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380042552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31505608558655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26988613605499</t>
   </si>
   <si>
     <t xml:space="preserve">1.20315825939178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27296602725983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22368967533112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17441368103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10152626037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26064693927765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2298492193222</t>
+    <t xml:space="preserve">1.27296590805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22368979454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17441380023956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10152614116669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26064705848694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22984945774078</t>
   </si>
   <si>
     <t xml:space="preserve">1.25243437290192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28220510482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21958339214325</t>
+    <t xml:space="preserve">1.28220522403717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21958351135254</t>
   </si>
   <si>
     <t xml:space="preserve">1.19494557380676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23395597934723</t>
+    <t xml:space="preserve">1.23395574092865</t>
   </si>
   <si>
     <t xml:space="preserve">1.20110487937927</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">1.16004145145416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18057310581207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20007836818695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20213150978088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22471618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2709127664566</t>
+    <t xml:space="preserve">1.18057322502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20007860660553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20213139057159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22471642494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27091264724731</t>
   </si>
   <si>
     <t xml:space="preserve">1.32224202156067</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">1.29555082321167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26475322246552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27604556083679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144442081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30581641197205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40334224700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37459802627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36022567749023</t>
+    <t xml:space="preserve">1.2647533416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27604568004608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2914445400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3058168888092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40334248542786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37459790706635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36022579669952</t>
   </si>
   <si>
     <t xml:space="preserve">1.33045482635498</t>
@@ -197,28 +197,28 @@
     <t xml:space="preserve">1.29349756240845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27912580966949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29247093200684</t>
+    <t xml:space="preserve">1.27912569046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29247117042542</t>
   </si>
   <si>
     <t xml:space="preserve">1.25756728649139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23600876331329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24935472011566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24114191532135</t>
+    <t xml:space="preserve">1.23600888252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24935448169708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24114167690277</t>
   </si>
   <si>
     <t xml:space="preserve">1.21753025054932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18673276901245</t>
+    <t xml:space="preserve">1.18673288822174</t>
   </si>
   <si>
     <t xml:space="preserve">1.13540351390839</t>
@@ -227,31 +227,31 @@
     <t xml:space="preserve">1.1487489938736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1107656955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17749321460724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1980254650116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2442215681076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2503809928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25654065608978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26270031929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24216854572296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27809906005859</t>
+    <t xml:space="preserve">1.11076557636261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17749345302582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19802534580231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24422168731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25038111209869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2565404176712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26270020008087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24216830730438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27809882164001</t>
   </si>
   <si>
     <t xml:space="preserve">1.23190248012543</t>
@@ -269,265 +269,265 @@
     <t xml:space="preserve">1.16209471225739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13950991630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1425895690918</t>
+    <t xml:space="preserve">1.13951003551483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14258968830109</t>
   </si>
   <si>
     <t xml:space="preserve">1.14977562427521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15798830986023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14566934108734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14156293869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12924408912659</t>
+    <t xml:space="preserve">1.15798842906952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14566957950592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14156305789948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1292439699173</t>
   </si>
   <si>
     <t xml:space="preserve">1.12103128433228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1508024930954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17851996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18775928020477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18666660785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25878429412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28719484806061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29702889919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26097011566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24020874500275</t>
+    <t xml:space="preserve">1.15080225467682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17852008342743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18775916099548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18666672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.258784532547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28719449043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2970290184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26096975803375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24020886421204</t>
   </si>
   <si>
     <t xml:space="preserve">1.23037457466125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20852053165436</t>
+    <t xml:space="preserve">1.20852041244507</t>
   </si>
   <si>
     <t xml:space="preserve">1.20414984226227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22491109371185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2107058763504</t>
+    <t xml:space="preserve">1.22491097450256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21070575714111</t>
   </si>
   <si>
     <t xml:space="preserve">1.19977903366089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15060770511627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08286070823669</t>
+    <t xml:space="preserve">1.15060746669769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0828605890274</t>
   </si>
   <si>
     <t xml:space="preserve">1.04516267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07466542720795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06537759304047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1145486831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14842212200165</t>
+    <t xml:space="preserve">1.07466554641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06537747383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11454892158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14842224121094</t>
   </si>
   <si>
     <t xml:space="preserve">1.17683255672455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17573964595795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23365259170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950644671916962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846838414669037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887268126010895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900380611419678</t>
+    <t xml:space="preserve">1.17573976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23365247249603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950644612312317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846838653087616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88726818561554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900380551815033</t>
   </si>
   <si>
     <t xml:space="preserve">0.929883301258087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917863488197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889999866485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870331645011902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868692517280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874155938625336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961571574211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983425319194794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04789435863495</t>
+    <t xml:space="preserve">0.917863786220551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889999985694885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870331466197968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868692457675934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87415611743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961571335792542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983425498008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04789447784424</t>
   </si>
   <si>
     <t xml:space="preserve">1.03587472438812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05772876739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05499684810638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05718207359314</t>
+    <t xml:space="preserve">1.05772864818573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05499672889709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05718219280243</t>
   </si>
   <si>
     <t xml:space="preserve">1.05062592029572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06373858451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0670166015625</t>
+    <t xml:space="preserve">1.06373834609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06701648235321</t>
   </si>
   <si>
     <t xml:space="preserve">1.06865572929382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04898691177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05335795879364</t>
+    <t xml:space="preserve">1.04898715019226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05335783958435</t>
   </si>
   <si>
     <t xml:space="preserve">1.0719336271286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03969919681549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07630431652069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03860652446747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999269485473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993806123733521</t>
+    <t xml:space="preserve">1.03969931602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07630455493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03860640525818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999269545078278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993805944919586</t>
   </si>
   <si>
     <t xml:space="preserve">0.994352400302887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03806030750275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0511726140976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05608975887299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07958245277405</t>
+    <t xml:space="preserve">1.03806006908417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05117249488831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0560896396637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07958257198334</t>
   </si>
   <si>
     <t xml:space="preserve">1.05827498435974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03041124343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00965011119843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05991399288177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09214854240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08231437206268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10034370422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08996319770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11673414707184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16372001171112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19759356975555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19213008880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1680908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17901766300201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18338859081268</t>
+    <t xml:space="preserve">1.03041136264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00964987277985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05991411209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09214842319489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08231425285339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10034358501434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08996295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11673426628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1637202501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19759368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19212996959686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16809070110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17901790142059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18338847160339</t>
   </si>
   <si>
     <t xml:space="preserve">1.15934932231903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13749539852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13640260696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12766122817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09706556797028</t>
+    <t xml:space="preserve">1.13749527931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1364027261734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12766098976135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09706568717957</t>
   </si>
   <si>
     <t xml:space="preserve">1.11236333847046</t>
@@ -536,67 +536,67 @@
     <t xml:space="preserve">1.12656855583191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09050953388214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07794344425201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06428480148315</t>
+    <t xml:space="preserve">1.09050941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0779435634613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06428492069244</t>
   </si>
   <si>
     <t xml:space="preserve">1.0615531206131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06319200992584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07848978042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05445063114166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08941674232483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09378755092621</t>
+    <t xml:space="preserve">1.06319224834442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07848989963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05445051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08941686153412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0937876701355</t>
   </si>
   <si>
     <t xml:space="preserve">1.07685089111328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08340704441071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12329030036926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13093912601471</t>
+    <t xml:space="preserve">1.08340716362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12329018115997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.130939245224</t>
   </si>
   <si>
     <t xml:space="preserve">1.15170037746429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15388584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1779248714447</t>
+    <t xml:space="preserve">1.15388596057892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17792499065399</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196437835693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18229591846466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15279316902161</t>
+    <t xml:space="preserve">1.18229603767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15279293060303</t>
   </si>
   <si>
     <t xml:space="preserve">1.13858819007874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09925103187561</t>
+    <t xml:space="preserve">1.09925127029419</t>
   </si>
   <si>
     <t xml:space="preserve">1.09597301483154</t>
@@ -605,34 +605,34 @@
     <t xml:space="preserve">1.16044187545776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16918349266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22054004669189</t>
+    <t xml:space="preserve">1.16918361186981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22054016590118</t>
   </si>
   <si>
     <t xml:space="preserve">1.21835482120514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15497875213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14186632633209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11891961097717</t>
+    <t xml:space="preserve">1.15497851371765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1418662071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11891973018646</t>
   </si>
   <si>
     <t xml:space="preserve">1.10362184047699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06810939311981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11345624923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14514422416687</t>
+    <t xml:space="preserve">1.06810915470123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11345613002777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14514410495758</t>
   </si>
   <si>
     <t xml:space="preserve">1.24567210674286</t>
@@ -641,79 +641,79 @@
     <t xml:space="preserve">1.26643335819244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30904841423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27845311164856</t>
+    <t xml:space="preserve">1.30904853343964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27845299243927</t>
   </si>
   <si>
     <t xml:space="preserve">1.32762432098389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29265797138214</t>
+    <t xml:space="preserve">1.29265785217285</t>
   </si>
   <si>
     <t xml:space="preserve">1.33636593818665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31888270378113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33745884895325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33855128288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34401476383209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964383602142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871675491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3177901506424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32543873786926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36805391311646</t>
+    <t xml:space="preserve">1.31888294219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33745837211609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855140209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34401488304138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964419364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871699333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31778991222382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32543909549713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36805403232574</t>
   </si>
   <si>
     <t xml:space="preserve">1.38772237300873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39755690097809</t>
+    <t xml:space="preserve">1.39755666255951</t>
   </si>
   <si>
     <t xml:space="preserve">1.38990807533264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35275614261627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3483852148056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34619998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34729290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32216084003448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34292197227478</t>
+    <t xml:space="preserve">1.35275626182556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34838545322418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34620022773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34729266166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3221607208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34292185306549</t>
   </si>
   <si>
     <t xml:space="preserve">1.3494781255722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31014120578766</t>
+    <t xml:space="preserve">1.31014132499695</t>
   </si>
   <si>
     <t xml:space="preserve">1.25222849845886</t>
@@ -725,25 +725,25 @@
     <t xml:space="preserve">1.22928178310394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23911607265472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2008718252182</t>
+    <t xml:space="preserve">1.23911595344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20087170600891</t>
   </si>
   <si>
     <t xml:space="preserve">1.18557405471802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19103753566742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22272539138794</t>
+    <t xml:space="preserve">1.19103765487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22272551059723</t>
   </si>
   <si>
     <t xml:space="preserve">1.19322276115417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17027640342712</t>
+    <t xml:space="preserve">1.17027604579926</t>
   </si>
   <si>
     <t xml:space="preserve">1.1735543012619</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">1.19650101661682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18120312690735</t>
+    <t xml:space="preserve">1.18120300769806</t>
   </si>
   <si>
     <t xml:space="preserve">1.13421738147736</t>
@@ -773,28 +773,28 @@
     <t xml:space="preserve">1.26861870288849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27189683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27408242225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30577039718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34182918071747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32325375080109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35057079792023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35603427886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36914682388306</t>
+    <t xml:space="preserve">1.27189695835114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27408218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30577051639557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34182941913605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3232536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35057067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35603451728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36914658546448</t>
   </si>
   <si>
     <t xml:space="preserve">1.39100050926208</t>
@@ -806,103 +806,103 @@
     <t xml:space="preserve">1.38335180282593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3767956495285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38007354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37898075580597</t>
+    <t xml:space="preserve">1.37679553031921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38007378578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37898099422455</t>
   </si>
   <si>
     <t xml:space="preserve">1.37461018562317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36696171760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384881496429</t>
+    <t xml:space="preserve">1.36696135997772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384905338287</t>
   </si>
   <si>
     <t xml:space="preserve">1.33199501037598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30467772483826</t>
+    <t xml:space="preserve">1.30467784404755</t>
   </si>
   <si>
     <t xml:space="preserve">1.35166347026825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36040532588959</t>
+    <t xml:space="preserve">1.36040508747101</t>
   </si>
   <si>
     <t xml:space="preserve">1.37351751327515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47623062133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50573372840881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49480664730072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45984029769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.460932970047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46311831474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47076761722565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50791895389557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5527195930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55818271636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55599749088287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55709004402161</t>
+    <t xml:space="preserve">1.47623085975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50573360919952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49480652809143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45984041690826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46093285083771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46311843395233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47076737880707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5079185962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55271947383881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5581830739975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55599796772003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55709028244019</t>
   </si>
   <si>
     <t xml:space="preserve">1.5472559928894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54507076740265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55162644386292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52868032455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52212417125702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52977287769318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56594610214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57061374187469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56711292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55427718162537</t>
+    <t xml:space="preserve">1.54507064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55162692070007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52868020534515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52212405204773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52977275848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56594586372375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57061362266541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56711280345917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55427730083466</t>
   </si>
   <si>
     <t xml:space="preserve">1.5297726392746</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">1.49826717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48893225193024</t>
+    <t xml:space="preserve">1.48893213272095</t>
   </si>
   <si>
     <t xml:space="preserve">1.4865984916687</t>
@@ -920,37 +920,37 @@
     <t xml:space="preserve">1.50060105323792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51110291481018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49126601219177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48426485061646</t>
+    <t xml:space="preserve">1.51110303401947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49126625061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48426496982574</t>
   </si>
   <si>
     <t xml:space="preserve">1.4994341135025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50876939296722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50176787376404</t>
+    <t xml:space="preserve">1.50876903533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50176799297333</t>
   </si>
   <si>
     <t xml:space="preserve">1.50410187244415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49710011482239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47843062877655</t>
+    <t xml:space="preserve">1.49710035324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47843039035797</t>
   </si>
   <si>
     <t xml:space="preserve">1.51460373401642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52510559558868</t>
+    <t xml:space="preserve">1.5251053571701</t>
   </si>
   <si>
     <t xml:space="preserve">1.52627229690552</t>
@@ -962,208 +962,208 @@
     <t xml:space="preserve">1.60795366764069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64062595367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61845552921295</t>
+    <t xml:space="preserve">1.64062583446503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61845541000366</t>
   </si>
   <si>
     <t xml:space="preserve">1.61962223052979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66279649734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65929579734802</t>
+    <t xml:space="preserve">1.66279673576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65929615497589</t>
   </si>
   <si>
     <t xml:space="preserve">1.6721316576004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65696203708649</t>
+    <t xml:space="preserve">1.65696227550507</t>
   </si>
   <si>
     <t xml:space="preserve">1.66863095760345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65346169471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66162979602814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66396343708038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67096495628357</t>
+    <t xml:space="preserve">1.6534618139267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66163003444672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66396355628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67096471786499</t>
   </si>
   <si>
     <t xml:space="preserve">1.67446517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66629707813263</t>
+    <t xml:space="preserve">1.6662974357605</t>
   </si>
   <si>
     <t xml:space="preserve">1.67329859733582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68380010128021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69313538074493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69546937942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69430208206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69896972179413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70130336284637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69196844100952</t>
+    <t xml:space="preserve">1.68380033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69313502311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69546890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69430255889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69896960258484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70130360126495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69196856021881</t>
   </si>
   <si>
     <t xml:space="preserve">1.70363736152649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70830476284027</t>
+    <t xml:space="preserve">1.70830464363098</t>
   </si>
   <si>
     <t xml:space="preserve">1.70480406284332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68263363838196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6779659986496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66046297550201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70713806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68963468074799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64296007156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65462851524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65812933444977</t>
+    <t xml:space="preserve">1.68263351917267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67796623706818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66046273708344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70713782310486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68963479995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64295947551727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65462839603424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65812921524048</t>
   </si>
   <si>
     <t xml:space="preserve">1.63712513446808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66513049602509</t>
+    <t xml:space="preserve">1.6651303768158</t>
   </si>
   <si>
     <t xml:space="preserve">1.68146646022797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70013654232025</t>
+    <t xml:space="preserve">1.70013678073883</t>
   </si>
   <si>
     <t xml:space="preserve">1.71063852310181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71763980388641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73280906677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73397564888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7246413230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73514306545258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74214422702789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74564456939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74681162834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74097716808319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71180534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71530592441559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7094714641571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68496704101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66746413707733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68029987812042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597100257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6791330575943</t>
+    <t xml:space="preserve">1.71763968467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73280930519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73397588729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72464120388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.735142827034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447798728943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74214398860931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74564468860626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74681174755096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7409770488739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71180522441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71530604362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70947158336639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6849672794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66746401786804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68029975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597088336945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67913293838501</t>
   </si>
   <si>
     <t xml:space="preserve">1.65112793445587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63362491130829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63479149341583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61728858947754</t>
+    <t xml:space="preserve">1.633624792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63479161262512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61728847026825</t>
   </si>
   <si>
     <t xml:space="preserve">1.61495471000671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64412665367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61378800868988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64529371261597</t>
+    <t xml:space="preserve">1.64412653446198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61378788948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6452933549881</t>
   </si>
   <si>
     <t xml:space="preserve">1.64646065235138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67563199996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63829207420349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62895727157593</t>
+    <t xml:space="preserve">1.67563223838806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63829231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62895703315735</t>
   </si>
   <si>
     <t xml:space="preserve">1.62662363052368</t>
@@ -1172,34 +1172,34 @@
     <t xml:space="preserve">1.62779021263123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61612176895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60678648948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60445296764374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74331068992615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76548147201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77248311042786</t>
+    <t xml:space="preserve">1.61612164974213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6067863702774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60445284843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74331104755402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76548182964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77248275279999</t>
   </si>
   <si>
     <t xml:space="preserve">1.77598345279694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78415155410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8051552772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80165469646454</t>
+    <t xml:space="preserve">1.78415167331696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80515539646149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80165505409241</t>
   </si>
   <si>
     <t xml:space="preserve">1.82382500171661</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">1.84366238117218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85824835300446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83549392223358</t>
+    <t xml:space="preserve">1.85824823379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83549404144287</t>
   </si>
   <si>
     <t xml:space="preserve">1.84395408630371</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">1.83111822605133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81769931316376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902899265289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81098985671997</t>
+    <t xml:space="preserve">1.81769943237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902911186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81098961830139</t>
   </si>
   <si>
     <t xml:space="preserve">1.87283420562744</t>
@@ -1244,79 +1244,79 @@
     <t xml:space="preserve">1.83636939525604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81157314777374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377830028534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8092395067215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80690550804138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8305344581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81303179264069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8022381067276</t>
+    <t xml:space="preserve">1.81157302856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377853870392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923938751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8069052696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83053505420685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81303191184998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223834514618</t>
   </si>
   <si>
     <t xml:space="preserve">1.80748915672302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78444361686707</t>
+    <t xml:space="preserve">1.78444337844849</t>
   </si>
   <si>
     <t xml:space="preserve">1.79873752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79990458488464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80982303619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80632209777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79290330410004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75410437583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72930824756622</t>
+    <t xml:space="preserve">1.79990434646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80982279777527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8063223361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79290318489075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75410461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72930812835693</t>
   </si>
   <si>
     <t xml:space="preserve">1.74535286426544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76518976688385</t>
+    <t xml:space="preserve">1.76519000530243</t>
   </si>
   <si>
     <t xml:space="preserve">1.77510857582092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78035950660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540028095245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7488534450531</t>
+    <t xml:space="preserve">1.78035938739777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74885392189026</t>
   </si>
   <si>
     <t xml:space="preserve">1.76081418991089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7952367067337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77364945411682</t>
+    <t xml:space="preserve">1.79523682594299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77364957332611</t>
   </si>
   <si>
     <t xml:space="preserve">1.78473484516144</t>
@@ -1325,22 +1325,22 @@
     <t xml:space="preserve">1.77423298358917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74272751808167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72259902954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70742964744568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72289097309113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72318267822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72522413730621</t>
+    <t xml:space="preserve">1.74272775650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72259914875031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7074294090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72289061546326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72318255901337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7252242565155</t>
   </si>
   <si>
     <t xml:space="preserve">1.71909821033478</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">1.75206255912781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74768698215485</t>
+    <t xml:space="preserve">1.74768674373627</t>
   </si>
   <si>
     <t xml:space="preserve">1.76256430149078</t>
@@ -1358,76 +1358,76 @@
     <t xml:space="preserve">1.77131605148315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75906383991241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77948403358459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7894024848938</t>
+    <t xml:space="preserve">1.75906407833099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77948391437531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78940260410309</t>
   </si>
   <si>
     <t xml:space="preserve">1.79465341567993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81449043750763</t>
+    <t xml:space="preserve">1.81449031829834</t>
   </si>
   <si>
     <t xml:space="preserve">1.8153657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82907652854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84832990169525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86437451839447</t>
+    <t xml:space="preserve">1.8290764093399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84832954406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86437404155731</t>
   </si>
   <si>
     <t xml:space="preserve">1.83986985683441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85124695301056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83957827091217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84191203117371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8486213684082</t>
+    <t xml:space="preserve">1.85124683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83957839012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84191191196442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84862148761749</t>
   </si>
   <si>
     <t xml:space="preserve">1.83811962604523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84453737735748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83403551578522</t>
+    <t xml:space="preserve">1.84453725814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83403587341309</t>
   </si>
   <si>
     <t xml:space="preserve">1.82674241065979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83782815933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85416424274445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80865573883057</t>
+    <t xml:space="preserve">1.83782804012299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85416376590729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80865633487701</t>
   </si>
   <si>
     <t xml:space="preserve">1.79436182975769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75031244754791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73967409133911</t>
+    <t xml:space="preserve">1.75031197071075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73967373371124</t>
   </si>
   <si>
     <t xml:space="preserve">1.75156378746033</t>
@@ -1436,169 +1436,169 @@
     <t xml:space="preserve">1.72090041637421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70494329929352</t>
+    <t xml:space="preserve">1.70494318008423</t>
   </si>
   <si>
     <t xml:space="preserve">1.65081286430359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59730839729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53191459178925</t>
+    <t xml:space="preserve">1.59730875492096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53191411495209</t>
   </si>
   <si>
     <t xml:space="preserve">1.57759618759155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57352888584137</t>
+    <t xml:space="preserve">1.57352864742279</t>
   </si>
   <si>
     <t xml:space="preserve">1.62546861171722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62515592575073</t>
+    <t xml:space="preserve">1.62515568733215</t>
   </si>
   <si>
     <t xml:space="preserve">1.56289041042328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55475533008575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53629446029663</t>
+    <t xml:space="preserve">1.55475497245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53629457950592</t>
   </si>
   <si>
     <t xml:space="preserve">1.51752126216888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6182724237442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62578165531158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6232784986496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59417939186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59793436527252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6057562828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63548123836517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6032532453537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61952376365662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56695806980133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55068755149841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5269079208374</t>
+    <t xml:space="preserve">1.61827206611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6173335313797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62578141689301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62327837944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59417974948883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59793424606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60575664043427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63548135757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60325360298157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61952364444733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56695818901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5506876707077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690815925598</t>
   </si>
   <si>
     <t xml:space="preserve">1.55694544315338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55600678920746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54474306106567</t>
+    <t xml:space="preserve">1.55600702762604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54474258422852</t>
   </si>
   <si>
     <t xml:space="preserve">1.57634484767914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5841668844223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6051310300827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60294044017792</t>
+    <t xml:space="preserve">1.58416712284088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60513091087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6029406785965</t>
   </si>
   <si>
     <t xml:space="preserve">1.60606944561005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58041226863861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54881036281586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53066277503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5397367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53660762310028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5519392490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54161405563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51658260822296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50531852245331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250256061554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53097558021545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55037474632263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57039988040924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58322834968567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64830982685089</t>
+    <t xml:space="preserve">1.58041262626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54881024360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53066265583038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973662853241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53660750389099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55193936824799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54161381721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51658272743225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5053186416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53097569942474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55037462711334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57039999961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58322858810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6483097076416</t>
   </si>
   <si>
     <t xml:space="preserve">1.57259011268616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51188933849335</t>
+    <t xml:space="preserve">1.51188945770264</t>
   </si>
   <si>
     <t xml:space="preserve">1.53003704547882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50844764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49249005317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43804693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41426753997803</t>
+    <t xml:space="preserve">1.50844752788544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49248993396759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43804717063904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41426730155945</t>
   </si>
   <si>
     <t xml:space="preserve">1.40175151824951</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">1.37640762329102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36576914787292</t>
+    <t xml:space="preserve">1.36576926708221</t>
   </si>
   <si>
     <t xml:space="preserve">1.35732102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40331614017487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38329112529755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3767204284668</t>
+    <t xml:space="preserve">1.40331625938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38329100608826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37672030925751</t>
   </si>
   <si>
     <t xml:space="preserve">1.37891066074371</t>
@@ -1628,64 +1628,64 @@
     <t xml:space="preserve">1.37859773635864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36357879638672</t>
+    <t xml:space="preserve">1.36357867717743</t>
   </si>
   <si>
     <t xml:space="preserve">1.38172650337219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34918570518494</t>
+    <t xml:space="preserve">1.34918594360352</t>
   </si>
   <si>
     <t xml:space="preserve">1.3313512802124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35857272148132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897307872772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45901083946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43929851055145</t>
+    <t xml:space="preserve">1.35857284069061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4590106010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43929874897003</t>
   </si>
   <si>
     <t xml:space="preserve">1.41583156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47997450828552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45650744438171</t>
+    <t xml:space="preserve">1.47997426986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45650768280029</t>
   </si>
   <si>
     <t xml:space="preserve">1.46432971954346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45744645595551</t>
+    <t xml:space="preserve">1.45744633674622</t>
   </si>
   <si>
     <t xml:space="preserve">1.46683311462402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50093805789948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49906098842621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51908576488495</t>
+    <t xml:space="preserve">1.50093793869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49906086921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51908564567566</t>
   </si>
   <si>
     <t xml:space="preserve">1.51157629489899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53222727775574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49999952316284</t>
+    <t xml:space="preserve">1.53222715854645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49999964237213</t>
   </si>
   <si>
     <t xml:space="preserve">1.54568147659302</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">1.52221465110779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50437998771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37734627723694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32352888584137</t>
+    <t xml:space="preserve">1.50438010692596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37734603881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32352876663208</t>
   </si>
   <si>
     <t xml:space="preserve">1.31914842128754</t>
@@ -1709,82 +1709,82 @@
     <t xml:space="preserve">1.32634472846985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35481822490692</t>
+    <t xml:space="preserve">1.35481798648834</t>
   </si>
   <si>
     <t xml:space="preserve">1.31320345401764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27033746242523</t>
+    <t xml:space="preserve">1.27033734321594</t>
   </si>
   <si>
     <t xml:space="preserve">1.29818487167358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30506825447083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27284038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26783442497253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27753400802612</t>
+    <t xml:space="preserve">1.30506801605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27284061908722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26783418655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27753376960754</t>
   </si>
   <si>
     <t xml:space="preserve">1.29536867141724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28066277503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23842239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24167680740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23128855228424</t>
+    <t xml:space="preserve">1.28066265583038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2384227514267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24167668819427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23128867149353</t>
   </si>
   <si>
     <t xml:space="preserve">1.23166394233704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18936145305634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22227740287781</t>
+    <t xml:space="preserve">1.18936121463776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22227728366852</t>
   </si>
   <si>
     <t xml:space="preserve">1.21264040470123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24943649768829</t>
+    <t xml:space="preserve">1.249436378479</t>
   </si>
   <si>
     <t xml:space="preserve">1.24655771255493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22215235233307</t>
+    <t xml:space="preserve">1.22215211391449</t>
   </si>
   <si>
     <t xml:space="preserve">1.24267792701721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25563156604767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2366703748703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25250256061554</t>
+    <t xml:space="preserve">1.25563168525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23667025566101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25250267982483</t>
   </si>
   <si>
     <t xml:space="preserve">1.28598201274872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26971161365509</t>
+    <t xml:space="preserve">1.26971185207367</t>
   </si>
   <si>
     <t xml:space="preserve">1.25500583648682</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">1.25312840938568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23829734325409</t>
+    <t xml:space="preserve">1.23829758167267</t>
   </si>
   <si>
     <t xml:space="preserve">1.2226527929306</t>
@@ -1805,88 +1805,88 @@
     <t xml:space="preserve">1.20112586021423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20538115501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17571926116943</t>
+    <t xml:space="preserve">1.20538127422333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17571914196014</t>
   </si>
   <si>
     <t xml:space="preserve">1.20901083946228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20888566970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22165167331696</t>
+    <t xml:space="preserve">1.20888543128967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22165143489838</t>
   </si>
   <si>
     <t xml:space="preserve">1.27690815925598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27628242969513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28535604476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2719019651413</t>
+    <t xml:space="preserve">1.27628254890442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28535616397858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27190184593201</t>
   </si>
   <si>
     <t xml:space="preserve">1.28160166740417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32196426391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29161405563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3019392490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23491823673248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24029994010925</t>
+    <t xml:space="preserve">1.32196438312531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29161393642426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30193936824799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23491811752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24029970169067</t>
   </si>
   <si>
     <t xml:space="preserve">1.21376669406891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21026229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25969922542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27158904075623</t>
+    <t xml:space="preserve">1.21026241779327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25969910621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27158915996552</t>
   </si>
   <si>
     <t xml:space="preserve">1.26032471656799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23466789722443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2421772480011</t>
+    <t xml:space="preserve">1.23466777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24217736721039</t>
   </si>
   <si>
     <t xml:space="preserve">1.26345384120941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21714603900909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19662022590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19461798667908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21389210224152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.192990899086</t>
+    <t xml:space="preserve">1.2171459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19662034511566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1946177482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21389186382294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19299066066742</t>
   </si>
   <si>
     <t xml:space="preserve">1.18986189365387</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">1.25106346607208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27221465110779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2575089931488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26470530033112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25844740867615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24017477035522</t>
+    <t xml:space="preserve">1.27221488952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25750875473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26470518112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25844752788544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24017465114594</t>
   </si>
   <si>
     <t xml:space="preserve">1.22465538978577</t>
@@ -1925,43 +1925,43 @@
     <t xml:space="preserve">1.26814723014832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26908600330353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29192709922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28003692626953</t>
+    <t xml:space="preserve">1.26908576488495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29192674160004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28003716468811</t>
   </si>
   <si>
     <t xml:space="preserve">1.28191435337067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2897367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24830996990204</t>
+    <t xml:space="preserve">1.28973698616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24830985069275</t>
   </si>
   <si>
     <t xml:space="preserve">1.22815978527069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22753381729126</t>
+    <t xml:space="preserve">1.22753369808197</t>
   </si>
   <si>
     <t xml:space="preserve">1.24705827236176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24180173873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2361695766449</t>
+    <t xml:space="preserve">1.24180197715759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23616969585419</t>
   </si>
   <si>
     <t xml:space="preserve">1.25131368637085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2553186416626</t>
+    <t xml:space="preserve">1.25531888008118</t>
   </si>
   <si>
     <t xml:space="preserve">1.24155139923096</t>
@@ -1970,55 +1970,55 @@
     <t xml:space="preserve">1.28097569942474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29223990440369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2862948179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28692054748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27659523487091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27784669399261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30444264411926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29943633079529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33385443687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35043740272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513091087341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35262787342072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36545634269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33510589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32603180408478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33760905265808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33667016029358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34824740886688</t>
+    <t xml:space="preserve">1.29223966598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28629493713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28692066669464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2765953540802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2778468132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30444276332855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.299436211586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33385419845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35043752193451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513067245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35262775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36545622348785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33510613441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32603192329407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33760893344879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33667004108429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34824728965759</t>
   </si>
   <si>
     <t xml:space="preserve">1.35794711112976</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">1.39737129211426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39924848079681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39549374580383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38610696792603</t>
+    <t xml:space="preserve">1.3992486000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39549386501312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38610708713531</t>
   </si>
   <si>
     <t xml:space="preserve">1.34949886798859</t>
@@ -2045,10 +2045,10 @@
     <t xml:space="preserve">1.34480535984039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34136378765106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35168921947479</t>
+    <t xml:space="preserve">1.34136390686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35168933868408</t>
   </si>
   <si>
     <t xml:space="preserve">1.35419225692749</t>
@@ -2057,13 +2057,13 @@
     <t xml:space="preserve">1.38016211986542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37546873092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38767158985138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39799678325653</t>
+    <t xml:space="preserve">1.3754688501358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38767147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39799690246582</t>
   </si>
   <si>
     <t xml:space="preserve">1.39956140518188</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">1.39017474651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39830982685089</t>
+    <t xml:space="preserve">1.3983097076416</t>
   </si>
   <si>
     <t xml:space="preserve">1.4399242401123</t>
@@ -2081,40 +2081,40 @@
     <t xml:space="preserve">1.45337867736816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46558141708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45963656902313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45243990421295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42365407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42490553855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42991209030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45932364463806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46245276927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45619475841522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4530656337738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43272805213928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40300333499908</t>
+    <t xml:space="preserve">1.46558129787445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45963668823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45244002342224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42365396022797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42490577697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42991173267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45932352542877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46245229244232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45619463920593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45306575298309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4327278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40300309658051</t>
   </si>
   <si>
     <t xml:space="preserve">1.38673281669617</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">1.35450518131256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35137617588043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32540643215179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34543120861053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36639487743378</t>
+    <t xml:space="preserve">1.35137629508972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32540619373322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34543144702911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36639499664307</t>
   </si>
   <si>
     <t xml:space="preserve">1.35825979709625</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">1.33630466461182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30973827838898</t>
+    <t xml:space="preserve">1.3097380399704</t>
   </si>
   <si>
     <t xml:space="preserve">1.32061266899109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31331717967987</t>
+    <t xml:space="preserve">1.31331729888916</t>
   </si>
   <si>
     <t xml:space="preserve">1.29872632026672</t>
@@ -2162,88 +2162,88 @@
     <t xml:space="preserve">1.28413546085358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28372240066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26211130619049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25674295425415</t>
+    <t xml:space="preserve">1.28372251987457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26211142539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25674307346344</t>
   </si>
   <si>
     <t xml:space="preserve">1.28441071510315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27326095104218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25701832771301</t>
+    <t xml:space="preserve">1.27326118946075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2570184469223</t>
   </si>
   <si>
     <t xml:space="preserve">1.26142311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27037048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133393287659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25811958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2677549123764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2645890712738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26018440723419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28936588764191</t>
+    <t xml:space="preserve">1.27037024497986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133405208588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2581193447113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26775503158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26458895206451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26018416881561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2893660068512</t>
   </si>
   <si>
     <t xml:space="preserve">1.312628865242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30134165287018</t>
+    <t xml:space="preserve">1.30134153366089</t>
   </si>
   <si>
     <t xml:space="preserve">1.29046726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29032945632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28592467308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29239439964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2929447889328</t>
+    <t xml:space="preserve">1.29032957553864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28592479228973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29239428043365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29294502735138</t>
   </si>
   <si>
     <t xml:space="preserve">1.29528498649597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2853741645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29734981060028</t>
+    <t xml:space="preserve">1.28537392616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2973495721817</t>
   </si>
   <si>
     <t xml:space="preserve">1.36328399181366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39439284801483</t>
+    <t xml:space="preserve">1.39439272880554</t>
   </si>
   <si>
     <t xml:space="preserve">1.39852249622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38854253292084</t>
+    <t xml:space="preserve">1.38854277133942</t>
   </si>
   <si>
     <t xml:space="preserve">1.38097202777863</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">1.39783406257629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41469621658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41159904003143</t>
+    <t xml:space="preserve">1.41469633579254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41159915924072</t>
   </si>
   <si>
     <t xml:space="preserve">1.40987861156464</t>
@@ -2270,151 +2270,151 @@
     <t xml:space="preserve">1.41091084480286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38200414180756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38441300392151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40058708190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39026343822479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38338088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37044179439545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3530980348587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34924376010895</t>
+    <t xml:space="preserve">1.38200426101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3844131231308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40058720111847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3902633190155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38338077068329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37044167518616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35309791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34924364089966</t>
   </si>
   <si>
     <t xml:space="preserve">1.37649834156036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34387540817261</t>
+    <t xml:space="preserve">1.34387528896332</t>
   </si>
   <si>
     <t xml:space="preserve">1.35433673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33836948871613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31455588340759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33891999721527</t>
+    <t xml:space="preserve">1.33836936950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31455600261688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33891987800598</t>
   </si>
   <si>
     <t xml:space="preserve">1.26362562179565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29886400699615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27023267745972</t>
+    <t xml:space="preserve">1.29886376857758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27023279666901</t>
   </si>
   <si>
     <t xml:space="preserve">1.31744658946991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31001341342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32322788238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33644247055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30987584590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33520352840424</t>
+    <t xml:space="preserve">1.31001365184784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32322776317596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33644223213196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30987572669983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33520364761353</t>
   </si>
   <si>
     <t xml:space="preserve">1.34084713459015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35488736629486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38578987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37181854248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37890720367432</t>
+    <t xml:space="preserve">1.35488748550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38578963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3718181848526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37890732288361</t>
   </si>
   <si>
     <t xml:space="preserve">1.37684237957001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39542520046234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41504013538361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42261111736298</t>
+    <t xml:space="preserve">1.39542508125305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41504049301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42261123657227</t>
   </si>
   <si>
     <t xml:space="preserve">1.44635570049286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46149718761444</t>
+    <t xml:space="preserve">1.46149706840515</t>
   </si>
   <si>
     <t xml:space="preserve">1.45082926750183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46080899238586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50175988674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47526216506958</t>
+    <t xml:space="preserve">1.46080887317657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50175964832306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47526228427887</t>
   </si>
   <si>
     <t xml:space="preserve">1.46252954006195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46321773529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48937129974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49074769020081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319757938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4659708738327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46941208839417</t>
+    <t xml:space="preserve">1.46321749687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48937141895294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49074757099152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319746017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46597111225128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46941196918488</t>
   </si>
   <si>
     <t xml:space="preserve">1.47491800785065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48696219921112</t>
+    <t xml:space="preserve">1.48696231842041</t>
   </si>
   <si>
     <t xml:space="preserve">1.49728608131409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48317694664001</t>
+    <t xml:space="preserve">1.48317718505859</t>
   </si>
   <si>
     <t xml:space="preserve">1.44119393825531</t>
@@ -2423,31 +2423,31 @@
     <t xml:space="preserve">1.439129114151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44222617149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43568778038025</t>
+    <t xml:space="preserve">1.44222629070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43568789958954</t>
   </si>
   <si>
     <t xml:space="preserve">1.4477322101593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47939169406891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50451290607452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50038349628448</t>
+    <t xml:space="preserve">1.47939157485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50451278686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50038325786591</t>
   </si>
   <si>
     <t xml:space="preserve">1.52103078365326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5406459569931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53582811355591</t>
+    <t xml:space="preserve">1.54064583778381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53582799434662</t>
   </si>
   <si>
     <t xml:space="preserve">1.53789281845093</t>
@@ -2462,58 +2462,58 @@
     <t xml:space="preserve">1.56232583522797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56301403045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56404614448547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56817591190338</t>
+    <t xml:space="preserve">1.56301379203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56404638290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56817579269409</t>
   </si>
   <si>
     <t xml:space="preserve">1.56370222568512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54752850532532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54580795764923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56439030170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58710277080536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61050307750702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60878252983093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62151539325714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256790161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62220346927643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63665652275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61394429206848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60086739063263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60912656784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61738562583923</t>
+    <t xml:space="preserve">1.54752838611603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54580783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5643904209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58710253238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61050283908844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60878241062164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62151503562927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256802082062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62220370769501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63665664196014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61394441127777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60086750984192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60912668704987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61738574504852</t>
   </si>
   <si>
     <t xml:space="preserve">1.61566507816315</t>
@@ -2522,52 +2522,52 @@
     <t xml:space="preserve">1.62013876438141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61291193962097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61910605430603</t>
+    <t xml:space="preserve">1.61291182041168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61910617351532</t>
   </si>
   <si>
     <t xml:space="preserve">1.61187958717346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60189998149872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58985555171967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58331704139709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54511952400208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57677900791168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57471442222595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59226453304291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58090829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58572590351105</t>
+    <t xml:space="preserve">1.6019002199173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58985567092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58331751823425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54511940479279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57677888870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57471418380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5922646522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58090817928314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58572614192963</t>
   </si>
   <si>
     <t xml:space="preserve">1.59054386615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60224413871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61497664451599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6263325214386</t>
+    <t xml:space="preserve">1.60224425792694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61497676372528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62633275985718</t>
   </si>
   <si>
     <t xml:space="preserve">1.6283974647522</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">1.63803327083588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65523910522461</t>
+    <t xml:space="preserve">1.65523934364319</t>
   </si>
   <si>
     <t xml:space="preserve">1.65214240550995</t>
@@ -2588,67 +2588,67 @@
     <t xml:space="preserve">1.61635315418243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63872134685516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61704134941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63390374183655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61119151115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61532080173492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59673810005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59845876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60809409618378</t>
+    <t xml:space="preserve">1.63872122764587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6170414686203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63390362262726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61119139194489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61532092094421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59673798084259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59845852851868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60809433460236</t>
   </si>
   <si>
     <t xml:space="preserve">1.59570574760437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56920802593231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56094920635223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56783163547516</t>
+    <t xml:space="preserve">1.5692081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56094896793365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56783187389374</t>
   </si>
   <si>
     <t xml:space="preserve">1.55200207233429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58675873279572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57712316513062</t>
+    <t xml:space="preserve">1.58675825595856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57712304592133</t>
   </si>
   <si>
     <t xml:space="preserve">1.54546368122101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57264959812164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61841797828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68586647510529</t>
+    <t xml:space="preserve">1.57264935970306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61841773986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.685866355896</t>
   </si>
   <si>
     <t xml:space="preserve">1.70100772380829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70410490036011</t>
+    <t xml:space="preserve">1.7041050195694</t>
   </si>
   <si>
     <t xml:space="preserve">1.69240486621857</t>
@@ -2657,88 +2657,88 @@
     <t xml:space="preserve">1.70857858657837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72578477859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72750544548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74815285205841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78944802284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79185652732849</t>
+    <t xml:space="preserve">1.72578489780426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72750532627106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74815309047699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78944778442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79185676574707</t>
   </si>
   <si>
     <t xml:space="preserve">1.7550356388092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73542034626007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63562428951263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60362064838409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57505834102631</t>
+    <t xml:space="preserve">1.73542046546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63562417030334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60362076759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5750584602356</t>
   </si>
   <si>
     <t xml:space="preserve">1.51311564445496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4704442024231</t>
+    <t xml:space="preserve">1.47044432163239</t>
   </si>
   <si>
     <t xml:space="preserve">1.45839989185333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46425044536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4085019826889</t>
+    <t xml:space="preserve">1.46425020694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40850186347961</t>
   </si>
   <si>
     <t xml:space="preserve">1.36080622673035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20443606376648</t>
+    <t xml:space="preserve">1.20443594455719</t>
   </si>
   <si>
     <t xml:space="preserve">1.17608022689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22453308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00677108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06981468200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965475976467133</t>
+    <t xml:space="preserve">1.22453284263611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00677096843719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06981456279755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965476095676422</t>
   </si>
   <si>
     <t xml:space="preserve">0.998924851417542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969467997550964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980892777442932</t>
+    <t xml:space="preserve">0.96946781873703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980892837047577</t>
   </si>
   <si>
     <t xml:space="preserve">1.00856029987335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997135519981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08991134166718</t>
+    <t xml:space="preserve">0.997135400772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08991158008575</t>
   </si>
   <si>
     <t xml:space="preserve">1.11234843730927</t>
@@ -2747,133 +2747,133 @@
     <t xml:space="preserve">1.12253439426422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07821130752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01227700710297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02439022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987499952316284</t>
+    <t xml:space="preserve">1.07821118831635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01227712631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02438986301422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987500071525574</t>
   </si>
   <si>
     <t xml:space="preserve">0.989564716815948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914820909500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00360488891602</t>
+    <t xml:space="preserve">0.914820849895477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00360465049744</t>
   </si>
   <si>
     <t xml:space="preserve">1.01103794574738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997410774230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99452018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967816054821014</t>
+    <t xml:space="preserve">0.997410714626312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99452006816864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967816174030304</t>
   </si>
   <si>
     <t xml:space="preserve">0.928035199642181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.936156511306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947168588638306</t>
+    <t xml:space="preserve">0.936156630516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947168469429016</t>
   </si>
   <si>
     <t xml:space="preserve">0.951848685741425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908488988876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92101514339447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952812314033508</t>
+    <t xml:space="preserve">0.908488929271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921015024185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952812194824219</t>
   </si>
   <si>
     <t xml:space="preserve">0.924869179725647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960245132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99603408575058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01888394355774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979378700256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947031021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998649656772614</t>
+    <t xml:space="preserve">0.960245370864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996034264564514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01888406276703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979378461837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947030961513519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998649597167969</t>
   </si>
   <si>
     <t xml:space="preserve">0.97745156288147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966577053070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973184466362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97001838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977864444255829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959144115447998</t>
+    <t xml:space="preserve">0.966577112674713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973184525966644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970018446445465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977864384651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959143996238708</t>
   </si>
   <si>
     <t xml:space="preserve">0.952261507511139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952399253845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999475657939911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984746932983398</t>
+    <t xml:space="preserve">0.952399075031281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999475598335266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984746754169464</t>
   </si>
   <si>
     <t xml:space="preserve">0.990390717983246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978690326213837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994244873523712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00319218635559</t>
+    <t xml:space="preserve">0.978690266609192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994244694709778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00319194793701</t>
   </si>
   <si>
     <t xml:space="preserve">1.0331996679306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05880272388458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07270503044128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06843793392181</t>
+    <t xml:space="preserve">1.05880260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07270514965057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0684380531311</t>
   </si>
   <si>
     <t xml:space="preserve">1.08743369579315</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">1.11840498447418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15157866477966</t>
+    <t xml:space="preserve">1.15157854557037</t>
   </si>
   <si>
     <t xml:space="preserve">1.16575646400452</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">1.18378865718842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17181301116943</t>
+    <t xml:space="preserve">1.17181313037872</t>
   </si>
   <si>
     <t xml:space="preserve">1.11344945430756</t>
@@ -2909,16 +2909,16 @@
     <t xml:space="preserve">1.11950612068176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16947329044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17263889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16025054454803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15956246852875</t>
+    <t xml:space="preserve">1.16947305202484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17263901233673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16025030612946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15956223011017</t>
   </si>
   <si>
     <t xml:space="preserve">1.15791034698486</t>
@@ -2927,55 +2927,55 @@
     <t xml:space="preserve">1.17786979675293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14717388153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.142493724823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17140007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1725013256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16355395317078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20636320114136</t>
+    <t xml:space="preserve">1.14717376232147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14249360561371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17140018939972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17250120639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16355419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20636308193207</t>
   </si>
   <si>
     <t xml:space="preserve">1.20223355293274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23348009586334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22962605953217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.213383436203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19149696826935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21503508090973</t>
+    <t xml:space="preserve">1.23348021507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22962582111359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21338331699371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19149684906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21503531932831</t>
   </si>
   <si>
     <t xml:space="preserve">1.22604715824127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22577178478241</t>
+    <t xml:space="preserve">1.2257719039917</t>
   </si>
   <si>
     <t xml:space="preserve">1.24875938892365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26596570014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26073479652405</t>
+    <t xml:space="preserve">1.26596558094025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26073491573334</t>
   </si>
   <si>
     <t xml:space="preserve">1.27628946304321</t>
@@ -2987,70 +2987,70 @@
     <t xml:space="preserve">1.29129314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27271032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24944770336151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23981201648712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2293506860733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23155307769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1941123008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1749792098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17566728591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23444378376007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26252424716949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24834632873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24256503582001</t>
+    <t xml:space="preserve">1.27271044254303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24944758415222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23981213569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22935080528259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23155295848846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19411242008209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17497885227203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1756671667099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23444366455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26252436637878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24834644794464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2425651550293</t>
   </si>
   <si>
     <t xml:space="preserve">1.24848401546478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28096950054169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29583537578583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28399765491486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27436220645905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25564169883728</t>
+    <t xml:space="preserve">1.28096926212311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2958357334137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28399777412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27436232566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25564181804657</t>
   </si>
   <si>
     <t xml:space="preserve">1.24903464317322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26981961727142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24999797344208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24683225154877</t>
+    <t xml:space="preserve">1.26981985569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24999809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24683237075806</t>
   </si>
   <si>
     <t xml:space="preserve">1.2658280134201</t>
@@ -3062,31 +3062,31 @@
     <t xml:space="preserve">1.2681679725647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24146378040314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25605487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24242758750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24008727073669</t>
+    <t xml:space="preserve">1.24146389961243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25605475902557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24242746829987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24008738994598</t>
   </si>
   <si>
     <t xml:space="preserve">1.22425758838654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22412014007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23458135128021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21269500255585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23210370540619</t>
+    <t xml:space="preserve">1.22411978244781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23458158969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21269512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23210382461548</t>
   </si>
   <si>
     <t xml:space="preserve">1.23967444896698</t>
@@ -3095,88 +3095,88 @@
     <t xml:space="preserve">1.22439539432526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21737515926361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21145617961884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19989371299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18020975589752</t>
+    <t xml:space="preserve">1.2173752784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21145629882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19989347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18020963668823</t>
   </si>
   <si>
     <t xml:space="preserve">1.12570035457611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12996745109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10959529876709</t>
+    <t xml:space="preserve">1.12996757030487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10959553718567</t>
   </si>
   <si>
     <t xml:space="preserve">1.10670471191406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08674550056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11812973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10587871074677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10326337814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09183859825134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09596788883209</t>
+    <t xml:space="preserve">1.08674538135529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11812961101532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10587882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10326361656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09183847904205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09596812725067</t>
   </si>
   <si>
     <t xml:space="preserve">1.12404870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14827489852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13478517532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15309274196625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15557038784027</t>
+    <t xml:space="preserve">1.14827501773834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13478529453278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15309262275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15557026863098</t>
   </si>
   <si>
     <t xml:space="preserve">1.14978921413422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11317443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05825197696686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07077813148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07353115081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05701327323914</t>
+    <t xml:space="preserve">1.11317431926727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05825209617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0707780122757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07353127002716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05701303482056</t>
   </si>
   <si>
     <t xml:space="preserve">1.05770134925842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07449471950531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05095660686493</t>
+    <t xml:space="preserve">1.07449448108673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05095648765564</t>
   </si>
   <si>
     <t xml:space="preserve">1.02590417861938</t>
@@ -3185,19 +3185,19 @@
     <t xml:space="preserve">0.97593742609024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962998270988464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977038443088531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02026069164276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06031668186188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09968459606171</t>
+    <t xml:space="preserve">0.962998151779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977038681507111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02026057243347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0603164434433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09968483448029</t>
   </si>
   <si>
     <t xml:space="preserve">1.12680160999298</t>
@@ -3206,64 +3206,64 @@
     <t xml:space="preserve">1.11276113986969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21531057357788</t>
+    <t xml:space="preserve">1.21531045436859</t>
   </si>
   <si>
     <t xml:space="preserve">1.26926910877228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25591731071472</t>
+    <t xml:space="preserve">1.25591695308685</t>
   </si>
   <si>
     <t xml:space="preserve">1.24022507667542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25109958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26637840270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27615165710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28730130195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28248369693756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31868541240692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33671772480011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3277702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32515490055084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35653913021088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36700069904327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37002885341644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35667681694031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35516250133514</t>
+    <t xml:space="preserve">1.25109934806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26637852191925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27615177631378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28730118274689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28248357772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31868553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33671748638153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32777047157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32515501976013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35653924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36700046062469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37002873420715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3566769361496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516273975372</t>
   </si>
   <si>
     <t xml:space="preserve">1.35998034477234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3495192527771</t>
+    <t xml:space="preserve">1.34951901435852</t>
   </si>
   <si>
     <t xml:space="preserve">1.33231282234192</t>
@@ -3272,64 +3272,64 @@
     <t xml:space="preserve">1.33465301990509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35929226875305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33726823329926</t>
+    <t xml:space="preserve">1.35929203033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33726835250854</t>
   </si>
   <si>
     <t xml:space="preserve">1.33823180198669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33189976215363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29473423957825</t>
+    <t xml:space="preserve">1.33189988136292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29473435878754</t>
   </si>
   <si>
     <t xml:space="preserve">1.3166207075119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32309019565582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32130074501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31634533405304</t>
+    <t xml:space="preserve">1.32309031486511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32130086421967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31634545326233</t>
   </si>
   <si>
     <t xml:space="preserve">1.31125247478485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29693686962128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35447442531586</t>
+    <t xml:space="preserve">1.29693675041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35447454452515</t>
   </si>
   <si>
     <t xml:space="preserve">1.34552729129791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33713054656982</t>
+    <t xml:space="preserve">1.3371307849884</t>
   </si>
   <si>
     <t xml:space="preserve">1.33396446704865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31799721717834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30904996395111</t>
+    <t xml:space="preserve">1.31799697875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30904984474182</t>
   </si>
   <si>
     <t xml:space="preserve">1.31951129436493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31483149528503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32584321498871</t>
+    <t xml:space="preserve">1.31483125686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32584309577942</t>
   </si>
   <si>
     <t xml:space="preserve">1.29679918289185</t>
@@ -3338,55 +3338,55 @@
     <t xml:space="preserve">1.25481593608856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26610314846039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24407923221588</t>
+    <t xml:space="preserve">1.26610326766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24407935142517</t>
   </si>
   <si>
     <t xml:space="preserve">1.26197373867035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25399029254913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771424293518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34291195869446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38234865665436</t>
+    <t xml:space="preserve">1.25398993492126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771436214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34291183948517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38234853744507</t>
   </si>
   <si>
     <t xml:space="preserve">1.41848170757294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43844091892242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637597560883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43155825138092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43603181838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44257044792175</t>
+    <t xml:space="preserve">1.43844079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637585639954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43155837059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43603193759918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44257032871246</t>
   </si>
   <si>
     <t xml:space="preserve">1.45736765861511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45392620563507</t>
+    <t xml:space="preserve">1.45392632484436</t>
   </si>
   <si>
     <t xml:space="preserve">1.45117354393005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44532322883606</t>
+    <t xml:space="preserve">1.44532310962677</t>
   </si>
   <si>
     <t xml:space="preserve">1.45358228683472</t>
@@ -3395,34 +3395,34 @@
     <t xml:space="preserve">1.481112241745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46872365474701</t>
+    <t xml:space="preserve">1.4687237739563</t>
   </si>
   <si>
     <t xml:space="preserve">1.48661828041077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48283314704895</t>
+    <t xml:space="preserve">1.48283290863037</t>
   </si>
   <si>
     <t xml:space="preserve">1.51621317863464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50864207744598</t>
+    <t xml:space="preserve">1.50864219665527</t>
   </si>
   <si>
     <t xml:space="preserve">1.51036274433136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56198155879974</t>
+    <t xml:space="preserve">1.56198143959045</t>
   </si>
   <si>
     <t xml:space="preserve">1.56507861614227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55991685390472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56955218315125</t>
+    <t xml:space="preserve">1.55991697311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56955230236053</t>
   </si>
   <si>
     <t xml:space="preserve">1.55888450145721</t>
@@ -3431,49 +3431,49 @@
     <t xml:space="preserve">1.57884347438812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59329700469971</t>
+    <t xml:space="preserve">1.59329676628113</t>
   </si>
   <si>
     <t xml:space="preserve">1.61669731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59260869026184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58194077014923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57540249824524</t>
+    <t xml:space="preserve">1.59260833263397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58194088935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57540237903595</t>
   </si>
   <si>
     <t xml:space="preserve">1.5798761844635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57918775081635</t>
+    <t xml:space="preserve">1.57918798923492</t>
   </si>
   <si>
     <t xml:space="preserve">1.58125245571136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57333755493164</t>
+    <t xml:space="preserve">1.57333791255951</t>
   </si>
   <si>
     <t xml:space="preserve">1.59914684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59019994735718</t>
+    <t xml:space="preserve">1.59019958972931</t>
   </si>
   <si>
     <t xml:space="preserve">1.59536170959473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58503770828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55750823020935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55096936225891</t>
+    <t xml:space="preserve">1.58503806591034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55750799179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55096971988678</t>
   </si>
   <si>
     <t xml:space="preserve">1.5557873249054</t>
@@ -3482,13 +3482,13 @@
     <t xml:space="preserve">1.56989634037018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52791321277618</t>
+    <t xml:space="preserve">1.52791333198547</t>
   </si>
   <si>
     <t xml:space="preserve">1.53204274177551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52860152721405</t>
+    <t xml:space="preserve">1.52860140800476</t>
   </si>
   <si>
     <t xml:space="preserve">1.58056402206421</t>
@@ -3497,40 +3497,40 @@
     <t xml:space="preserve">1.5950174331665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59742641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60637366771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5884792804718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62357997894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62564468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64457166194916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63837742805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63975346088409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63287150859833</t>
+    <t xml:space="preserve">1.59742629528046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60637354850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58847904205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62357985973358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6256445646286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64457142353058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63837718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63975369930267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63287115097046</t>
   </si>
   <si>
     <t xml:space="preserve">1.64319503307343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65868079662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6535187959671</t>
+    <t xml:space="preserve">1.65868055820465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65351855754852</t>
   </si>
   <si>
     <t xml:space="preserve">1.65116274356842</t>
@@ -3539,37 +3539,37 @@
     <t xml:space="preserve">1.64976525306702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63928401470184</t>
+    <t xml:space="preserve">1.63928389549255</t>
   </si>
   <si>
     <t xml:space="preserve">1.67282438278198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68330574035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68854653835297</t>
+    <t xml:space="preserve">1.68330585956573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68854629993439</t>
   </si>
   <si>
     <t xml:space="preserve">1.70881032943726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72767651081085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73012232780457</t>
+    <t xml:space="preserve">1.72767698764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73012244701385</t>
   </si>
   <si>
     <t xml:space="preserve">1.73326671123505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73676085472107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71894240379333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71440029144287</t>
+    <t xml:space="preserve">1.73676073551178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71894228458405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71440041065216</t>
   </si>
   <si>
     <t xml:space="preserve">1.70426833629608</t>
@@ -3578,10 +3578,10 @@
     <t xml:space="preserve">1.69448578357697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71195459365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7126532793045</t>
+    <t xml:space="preserve">1.71195507049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71265363693237</t>
   </si>
   <si>
     <t xml:space="preserve">1.68749833106995</t>
@@ -3590,91 +3590,91 @@
     <t xml:space="preserve">1.63788664340973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65360867977142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63648903369904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61832106113434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65186166763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6668848991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62775456905365</t>
+    <t xml:space="preserve">1.65360844135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63648891448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6183215379715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65186190605164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66688501834869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62775433063507</t>
   </si>
   <si>
     <t xml:space="preserve">1.64662086963654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64592206478119</t>
+    <t xml:space="preserve">1.64592218399048</t>
   </si>
   <si>
     <t xml:space="preserve">1.63229656219482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65535521507263</t>
+    <t xml:space="preserve">1.65535533428192</t>
   </si>
   <si>
     <t xml:space="preserve">1.6214656829834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60958683490753</t>
+    <t xml:space="preserve">1.60958671569824</t>
   </si>
   <si>
     <t xml:space="preserve">1.56242084503174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5959609746933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61098444461823</t>
+    <t xml:space="preserve">1.59596109390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61098408699036</t>
   </si>
   <si>
     <t xml:space="preserve">1.58617866039276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59631049633026</t>
+    <t xml:space="preserve">1.59631037712097</t>
   </si>
   <si>
     <t xml:space="preserve">1.57639598846436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55962562561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49359309673309</t>
+    <t xml:space="preserve">1.55962574481964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49359321594238</t>
   </si>
   <si>
     <t xml:space="preserve">1.52259147167206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56277000904083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59666001796722</t>
+    <t xml:space="preserve">1.56277012825012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255244255066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59665977954865</t>
   </si>
   <si>
     <t xml:space="preserve">1.63334453105927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61657428741455</t>
+    <t xml:space="preserve">1.61657452583313</t>
   </si>
   <si>
     <t xml:space="preserve">1.62111616134644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6399827003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62915205955505</t>
+    <t xml:space="preserve">1.63998281955719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62915170192719</t>
   </si>
   <si>
     <t xml:space="preserve">1.61727321147919</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">1.62565839290619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63509130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63858509063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67596888542175</t>
+    <t xml:space="preserve">1.63509118556976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63858532905579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67596864700317</t>
   </si>
   <si>
     <t xml:space="preserve">1.68016123771667</t>
@@ -3698,19 +3698,19 @@
     <t xml:space="preserve">1.68260681629181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71125566959381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71055746078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69204020500183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66898107528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68225741386414</t>
+    <t xml:space="preserve">1.71125590801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71055698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69204008579254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66898119449615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68225753307343</t>
   </si>
   <si>
     <t xml:space="preserve">1.66723418235779</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">1.66304194927216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67002928256989</t>
+    <t xml:space="preserve">1.67002940177917</t>
   </si>
   <si>
     <t xml:space="preserve">1.66164422035217</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">1.6752701997757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68365478515625</t>
+    <t xml:space="preserve">1.68365490436554</t>
   </si>
   <si>
     <t xml:space="preserve">1.6682825088501</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">1.6483678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65710246562958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63963305950165</t>
+    <t xml:space="preserve">1.657102227211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63963341712952</t>
   </si>
   <si>
     <t xml:space="preserve">1.66758346557617</t>
@@ -3755,22 +3755,22 @@
     <t xml:space="preserve">1.66094565391541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65884935855865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60853862762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62251365184784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65815043449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69623243808746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69413650035858</t>
+    <t xml:space="preserve">1.65884923934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6085387468338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62251377105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65815031528473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69623279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69413638114929</t>
   </si>
   <si>
     <t xml:space="preserve">1.72732710838318</t>
@@ -3779,13 +3779,13 @@
     <t xml:space="preserve">1.69763016700745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7182434797287</t>
+    <t xml:space="preserve">1.71824359893799</t>
   </si>
   <si>
     <t xml:space="preserve">1.74898898601532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72942340373993</t>
+    <t xml:space="preserve">1.72942352294922</t>
   </si>
   <si>
     <t xml:space="preserve">1.7538800239563</t>
@@ -3794,154 +3794,154 @@
     <t xml:space="preserve">1.75912070274353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74933815002441</t>
+    <t xml:space="preserve">1.7493382692337</t>
   </si>
   <si>
     <t xml:space="preserve">1.75562727451324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74339866638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76331317424774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79929971694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81100213527679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78156352043152</t>
+    <t xml:space="preserve">1.74339890480042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76331329345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79929935932159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81100165843964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7815637588501</t>
   </si>
   <si>
     <t xml:space="preserve">1.79319369792938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77720248699188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78192698955536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79028618335724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80373311042786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78301727771759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77211427688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78628826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81354582309723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82590293884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81863451004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78556156158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80518698692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81172871589661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573786258698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80046236515045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79682767391205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7964643239975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80991208553314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80446028709412</t>
+    <t xml:space="preserve">1.77720236778259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78192687034607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79028654098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80373334884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78301763534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77211439609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78628790378571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81354606151581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82590281963348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81863415241241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78556132316589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80518710613251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8117288351059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7957376241684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80046224594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79682779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646444320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80991172790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80446016788483</t>
   </si>
   <si>
     <t xml:space="preserve">1.8040965795517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73286306858063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74418127536774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72544264793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72581768035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71494913101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61638462543488</t>
+    <t xml:space="preserve">1.73286330699921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74418115615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72544276714325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7258175611496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71494936943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61638474464417</t>
   </si>
   <si>
     <t xml:space="preserve">1.60626566410065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58565330505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62537908554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60963881015778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60888934135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6587336063385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69246292114258</t>
+    <t xml:space="preserve">1.585653424263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62537884712219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60963869094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60888910293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65873372554779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.692462682724</t>
   </si>
   <si>
     <t xml:space="preserve">1.6722252368927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6677280664444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66060757637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65273725986481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66735339164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65011370182037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68084514141083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311193466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63549792766571</t>
+    <t xml:space="preserve">1.66772818565369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66060769557953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6527373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66735327243805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65011394023895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68084502220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311217308044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63549780845642</t>
   </si>
   <si>
     <t xml:space="preserve">1.67334961891174</t>
@@ -3950,103 +3950,103 @@
     <t xml:space="preserve">1.67185056209564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68721604347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69583582878113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71157598495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70670413970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70445561408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75767302513123</t>
+    <t xml:space="preserve">1.68721616268158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69583594799042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71157622337341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70670425891876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70445549488068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75767290592194</t>
   </si>
   <si>
     <t xml:space="preserve">1.7944004535675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81238973140717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82363259792328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83749902248383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84611880779266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86036014556885</t>
+    <t xml:space="preserve">1.81238925457001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82363247871399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8374992609024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84611904621124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86036002635956</t>
   </si>
   <si>
     <t xml:space="preserve">1.90795600414276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91919910907745</t>
+    <t xml:space="preserve">1.91919887065887</t>
   </si>
   <si>
     <t xml:space="preserve">1.92032337188721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93194127082825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93006765842438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89933609962463</t>
+    <t xml:space="preserve">1.93194115161896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93006718158722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89933621883392</t>
   </si>
   <si>
     <t xml:space="preserve">1.91245329380035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91282820701599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84874224662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86560690402985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92219722270966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95817506313324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9465571641922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96342194080353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00127363204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02151107788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04474711418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99902498722076</t>
+    <t xml:space="preserve">1.9128280878067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8487423658371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86560678482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92219698429108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95817518234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94655740261078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96342182159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00127387046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02151131629944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04474687576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99902510643005</t>
   </si>
   <si>
     <t xml:space="preserve">2.03500294685364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07585310935974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13881421089172</t>
+    <t xml:space="preserve">2.07585334777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13881468772888</t>
   </si>
   <si>
     <t xml:space="preserve">2.18865895271301</t>
@@ -4058,46 +4058,46 @@
     <t xml:space="preserve">2.13843965530396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09196805953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05299186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04024982452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00427174568176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99377858638763</t>
+    <t xml:space="preserve">2.09196829795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05299210548401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04024958610535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00427198410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99377822875977</t>
   </si>
   <si>
     <t xml:space="preserve">1.96417164802551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80789232254028</t>
+    <t xml:space="preserve">1.8078920841217</t>
   </si>
   <si>
     <t xml:space="preserve">1.85698711872101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71907162666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58640277385712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60851430892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56204283237457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42127895355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38155341148376</t>
+    <t xml:space="preserve">1.71907186508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5864030122757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60851442813873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56204295158386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42127907276154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38155353069305</t>
   </si>
   <si>
     <t xml:space="preserve">1.39834320545197</t>
@@ -4112,10 +4112,10 @@
     <t xml:space="preserve">1.43866837024689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49158596992493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50507760047913</t>
+    <t xml:space="preserve">1.49158620834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50507771968842</t>
   </si>
   <si>
     <t xml:space="preserve">1.61001348495483</t>
@@ -4124,22 +4124,22 @@
     <t xml:space="preserve">1.55304837226868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56354188919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54892599582672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57403540611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53505945205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52231705188751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5238162279129</t>
+    <t xml:space="preserve">1.56354200839996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54892587661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57403528690338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53505957126617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5223171710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52381634712219</t>
   </si>
   <si>
     <t xml:space="preserve">1.53243613243103</t>
@@ -4148,16 +4148,16 @@
     <t xml:space="preserve">1.61975753307343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59951996803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56166791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57778334617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57028758525848</t>
+    <t xml:space="preserve">1.59951984882355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56166803836823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57778310775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57028782367706</t>
   </si>
   <si>
     <t xml:space="preserve">1.53056216239929</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">1.48573970794678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46280372142792</t>
+    <t xml:space="preserve">1.46280360221863</t>
   </si>
   <si>
     <t xml:space="preserve">1.48558974266052</t>
@@ -4175,37 +4175,37 @@
     <t xml:space="preserve">1.48469030857086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45500838756561</t>
+    <t xml:space="preserve">1.4550085067749</t>
   </si>
   <si>
     <t xml:space="preserve">1.4572571516037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47734463214874</t>
+    <t xml:space="preserve">1.47734475135803</t>
   </si>
   <si>
     <t xml:space="preserve">1.47884392738342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51444709300995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5178200006485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48618936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46055507659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43761909008026</t>
+    <t xml:space="preserve">1.51444685459137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51782011985779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48618948459625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46055495738983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43761897087097</t>
   </si>
   <si>
     <t xml:space="preserve">1.4397177696228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44361555576324</t>
+    <t xml:space="preserve">1.44361531734467</t>
   </si>
   <si>
     <t xml:space="preserve">1.46520221233368</t>
@@ -4214,13 +4214,13 @@
     <t xml:space="preserve">1.44091701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4692497253418</t>
+    <t xml:space="preserve">1.46924960613251</t>
   </si>
   <si>
     <t xml:space="preserve">1.44301569461823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44256603717804</t>
+    <t xml:space="preserve">1.44256615638733</t>
   </si>
   <si>
     <t xml:space="preserve">1.40913653373718</t>
@@ -4232,25 +4232,25 @@
     <t xml:space="preserve">1.39534509181976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45410907268524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47074890136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47839403152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46490228176117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49188578128815</t>
+    <t xml:space="preserve">1.45410919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47074902057648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47839415073395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46490240097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49188590049744</t>
   </si>
   <si>
     <t xml:space="preserve">1.49008703231812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48633933067322</t>
+    <t xml:space="preserve">1.48633921146393</t>
   </si>
   <si>
     <t xml:space="preserve">1.54183983802795</t>
@@ -4259,10 +4259,10 @@
     <t xml:space="preserve">1.54496228694916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58695840835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60139954090118</t>
+    <t xml:space="preserve">1.58695864677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60139966011047</t>
   </si>
   <si>
     <t xml:space="preserve">1.59788680076599</t>
@@ -4277,43 +4277,43 @@
     <t xml:space="preserve">1.56119871139526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54012262821198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59047114849091</t>
+    <t xml:space="preserve">1.54012250900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59047102928162</t>
   </si>
   <si>
     <t xml:space="preserve">1.5631502866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5533926486969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53528273105621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42193973064423</t>
+    <t xml:space="preserve">1.55339276790619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5352828502655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42193984985352</t>
   </si>
   <si>
     <t xml:space="preserve">1.3730742931366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38166081905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44520151615143</t>
+    <t xml:space="preserve">1.38166093826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44520163536072</t>
   </si>
   <si>
     <t xml:space="preserve">1.39961457252502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40788888931274</t>
+    <t xml:space="preserve">1.40788900852203</t>
   </si>
   <si>
     <t xml:space="preserve">1.46175026893616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47221028804779</t>
+    <t xml:space="preserve">1.47221040725708</t>
   </si>
   <si>
     <t xml:space="preserve">1.46799516677856</t>
@@ -4322,19 +4322,19 @@
     <t xml:space="preserve">1.43630290031433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4692440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47798669338226</t>
+    <t xml:space="preserve">1.46924424171448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47798693180084</t>
   </si>
   <si>
     <t xml:space="preserve">1.48204600811005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46440434455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3894670009613</t>
+    <t xml:space="preserve">1.46440446376801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38946688175201</t>
   </si>
   <si>
     <t xml:space="preserve">1.37978744506836</t>
@@ -4343,31 +4343,31 @@
     <t xml:space="preserve">1.34669005870819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30469381809235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31000173091888</t>
+    <t xml:space="preserve">1.30469369888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31000196933746</t>
   </si>
   <si>
     <t xml:space="preserve">1.36230206489563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37588429450989</t>
+    <t xml:space="preserve">1.37588441371918</t>
   </si>
   <si>
     <t xml:space="preserve">1.35199809074402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33295142650604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3276435136795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25411093235016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27393817901611</t>
+    <t xml:space="preserve">1.33295154571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32764339447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25411105155945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27393805980682</t>
   </si>
   <si>
     <t xml:space="preserve">1.30672335624695</t>
@@ -4379,13 +4379,13 @@
     <t xml:space="preserve">1.33513724803925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2981368303299</t>
+    <t xml:space="preserve">1.29813659191132</t>
   </si>
   <si>
     <t xml:space="preserve">1.29579484462738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31765162944794</t>
+    <t xml:space="preserve">1.31765174865723</t>
   </si>
   <si>
     <t xml:space="preserve">1.29329705238342</t>
@@ -4394,7 +4394,7 @@
     <t xml:space="preserve">1.3092212677002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33154654502869</t>
+    <t xml:space="preserve">1.3315464258194</t>
   </si>
   <si>
     <t xml:space="preserve">1.34934401512146</t>
@@ -4403,22 +4403,22 @@
     <t xml:space="preserve">1.36542439460754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36370706558228</t>
+    <t xml:space="preserve">1.36370694637299</t>
   </si>
   <si>
     <t xml:space="preserve">1.38462710380554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39180874824524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41600716114044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41850519180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4175683259964</t>
+    <t xml:space="preserve">1.39180862903595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41600728034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41850507259369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41756844520569</t>
   </si>
   <si>
     <t xml:space="preserve">1.43052637577057</t>
@@ -4427,43 +4427,43 @@
     <t xml:space="preserve">1.4470751285553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44785571098328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42740404605865</t>
+    <t xml:space="preserve">1.44785559177399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42740392684937</t>
   </si>
   <si>
     <t xml:space="preserve">1.42615497112274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3841587305069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34138190746307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36573660373688</t>
+    <t xml:space="preserve">1.38415884971619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34138202667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36573672294617</t>
   </si>
   <si>
     <t xml:space="preserve">1.37666499614716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35699391365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31530976295471</t>
+    <t xml:space="preserve">1.3569940328598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.315309882164</t>
   </si>
   <si>
     <t xml:space="preserve">1.32811176776886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34996855258942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34497261047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32217919826508</t>
+    <t xml:space="preserve">1.34996843338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34497284889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32217907905579</t>
   </si>
   <si>
     <t xml:space="preserve">1.3568377494812</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">1.32467722892761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32998526096344</t>
+    <t xml:space="preserve">1.32998514175415</t>
   </si>
   <si>
     <t xml:space="preserve">1.32701897621155</t>
@@ -4487,19 +4487,19 @@
     <t xml:space="preserve">1.48001635074615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46846354007721</t>
+    <t xml:space="preserve">1.46846342086792</t>
   </si>
   <si>
     <t xml:space="preserve">1.48329496383667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4987508058548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49484777450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49515998363495</t>
+    <t xml:space="preserve">1.49875068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49484765529633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49516010284424</t>
   </si>
   <si>
     <t xml:space="preserve">1.44348430633545</t>
@@ -4508,19 +4508,19 @@
     <t xml:space="preserve">1.43364870548248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44566988945007</t>
+    <t xml:space="preserve">1.44567000865936</t>
   </si>
   <si>
     <t xml:space="preserve">1.37697744369507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38041174411774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34825122356415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32592618465424</t>
+    <t xml:space="preserve">1.38041186332703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34825134277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32592594623566</t>
   </si>
   <si>
     <t xml:space="preserve">1.29189193248749</t>
@@ -4535,28 +4535,28 @@
     <t xml:space="preserve">1.39571166038513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35917961597443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33654224872589</t>
+    <t xml:space="preserve">1.35917949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33654236793518</t>
   </si>
   <si>
     <t xml:space="preserve">1.33139026165009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3234281539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30781626701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33201467990875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3366984128952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36058485507965</t>
+    <t xml:space="preserve">1.32342827320099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30781614780426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33201479911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33669817447662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36058461666107</t>
   </si>
   <si>
     <t xml:space="preserve">1.40726459026337</t>
@@ -4565,19 +4565,19 @@
     <t xml:space="preserve">1.39852178096771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42771625518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42662334442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44863617420197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45550560951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45644235610962</t>
+    <t xml:space="preserve">1.42771601676941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42662346363068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44863641262054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45550537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45644223690033</t>
   </si>
   <si>
     <t xml:space="preserve">1.48766624927521</t>
@@ -4586,37 +4586,37 @@
     <t xml:space="preserve">1.48719787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50577616691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51842176914215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51810956001282</t>
+    <t xml:space="preserve">1.50577628612518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51842188835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51810967922211</t>
   </si>
   <si>
     <t xml:space="preserve">1.53746843338013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61193764209747</t>
+    <t xml:space="preserve">1.61193776130676</t>
   </si>
   <si>
     <t xml:space="preserve">1.6618959903717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67672741413116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68141090869904</t>
+    <t xml:space="preserve">1.67672753334045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68141114711761</t>
   </si>
   <si>
     <t xml:space="preserve">1.69936490058899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68648493289948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678043365479</t>
+    <t xml:space="preserve">1.68648481369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678055286407</t>
   </si>
   <si>
     <t xml:space="preserve">1.70951271057129</t>
@@ -4625,22 +4625,22 @@
     <t xml:space="preserve">1.70990288257599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70014548301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73019862174988</t>
+    <t xml:space="preserve">1.70014536380768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73019850254059</t>
   </si>
   <si>
     <t xml:space="preserve">1.72882580757141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74457180500031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73165214061737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7441680431366</t>
+    <t xml:space="preserve">1.74457168579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73165190219879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74416792392731</t>
   </si>
   <si>
     <t xml:space="preserve">1.74295675754547</t>
@@ -4649,25 +4649,25 @@
     <t xml:space="preserve">1.70863854885101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72357726097107</t>
+    <t xml:space="preserve">1.72357714176178</t>
   </si>
   <si>
     <t xml:space="preserve">1.71348357200623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68320298194885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69289255142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67835783958435</t>
+    <t xml:space="preserve">1.68320286273956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69289267063141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67835807800293</t>
   </si>
   <si>
     <t xml:space="preserve">1.66866815090179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66463077068329</t>
+    <t xml:space="preserve">1.664630651474</t>
   </si>
   <si>
     <t xml:space="preserve">1.66140067577362</t>
@@ -4679,13 +4679,13 @@
     <t xml:space="preserve">1.67028319835663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6965264081955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68562543392181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61044859886169</t>
+    <t xml:space="preserve">1.69652652740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68562531471252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6104484796524</t>
   </si>
   <si>
     <t xml:space="preserve">1.66180455684662</t>
@@ -4697,22 +4697,22 @@
     <t xml:space="preserve">1.67593550682068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69612276554108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68279910087585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68966269493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68118417263031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6799727678299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70137155056</t>
+    <t xml:space="preserve">1.69612264633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68279933929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68966257572174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68118405342102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67997288703918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70137143135071</t>
   </si>
   <si>
     <t xml:space="preserve">1.67795419692993</t>
@@ -4730,22 +4730,22 @@
     <t xml:space="preserve">1.78857958316803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8035181760788</t>
+    <t xml:space="preserve">1.80351805686951</t>
   </si>
   <si>
     <t xml:space="preserve">1.81684172153473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82451272010803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84429609775543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84752607345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84510362148285</t>
+    <t xml:space="preserve">1.82451283931732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84429597854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8475261926651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84510385990143</t>
   </si>
   <si>
     <t xml:space="preserve">1.82572388648987</t>
@@ -4760,121 +4760,121 @@
     <t xml:space="preserve">1.80836308002472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84550726413727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317850112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89153373241425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.898397564888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89274525642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94603955745697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98076128959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98237609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423701286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97591638565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99327731132507</t>
+    <t xml:space="preserve">1.84550750255585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85317862033844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89153397083282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89839780330658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89274537563324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94603931903839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98076117038727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9823762178421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423725128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97591626644135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99327719211578</t>
   </si>
   <si>
     <t xml:space="preserve">1.99368095397949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02194285392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00014090538025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01790571212769</t>
+    <t xml:space="preserve">2.02194261550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00014066696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01790547370911</t>
   </si>
   <si>
     <t xml:space="preserve">2.02073168754578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01467561721802</t>
+    <t xml:space="preserve">2.01467537879944</t>
   </si>
   <si>
     <t xml:space="preserve">2.05989480018616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07079577445984</t>
+    <t xml:space="preserve">2.07079601287842</t>
   </si>
   <si>
     <t xml:space="preserve">2.06231713294983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06150960922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99973714351654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03001761436462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04535984992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837344169617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04858994483948</t>
+    <t xml:space="preserve">2.06151008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99973690509796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0300178527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04536008834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837320327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04859018325806</t>
   </si>
   <si>
     <t xml:space="preserve">2.05262756347656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07887053489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0934054851532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07119965553284</t>
+    <t xml:space="preserve">2.07887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09340524673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07119941711426</t>
   </si>
   <si>
     <t xml:space="preserve">2.0772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04414868354797</t>
+    <t xml:space="preserve">2.04414892196655</t>
   </si>
   <si>
     <t xml:space="preserve">2.00417828559875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88184404373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94482803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8115930557251</t>
+    <t xml:space="preserve">1.8818439245224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94482791423798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81159293651581</t>
   </si>
   <si>
     <t xml:space="preserve">1.81522655487061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77081513404846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83702874183655</t>
+    <t xml:space="preserve">1.77081501483917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83702886104584</t>
   </si>
   <si>
     <t xml:space="preserve">1.90162754058838</t>
@@ -4886,130 +4886,130 @@
     <t xml:space="preserve">1.87255799770355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82733905315399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83420252799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85196721553802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87982559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90970242023468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91172134876251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86448311805725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90404999256134</t>
+    <t xml:space="preserve">1.82733881473541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83420264720917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85196733474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87982547283173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90970253944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91172122955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86448323726654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90405011177063</t>
   </si>
   <si>
     <t xml:space="preserve">1.91939234733582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93433082103729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92827463150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97147512435913</t>
+    <t xml:space="preserve">1.93433058261871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92827475070953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97147500514984</t>
   </si>
   <si>
     <t xml:space="preserve">2.00094819068909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01750159263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01023435592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00619697570801</t>
+    <t xml:space="preserve">2.01750206947327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01023459434509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00619673728943</t>
   </si>
   <si>
     <t xml:space="preserve">2.02436518669128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98722100257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96541917324066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98479843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92544853687286</t>
+    <t xml:space="preserve">1.98722112178802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9654186964035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98479866981506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92544865608215</t>
   </si>
   <si>
     <t xml:space="preserve">1.88022923469543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91293263435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395618438721</t>
+    <t xml:space="preserve">1.91293251514435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89395654201508</t>
   </si>
   <si>
     <t xml:space="preserve">1.96380388736725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98883605003357</t>
+    <t xml:space="preserve">1.98883616924286</t>
   </si>
   <si>
     <t xml:space="preserve">1.98358738422394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9504805803299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93917572498322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96057415008545</t>
+    <t xml:space="preserve">1.95048046112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93917536735535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96057403087616</t>
   </si>
   <si>
     <t xml:space="preserve">1.9545179605484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94038701057434</t>
+    <t xml:space="preserve">1.94038689136505</t>
   </si>
   <si>
     <t xml:space="preserve">1.92948591709137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9512882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96353387832642</t>
+    <t xml:space="preserve">1.95128786563873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96353375911713</t>
   </si>
   <si>
     <t xml:space="preserve">1.96437251567841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88888442516327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88804566860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88301301002502</t>
+    <t xml:space="preserve">1.88888430595398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88804543018341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88301289081573</t>
   </si>
   <si>
     <t xml:space="preserve">1.86665725708008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85365653038025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80794417858124</t>
+    <t xml:space="preserve">1.85365641117096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80794405937195</t>
   </si>
   <si>
     <t xml:space="preserve">1.87043154239655</t>
@@ -5021,16 +5021,16 @@
     <t xml:space="preserve">1.89475572109222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91698265075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93166089057922</t>
+    <t xml:space="preserve">1.91698288917542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93166100978851</t>
   </si>
   <si>
     <t xml:space="preserve">1.94927477836609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93711292743683</t>
+    <t xml:space="preserve">1.93711280822754</t>
   </si>
   <si>
     <t xml:space="preserve">1.93417716026306</t>
@@ -5039,16 +5039,16 @@
     <t xml:space="preserve">1.93920993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97108268737793</t>
+    <t xml:space="preserve">1.97108244895935</t>
   </si>
   <si>
     <t xml:space="preserve">1.97779285907745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99037408828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00840735435486</t>
+    <t xml:space="preserve">1.99037384986877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00840759277344</t>
   </si>
   <si>
     <t xml:space="preserve">2.00169730186462</t>
@@ -5057,55 +5057,55 @@
     <t xml:space="preserve">2.01805305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99540638923645</t>
+    <t xml:space="preserve">1.99540627002716</t>
   </si>
   <si>
     <t xml:space="preserve">1.95850133895874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9559850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98072814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98240578174591</t>
+    <t xml:space="preserve">1.95598495006561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98072850704193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9824059009552</t>
   </si>
   <si>
     <t xml:space="preserve">2.00127792358398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01302051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04405498504639</t>
+    <t xml:space="preserve">2.01302075386047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04405450820923</t>
   </si>
   <si>
     <t xml:space="preserve">2.03021502494812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02056956291199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96311438083649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97024381160736</t>
+    <t xml:space="preserve">2.02056932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96311450004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97024369239807</t>
   </si>
   <si>
     <t xml:space="preserve">1.97695410251617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99666488170624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01973032951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04992604255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03860259056091</t>
+    <t xml:space="preserve">1.99666500091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01973056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04992628097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03860282897949</t>
   </si>
   <si>
     <t xml:space="preserve">2.04237699508667</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">2.11534905433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12289786338806</t>
+    <t xml:space="preserve">2.12289762496948</t>
   </si>
   <si>
     <t xml:space="preserve">2.12709164619446</t>
@@ -5132,19 +5132,19 @@
     <t xml:space="preserve">2.15812587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18874025344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20509648323059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18832087516785</t>
+    <t xml:space="preserve">2.18874049186707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20509624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18832111358643</t>
   </si>
   <si>
     <t xml:space="preserve">2.149738073349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13506007194519</t>
+    <t xml:space="preserve">2.13505983352661</t>
   </si>
   <si>
     <t xml:space="preserve">2.13338255882263</t>
@@ -5153,19 +5153,19 @@
     <t xml:space="preserve">2.14722180366516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96101760864258</t>
+    <t xml:space="preserve">1.961017370224</t>
   </si>
   <si>
     <t xml:space="preserve">2.0067298412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04489326477051</t>
+    <t xml:space="preserve">2.04489374160767</t>
   </si>
   <si>
     <t xml:space="preserve">2.04615163803101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05076479911804</t>
+    <t xml:space="preserve">2.05076456069946</t>
   </si>
   <si>
     <t xml:space="preserve">2.03734445571899</t>
@@ -5180,16 +5180,16 @@
     <t xml:space="preserve">2.04573202133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06292700767517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05915236473083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0532808303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453896522522</t>
+    <t xml:space="preserve">2.06292676925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05915212631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05328106880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0545392036438</t>
   </si>
   <si>
     <t xml:space="preserve">2.0776047706604</t>
@@ -5204,13 +5204,13 @@
     <t xml:space="preserve">2.073410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0587329864502</t>
+    <t xml:space="preserve">2.05873274803162</t>
   </si>
   <si>
     <t xml:space="preserve">2.05202269554138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0058913230896</t>
+    <t xml:space="preserve">2.00589108467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.00043916702271</t>
@@ -5219,13 +5219,13 @@
     <t xml:space="preserve">2.02434396743774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08012127876282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07634711265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06544327735901</t>
+    <t xml:space="preserve">2.0801215171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07634687423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06544303894043</t>
   </si>
   <si>
     <t xml:space="preserve">2.07592749595642</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">2.10821962356567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09102535247803</t>
+    <t xml:space="preserve">2.09102511405945</t>
   </si>
   <si>
     <t xml:space="preserve">2.06418466567993</t>
@@ -5252,10 +5252,10 @@
     <t xml:space="preserve">2.03482842445374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0323121547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04657125473022</t>
+    <t xml:space="preserve">2.03231191635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04657101631165</t>
   </si>
   <si>
     <t xml:space="preserve">1.98156714439392</t>
@@ -5264,19 +5264,19 @@
     <t xml:space="preserve">1.98282539844513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01427888870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99330973625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03398966789246</t>
+    <t xml:space="preserve">2.01427865028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99330961704254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03398942947388</t>
   </si>
   <si>
     <t xml:space="preserve">2.04908728599548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05286145210266</t>
+    <t xml:space="preserve">2.05286169052124</t>
   </si>
   <si>
     <t xml:space="preserve">2.02686023712158</t>
@@ -5285,13 +5285,13 @@
     <t xml:space="preserve">2.03650593757629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99205148220062</t>
+    <t xml:space="preserve">1.9920517206192</t>
   </si>
   <si>
     <t xml:space="preserve">1.96605014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99079370498657</t>
+    <t xml:space="preserve">1.99079346656799</t>
   </si>
   <si>
     <t xml:space="preserve">1.97611498832703</t>
@@ -5309,19 +5309,19 @@
     <t xml:space="preserve">2.08934760093689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11702656745911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15015745162964</t>
+    <t xml:space="preserve">2.11702680587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15015769004822</t>
   </si>
   <si>
     <t xml:space="preserve">2.15225434303284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15057682991028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15435147285461</t>
+    <t xml:space="preserve">2.1505765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15435123443604</t>
   </si>
   <si>
     <t xml:space="preserve">2.16231966018677</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">2.18286919593811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20551538467407</t>
+    <t xml:space="preserve">2.20551562309265</t>
   </si>
   <si>
     <t xml:space="preserve">2.21893572807312</t>
@@ -5339,7 +5339,7 @@
     <t xml:space="preserve">2.21977472305298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25164747238159</t>
+    <t xml:space="preserve">2.25164723396301</t>
   </si>
   <si>
     <t xml:space="preserve">2.27114582061768</t>
@@ -5348,7 +5348,7 @@
     <t xml:space="preserve">2.23835301399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25209045410156</t>
+    <t xml:space="preserve">2.25209021568298</t>
   </si>
   <si>
     <t xml:space="preserve">2.26848697662354</t>
@@ -5357,19 +5357,19 @@
     <t xml:space="preserve">2.3039391040802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30438232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.326096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34559535980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34116363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36287784576416</t>
+    <t xml:space="preserve">2.30438208580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32609677314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34559559822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34116387367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36287808418274</t>
   </si>
   <si>
     <t xml:space="preserve">2.38858079910278</t>
@@ -5381,16 +5381,16 @@
     <t xml:space="preserve">2.39788699150085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37307047843933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39301228523254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38503551483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37705874443054</t>
+    <t xml:space="preserve">2.37307071685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39301252365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38503575325012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37705898284912</t>
   </si>
   <si>
     <t xml:space="preserve">2.37572956085205</t>
@@ -5402,28 +5402,28 @@
     <t xml:space="preserve">2.33540272712708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32653951644897</t>
+    <t xml:space="preserve">2.32653999328613</t>
   </si>
   <si>
     <t xml:space="preserve">2.35046982765198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3371753692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33097147941589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3460385799408</t>
+    <t xml:space="preserve">2.33717560768127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33097124099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34603834152222</t>
   </si>
   <si>
     <t xml:space="preserve">2.35445833206177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34204983711243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34293651580811</t>
+    <t xml:space="preserve">2.34205007553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34293627738953</t>
   </si>
   <si>
     <t xml:space="preserve">2.38813757896423</t>
@@ -5432,7 +5432,7 @@
     <t xml:space="preserve">2.38592195510864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44131588935852</t>
+    <t xml:space="preserve">2.44131565093994</t>
   </si>
   <si>
     <t xml:space="preserve">2.47056365013123</t>
@@ -5441,13 +5441,13 @@
     <t xml:space="preserve">2.47765421867371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44353127479553</t>
+    <t xml:space="preserve">2.44353151321411</t>
   </si>
   <si>
     <t xml:space="preserve">2.43599796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41694259643555</t>
+    <t xml:space="preserve">2.41694235801697</t>
   </si>
   <si>
     <t xml:space="preserve">2.41339731216431</t>
@@ -5462,7 +5462,7 @@
     <t xml:space="preserve">2.43732738494873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44220185279846</t>
+    <t xml:space="preserve">2.44220209121704</t>
   </si>
   <si>
     <t xml:space="preserve">2.45328068733215</t>
@@ -5477,7 +5477,7 @@
     <t xml:space="preserve">2.48873281478882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49139189720154</t>
+    <t xml:space="preserve">2.49139165878296</t>
   </si>
   <si>
     <t xml:space="preserve">2.46568894386292</t>
@@ -5510,22 +5510,22 @@
     <t xml:space="preserve">2.46879100799561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50247025489807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4869601726532</t>
+    <t xml:space="preserve">2.50247049331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48696041107178</t>
   </si>
   <si>
     <t xml:space="preserve">2.49538016319275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50690221786499</t>
+    <t xml:space="preserve">2.50690197944641</t>
   </si>
   <si>
     <t xml:space="preserve">2.50379991531372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51620817184448</t>
+    <t xml:space="preserve">2.5162079334259</t>
   </si>
   <si>
     <t xml:space="preserve">2.52551436424255</t>
@@ -5537,7 +5537,7 @@
     <t xml:space="preserve">2.5671706199646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60483813285828</t>
+    <t xml:space="preserve">2.6048378944397</t>
   </si>
   <si>
     <t xml:space="preserve">2.61857581138611</t>
@@ -5546,7 +5546,7 @@
     <t xml:space="preserve">2.61680340766907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61458778381348</t>
+    <t xml:space="preserve">2.6145875453949</t>
   </si>
   <si>
     <t xml:space="preserve">2.60395193099976</t>
@@ -5555,7 +5555,7 @@
     <t xml:space="preserve">2.66289091110229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6589024066925</t>
+    <t xml:space="preserve">2.65890264511108</t>
   </si>
   <si>
     <t xml:space="preserve">2.71252369880676</t>
@@ -5564,7 +5564,7 @@
     <t xml:space="preserve">2.75019145011902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73601055145264</t>
+    <t xml:space="preserve">2.73601078987122</t>
   </si>
   <si>
     <t xml:space="preserve">2.74974846839905</t>
@@ -5573,7 +5573,7 @@
     <t xml:space="preserve">2.72183012962341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78475737571716</t>
+    <t xml:space="preserve">2.78475713729858</t>
   </si>
   <si>
     <t xml:space="preserve">2.82109570503235</t>
@@ -5582,10 +5582,10 @@
     <t xml:space="preserve">2.81046009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86053609848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86186552047729</t>
+    <t xml:space="preserve">2.86053586006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86186575889587</t>
   </si>
   <si>
     <t xml:space="preserve">2.90352177619934</t>
@@ -5594,40 +5594,40 @@
     <t xml:space="preserve">2.899090051651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91858863830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92036151885986</t>
+    <t xml:space="preserve">2.91858887672424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92036128044128</t>
   </si>
   <si>
     <t xml:space="preserve">2.94384837150574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96511960029602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96733546257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98062992095947</t>
+    <t xml:space="preserve">2.96511936187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96733522415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98062968254089</t>
   </si>
   <si>
     <t xml:space="preserve">2.96689224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01608180999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00012826919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95049548149109</t>
+    <t xml:space="preserve">3.01608204841614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00012850761414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95049571990967</t>
   </si>
   <si>
     <t xml:space="preserve">2.97442579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93498539924622</t>
+    <t xml:space="preserve">2.93498563766479</t>
   </si>
   <si>
     <t xml:space="preserve">2.96910786628723</t>
@@ -5639,7 +5639,7 @@
     <t xml:space="preserve">2.91592979431152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94828009605408</t>
+    <t xml:space="preserve">2.94827961921692</t>
   </si>
   <si>
     <t xml:space="preserve">2.88225054740906</t>
@@ -5648,13 +5648,13 @@
     <t xml:space="preserve">2.92390656471252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96866488456726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03868246078491</t>
+    <t xml:space="preserve">2.96866464614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303793907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03868269920349</t>
   </si>
   <si>
     <t xml:space="preserve">3.11933588981628</t>
@@ -5681,16 +5681,16 @@
     <t xml:space="preserve">3.06837344169617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15789008140564</t>
+    <t xml:space="preserve">3.15788984298706</t>
   </si>
   <si>
     <t xml:space="preserve">3.18935370445251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18492221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17251420021057</t>
+    <t xml:space="preserve">3.18492197990417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17251372337341</t>
   </si>
   <si>
     <t xml:space="preserve">3.19112634658813</t>
@@ -5699,13 +5699,13 @@
     <t xml:space="preserve">3.21417021751404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2819721698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3032431602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30856132507324</t>
+    <t xml:space="preserve">3.28197193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30324339866638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30856108665466</t>
   </si>
   <si>
     <t xml:space="preserve">3.34046792984009</t>
@@ -5738,13 +5738,13 @@
     <t xml:space="preserve">3.33677363395691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33030867576599</t>
+    <t xml:space="preserve">3.33030891418457</t>
   </si>
   <si>
     <t xml:space="preserve">3.36170959472656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27628111839294</t>
+    <t xml:space="preserve">3.27628135681152</t>
   </si>
   <si>
     <t xml:space="preserve">3.2721254825592</t>
@@ -5753,7 +5753,7 @@
     <t xml:space="preserve">3.32569122314453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31276154518127</t>
+    <t xml:space="preserve">3.3127613067627</t>
   </si>
   <si>
     <t xml:space="preserve">3.29521417617798</t>
@@ -5762,7 +5762,7 @@
     <t xml:space="preserve">3.21070957183838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26058125495911</t>
+    <t xml:space="preserve">3.26058101654053</t>
   </si>
   <si>
     <t xml:space="preserve">3.15391159057617</t>
@@ -5777,7 +5777,7 @@
     <t xml:space="preserve">3.15760564804077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1954710483551</t>
+    <t xml:space="preserve">3.19547128677368</t>
   </si>
   <si>
     <t xml:space="preserve">3.22640991210938</t>
@@ -5786,10 +5786,10 @@
     <t xml:space="preserve">3.18900632858276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24765133857727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25688695907593</t>
+    <t xml:space="preserve">3.24765157699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25688672065735</t>
   </si>
   <si>
     <t xml:space="preserve">3.199627161026</t>
@@ -5804,13 +5804,13 @@
     <t xml:space="preserve">3.26011943817139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30583500862122</t>
+    <t xml:space="preserve">3.30583477020264</t>
   </si>
   <si>
     <t xml:space="preserve">3.27812838554382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2933669090271</t>
+    <t xml:space="preserve">3.29336714744568</t>
   </si>
   <si>
     <t xml:space="preserve">3.28136086463928</t>
@@ -5822,7 +5822,7 @@
     <t xml:space="preserve">3.31645584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34277677536011</t>
+    <t xml:space="preserve">3.34277653694153</t>
   </si>
   <si>
     <t xml:space="preserve">3.33215594291687</t>
@@ -5831,7 +5831,7 @@
     <t xml:space="preserve">3.34600901603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36909770965576</t>
+    <t xml:space="preserve">3.36909794807434</t>
   </si>
   <si>
     <t xml:space="preserve">3.38710713386536</t>
@@ -5864,7 +5864,7 @@
     <t xml:space="preserve">3.32800006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18115615844727</t>
+    <t xml:space="preserve">3.18115592002869</t>
   </si>
   <si>
     <t xml:space="preserve">3.15021729469299</t>
@@ -5885,16 +5885,16 @@
     <t xml:space="preserve">3.2051682472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22225403785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32199668884277</t>
+    <t xml:space="preserve">3.22225379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32199692726135</t>
   </si>
   <si>
     <t xml:space="preserve">3.33769726753235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31968832015991</t>
+    <t xml:space="preserve">3.31968808174133</t>
   </si>
   <si>
     <t xml:space="preserve">3.33954429626465</t>
@@ -5912,13 +5912,13 @@
     <t xml:space="preserve">3.41712236404419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41850757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44344305992126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47669100761414</t>
+    <t xml:space="preserve">3.41850733757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44344329833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47669076919556</t>
   </si>
   <si>
     <t xml:space="preserve">3.48500299453735</t>
@@ -5930,7 +5930,7 @@
     <t xml:space="preserve">3.43005180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4642231464386</t>
+    <t xml:space="preserve">3.46422290802002</t>
   </si>
   <si>
     <t xml:space="preserve">3.38618350028992</t>
@@ -5942,7 +5942,7 @@
     <t xml:space="preserve">3.40696310997009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41296625137329</t>
+    <t xml:space="preserve">3.41296601295471</t>
   </si>
   <si>
     <t xml:space="preserve">3.4485228061676</t>
@@ -5951,7 +5951,7 @@
     <t xml:space="preserve">3.46791744232178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45314073562622</t>
+    <t xml:space="preserve">3.45314049720764</t>
   </si>
   <si>
     <t xml:space="preserve">3.47715282440186</t>
@@ -5966,7 +5966,7 @@
     <t xml:space="preserve">3.53256559371948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4660701751709</t>
+    <t xml:space="preserve">3.46607041358948</t>
   </si>
   <si>
     <t xml:space="preserve">3.48869705200195</t>
@@ -5975,7 +5975,7 @@
     <t xml:space="preserve">3.57966637611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57458710670471</t>
+    <t xml:space="preserve">3.57458686828613</t>
   </si>
   <si>
     <t xml:space="preserve">3.54411005973816</t>
@@ -5999,7 +5999,7 @@
     <t xml:space="preserve">3.49654722213745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51686549186707</t>
+    <t xml:space="preserve">3.51686525344849</t>
   </si>
   <si>
     <t xml:space="preserve">3.55565404891968</t>
@@ -6014,10 +6014,10 @@
     <t xml:space="preserve">3.62999987602234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62030267715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66694164276123</t>
+    <t xml:space="preserve">3.62030243873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66694140434265</t>
   </si>
   <si>
     <t xml:space="preserve">3.69418621063232</t>
@@ -6029,7 +6029,7 @@
     <t xml:space="preserve">3.63046145439148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58705472946167</t>
+    <t xml:space="preserve">3.58705496788025</t>
   </si>
   <si>
     <t xml:space="preserve">3.58289885520935</t>
@@ -6047,16 +6047,16 @@
     <t xml:space="preserve">3.63600277900696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72512531280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75744938850403</t>
+    <t xml:space="preserve">3.7251250743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75744915008545</t>
   </si>
   <si>
     <t xml:space="preserve">3.78654074668884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66832661628723</t>
+    <t xml:space="preserve">3.66832685470581</t>
   </si>
   <si>
     <t xml:space="preserve">3.5602719783783</t>
@@ -6065,10 +6065,10 @@
     <t xml:space="preserve">3.54226279258728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60090780258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51270914077759</t>
+    <t xml:space="preserve">3.60090804100037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51270937919617</t>
   </si>
   <si>
     <t xml:space="preserve">3.53071856498718</t>
@@ -6732,6 +6732,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.50799989700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48000001907349</t>
   </si>
 </sst>
 </file>
@@ -71706,7 +71709,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6515509259</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>48222876</v>
@@ -71727,6 +71730,32 @@
         <v>2200</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.650162037</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>38242104</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>5.5019998550415</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>5.45100021362305</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>5.46999979019165</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>5.48000001907349</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>2240</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISP.MI.xlsx
+++ b/data/ISP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="2241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="2242">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,145 +44,145 @@
     <t xml:space="preserve">ISP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56040990352631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51831960678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4926552772522</t>
+    <t xml:space="preserve">1.56040978431702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5183197259903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49265503883362</t>
   </si>
   <si>
     <t xml:space="preserve">1.48752236366272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46699047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49676167964935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52447950839996</t>
+    <t xml:space="preserve">1.46699070930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49676144123077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52447915077209</t>
   </si>
   <si>
     <t xml:space="preserve">1.48546922206879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43824625015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36638534069061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38075733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3047901391983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36843848228455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39307618141174</t>
+    <t xml:space="preserve">1.4382461309433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3663854598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38075721263885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30479025840759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36843836307526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39307641983032</t>
   </si>
   <si>
     <t xml:space="preserve">1.35406613349915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37254452705383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35919940471649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2904177904129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380042552948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31505608558655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26988613605499</t>
+    <t xml:space="preserve">1.37254500389099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35919892787933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29041802883148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380030632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31505572795868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26988637447357</t>
   </si>
   <si>
     <t xml:space="preserve">1.20315825939178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27296590805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22368979454041</t>
+    <t xml:space="preserve">1.27296578884125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22368991374969</t>
   </si>
   <si>
     <t xml:space="preserve">1.17441380023956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10152614116669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26064705848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22984945774078</t>
+    <t xml:space="preserve">1.10152626037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26064717769623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2298492193222</t>
   </si>
   <si>
     <t xml:space="preserve">1.25243437290192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28220522403717</t>
+    <t xml:space="preserve">1.28220534324646</t>
   </si>
   <si>
     <t xml:space="preserve">1.21958351135254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19494557380676</t>
+    <t xml:space="preserve">1.19494569301605</t>
   </si>
   <si>
     <t xml:space="preserve">1.23395574092865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20110487937927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16004145145416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18057322502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20007860660553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20213139057159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22471642494202</t>
+    <t xml:space="preserve">1.20110511779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16004157066345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18057334423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20007824897766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20213174819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22471630573273</t>
   </si>
   <si>
     <t xml:space="preserve">1.27091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32224202156067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29555082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2647533416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27604568004608</t>
+    <t xml:space="preserve">1.32224225997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29555094242096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27604579925537</t>
   </si>
   <si>
     <t xml:space="preserve">1.2914445400238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3058168888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40334248542786</t>
+    <t xml:space="preserve">1.30581665039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40334212779999</t>
   </si>
   <si>
     <t xml:space="preserve">1.37459790706635</t>
@@ -203,64 +203,64 @@
     <t xml:space="preserve">1.29247117042542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25756728649139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23600888252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24935448169708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24114167690277</t>
+    <t xml:space="preserve">1.25756752490997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.236008644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24935472011566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24114179611206</t>
   </si>
   <si>
     <t xml:space="preserve">1.21753025054932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18673288822174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13540351390839</t>
+    <t xml:space="preserve">1.18673276901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1354033946991</t>
   </si>
   <si>
     <t xml:space="preserve">1.1487489938736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11076557636261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17749345302582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19802534580231</t>
+    <t xml:space="preserve">1.1107656955719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17749357223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1980254650116</t>
   </si>
   <si>
     <t xml:space="preserve">1.24422168731689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25038111209869</t>
+    <t xml:space="preserve">1.2503809928894</t>
   </si>
   <si>
     <t xml:space="preserve">1.2565404176712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26270020008087</t>
+    <t xml:space="preserve">1.262699842453</t>
   </si>
   <si>
     <t xml:space="preserve">1.24216830730438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27809882164001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23190248012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26680636405945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26783311367035</t>
+    <t xml:space="preserve">1.2780989408493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23190259933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26680648326874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26783299446106</t>
   </si>
   <si>
     <t xml:space="preserve">1.18878602981567</t>
@@ -275,22 +275,22 @@
     <t xml:space="preserve">1.14258968830109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14977562427521</t>
+    <t xml:space="preserve">1.14977550506592</t>
   </si>
   <si>
     <t xml:space="preserve">1.15798842906952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14566957950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14156305789948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1292439699173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12103128433228</t>
+    <t xml:space="preserve">1.14566946029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14156293869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12924408912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12103140354156</t>
   </si>
   <si>
     <t xml:space="preserve">1.15080225467682</t>
@@ -299,25 +299,25 @@
     <t xml:space="preserve">1.17852008342743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18775916099548</t>
+    <t xml:space="preserve">1.18775928020477</t>
   </si>
   <si>
     <t xml:space="preserve">1.18666672706604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.258784532547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28719449043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2970290184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26096975803375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24020886421204</t>
+    <t xml:space="preserve">1.25878441333771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28719437122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29702889919281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26096987724304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24020862579346</t>
   </si>
   <si>
     <t xml:space="preserve">1.23037457466125</t>
@@ -326,109 +326,109 @@
     <t xml:space="preserve">1.20852041244507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20414984226227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22491097450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21070575714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19977903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15060746669769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0828605890274</t>
+    <t xml:space="preserve">1.20414972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22491085529327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2107058763504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1997789144516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15060770511627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08286082744598</t>
   </si>
   <si>
     <t xml:space="preserve">1.04516267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07466554641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06537747383118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11454892158508</t>
+    <t xml:space="preserve">1.07466542720795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06537759304047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11454880237579</t>
   </si>
   <si>
     <t xml:space="preserve">1.14842224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17683255672455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17573976516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23365247249603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950644612312317</t>
+    <t xml:space="preserve">1.17683219909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17573964595795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23365259170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950644552707672</t>
   </si>
   <si>
     <t xml:space="preserve">0.846838653087616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88726818561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900380551815033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929883301258087</t>
+    <t xml:space="preserve">0.887268126010895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900380611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929883360862732</t>
   </si>
   <si>
     <t xml:space="preserve">0.917863786220551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.889999985694885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870331466197968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868692457675934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87415611743927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961571335792542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983425498008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04789447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03587472438812</t>
+    <t xml:space="preserve">0.889999866485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870331525802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868692338466644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874155819416046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961571574211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983425140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04789423942566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03587460517883</t>
   </si>
   <si>
     <t xml:space="preserve">1.05772864818573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05499672889709</t>
+    <t xml:space="preserve">1.05499696731567</t>
   </si>
   <si>
     <t xml:space="preserve">1.05718219280243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05062592029572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06373834609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06701648235321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06865572929382</t>
+    <t xml:space="preserve">1.05062615871429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06373846530914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0670166015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06865561008453</t>
   </si>
   <si>
     <t xml:space="preserve">1.04898715019226</t>
@@ -437,28 +437,28 @@
     <t xml:space="preserve">1.05335783958435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0719336271286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03969931602478</t>
+    <t xml:space="preserve">1.07193374633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03969919681549</t>
   </si>
   <si>
     <t xml:space="preserve">1.07630455493927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03860640525818</t>
+    <t xml:space="preserve">1.03860652446747</t>
   </si>
   <si>
     <t xml:space="preserve">0.999269545078278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993805944919586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994352400302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03806006908417</t>
+    <t xml:space="preserve">0.993806004524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994352579116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03806018829346</t>
   </si>
   <si>
     <t xml:space="preserve">1.05117249488831</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">1.07958257198334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05827498435974</t>
+    <t xml:space="preserve">1.05827486515045</t>
   </si>
   <si>
     <t xml:space="preserve">1.03041136264801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00964987277985</t>
+    <t xml:space="preserve">1.00965011119843</t>
   </si>
   <si>
     <t xml:space="preserve">1.05991411209106</t>
@@ -485,49 +485,49 @@
     <t xml:space="preserve">1.09214842319489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08231425285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10034358501434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08996295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11673426628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1637202501297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19759368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19212996959686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16809070110321</t>
+    <t xml:space="preserve">1.08231449127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10034370422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08996319770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11673414707184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16372013092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19759356975555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19213008880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1680908203125</t>
   </si>
   <si>
     <t xml:space="preserve">1.17901790142059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18338847160339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15934932231903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13749527931213</t>
+    <t xml:space="preserve">1.18338871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15934920310974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13749551773071</t>
   </si>
   <si>
     <t xml:space="preserve">1.1364027261734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12766098976135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09706568717957</t>
+    <t xml:space="preserve">1.12766110897064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09706556797028</t>
   </si>
   <si>
     <t xml:space="preserve">1.11236333847046</t>
@@ -536,115 +536,115 @@
     <t xml:space="preserve">1.12656855583191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09050941467285</t>
+    <t xml:space="preserve">1.09050965309143</t>
   </si>
   <si>
     <t xml:space="preserve">1.0779435634613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06428492069244</t>
+    <t xml:space="preserve">1.06428480148315</t>
   </si>
   <si>
     <t xml:space="preserve">1.0615531206131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06319224834442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07848989963531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05445051193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08941686153412</t>
+    <t xml:space="preserve">1.06319212913513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07848966121674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05445075035095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08941674232483</t>
   </si>
   <si>
     <t xml:space="preserve">1.0937876701355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07685089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08340716362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12329018115997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.130939245224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15170037746429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15388596057892</t>
+    <t xml:space="preserve">1.07685077190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08340692520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12329030036926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13093912601471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15170049667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15388572216034</t>
   </si>
   <si>
     <t xml:space="preserve">1.17792499065399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20196437835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18229603767395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15279293060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13858819007874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09925127029419</t>
+    <t xml:space="preserve">1.20196449756622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18229591846466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15279316902161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13858807086945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0992511510849</t>
   </si>
   <si>
     <t xml:space="preserve">1.09597301483154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16044187545776</t>
+    <t xml:space="preserve">1.16044199466705</t>
   </si>
   <si>
     <t xml:space="preserve">1.16918361186981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22054016590118</t>
+    <t xml:space="preserve">1.22054004669189</t>
   </si>
   <si>
     <t xml:space="preserve">1.21835482120514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15497851371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1418662071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11891973018646</t>
+    <t xml:space="preserve">1.15497863292694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14186608791351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11891961097717</t>
   </si>
   <si>
     <t xml:space="preserve">1.10362184047699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06810915470123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11345613002777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14514410495758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24567210674286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26643335819244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30904853343964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27845299243927</t>
+    <t xml:space="preserve">1.06810927391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11345624923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14514446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24567198753357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26643347740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30904829502106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27845311164856</t>
   </si>
   <si>
     <t xml:space="preserve">1.32762432098389</t>
@@ -656,127 +656,127 @@
     <t xml:space="preserve">1.33636593818665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31888294219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33745837211609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33855140209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34401488304138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964419364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871699333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31778991222382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32543909549713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36805403232574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38772237300873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39755666255951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38990807533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35275626182556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34838545322418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34620022773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34729266166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3221607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34292185306549</t>
+    <t xml:space="preserve">1.31888282299042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3374582529068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855152130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34401476383209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964395523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871687412262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3177901506424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32543897628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36805379390717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38772261142731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39755690097809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38990795612335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35275602340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34838557243347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34619987010956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34729278087616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32216084003448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34292197227478</t>
   </si>
   <si>
     <t xml:space="preserve">1.3494781255722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31014132499695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25222849845886</t>
+    <t xml:space="preserve">1.31014120578766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25222826004028</t>
   </si>
   <si>
     <t xml:space="preserve">1.25659906864166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22928178310394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23911595344543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20087170600891</t>
+    <t xml:space="preserve">1.22928190231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23911619186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20087158679962</t>
   </si>
   <si>
     <t xml:space="preserve">1.18557405471802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19103765487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22272551059723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19322276115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17027604579926</t>
+    <t xml:space="preserve">1.19103741645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22272562980652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19322299957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17027628421783</t>
   </si>
   <si>
     <t xml:space="preserve">1.1735543012619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16590547561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17136895656586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19650101661682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18120300769806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13421738147736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25113558769226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27626764774323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26861870288849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189695835114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27408218383789</t>
+    <t xml:space="preserve">1.16590535640717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17136907577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19650113582611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18120324611664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13421714305878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25113570690155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2762678861618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2686185836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189707756042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27408230304718</t>
   </si>
   <si>
     <t xml:space="preserve">1.30577051639557</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">1.3232536315918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35057067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35603451728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36914658546448</t>
+    <t xml:space="preserve">1.35057079792023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35603439807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36914682388306</t>
   </si>
   <si>
     <t xml:space="preserve">1.39100050926208</t>
@@ -809,19 +809,19 @@
     <t xml:space="preserve">1.37679553031921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38007378578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37898099422455</t>
+    <t xml:space="preserve">1.38007390499115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37898087501526</t>
   </si>
   <si>
     <t xml:space="preserve">1.37461018562317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36696135997772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384905338287</t>
+    <t xml:space="preserve">1.36696147918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384893417358</t>
   </si>
   <si>
     <t xml:space="preserve">1.33199501037598</t>
@@ -830,28 +830,28 @@
     <t xml:space="preserve">1.30467784404755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35166347026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36040508747101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37351751327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47623085975647</t>
+    <t xml:space="preserve">1.35166370868683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36040532588959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37351763248444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47623074054718</t>
   </si>
   <si>
     <t xml:space="preserve">1.50573360919952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49480652809143</t>
+    <t xml:space="preserve">1.49480664730072</t>
   </si>
   <si>
     <t xml:space="preserve">1.45984041690826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46093285083771</t>
+    <t xml:space="preserve">1.46093332767487</t>
   </si>
   <si>
     <t xml:space="preserve">1.46311843395233</t>
@@ -860,79 +860,79 @@
     <t xml:space="preserve">1.47076737880707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5079185962677</t>
+    <t xml:space="preserve">1.50791919231415</t>
   </si>
   <si>
     <t xml:space="preserve">1.55271947383881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5581830739975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55599796772003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55709028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5472559928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54507064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55162692070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52868020534515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52212405204773</t>
+    <t xml:space="preserve">1.55818295478821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55599772930145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5570901632309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54725587368011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54507052898407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55162680149078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52868008613586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52212393283844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52977299690247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56594610214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57061350345612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56711292266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55427742004395</t>
   </si>
   <si>
     <t xml:space="preserve">1.52977275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56594586372375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57061362266541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56711280345917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55427730083466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5297726392746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49826717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48893213272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4865984916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50060105323792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51110303401947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49126625061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48426496982574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4994341135025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50876903533936</t>
+    <t xml:space="preserve">1.49826729297638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48893237113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659861087799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50060141086578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5111026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49126589298248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48426485061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49943399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50876915454865</t>
   </si>
   <si>
     <t xml:space="preserve">1.50176799297333</t>
@@ -944,43 +944,43 @@
     <t xml:space="preserve">1.49710035324097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47843039035797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51460373401642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5251053571701</t>
+    <t xml:space="preserve">1.47843050956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51460313796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52510547637939</t>
   </si>
   <si>
     <t xml:space="preserve">1.52627229690552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57994842529297</t>
+    <t xml:space="preserve">1.57994830608368</t>
   </si>
   <si>
     <t xml:space="preserve">1.60795366764069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64062583446503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61845541000366</t>
+    <t xml:space="preserve">1.64062595367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61845517158508</t>
   </si>
   <si>
     <t xml:space="preserve">1.61962223052979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66279673576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65929615497589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6721316576004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65696227550507</t>
+    <t xml:space="preserve">1.66279649734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6592960357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67213177680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65696239471436</t>
   </si>
   <si>
     <t xml:space="preserve">1.66863095760345</t>
@@ -989,328 +989,328 @@
     <t xml:space="preserve">1.6534618139267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66163003444672</t>
+    <t xml:space="preserve">1.66162991523743</t>
   </si>
   <si>
     <t xml:space="preserve">1.66396355628967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67096471786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67446517944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6662974357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67329859733582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68380033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69313502311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69546890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69430255889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69896960258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70130360126495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69196856021881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70363736152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70830464363098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70480406284332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263351917267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67796623706818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66046273708344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70713782310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68963479995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64295947551727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65462839603424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65812921524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63712513446808</t>
+    <t xml:space="preserve">1.6709645986557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67446529865265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66629731655121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67329847812653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6838002204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69313526153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69546902179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69430243968964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69896972179413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70130348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6919686794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7036372423172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70830476284027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70480418205261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263363838196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67796611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66046285629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70713818073273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68963444232941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64295959472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65462863445282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65812909603119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63712525367737</t>
   </si>
   <si>
     <t xml:space="preserve">1.6651303768158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68146646022797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70013678073883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71063852310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71763968467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73280930519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73397588729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72464120388031</t>
+    <t xml:space="preserve">1.68146681785583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70013666152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71063840389252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71763956546783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73280894756317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73397600650787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72464084625244</t>
   </si>
   <si>
     <t xml:space="preserve">1.735142827034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74447798728943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74214398860931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74564468860626</t>
+    <t xml:space="preserve">1.74447774887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74214422702789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74564504623413</t>
   </si>
   <si>
     <t xml:space="preserve">1.74681174755096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7409770488739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71180522441864</t>
+    <t xml:space="preserve">1.74097728729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71180534362793</t>
   </si>
   <si>
     <t xml:space="preserve">1.71530604362488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70947158336639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6849672794342</t>
+    <t xml:space="preserve">1.70947194099426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68496739864349</t>
   </si>
   <si>
     <t xml:space="preserve">1.66746401786804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68029975891113</t>
+    <t xml:space="preserve">1.68029963970184</t>
   </si>
   <si>
     <t xml:space="preserve">1.70597088336945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67913293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65112793445587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.633624792099</t>
+    <t xml:space="preserve">1.67913281917572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65112769603729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63362491130829</t>
   </si>
   <si>
     <t xml:space="preserve">1.63479161262512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61728847026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61495471000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64412653446198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61378788948059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6452933549881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64646065235138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67563223838806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63829231262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62895703315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62662363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62779021263123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61612164974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6067863702774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60445284843445</t>
+    <t xml:space="preserve">1.61728870868683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.614954829216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64412665367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61378800868988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64529347419739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64646029472351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67563199996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63829243183136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62895739078522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62662374973297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62779033184052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61612153053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60678672790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60445308685303</t>
   </si>
   <si>
     <t xml:space="preserve">1.74331104755402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76548182964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77248275279999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77598345279694</t>
+    <t xml:space="preserve">1.76548159122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77248299121857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77598369121552</t>
   </si>
   <si>
     <t xml:space="preserve">1.78415167331696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80515539646149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80165505409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82382500171661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82499241828918</t>
+    <t xml:space="preserve">1.80515551567078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80165481567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8238251209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82499206066132</t>
   </si>
   <si>
     <t xml:space="preserve">1.79815399646759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82149171829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84366238117218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824823379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83549404144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84395408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111822605133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81769943237305</t>
+    <t xml:space="preserve">1.82149147987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84366226196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824811458588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83549416065216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84395384788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111810684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81769967079163</t>
   </si>
   <si>
     <t xml:space="preserve">1.79902911186218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81098961830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87283420562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83636939525604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81157302856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377853870392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80923938751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8069052696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83053505420685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81303191184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223834514618</t>
+    <t xml:space="preserve">1.81098985671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87283396720886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83636951446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81157338619232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377830028534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8092395067215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80690550804138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83053493499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81303179264069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223798751831</t>
   </si>
   <si>
     <t xml:space="preserve">1.80748915672302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78444337844849</t>
+    <t xml:space="preserve">1.78444349765778</t>
   </si>
   <si>
     <t xml:space="preserve">1.79873752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79990434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80982279777527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8063223361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79290318489075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75410461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72930812835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74535286426544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76519000530243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77510857582092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78035938739777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74885392189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76081418991089</t>
+    <t xml:space="preserve">1.79990410804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80982267856598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80632221698761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79290306568146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75410485267639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72930836677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74535298347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76519012451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77510833740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78035914897919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540004253387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74885368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76081383228302</t>
   </si>
   <si>
     <t xml:space="preserve">1.79523682594299</t>
@@ -1319,193 +1319,193 @@
     <t xml:space="preserve">1.77364957332611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78473484516144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77423298358917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74272775650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72259914875031</t>
+    <t xml:space="preserve">1.78473520278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77423286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74272763729095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72259902954102</t>
   </si>
   <si>
     <t xml:space="preserve">1.7074294090271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72289061546326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72318255901337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7252242565155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71909821033478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75206255912781</t>
+    <t xml:space="preserve">1.72289073467255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72318232059479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72522437572479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71909844875336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75206232070923</t>
   </si>
   <si>
     <t xml:space="preserve">1.74768674373627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76256430149078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77131605148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75906407833099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77948391437531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78940260410309</t>
+    <t xml:space="preserve">1.76256442070007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77131593227386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7590639591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77948415279388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78940272331238</t>
   </si>
   <si>
     <t xml:space="preserve">1.79465341567993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81449031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8153657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8290764093399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84832954406738</t>
+    <t xml:space="preserve">1.81449043750763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81536543369293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82907605171204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84832978248596</t>
   </si>
   <si>
     <t xml:space="preserve">1.86437404155731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83986985683441</t>
+    <t xml:space="preserve">1.83986961841583</t>
   </si>
   <si>
     <t xml:space="preserve">1.85124683380127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83957839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84191191196442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84862148761749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83811962604523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84453725814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83403587341309</t>
+    <t xml:space="preserve">1.83957827091217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.841912150383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84862124919891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83811938762665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84453749656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83403563499451</t>
   </si>
   <si>
     <t xml:space="preserve">1.82674241065979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83782804012299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85416376590729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80865633487701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79436182975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031197071075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73967373371124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75156378746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72090041637421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70494318008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65081286430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59730875492096</t>
+    <t xml:space="preserve">1.83782815933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85416412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80865609645844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7943617105484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031244754791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73967385292053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75156366825104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72090065479279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70494282245636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6508127450943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59730851650238</t>
   </si>
   <si>
     <t xml:space="preserve">1.53191411495209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57759618759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57352864742279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62546861171722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62515568733215</t>
+    <t xml:space="preserve">1.57759630680084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57352888584137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62546873092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62515580654144</t>
   </si>
   <si>
     <t xml:space="preserve">1.56289041042328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55475497245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53629457950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51752126216888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61827206611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6173335313797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62578141689301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62327837944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59417974948883</t>
+    <t xml:space="preserve">1.55475544929504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53629469871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51752114295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61827218532562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61733341217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62578165531158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6232784986496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59417951107025</t>
   </si>
   <si>
     <t xml:space="preserve">1.59793424606323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60575664043427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63548135757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60325360298157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61952364444733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56695818901062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5506876707077</t>
+    <t xml:space="preserve">1.60575652122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63548147678375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6032532453537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56695795059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55068778991699</t>
   </si>
   <si>
     <t xml:space="preserve">1.52690815925598</t>
@@ -1514,79 +1514,79 @@
     <t xml:space="preserve">1.55694544315338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55600702762604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54474258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57634484767914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58416712284088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60513091087341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6029406785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60606944561005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58041262626648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54881024360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53066265583038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973662853241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53660750389099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55193936824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54161381721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51658272743225</t>
+    <t xml:space="preserve">1.55600678920746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54474294185638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57634472846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58416724205017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60513079166412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60294044017792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60606920719147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58041250705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54881036281586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53066289424896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973650932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53660786151886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5519392490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54161417484283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51658236980438</t>
   </si>
   <si>
     <t xml:space="preserve">1.5053186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50250244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53097569942474</t>
+    <t xml:space="preserve">1.50250232219696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53097546100616</t>
   </si>
   <si>
     <t xml:space="preserve">1.55037462711334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57039999961853</t>
+    <t xml:space="preserve">1.57039976119995</t>
   </si>
   <si>
     <t xml:space="preserve">1.58322858810425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6483097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57259011268616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51188945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53003704547882</t>
+    <t xml:space="preserve">1.64830958843231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57259023189545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51188933849335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53003692626953</t>
   </si>
   <si>
     <t xml:space="preserve">1.50844752788544</t>
@@ -1595,31 +1595,31 @@
     <t xml:space="preserve">1.49248993396759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43804717063904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41426730155945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40175151824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37640762329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36576926708221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35732102394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40331625938416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38329100608826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37672030925751</t>
+    <t xml:space="preserve">1.43804693222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41426742076874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40175139904022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37640726566315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36576902866364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35732114315033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40331614017487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38329112529755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37672054767609</t>
   </si>
   <si>
     <t xml:space="preserve">1.37891066074371</t>
@@ -1628,85 +1628,85 @@
     <t xml:space="preserve">1.37859773635864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36357867717743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38172650337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34918594360352</t>
+    <t xml:space="preserve">1.36357879638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38172662258148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34918570518494</t>
   </si>
   <si>
     <t xml:space="preserve">1.3313512802124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35857284069061</t>
+    <t xml:space="preserve">1.35857272148132</t>
   </si>
   <si>
     <t xml:space="preserve">1.42897319793701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4590106010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43929874897003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41583156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47997426986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45650768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46432971954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45744633674622</t>
+    <t xml:space="preserve">1.45901048183441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43929851055145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41583180427551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47997450828552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.456507563591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46432995796204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45744645595551</t>
   </si>
   <si>
     <t xml:space="preserve">1.46683311462402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50093793869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49906086921692</t>
+    <t xml:space="preserve">1.50093805789948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49906063079834</t>
   </si>
   <si>
     <t xml:space="preserve">1.51908564567566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51157629489899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53222715854645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49999964237213</t>
+    <t xml:space="preserve">1.5115761756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53222727775574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49999928474426</t>
   </si>
   <si>
     <t xml:space="preserve">1.54568147659302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52221465110779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50438010692596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37734603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32352876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31914842128754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32634472846985</t>
+    <t xml:space="preserve">1.5222145318985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50437998771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37734627723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32352888584137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31914854049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32634484767914</t>
   </si>
   <si>
     <t xml:space="preserve">1.35481798648834</t>
@@ -1715,31 +1715,31 @@
     <t xml:space="preserve">1.31320345401764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27033734321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29818487167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30506801605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27284061908722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26783418655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27753376960754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29536867141724</t>
+    <t xml:space="preserve">1.27033746242523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29818475246429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30506837368011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27284049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26783430576324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27753400802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29536855220795</t>
   </si>
   <si>
     <t xml:space="preserve">1.28066265583038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2384227514267</t>
+    <t xml:space="preserve">1.23842263221741</t>
   </si>
   <si>
     <t xml:space="preserve">1.24167668819427</t>
@@ -1748,46 +1748,46 @@
     <t xml:space="preserve">1.23128867149353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23166394233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18936121463776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22227728366852</t>
+    <t xml:space="preserve">1.23166418075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18936133384705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22227740287781</t>
   </si>
   <si>
     <t xml:space="preserve">1.21264040470123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.249436378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24655771255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22215211391449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24267792701721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25563168525696</t>
+    <t xml:space="preserve">1.24943614006042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24655759334564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22215223312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24267780780792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25563156604767</t>
   </si>
   <si>
     <t xml:space="preserve">1.23667025566101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25250267982483</t>
+    <t xml:space="preserve">1.25250244140625</t>
   </si>
   <si>
     <t xml:space="preserve">1.28598201274872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26971185207367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25500583648682</t>
+    <t xml:space="preserve">1.26971173286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25500571727753</t>
   </si>
   <si>
     <t xml:space="preserve">1.22665774822235</t>
@@ -1796,46 +1796,46 @@
     <t xml:space="preserve">1.25312840938568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23829758167267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2226527929306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20112586021423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20538127422333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17571914196014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20901083946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20888543128967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22165143489838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27690815925598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27628254890442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28535616397858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27190184593201</t>
+    <t xml:space="preserve">1.23829734325409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22265291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20112597942352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20538139343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17571926116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20901072025299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20888555049896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22165167331696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2769079208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27628231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28535628318787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2719019651413</t>
   </si>
   <si>
     <t xml:space="preserve">1.28160166740417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32196438312531</t>
+    <t xml:space="preserve">1.32196426391602</t>
   </si>
   <si>
     <t xml:space="preserve">1.29161393642426</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">1.23491811752319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24029970169067</t>
+    <t xml:space="preserve">1.24029994010925</t>
   </si>
   <si>
     <t xml:space="preserve">1.21376669406891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21026241779327</t>
+    <t xml:space="preserve">1.21026217937469</t>
   </si>
   <si>
     <t xml:space="preserve">1.25969910621643</t>
@@ -1865,70 +1865,70 @@
     <t xml:space="preserve">1.26032471656799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23466777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24217736721039</t>
+    <t xml:space="preserve">1.23466801643372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24217712879181</t>
   </si>
   <si>
     <t xml:space="preserve">1.26345384120941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2171459197998</t>
+    <t xml:space="preserve">1.21714603900909</t>
   </si>
   <si>
     <t xml:space="preserve">1.19662034511566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1946177482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21389186382294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19299066066742</t>
+    <t xml:space="preserve">1.19461786746979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21389198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19299077987671</t>
   </si>
   <si>
     <t xml:space="preserve">1.18986189365387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25106346607208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27221488952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25750875473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26470518112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25844752788544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24017465114594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22465538978577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2600120306015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27565658092499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27596938610077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26814723014832</t>
+    <t xml:space="preserve">1.25106334686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27221477031708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25750887393951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26470541954041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25844740867615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24017477035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22465527057648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26001226902008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27565670013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27596962451935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26814711093903</t>
   </si>
   <si>
     <t xml:space="preserve">1.26908576488495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29192674160004</t>
+    <t xml:space="preserve">1.29192709922791</t>
   </si>
   <si>
     <t xml:space="preserve">1.28003716468811</t>
@@ -1937,31 +1937,31 @@
     <t xml:space="preserve">1.28191435337067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28973698616028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24830985069275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22815978527069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22753369808197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24705827236176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24180197715759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23616969585419</t>
+    <t xml:space="preserve">1.28973662853241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24830973148346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22815954685211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22753393650055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24705862998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2418018579483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23616981506348</t>
   </si>
   <si>
     <t xml:space="preserve">1.25131368637085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25531888008118</t>
+    <t xml:space="preserve">1.25531852245331</t>
   </si>
   <si>
     <t xml:space="preserve">1.24155139923096</t>
@@ -1970,151 +1970,151 @@
     <t xml:space="preserve">1.28097569942474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29223966598511</t>
+    <t xml:space="preserve">1.2922397851944</t>
   </si>
   <si>
     <t xml:space="preserve">1.28629493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28692066669464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2765953540802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2778468132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30444276332855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.299436211586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33385419845581</t>
+    <t xml:space="preserve">1.28692054748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27659523487091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27784693241119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30444252490997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29943645000458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3338543176651</t>
   </si>
   <si>
     <t xml:space="preserve">1.35043752193451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35513067245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35262775421143</t>
+    <t xml:space="preserve">1.35513091087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35262787342072</t>
   </si>
   <si>
     <t xml:space="preserve">1.36545622348785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33510613441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32603192329407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33760893344879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33667004108429</t>
+    <t xml:space="preserve">1.33510601520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32603204250336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33760905265808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33667027950287</t>
   </si>
   <si>
     <t xml:space="preserve">1.34824728965759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35794711112976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37609457969666</t>
+    <t xml:space="preserve">1.35794699192047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37609446048737</t>
   </si>
   <si>
     <t xml:space="preserve">1.39737129211426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3992486000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39549386501312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38610708713531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34949886798859</t>
+    <t xml:space="preserve">1.39924848079681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39549374580383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38610696792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34949910640717</t>
   </si>
   <si>
     <t xml:space="preserve">1.34480535984039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34136390686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35168933868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35419225692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38016211986542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3754688501358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38767147064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39799690246582</t>
+    <t xml:space="preserve">1.34136378765106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3516891002655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35419237613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38016200065613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37546873092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38767170906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39799678325653</t>
   </si>
   <si>
     <t xml:space="preserve">1.39956140518188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39017474651337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3983097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4399242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45337867736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46558129787445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45963668823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45244002342224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42365396022797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42490577697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42991173267365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45932352542877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46245229244232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45619463920593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45306575298309</t>
+    <t xml:space="preserve">1.39017462730408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39830982685089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43992447853088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45337879657745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46558165550232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45963633060455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45243990421295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42365419864655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42490565776825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42991197109222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45932376384735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4624525308609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45619451999664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4530656337738</t>
   </si>
   <si>
     <t xml:space="preserve">1.4327278137207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40300309658051</t>
+    <t xml:space="preserve">1.40300321578979</t>
   </si>
   <si>
     <t xml:space="preserve">1.38673281669617</t>
@@ -2123,43 +2123,43 @@
     <t xml:space="preserve">1.35450518131256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35137629508972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32540619373322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34543144702911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36639499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35825979709625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36135685443878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36066877841949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33630466461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3097380399704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32061266899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31331729888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29872632026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28413546085358</t>
+    <t xml:space="preserve">1.35137605667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3254063129425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34543132781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36639487743378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35825991630554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36135697364807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36066854000092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33630454540253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30973827838898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3206125497818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31331706047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29872620105743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28413534164429</t>
   </si>
   <si>
     <t xml:space="preserve">1.28372251987457</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">1.26211142539978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25674307346344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28441071510315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27326118946075</t>
+    <t xml:space="preserve">1.25674319267273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28441059589386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27326095104218</t>
   </si>
   <si>
     <t xml:space="preserve">1.2570184469223</t>
@@ -2186,25 +2186,25 @@
     <t xml:space="preserve">1.27037024497986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27133405208588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2581193447113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26775503158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26458895206451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26018416881561</t>
+    <t xml:space="preserve">1.2713338136673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25811946392059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2677549123764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26458919048309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2601842880249</t>
   </si>
   <si>
     <t xml:space="preserve">1.2893660068512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.312628865242</t>
+    <t xml:space="preserve">1.31262898445129</t>
   </si>
   <si>
     <t xml:space="preserve">1.30134153366089</t>
@@ -2213,37 +2213,37 @@
     <t xml:space="preserve">1.29046726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29032957553864</t>
+    <t xml:space="preserve">1.29032969474792</t>
   </si>
   <si>
     <t xml:space="preserve">1.28592479228973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29239428043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29294502735138</t>
+    <t xml:space="preserve">1.29239439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29294490814209</t>
   </si>
   <si>
     <t xml:space="preserve">1.29528498649597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28537392616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2973495721817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36328399181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39439272880554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852249622345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38854277133942</t>
+    <t xml:space="preserve">1.28537404537201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29734969139099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36328387260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39439296722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39852237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38854265213013</t>
   </si>
   <si>
     <t xml:space="preserve">1.38097202777863</t>
@@ -2252,25 +2252,25 @@
     <t xml:space="preserve">1.39783406257629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41469633579254</t>
+    <t xml:space="preserve">1.41469621658325</t>
   </si>
   <si>
     <t xml:space="preserve">1.41159915924072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40987861156464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4191700220108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40609323978424</t>
+    <t xml:space="preserve">1.40987837314606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41916990280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40609312057495</t>
   </si>
   <si>
     <t xml:space="preserve">1.41091084480286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38200426101685</t>
+    <t xml:space="preserve">1.38200414180756</t>
   </si>
   <si>
     <t xml:space="preserve">1.3844131231308</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">1.3902633190155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38338077068329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37044167518616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35309791564941</t>
+    <t xml:space="preserve">1.38338100910187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37044191360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35309779644012</t>
   </si>
   <si>
     <t xml:space="preserve">1.34924364089966</t>
@@ -2297,46 +2297,46 @@
     <t xml:space="preserve">1.37649834156036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34387528896332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35433673858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33836936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31455600261688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33891987800598</t>
+    <t xml:space="preserve">1.3438755273819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35433685779572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33836960792542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31455612182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33891999721527</t>
   </si>
   <si>
     <t xml:space="preserve">1.26362562179565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29886376857758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27023279666901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31744658946991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31001365184784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32322776317596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33644223213196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30987572669983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33520364761353</t>
+    <t xml:space="preserve">1.29886388778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2702329158783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31744647026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31001353263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32322788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33644235134125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30987596511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33520352840424</t>
   </si>
   <si>
     <t xml:space="preserve">1.34084713459015</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">1.35488748550415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38578963279724</t>
+    <t xml:space="preserve">1.38578975200653</t>
   </si>
   <si>
     <t xml:space="preserve">1.3718181848526</t>
@@ -2354,28 +2354,28 @@
     <t xml:space="preserve">1.37890732288361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37684237957001</t>
+    <t xml:space="preserve">1.3768424987793</t>
   </si>
   <si>
     <t xml:space="preserve">1.39542508125305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41504049301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42261123657227</t>
+    <t xml:space="preserve">1.4150402545929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42261111736298</t>
   </si>
   <si>
     <t xml:space="preserve">1.44635570049286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46149706840515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45082926750183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46080887317657</t>
+    <t xml:space="preserve">1.46149718761444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45082938671112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46080911159515</t>
   </si>
   <si>
     <t xml:space="preserve">1.50175964832306</t>
@@ -2387,34 +2387,34 @@
     <t xml:space="preserve">1.46252954006195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46321749687195</t>
+    <t xml:space="preserve">1.46321761608124</t>
   </si>
   <si>
     <t xml:space="preserve">1.48937141895294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49074757099152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319746017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46597111225128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46941196918488</t>
+    <t xml:space="preserve">1.4907478094101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319757938385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4659708738327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46941184997559</t>
   </si>
   <si>
     <t xml:space="preserve">1.47491800785065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48696231842041</t>
+    <t xml:space="preserve">1.4869624376297</t>
   </si>
   <si>
     <t xml:space="preserve">1.49728608131409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48317718505859</t>
+    <t xml:space="preserve">1.48317694664001</t>
   </si>
   <si>
     <t xml:space="preserve">1.44119393825531</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">1.44222629070282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43568789958954</t>
+    <t xml:space="preserve">1.43568778038025</t>
   </si>
   <si>
     <t xml:space="preserve">1.4477322101593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47939157485962</t>
+    <t xml:space="preserve">1.47939145565033</t>
   </si>
   <si>
     <t xml:space="preserve">1.50451278686523</t>
@@ -2444,25 +2444,25 @@
     <t xml:space="preserve">1.52103078365326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54064583778381</t>
+    <t xml:space="preserve">1.5406459569931</t>
   </si>
   <si>
     <t xml:space="preserve">1.53582799434662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53789281845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55062544345856</t>
+    <t xml:space="preserve">1.53789269924164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55062556266785</t>
   </si>
   <si>
     <t xml:space="preserve">1.56576693058014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56232583522797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56301379203796</t>
+    <t xml:space="preserve">1.56232559680939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56301391124725</t>
   </si>
   <si>
     <t xml:space="preserve">1.56404638290405</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">1.56817579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56370222568512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54752838611603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54580783843994</t>
+    <t xml:space="preserve">1.56370234489441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54752850532532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54580771923065</t>
   </si>
   <si>
     <t xml:space="preserve">1.5643904209137</t>
@@ -2486,40 +2486,40 @@
     <t xml:space="preserve">1.58710253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61050283908844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60878241062164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62151503562927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256802082062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62220370769501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63665664196014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61394441127777</t>
+    <t xml:space="preserve">1.6105033159256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60878252983093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62151515483856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256778240204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62220346927643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63665640354156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61394453048706</t>
   </si>
   <si>
     <t xml:space="preserve">1.60086750984192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60912668704987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61738574504852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61566507816315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62013876438141</t>
+    <t xml:space="preserve">1.60912644863129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61738562583923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61566495895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62013864517212</t>
   </si>
   <si>
     <t xml:space="preserve">1.61291182041168</t>
@@ -2528,34 +2528,34 @@
     <t xml:space="preserve">1.61910617351532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61187958717346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6019002199173</t>
+    <t xml:space="preserve">1.61187982559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60189998149872</t>
   </si>
   <si>
     <t xml:space="preserve">1.58985567092896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58331751823425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54511940479279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57677888870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57471418380737</t>
+    <t xml:space="preserve">1.58331739902496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54511952400208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5767787694931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57471430301666</t>
   </si>
   <si>
     <t xml:space="preserve">1.5922646522522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58090817928314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58572614192963</t>
+    <t xml:space="preserve">1.58090829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58572590351105</t>
   </si>
   <si>
     <t xml:space="preserve">1.59054386615753</t>
@@ -2570,112 +2570,112 @@
     <t xml:space="preserve">1.62633275985718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6283974647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63803327083588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65523934364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65214240550995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62082672119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61635315418243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63872122764587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6170414686203</t>
+    <t xml:space="preserve">1.62839734554291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6380330324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6552392244339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65214228630066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62082660198212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61635327339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63872146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61704134941101</t>
   </si>
   <si>
     <t xml:space="preserve">1.63390362262726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61119139194489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61532092094421</t>
+    <t xml:space="preserve">1.61119151115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61532080173492</t>
   </si>
   <si>
     <t xml:space="preserve">1.59673798084259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59845852851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60809433460236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59570574760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5692081451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56094896793365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56783187389374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55200207233429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58675825595856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57712304592133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54546368122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57264935970306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61841773986816</t>
+    <t xml:space="preserve">1.59845900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60809421539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59570562839508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56920802593231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56094932556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56783199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55200231075287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58675861358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57712316513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54546356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57264959812164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61841785907745</t>
   </si>
   <si>
     <t xml:space="preserve">1.685866355896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70100772380829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7041050195694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69240486621857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70857858657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72578489780426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72750532627106</t>
+    <t xml:space="preserve">1.70100784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70410478115082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69240474700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70857846736908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72578477859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72750556468964</t>
   </si>
   <si>
     <t xml:space="preserve">1.74815309047699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78944778442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79185676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7550356388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73542046546936</t>
+    <t xml:space="preserve">1.78944790363312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79185664653778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75503528118134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73542022705078</t>
   </si>
   <si>
     <t xml:space="preserve">1.63562417030334</t>
@@ -2690,184 +2690,184 @@
     <t xml:space="preserve">1.51311564445496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47044432163239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45839989185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46425020694733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40850186347961</t>
+    <t xml:space="preserve">1.47044444084167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45840013027191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46425032615662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4085019826889</t>
   </si>
   <si>
     <t xml:space="preserve">1.36080622673035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20443594455719</t>
+    <t xml:space="preserve">1.20443618297577</t>
   </si>
   <si>
     <t xml:space="preserve">1.17608022689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22453284263611</t>
+    <t xml:space="preserve">1.22453320026398</t>
   </si>
   <si>
     <t xml:space="preserve">1.00677096843719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06981456279755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965476095676422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998924851417542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96946781873703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980892837047577</t>
+    <t xml:space="preserve">1.06981444358826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965475857257843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998924911022186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969467759132385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980892896652222</t>
   </si>
   <si>
     <t xml:space="preserve">1.00856029987335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997135400772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08991158008575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11234843730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12253439426422</t>
+    <t xml:space="preserve">0.997135579586029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08991146087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11234855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12253451347351</t>
   </si>
   <si>
     <t xml:space="preserve">1.07821118831635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01227712631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02438986301422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987500071525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989564716815948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914820849895477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00360465049744</t>
+    <t xml:space="preserve">1.01227676868439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0243901014328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987499952316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989564776420593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914821028709412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00360500812531</t>
   </si>
   <si>
     <t xml:space="preserve">1.01103794574738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997410714626312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99452006816864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967816174030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928035199642181</t>
+    <t xml:space="preserve">0.997410833835602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994520127773285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967815935611725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928035140037537</t>
   </si>
   <si>
     <t xml:space="preserve">0.936156630516052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947168469429016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951848685741425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908488929271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921015024185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952812194824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924869179725647</t>
+    <t xml:space="preserve">0.947168707847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951848745346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908488988876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921014964580536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952812135219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924869239330292</t>
   </si>
   <si>
     <t xml:space="preserve">0.960245370864868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996034264564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01888406276703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979378461837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947030961513519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998649597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97745156288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966577112674713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973184525966644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970018446445465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977864384651184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959143996238708</t>
+    <t xml:space="preserve">0.996034204959869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01888394355774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979378700256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947030901908875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998649656772614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977451503276825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966577053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973184406757355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97001850605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977864503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959144055843353</t>
   </si>
   <si>
     <t xml:space="preserve">0.952261507511139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952399075031281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999475598335266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984746754169464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990390717983246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978690266609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994244694709778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00319194793701</t>
+    <t xml:space="preserve">0.952399253845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999475538730621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984746813774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990390539169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978690326213837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994244754314423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00319182872772</t>
   </si>
   <si>
     <t xml:space="preserve">1.0331996679306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05880260467529</t>
+    <t xml:space="preserve">1.05880272388458</t>
   </si>
   <si>
     <t xml:space="preserve">1.07270514965057</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">1.08743369579315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11840498447418</t>
+    <t xml:space="preserve">1.11840486526489</t>
   </si>
   <si>
     <t xml:space="preserve">1.15157854557037</t>
@@ -2894,28 +2894,28 @@
     <t xml:space="preserve">1.24118864536285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18378865718842</t>
+    <t xml:space="preserve">1.18378877639771</t>
   </si>
   <si>
     <t xml:space="preserve">1.17181313037872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11344945430756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11634016036987</t>
+    <t xml:space="preserve">1.11344969272614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11634004116058</t>
   </si>
   <si>
     <t xml:space="preserve">1.11950612068176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16947305202484</t>
+    <t xml:space="preserve">1.16947317123413</t>
   </si>
   <si>
     <t xml:space="preserve">1.17263901233673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16025030612946</t>
+    <t xml:space="preserve">1.16025042533875</t>
   </si>
   <si>
     <t xml:space="preserve">1.15956223011017</t>
@@ -2924,22 +2924,22 @@
     <t xml:space="preserve">1.15791034698486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17786979675293</t>
+    <t xml:space="preserve">1.17786991596222</t>
   </si>
   <si>
     <t xml:space="preserve">1.14717376232147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14249360561371</t>
+    <t xml:space="preserve">1.142493724823</t>
   </si>
   <si>
     <t xml:space="preserve">1.17140018939972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17250120639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16355419158936</t>
+    <t xml:space="preserve">1.17250144481659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16355407238007</t>
   </si>
   <si>
     <t xml:space="preserve">1.20636308193207</t>
@@ -2951,16 +2951,16 @@
     <t xml:space="preserve">1.23348021507263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22962582111359</t>
+    <t xml:space="preserve">1.22962605953217</t>
   </si>
   <si>
     <t xml:space="preserve">1.21338331699371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19149684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21503531932831</t>
+    <t xml:space="preserve">1.19149696826935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21503508090973</t>
   </si>
   <si>
     <t xml:space="preserve">1.22604715824127</t>
@@ -2987,46 +2987,46 @@
     <t xml:space="preserve">1.29129314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27271044254303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24944758415222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23981213569641</t>
+    <t xml:space="preserve">1.27271032333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24944746494293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23981201648712</t>
   </si>
   <si>
     <t xml:space="preserve">1.22935080528259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23155295848846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19411242008209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17497885227203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1756671667099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23444366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26252436637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24834644794464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2425651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24848401546478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28096926212311</t>
+    <t xml:space="preserve">1.23155319690704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1941123008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17497909069061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17566740512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23444378376007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26252448558807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24834632873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24256503582001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24848413467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28096961975098</t>
   </si>
   <si>
     <t xml:space="preserve">1.2958357334137</t>
@@ -3035,34 +3035,34 @@
     <t xml:space="preserve">1.28399777412415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27436232566833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25564181804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24903464317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26981985569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24999809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24683237075806</t>
+    <t xml:space="preserve">1.27436220645905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25564193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24903476238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26981961727142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24999821186066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24683225154877</t>
   </si>
   <si>
     <t xml:space="preserve">1.2658280134201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26224899291992</t>
+    <t xml:space="preserve">1.2622492313385</t>
   </si>
   <si>
     <t xml:space="preserve">1.2681679725647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24146389961243</t>
+    <t xml:space="preserve">1.24146378040314</t>
   </si>
   <si>
     <t xml:space="preserve">1.25605475902557</t>
@@ -3074,22 +3074,22 @@
     <t xml:space="preserve">1.24008738994598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22425758838654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22411978244781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23458158969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21269512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23210382461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23967444896698</t>
+    <t xml:space="preserve">1.22425782680511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2241199016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2345814704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21269500255585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2321035861969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23967432975769</t>
   </si>
   <si>
     <t xml:space="preserve">1.22439539432526</t>
@@ -3101,10 +3101,10 @@
     <t xml:space="preserve">1.21145629882812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19989347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18020963668823</t>
+    <t xml:space="preserve">1.19989359378815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18020975589752</t>
   </si>
   <si>
     <t xml:space="preserve">1.12570035457611</t>
@@ -3113,31 +3113,31 @@
     <t xml:space="preserve">1.12996757030487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10959553718567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10670471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08674538135529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11812961101532</t>
+    <t xml:space="preserve">1.10959541797638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10670459270477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08674550056458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11812973022461</t>
   </si>
   <si>
     <t xml:space="preserve">1.10587882995605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10326361656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09183847904205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09596812725067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12404870986938</t>
+    <t xml:space="preserve">1.10326337814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09183859825134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09596800804138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1240485906601</t>
   </si>
   <si>
     <t xml:space="preserve">1.14827501773834</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">1.15309262275696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15557026863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14978921413422</t>
+    <t xml:space="preserve">1.15557038784027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14978909492493</t>
   </si>
   <si>
     <t xml:space="preserve">1.11317431926727</t>
@@ -3164,19 +3164,19 @@
     <t xml:space="preserve">1.0707780122757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07353127002716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05701303482056</t>
+    <t xml:space="preserve">1.07353103160858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05701315402985</t>
   </si>
   <si>
     <t xml:space="preserve">1.05770134925842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07449448108673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05095648765564</t>
+    <t xml:space="preserve">1.07449460029602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05095660686493</t>
   </si>
   <si>
     <t xml:space="preserve">1.02590417861938</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">0.97593742609024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962998151779175</t>
+    <t xml:space="preserve">0.96299821138382</t>
   </si>
   <si>
     <t xml:space="preserve">0.977038681507111</t>
@@ -3194,109 +3194,109 @@
     <t xml:space="preserve">1.02026057243347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0603164434433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09968483448029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12680160999298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11276113986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21531045436859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26926910877228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25591695308685</t>
+    <t xml:space="preserve">1.06031656265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09968447685242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12680149078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11276137828827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2153103351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26926922798157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25591719150543</t>
   </si>
   <si>
     <t xml:space="preserve">1.24022507667542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25109934806824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26637852191925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27615177631378</t>
+    <t xml:space="preserve">1.25109946727753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26637864112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27615165710449</t>
   </si>
   <si>
     <t xml:space="preserve">1.28730118274689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28248357772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31868553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33671748638153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32777047157288</t>
+    <t xml:space="preserve">1.28248369693756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31868541240692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33671772480011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32777035236359</t>
   </si>
   <si>
     <t xml:space="preserve">1.32515501976013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35653924942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36700046062469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37002873420715</t>
+    <t xml:space="preserve">1.35653913021088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36700057983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37002897262573</t>
   </si>
   <si>
     <t xml:space="preserve">1.3566769361496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35516273975372</t>
+    <t xml:space="preserve">1.35516262054443</t>
   </si>
   <si>
     <t xml:space="preserve">1.35998034477234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34951901435852</t>
+    <t xml:space="preserve">1.34951913356781</t>
   </si>
   <si>
     <t xml:space="preserve">1.33231282234192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33465301990509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35929203033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33726835250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33823180198669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33189988136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29473435878754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3166207075119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32309031486511</t>
+    <t xml:space="preserve">1.3346529006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35929214954376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33726823329926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33823192119598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33189976215363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29473447799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31662082672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32309019565582</t>
   </si>
   <si>
     <t xml:space="preserve">1.32130086421967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31634545326233</t>
+    <t xml:space="preserve">1.31634557247162</t>
   </si>
   <si>
     <t xml:space="preserve">1.31125247478485</t>
@@ -3305,22 +3305,22 @@
     <t xml:space="preserve">1.29693675041199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35447454452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34552729129791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3371307849884</t>
+    <t xml:space="preserve">1.35447442531586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34552717208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33713054656982</t>
   </si>
   <si>
     <t xml:space="preserve">1.33396446704865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31799697875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30904984474182</t>
+    <t xml:space="preserve">1.31799709796906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30904996395111</t>
   </si>
   <si>
     <t xml:space="preserve">1.31951129436493</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">1.31483125686646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32584309577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29679918289185</t>
+    <t xml:space="preserve">1.32584321498871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29679930210114</t>
   </si>
   <si>
     <t xml:space="preserve">1.25481593608856</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">1.26610326766968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24407935142517</t>
+    <t xml:space="preserve">1.24407911300659</t>
   </si>
   <si>
     <t xml:space="preserve">1.26197373867035</t>
@@ -3350,28 +3350,28 @@
     <t xml:space="preserve">1.25398993492126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28771436214447</t>
+    <t xml:space="preserve">1.28771424293518</t>
   </si>
   <si>
     <t xml:space="preserve">1.34291183948517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38234853744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41848170757294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43844079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637585639954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43155837059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43603193759918</t>
+    <t xml:space="preserve">1.38234865665436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41848158836365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43844068050385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637597560883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43155825138092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43603181838989</t>
   </si>
   <si>
     <t xml:space="preserve">1.44257032871246</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">1.45392632484436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45117354393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44532310962677</t>
+    <t xml:space="preserve">1.45117342472076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44532322883606</t>
   </si>
   <si>
     <t xml:space="preserve">1.45358228683472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.481112241745</t>
+    <t xml:space="preserve">1.48111212253571</t>
   </si>
   <si>
     <t xml:space="preserve">1.4687237739563</t>
@@ -3404,40 +3404,40 @@
     <t xml:space="preserve">1.48283290863037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51621317863464</t>
+    <t xml:space="preserve">1.51621305942535</t>
   </si>
   <si>
     <t xml:space="preserve">1.50864219665527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51036274433136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56198143959045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56507861614227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55991697311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56955230236053</t>
+    <t xml:space="preserve">1.51036286354065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56198132038116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56507873535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55991673469543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56955218315125</t>
   </si>
   <si>
     <t xml:space="preserve">1.55888450145721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57884347438812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59329676628113</t>
+    <t xml:space="preserve">1.5788437128067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59329664707184</t>
   </si>
   <si>
     <t xml:space="preserve">1.61669731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59260833263397</t>
+    <t xml:space="preserve">1.59260857105255</t>
   </si>
   <si>
     <t xml:space="preserve">1.58194088935852</t>
@@ -3449,37 +3449,37 @@
     <t xml:space="preserve">1.5798761844635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57918798923492</t>
+    <t xml:space="preserve">1.57918775081635</t>
   </si>
   <si>
     <t xml:space="preserve">1.58125245571136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57333791255951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59914684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59019958972931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59536170959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58503806591034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55750799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55096971988678</t>
+    <t xml:space="preserve">1.57333755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59914708137512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5901997089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59536159038544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58503782749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55750787258148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5509694814682</t>
   </si>
   <si>
     <t xml:space="preserve">1.5557873249054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56989634037018</t>
+    <t xml:space="preserve">1.56989622116089</t>
   </si>
   <si>
     <t xml:space="preserve">1.52791333198547</t>
@@ -3491,19 +3491,19 @@
     <t xml:space="preserve">1.52860140800476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58056402206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5950174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59742629528046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60637354850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58847904205322</t>
+    <t xml:space="preserve">1.58056461811066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59501755237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59742617607117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60637366771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58847916126251</t>
   </si>
   <si>
     <t xml:space="preserve">1.62357985973358</t>
@@ -3512,94 +3512,94 @@
     <t xml:space="preserve">1.6256445646286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64457142353058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63837718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63975369930267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63287115097046</t>
+    <t xml:space="preserve">1.64457130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63837730884552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63975381851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63287103176117</t>
   </si>
   <si>
     <t xml:space="preserve">1.64319503307343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65868055820465</t>
+    <t xml:space="preserve">1.65868079662323</t>
   </si>
   <si>
     <t xml:space="preserve">1.65351855754852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65116274356842</t>
+    <t xml:space="preserve">1.65116286277771</t>
   </si>
   <si>
     <t xml:space="preserve">1.64976525306702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63928389549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67282438278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68330585956573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68854629993439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70881032943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72767698764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73012244701385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73326671123505</t>
+    <t xml:space="preserve">1.63928401470184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67282450199127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68330574035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68854641914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70881009101868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72767686843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73012220859528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73326683044434</t>
   </si>
   <si>
     <t xml:space="preserve">1.73676073551178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71894228458405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71440041065216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70426833629608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69448578357697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71195507049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71265363693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68749833106995</t>
+    <t xml:space="preserve">1.71894252300262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71440052986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7042680978775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69448602199554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71195483207703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71265375614166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68749809265137</t>
   </si>
   <si>
     <t xml:space="preserve">1.63788664340973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65360844135284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63648891448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6183215379715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65186190605164</t>
+    <t xml:space="preserve">1.65360867977142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63648903369904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61832118034363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65186178684235</t>
   </si>
   <si>
     <t xml:space="preserve">1.66688501834869</t>
@@ -3608,10 +3608,10 @@
     <t xml:space="preserve">1.62775433063507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64662086963654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64592218399048</t>
+    <t xml:space="preserve">1.64662075042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64592206478119</t>
   </si>
   <si>
     <t xml:space="preserve">1.63229656219482</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">1.65535533428192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6214656829834</t>
+    <t xml:space="preserve">1.62146580219269</t>
   </si>
   <si>
     <t xml:space="preserve">1.60958671569824</t>
@@ -3629,103 +3629,103 @@
     <t xml:space="preserve">1.56242084503174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59596109390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61098408699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58617866039276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59631037712097</t>
+    <t xml:space="preserve">1.59596085548401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61098420619965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58617854118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59631049633026</t>
   </si>
   <si>
     <t xml:space="preserve">1.57639598846436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55962574481964</t>
+    <t xml:space="preserve">1.55962586402893</t>
   </si>
   <si>
     <t xml:space="preserve">1.49359321594238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52259147167206</t>
+    <t xml:space="preserve">1.52259159088135</t>
   </si>
   <si>
     <t xml:space="preserve">1.56277012825012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57255244255066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59665977954865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63334453105927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61657452583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62111616134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63998281955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62915170192719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61727321147919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62565839290619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63509118556976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63858532905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67596864700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68016123771667</t>
+    <t xml:space="preserve">1.57255280017853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59665989875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63334465026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61657440662384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62111628055573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6399827003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62915217876434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6256582736969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63509142398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63858544826508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67596888542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68016135692596</t>
   </si>
   <si>
     <t xml:space="preserve">1.68260681629181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71125590801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71055698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69204008579254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66898119449615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68225753307343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66723418235779</t>
+    <t xml:space="preserve">1.71125602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71055722236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69203996658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66898131370544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.682257771492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66723430156708</t>
   </si>
   <si>
     <t xml:space="preserve">1.66304194927216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67002940177917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66164422035217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6752701997757</t>
+    <t xml:space="preserve">1.67002928256989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66164410114288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67526996135712</t>
   </si>
   <si>
     <t xml:space="preserve">1.68365490436554</t>
@@ -3734,205 +3734,205 @@
     <t xml:space="preserve">1.6682825088501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67911338806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.665487408638</t>
+    <t xml:space="preserve">1.67911326885223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66548728942871</t>
   </si>
   <si>
     <t xml:space="preserve">1.6483678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.657102227211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63963341712952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66758346557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66094565391541</t>
+    <t xml:space="preserve">1.65710234642029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63963329792023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66758358478546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66094541549683</t>
   </si>
   <si>
     <t xml:space="preserve">1.65884923934937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6085387468338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62251377105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65815031528473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69623279571533</t>
+    <t xml:space="preserve">1.60853886604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62251365184784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65815043449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69623267650604</t>
   </si>
   <si>
     <t xml:space="preserve">1.69413638114929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72732710838318</t>
+    <t xml:space="preserve">1.72732722759247</t>
   </si>
   <si>
     <t xml:space="preserve">1.69763016700745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71824359893799</t>
+    <t xml:space="preserve">1.71824371814728</t>
   </si>
   <si>
     <t xml:space="preserve">1.74898898601532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72942352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7538800239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75912070274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7493382692337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75562727451324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74339890480042</t>
+    <t xml:space="preserve">1.72942340373993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75388038158417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75912082195282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74933838844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75562715530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74339878559113</t>
   </si>
   <si>
     <t xml:space="preserve">1.76331329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79929935932159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81100165843964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7815637588501</t>
+    <t xml:space="preserve">1.79929959774017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81100177764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78156387805939</t>
   </si>
   <si>
     <t xml:space="preserve">1.79319369792938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77720236778259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78192687034607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79028654098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80373334884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78301763534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77211439609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78628790378571</t>
+    <t xml:space="preserve">1.77720248699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78192698955536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79028642177582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80373322963715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78301739692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77211427688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78628838062286</t>
   </si>
   <si>
     <t xml:space="preserve">1.81354606151581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82590281963348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81863415241241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78556132316589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80518710613251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8117288351059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7957376241684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80046224594116</t>
+    <t xml:space="preserve">1.82590317726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8186342716217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78556156158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80518686771393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81172895431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573750495911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80046212673187</t>
   </si>
   <si>
     <t xml:space="preserve">1.79682779312134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79646444320679</t>
+    <t xml:space="preserve">1.7964643239975</t>
   </si>
   <si>
     <t xml:space="preserve">1.80991172790527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80446016788483</t>
+    <t xml:space="preserve">1.80445992946625</t>
   </si>
   <si>
     <t xml:space="preserve">1.8040965795517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73286330699921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74418115615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72544276714325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7258175611496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71494936943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61638474464417</t>
+    <t xml:space="preserve">1.73286306858063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74418127536774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72544288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72581744194031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71494925022125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61638462543488</t>
   </si>
   <si>
     <t xml:space="preserve">1.60626566410065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.585653424263</t>
+    <t xml:space="preserve">1.58565318584442</t>
   </si>
   <si>
     <t xml:space="preserve">1.62537884712219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60963869094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60888910293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65873372554779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.692462682724</t>
+    <t xml:space="preserve">1.60963881015778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60888922214508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6587336063385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69246304035187</t>
   </si>
   <si>
     <t xml:space="preserve">1.6722252368927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66772818565369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66060769557953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6527373790741</t>
+    <t xml:space="preserve">1.66772794723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66060745716095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65273725986481</t>
   </si>
   <si>
     <t xml:space="preserve">1.66735327243805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65011394023895</t>
+    <t xml:space="preserve">1.65011382102966</t>
   </si>
   <si>
     <t xml:space="preserve">1.68084502220154</t>
@@ -3941,10 +3941,10 @@
     <t xml:space="preserve">1.65311217308044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63549780845642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67334961891174</t>
+    <t xml:space="preserve">1.63549792766571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67334997653961</t>
   </si>
   <si>
     <t xml:space="preserve">1.67185056209564</t>
@@ -3965,67 +3965,67 @@
     <t xml:space="preserve">1.70445549488068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75767290592194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7944004535675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81238925457001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82363247871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8374992609024</t>
+    <t xml:space="preserve">1.75767314434052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79440069198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81238949298859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82363271713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83749902248383</t>
   </si>
   <si>
     <t xml:space="preserve">1.84611904621124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86036002635956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90795600414276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91919887065887</t>
+    <t xml:space="preserve">1.86035990715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90795588493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91919898986816</t>
   </si>
   <si>
     <t xml:space="preserve">1.92032337188721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93194115161896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93006718158722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89933621883392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91245329380035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9128280878067</t>
+    <t xml:space="preserve">1.93194127082825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93006765842438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89933586120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91245305538177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91282784938812</t>
   </si>
   <si>
     <t xml:space="preserve">1.8487423658371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86560678482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92219698429108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95817518234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94655740261078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96342182159424</t>
+    <t xml:space="preserve">1.86560690402985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92219734191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95817506313324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9465571641922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96342217922211</t>
   </si>
   <si>
     <t xml:space="preserve">2.00127387046814</t>
@@ -4037,16 +4037,16 @@
     <t xml:space="preserve">2.04474687576294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99902510643005</t>
+    <t xml:space="preserve">1.99902546405792</t>
   </si>
   <si>
     <t xml:space="preserve">2.03500294685364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07585334777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13881468772888</t>
+    <t xml:space="preserve">2.07585310935974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1388144493103</t>
   </si>
   <si>
     <t xml:space="preserve">2.18865895271301</t>
@@ -4064,31 +4064,31 @@
     <t xml:space="preserve">2.05299210548401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04024958610535</t>
+    <t xml:space="preserve">2.04024982452393</t>
   </si>
   <si>
     <t xml:space="preserve">2.00427198410034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99377822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96417164802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8078920841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85698711872101</t>
+    <t xml:space="preserve">1.99377834796906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96417152881622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80789232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8569872379303</t>
   </si>
   <si>
     <t xml:space="preserve">1.71907186508179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5864030122757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60851442813873</t>
+    <t xml:space="preserve">1.58640289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60851407051086</t>
   </si>
   <si>
     <t xml:space="preserve">1.56204295158386</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">1.38155353069305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39834320545197</t>
+    <t xml:space="preserve">1.39834332466125</t>
   </si>
   <si>
     <t xml:space="preserve">1.55342316627502</t>
@@ -4109,31 +4109,31 @@
     <t xml:space="preserve">1.4352205991745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43866837024689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49158620834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50507771968842</t>
+    <t xml:space="preserve">1.43866848945618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49158608913422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50507760047913</t>
   </si>
   <si>
     <t xml:space="preserve">1.61001348495483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55304837226868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56354200839996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54892587661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57403528690338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53505957126617</t>
+    <t xml:space="preserve">1.55304849147797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56354188919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54892611503601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57403540611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53505945205688</t>
   </si>
   <si>
     <t xml:space="preserve">1.5223171710968</t>
@@ -4142,34 +4142,34 @@
     <t xml:space="preserve">1.52381634712219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53243613243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61975753307343</t>
+    <t xml:space="preserve">1.53243625164032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61975741386414</t>
   </si>
   <si>
     <t xml:space="preserve">1.59951984882355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56166803836823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57778310775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57028782367706</t>
+    <t xml:space="preserve">1.56166815757751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57778334617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57028794288635</t>
   </si>
   <si>
     <t xml:space="preserve">1.53056216239929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48573970794678</t>
+    <t xml:space="preserve">1.48573958873749</t>
   </si>
   <si>
     <t xml:space="preserve">1.46280360221863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48558974266052</t>
+    <t xml:space="preserve">1.48558986186981</t>
   </si>
   <si>
     <t xml:space="preserve">1.48469030857086</t>
@@ -4181,31 +4181,31 @@
     <t xml:space="preserve">1.4572571516037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47734475135803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47884392738342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51444685459137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51782011985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48618948459625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46055495738983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43761897087097</t>
+    <t xml:space="preserve">1.47734463214874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47884380817413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51444709300995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5178200006485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48618936538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46055519580841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43761909008026</t>
   </si>
   <si>
     <t xml:space="preserve">1.4397177696228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44361531734467</t>
+    <t xml:space="preserve">1.44361543655396</t>
   </si>
   <si>
     <t xml:space="preserve">1.46520221233368</t>
@@ -4217,28 +4217,28 @@
     <t xml:space="preserve">1.46924960613251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44301569461823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44256615638733</t>
+    <t xml:space="preserve">1.44301581382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44256603717804</t>
   </si>
   <si>
     <t xml:space="preserve">1.40913653373718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37165951728821</t>
+    <t xml:space="preserve">1.3716596364975</t>
   </si>
   <si>
     <t xml:space="preserve">1.39534509181976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45410919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47074902057648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47839415073395</t>
+    <t xml:space="preserve">1.45410895347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47074890136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47839403152466</t>
   </si>
   <si>
     <t xml:space="preserve">1.46490240097046</t>
@@ -4247,34 +4247,34 @@
     <t xml:space="preserve">1.49188590049744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49008703231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48633921146393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54183983802795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54496228694916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58695864677429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60139966011047</t>
+    <t xml:space="preserve">1.49008691310883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48633944988251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54183995723724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54496216773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.586958527565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60139954090118</t>
   </si>
   <si>
     <t xml:space="preserve">1.59788680076599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6076443195343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58500707149506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56119871139526</t>
+    <t xml:space="preserve">1.60764420032501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58500683307648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56119883060455</t>
   </si>
   <si>
     <t xml:space="preserve">1.54012250900269</t>
@@ -4283,49 +4283,49 @@
     <t xml:space="preserve">1.59047102928162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5631502866745</t>
+    <t xml:space="preserve">1.56315040588379</t>
   </si>
   <si>
     <t xml:space="preserve">1.55339276790619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5352828502655</t>
+    <t xml:space="preserve">1.53528273105621</t>
   </si>
   <si>
     <t xml:space="preserve">1.42193984985352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3730742931366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38166093826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44520163536072</t>
+    <t xml:space="preserve">1.37307417392731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38166081905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44520151615143</t>
   </si>
   <si>
     <t xml:space="preserve">1.39961457252502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40788900852203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46175026893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47221040725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46799516677856</t>
+    <t xml:space="preserve">1.40788888931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46175038814545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47221028804779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46799528598785</t>
   </si>
   <si>
     <t xml:space="preserve">1.43630290031433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46924424171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47798693180084</t>
+    <t xml:space="preserve">1.46924412250519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47798669338226</t>
   </si>
   <si>
     <t xml:space="preserve">1.48204600811005</t>
@@ -4340,31 +4340,31 @@
     <t xml:space="preserve">1.37978744506836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34669005870819</t>
+    <t xml:space="preserve">1.3466899394989</t>
   </si>
   <si>
     <t xml:space="preserve">1.30469369888306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31000196933746</t>
+    <t xml:space="preserve">1.31000185012817</t>
   </si>
   <si>
     <t xml:space="preserve">1.36230206489563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37588441371918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35199809074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33295154571533</t>
+    <t xml:space="preserve">1.37588453292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35199797153473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33295142650604</t>
   </si>
   <si>
     <t xml:space="preserve">1.32764339447021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25411105155945</t>
+    <t xml:space="preserve">1.25411081314087</t>
   </si>
   <si>
     <t xml:space="preserve">1.27393805980682</t>
@@ -4376,22 +4376,22 @@
     <t xml:space="preserve">1.38369047641754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33513724803925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29813659191132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29579484462738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31765174865723</t>
+    <t xml:space="preserve">1.33513712882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2981368303299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29579496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31765162944794</t>
   </si>
   <si>
     <t xml:space="preserve">1.29329705238342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3092212677002</t>
+    <t xml:space="preserve">1.30922114849091</t>
   </si>
   <si>
     <t xml:space="preserve">1.3315464258194</t>
@@ -4403,10 +4403,10 @@
     <t xml:space="preserve">1.36542439460754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36370694637299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38462710380554</t>
+    <t xml:space="preserve">1.36370706558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38462698459625</t>
   </si>
   <si>
     <t xml:space="preserve">1.39180862903595</t>
@@ -4415,10 +4415,10 @@
     <t xml:space="preserve">1.41600728034973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41850507259369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41756844520569</t>
+    <t xml:space="preserve">1.41850519180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4175683259964</t>
   </si>
   <si>
     <t xml:space="preserve">1.43052637577057</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">1.38415884971619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34138202667236</t>
+    <t xml:space="preserve">1.34138190746307</t>
   </si>
   <si>
     <t xml:space="preserve">1.36573672294617</t>
@@ -4448,43 +4448,43 @@
     <t xml:space="preserve">1.37666499614716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3569940328598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.315309882164</t>
+    <t xml:space="preserve">1.35699391365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31530976295471</t>
   </si>
   <si>
     <t xml:space="preserve">1.32811176776886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34996843338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34497284889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32217907905579</t>
+    <t xml:space="preserve">1.34996855258942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34497272968292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32217931747437</t>
   </si>
   <si>
     <t xml:space="preserve">1.3568377494812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32467722892761</t>
+    <t xml:space="preserve">1.32467710971832</t>
   </si>
   <si>
     <t xml:space="preserve">1.32998514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32701897621155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35855507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43099474906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48001635074615</t>
+    <t xml:space="preserve">1.32701885700226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35855519771576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43099462985992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48001623153687</t>
   </si>
   <si>
     <t xml:space="preserve">1.46846342086792</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">1.49875068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49484765529633</t>
+    <t xml:space="preserve">1.49484777450562</t>
   </si>
   <si>
     <t xml:space="preserve">1.49516010284424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44348430633545</t>
+    <t xml:space="preserve">1.44348418712616</t>
   </si>
   <si>
     <t xml:space="preserve">1.43364870548248</t>
@@ -4511,25 +4511,25 @@
     <t xml:space="preserve">1.44567000865936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37697744369507</t>
+    <t xml:space="preserve">1.37697732448578</t>
   </si>
   <si>
     <t xml:space="preserve">1.38041186332703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34825134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32592594623566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29189193248749</t>
+    <t xml:space="preserve">1.34825122356415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32592606544495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29189205169678</t>
   </si>
   <si>
     <t xml:space="preserve">1.32920467853546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35355925559998</t>
+    <t xml:space="preserve">1.35355913639069</t>
   </si>
   <si>
     <t xml:space="preserve">1.39571166038513</t>
@@ -4538,22 +4538,22 @@
     <t xml:space="preserve">1.35917949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33654236793518</t>
+    <t xml:space="preserve">1.33654224872589</t>
   </si>
   <si>
     <t xml:space="preserve">1.33139026165009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32342827320099</t>
+    <t xml:space="preserve">1.3234281539917</t>
   </si>
   <si>
     <t xml:space="preserve">1.30781614780426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33201479911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33669817447662</t>
+    <t xml:space="preserve">1.33201491832733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3366984128952</t>
   </si>
   <si>
     <t xml:space="preserve">1.36058461666107</t>
@@ -4565,19 +4565,19 @@
     <t xml:space="preserve">1.39852178096771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42771601676941</t>
+    <t xml:space="preserve">1.42771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">1.42662346363068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44863641262054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45550537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45644223690033</t>
+    <t xml:space="preserve">1.44863629341125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45550560951233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45644235610962</t>
   </si>
   <si>
     <t xml:space="preserve">1.48766624927521</t>
@@ -4586,7 +4586,7 @@
     <t xml:space="preserve">1.48719787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50577628612518</t>
+    <t xml:space="preserve">1.5057760477066</t>
   </si>
   <si>
     <t xml:space="preserve">1.51842188835144</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">1.51810967922211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53746843338013</t>
+    <t xml:space="preserve">1.53746855258942</t>
   </si>
   <si>
     <t xml:space="preserve">1.61193776130676</t>
@@ -4604,16 +4604,16 @@
     <t xml:space="preserve">1.6618959903717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67672753334045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68141114711761</t>
+    <t xml:space="preserve">1.67672741413116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68141102790833</t>
   </si>
   <si>
     <t xml:space="preserve">1.69936490058899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68648481369019</t>
+    <t xml:space="preserve">1.68648493289948</t>
   </si>
   <si>
     <t xml:space="preserve">1.70678055286407</t>
@@ -4622,19 +4622,19 @@
     <t xml:space="preserve">1.70951271057129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70990288257599</t>
+    <t xml:space="preserve">1.70990300178528</t>
   </si>
   <si>
     <t xml:space="preserve">1.70014536380768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73019850254059</t>
+    <t xml:space="preserve">1.7301983833313</t>
   </si>
   <si>
     <t xml:space="preserve">1.72882580757141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74457168579102</t>
+    <t xml:space="preserve">1.74457180500031</t>
   </si>
   <si>
     <t xml:space="preserve">1.73165190219879</t>
@@ -4646,22 +4646,22 @@
     <t xml:space="preserve">1.74295675754547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70863854885101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72357714176178</t>
+    <t xml:space="preserve">1.7086386680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72357726097107</t>
   </si>
   <si>
     <t xml:space="preserve">1.71348357200623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68320286273956</t>
+    <t xml:space="preserve">1.68320298194885</t>
   </si>
   <si>
     <t xml:space="preserve">1.69289267063141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67835807800293</t>
+    <t xml:space="preserve">1.67835795879364</t>
   </si>
   <si>
     <t xml:space="preserve">1.66866815090179</t>
@@ -4673,16 +4673,16 @@
     <t xml:space="preserve">1.66140067577362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66907179355621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67028319835663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69652652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68562531471252</t>
+    <t xml:space="preserve">1.6690719127655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67028307914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6965264081955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68562543392181</t>
   </si>
   <si>
     <t xml:space="preserve">1.6104484796524</t>
@@ -4700,22 +4700,22 @@
     <t xml:space="preserve">1.69612264633179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68279933929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68966257572174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68118405342102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67997288703918</t>
+    <t xml:space="preserve">1.68279922008514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68966269493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68118417263031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6799727678299</t>
   </si>
   <si>
     <t xml:space="preserve">1.70137143135071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67795419692993</t>
+    <t xml:space="preserve">1.67795431613922</t>
   </si>
   <si>
     <t xml:space="preserve">1.71429097652435</t>
@@ -4727,28 +4727,28 @@
     <t xml:space="preserve">1.79948055744171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78857958316803</t>
+    <t xml:space="preserve">1.78857946395874</t>
   </si>
   <si>
     <t xml:space="preserve">1.80351805686951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81684172153473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82451283931732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84429597854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8475261926651</t>
+    <t xml:space="preserve">1.81684160232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82451272010803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84429609775543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84752631187439</t>
   </si>
   <si>
     <t xml:space="preserve">1.84510385990143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82572388648987</t>
+    <t xml:space="preserve">1.82572400569916</t>
   </si>
   <si>
     <t xml:space="preserve">1.79503953456879</t>
@@ -4760,16 +4760,16 @@
     <t xml:space="preserve">1.80836308002472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84550750255585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317862033844</t>
+    <t xml:space="preserve">1.84550726413727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85317850112915</t>
   </si>
   <si>
     <t xml:space="preserve">1.89153397083282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89839780330658</t>
+    <t xml:space="preserve">1.89839768409729</t>
   </si>
   <si>
     <t xml:space="preserve">1.89274537563324</t>
@@ -4781,10 +4781,10 @@
     <t xml:space="preserve">1.98076117038727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9823762178421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423725128174</t>
+    <t xml:space="preserve">1.98237597942352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423713207245</t>
   </si>
   <si>
     <t xml:space="preserve">1.97591626644135</t>
@@ -4796,49 +4796,49 @@
     <t xml:space="preserve">1.99368095397949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02194261550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00014066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01790547370911</t>
+    <t xml:space="preserve">2.02194285392761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00014090538025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01790571212769</t>
   </si>
   <si>
     <t xml:space="preserve">2.02073168754578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01467537879944</t>
+    <t xml:space="preserve">2.01467561721802</t>
   </si>
   <si>
     <t xml:space="preserve">2.05989480018616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07079601287842</t>
+    <t xml:space="preserve">2.07079577445984</t>
   </si>
   <si>
     <t xml:space="preserve">2.06231713294983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06151008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99973690509796</t>
+    <t xml:space="preserve">2.06150960922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99973714351654</t>
   </si>
   <si>
     <t xml:space="preserve">2.0300178527832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04536008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837320327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04859018325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05262756347656</t>
+    <t xml:space="preserve">2.04535984992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837344169617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04858994483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05262732505798</t>
   </si>
   <si>
     <t xml:space="preserve">2.07887077331543</t>
@@ -4856,13 +4856,13 @@
     <t xml:space="preserve">2.04414892196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00417828559875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8818439245224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94482791423798</t>
+    <t xml:space="preserve">2.00417804718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88184416294098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94482815265656</t>
   </si>
   <si>
     <t xml:space="preserve">1.81159293651581</t>
@@ -4877,46 +4877,46 @@
     <t xml:space="preserve">1.83702886104584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90162754058838</t>
+    <t xml:space="preserve">1.90162765979767</t>
   </si>
   <si>
     <t xml:space="preserve">1.89193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87255799770355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82733881473541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83420264720917</t>
+    <t xml:space="preserve">1.87255823612213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82733905315399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83420252799988</t>
   </si>
   <si>
     <t xml:space="preserve">1.85196733474731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87982547283173</t>
+    <t xml:space="preserve">1.87982583045959</t>
   </si>
   <si>
     <t xml:space="preserve">1.90970253944397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91172122955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86448323726654</t>
+    <t xml:space="preserve">1.91172111034393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86448335647583</t>
   </si>
   <si>
     <t xml:space="preserve">1.90405011177063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91939234733582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93433058261871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92827475070953</t>
+    <t xml:space="preserve">1.91939258575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.934330701828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92827451229095</t>
   </si>
   <si>
     <t xml:space="preserve">1.97147500514984</t>
@@ -4934,31 +4934,31 @@
     <t xml:space="preserve">2.00619673728943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02436518669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98722112178802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9654186964035</t>
+    <t xml:space="preserve">2.02436542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98722088336945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96541893482208</t>
   </si>
   <si>
     <t xml:space="preserve">1.98479866981506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92544865608215</t>
+    <t xml:space="preserve">1.92544841766357</t>
   </si>
   <si>
     <t xml:space="preserve">1.88022923469543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91293251514435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395654201508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96380388736725</t>
+    <t xml:space="preserve">1.91293227672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8939563035965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96380412578583</t>
   </si>
   <si>
     <t xml:space="preserve">1.98883616924286</t>
@@ -4967,13 +4967,13 @@
     <t xml:space="preserve">1.98358738422394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95048046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93917536735535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96057403087616</t>
+    <t xml:space="preserve">1.95048022270203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9391758441925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96057426929474</t>
   </si>
   <si>
     <t xml:space="preserve">1.9545179605484</t>
@@ -4997,10 +4997,10 @@
     <t xml:space="preserve">1.88888430595398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88804543018341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88301289081573</t>
+    <t xml:space="preserve">1.8880455493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88301312923431</t>
   </si>
   <si>
     <t xml:space="preserve">1.86665725708008</t>
@@ -5015,28 +5015,28 @@
     <t xml:space="preserve">1.87043154239655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90524017810822</t>
+    <t xml:space="preserve">1.90524005889893</t>
   </si>
   <si>
     <t xml:space="preserve">1.89475572109222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91698288917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93166100978851</t>
+    <t xml:space="preserve">1.91698265075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93166077136993</t>
   </si>
   <si>
     <t xml:space="preserve">1.94927477836609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93711280822754</t>
+    <t xml:space="preserve">1.93711304664612</t>
   </si>
   <si>
     <t xml:space="preserve">1.93417716026306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93920993804932</t>
+    <t xml:space="preserve">1.93920969963074</t>
   </si>
   <si>
     <t xml:space="preserve">1.97108244895935</t>
@@ -5045,10 +5045,10 @@
     <t xml:space="preserve">1.97779285907745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99037384986877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00840759277344</t>
+    <t xml:space="preserve">1.99037396907806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00840735435486</t>
   </si>
   <si>
     <t xml:space="preserve">2.00169730186462</t>
@@ -5057,13 +5057,13 @@
     <t xml:space="preserve">2.01805305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99540627002716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95850133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95598495006561</t>
+    <t xml:space="preserve">1.99540650844574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95850145816803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95598518848419</t>
   </si>
   <si>
     <t xml:space="preserve">1.98072850704193</t>
@@ -5075,10 +5075,10 @@
     <t xml:space="preserve">2.00127792358398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01302075386047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04405450820923</t>
+    <t xml:space="preserve">2.01302051544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04405474662781</t>
   </si>
   <si>
     <t xml:space="preserve">2.03021502494812</t>
@@ -5102,7 +5102,7 @@
     <t xml:space="preserve">2.01973056793213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04992628097534</t>
+    <t xml:space="preserve">2.04992604255676</t>
   </si>
   <si>
     <t xml:space="preserve">2.03860282897949</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">2.09018659591675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11534905433655</t>
+    <t xml:space="preserve">2.11534929275513</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289762496948</t>
@@ -5126,16 +5126,16 @@
     <t xml:space="preserve">2.12709164619446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12960815429688</t>
+    <t xml:space="preserve">2.1296079158783</t>
   </si>
   <si>
     <t xml:space="preserve">2.15812587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18874049186707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20509624481201</t>
+    <t xml:space="preserve">2.18874025344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20509600639343</t>
   </si>
   <si>
     <t xml:space="preserve">2.18832111358643</t>
@@ -5144,7 +5144,7 @@
     <t xml:space="preserve">2.149738073349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13505983352661</t>
+    <t xml:space="preserve">2.13506007194519</t>
   </si>
   <si>
     <t xml:space="preserve">2.13338255882263</t>
@@ -5153,13 +5153,13 @@
     <t xml:space="preserve">2.14722180366516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.961017370224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0067298412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04489374160767</t>
+    <t xml:space="preserve">1.96101784706116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00673007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04489350318909</t>
   </si>
   <si>
     <t xml:space="preserve">2.04615163803101</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">2.02224707603455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04573202133179</t>
+    <t xml:space="preserve">2.04573178291321</t>
   </si>
   <si>
     <t xml:space="preserve">2.06292676925659</t>
@@ -5192,10 +5192,10 @@
     <t xml:space="preserve">2.0545392036438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0776047706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09060573577881</t>
+    <t xml:space="preserve">2.07760500907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09060597419739</t>
   </si>
   <si>
     <t xml:space="preserve">2.09857416152954</t>
@@ -5204,28 +5204,28 @@
     <t xml:space="preserve">2.073410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05873274803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05202269554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00589108467102</t>
+    <t xml:space="preserve">2.0587329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05202293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0058913230896</t>
   </si>
   <si>
     <t xml:space="preserve">2.00043916702271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02434396743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0801215171814</t>
+    <t xml:space="preserve">2.02434372901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08012104034424</t>
   </si>
   <si>
     <t xml:space="preserve">2.07634687423706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06544303894043</t>
+    <t xml:space="preserve">2.06544327735901</t>
   </si>
   <si>
     <t xml:space="preserve">2.07592749595642</t>
@@ -5240,7 +5240,7 @@
     <t xml:space="preserve">2.04782891273499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10821962356567</t>
+    <t xml:space="preserve">2.10821938514709</t>
   </si>
   <si>
     <t xml:space="preserve">2.09102511405945</t>
@@ -5249,13 +5249,13 @@
     <t xml:space="preserve">2.06418466567993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03482842445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03231191635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04657101631165</t>
+    <t xml:space="preserve">2.03482866287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0323121547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04657077789307</t>
   </si>
   <si>
     <t xml:space="preserve">1.98156714439392</t>
@@ -5264,22 +5264,22 @@
     <t xml:space="preserve">1.98282539844513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01427865028381</t>
+    <t xml:space="preserve">2.01427888870239</t>
   </si>
   <si>
     <t xml:space="preserve">1.99330961704254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03398942947388</t>
+    <t xml:space="preserve">2.03398966789246</t>
   </si>
   <si>
     <t xml:space="preserve">2.04908728599548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05286169052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02686023712158</t>
+    <t xml:space="preserve">2.05286145210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.026859998703</t>
   </si>
   <si>
     <t xml:space="preserve">2.03650593757629</t>
@@ -5294,7 +5294,7 @@
     <t xml:space="preserve">1.99079346656799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97611498832703</t>
+    <t xml:space="preserve">1.97611522674561</t>
   </si>
   <si>
     <t xml:space="preserve">1.98785769939423</t>
@@ -5312,31 +5312,31 @@
     <t xml:space="preserve">2.11702680587769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15015769004822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15225434303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1505765914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15435123443604</t>
+    <t xml:space="preserve">2.15015745162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15225458145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15057682991028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15435147285461</t>
   </si>
   <si>
     <t xml:space="preserve">2.16231966018677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18286919593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20551562309265</t>
+    <t xml:space="preserve">2.18286895751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20551586151123</t>
   </si>
   <si>
     <t xml:space="preserve">2.21893572807312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21977472305298</t>
+    <t xml:space="preserve">2.2197744846344</t>
   </si>
   <si>
     <t xml:space="preserve">2.25164723396301</t>
@@ -6735,6 +6735,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.48000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47100019454956</t>
   </si>
 </sst>
 </file>
@@ -71735,7 +71738,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.650162037</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>38242104</v>
@@ -71756,6 +71759,32 @@
         <v>2240</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6503125</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>58968702</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>5.47499990463257</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>5.34600019454956</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>5.47100019454956</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>2241</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISP.MI.xlsx
+++ b/data/ISP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="2242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="2243">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53063905239105</t>
+    <t xml:space="preserve">1.53063881397247</t>
   </si>
   <si>
     <t xml:space="preserve">ISP.MI</t>
@@ -50,31 +50,31 @@
     <t xml:space="preserve">1.5183197259903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49265503883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48752236366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46699070930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49676144123077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52447915077209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48546922206879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4382461309433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3663854598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38075721263885</t>
+    <t xml:space="preserve">1.49265551567078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48752224445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46699059009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49676156044006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52447938919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48546934127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43824625015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36638522148132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38075745105743</t>
   </si>
   <si>
     <t xml:space="preserve">1.30479025840759</t>
@@ -83,37 +83,37 @@
     <t xml:space="preserve">1.36843836307526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39307641983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35406613349915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37254500389099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35919892787933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29041802883148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380030632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31505572795868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26988637447357</t>
+    <t xml:space="preserve">1.39307653903961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35406637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37254464626312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35919916629791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2904177904129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380042552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31505584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26988613605499</t>
   </si>
   <si>
     <t xml:space="preserve">1.20315825939178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27296578884125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22368991374969</t>
+    <t xml:space="preserve">1.27296602725983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">1.17441380023956</t>
@@ -128,127 +128,127 @@
     <t xml:space="preserve">1.2298492193222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25243437290192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28220534324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21958351135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19494569301605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23395574092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20110511779785</t>
+    <t xml:space="preserve">1.25243425369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28220522403717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21958327293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19494557380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23395586013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20110487937927</t>
   </si>
   <si>
     <t xml:space="preserve">1.16004157066345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18057334423065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20007824897766</t>
+    <t xml:space="preserve">1.18057322502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20007848739624</t>
   </si>
   <si>
     <t xml:space="preserve">1.20213174819946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22471630573273</t>
+    <t xml:space="preserve">1.22471654415131</t>
   </si>
   <si>
     <t xml:space="preserve">1.27091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32224225997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29555094242096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27604579925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2914445400238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30581665039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40334212779999</t>
+    <t xml:space="preserve">1.32224214076996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29555082321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26475346088409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27604591846466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29144442081451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30581653118134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40334224700928</t>
   </si>
   <si>
     <t xml:space="preserve">1.37459790706635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36022579669952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33045482635498</t>
+    <t xml:space="preserve">1.36022567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33045470714569</t>
   </si>
   <si>
     <t xml:space="preserve">1.29349756240845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27912569046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29247117042542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25756752490997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.236008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24935472011566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24114179611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21753025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18673276901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1354033946991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1487489938736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1107656955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17749357223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1980254650116</t>
+    <t xml:space="preserve">1.27912545204163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29247093200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2575671672821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23600912094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24935436248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24114191532135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21753013134003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18673300743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13540351390839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14874911308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11076545715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1774936914444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19802534580231</t>
   </si>
   <si>
     <t xml:space="preserve">1.24422168731689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2503809928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2565404176712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.262699842453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24216830730438</t>
+    <t xml:space="preserve">1.25038123130798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25654053688049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26270020008087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24216842651367</t>
   </si>
   <si>
     <t xml:space="preserve">1.2780989408493</t>
@@ -257,133 +257,133 @@
     <t xml:space="preserve">1.23190259933472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26680648326874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26783299446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18878602981567</t>
+    <t xml:space="preserve">1.26680636405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26783323287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18878591060638</t>
   </si>
   <si>
     <t xml:space="preserve">1.16209471225739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13951003551483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14258968830109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14977550506592</t>
+    <t xml:space="preserve">1.13950991630554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1425895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14977562427521</t>
   </si>
   <si>
     <t xml:space="preserve">1.15798842906952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14566946029663</t>
+    <t xml:space="preserve">1.14566934108734</t>
   </si>
   <si>
     <t xml:space="preserve">1.14156293869019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12924408912659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12103140354156</t>
+    <t xml:space="preserve">1.1292439699173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12103128433228</t>
   </si>
   <si>
     <t xml:space="preserve">1.15080225467682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17852008342743</t>
+    <t xml:space="preserve">1.17852032184601</t>
   </si>
   <si>
     <t xml:space="preserve">1.18775928020477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18666672706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25878441333771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28719437122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29702889919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26096987724304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24020862579346</t>
+    <t xml:space="preserve">1.18666660785675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.258784532547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28719460964203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2970290184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26096999645233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24020874500275</t>
   </si>
   <si>
     <t xml:space="preserve">1.23037457466125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20852041244507</t>
+    <t xml:space="preserve">1.20852053165436</t>
   </si>
   <si>
     <t xml:space="preserve">1.20414972305298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22491085529327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2107058763504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1997789144516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15060770511627</t>
+    <t xml:space="preserve">1.22491109371185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21070611476898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19977915287018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15060782432556</t>
   </si>
   <si>
     <t xml:space="preserve">1.08286082744598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04516267776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07466542720795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06537759304047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11454880237579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14842224121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17683219909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17573964595795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23365259170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950644552707672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846838653087616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887268126010895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900380611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929883360862732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917863786220551</t>
+    <t xml:space="preserve">1.0451625585556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07466530799866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06537747383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1145486831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14842247962952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17683267593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17573976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23365247249603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950644612312317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846838533878326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887268245220184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900380730628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929883480072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917863667011261</t>
   </si>
   <si>
     <t xml:space="preserve">0.889999866485596</t>
@@ -392,40 +392,40 @@
     <t xml:space="preserve">0.870331525802612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868692338466644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874155819416046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961571574211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983425140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04789423942566</t>
+    <t xml:space="preserve">0.868692457675934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874155759811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961571514606476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983425319194794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04789435863495</t>
   </si>
   <si>
     <t xml:space="preserve">1.03587460517883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05772864818573</t>
+    <t xml:space="preserve">1.05772888660431</t>
   </si>
   <si>
     <t xml:space="preserve">1.05499696731567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05718219280243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05062615871429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06373846530914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0670166015625</t>
+    <t xml:space="preserve">1.05718243122101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.050626039505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06373834609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06701636314392</t>
   </si>
   <si>
     <t xml:space="preserve">1.06865561008453</t>
@@ -440,40 +440,40 @@
     <t xml:space="preserve">1.07193374633789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03969919681549</t>
+    <t xml:space="preserve">1.03969931602478</t>
   </si>
   <si>
     <t xml:space="preserve">1.07630455493927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03860652446747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999269545078278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993806004524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994352579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03806018829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05117249488831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0560896396637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07958257198334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05827486515045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03041136264801</t>
+    <t xml:space="preserve">1.03860628604889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999269425868988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993806064128876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994352519512177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03806006908417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0511726140976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05608952045441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07958269119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05827510356903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03041124343872</t>
   </si>
   <si>
     <t xml:space="preserve">1.00965011119843</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">1.09214842319489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08231449127197</t>
+    <t xml:space="preserve">1.08231437206268</t>
   </si>
   <si>
     <t xml:space="preserve">1.10034370422363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08996319770813</t>
+    <t xml:space="preserve">1.08996307849884</t>
   </si>
   <si>
     <t xml:space="preserve">1.11673414707184</t>
@@ -500,19 +500,19 @@
     <t xml:space="preserve">1.16372013092041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19759356975555</t>
+    <t xml:space="preserve">1.19759368896484</t>
   </si>
   <si>
     <t xml:space="preserve">1.19213008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1680908203125</t>
+    <t xml:space="preserve">1.16809093952179</t>
   </si>
   <si>
     <t xml:space="preserve">1.17901790142059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18338871002197</t>
+    <t xml:space="preserve">1.1833883523941</t>
   </si>
   <si>
     <t xml:space="preserve">1.15934920310974</t>
@@ -521,52 +521,52 @@
     <t xml:space="preserve">1.13749551773071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1364027261734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12766110897064</t>
+    <t xml:space="preserve">1.13640260696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12766098976135</t>
   </si>
   <si>
     <t xml:space="preserve">1.09706556797028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11236333847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12656855583191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09050965309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0779435634613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06428480148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0615531206131</t>
+    <t xml:space="preserve">1.11236321926117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12656843662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09050953388214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07794344425201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06428468227386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06155288219452</t>
   </si>
   <si>
     <t xml:space="preserve">1.06319212913513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07848966121674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05445075035095</t>
+    <t xml:space="preserve">1.07848989963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05445051193237</t>
   </si>
   <si>
     <t xml:space="preserve">1.08941674232483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0937876701355</t>
+    <t xml:space="preserve">1.09378755092621</t>
   </si>
   <si>
     <t xml:space="preserve">1.07685077190399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08340692520142</t>
+    <t xml:space="preserve">1.08340704441071</t>
   </si>
   <si>
     <t xml:space="preserve">1.12329030036926</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">1.13093912601471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15170049667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15388572216034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17792499065399</t>
+    <t xml:space="preserve">1.15170037746429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15388584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17792522907257</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196449756622</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">1.18229591846466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15279316902161</t>
+    <t xml:space="preserve">1.15279304981232</t>
   </si>
   <si>
     <t xml:space="preserve">1.13858807086945</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">1.16918361186981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22054004669189</t>
+    <t xml:space="preserve">1.22054016590118</t>
   </si>
   <si>
     <t xml:space="preserve">1.21835482120514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15497863292694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14186608791351</t>
+    <t xml:space="preserve">1.15497851371765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1418662071228</t>
   </si>
   <si>
     <t xml:space="preserve">1.11891961097717</t>
@@ -626,46 +626,46 @@
     <t xml:space="preserve">1.10362184047699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06810927391052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11345624923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14514446258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24567198753357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26643347740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30904829502106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27845311164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32762432098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29265785217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33636593818665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31888282299042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3374582529068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33855152130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34401476383209</t>
+    <t xml:space="preserve">1.06810939311981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11345613002777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14514422416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24567222595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26643323898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30904853343964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27845299243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32762444019318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29265797138214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33636605739594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31888294219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33745849132538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855140209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34401488304138</t>
   </si>
   <si>
     <t xml:space="preserve">1.33964395523071</t>
@@ -674,43 +674,43 @@
     <t xml:space="preserve">1.32871687412262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3177901506424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32543897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36805379390717</t>
+    <t xml:space="preserve">1.31779026985168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32543909549713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36805391311646</t>
   </si>
   <si>
     <t xml:space="preserve">1.38772261142731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39755690097809</t>
+    <t xml:space="preserve">1.3975567817688</t>
   </si>
   <si>
     <t xml:space="preserve">1.38990795612335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35275602340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34838557243347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34619987010956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34729278087616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32216084003448</t>
+    <t xml:space="preserve">1.35275638103485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3483852148056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34620010852814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34729266166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32216095924377</t>
   </si>
   <si>
     <t xml:space="preserve">1.34292197227478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3494781255722</t>
+    <t xml:space="preserve">1.34947824478149</t>
   </si>
   <si>
     <t xml:space="preserve">1.31014120578766</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">1.25659906864166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22928190231323</t>
+    <t xml:space="preserve">1.22928178310394</t>
   </si>
   <si>
     <t xml:space="preserve">1.23911619186401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20087158679962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18557405471802</t>
+    <t xml:space="preserve">1.20087194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18557393550873</t>
   </si>
   <si>
     <t xml:space="preserve">1.19103741645813</t>
@@ -740,64 +740,64 @@
     <t xml:space="preserve">1.22272562980652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19322299957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17027628421783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1735543012619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16590535640717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17136907577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19650113582611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18120324611664</t>
+    <t xml:space="preserve">1.19322264194489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17027604579926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17355453968048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16590547561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17136895656586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19650101661682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18120312690735</t>
   </si>
   <si>
     <t xml:space="preserve">1.13421714305878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25113570690155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2762678861618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2686185836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189707756042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27408230304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30577051639557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34182941913605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3232536315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35057079792023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35603439807892</t>
+    <t xml:space="preserve">1.25113546848297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27626776695251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26861882209778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189683914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27408218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30577027797699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34182965755463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32325351238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35057103633881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35603451728821</t>
   </si>
   <si>
     <t xml:space="preserve">1.36914682388306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39100050926208</t>
+    <t xml:space="preserve">1.39100074768066</t>
   </si>
   <si>
     <t xml:space="preserve">1.38662993907928</t>
@@ -809,151 +809,151 @@
     <t xml:space="preserve">1.37679553031921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38007390499115</t>
+    <t xml:space="preserve">1.38007378578186</t>
   </si>
   <si>
     <t xml:space="preserve">1.37898087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37461018562317</t>
+    <t xml:space="preserve">1.37461042404175</t>
   </si>
   <si>
     <t xml:space="preserve">1.36696147918701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35384893417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33199501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30467784404755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35166370868683</t>
+    <t xml:space="preserve">1.35384917259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33199512958527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30467772483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35166347026825</t>
   </si>
   <si>
     <t xml:space="preserve">1.36040532588959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37351763248444</t>
+    <t xml:space="preserve">1.37351751327515</t>
   </si>
   <si>
     <t xml:space="preserve">1.47623074054718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50573360919952</t>
+    <t xml:space="preserve">1.5057338476181</t>
   </si>
   <si>
     <t xml:space="preserve">1.49480664730072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45984041690826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46093332767487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46311843395233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47076737880707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50791919231415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55271947383881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55818295478821</t>
+    <t xml:space="preserve">1.45984029769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46093308925629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46311855316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47076725959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50791895389557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55271923542023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55818283557892</t>
   </si>
   <si>
     <t xml:space="preserve">1.55599772930145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5570901632309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54725587368011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54507052898407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55162680149078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52868008613586</t>
+    <t xml:space="preserve">1.55708992481232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54725623130798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54507064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55162668228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52868020534515</t>
   </si>
   <si>
     <t xml:space="preserve">1.52212393283844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52977299690247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56594610214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57061350345612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56711292266846</t>
+    <t xml:space="preserve">1.52977275848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56594622135162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57061326503754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56711280345917</t>
   </si>
   <si>
     <t xml:space="preserve">1.55427742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52977275848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49826729297638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48893237113953</t>
+    <t xml:space="preserve">1.52977287769318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49826717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48893249034882</t>
   </si>
   <si>
     <t xml:space="preserve">1.48659861087799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50060141086578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5111026763916</t>
+    <t xml:space="preserve">1.50060129165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51110315322876</t>
   </si>
   <si>
     <t xml:space="preserve">1.49126589298248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48426485061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49943399429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50876915454865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50176799297333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50410187244415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49710035324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47843050956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51460313796997</t>
+    <t xml:space="preserve">1.48426461219788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4994341135025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50876903533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50176763534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50410175323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49710047245026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47843039035797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51460349559784</t>
   </si>
   <si>
     <t xml:space="preserve">1.52510547637939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52627229690552</t>
+    <t xml:space="preserve">1.52627205848694</t>
   </si>
   <si>
     <t xml:space="preserve">1.57994830608368</t>
@@ -962,49 +962,49 @@
     <t xml:space="preserve">1.60795366764069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64062595367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61845517158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61962223052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66279649734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6592960357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67213177680969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65696239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66863095760345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6534618139267</t>
+    <t xml:space="preserve">1.64062607288361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61845505237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6196221113205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66279673576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65929615497589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67213153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65696227550507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66863107681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65346157550812</t>
   </si>
   <si>
     <t xml:space="preserve">1.66162991523743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66396355628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6709645986557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67446529865265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66629731655121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67329847812653</t>
+    <t xml:space="preserve">1.6639631986618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67096483707428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67446517944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66629719734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67329859733582</t>
   </si>
   <si>
     <t xml:space="preserve">1.6838002204895</t>
@@ -1013,46 +1013,46 @@
     <t xml:space="preserve">1.69313526153564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69546902179718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69430243968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69896972179413</t>
+    <t xml:space="preserve">1.69546937942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69430220127106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69896960258484</t>
   </si>
   <si>
     <t xml:space="preserve">1.70130348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6919686794281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7036372423172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70830476284027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70480418205261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263363838196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67796611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66046285629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70713818073273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68963444232941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64295959472656</t>
+    <t xml:space="preserve">1.69196856021881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70363748073578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70830464363098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70480394363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67796587944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66046273708344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70713794231415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68963468074799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64295971393585</t>
   </si>
   <si>
     <t xml:space="preserve">1.65462863445282</t>
@@ -1061,106 +1061,106 @@
     <t xml:space="preserve">1.65812909603119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63712525367737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6651303768158</t>
+    <t xml:space="preserve">1.63712561130524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66513049602509</t>
   </si>
   <si>
     <t xml:space="preserve">1.68146681785583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70013666152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71063840389252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71763956546783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73280894756317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73397600650787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72464084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.735142827034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447774887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74214422702789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74564504623413</t>
+    <t xml:space="preserve">1.70013654232025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7106386423111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71763980388641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73280942440033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73397612571716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72464108467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73514294624329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74214398860931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74564468860626</t>
   </si>
   <si>
     <t xml:space="preserve">1.74681174755096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74097728729248</t>
+    <t xml:space="preserve">1.7409770488739</t>
   </si>
   <si>
     <t xml:space="preserve">1.71180534362793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71530604362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70947194099426</t>
+    <t xml:space="preserve">1.71530592441559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70947182178497</t>
   </si>
   <si>
     <t xml:space="preserve">1.68496739864349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66746401786804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68029963970184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597088336945</t>
+    <t xml:space="preserve">1.66746425628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68029999732971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597112178802</t>
   </si>
   <si>
     <t xml:space="preserve">1.67913281917572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65112769603729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63362491130829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63479161262512</t>
+    <t xml:space="preserve">1.65112781524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.633624792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63479137420654</t>
   </si>
   <si>
     <t xml:space="preserve">1.61728870868683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.614954829216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64412665367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61378800868988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64529347419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64646029472351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67563199996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63829243183136</t>
+    <t xml:space="preserve">1.61495471000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64412701129913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61378788948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64529323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64646053314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67563223838806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63829207420349</t>
   </si>
   <si>
     <t xml:space="preserve">1.62895739078522</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">1.62662374973297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62779033184052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61612153053284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60678672790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60445308685303</t>
+    <t xml:space="preserve">1.62779021263123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61612164974213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60678660869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60445249080658</t>
   </si>
   <si>
     <t xml:space="preserve">1.74331104755402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76548159122467</t>
+    <t xml:space="preserve">1.76548194885254</t>
   </si>
   <si>
     <t xml:space="preserve">1.77248299121857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77598369121552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78415167331696</t>
+    <t xml:space="preserve">1.77598357200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78415179252625</t>
   </si>
   <si>
     <t xml:space="preserve">1.80515551567078</t>
@@ -1202,157 +1202,157 @@
     <t xml:space="preserve">1.80165481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8238251209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82499206066132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79815399646759</t>
+    <t xml:space="preserve">1.82382524013519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8249922990799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79815411567688</t>
   </si>
   <si>
     <t xml:space="preserve">1.82149147987366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84366226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824811458588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83549416065216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84395384788513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111810684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81769967079163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902911186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81098985671997</t>
+    <t xml:space="preserve">1.84366250038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824823379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83549404144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84395360946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8311185836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81769943237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902899265289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81098973751068</t>
   </si>
   <si>
     <t xml:space="preserve">1.87283396720886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83636951446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81157338619232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377830028534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8092395067215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80690550804138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83053493499756</t>
+    <t xml:space="preserve">1.83636963367462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81157314777374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377841949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923938751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80690562725067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83053505420685</t>
   </si>
   <si>
     <t xml:space="preserve">1.81303179264069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80223798751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80748915672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78444349765778</t>
+    <t xml:space="preserve">1.80223834514618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80748903751373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78444302082062</t>
   </si>
   <si>
     <t xml:space="preserve">1.79873752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79990410804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80982267856598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80632221698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79290306568146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75410485267639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72930836677551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74535298347473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76519012451172</t>
+    <t xml:space="preserve">1.79990434646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80982291698456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80632245540619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79290318489075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75410461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7293084859848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74535310268402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76518952846527</t>
   </si>
   <si>
     <t xml:space="preserve">1.77510833740234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78035914897919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540004253387</t>
+    <t xml:space="preserve">1.78035926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540016174316</t>
   </si>
   <si>
     <t xml:space="preserve">1.74885368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76081383228302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79523682594299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77364957332611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78473520278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77423286437988</t>
+    <t xml:space="preserve">1.76081418991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79523694515228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7736496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78473508358002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77423310279846</t>
   </si>
   <si>
     <t xml:space="preserve">1.74272763729095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72259902954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7074294090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72289073467255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72318232059479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72522437572479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71909844875336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75206232070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74768674373627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76256442070007</t>
+    <t xml:space="preserve">1.72259914875031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70742964744568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72289061546326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72318279743195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72522461414337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71909832954407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7520626783371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74768686294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76256453990936</t>
   </si>
   <si>
     <t xml:space="preserve">1.77131593227386</t>
@@ -1361,235 +1361,235 @@
     <t xml:space="preserve">1.7590639591217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77948415279388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78940272331238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79465341567993</t>
+    <t xml:space="preserve">1.77948439121246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78940236568451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79465329647064</t>
   </si>
   <si>
     <t xml:space="preserve">1.81449043750763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81536543369293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82907605171204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84832978248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86437404155731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83986961841583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85124683380127</t>
+    <t xml:space="preserve">1.8153657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82907629013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84832942485809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86437439918518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986985683441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85124695301056</t>
   </si>
   <si>
     <t xml:space="preserve">1.83957827091217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.841912150383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84862124919891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83811938762665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84453749656677</t>
+    <t xml:space="preserve">1.84191226959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84862172603607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83811950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84453761577606</t>
   </si>
   <si>
     <t xml:space="preserve">1.83403563499451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82674241065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83782815933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85416412353516</t>
+    <t xml:space="preserve">1.82674264907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83782804012299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85416400432587</t>
   </si>
   <si>
     <t xml:space="preserve">1.80865609645844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7943617105484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031244754791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73967385292053</t>
+    <t xml:space="preserve">1.79436159133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031208992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73967409133911</t>
   </si>
   <si>
     <t xml:space="preserve">1.75156366825104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72090065479279</t>
+    <t xml:space="preserve">1.72090005874634</t>
   </si>
   <si>
     <t xml:space="preserve">1.70494282245636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6508127450943</t>
+    <t xml:space="preserve">1.65081286430359</t>
   </si>
   <si>
     <t xml:space="preserve">1.59730851650238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53191411495209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57759630680084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57352888584137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62546873092651</t>
+    <t xml:space="preserve">1.53191435337067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57759654521942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57352876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6254688501358</t>
   </si>
   <si>
     <t xml:space="preserve">1.62515580654144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56289041042328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55475544929504</t>
+    <t xml:space="preserve">1.56289052963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55475521087646</t>
   </si>
   <si>
     <t xml:space="preserve">1.53629469871521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51752114295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61827218532562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62578165531158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6232784986496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59417951107025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59793424606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60575652122498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63548147678375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6032532453537</t>
+    <t xml:space="preserve">1.51752150058746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61827206611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6173335313797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62578153610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62327837944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59417963027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59793412685394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60575664043427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63548135757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60325360298157</t>
   </si>
   <si>
     <t xml:space="preserve">1.6195240020752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56695795059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55068778991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690815925598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55694544315338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55600678920746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54474294185638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57634472846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58416724205017</t>
+    <t xml:space="preserve">1.56695783138275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55068790912628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690804004669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55694556236267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55600702762604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54474258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57634484767914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58416736125946</t>
   </si>
   <si>
     <t xml:space="preserve">1.60513079166412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60294044017792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60606920719147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58041250705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54881036281586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53066289424896</t>
+    <t xml:space="preserve">1.60294055938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60606932640076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58041214942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54881024360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53066277503967</t>
   </si>
   <si>
     <t xml:space="preserve">1.53973650932312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53660786151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5519392490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54161417484283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51658236980438</t>
+    <t xml:space="preserve">1.53660762310028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55193936824799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54161393642426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51658284664154</t>
   </si>
   <si>
     <t xml:space="preserve">1.5053186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50250232219696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53097546100616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55037462711334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57039976119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58322858810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64830958843231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57259023189545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51188933849335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53003692626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50844752788544</t>
+    <t xml:space="preserve">1.50250256061554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53097569942474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55037486553192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57039964199066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58322834968567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6483097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57259011268616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51188910007477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53003716468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50844776630402</t>
   </si>
   <si>
     <t xml:space="preserve">1.49248993396759</t>
@@ -1604,37 +1604,37 @@
     <t xml:space="preserve">1.40175139904022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37640726566315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36576902866364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35732114315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40331614017487</t>
+    <t xml:space="preserve">1.37640738487244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36576926708221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35732126235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40331590175629</t>
   </si>
   <si>
     <t xml:space="preserve">1.38329112529755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37672054767609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37891066074371</t>
+    <t xml:space="preserve">1.3767204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37891054153442</t>
   </si>
   <si>
     <t xml:space="preserve">1.37859773635864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36357879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38172662258148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34918570518494</t>
+    <t xml:space="preserve">1.3635790348053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38172650337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34918618202209</t>
   </si>
   <si>
     <t xml:space="preserve">1.3313512802124</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">1.42897319793701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45901048183441</t>
+    <t xml:space="preserve">1.45901072025299</t>
   </si>
   <si>
     <t xml:space="preserve">1.43929851055145</t>
@@ -1655,16 +1655,16 @@
     <t xml:space="preserve">1.41583180427551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47997450828552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.456507563591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46432995796204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45744645595551</t>
+    <t xml:space="preserve">1.47997415065765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45650780200958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46432960033417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45744621753693</t>
   </si>
   <si>
     <t xml:space="preserve">1.46683311462402</t>
@@ -1673,82 +1673,82 @@
     <t xml:space="preserve">1.50093805789948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49906063079834</t>
+    <t xml:space="preserve">1.49906051158905</t>
   </si>
   <si>
     <t xml:space="preserve">1.51908564567566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5115761756897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53222727775574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49999928474426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54568147659302</t>
+    <t xml:space="preserve">1.51157641410828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53222703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49999964237213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54568159580231</t>
   </si>
   <si>
     <t xml:space="preserve">1.5222145318985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50437998771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37734627723694</t>
+    <t xml:space="preserve">1.50437986850739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37734591960907</t>
   </si>
   <si>
     <t xml:space="preserve">1.32352888584137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31914854049683</t>
+    <t xml:space="preserve">1.31914842128754</t>
   </si>
   <si>
     <t xml:space="preserve">1.32634484767914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35481798648834</t>
+    <t xml:space="preserve">1.35481774806976</t>
   </si>
   <si>
     <t xml:space="preserve">1.31320345401764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27033746242523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29818475246429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30506837368011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27284049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26783430576324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27753400802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29536855220795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28066265583038</t>
+    <t xml:space="preserve">1.27033722400665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29818487167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30506825447083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27284073829651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26783442497253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27753412723541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29536867141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28066277503967</t>
   </si>
   <si>
     <t xml:space="preserve">1.23842263221741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24167668819427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23128867149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23166418075562</t>
+    <t xml:space="preserve">1.2416764497757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23128855228424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23166394233704</t>
   </si>
   <si>
     <t xml:space="preserve">1.18936133384705</t>
@@ -1757,19 +1757,19 @@
     <t xml:space="preserve">1.22227740287781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21264040470123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24943614006042</t>
+    <t xml:space="preserve">1.21264028549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24943625926971</t>
   </si>
   <si>
     <t xml:space="preserve">1.24655759334564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22215223312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24267780780792</t>
+    <t xml:space="preserve">1.2221519947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24267792701721</t>
   </si>
   <si>
     <t xml:space="preserve">1.25563156604767</t>
@@ -1784,43 +1784,43 @@
     <t xml:space="preserve">1.28598201274872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26971173286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25500571727753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22665774822235</t>
+    <t xml:space="preserve">1.2697114944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25500583648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22665786743164</t>
   </si>
   <si>
     <t xml:space="preserve">1.25312840938568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23829734325409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22265291213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20112597942352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20538139343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17571926116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20901072025299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20888555049896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22165167331696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2769079208374</t>
+    <t xml:space="preserve">1.23829746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2226527929306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20112574100494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20538115501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17571914196014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2090106010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20888566970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22165143489838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27690815925598</t>
   </si>
   <si>
     <t xml:space="preserve">1.27628231048584</t>
@@ -1832,214 +1832,214 @@
     <t xml:space="preserve">1.2719019651413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28160166740417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32196426391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29161393642426</t>
+    <t xml:space="preserve">1.28160154819489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32196450233459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29161381721497</t>
   </si>
   <si>
     <t xml:space="preserve">1.30193936824799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23491811752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24029994010925</t>
+    <t xml:space="preserve">1.23491823673248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24029982089996</t>
   </si>
   <si>
     <t xml:space="preserve">1.21376669406891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21026217937469</t>
+    <t xml:space="preserve">1.21026229858398</t>
   </si>
   <si>
     <t xml:space="preserve">1.25969910621643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27158915996552</t>
+    <t xml:space="preserve">1.27158904075623</t>
   </si>
   <si>
     <t xml:space="preserve">1.26032471656799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23466801643372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24217712879181</t>
+    <t xml:space="preserve">1.23466777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2421772480011</t>
   </si>
   <si>
     <t xml:space="preserve">1.26345384120941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21714603900909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19662034511566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19461786746979</t>
+    <t xml:space="preserve">1.2171459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19662022590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1946177482605</t>
   </si>
   <si>
     <t xml:space="preserve">1.21389198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19299077987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18986189365387</t>
+    <t xml:space="preserve">1.19299054145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18986201286316</t>
   </si>
   <si>
     <t xml:space="preserve">1.25106334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27221477031708</t>
+    <t xml:space="preserve">1.27221488952637</t>
   </si>
   <si>
     <t xml:space="preserve">1.25750887393951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26470541954041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25844740867615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24017477035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22465527057648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26001226902008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27565670013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27596962451935</t>
+    <t xml:space="preserve">1.26470530033112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25844752788544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24017465114594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22465538978577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26001214981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27565658092499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27596950531006</t>
   </si>
   <si>
     <t xml:space="preserve">1.26814711093903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26908576488495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29192709922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28003716468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28191435337067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28973662853241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24830973148346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22815954685211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22753393650055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24705862998962</t>
+    <t xml:space="preserve">1.26908612251282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29192686080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28003704547882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28191447257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28973686695099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24830996990204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22815978527069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22753381729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24705827236176</t>
   </si>
   <si>
     <t xml:space="preserve">1.2418018579483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23616981506348</t>
+    <t xml:space="preserve">1.2361695766449</t>
   </si>
   <si>
     <t xml:space="preserve">1.25131368637085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25531852245331</t>
+    <t xml:space="preserve">1.25531876087189</t>
   </si>
   <si>
     <t xml:space="preserve">1.24155139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28097569942474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2922397851944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28629493713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28692054748535</t>
+    <t xml:space="preserve">1.28097581863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29223990440369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28629469871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28692066669464</t>
   </si>
   <si>
     <t xml:space="preserve">1.27659523487091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27784693241119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30444252490997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29943645000458</t>
+    <t xml:space="preserve">1.27784669399261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30444240570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.299436211586</t>
   </si>
   <si>
     <t xml:space="preserve">1.3338543176651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35043752193451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513091087341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35262787342072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36545622348785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33510601520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32603204250336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33760905265808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33667027950287</t>
+    <t xml:space="preserve">1.35043740272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513079166412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35262763500214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36545610427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3351057767868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32603192329407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33760893344879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33667039871216</t>
   </si>
   <si>
     <t xml:space="preserve">1.34824728965759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35794699192047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37609446048737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39737129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39924848079681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39549374580383</t>
+    <t xml:space="preserve">1.35794687271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37609434127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39737117290497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3992486000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39549398422241</t>
   </si>
   <si>
     <t xml:space="preserve">1.38610696792603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34949910640717</t>
+    <t xml:space="preserve">1.34949898719788</t>
   </si>
   <si>
     <t xml:space="preserve">1.34480535984039</t>
@@ -2051,124 +2051,124 @@
     <t xml:space="preserve">1.3516891002655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35419237613678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38016200065613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37546873092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38767170906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39799678325653</t>
+    <t xml:space="preserve">1.35419225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38016211986542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37546896934509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38767147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39799666404724</t>
   </si>
   <si>
     <t xml:space="preserve">1.39956140518188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39017462730408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39830982685089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43992447853088</t>
+    <t xml:space="preserve">1.39017450809479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39830958843231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43992435932159</t>
   </si>
   <si>
     <t xml:space="preserve">1.45337879657745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46558165550232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45963633060455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45243990421295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42365419864655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42490565776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42991197109222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45932376384735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4624525308609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45619451999664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4530656337738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4327278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40300321578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38673281669617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35450518131256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35137605667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3254063129425</t>
+    <t xml:space="preserve">1.46558129787445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45963644981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45244002342224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42365396022797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42490553855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42991185188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45932364463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46245265007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45619463920593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45306587219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43272793292999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40300333499908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38673293590546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35450541973114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35137593746185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32540607452393</t>
   </si>
   <si>
     <t xml:space="preserve">1.34543132781982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36639487743378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35825991630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36135697364807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36066854000092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33630454540253</t>
+    <t xml:space="preserve">1.36639499664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35825979709625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36135709285736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36066877841949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33630478382111</t>
   </si>
   <si>
     <t xml:space="preserve">1.30973827838898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3206125497818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31331706047058</t>
+    <t xml:space="preserve">1.32061266899109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31331717967987</t>
   </si>
   <si>
     <t xml:space="preserve">1.29872620105743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28413534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28372251987457</t>
+    <t xml:space="preserve">1.28413546085358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28372240066528</t>
   </si>
   <si>
     <t xml:space="preserve">1.26211142539978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25674319267273</t>
+    <t xml:space="preserve">1.25674283504486</t>
   </si>
   <si>
     <t xml:space="preserve">1.28441059589386</t>
@@ -2177,34 +2177,34 @@
     <t xml:space="preserve">1.27326095104218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2570184469223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26142311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27037024497986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2713338136673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25811946392059</t>
+    <t xml:space="preserve">1.25701832771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2614232301712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27037036418915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133405208588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25811970233917</t>
   </si>
   <si>
     <t xml:space="preserve">1.2677549123764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26458919048309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2601842880249</t>
+    <t xml:space="preserve">1.2645890712738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26018416881561</t>
   </si>
   <si>
     <t xml:space="preserve">1.2893660068512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31262898445129</t>
+    <t xml:space="preserve">1.312628865242</t>
   </si>
   <si>
     <t xml:space="preserve">1.30134153366089</t>
@@ -2213,43 +2213,43 @@
     <t xml:space="preserve">1.29046726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29032969474792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28592479228973</t>
+    <t xml:space="preserve">1.29032957553864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28592467308044</t>
   </si>
   <si>
     <t xml:space="preserve">1.29239439964294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29294490814209</t>
+    <t xml:space="preserve">1.29294502735138</t>
   </si>
   <si>
     <t xml:space="preserve">1.29528498649597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28537404537201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29734969139099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36328387260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39439296722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38854265213013</t>
+    <t xml:space="preserve">1.28537428379059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29734981060028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36328399181366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39439272880554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39852249622345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38854277133942</t>
   </si>
   <si>
     <t xml:space="preserve">1.38097202777863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39783406257629</t>
+    <t xml:space="preserve">1.397833943367</t>
   </si>
   <si>
     <t xml:space="preserve">1.41469621658325</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">1.41159915924072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40987837314606</t>
+    <t xml:space="preserve">1.40987861156464</t>
   </si>
   <si>
     <t xml:space="preserve">1.41916990280151</t>
@@ -2267,13 +2267,13 @@
     <t xml:space="preserve">1.40609312057495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41091084480286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38200414180756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3844131231308</t>
+    <t xml:space="preserve">1.41091072559357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38200449943542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38441324234009</t>
   </si>
   <si>
     <t xml:space="preserve">1.40058720111847</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">1.3902633190155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38338100910187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37044191360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35309779644012</t>
+    <t xml:space="preserve">1.38338077068329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37044179439545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35309791564941</t>
   </si>
   <si>
     <t xml:space="preserve">1.34924364089966</t>
@@ -2297,31 +2297,31 @@
     <t xml:space="preserve">1.37649834156036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3438755273819</t>
+    <t xml:space="preserve">1.34387528896332</t>
   </si>
   <si>
     <t xml:space="preserve">1.35433685779572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33836960792542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31455612182617</t>
+    <t xml:space="preserve">1.33836948871613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31455588340759</t>
   </si>
   <si>
     <t xml:space="preserve">1.33891999721527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26362562179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29886388778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2702329158783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31744647026062</t>
+    <t xml:space="preserve">1.26362574100494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29886412620544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27023267745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3174467086792</t>
   </si>
   <si>
     <t xml:space="preserve">1.31001353263855</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">1.32322788238525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33644235134125</t>
+    <t xml:space="preserve">1.33644223213196</t>
   </si>
   <si>
     <t xml:space="preserve">1.30987596511841</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">1.33520352840424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34084713459015</t>
+    <t xml:space="preserve">1.34084725379944</t>
   </si>
   <si>
     <t xml:space="preserve">1.35488748550415</t>
@@ -2357,31 +2357,31 @@
     <t xml:space="preserve">1.3768424987793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39542508125305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4150402545929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42261111736298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44635570049286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46149718761444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45082938671112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46080911159515</t>
+    <t xml:space="preserve">1.39542531967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41504049301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42261099815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44635558128357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46149730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45082926750183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46080887317657</t>
   </si>
   <si>
     <t xml:space="preserve">1.50175964832306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47526228427887</t>
+    <t xml:space="preserve">1.47526240348816</t>
   </si>
   <si>
     <t xml:space="preserve">1.46252954006195</t>
@@ -2393,22 +2393,22 @@
     <t xml:space="preserve">1.48937141895294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4907478094101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319757938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4659708738327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46941184997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47491800785065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4869624376297</t>
+    <t xml:space="preserve">1.49074769020081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319746017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46597099304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46941208839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47491788864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48696231842041</t>
   </si>
   <si>
     <t xml:space="preserve">1.49728608131409</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">1.48317694664001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44119393825531</t>
+    <t xml:space="preserve">1.4411940574646</t>
   </si>
   <si>
     <t xml:space="preserve">1.439129114151</t>
@@ -2435,19 +2435,19 @@
     <t xml:space="preserve">1.47939145565033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50451278686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50038325786591</t>
+    <t xml:space="preserve">1.50451290607452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50038349628448</t>
   </si>
   <si>
     <t xml:space="preserve">1.52103078365326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5406459569931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53582799434662</t>
+    <t xml:space="preserve">1.54064607620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53582787513733</t>
   </si>
   <si>
     <t xml:space="preserve">1.53789269924164</t>
@@ -2465,217 +2465,217 @@
     <t xml:space="preserve">1.56301391124725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56404638290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56817579269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56370234489441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54752850532532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54580771923065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5643904209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58710253238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6105033159256</t>
+    <t xml:space="preserve">1.56404650211334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5681756734848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56370222568512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54752826690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54580783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56439054012299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58710277080536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61050295829773</t>
   </si>
   <si>
     <t xml:space="preserve">1.60878252983093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62151515483856</t>
+    <t xml:space="preserve">1.62151539325714</t>
   </si>
   <si>
     <t xml:space="preserve">1.61256778240204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62220346927643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63665640354156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61394453048706</t>
+    <t xml:space="preserve">1.62220335006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63665664196014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61394429206848</t>
   </si>
   <si>
     <t xml:space="preserve">1.60086750984192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60912644863129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61738562583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61566495895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62013864517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61291182041168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61910617351532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61187982559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60189998149872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58985567092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58331739902496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54511952400208</t>
+    <t xml:space="preserve">1.60912680625916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61738550662994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61566543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62013852596283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61291193962097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61910629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61187970638275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60190033912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58985543251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58331727981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5451192855835</t>
   </si>
   <si>
     <t xml:space="preserve">1.5767787694931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57471430301666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5922646522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58090829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58572590351105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59054386615753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60224425792694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61497676372528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62633275985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62839734554291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6380330324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6552392244339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65214228630066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62082660198212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61635327339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63872146606445</t>
+    <t xml:space="preserve">1.57471442222595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59226429462433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58090841770172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58572626113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59054398536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60224401950836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61497664451599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62633287906647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6283974647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63803315162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65523946285248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65214192867279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62082695960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61635303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63872134685516</t>
   </si>
   <si>
     <t xml:space="preserve">1.61704134941101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63390362262726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61119151115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61532080173492</t>
+    <t xml:space="preserve">1.63390374183655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61119115352631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61532092094421</t>
   </si>
   <si>
     <t xml:space="preserve">1.59673798084259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59845900535583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60809421539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59570562839508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56920802593231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56094932556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56783199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55200231075287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58675861358643</t>
+    <t xml:space="preserve">1.59845876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60809445381165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59570586681366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56920826435089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56094944477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56783175468445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55200219154358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58675837516785</t>
   </si>
   <si>
     <t xml:space="preserve">1.57712316513062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54546356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57264959812164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61841785907745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.685866355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70100784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70410478115082</t>
+    <t xml:space="preserve">1.5454638004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57264947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61841797828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68586623668671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70100772380829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7041050195694</t>
   </si>
   <si>
     <t xml:space="preserve">1.69240474700928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70857846736908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72578477859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72750556468964</t>
+    <t xml:space="preserve">1.70857870578766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72578454017639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72750544548035</t>
   </si>
   <si>
     <t xml:space="preserve">1.74815309047699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78944790363312</t>
+    <t xml:space="preserve">1.78944754600525</t>
   </si>
   <si>
     <t xml:space="preserve">1.79185664653778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75503528118134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73542022705078</t>
+    <t xml:space="preserve">1.75503551959991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73542070388794</t>
   </si>
   <si>
     <t xml:space="preserve">1.63562417030334</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">1.51311564445496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47044444084167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45840013027191</t>
+    <t xml:space="preserve">1.4704442024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45840001106262</t>
   </si>
   <si>
     <t xml:space="preserve">1.46425032615662</t>
@@ -2705,97 +2705,97 @@
     <t xml:space="preserve">1.36080622673035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20443618297577</t>
+    <t xml:space="preserve">1.20443606376648</t>
   </si>
   <si>
     <t xml:space="preserve">1.17608022689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22453320026398</t>
+    <t xml:space="preserve">1.2245329618454</t>
   </si>
   <si>
     <t xml:space="preserve">1.00677096843719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06981444358826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965475857257843</t>
+    <t xml:space="preserve">1.06981456279755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965475976467133</t>
   </si>
   <si>
     <t xml:space="preserve">0.998924911022186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969467759132385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980892896652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00856029987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997135579586029</t>
+    <t xml:space="preserve">0.969467639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980892717838287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00856041908264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997135400772095</t>
   </si>
   <si>
     <t xml:space="preserve">1.08991146087646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11234855651855</t>
+    <t xml:space="preserve">1.11234831809998</t>
   </si>
   <si>
     <t xml:space="preserve">1.12253451347351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07821118831635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01227676868439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0243901014328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987499952316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989564776420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914821028709412</t>
+    <t xml:space="preserve">1.07821106910706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01227688789368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02439022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987500190734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989564597606659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914820909500122</t>
   </si>
   <si>
     <t xml:space="preserve">1.00360500812531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01103794574738</t>
+    <t xml:space="preserve">1.01103806495667</t>
   </si>
   <si>
     <t xml:space="preserve">0.997410833835602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994520127773285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967815935611725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928035140037537</t>
+    <t xml:space="preserve">0.99452006816864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967816114425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928035199642181</t>
   </si>
   <si>
     <t xml:space="preserve">0.936156630516052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947168707847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951848745346069</t>
+    <t xml:space="preserve">0.947168529033661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95184850692749</t>
   </si>
   <si>
     <t xml:space="preserve">0.908488988876343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921014964580536</t>
+    <t xml:space="preserve">0.921015202999115</t>
   </si>
   <si>
     <t xml:space="preserve">0.952812135219574</t>
@@ -2804,70 +2804,70 @@
     <t xml:space="preserve">0.924869239330292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960245370864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996034204959869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01888394355774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979378700256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947030901908875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998649656772614</t>
+    <t xml:space="preserve">0.960245430469513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996034145355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01888418197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979378640651703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947030961513519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998649477958679</t>
   </si>
   <si>
     <t xml:space="preserve">0.977451503276825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966577053070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973184406757355</t>
+    <t xml:space="preserve">0.966577172279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973184466362</t>
   </si>
   <si>
     <t xml:space="preserve">0.97001850605011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977864503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959144055843353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952261507511139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952399253845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999475538730621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984746813774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990390539169312</t>
+    <t xml:space="preserve">0.977864384651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959143996238708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952261745929718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952399432659149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999475359916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984746992588043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990390658378601</t>
   </si>
   <si>
     <t xml:space="preserve">0.978690326213837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994244754314423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00319182872772</t>
+    <t xml:space="preserve">0.994244813919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0031920671463</t>
   </si>
   <si>
     <t xml:space="preserve">1.0331996679306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05880272388458</t>
+    <t xml:space="preserve">1.05880260467529</t>
   </si>
   <si>
     <t xml:space="preserve">1.07270514965057</t>
@@ -2879,13 +2879,13 @@
     <t xml:space="preserve">1.08743369579315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11840486526489</t>
+    <t xml:space="preserve">1.11840510368347</t>
   </si>
   <si>
     <t xml:space="preserve">1.15157854557037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16575646400452</t>
+    <t xml:space="preserve">1.16575658321381</t>
   </si>
   <si>
     <t xml:space="preserve">1.2201281785965</t>
@@ -2894,61 +2894,61 @@
     <t xml:space="preserve">1.24118864536285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18378877639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17181313037872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11344969272614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11634004116058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11950612068176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16947317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17263901233673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16025042533875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15956223011017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15791034698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17786991596222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14717376232147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.142493724823</t>
+    <t xml:space="preserve">1.18378853797913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17181301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11344945430756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11634016036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11950623989105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16947305202484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17263889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16025054454803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15956211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15791046619415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17786967754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14717364311218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14249360561371</t>
   </si>
   <si>
     <t xml:space="preserve">1.17140018939972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17250144481659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16355407238007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20636308193207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20223355293274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23348021507263</t>
+    <t xml:space="preserve">1.1725013256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16355419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20636320114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20223343372345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23348033428192</t>
   </si>
   <si>
     <t xml:space="preserve">1.22962605953217</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">1.19149696826935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21503508090973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22604715824127</t>
+    <t xml:space="preserve">1.21503520011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22604727745056</t>
   </si>
   <si>
     <t xml:space="preserve">1.2257719039917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24875938892365</t>
+    <t xml:space="preserve">1.24875926971436</t>
   </si>
   <si>
     <t xml:space="preserve">1.26596558094025</t>
@@ -2978,91 +2978,91 @@
     <t xml:space="preserve">1.26073491573334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27628946304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29721200466156</t>
+    <t xml:space="preserve">1.27628934383392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29721188545227</t>
   </si>
   <si>
     <t xml:space="preserve">1.29129314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27271032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24944746494293</t>
+    <t xml:space="preserve">1.27271044254303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24944758415222</t>
   </si>
   <si>
     <t xml:space="preserve">1.23981201648712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22935080528259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23155319690704</t>
+    <t xml:space="preserve">1.22935056686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23155307769775</t>
   </si>
   <si>
     <t xml:space="preserve">1.1941123008728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17497909069061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17566740512848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23444378376007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26252448558807</t>
+    <t xml:space="preserve">1.17497897148132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1756671667099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23444366455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26252436637878</t>
   </si>
   <si>
     <t xml:space="preserve">1.24834632873535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24256503582001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24848413467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28096961975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2958357334137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28399777412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27436220645905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25564193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24903476238251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26981961727142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24999821186066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24683225154877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2658280134201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2622492313385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2681679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24146378040314</t>
+    <t xml:space="preserve">1.2425651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24848401546478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28096926212311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29583561420441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28399765491486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27436232566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25564181804657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24903464317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26981985569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24999833106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24683237075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26582789421082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26224899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26816809177399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24146389961243</t>
   </si>
   <si>
     <t xml:space="preserve">1.25605475902557</t>
@@ -3071,28 +3071,28 @@
     <t xml:space="preserve">1.24242746829987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24008738994598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22425782680511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2241199016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2345814704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21269500255585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2321035861969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23967432975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22439539432526</t>
+    <t xml:space="preserve">1.24008727073669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22425758838654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22411978244781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23458135128021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21269512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23210382461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23967444896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22439527511597</t>
   </si>
   <si>
     <t xml:space="preserve">1.2173752784729</t>
@@ -3101,10 +3101,10 @@
     <t xml:space="preserve">1.21145629882812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19989359378815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18020975589752</t>
+    <t xml:space="preserve">1.19989371299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18020963668823</t>
   </si>
   <si>
     <t xml:space="preserve">1.12570035457611</t>
@@ -3116,31 +3116,31 @@
     <t xml:space="preserve">1.10959541797638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10670459270477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08674550056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11812973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10587882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10326337814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09183859825134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09596800804138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1240485906601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14827501773834</t>
+    <t xml:space="preserve">1.10670483112335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08674538135529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1181298494339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10587894916534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1032634973526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09183847904205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09596812725067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12404870986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14827489852905</t>
   </si>
   <si>
     <t xml:space="preserve">1.13478529453278</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">1.15557038784027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14978909492493</t>
+    <t xml:space="preserve">1.14978933334351</t>
   </si>
   <si>
     <t xml:space="preserve">1.11317431926727</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">1.0707780122757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07353103160858</t>
+    <t xml:space="preserve">1.07353127002716</t>
   </si>
   <si>
     <t xml:space="preserve">1.05701315402985</t>
@@ -3176,37 +3176,37 @@
     <t xml:space="preserve">1.07449460029602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05095660686493</t>
+    <t xml:space="preserve">1.05095648765564</t>
   </si>
   <si>
     <t xml:space="preserve">1.02590417861938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97593742609024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96299821138382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977038681507111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02026057243347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06031656265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09968447685242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12680149078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11276137828827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2153103351593</t>
+    <t xml:space="preserve">0.975937366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962998330593109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977038443088531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02026045322418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0603164434433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.099684715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12680160999298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11276113986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21531045436859</t>
   </si>
   <si>
     <t xml:space="preserve">1.26926922798157</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">1.24022507667542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25109946727753</t>
+    <t xml:space="preserve">1.25109934806824</t>
   </si>
   <si>
     <t xml:space="preserve">1.26637864112854</t>
@@ -3227,19 +3227,19 @@
     <t xml:space="preserve">1.27615165710449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28730118274689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28248369693756</t>
+    <t xml:space="preserve">1.28730142116547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28248357772827</t>
   </si>
   <si>
     <t xml:space="preserve">1.31868541240692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33671772480011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32777035236359</t>
+    <t xml:space="preserve">1.33671760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32777059078217</t>
   </si>
   <si>
     <t xml:space="preserve">1.32515501976013</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">1.36700057983398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37002897262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3566769361496</t>
+    <t xml:space="preserve">1.37002873420715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35667669773102</t>
   </si>
   <si>
     <t xml:space="preserve">1.35516262054443</t>
@@ -3263,46 +3263,46 @@
     <t xml:space="preserve">1.35998034477234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34951913356781</t>
+    <t xml:space="preserve">1.34951901435852</t>
   </si>
   <si>
     <t xml:space="preserve">1.33231282234192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3346529006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35929214954376</t>
+    <t xml:space="preserve">1.33465278148651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35929191112518</t>
   </si>
   <si>
     <t xml:space="preserve">1.33726823329926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33823192119598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33189976215363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29473447799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31662082672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32309019565582</t>
+    <t xml:space="preserve">1.3382316827774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33189988136292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29473435878754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31662058830261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32309031486511</t>
   </si>
   <si>
     <t xml:space="preserve">1.32130086421967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31634557247162</t>
+    <t xml:space="preserve">1.31634533405304</t>
   </si>
   <si>
     <t xml:space="preserve">1.31125247478485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29693675041199</t>
+    <t xml:space="preserve">1.2969366312027</t>
   </si>
   <si>
     <t xml:space="preserve">1.35447442531586</t>
@@ -3311,13 +3311,13 @@
     <t xml:space="preserve">1.34552717208862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33713054656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33396446704865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31799709796906</t>
+    <t xml:space="preserve">1.33713066577911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33396470546722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31799721717834</t>
   </si>
   <si>
     <t xml:space="preserve">1.30904996395111</t>
@@ -3326,13 +3326,13 @@
     <t xml:space="preserve">1.31951129436493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31483125686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32584321498871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29679930210114</t>
+    <t xml:space="preserve">1.31483137607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32584345340729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29679906368256</t>
   </si>
   <si>
     <t xml:space="preserve">1.25481593608856</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">1.26610326766968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24407911300659</t>
+    <t xml:space="preserve">1.24407923221588</t>
   </si>
   <si>
     <t xml:space="preserve">1.26197373867035</t>
@@ -3350,34 +3350,34 @@
     <t xml:space="preserve">1.25398993492126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28771424293518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34291183948517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38234865665436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41848158836365</t>
+    <t xml:space="preserve">1.28771436214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34291172027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38234853744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41848170757294</t>
   </si>
   <si>
     <t xml:space="preserve">1.43844068050385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43637597560883</t>
+    <t xml:space="preserve">1.43637585639954</t>
   </si>
   <si>
     <t xml:space="preserve">1.43155825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43603181838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44257032871246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45736765861511</t>
+    <t xml:space="preserve">1.43603193759918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44257020950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4573677778244</t>
   </si>
   <si>
     <t xml:space="preserve">1.45392632484436</t>
@@ -3386,19 +3386,19 @@
     <t xml:space="preserve">1.45117342472076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44532322883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45358228683472</t>
+    <t xml:space="preserve">1.44532334804535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45358240604401</t>
   </si>
   <si>
     <t xml:space="preserve">1.48111212253571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4687237739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48661828041077</t>
+    <t xml:space="preserve">1.46872365474701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48661816120148</t>
   </si>
   <si>
     <t xml:space="preserve">1.48283290863037</t>
@@ -3407,31 +3407,31 @@
     <t xml:space="preserve">1.51621305942535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50864219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51036286354065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56198132038116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56507873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55991673469543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56955218315125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55888450145721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5788437128067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59329664707184</t>
+    <t xml:space="preserve">1.50864207744598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51036310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56198155879974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56507849693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55991661548615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56955254077911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55888438224792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57884359359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59329688549042</t>
   </si>
   <si>
     <t xml:space="preserve">1.61669731140137</t>
@@ -3440,157 +3440,157 @@
     <t xml:space="preserve">1.59260857105255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58194088935852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57540237903595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5798761844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57918775081635</t>
+    <t xml:space="preserve">1.58194077014923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57540249824524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57987606525421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57918787002563</t>
   </si>
   <si>
     <t xml:space="preserve">1.58125245571136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57333755493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59914708137512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5901997089386</t>
+    <t xml:space="preserve">1.57333791255951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59914696216583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59019958972931</t>
   </si>
   <si>
     <t xml:space="preserve">1.59536159038544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58503782749176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55750787258148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5509694814682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5557873249054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56989622116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52791333198547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53204274177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52860140800476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58056461811066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59501755237579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59742617607117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60637366771698</t>
+    <t xml:space="preserve">1.58503806591034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55750775337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55096971988678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55578720569611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56989645957947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52791321277618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5320428609848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52860164642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58056437969208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5950174331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59742641448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60637354850769</t>
   </si>
   <si>
     <t xml:space="preserve">1.58847916126251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62357985973358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6256445646286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64457130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63837730884552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63975381851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63287103176117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64319503307343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65868079662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65351855754852</t>
+    <t xml:space="preserve">1.623579621315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62564480304718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64457142353058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63837707042694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63975358009338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63287115097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64319515228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65868067741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65351867675781</t>
   </si>
   <si>
     <t xml:space="preserve">1.65116286277771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64976525306702</t>
+    <t xml:space="preserve">1.64976537227631</t>
   </si>
   <si>
     <t xml:space="preserve">1.63928401470184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67282450199127</t>
+    <t xml:space="preserve">1.67282438278198</t>
   </si>
   <si>
     <t xml:space="preserve">1.68330574035645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68854641914368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70881009101868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72767686843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73012220859528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73326683044434</t>
+    <t xml:space="preserve">1.6885461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70881032943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72767698764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73012244701385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73326694965363</t>
   </si>
   <si>
     <t xml:space="preserve">1.73676073551178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71894252300262</t>
+    <t xml:space="preserve">1.71894216537476</t>
   </si>
   <si>
     <t xml:space="preserve">1.71440052986145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7042680978775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69448602199554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71195483207703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71265375614166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68749809265137</t>
+    <t xml:space="preserve">1.70426857471466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69448566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71195471286774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71265351772308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68749833106995</t>
   </si>
   <si>
     <t xml:space="preserve">1.63788664340973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65360867977142</t>
+    <t xml:space="preserve">1.65360832214355</t>
   </si>
   <si>
     <t xml:space="preserve">1.63648903369904</t>
@@ -3602,61 +3602,61 @@
     <t xml:space="preserve">1.65186178684235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66688501834869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62775433063507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64662075042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64592206478119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63229656219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65535533428192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62146580219269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60958671569824</t>
+    <t xml:space="preserve">1.6668848991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62775456905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64662086963654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64592230319977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63229632377625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65535545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6214656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60958683490753</t>
   </si>
   <si>
     <t xml:space="preserve">1.56242084503174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59596085548401</t>
+    <t xml:space="preserve">1.5959609746933</t>
   </si>
   <si>
     <t xml:space="preserve">1.61098420619965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58617854118347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59631049633026</t>
+    <t xml:space="preserve">1.58617842197418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59631025791168</t>
   </si>
   <si>
     <t xml:space="preserve">1.57639598846436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55962586402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49359321594238</t>
+    <t xml:space="preserve">1.55962562561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4935929775238</t>
   </si>
   <si>
     <t xml:space="preserve">1.52259159088135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56277012825012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255280017853</t>
+    <t xml:space="preserve">1.56277024745941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255256175995</t>
   </si>
   <si>
     <t xml:space="preserve">1.59665989875793</t>
@@ -3665,157 +3665,157 @@
     <t xml:space="preserve">1.63334465026855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61657440662384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62111628055573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6399827003479</t>
+    <t xml:space="preserve">1.61657416820526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62111616134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63998281955719</t>
   </si>
   <si>
     <t xml:space="preserve">1.62915217876434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61727333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6256582736969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63509142398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63858544826508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67596888542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68016135692596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68260681629181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71125602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71055722236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69203996658325</t>
+    <t xml:space="preserve">1.61727321147919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62565815448761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63509130477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6385852098465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67596864700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68016123771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68260705471039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71125566959381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71055710315704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69204008579254</t>
   </si>
   <si>
     <t xml:space="preserve">1.66898131370544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.682257771492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66723430156708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66304194927216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67002928256989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66164410114288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67526996135712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68365490436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6682825088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67911326885223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66548728942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6483678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65710234642029</t>
+    <t xml:space="preserve">1.68225765228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66723418235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66304183006287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67002904415131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66164422035217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67527008056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68365478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66828262805939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67911338806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66548752784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64836764335632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65710246562958</t>
   </si>
   <si>
     <t xml:space="preserve">1.63963329792023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66758358478546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66094541549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65884923934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60853886604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62251365184784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65815043449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69623267650604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69413638114929</t>
+    <t xml:space="preserve">1.66758346557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66094529628754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65884935855865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60853862762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.622514128685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6581506729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69623255729675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69413626194</t>
   </si>
   <si>
     <t xml:space="preserve">1.72732722759247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69763016700745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71824371814728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74898898601532</t>
+    <t xml:space="preserve">1.69763028621674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7182434797287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74898886680603</t>
   </si>
   <si>
     <t xml:space="preserve">1.72942340373993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75388038158417</t>
+    <t xml:space="preserve">1.75388014316559</t>
   </si>
   <si>
     <t xml:space="preserve">1.75912082195282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74933838844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75562715530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74339878559113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76331329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79929959774017</t>
+    <t xml:space="preserve">1.74933803081512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75562739372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74339866638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76331317424774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79929947853088</t>
   </si>
   <si>
     <t xml:space="preserve">1.81100177764893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78156387805939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79319369792938</t>
+    <t xml:space="preserve">1.7815637588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79319357872009</t>
   </si>
   <si>
     <t xml:space="preserve">1.77720248699188</t>
@@ -3824,70 +3824,70 @@
     <t xml:space="preserve">1.78192698955536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79028642177582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80373322963715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78301739692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77211427688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78628838062286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81354606151581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82590317726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8186342716217</t>
+    <t xml:space="preserve">1.79028618335724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80373311042786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78301727771759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77211451530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78628814220428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81354582309723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82590293884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81863403320312</t>
   </si>
   <si>
     <t xml:space="preserve">1.78556156158447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80518686771393</t>
+    <t xml:space="preserve">1.80518698692322</t>
   </si>
   <si>
     <t xml:space="preserve">1.81172895431519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79573750495911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80046212673187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7964643239975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80991172790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80445992946625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8040965795517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73286306858063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74418127536774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72544288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72581744194031</t>
+    <t xml:space="preserve">1.79573786258698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80046224594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79682791233063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646444320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80991184711456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80446028709412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80409669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73286330699921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74418115615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72544264793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7258175611496</t>
   </si>
   <si>
     <t xml:space="preserve">1.71494925022125</t>
@@ -3899,22 +3899,22 @@
     <t xml:space="preserve">1.60626566410065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58565318584442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62537884712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60963881015778</t>
+    <t xml:space="preserve">1.58565330505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62537908554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60963869094849</t>
   </si>
   <si>
     <t xml:space="preserve">1.60888922214508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6587336063385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69246304035187</t>
+    <t xml:space="preserve">1.65873372554779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69246280193329</t>
   </si>
   <si>
     <t xml:space="preserve">1.6722252368927</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">1.66772794723511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66060745716095</t>
+    <t xml:space="preserve">1.66060757637024</t>
   </si>
   <si>
     <t xml:space="preserve">1.65273725986481</t>
@@ -3935,82 +3935,82 @@
     <t xml:space="preserve">1.65011382102966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68084502220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311217308044</t>
+    <t xml:space="preserve">1.68084514141083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311193466187</t>
   </si>
   <si>
     <t xml:space="preserve">1.63549792766571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67334997653961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67185056209564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68721616268158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69583594799042</t>
+    <t xml:space="preserve">1.67334961891174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67185068130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.687215924263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69583606719971</t>
   </si>
   <si>
     <t xml:space="preserve">1.71157622337341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70670425891876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70445549488068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75767314434052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79440069198608</t>
+    <t xml:space="preserve">1.70670413970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70445561408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75767290592194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7944004535675</t>
   </si>
   <si>
     <t xml:space="preserve">1.81238949298859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82363271713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83749902248383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84611904621124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86035990715027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90795588493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91919898986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92032337188721</t>
+    <t xml:space="preserve">1.82363259792328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83749890327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84611880779266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86036014556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90795612335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91919922828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92032313346863</t>
   </si>
   <si>
     <t xml:space="preserve">1.93194127082825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93006765842438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89933586120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91245305538177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91282784938812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8487423658371</t>
+    <t xml:space="preserve">1.9300674200058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89933609962463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91245317459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9128280878067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84874224662781</t>
   </si>
   <si>
     <t xml:space="preserve">1.86560690402985</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">1.9465571641922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96342217922211</t>
+    <t xml:space="preserve">1.96342194080353</t>
   </si>
   <si>
     <t xml:space="preserve">2.00127387046814</t>
@@ -4034,37 +4034,37 @@
     <t xml:space="preserve">2.02151131629944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04474687576294</t>
+    <t xml:space="preserve">2.04474711418152</t>
   </si>
   <si>
     <t xml:space="preserve">1.99902546405792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03500294685364</t>
+    <t xml:space="preserve">2.0350034236908</t>
   </si>
   <si>
     <t xml:space="preserve">2.07585310935974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1388144493103</t>
+    <t xml:space="preserve">2.13881421089172</t>
   </si>
   <si>
     <t xml:space="preserve">2.18865895271301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07435393333435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13843965530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09196829795837</t>
+    <t xml:space="preserve">2.07435417175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13843989372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09196805953979</t>
   </si>
   <si>
     <t xml:space="preserve">2.05299210548401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04024982452393</t>
+    <t xml:space="preserve">2.04024958610535</t>
   </si>
   <si>
     <t xml:space="preserve">2.00427198410034</t>
@@ -4073,22 +4073,22 @@
     <t xml:space="preserve">1.99377834796906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96417152881622</t>
+    <t xml:space="preserve">1.96417164802551</t>
   </si>
   <si>
     <t xml:space="preserve">1.80789232254028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8569872379303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71907186508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58640289306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60851407051086</t>
+    <t xml:space="preserve">1.85698711872101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7190717458725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58640277385712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60851442813873</t>
   </si>
   <si>
     <t xml:space="preserve">1.56204295158386</t>
@@ -4097,7 +4097,7 @@
     <t xml:space="preserve">1.42127907276154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38155353069305</t>
+    <t xml:space="preserve">1.38155341148376</t>
   </si>
   <si>
     <t xml:space="preserve">1.39834332466125</t>
@@ -4121,61 +4121,61 @@
     <t xml:space="preserve">1.61001348495483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55304849147797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56354188919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54892611503601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57403540611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53505945205688</t>
+    <t xml:space="preserve">1.55304837226868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56354200839996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54892599582672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57403528690338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53505957126617</t>
   </si>
   <si>
     <t xml:space="preserve">1.5223171710968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52381634712219</t>
+    <t xml:space="preserve">1.5238162279129</t>
   </si>
   <si>
     <t xml:space="preserve">1.53243625164032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61975741386414</t>
+    <t xml:space="preserve">1.61975765228271</t>
   </si>
   <si>
     <t xml:space="preserve">1.59951984882355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56166815757751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57778334617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57028794288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53056216239929</t>
+    <t xml:space="preserve">1.5616682767868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57778310775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57028770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53056228160858</t>
   </si>
   <si>
     <t xml:space="preserve">1.48573958873749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46280360221863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48558986186981</t>
+    <t xml:space="preserve">1.46280372142792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48558974266052</t>
   </si>
   <si>
     <t xml:space="preserve">1.48469030857086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4550085067749</t>
+    <t xml:space="preserve">1.45500838756561</t>
   </si>
   <si>
     <t xml:space="preserve">1.4572571516037</t>
@@ -4187,16 +4187,16 @@
     <t xml:space="preserve">1.47884380817413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51444709300995</t>
+    <t xml:space="preserve">1.51444697380066</t>
   </si>
   <si>
     <t xml:space="preserve">1.5178200006485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48618936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46055519580841</t>
+    <t xml:space="preserve">1.48618948459625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46055495738983</t>
   </si>
   <si>
     <t xml:space="preserve">1.43761909008026</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">1.4397177696228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44361543655396</t>
+    <t xml:space="preserve">1.44361531734467</t>
   </si>
   <si>
     <t xml:space="preserve">1.46520221233368</t>
@@ -4214,19 +4214,19 @@
     <t xml:space="preserve">1.44091701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46924960613251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44301581382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44256603717804</t>
+    <t xml:space="preserve">1.4692497253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44301569461823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44256591796875</t>
   </si>
   <si>
     <t xml:space="preserve">1.40913653373718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3716596364975</t>
+    <t xml:space="preserve">1.37165951728821</t>
   </si>
   <si>
     <t xml:space="preserve">1.39534509181976</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">1.47074890136719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47839403152466</t>
+    <t xml:space="preserve">1.47839415073395</t>
   </si>
   <si>
     <t xml:space="preserve">1.46490240097046</t>
@@ -4247,31 +4247,31 @@
     <t xml:space="preserve">1.49188590049744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49008691310883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48633944988251</t>
+    <t xml:space="preserve">1.49008703231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48633933067322</t>
   </si>
   <si>
     <t xml:space="preserve">1.54183995723724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54496216773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.586958527565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60139954090118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59788680076599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60764420032501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58500683307648</t>
+    <t xml:space="preserve">1.54496228694916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58695840835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60139966011047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59788691997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6076443195343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58500695228577</t>
   </si>
   <si>
     <t xml:space="preserve">1.56119883060455</t>
@@ -4283,7 +4283,7 @@
     <t xml:space="preserve">1.59047102928162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56315040588379</t>
+    <t xml:space="preserve">1.5631502866745</t>
   </si>
   <si>
     <t xml:space="preserve">1.55339276790619</t>
@@ -4295,55 +4295,55 @@
     <t xml:space="preserve">1.42193984985352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37307417392731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38166081905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44520151615143</t>
+    <t xml:space="preserve">1.3730742931366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38166093826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44520175457001</t>
   </si>
   <si>
     <t xml:space="preserve">1.39961457252502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40788888931274</t>
+    <t xml:space="preserve">1.40788900852203</t>
   </si>
   <si>
     <t xml:space="preserve">1.46175038814545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47221028804779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46799528598785</t>
+    <t xml:space="preserve">1.47221040725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46799516677856</t>
   </si>
   <si>
     <t xml:space="preserve">1.43630290031433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46924412250519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47798669338226</t>
+    <t xml:space="preserve">1.46924424171448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47798681259155</t>
   </si>
   <si>
     <t xml:space="preserve">1.48204600811005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46440446376801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38946688175201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37978744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3466899394989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30469369888306</t>
+    <t xml:space="preserve">1.46440434455872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38946676254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37978732585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34669017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30469357967377</t>
   </si>
   <si>
     <t xml:space="preserve">1.31000185012817</t>
@@ -4352,13 +4352,13 @@
     <t xml:space="preserve">1.36230206489563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37588453292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35199797153473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33295142650604</t>
+    <t xml:space="preserve">1.37588441371918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35199809074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33295154571533</t>
   </si>
   <si>
     <t xml:space="preserve">1.32764339447021</t>
@@ -4367,37 +4367,37 @@
     <t xml:space="preserve">1.25411081314087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27393805980682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30672335624695</t>
+    <t xml:space="preserve">1.27393817901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30672347545624</t>
   </si>
   <si>
     <t xml:space="preserve">1.38369047641754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33513712882996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2981368303299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29579496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31765162944794</t>
+    <t xml:space="preserve">1.33513724803925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29813671112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29579484462738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31765174865723</t>
   </si>
   <si>
     <t xml:space="preserve">1.29329705238342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30922114849091</t>
+    <t xml:space="preserve">1.3092212677002</t>
   </si>
   <si>
     <t xml:space="preserve">1.3315464258194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34934401512146</t>
+    <t xml:space="preserve">1.34934413433075</t>
   </si>
   <si>
     <t xml:space="preserve">1.36542439460754</t>
@@ -4406,16 +4406,16 @@
     <t xml:space="preserve">1.36370706558228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38462698459625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39180862903595</t>
+    <t xml:space="preserve">1.38462722301483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39180874824524</t>
   </si>
   <si>
     <t xml:space="preserve">1.41600728034973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41850519180298</t>
+    <t xml:space="preserve">1.41850507259369</t>
   </si>
   <si>
     <t xml:space="preserve">1.4175683259964</t>
@@ -4424,25 +4424,25 @@
     <t xml:space="preserve">1.43052637577057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4470751285553</t>
+    <t xml:space="preserve">1.44707524776459</t>
   </si>
   <si>
     <t xml:space="preserve">1.44785559177399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42740392684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42615497112274</t>
+    <t xml:space="preserve">1.42740404605865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42615509033203</t>
   </si>
   <si>
     <t xml:space="preserve">1.38415884971619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34138190746307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36573672294617</t>
+    <t xml:space="preserve">1.34138178825378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36573660373688</t>
   </si>
   <si>
     <t xml:space="preserve">1.37666499614716</t>
@@ -4460,13 +4460,13 @@
     <t xml:space="preserve">1.34996855258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34497272968292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32217931747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3568377494812</t>
+    <t xml:space="preserve">1.34497261047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32217907905579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35683786869049</t>
   </si>
   <si>
     <t xml:space="preserve">1.32467710971832</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">1.32998514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32701885700226</t>
+    <t xml:space="preserve">1.32701897621155</t>
   </si>
   <si>
     <t xml:space="preserve">1.35855519771576</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">1.43099462985992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48001623153687</t>
+    <t xml:space="preserve">1.48001635074615</t>
   </si>
   <si>
     <t xml:space="preserve">1.46846342086792</t>
@@ -4499,16 +4499,16 @@
     <t xml:space="preserve">1.49484777450562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49516010284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44348418712616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43364870548248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44567000865936</t>
+    <t xml:space="preserve">1.49516022205353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44348430633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43364882469177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44566988945007</t>
   </si>
   <si>
     <t xml:space="preserve">1.37697732448578</t>
@@ -4523,22 +4523,22 @@
     <t xml:space="preserve">1.32592606544495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29189205169678</t>
+    <t xml:space="preserve">1.2918918132782</t>
   </si>
   <si>
     <t xml:space="preserve">1.32920467853546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35355913639069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39571166038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35917949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33654224872589</t>
+    <t xml:space="preserve">1.35355925559998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39571177959442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35917961597443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33654236793518</t>
   </si>
   <si>
     <t xml:space="preserve">1.33139026165009</t>
@@ -4550,13 +4550,13 @@
     <t xml:space="preserve">1.30781614780426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33201491832733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3366984128952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36058461666107</t>
+    <t xml:space="preserve">1.33201479911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33669817447662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36058473587036</t>
   </si>
   <si>
     <t xml:space="preserve">1.40726459026337</t>
@@ -4568,16 +4568,16 @@
     <t xml:space="preserve">1.42771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42662346363068</t>
+    <t xml:space="preserve">1.42662334442139</t>
   </si>
   <si>
     <t xml:space="preserve">1.44863629341125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45550560951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45644235610962</t>
+    <t xml:space="preserve">1.45550549030304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45644223690033</t>
   </si>
   <si>
     <t xml:space="preserve">1.48766624927521</t>
@@ -4586,22 +4586,22 @@
     <t xml:space="preserve">1.48719787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5057760477066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51842188835144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51810967922211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53746855258942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61193776130676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6618959903717</t>
+    <t xml:space="preserve">1.50577628612518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51842176914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51810944080353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53746843338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61193764209747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66189587116241</t>
   </si>
   <si>
     <t xml:space="preserve">1.67672741413116</t>
@@ -4613,7 +4613,7 @@
     <t xml:space="preserve">1.69936490058899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68648493289948</t>
+    <t xml:space="preserve">1.68648481369019</t>
   </si>
   <si>
     <t xml:space="preserve">1.70678055286407</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">1.70951271057129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70990300178528</t>
+    <t xml:space="preserve">1.70990288257599</t>
   </si>
   <si>
     <t xml:space="preserve">1.70014536380768</t>
@@ -4634,31 +4634,31 @@
     <t xml:space="preserve">1.72882580757141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74457180500031</t>
+    <t xml:space="preserve">1.74457168579102</t>
   </si>
   <si>
     <t xml:space="preserve">1.73165190219879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74416792392731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74295675754547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7086386680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72357726097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71348357200623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68320298194885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69289267063141</t>
+    <t xml:space="preserve">1.7441680431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74295687675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70863842964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72357714176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71348345279694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68320286273956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69289255142212</t>
   </si>
   <si>
     <t xml:space="preserve">1.67835795879364</t>
@@ -4667,16 +4667,16 @@
     <t xml:space="preserve">1.66866815090179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.664630651474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66140067577362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6690719127655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67028307914734</t>
+    <t xml:space="preserve">1.66463077068329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66140079498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66907179355621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67028319835663</t>
   </si>
   <si>
     <t xml:space="preserve">1.6965264081955</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">1.68562543392181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6104484796524</t>
+    <t xml:space="preserve">1.61044859886169</t>
   </si>
   <si>
     <t xml:space="preserve">1.66180455684662</t>
@@ -4694,7 +4694,7 @@
     <t xml:space="preserve">1.64282846450806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67593550682068</t>
+    <t xml:space="preserve">1.67593562602997</t>
   </si>
   <si>
     <t xml:space="preserve">1.69612264633179</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">1.71429097652435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75426149368286</t>
+    <t xml:space="preserve">1.75426137447357</t>
   </si>
   <si>
     <t xml:space="preserve">1.79948055744171</t>
@@ -4730,10 +4730,10 @@
     <t xml:space="preserve">1.78857946395874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80351805686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81684160232544</t>
+    <t xml:space="preserve">1.8035181760788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81684172153473</t>
   </si>
   <si>
     <t xml:space="preserve">1.82451272010803</t>
@@ -4742,22 +4742,22 @@
     <t xml:space="preserve">1.84429609775543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84752631187439</t>
+    <t xml:space="preserve">1.8475261926651</t>
   </si>
   <si>
     <t xml:space="preserve">1.84510385990143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82572400569916</t>
+    <t xml:space="preserve">1.82572388648987</t>
   </si>
   <si>
     <t xml:space="preserve">1.79503953456879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76072144508362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80836308002472</t>
+    <t xml:space="preserve">1.76072132587433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80836319923401</t>
   </si>
   <si>
     <t xml:space="preserve">1.84550726413727</t>
@@ -4769,25 +4769,25 @@
     <t xml:space="preserve">1.89153397083282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89839768409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89274537563324</t>
+    <t xml:space="preserve">1.898397564888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89274549484253</t>
   </si>
   <si>
     <t xml:space="preserve">1.94603931903839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98076117038727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98237597942352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423713207245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97591626644135</t>
+    <t xml:space="preserve">1.98076105117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98237609863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423701286316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97591614723206</t>
   </si>
   <si>
     <t xml:space="preserve">1.99327719211578</t>
@@ -4802,7 +4802,7 @@
     <t xml:space="preserve">2.00014090538025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01790571212769</t>
+    <t xml:space="preserve">2.01790547370911</t>
   </si>
   <si>
     <t xml:space="preserve">2.02073168754578</t>
@@ -4814,19 +4814,19 @@
     <t xml:space="preserve">2.05989480018616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07079577445984</t>
+    <t xml:space="preserve">2.07079601287842</t>
   </si>
   <si>
     <t xml:space="preserve">2.06231713294983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06150960922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99973714351654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0300178527832</t>
+    <t xml:space="preserve">2.06150984764099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99973690509796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03001761436462</t>
   </si>
   <si>
     <t xml:space="preserve">2.04535984992981</t>
@@ -4838,16 +4838,16 @@
     <t xml:space="preserve">2.04858994483948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05262732505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09340524673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07119941711426</t>
+    <t xml:space="preserve">2.05262756347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07887053489685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0934054851532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07119965553284</t>
   </si>
   <si>
     <t xml:space="preserve">2.0772557258606</t>
@@ -4856,16 +4856,16 @@
     <t xml:space="preserve">2.04414892196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00417804718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88184416294098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94482815265656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81159293651581</t>
+    <t xml:space="preserve">2.00417828559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88184404373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94482779502869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8115930557251</t>
   </si>
   <si>
     <t xml:space="preserve">1.81522655487061</t>
@@ -4874,31 +4874,31 @@
     <t xml:space="preserve">1.77081501483917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83702886104584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90162765979767</t>
+    <t xml:space="preserve">1.83702874183655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90162754058838</t>
   </si>
   <si>
     <t xml:space="preserve">1.89193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87255823612213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82733905315399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83420252799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85196733474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87982583045959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90970253944397</t>
+    <t xml:space="preserve">1.87255799770355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82733881473541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83420264720917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8519674539566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87982559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90970242023468</t>
   </si>
   <si>
     <t xml:space="preserve">1.91172111034393</t>
@@ -4907,100 +4907,100 @@
     <t xml:space="preserve">1.86448335647583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90405011177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91939258575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.934330701828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92827451229095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97147500514984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00094819068909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01750206947327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01023459434509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00619673728943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02436542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98722088336945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96541893482208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98479866981506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92544841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88022923469543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91293227672577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8939563035965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96380412578583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883616924286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98358738422394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95048022270203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9391758441925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96057426929474</t>
+    <t xml:space="preserve">1.90404999256134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91939210891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93433058261871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92827463150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97147512435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00094842910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01750183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01023435592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00619697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02436518669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98722100257874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9654186964035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98479843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92544853687286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88022899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91293263435364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89395666122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96380388736725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883605003357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98358714580536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9504805803299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93917572498322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96057415008545</t>
   </si>
   <si>
     <t xml:space="preserve">1.9545179605484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94038689136505</t>
+    <t xml:space="preserve">1.94038701057434</t>
   </si>
   <si>
     <t xml:space="preserve">1.92948591709137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95128786563873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96353375911713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96437251567841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88888430595398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8880455493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88301312923431</t>
+    <t xml:space="preserve">1.95128798484802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96353387832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96437239646912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88888442516327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88804543018341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88301277160645</t>
   </si>
   <si>
     <t xml:space="preserve">1.86665725708008</t>
@@ -5009,13 +5009,13 @@
     <t xml:space="preserve">1.85365641117096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80794405937195</t>
+    <t xml:space="preserve">1.80794417858124</t>
   </si>
   <si>
     <t xml:space="preserve">1.87043154239655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90524005889893</t>
+    <t xml:space="preserve">1.90524017810822</t>
   </si>
   <si>
     <t xml:space="preserve">1.89475572109222</t>
@@ -5024,58 +5024,58 @@
     <t xml:space="preserve">1.91698265075684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93166077136993</t>
+    <t xml:space="preserve">1.9316611289978</t>
   </si>
   <si>
     <t xml:space="preserve">1.94927477836609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93711304664612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93417716026306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93920969963074</t>
+    <t xml:space="preserve">1.93711280822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93417739868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93920993804932</t>
   </si>
   <si>
     <t xml:space="preserve">1.97108244895935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97779285907745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99037396907806</t>
+    <t xml:space="preserve">1.97779262065887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99037408828735</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840735435486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00169730186462</t>
+    <t xml:space="preserve">2.0016975402832</t>
   </si>
   <si>
     <t xml:space="preserve">2.01805305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99540650844574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95850145816803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95598518848419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98072850704193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9824059009552</t>
+    <t xml:space="preserve">1.99540662765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95850133895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95598483085632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98072838783264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98240578174591</t>
   </si>
   <si>
     <t xml:space="preserve">2.00127792358398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01302051544189</t>
+    <t xml:space="preserve">2.01302075386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.04405474662781</t>
@@ -5087,16 +5087,16 @@
     <t xml:space="preserve">2.02056932449341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96311450004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97024369239807</t>
+    <t xml:space="preserve">1.96311438083649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97024381160736</t>
   </si>
   <si>
     <t xml:space="preserve">1.97695410251617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99666500091553</t>
+    <t xml:space="preserve">1.99666464328766</t>
   </si>
   <si>
     <t xml:space="preserve">2.01973056793213</t>
@@ -5105,28 +5105,28 @@
     <t xml:space="preserve">2.04992604255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03860282897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04237699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837868690491</t>
+    <t xml:space="preserve">2.03860259056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04237723350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837892532349</t>
   </si>
   <si>
     <t xml:space="preserve">2.09018659591675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11534929275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12289762496948</t>
+    <t xml:space="preserve">2.11534905433655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12289786338806</t>
   </si>
   <si>
     <t xml:space="preserve">2.12709164619446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1296079158783</t>
+    <t xml:space="preserve">2.12960815429688</t>
   </si>
   <si>
     <t xml:space="preserve">2.15812587738037</t>
@@ -5135,31 +5135,31 @@
     <t xml:space="preserve">2.18874025344849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20509600639343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18832111358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.149738073349</t>
+    <t xml:space="preserve">2.20509648323059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18832087516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14973831176758</t>
   </si>
   <si>
     <t xml:space="preserve">2.13506007194519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13338255882263</t>
+    <t xml:space="preserve">2.13338232040405</t>
   </si>
   <si>
     <t xml:space="preserve">2.14722180366516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96101784706116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00673007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04489350318909</t>
+    <t xml:space="preserve">1.96101760864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0067298412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04489326477051</t>
   </si>
   <si>
     <t xml:space="preserve">2.04615163803101</t>
@@ -5168,7 +5168,7 @@
     <t xml:space="preserve">2.05076456069946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03734445571899</t>
+    <t xml:space="preserve">2.03734421730042</t>
   </si>
   <si>
     <t xml:space="preserve">2.02937650680542</t>
@@ -5177,61 +5177,61 @@
     <t xml:space="preserve">2.02224707603455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04573178291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06292676925659</t>
+    <t xml:space="preserve">2.04573202133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06292700767517</t>
   </si>
   <si>
     <t xml:space="preserve">2.05915212631226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05328106880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0545392036438</t>
+    <t xml:space="preserve">2.0532808303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453896522522</t>
   </si>
   <si>
     <t xml:space="preserve">2.07760500907898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09060597419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09857416152954</t>
+    <t xml:space="preserve">2.09060573577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09857392311096</t>
   </si>
   <si>
     <t xml:space="preserve">2.073410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0587329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05202293395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0058913230896</t>
+    <t xml:space="preserve">2.05873274803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05202269554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00589108467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.00043916702271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02434372901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08012104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07634687423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06544327735901</t>
+    <t xml:space="preserve">2.02434396743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08012127876282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07634711265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06544303894043</t>
   </si>
   <si>
     <t xml:space="preserve">2.07592749595642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07089495658875</t>
+    <t xml:space="preserve">2.07089519500732</t>
   </si>
   <si>
     <t xml:space="preserve">2.03818345069885</t>
@@ -5240,25 +5240,25 @@
     <t xml:space="preserve">2.04782891273499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10821938514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09102511405945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06418466567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03482866287231</t>
+    <t xml:space="preserve">2.10821962356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09102535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06418490409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03482842445374</t>
   </si>
   <si>
     <t xml:space="preserve">2.0323121547699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04657077789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98156714439392</t>
+    <t xml:space="preserve">2.04657101631165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9815673828125</t>
   </si>
   <si>
     <t xml:space="preserve">1.98282539844513</t>
@@ -5267,25 +5267,25 @@
     <t xml:space="preserve">2.01427888870239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99330961704254</t>
+    <t xml:space="preserve">1.99330973625183</t>
   </si>
   <si>
     <t xml:space="preserve">2.03398966789246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04908728599548</t>
+    <t xml:space="preserve">2.04908752441406</t>
   </si>
   <si>
     <t xml:space="preserve">2.05286145210266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.026859998703</t>
+    <t xml:space="preserve">2.02686023712158</t>
   </si>
   <si>
     <t xml:space="preserve">2.03650593757629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9920517206192</t>
+    <t xml:space="preserve">1.99205148220062</t>
   </si>
   <si>
     <t xml:space="preserve">1.96605014801025</t>
@@ -5294,7 +5294,7 @@
     <t xml:space="preserve">1.99079346656799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97611522674561</t>
+    <t xml:space="preserve">1.97611498832703</t>
   </si>
   <si>
     <t xml:space="preserve">1.98785769939423</t>
@@ -5306,10 +5306,10 @@
     <t xml:space="preserve">2.06041049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08934760093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11702680587769</t>
+    <t xml:space="preserve">2.08934736251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11702656745911</t>
   </si>
   <si>
     <t xml:space="preserve">2.15015745162964</t>
@@ -5327,19 +5327,19 @@
     <t xml:space="preserve">2.16231966018677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18286895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20551586151123</t>
+    <t xml:space="preserve">2.18286919593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20551538467407</t>
   </si>
   <si>
     <t xml:space="preserve">2.21893572807312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2197744846344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25164723396301</t>
+    <t xml:space="preserve">2.21977472305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25164747238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.27114582061768</t>
@@ -5348,7 +5348,7 @@
     <t xml:space="preserve">2.23835301399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25209021568298</t>
+    <t xml:space="preserve">2.25209045410156</t>
   </si>
   <si>
     <t xml:space="preserve">2.26848697662354</t>
@@ -5357,19 +5357,19 @@
     <t xml:space="preserve">2.3039391040802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30438208580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32609677314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34559559822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34116387367249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36287808418274</t>
+    <t xml:space="preserve">2.30438232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.326096534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34559535980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34116363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36287784576416</t>
   </si>
   <si>
     <t xml:space="preserve">2.38858079910278</t>
@@ -5381,16 +5381,16 @@
     <t xml:space="preserve">2.39788699150085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37307071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39301252365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38503575325012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37705898284912</t>
+    <t xml:space="preserve">2.37307047843933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39301228523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38503551483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37705874443054</t>
   </si>
   <si>
     <t xml:space="preserve">2.37572956085205</t>
@@ -5402,28 +5402,28 @@
     <t xml:space="preserve">2.33540272712708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32653999328613</t>
+    <t xml:space="preserve">2.32653951644897</t>
   </si>
   <si>
     <t xml:space="preserve">2.35046982765198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33717560768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33097124099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34603834152222</t>
+    <t xml:space="preserve">2.3371753692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33097147941589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3460385799408</t>
   </si>
   <si>
     <t xml:space="preserve">2.35445833206177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34205007553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34293627738953</t>
+    <t xml:space="preserve">2.34204983711243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34293651580811</t>
   </si>
   <si>
     <t xml:space="preserve">2.38813757896423</t>
@@ -5432,7 +5432,7 @@
     <t xml:space="preserve">2.38592195510864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44131565093994</t>
+    <t xml:space="preserve">2.44131588935852</t>
   </si>
   <si>
     <t xml:space="preserve">2.47056365013123</t>
@@ -5441,13 +5441,13 @@
     <t xml:space="preserve">2.47765421867371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44353151321411</t>
+    <t xml:space="preserve">2.44353127479553</t>
   </si>
   <si>
     <t xml:space="preserve">2.43599796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41694235801697</t>
+    <t xml:space="preserve">2.41694259643555</t>
   </si>
   <si>
     <t xml:space="preserve">2.41339731216431</t>
@@ -5462,7 +5462,7 @@
     <t xml:space="preserve">2.43732738494873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44220209121704</t>
+    <t xml:space="preserve">2.44220185279846</t>
   </si>
   <si>
     <t xml:space="preserve">2.45328068733215</t>
@@ -5477,7 +5477,7 @@
     <t xml:space="preserve">2.48873281478882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49139165878296</t>
+    <t xml:space="preserve">2.49139189720154</t>
   </si>
   <si>
     <t xml:space="preserve">2.46568894386292</t>
@@ -5510,22 +5510,22 @@
     <t xml:space="preserve">2.46879100799561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50247049331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48696041107178</t>
+    <t xml:space="preserve">2.50247025489807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4869601726532</t>
   </si>
   <si>
     <t xml:space="preserve">2.49538016319275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50690197944641</t>
+    <t xml:space="preserve">2.50690221786499</t>
   </si>
   <si>
     <t xml:space="preserve">2.50379991531372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5162079334259</t>
+    <t xml:space="preserve">2.51620817184448</t>
   </si>
   <si>
     <t xml:space="preserve">2.52551436424255</t>
@@ -5537,7 +5537,7 @@
     <t xml:space="preserve">2.5671706199646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6048378944397</t>
+    <t xml:space="preserve">2.60483813285828</t>
   </si>
   <si>
     <t xml:space="preserve">2.61857581138611</t>
@@ -5546,7 +5546,7 @@
     <t xml:space="preserve">2.61680340766907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6145875453949</t>
+    <t xml:space="preserve">2.61458778381348</t>
   </si>
   <si>
     <t xml:space="preserve">2.60395193099976</t>
@@ -5555,7 +5555,7 @@
     <t xml:space="preserve">2.66289091110229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65890264511108</t>
+    <t xml:space="preserve">2.6589024066925</t>
   </si>
   <si>
     <t xml:space="preserve">2.71252369880676</t>
@@ -5564,7 +5564,7 @@
     <t xml:space="preserve">2.75019145011902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73601078987122</t>
+    <t xml:space="preserve">2.73601055145264</t>
   </si>
   <si>
     <t xml:space="preserve">2.74974846839905</t>
@@ -5573,7 +5573,7 @@
     <t xml:space="preserve">2.72183012962341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78475713729858</t>
+    <t xml:space="preserve">2.78475737571716</t>
   </si>
   <si>
     <t xml:space="preserve">2.82109570503235</t>
@@ -5582,10 +5582,10 @@
     <t xml:space="preserve">2.81046009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86053586006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86186575889587</t>
+    <t xml:space="preserve">2.86053609848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86186552047729</t>
   </si>
   <si>
     <t xml:space="preserve">2.90352177619934</t>
@@ -5594,40 +5594,40 @@
     <t xml:space="preserve">2.899090051651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91858887672424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92036128044128</t>
+    <t xml:space="preserve">2.91858863830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92036151885986</t>
   </si>
   <si>
     <t xml:space="preserve">2.94384837150574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96511936187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96733522415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98062968254089</t>
+    <t xml:space="preserve">2.96511960029602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96733546257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98062992095947</t>
   </si>
   <si>
     <t xml:space="preserve">2.96689224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01608204841614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00012850761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95049571990967</t>
+    <t xml:space="preserve">3.01608180999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00012826919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95049548149109</t>
   </si>
   <si>
     <t xml:space="preserve">2.97442579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93498563766479</t>
+    <t xml:space="preserve">2.93498539924622</t>
   </si>
   <si>
     <t xml:space="preserve">2.96910786628723</t>
@@ -5639,7 +5639,7 @@
     <t xml:space="preserve">2.91592979431152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94827961921692</t>
+    <t xml:space="preserve">2.94828009605408</t>
   </si>
   <si>
     <t xml:space="preserve">2.88225054740906</t>
@@ -5648,13 +5648,13 @@
     <t xml:space="preserve">2.92390656471252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96866464614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303793907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03868269920349</t>
+    <t xml:space="preserve">2.96866488456726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03868246078491</t>
   </si>
   <si>
     <t xml:space="preserve">3.11933588981628</t>
@@ -5681,16 +5681,16 @@
     <t xml:space="preserve">3.06837344169617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15788984298706</t>
+    <t xml:space="preserve">3.15789008140564</t>
   </si>
   <si>
     <t xml:space="preserve">3.18935370445251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18492197990417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17251372337341</t>
+    <t xml:space="preserve">3.18492221832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17251420021057</t>
   </si>
   <si>
     <t xml:space="preserve">3.19112634658813</t>
@@ -5699,13 +5699,13 @@
     <t xml:space="preserve">3.21417021751404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28197193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30324339866638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30856108665466</t>
+    <t xml:space="preserve">3.2819721698761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3032431602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30856132507324</t>
   </si>
   <si>
     <t xml:space="preserve">3.34046792984009</t>
@@ -5738,13 +5738,13 @@
     <t xml:space="preserve">3.33677363395691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33030891418457</t>
+    <t xml:space="preserve">3.33030867576599</t>
   </si>
   <si>
     <t xml:space="preserve">3.36170959472656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27628135681152</t>
+    <t xml:space="preserve">3.27628111839294</t>
   </si>
   <si>
     <t xml:space="preserve">3.2721254825592</t>
@@ -5753,7 +5753,7 @@
     <t xml:space="preserve">3.32569122314453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3127613067627</t>
+    <t xml:space="preserve">3.31276154518127</t>
   </si>
   <si>
     <t xml:space="preserve">3.29521417617798</t>
@@ -5762,7 +5762,7 @@
     <t xml:space="preserve">3.21070957183838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26058101654053</t>
+    <t xml:space="preserve">3.26058125495911</t>
   </si>
   <si>
     <t xml:space="preserve">3.15391159057617</t>
@@ -5777,7 +5777,7 @@
     <t xml:space="preserve">3.15760564804077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19547128677368</t>
+    <t xml:space="preserve">3.1954710483551</t>
   </si>
   <si>
     <t xml:space="preserve">3.22640991210938</t>
@@ -5786,10 +5786,10 @@
     <t xml:space="preserve">3.18900632858276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24765157699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25688672065735</t>
+    <t xml:space="preserve">3.24765133857727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25688695907593</t>
   </si>
   <si>
     <t xml:space="preserve">3.199627161026</t>
@@ -5804,13 +5804,13 @@
     <t xml:space="preserve">3.26011943817139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30583477020264</t>
+    <t xml:space="preserve">3.30583500862122</t>
   </si>
   <si>
     <t xml:space="preserve">3.27812838554382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29336714744568</t>
+    <t xml:space="preserve">3.2933669090271</t>
   </si>
   <si>
     <t xml:space="preserve">3.28136086463928</t>
@@ -5822,7 +5822,7 @@
     <t xml:space="preserve">3.31645584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34277653694153</t>
+    <t xml:space="preserve">3.34277677536011</t>
   </si>
   <si>
     <t xml:space="preserve">3.33215594291687</t>
@@ -5831,7 +5831,7 @@
     <t xml:space="preserve">3.34600901603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36909794807434</t>
+    <t xml:space="preserve">3.36909770965576</t>
   </si>
   <si>
     <t xml:space="preserve">3.38710713386536</t>
@@ -5864,7 +5864,7 @@
     <t xml:space="preserve">3.32800006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18115592002869</t>
+    <t xml:space="preserve">3.18115615844727</t>
   </si>
   <si>
     <t xml:space="preserve">3.15021729469299</t>
@@ -5885,16 +5885,16 @@
     <t xml:space="preserve">3.2051682472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22225379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32199692726135</t>
+    <t xml:space="preserve">3.22225403785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32199668884277</t>
   </si>
   <si>
     <t xml:space="preserve">3.33769726753235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31968808174133</t>
+    <t xml:space="preserve">3.31968832015991</t>
   </si>
   <si>
     <t xml:space="preserve">3.33954429626465</t>
@@ -5912,13 +5912,13 @@
     <t xml:space="preserve">3.41712236404419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41850733757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44344329833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47669076919556</t>
+    <t xml:space="preserve">3.41850757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44344305992126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47669100761414</t>
   </si>
   <si>
     <t xml:space="preserve">3.48500299453735</t>
@@ -5930,7 +5930,7 @@
     <t xml:space="preserve">3.43005180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46422290802002</t>
+    <t xml:space="preserve">3.4642231464386</t>
   </si>
   <si>
     <t xml:space="preserve">3.38618350028992</t>
@@ -5942,7 +5942,7 @@
     <t xml:space="preserve">3.40696310997009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41296601295471</t>
+    <t xml:space="preserve">3.41296625137329</t>
   </si>
   <si>
     <t xml:space="preserve">3.4485228061676</t>
@@ -5951,7 +5951,7 @@
     <t xml:space="preserve">3.46791744232178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45314049720764</t>
+    <t xml:space="preserve">3.45314073562622</t>
   </si>
   <si>
     <t xml:space="preserve">3.47715282440186</t>
@@ -5966,7 +5966,7 @@
     <t xml:space="preserve">3.53256559371948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46607041358948</t>
+    <t xml:space="preserve">3.4660701751709</t>
   </si>
   <si>
     <t xml:space="preserve">3.48869705200195</t>
@@ -5975,7 +5975,7 @@
     <t xml:space="preserve">3.57966637611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57458686828613</t>
+    <t xml:space="preserve">3.57458710670471</t>
   </si>
   <si>
     <t xml:space="preserve">3.54411005973816</t>
@@ -5999,7 +5999,7 @@
     <t xml:space="preserve">3.49654722213745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51686525344849</t>
+    <t xml:space="preserve">3.51686549186707</t>
   </si>
   <si>
     <t xml:space="preserve">3.55565404891968</t>
@@ -6014,10 +6014,10 @@
     <t xml:space="preserve">3.62999987602234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62030243873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66694140434265</t>
+    <t xml:space="preserve">3.62030267715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66694164276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.69418621063232</t>
@@ -6029,7 +6029,7 @@
     <t xml:space="preserve">3.63046145439148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58705496788025</t>
+    <t xml:space="preserve">3.58705472946167</t>
   </si>
   <si>
     <t xml:space="preserve">3.58289885520935</t>
@@ -6047,16 +6047,16 @@
     <t xml:space="preserve">3.63600277900696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7251250743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75744915008545</t>
+    <t xml:space="preserve">3.72512531280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75744938850403</t>
   </si>
   <si>
     <t xml:space="preserve">3.78654074668884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66832685470581</t>
+    <t xml:space="preserve">3.66832661628723</t>
   </si>
   <si>
     <t xml:space="preserve">3.5602719783783</t>
@@ -6065,10 +6065,10 @@
     <t xml:space="preserve">3.54226279258728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60090804100037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51270937919617</t>
+    <t xml:space="preserve">3.60090780258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51270914077759</t>
   </si>
   <si>
     <t xml:space="preserve">3.53071856498718</t>
@@ -6738,6 +6738,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.47100019454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38399982452393</t>
   </si>
 </sst>
 </file>
@@ -71764,7 +71767,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6503125</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>58968702</v>
@@ -71785,6 +71788,32 @@
         <v>2241</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6513078704</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>44190749</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>5.50299978256226</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>5.38399982452393</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>5.48999977111816</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>5.38399982452393</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>2242</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISP.MI.xlsx
+++ b/data/ISP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="2243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="2244">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53063881397247</t>
+    <t xml:space="preserve">1.53063893318176</t>
   </si>
   <si>
     <t xml:space="preserve">ISP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56040978431702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5183197259903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49265551567078</t>
+    <t xml:space="preserve">1.5604100227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51832008361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4926552772522</t>
   </si>
   <si>
     <t xml:space="preserve">1.48752224445343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46699059009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49676156044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52447938919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48546934127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43824625015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36638522148132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38075745105743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30479025840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36843836307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39307653903961</t>
+    <t xml:space="preserve">1.46699070930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49676144123077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52447962760925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48546898365021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43824636936188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3663854598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38075768947601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30479001998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36843848228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39307641983032</t>
   </si>
   <si>
     <t xml:space="preserve">1.35406637191772</t>
@@ -95,22 +95,22 @@
     <t xml:space="preserve">1.35919916629791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2904177904129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380042552948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31505584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26988613605499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20315825939178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27296602725983</t>
+    <t xml:space="preserve">1.29041814804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3438001871109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31505620479584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2698860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2031581401825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27296566963196</t>
   </si>
   <si>
     <t xml:space="preserve">1.22368979454041</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">1.17441380023956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10152626037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26064717769623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2298492193222</t>
+    <t xml:space="preserve">1.1015260219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26064693927765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22984933853149</t>
   </si>
   <si>
     <t xml:space="preserve">1.25243425369263</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">1.28220522403717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21958327293396</t>
+    <t xml:space="preserve">1.21958339214325</t>
   </si>
   <si>
     <t xml:space="preserve">1.19494557380676</t>
@@ -149,118 +149,118 @@
     <t xml:space="preserve">1.16004157066345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18057322502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20007848739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20213174819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22471654415131</t>
+    <t xml:space="preserve">1.18057346343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20007860660553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20213162899017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22471642494202</t>
   </si>
   <si>
     <t xml:space="preserve">1.27091264724731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32224214076996</t>
+    <t xml:space="preserve">1.32224202156067</t>
   </si>
   <si>
     <t xml:space="preserve">1.29555082321167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26475346088409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27604591846466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144442081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30581653118134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40334224700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37459790706635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36022567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33045470714569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29349756240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27912545204163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29247093200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2575671672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23600912094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24935436248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24114191532135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21753013134003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18673300743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13540351390839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14874911308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11076545715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1774936914444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19802534580231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24422168731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25038123130798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25654053688049</t>
+    <t xml:space="preserve">1.2647533416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27604568004608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2914445400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3058168888092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40334236621857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37459766864777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36022591590881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33045482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29349768161774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27912533283234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29247117042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25756728649139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23600888252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24935460090637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24114179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21753036975861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18673288822174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13540363311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1487489938736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1107656955719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17749345302582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19802510738373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2442215681076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25038111209869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25654077529907</t>
   </si>
   <si>
     <t xml:space="preserve">1.26270020008087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24216842651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2780989408493</t>
+    <t xml:space="preserve">1.24216854572296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27809882164001</t>
   </si>
   <si>
     <t xml:space="preserve">1.23190259933472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26680636405945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26783323287964</t>
+    <t xml:space="preserve">1.26680660247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26783299446106</t>
   </si>
   <si>
     <t xml:space="preserve">1.18878591060638</t>
@@ -272,196 +272,196 @@
     <t xml:space="preserve">1.13950991630554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1425895690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14977562427521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15798842906952</t>
+    <t xml:space="preserve">1.14258968830109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14977586269379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15798830986023</t>
   </si>
   <si>
     <t xml:space="preserve">1.14566934108734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14156293869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1292439699173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12103128433228</t>
+    <t xml:space="preserve">1.14156305789948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12924420833588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12103140354156</t>
   </si>
   <si>
     <t xml:space="preserve">1.15080225467682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17852032184601</t>
+    <t xml:space="preserve">1.17852020263672</t>
   </si>
   <si>
     <t xml:space="preserve">1.18775928020477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18666660785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.258784532547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28719460964203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2970290184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26096999645233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24020874500275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23037457466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20852053165436</t>
+    <t xml:space="preserve">1.18666672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25878441333771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28719449043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29702889919281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26097011566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24020886421204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23037445545197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20852041244507</t>
   </si>
   <si>
     <t xml:space="preserve">1.20414972305298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22491109371185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21070611476898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19977915287018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15060782432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08286082744598</t>
+    <t xml:space="preserve">1.22491097450256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21070599555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1997789144516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15060770511627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08286046981812</t>
   </si>
   <si>
     <t xml:space="preserve">1.0451625585556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07466530799866</t>
+    <t xml:space="preserve">1.07466542720795</t>
   </si>
   <si>
     <t xml:space="preserve">1.06537747383118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1145486831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14842247962952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17683267593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17573976516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23365247249603</t>
+    <t xml:space="preserve">1.11454880237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14842236042023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17683231830597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17573952674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23365235328674</t>
   </si>
   <si>
     <t xml:space="preserve">0.950644612312317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846838533878326</t>
+    <t xml:space="preserve">0.846838414669037</t>
   </si>
   <si>
     <t xml:space="preserve">0.887268245220184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900380730628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929883480072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917863667011261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889999866485596</t>
+    <t xml:space="preserve">0.900380492210388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929883360862732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917863786220551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889999985694885</t>
   </si>
   <si>
     <t xml:space="preserve">0.870331525802612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868692457675934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874155759811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961571514606476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983425319194794</t>
+    <t xml:space="preserve">0.868692517280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874155938625336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961571395397186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983425438404083</t>
   </si>
   <si>
     <t xml:space="preserve">1.04789435863495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03587460517883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05772888660431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05499696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05718243122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.050626039505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06373834609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06701636314392</t>
+    <t xml:space="preserve">1.03587472438812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05772864818573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05499684810638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05718231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05062615871429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06373846530914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06701648235321</t>
   </si>
   <si>
     <t xml:space="preserve">1.06865561008453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04898715019226</t>
+    <t xml:space="preserve">1.04898703098297</t>
   </si>
   <si>
     <t xml:space="preserve">1.05335783958435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07193374633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03969931602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07630455493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03860628604889</t>
+    <t xml:space="preserve">1.0719336271286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03969919681549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07630467414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03860676288605</t>
   </si>
   <si>
     <t xml:space="preserve">0.999269425868988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993806064128876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994352519512177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03806006908417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0511726140976</t>
+    <t xml:space="preserve">0.993806004524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994352161884308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03806018829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05117249488831</t>
   </si>
   <si>
     <t xml:space="preserve">1.05608952045441</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">1.07958269119263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05827510356903</t>
+    <t xml:space="preserve">1.05827498435974</t>
   </si>
   <si>
     <t xml:space="preserve">1.03041124343872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00965011119843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05991411209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09214842319489</t>
+    <t xml:space="preserve">1.00965023040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05991423130035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09214854240417</t>
   </si>
   <si>
     <t xml:space="preserve">1.08231437206268</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">1.11673414707184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16372013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19759368896484</t>
+    <t xml:space="preserve">1.1637202501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19759356975555</t>
   </si>
   <si>
     <t xml:space="preserve">1.19213008880615</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">1.16809093952179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17901790142059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1833883523941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15934920310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13749551773071</t>
+    <t xml:space="preserve">1.1790177822113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18338871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15934932231903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13749539852142</t>
   </si>
   <si>
     <t xml:space="preserve">1.13640260696411</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">1.12766098976135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09706556797028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11236321926117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12656843662262</t>
+    <t xml:space="preserve">1.09706568717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11236345767975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12656831741333</t>
   </si>
   <si>
     <t xml:space="preserve">1.09050953388214</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">1.06428468227386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06155288219452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06319212913513</t>
+    <t xml:space="preserve">1.0615531206131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06319200992584</t>
   </si>
   <si>
     <t xml:space="preserve">1.07848989963531</t>
@@ -566,22 +566,22 @@
     <t xml:space="preserve">1.07685077190399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08340704441071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12329030036926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13093912601471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15170037746429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15388584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17792522907257</t>
+    <t xml:space="preserve">1.08340716362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12329041957855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13093900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15170049667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15388596057892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17792510986328</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196449756622</t>
@@ -590,22 +590,22 @@
     <t xml:space="preserve">1.18229591846466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15279304981232</t>
+    <t xml:space="preserve">1.15279316902161</t>
   </si>
   <si>
     <t xml:space="preserve">1.13858807086945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0992511510849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09597301483154</t>
+    <t xml:space="preserve">1.09925103187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09597313404083</t>
   </si>
   <si>
     <t xml:space="preserve">1.16044199466705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16918361186981</t>
+    <t xml:space="preserve">1.1691837310791</t>
   </si>
   <si>
     <t xml:space="preserve">1.22054016590118</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">1.15497851371765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1418662071228</t>
+    <t xml:space="preserve">1.14186632633209</t>
   </si>
   <si>
     <t xml:space="preserve">1.11891961097717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10362184047699</t>
+    <t xml:space="preserve">1.1036217212677</t>
   </si>
   <si>
     <t xml:space="preserve">1.06810939311981</t>
@@ -638,52 +638,52 @@
     <t xml:space="preserve">1.24567222595215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26643323898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30904853343964</t>
+    <t xml:space="preserve">1.26643311977386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30904841423035</t>
   </si>
   <si>
     <t xml:space="preserve">1.27845299243927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32762444019318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29265797138214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33636605739594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31888294219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33745849132538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33855140209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34401488304138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964395523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871687412262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31779026985168</t>
+    <t xml:space="preserve">1.32762432098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29265809059143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33636581897736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31888282299042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33745884895325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855128288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3440146446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964419364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871699333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31779003143311</t>
   </si>
   <si>
     <t xml:space="preserve">1.32543909549713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36805391311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38772261142731</t>
+    <t xml:space="preserve">1.36805379390717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38772249221802</t>
   </si>
   <si>
     <t xml:space="preserve">1.3975567817688</t>
@@ -692,31 +692,31 @@
     <t xml:space="preserve">1.38990795612335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35275638103485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3483852148056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34620010852814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34729266166687</t>
+    <t xml:space="preserve">1.35275626182556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34838545322418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34619998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34729301929474</t>
   </si>
   <si>
     <t xml:space="preserve">1.32216095924377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34292197227478</t>
+    <t xml:space="preserve">1.34292209148407</t>
   </si>
   <si>
     <t xml:space="preserve">1.34947824478149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31014120578766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25222826004028</t>
+    <t xml:space="preserve">1.31014108657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25222849845886</t>
   </si>
   <si>
     <t xml:space="preserve">1.25659906864166</t>
@@ -725,31 +725,31 @@
     <t xml:space="preserve">1.22928178310394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23911619186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20087194442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18557393550873</t>
+    <t xml:space="preserve">1.23911595344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20087146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18557417392731</t>
   </si>
   <si>
     <t xml:space="preserve">1.19103741645813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22272562980652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19322264194489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17027604579926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17355453968048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16590547561646</t>
+    <t xml:space="preserve">1.22272539138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19322288036346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17027616500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1735543012619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16590559482574</t>
   </si>
   <si>
     <t xml:space="preserve">1.17136895656586</t>
@@ -761,10 +761,10 @@
     <t xml:space="preserve">1.18120312690735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13421714305878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25113546848297</t>
+    <t xml:space="preserve">1.13421738147736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25113582611084</t>
   </si>
   <si>
     <t xml:space="preserve">1.27626776695251</t>
@@ -773,25 +773,25 @@
     <t xml:space="preserve">1.26861882209778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27189683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27408218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30577027797699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34182965755463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32325351238251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35057103633881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35603451728821</t>
+    <t xml:space="preserve">1.27189695835114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27408230304718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30577051639557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34182929992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3232536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35057079792023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35603427886963</t>
   </si>
   <si>
     <t xml:space="preserve">1.36914682388306</t>
@@ -800,28 +800,28 @@
     <t xml:space="preserve">1.39100074768066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38662993907928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38335180282593</t>
+    <t xml:space="preserve">1.38663005828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38335168361664</t>
   </si>
   <si>
     <t xml:space="preserve">1.37679553031921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38007378578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37898087501526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37461042404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36696147918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384917259216</t>
+    <t xml:space="preserve">1.38007390499115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37898111343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37460994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36696135997772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.353848695755</t>
   </si>
   <si>
     <t xml:space="preserve">1.33199512958527</t>
@@ -830,118 +830,118 @@
     <t xml:space="preserve">1.30467772483826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35166347026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36040532588959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37351751327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47623074054718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5057338476181</t>
+    <t xml:space="preserve">1.35166358947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36040508747101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37351739406586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47623062133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50573360919952</t>
   </si>
   <si>
     <t xml:space="preserve">1.49480664730072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45984029769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46093308925629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46311855316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47076725959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50791895389557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55271923542023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55818283557892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55599772930145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55708992481232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54725623130798</t>
+    <t xml:space="preserve">1.45984041690826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.460932970047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46311819553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47076737880707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50791907310486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55271947383881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5581830739975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55599784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5570901632309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5472559928894</t>
   </si>
   <si>
     <t xml:space="preserve">1.54507064819336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55162668228149</t>
+    <t xml:space="preserve">1.55162680149078</t>
   </si>
   <si>
     <t xml:space="preserve">1.52868020534515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52212393283844</t>
+    <t xml:space="preserve">1.52212405204773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5297726392746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56594574451447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57061350345612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56711316108704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55427706241608</t>
   </si>
   <si>
     <t xml:space="preserve">1.52977275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56594622135162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57061326503754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56711280345917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55427742004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52977287769318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49826717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48893249034882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48659861087799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50060129165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51110315322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49126589298248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48426461219788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4994341135025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50876903533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50176763534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50410175323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49710047245026</t>
+    <t xml:space="preserve">1.49826741218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48893237113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659884929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5006011724472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51110303401947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49126601219177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48426485061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49943399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50876927375793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50176775455475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50410163402557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49710023403168</t>
   </si>
   <si>
     <t xml:space="preserve">1.47843039035797</t>
@@ -950,58 +950,58 @@
     <t xml:space="preserve">1.51460349559784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52510547637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52627205848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57994830608368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60795366764069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64062607288361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61845505237579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6196221113205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66279673576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65929615497589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67213153839111</t>
+    <t xml:space="preserve">1.5251053571701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52627217769623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57994842529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6079535484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64062631130219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61845517158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61962234973907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66279661655426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65929627418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6721316576004</t>
   </si>
   <si>
     <t xml:space="preserve">1.65696227550507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66863107681274</t>
+    <t xml:space="preserve">1.66863059997559</t>
   </si>
   <si>
     <t xml:space="preserve">1.65346157550812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66162991523743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6639631986618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67096483707428</t>
+    <t xml:space="preserve">1.66163003444672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66396367549896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67096507549286</t>
   </si>
   <si>
     <t xml:space="preserve">1.67446517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66629719734192</t>
+    <t xml:space="preserve">1.66629695892334</t>
   </si>
   <si>
     <t xml:space="preserve">1.67329859733582</t>
@@ -1010,58 +1010,58 @@
     <t xml:space="preserve">1.6838002204895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69313526153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69546937942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69430220127106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69896960258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70130348205566</t>
+    <t xml:space="preserve">1.69313549995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69546902179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69430232048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69896972179413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70130336284637</t>
   </si>
   <si>
     <t xml:space="preserve">1.69196856021881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70363748073578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70830464363098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70480394363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67796587944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66046273708344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70713794231415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68963468074799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64295971393585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65462863445282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65812909603119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63712561130524</t>
+    <t xml:space="preserve">1.7036372423172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70830476284027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70480418205261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263375759125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67796564102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6604630947113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70713806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6896345615387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64295983314514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65462851524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65812921524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63712537288666</t>
   </si>
   <si>
     <t xml:space="preserve">1.66513049602509</t>
@@ -1073,16 +1073,16 @@
     <t xml:space="preserve">1.70013654232025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7106386423111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71763980388641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73280942440033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73397612571716</t>
+    <t xml:space="preserve">1.71063840389252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71764004230499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73280918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73397624492645</t>
   </si>
   <si>
     <t xml:space="preserve">1.72464108467102</t>
@@ -1091,67 +1091,67 @@
     <t xml:space="preserve">1.73514294624329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74447822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74214398860931</t>
+    <t xml:space="preserve">1.74447798728943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74214386940002</t>
   </si>
   <si>
     <t xml:space="preserve">1.74564468860626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74681174755096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7409770488739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71180534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71530592441559</t>
+    <t xml:space="preserve">1.74681127071381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74097728729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7118057012558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71530604362488</t>
   </si>
   <si>
     <t xml:space="preserve">1.70947182178497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68496739864349</t>
+    <t xml:space="preserve">1.6849672794342</t>
   </si>
   <si>
     <t xml:space="preserve">1.66746425628662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68029999732971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597112178802</t>
+    <t xml:space="preserve">1.68029975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597100257874</t>
   </si>
   <si>
     <t xml:space="preserve">1.67913281917572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65112781524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.633624792099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63479137420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61728870868683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61495471000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64412701129913</t>
+    <t xml:space="preserve">1.65112805366516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63362455368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6347918510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61728847026825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61495459079742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64412677288055</t>
   </si>
   <si>
     <t xml:space="preserve">1.61378788948059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64529323577881</t>
+    <t xml:space="preserve">1.6452933549881</t>
   </si>
   <si>
     <t xml:space="preserve">1.64646053314209</t>
@@ -1160,46 +1160,46 @@
     <t xml:space="preserve">1.67563223838806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63829207420349</t>
+    <t xml:space="preserve">1.63829231262207</t>
   </si>
   <si>
     <t xml:space="preserve">1.62895739078522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62662374973297</t>
+    <t xml:space="preserve">1.62662351131439</t>
   </si>
   <si>
     <t xml:space="preserve">1.62779021263123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61612164974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60678660869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60445249080658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74331104755402</t>
+    <t xml:space="preserve">1.61612141132355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60678648948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60445284843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74331057071686</t>
   </si>
   <si>
     <t xml:space="preserve">1.76548194885254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77248299121857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77598357200623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78415179252625</t>
+    <t xml:space="preserve">1.77248275279999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77598369121552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78415167331696</t>
   </si>
   <si>
     <t xml:space="preserve">1.80515551567078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80165481567383</t>
+    <t xml:space="preserve">1.80165469646454</t>
   </si>
   <si>
     <t xml:space="preserve">1.82382524013519</t>
@@ -1208,25 +1208,25 @@
     <t xml:space="preserve">1.8249922990799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79815411567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82149147987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84366250038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824823379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83549404144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84395360946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8311185836792</t>
+    <t xml:space="preserve">1.79815399646759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82149159908295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84366202354431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824799537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83549439907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84395396709442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111810684204</t>
   </si>
   <si>
     <t xml:space="preserve">1.81769943237305</t>
@@ -1235,109 +1235,109 @@
     <t xml:space="preserve">1.79902899265289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81098973751068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87283396720886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83636963367462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81157314777374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377841949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80923938751221</t>
+    <t xml:space="preserve">1.81098961830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87283384799957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83636939525604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81157326698303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377830028534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923914909363</t>
   </si>
   <si>
     <t xml:space="preserve">1.80690562725067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83053505420685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81303179264069</t>
+    <t xml:space="preserve">1.83053481578827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8130316734314</t>
   </si>
   <si>
     <t xml:space="preserve">1.80223834514618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80748903751373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78444302082062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79873752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79990434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80982291698456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80632245540619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79290318489075</t>
+    <t xml:space="preserve">1.8074893951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78444337844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79873740673065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79990446567535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80982279777527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8063223361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79290294647217</t>
   </si>
   <si>
     <t xml:space="preserve">1.75410461425781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7293084859848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74535310268402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76518952846527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77510833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78035926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540016174316</t>
+    <t xml:space="preserve">1.72930860519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74535298347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76518988609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77510821819305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78035938739777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77539968490601</t>
   </si>
   <si>
     <t xml:space="preserve">1.74885368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76081418991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79523694515228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7736496925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78473508358002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77423310279846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74272763729095</t>
+    <t xml:space="preserve">1.76081371307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79523682594299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77364981174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78473496437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77423298358917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74272751808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.72259914875031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70742964744568</t>
+    <t xml:space="preserve">1.70742952823639</t>
   </si>
   <si>
     <t xml:space="preserve">1.72289061546326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72318279743195</t>
+    <t xml:space="preserve">1.72318243980408</t>
   </si>
   <si>
     <t xml:space="preserve">1.72522461414337</t>
@@ -1346,46 +1346,46 @@
     <t xml:space="preserve">1.71909832954407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7520626783371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74768686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76256453990936</t>
+    <t xml:space="preserve">1.75206243991852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74768698215485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76256442070007</t>
   </si>
   <si>
     <t xml:space="preserve">1.77131593227386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7590639591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77948439121246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78940236568451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79465329647064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81449043750763</t>
+    <t xml:space="preserve">1.75906383991241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77948427200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7894024848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79465389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81449019908905</t>
   </si>
   <si>
     <t xml:space="preserve">1.8153657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82907629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84832942485809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86437439918518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83986985683441</t>
+    <t xml:space="preserve">1.82907652854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84832978248596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8643741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83987009525299</t>
   </si>
   <si>
     <t xml:space="preserve">1.85124695301056</t>
@@ -1394,16 +1394,16 @@
     <t xml:space="preserve">1.83957827091217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84191226959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84862172603607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83811950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84453761577606</t>
+    <t xml:space="preserve">1.841912150383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8486213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83811974525452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84453737735748</t>
   </si>
   <si>
     <t xml:space="preserve">1.83403563499451</t>
@@ -1412,46 +1412,46 @@
     <t xml:space="preserve">1.82674264907837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83782804012299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85416400432587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80865609645844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79436159133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031208992004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73967409133911</t>
+    <t xml:space="preserve">1.83782768249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85416412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80865573883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79436194896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031197071075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73967373371124</t>
   </si>
   <si>
     <t xml:space="preserve">1.75156366825104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72090005874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70494282245636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65081286430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59730851650238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53191435337067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57759654521942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57352876663208</t>
+    <t xml:space="preserve">1.72090029716492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70494258403778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65081298351288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59730863571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53191459178925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57759618759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57352864742279</t>
   </si>
   <si>
     <t xml:space="preserve">1.6254688501358</t>
@@ -1460,280 +1460,280 @@
     <t xml:space="preserve">1.62515580654144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56289052963257</t>
+    <t xml:space="preserve">1.56289064884186</t>
   </si>
   <si>
     <t xml:space="preserve">1.55475521087646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53629469871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51752150058746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61827206611633</t>
+    <t xml:space="preserve">1.53629446029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51752102375031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61827230453491</t>
   </si>
   <si>
     <t xml:space="preserve">1.6173335313797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62578153610229</t>
+    <t xml:space="preserve">1.62578141689301</t>
   </si>
   <si>
     <t xml:space="preserve">1.62327837944031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59417963027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59793412685394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60575664043427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63548135757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60325360298157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6195240020752</t>
+    <t xml:space="preserve">1.59417927265167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59793400764465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60575640201569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63548111915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60325348377228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61952376365662</t>
   </si>
   <si>
     <t xml:space="preserve">1.56695783138275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55068790912628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690804004669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55694556236267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55600702762604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54474258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57634484767914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58416736125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60513079166412</t>
+    <t xml:space="preserve">1.55068755149841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690827846527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55694544315338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55600678920746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54474282264709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57634496688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58416712284088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60513067245483</t>
   </si>
   <si>
     <t xml:space="preserve">1.60294055938721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60606932640076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58041214942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54881024360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53066277503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973650932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53660762310028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55193936824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54161393642426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51658284664154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5053186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250256061554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53097569942474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55037486553192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57039964199066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58322834968567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6483097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57259011268616</t>
+    <t xml:space="preserve">1.60606920719147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5804123878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54881048202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53066265583038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973662853241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53660774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55193912982941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54161381721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51658260822296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50531840324402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250267982483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53097558021545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5503751039505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57039976119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58322846889496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64830994606018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57258999347687</t>
   </si>
   <si>
     <t xml:space="preserve">1.51188910007477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53003716468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50844776630402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49248993396759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43804693222046</t>
+    <t xml:space="preserve">1.53003680706024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50844740867615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49249017238617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43804705142975</t>
   </si>
   <si>
     <t xml:space="preserve">1.41426742076874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40175139904022</t>
+    <t xml:space="preserve">1.40175175666809</t>
   </si>
   <si>
     <t xml:space="preserve">1.37640738487244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36576926708221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35732126235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40331590175629</t>
+    <t xml:space="preserve">1.36576890945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35732102394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40331602096558</t>
   </si>
   <si>
     <t xml:space="preserve">1.38329112529755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3767204284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37891054153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37859773635864</t>
+    <t xml:space="preserve">1.37672054767609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37891066074371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37859761714935</t>
   </si>
   <si>
     <t xml:space="preserve">1.3635790348053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38172650337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34918618202209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3313512802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35857272148132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45901072025299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43929851055145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41583180427551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47997415065765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45650780200958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46432960033417</t>
+    <t xml:space="preserve">1.38172662258148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34918606281281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33135116100311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35857260227203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897307872772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45901095867157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43929839134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41583204269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47997438907623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45650768280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46432983875275</t>
   </si>
   <si>
     <t xml:space="preserve">1.45744621753693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46683311462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50093805789948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49906051158905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51908564567566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51157641410828</t>
+    <t xml:space="preserve">1.46683287620544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50093793869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49906063079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51908576488495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5115761756897</t>
   </si>
   <si>
     <t xml:space="preserve">1.53222703933716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49999964237213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54568159580231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5222145318985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50437986850739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37734591960907</t>
+    <t xml:space="preserve">1.49999940395355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54568147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52221477031708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50437998771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37734627723694</t>
   </si>
   <si>
     <t xml:space="preserve">1.32352888584137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31914842128754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32634484767914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35481774806976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31320345401764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27033722400665</t>
+    <t xml:space="preserve">1.31914854049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32634496688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35481810569763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31320321559906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27033734321594</t>
   </si>
   <si>
     <t xml:space="preserve">1.29818487167358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30506825447083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27284073829651</t>
+    <t xml:space="preserve">1.30506837368011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27284061908722</t>
   </si>
   <si>
     <t xml:space="preserve">1.26783442497253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27753412723541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29536867141724</t>
+    <t xml:space="preserve">1.27753388881683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29536855220795</t>
   </si>
   <si>
     <t xml:space="preserve">1.28066277503967</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">1.23842263221741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2416764497757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23128855228424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23166394233704</t>
+    <t xml:space="preserve">1.24167656898499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23128843307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23166418075562</t>
   </si>
   <si>
     <t xml:space="preserve">1.18936133384705</t>
@@ -1757,25 +1757,25 @@
     <t xml:space="preserve">1.22227740287781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21264028549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24943625926971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24655759334564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2221519947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24267792701721</t>
+    <t xml:space="preserve">1.21264040470123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.249436378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24655771255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22215223312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24267780780792</t>
   </si>
   <si>
     <t xml:space="preserve">1.25563156604767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23667025566101</t>
+    <t xml:space="preserve">1.2366703748703</t>
   </si>
   <si>
     <t xml:space="preserve">1.25250244140625</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">1.28598201274872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2697114944458</t>
+    <t xml:space="preserve">1.26971173286438</t>
   </si>
   <si>
     <t xml:space="preserve">1.25500583648682</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">1.22665786743164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25312840938568</t>
+    <t xml:space="preserve">1.25312852859497</t>
   </si>
   <si>
     <t xml:space="preserve">1.23829746246338</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">1.2226527929306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20112574100494</t>
+    <t xml:space="preserve">1.20112597942352</t>
   </si>
   <si>
     <t xml:space="preserve">1.20538115501404</t>
@@ -1811,46 +1811,46 @@
     <t xml:space="preserve">1.17571914196014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2090106010437</t>
+    <t xml:space="preserve">1.20901083946228</t>
   </si>
   <si>
     <t xml:space="preserve">1.20888566970825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22165143489838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27690815925598</t>
+    <t xml:space="preserve">1.22165167331696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2769079208374</t>
   </si>
   <si>
     <t xml:space="preserve">1.27628231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28535628318787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2719019651413</t>
+    <t xml:space="preserve">1.28535616397858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27190184593201</t>
   </si>
   <si>
     <t xml:space="preserve">1.28160154819489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32196450233459</t>
+    <t xml:space="preserve">1.32196438312531</t>
   </si>
   <si>
     <t xml:space="preserve">1.29161381721497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30193936824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23491823673248</t>
+    <t xml:space="preserve">1.30193948745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23491811752319</t>
   </si>
   <si>
     <t xml:space="preserve">1.24029982089996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21376669406891</t>
+    <t xml:space="preserve">1.2137668132782</t>
   </si>
   <si>
     <t xml:space="preserve">1.21026229858398</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">1.25969910621643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27158904075623</t>
+    <t xml:space="preserve">1.27158892154694</t>
   </si>
   <si>
     <t xml:space="preserve">1.26032471656799</t>
@@ -1871,25 +1871,25 @@
     <t xml:space="preserve">1.2421772480011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26345384120941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2171459197998</t>
+    <t xml:space="preserve">1.26345372200012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21714603900909</t>
   </si>
   <si>
     <t xml:space="preserve">1.19662022590637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1946177482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21389198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19299054145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18986201286316</t>
+    <t xml:space="preserve">1.19461786746979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21389186382294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19299066066742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18986177444458</t>
   </si>
   <si>
     <t xml:space="preserve">1.25106334686279</t>
@@ -1898,25 +1898,25 @@
     <t xml:space="preserve">1.27221488952637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25750887393951</t>
+    <t xml:space="preserve">1.2575089931488</t>
   </si>
   <si>
     <t xml:space="preserve">1.26470530033112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25844752788544</t>
+    <t xml:space="preserve">1.25844740867615</t>
   </si>
   <si>
     <t xml:space="preserve">1.24017465114594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22465538978577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26001214981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27565658092499</t>
+    <t xml:space="preserve">1.22465527057648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2600120306015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27565670013428</t>
   </si>
   <si>
     <t xml:space="preserve">1.27596950531006</t>
@@ -1925,25 +1925,25 @@
     <t xml:space="preserve">1.26814711093903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26908612251282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29192686080933</t>
+    <t xml:space="preserve">1.26908576488495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29192709922791</t>
   </si>
   <si>
     <t xml:space="preserve">1.28003704547882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28191447257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28973686695099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24830996990204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22815978527069</t>
+    <t xml:space="preserve">1.28191435337067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28973662853241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24830985069275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2281596660614</t>
   </si>
   <si>
     <t xml:space="preserve">1.22753381729126</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">1.2361695766449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25131368637085</t>
+    <t xml:space="preserve">1.25131356716156</t>
   </si>
   <si>
     <t xml:space="preserve">1.25531876087189</t>
@@ -1970,31 +1970,31 @@
     <t xml:space="preserve">1.28097581863403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29223990440369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28629469871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28692066669464</t>
+    <t xml:space="preserve">1.2922397851944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28629493713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28692054748535</t>
   </si>
   <si>
     <t xml:space="preserve">1.27659523487091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27784669399261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30444240570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.299436211586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3338543176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35043740272522</t>
+    <t xml:space="preserve">1.27784705162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30444276332855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29943633079529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33385419845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35043752193451</t>
   </si>
   <si>
     <t xml:space="preserve">1.35513079166412</t>
@@ -2003,109 +2003,109 @@
     <t xml:space="preserve">1.35262763500214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36545610427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3351057767868</t>
+    <t xml:space="preserve">1.36545634269714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33510601520538</t>
   </si>
   <si>
     <t xml:space="preserve">1.32603192329407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33760893344879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33667039871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34824728965759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35794687271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37609434127808</t>
+    <t xml:space="preserve">1.33760905265808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33667004108429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3482471704483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35794699192047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37609457969666</t>
   </si>
   <si>
     <t xml:space="preserve">1.39737117290497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3992486000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39549398422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38610696792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34949898719788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480535984039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136378765106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3516891002655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35419225692749</t>
+    <t xml:space="preserve">1.39924871921539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39549374580383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3861072063446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3494987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480559825897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136366844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35168921947479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35419237613678</t>
   </si>
   <si>
     <t xml:space="preserve">1.38016211986542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37546896934509</t>
+    <t xml:space="preserve">1.37546873092651</t>
   </si>
   <si>
     <t xml:space="preserve">1.38767147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39799666404724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39956140518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39017450809479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39830958843231</t>
+    <t xml:space="preserve">1.39799690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3995612859726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39017462730408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39830982685089</t>
   </si>
   <si>
     <t xml:space="preserve">1.43992435932159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45337879657745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46558129787445</t>
+    <t xml:space="preserve">1.45337855815887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46558165550232</t>
   </si>
   <si>
     <t xml:space="preserve">1.45963644981384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45244002342224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42365396022797</t>
+    <t xml:space="preserve">1.45243990421295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42365407943726</t>
   </si>
   <si>
     <t xml:space="preserve">1.42490553855896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42991185188293</t>
+    <t xml:space="preserve">1.42991209030151</t>
   </si>
   <si>
     <t xml:space="preserve">1.45932364463806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46245265007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45619463920593</t>
+    <t xml:space="preserve">1.46245229244232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45619451999664</t>
   </si>
   <si>
     <t xml:space="preserve">1.45306587219238</t>
@@ -2120,58 +2120,58 @@
     <t xml:space="preserve">1.38673293590546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35450541973114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35137593746185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32540607452393</t>
+    <t xml:space="preserve">1.35450506210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35137629508972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32540619373322</t>
   </si>
   <si>
     <t xml:space="preserve">1.34543132781982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36639499664307</t>
+    <t xml:space="preserve">1.36639487743378</t>
   </si>
   <si>
     <t xml:space="preserve">1.35825979709625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36135709285736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36066877841949</t>
+    <t xml:space="preserve">1.36135697364807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36066865921021</t>
   </si>
   <si>
     <t xml:space="preserve">1.33630478382111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30973827838898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32061266899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31331717967987</t>
+    <t xml:space="preserve">1.3097380399704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3206125497818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31331706047058</t>
   </si>
   <si>
     <t xml:space="preserve">1.29872620105743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28413546085358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28372240066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26211142539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25674283504486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28441059589386</t>
+    <t xml:space="preserve">1.28413534164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28372228145599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2621111869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25674307346344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28441071510315</t>
   </si>
   <si>
     <t xml:space="preserve">1.27326095104218</t>
@@ -2180,28 +2180,28 @@
     <t xml:space="preserve">1.25701832771301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2614232301712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27037036418915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133405208588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25811970233917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2677549123764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2645890712738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26018416881561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2893660068512</t>
+    <t xml:space="preserve">1.26142311096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27037048339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133393287659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2581193447113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26775515079498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26458919048309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2601842880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28936624526978</t>
   </si>
   <si>
     <t xml:space="preserve">1.312628865242</t>
@@ -2213,16 +2213,16 @@
     <t xml:space="preserve">1.29046726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29032957553864</t>
+    <t xml:space="preserve">1.29032969474792</t>
   </si>
   <si>
     <t xml:space="preserve">1.28592467308044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29239439964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29294502735138</t>
+    <t xml:space="preserve">1.29239428043365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29294490814209</t>
   </si>
   <si>
     <t xml:space="preserve">1.29528498649597</t>
@@ -2231,46 +2231,46 @@
     <t xml:space="preserve">1.28537428379059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29734981060028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36328399181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39439272880554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852249622345</t>
+    <t xml:space="preserve">1.29734969139099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36328411102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39439296722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39852225780487</t>
   </si>
   <si>
     <t xml:space="preserve">1.38854277133942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38097202777863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.397833943367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41469621658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41159915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40987861156464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41916990280151</t>
+    <t xml:space="preserve">1.38097190856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39783406257629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41469633579254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41159951686859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40987837314606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41916966438293</t>
   </si>
   <si>
     <t xml:space="preserve">1.40609312057495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41091072559357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38200449943542</t>
+    <t xml:space="preserve">1.41091096401215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38200438022614</t>
   </si>
   <si>
     <t xml:space="preserve">1.38441324234009</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">1.3902633190155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38338077068329</t>
+    <t xml:space="preserve">1.38338088989258</t>
   </si>
   <si>
     <t xml:space="preserve">1.37044179439545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35309791564941</t>
+    <t xml:space="preserve">1.35309779644012</t>
   </si>
   <si>
     <t xml:space="preserve">1.34924364089966</t>
@@ -2297,34 +2297,34 @@
     <t xml:space="preserve">1.37649834156036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34387528896332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35433685779572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33836948871613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31455588340759</t>
+    <t xml:space="preserve">1.34387540817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35433673858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33836960792542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31455600261688</t>
   </si>
   <si>
     <t xml:space="preserve">1.33891999721527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26362574100494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29886412620544</t>
+    <t xml:space="preserve">1.26362550258636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29886388778687</t>
   </si>
   <si>
     <t xml:space="preserve">1.27023267745972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3174467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31001353263855</t>
+    <t xml:space="preserve">1.31744658946991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31001365184784</t>
   </si>
   <si>
     <t xml:space="preserve">1.32322788238525</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">1.33644223213196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30987596511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33520352840424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34084725379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35488748550415</t>
+    <t xml:space="preserve">1.30987584590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33520364761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34084689617157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35488736629486</t>
   </si>
   <si>
     <t xml:space="preserve">1.38578975200653</t>
@@ -2357,295 +2357,295 @@
     <t xml:space="preserve">1.3768424987793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39542531967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41504049301147</t>
+    <t xml:space="preserve">1.39542520046234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41504037380219</t>
   </si>
   <si>
     <t xml:space="preserve">1.42261099815369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44635558128357</t>
+    <t xml:space="preserve">1.44635570049286</t>
   </si>
   <si>
     <t xml:space="preserve">1.46149730682373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45082926750183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46080887317657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50175964832306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47526240348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46252954006195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46321761608124</t>
+    <t xml:space="preserve">1.45082950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46080875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50175976753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47526228427887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46252942085266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46321773529053</t>
   </si>
   <si>
     <t xml:space="preserve">1.48937141895294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49074769020081</t>
+    <t xml:space="preserve">1.4907478094101</t>
   </si>
   <si>
     <t xml:space="preserve">1.47319746017456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46597099304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46941208839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47491788864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49728608131409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48317694664001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4411940574646</t>
+    <t xml:space="preserve">1.4659708738327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46941196918488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47491800785065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48696255683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4972859621048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48317718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44119381904602</t>
   </si>
   <si>
     <t xml:space="preserve">1.439129114151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44222629070282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43568778038025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4477322101593</t>
+    <t xml:space="preserve">1.44222605228424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43568801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44773197174072</t>
   </si>
   <si>
     <t xml:space="preserve">1.47939145565033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50451290607452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50038349628448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52103078365326</t>
+    <t xml:space="preserve">1.50451278686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50038313865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52103090286255</t>
   </si>
   <si>
     <t xml:space="preserve">1.54064607620239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53582787513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53789269924164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55062556266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56576693058014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56232559680939</t>
+    <t xml:space="preserve">1.53582811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53789281845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55062532424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56576704978943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56232571601868</t>
   </si>
   <si>
     <t xml:space="preserve">1.56301391124725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56404650211334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5681756734848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56370222568512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54752826690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54580783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56439054012299</t>
+    <t xml:space="preserve">1.56404626369476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56817579269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56370234489441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54752838611603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54580771923065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56439030170441</t>
   </si>
   <si>
     <t xml:space="preserve">1.58710277080536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61050295829773</t>
+    <t xml:space="preserve">1.61050307750702</t>
   </si>
   <si>
     <t xml:space="preserve">1.60878252983093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62151539325714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256778240204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62220335006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63665664196014</t>
+    <t xml:space="preserve">1.62151503562927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256790161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62220358848572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63665640354156</t>
   </si>
   <si>
     <t xml:space="preserve">1.61394429206848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60086750984192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60912680625916</t>
+    <t xml:space="preserve">1.60086762905121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60912692546844</t>
   </si>
   <si>
     <t xml:space="preserve">1.61738550662994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61566543579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62013852596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61291193962097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61910629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61187970638275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60190033912659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58985543251038</t>
+    <t xml:space="preserve">1.61566495895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62013864517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61291170120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61910617351532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61187994480133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60190010070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58985567092896</t>
   </si>
   <si>
     <t xml:space="preserve">1.58331727981567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5451192855835</t>
+    <t xml:space="preserve">1.54511952400208</t>
   </si>
   <si>
     <t xml:space="preserve">1.5767787694931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57471442222595</t>
+    <t xml:space="preserve">1.57471418380737</t>
   </si>
   <si>
     <t xml:space="preserve">1.59226429462433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58090841770172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58572626113892</t>
+    <t xml:space="preserve">1.58090829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58572614192963</t>
   </si>
   <si>
     <t xml:space="preserve">1.59054398536682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60224401950836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61497664451599</t>
+    <t xml:space="preserve">1.60224425792694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61497676372528</t>
   </si>
   <si>
     <t xml:space="preserve">1.62633287906647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6283974647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63803315162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65523946285248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65214192867279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62082695960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61635303497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63872134685516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61704134941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63390374183655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61119115352631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61532092094421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59673798084259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59845876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60809445381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59570586681366</t>
+    <t xml:space="preserve">1.62839758396149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63803291320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65523934364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65214216709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6208268404007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61635315418243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63872158527374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6170414686203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63390362262726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61119139194489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6153210401535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59673810005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59845864772797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60809433460236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59570574760437</t>
   </si>
   <si>
     <t xml:space="preserve">1.56920826435089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56094944477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56783175468445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55200219154358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58675837516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57712316513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5454638004303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57264947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61841797828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68586623668671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70100772380829</t>
+    <t xml:space="preserve">1.56094908714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56783163547516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.552001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58675873279572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5771232843399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54546368122101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57264971733093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61841809749603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68586647510529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70100784301758</t>
   </si>
   <si>
     <t xml:space="preserve">1.7041050195694</t>
@@ -2654,25 +2654,25 @@
     <t xml:space="preserve">1.69240474700928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70857870578766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72578454017639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72750544548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74815309047699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78944754600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79185664653778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75503551959991</t>
+    <t xml:space="preserve">1.70857846736908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72578501701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72750568389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7481529712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78944766521454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79185700416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75503540039062</t>
   </si>
   <si>
     <t xml:space="preserve">1.73542070388794</t>
@@ -2681,64 +2681,64 @@
     <t xml:space="preserve">1.63562417030334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60362076759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5750584602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51311564445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4704442024231</t>
+    <t xml:space="preserve">1.6036205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57505822181702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51311576366425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47044432163239</t>
   </si>
   <si>
     <t xml:space="preserve">1.45840001106262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46425032615662</t>
+    <t xml:space="preserve">1.46425020694733</t>
   </si>
   <si>
     <t xml:space="preserve">1.4085019826889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36080622673035</t>
+    <t xml:space="preserve">1.36080658435822</t>
   </si>
   <si>
     <t xml:space="preserve">1.20443606376648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17608022689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2245329618454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00677096843719</t>
+    <t xml:space="preserve">1.1760801076889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22453308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00677084922791</t>
   </si>
   <si>
     <t xml:space="preserve">1.06981456279755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965475976467133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998924911022186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969467639923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980892717838287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00856041908264</t>
+    <t xml:space="preserve">0.965475916862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998925089836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969467759132385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980892777442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00856029987335</t>
   </si>
   <si>
     <t xml:space="preserve">0.997135400772095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08991146087646</t>
+    <t xml:space="preserve">1.08991169929504</t>
   </si>
   <si>
     <t xml:space="preserve">1.11234831809998</t>
@@ -2747,55 +2747,55 @@
     <t xml:space="preserve">1.12253451347351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07821106910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01227688789368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02439022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987500190734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989564597606659</t>
+    <t xml:space="preserve">1.07821130752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01227712631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02438998222351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987500131130219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989564657211304</t>
   </si>
   <si>
     <t xml:space="preserve">0.914820909500122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00360500812531</t>
+    <t xml:space="preserve">1.00360488891602</t>
   </si>
   <si>
     <t xml:space="preserve">1.01103806495667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997410833835602</t>
+    <t xml:space="preserve">0.997410655021667</t>
   </si>
   <si>
     <t xml:space="preserve">0.99452006816864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967816114425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928035199642181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936156630516052</t>
+    <t xml:space="preserve">0.967816054821014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928035259246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936156451702118</t>
   </si>
   <si>
     <t xml:space="preserve">0.947168529033661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95184850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908488988876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921015202999115</t>
+    <t xml:space="preserve">0.951848566532135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908489048480988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921014964580536</t>
   </si>
   <si>
     <t xml:space="preserve">0.952812135219574</t>
@@ -2804,61 +2804,61 @@
     <t xml:space="preserve">0.924869239330292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960245430469513</t>
+    <t xml:space="preserve">0.960245311260223</t>
   </si>
   <si>
     <t xml:space="preserve">0.996034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01888418197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979378640651703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947030961513519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998649477958679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977451503276825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966577172279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973184466362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97001850605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977864384651184</t>
+    <t xml:space="preserve">1.01888406276703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979378700256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947030901908875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998649656772614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97745144367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966577053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973184406757355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970018267631531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977864503860474</t>
   </si>
   <si>
     <t xml:space="preserve">0.959143996238708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952261745929718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952399432659149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999475359916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984746992588043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990390658378601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978690326213837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994244813919067</t>
+    <t xml:space="preserve">0.952261626720428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952399253845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999475598335266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984746932983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990390598773956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978690445423126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994244754314423</t>
   </si>
   <si>
     <t xml:space="preserve">1.0031920671463</t>
@@ -2867,46 +2867,46 @@
     <t xml:space="preserve">1.0331996679306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05880260467529</t>
+    <t xml:space="preserve">1.058802485466</t>
   </si>
   <si>
     <t xml:space="preserve">1.07270514965057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0684380531311</t>
+    <t xml:space="preserve">1.06843781471252</t>
   </si>
   <si>
     <t xml:space="preserve">1.08743369579315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11840510368347</t>
+    <t xml:space="preserve">1.11840498447418</t>
   </si>
   <si>
     <t xml:space="preserve">1.15157854557037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16575658321381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2201281785965</t>
+    <t xml:space="preserve">1.16575646400452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22012805938721</t>
   </si>
   <si>
     <t xml:space="preserve">1.24118864536285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18378853797913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17181301116943</t>
+    <t xml:space="preserve">1.18378865718842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17181313037872</t>
   </si>
   <si>
     <t xml:space="preserve">1.11344945430756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11634016036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11950623989105</t>
+    <t xml:space="preserve">1.11634004116058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11950635910034</t>
   </si>
   <si>
     <t xml:space="preserve">1.16947305202484</t>
@@ -2918,43 +2918,43 @@
     <t xml:space="preserve">1.16025054454803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15956211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15791046619415</t>
+    <t xml:space="preserve">1.15956234931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15791058540344</t>
   </si>
   <si>
     <t xml:space="preserve">1.17786967754364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14717364311218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14249360561371</t>
+    <t xml:space="preserve">1.14717376232147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14249348640442</t>
   </si>
   <si>
     <t xml:space="preserve">1.17140018939972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1725013256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16355419158936</t>
+    <t xml:space="preserve">1.17250120639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16355407238007</t>
   </si>
   <si>
     <t xml:space="preserve">1.20636320114136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20223343372345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23348033428192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22962605953217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21338331699371</t>
+    <t xml:space="preserve">1.20223367214203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23348021507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22962617874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21338319778442</t>
   </si>
   <si>
     <t xml:space="preserve">1.19149696826935</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">1.21503520011902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22604727745056</t>
+    <t xml:space="preserve">1.22604703903198</t>
   </si>
   <si>
     <t xml:space="preserve">1.2257719039917</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">1.24875926971436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26596558094025</t>
+    <t xml:space="preserve">1.26596570014954</t>
   </si>
   <si>
     <t xml:space="preserve">1.26073491573334</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">1.27628934383392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29721188545227</t>
+    <t xml:space="preserve">1.29721212387085</t>
   </si>
   <si>
     <t xml:space="preserve">1.29129314422607</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">1.23981201648712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22935056686401</t>
+    <t xml:space="preserve">1.22935092449188</t>
   </si>
   <si>
     <t xml:space="preserve">1.23155307769775</t>
@@ -3005,19 +3005,19 @@
     <t xml:space="preserve">1.1941123008728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17497897148132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1756671667099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23444366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26252436637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24834632873535</t>
+    <t xml:space="preserve">1.17497909069061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17566728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23444378376007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26252424716949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24834644794464</t>
   </si>
   <si>
     <t xml:space="preserve">1.2425651550293</t>
@@ -3026,115 +3026,115 @@
     <t xml:space="preserve">1.24848401546478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28096926212311</t>
+    <t xml:space="preserve">1.2809693813324</t>
   </si>
   <si>
     <t xml:space="preserve">1.29583561420441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28399765491486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27436232566833</t>
+    <t xml:space="preserve">1.28399777412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27436220645905</t>
   </si>
   <si>
     <t xml:space="preserve">1.25564181804657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24903464317322</t>
+    <t xml:space="preserve">1.24903476238251</t>
   </si>
   <si>
     <t xml:space="preserve">1.26981985569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24999833106995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24683237075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26582789421082</t>
+    <t xml:space="preserve">1.24999809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24683225154877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26582813262939</t>
   </si>
   <si>
     <t xml:space="preserve">1.26224899291992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26816809177399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24146389961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25605475902557</t>
+    <t xml:space="preserve">1.2681679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24146378040314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25605463981628</t>
   </si>
   <si>
     <t xml:space="preserve">1.24242746829987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24008727073669</t>
+    <t xml:space="preserve">1.24008750915527</t>
   </si>
   <si>
     <t xml:space="preserve">1.22425758838654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22411978244781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23458135128021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21269512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23210382461548</t>
+    <t xml:space="preserve">1.22412002086639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2345814704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21269488334656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2321035861969</t>
   </si>
   <si>
     <t xml:space="preserve">1.23967444896698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22439527511597</t>
+    <t xml:space="preserve">1.22439539432526</t>
   </si>
   <si>
     <t xml:space="preserve">1.2173752784729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21145629882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19989371299744</t>
+    <t xml:space="preserve">1.21145617961884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19989359378815</t>
   </si>
   <si>
     <t xml:space="preserve">1.18020963668823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12570035457611</t>
+    <t xml:space="preserve">1.1257004737854</t>
   </si>
   <si>
     <t xml:space="preserve">1.12996757030487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10959541797638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10670483112335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08674538135529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1181298494339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10587894916534</t>
+    <t xml:space="preserve">1.10959529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10670495033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08674550056458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11812973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10587871074677</t>
   </si>
   <si>
     <t xml:space="preserve">1.1032634973526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09183847904205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09596812725067</t>
+    <t xml:space="preserve">1.09183859825134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09596800804138</t>
   </si>
   <si>
     <t xml:space="preserve">1.12404870986938</t>
@@ -3143,34 +3143,34 @@
     <t xml:space="preserve">1.14827489852905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13478529453278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15309262275696</t>
+    <t xml:space="preserve">1.1347850561142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15309274196625</t>
   </si>
   <si>
     <t xml:space="preserve">1.15557038784027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14978933334351</t>
+    <t xml:space="preserve">1.14978921413422</t>
   </si>
   <si>
     <t xml:space="preserve">1.11317431926727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05825209617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0707780122757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07353127002716</t>
+    <t xml:space="preserve">1.05825185775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07077813148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07353103160858</t>
   </si>
   <si>
     <t xml:space="preserve">1.05701315402985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05770134925842</t>
+    <t xml:space="preserve">1.05770146846771</t>
   </si>
   <si>
     <t xml:space="preserve">1.07449460029602</t>
@@ -3179,55 +3179,55 @@
     <t xml:space="preserve">1.05095648765564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02590417861938</t>
+    <t xml:space="preserve">1.02590441703796</t>
   </si>
   <si>
     <t xml:space="preserve">0.975937366485596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962998330593109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977038443088531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02026045322418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0603164434433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.099684715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12680160999298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11276113986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21531045436859</t>
+    <t xml:space="preserve">0.962998270988464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977038681507111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02026057243347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06031680107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09968447685242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12680172920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11276149749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2153103351593</t>
   </si>
   <si>
     <t xml:space="preserve">1.26926922798157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25591719150543</t>
+    <t xml:space="preserve">1.25591695308685</t>
   </si>
   <si>
     <t xml:space="preserve">1.24022507667542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25109934806824</t>
+    <t xml:space="preserve">1.25109922885895</t>
   </si>
   <si>
     <t xml:space="preserve">1.26637864112854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27615165710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28730142116547</t>
+    <t xml:space="preserve">1.27615177631378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28730118274689</t>
   </si>
   <si>
     <t xml:space="preserve">1.28248357772827</t>
@@ -3239,58 +3239,58 @@
     <t xml:space="preserve">1.33671760559082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32777059078217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32515501976013</t>
+    <t xml:space="preserve">1.32777047157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32515478134155</t>
   </si>
   <si>
     <t xml:space="preserve">1.35653913021088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36700057983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37002873420715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35667669773102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35516262054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35998034477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34951901435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231282234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33465278148651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35929191112518</t>
+    <t xml:space="preserve">1.36700046062469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37002897262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35667681694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516250133514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35998046398163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34951913356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231270313263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3346529006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35929214954376</t>
   </si>
   <si>
     <t xml:space="preserve">1.33726823329926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3382316827774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33189988136292</t>
+    <t xml:space="preserve">1.33823180198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33189976215363</t>
   </si>
   <si>
     <t xml:space="preserve">1.29473435878754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31662058830261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32309031486511</t>
+    <t xml:space="preserve">1.3166207075119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32309007644653</t>
   </si>
   <si>
     <t xml:space="preserve">1.32130086421967</t>
@@ -3299,73 +3299,73 @@
     <t xml:space="preserve">1.31634533405304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31125247478485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2969366312027</t>
+    <t xml:space="preserve">1.31125235557556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29693675041199</t>
   </si>
   <si>
     <t xml:space="preserve">1.35447442531586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34552717208862</t>
+    <t xml:space="preserve">1.34552729129791</t>
   </si>
   <si>
     <t xml:space="preserve">1.33713066577911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33396470546722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31799721717834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30904996395111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31951129436493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31483137607574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32584345340729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29679906368256</t>
+    <t xml:space="preserve">1.33396458625793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31799709796906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3090500831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31951141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31483113765717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.325843334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29679930210114</t>
   </si>
   <si>
     <t xml:space="preserve">1.25481593608856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26610326766968</t>
+    <t xml:space="preserve">1.26610314846039</t>
   </si>
   <si>
     <t xml:space="preserve">1.24407923221588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26197373867035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25398993492126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771436214447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34291172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38234853744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41848170757294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43844068050385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637585639954</t>
+    <t xml:space="preserve">1.26197361946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25399005413055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771412372589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34291183948517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38234865665436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41848158836365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43844079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637597560883</t>
   </si>
   <si>
     <t xml:space="preserve">1.43155825138092</t>
@@ -3374,19 +3374,19 @@
     <t xml:space="preserve">1.43603193759918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44257020950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4573677778244</t>
+    <t xml:space="preserve">1.44257032871246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45736789703369</t>
   </si>
   <si>
     <t xml:space="preserve">1.45392632484436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45117342472076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44532334804535</t>
+    <t xml:space="preserve">1.45117354393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44532322883606</t>
   </si>
   <si>
     <t xml:space="preserve">1.45358240604401</t>
@@ -3395,22 +3395,22 @@
     <t xml:space="preserve">1.48111212253571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46872365474701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48661816120148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48283290863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51621305942535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50864207744598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51036310195923</t>
+    <t xml:space="preserve">1.4687237739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48661839962006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48283278942108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51621282100677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50864219665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51036298274994</t>
   </si>
   <si>
     <t xml:space="preserve">1.56198155879974</t>
@@ -3419,28 +3419,28 @@
     <t xml:space="preserve">1.56507849693298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55991661548615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56955254077911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55888438224792</t>
+    <t xml:space="preserve">1.55991685390472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56955218315125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55888450145721</t>
   </si>
   <si>
     <t xml:space="preserve">1.57884359359741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59329688549042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61669731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59260857105255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58194077014923</t>
+    <t xml:space="preserve">1.59329676628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61669743061066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59260845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58194065093994</t>
   </si>
   <si>
     <t xml:space="preserve">1.57540249824524</t>
@@ -3449,34 +3449,34 @@
     <t xml:space="preserve">1.57987606525421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57918787002563</t>
+    <t xml:space="preserve">1.57918775081635</t>
   </si>
   <si>
     <t xml:space="preserve">1.58125245571136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57333791255951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59914696216583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59019958972931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59536159038544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58503806591034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55750775337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55096971988678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55578720569611</t>
+    <t xml:space="preserve">1.57333767414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59914672374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5901997089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59536147117615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58503782749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55750799179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55096936225891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5557873249054</t>
   </si>
   <si>
     <t xml:space="preserve">1.56989645957947</t>
@@ -3488,34 +3488,34 @@
     <t xml:space="preserve">1.5320428609848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52860164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58056437969208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5950174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59742641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60637354850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58847916126251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.623579621315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62564480304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64457142353058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63837707042694</t>
+    <t xml:space="preserve">1.52860128879547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58056426048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59501779079437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59742629528046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60637378692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5884792804718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62357985973358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62564468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64457154273987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63837718963623</t>
   </si>
   <si>
     <t xml:space="preserve">1.63975358009338</t>
@@ -3524,13 +3524,13 @@
     <t xml:space="preserve">1.63287115097046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64319515228271</t>
+    <t xml:space="preserve">1.643195271492</t>
   </si>
   <si>
     <t xml:space="preserve">1.65868067741394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65351867675781</t>
+    <t xml:space="preserve">1.6535187959671</t>
   </si>
   <si>
     <t xml:space="preserve">1.65116286277771</t>
@@ -3539,136 +3539,136 @@
     <t xml:space="preserve">1.64976537227631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63928401470184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67282438278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68330574035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6885461807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70881032943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72767698764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73012244701385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73326694965363</t>
+    <t xml:space="preserve">1.63928389549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67282426357269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68330550193787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68854665756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70881021022797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72767686843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73012232780457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73326671123505</t>
   </si>
   <si>
     <t xml:space="preserve">1.73676073551178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71894216537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71440052986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70426857471466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69448566436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71195471286774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71265351772308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68749833106995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63788664340973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65360832214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63648903369904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61832118034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65186178684235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6668848991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62775456905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64662086963654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64592230319977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63229632377625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65535545349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6214656829834</t>
+    <t xml:space="preserve">1.71894228458405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71440041065216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70426845550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69448554515839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71195483207703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7126532793045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68749809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63788652420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65360867977142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63648915290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61832141876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65186166763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66688466072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62775421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64662098884583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6459219455719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63229656219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65535533428192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62146580219269</t>
   </si>
   <si>
     <t xml:space="preserve">1.60958683490753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56242084503174</t>
+    <t xml:space="preserve">1.56242096424103</t>
   </si>
   <si>
     <t xml:space="preserve">1.5959609746933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61098420619965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58617842197418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59631025791168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57639598846436</t>
+    <t xml:space="preserve">1.61098456382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58617854118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59631013870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57639575004578</t>
   </si>
   <si>
     <t xml:space="preserve">1.55962562561035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4935929775238</t>
+    <t xml:space="preserve">1.49359321594238</t>
   </si>
   <si>
     <t xml:space="preserve">1.52259159088135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56277024745941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255256175995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59665989875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63334465026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61657416820526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62111616134644</t>
+    <t xml:space="preserve">1.56277000904083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255280017853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59666013717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63334453105927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61657428741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62111628055573</t>
   </si>
   <si>
     <t xml:space="preserve">1.63998281955719</t>
@@ -3677,13 +3677,13 @@
     <t xml:space="preserve">1.62915217876434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61727321147919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62565815448761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63509130477905</t>
+    <t xml:space="preserve">1.6172730922699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62565839290619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63509142398834</t>
   </si>
   <si>
     <t xml:space="preserve">1.6385852098465</t>
@@ -3695,52 +3695,52 @@
     <t xml:space="preserve">1.68016123771667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68260705471039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71125566959381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71055710315704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69204008579254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66898131370544</t>
+    <t xml:space="preserve">1.68260681629181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71125602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7105575799942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69204032421112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66898107528687</t>
   </si>
   <si>
     <t xml:space="preserve">1.68225765228271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66723418235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66304183006287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67002904415131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66164422035217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67527008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68365478515625</t>
+    <t xml:space="preserve">1.66723430156708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66304159164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67002940177917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66164410114288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6752701997757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68365502357483</t>
   </si>
   <si>
     <t xml:space="preserve">1.66828262805939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67911338806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66548752784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64836764335632</t>
+    <t xml:space="preserve">1.67911326885223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66548764705658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64836776256561</t>
   </si>
   <si>
     <t xml:space="preserve">1.65710246562958</t>
@@ -3752,76 +3752,76 @@
     <t xml:space="preserve">1.66758346557617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66094529628754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65884935855865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60853862762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.622514128685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6581506729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69623255729675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69413626194</t>
+    <t xml:space="preserve">1.66094565391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65884923934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60853886604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62251389026642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65815055370331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69623279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69413638114929</t>
   </si>
   <si>
     <t xml:space="preserve">1.72732722759247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69763028621674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7182434797287</t>
+    <t xml:space="preserve">1.69763004779816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71824359893799</t>
   </si>
   <si>
     <t xml:space="preserve">1.74898886680603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72942340373993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75388014316559</t>
+    <t xml:space="preserve">1.72942364215851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75388026237488</t>
   </si>
   <si>
     <t xml:space="preserve">1.75912082195282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74933803081512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75562739372253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74339866638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76331317424774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79929947853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81100177764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7815637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79319357872009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77720248699188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78192698955536</t>
+    <t xml:space="preserve">1.74933838844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75562715530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74339878559113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76331341266632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79929935932159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81100189685822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78156352043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79319381713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7772022485733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78192687034607</t>
   </si>
   <si>
     <t xml:space="preserve">1.79028618335724</t>
@@ -3830,82 +3830,82 @@
     <t xml:space="preserve">1.80373311042786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78301727771759</t>
+    <t xml:space="preserve">1.78301763534546</t>
   </si>
   <si>
     <t xml:space="preserve">1.77211451530457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78628814220428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81354582309723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82590293884277</t>
+    <t xml:space="preserve">1.78628826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81354606151581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82590281963348</t>
   </si>
   <si>
     <t xml:space="preserve">1.81863403320312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78556156158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80518698692322</t>
+    <t xml:space="preserve">1.78556132316589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80518710613251</t>
   </si>
   <si>
     <t xml:space="preserve">1.81172895431519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79573786258698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80046224594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79682791233063</t>
+    <t xml:space="preserve">1.79573774337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80046236515045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79682779312134</t>
   </si>
   <si>
     <t xml:space="preserve">1.79646444320679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80991184711456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80446028709412</t>
+    <t xml:space="preserve">1.80991160869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80445992946625</t>
   </si>
   <si>
     <t xml:space="preserve">1.80409669876099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73286330699921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74418115615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72544264793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7258175611496</t>
+    <t xml:space="preserve">1.73286306858063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74418151378632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72544288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72581768035889</t>
   </si>
   <si>
     <t xml:space="preserve">1.71494925022125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61638462543488</t>
+    <t xml:space="preserve">1.61638450622559</t>
   </si>
   <si>
     <t xml:space="preserve">1.60626566410065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58565330505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62537908554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60963869094849</t>
+    <t xml:space="preserve">1.58565318584442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62537920475006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60963881015778</t>
   </si>
   <si>
     <t xml:space="preserve">1.60888922214508</t>
@@ -3914,31 +3914,31 @@
     <t xml:space="preserve">1.65873372554779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69246280193329</t>
+    <t xml:space="preserve">1.69246304035187</t>
   </si>
   <si>
     <t xml:space="preserve">1.6722252368927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66772794723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66060757637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65273725986481</t>
+    <t xml:space="preserve">1.66772818565369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66060781478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65273714065552</t>
   </si>
   <si>
     <t xml:space="preserve">1.66735327243805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65011382102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68084514141083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311193466187</t>
+    <t xml:space="preserve">1.65011370182037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68084490299225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311205387115</t>
   </si>
   <si>
     <t xml:space="preserve">1.63549792766571</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">1.67185068130493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.687215924263</t>
+    <t xml:space="preserve">1.68721628189087</t>
   </si>
   <si>
     <t xml:space="preserve">1.69583606719971</t>
@@ -3959,19 +3959,19 @@
     <t xml:space="preserve">1.71157622337341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70670413970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70445561408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75767290592194</t>
+    <t xml:space="preserve">1.70670437812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70445549488068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75767302513123</t>
   </si>
   <si>
     <t xml:space="preserve">1.7944004535675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81238949298859</t>
+    <t xml:space="preserve">1.81238961219788</t>
   </si>
   <si>
     <t xml:space="preserve">1.82363259792328</t>
@@ -3980,19 +3980,19 @@
     <t xml:space="preserve">1.83749890327454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84611880779266</t>
+    <t xml:space="preserve">1.84611868858337</t>
   </si>
   <si>
     <t xml:space="preserve">1.86036014556885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90795612335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91919922828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92032313346863</t>
+    <t xml:space="preserve">1.90795600414276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91919910907745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92032325267792</t>
   </si>
   <si>
     <t xml:space="preserve">1.93194127082825</t>
@@ -4001,28 +4001,28 @@
     <t xml:space="preserve">1.9300674200058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89933609962463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91245317459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9128280878067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84874224662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86560690402985</t>
+    <t xml:space="preserve">1.89933621883392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91245329380035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91282796859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8487423658371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86560666561127</t>
   </si>
   <si>
     <t xml:space="preserve">1.92219734191895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95817506313324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9465571641922</t>
+    <t xml:space="preserve">1.95817530155182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94655728340149</t>
   </si>
   <si>
     <t xml:space="preserve">1.96342194080353</t>
@@ -4034,34 +4034,34 @@
     <t xml:space="preserve">2.02151131629944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04474711418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99902546405792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0350034236908</t>
+    <t xml:space="preserve">2.04474687576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99902534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03500318527222</t>
   </si>
   <si>
     <t xml:space="preserve">2.07585310935974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13881421089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18865895271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07435417175293</t>
+    <t xml:space="preserve">2.1388144493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18865871429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07435369491577</t>
   </si>
   <si>
     <t xml:space="preserve">2.13843989372253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09196805953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05299210548401</t>
+    <t xml:space="preserve">2.09196782112122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05299186706543</t>
   </si>
   <si>
     <t xml:space="preserve">2.04024958610535</t>
@@ -4070,37 +4070,37 @@
     <t xml:space="preserve">2.00427198410034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99377834796906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96417164802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80789232254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85698711872101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7190717458725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58640277385712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60851442813873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56204295158386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42127907276154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38155341148376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39834332466125</t>
+    <t xml:space="preserve">1.99377822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9641717672348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80789196491241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8569872379303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71907162666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58640313148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60851418972015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56204283237457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42127895355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38155329227448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39834308624268</t>
   </si>
   <si>
     <t xml:space="preserve">1.55342316627502</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">1.4352205991745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43866848945618</t>
+    <t xml:space="preserve">1.43866837024689</t>
   </si>
   <si>
     <t xml:space="preserve">1.49158608913422</t>
@@ -4118,7 +4118,7 @@
     <t xml:space="preserve">1.50507760047913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61001348495483</t>
+    <t xml:space="preserve">1.61001360416412</t>
   </si>
   <si>
     <t xml:space="preserve">1.55304837226868</t>
@@ -4127,13 +4127,13 @@
     <t xml:space="preserve">1.56354200839996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54892599582672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57403528690338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53505957126617</t>
+    <t xml:space="preserve">1.54892587661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57403540611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53505945205688</t>
   </si>
   <si>
     <t xml:space="preserve">1.5223171710968</t>
@@ -4142,22 +4142,22 @@
     <t xml:space="preserve">1.5238162279129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53243625164032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61975765228271</t>
+    <t xml:space="preserve">1.53243613243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61975741386414</t>
   </si>
   <si>
     <t xml:space="preserve">1.59951984882355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5616682767868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57778310775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57028770446777</t>
+    <t xml:space="preserve">1.56166815757751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57778322696686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57028782367706</t>
   </si>
   <si>
     <t xml:space="preserve">1.53056228160858</t>
@@ -4166,16 +4166,16 @@
     <t xml:space="preserve">1.48573958873749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46280372142792</t>
+    <t xml:space="preserve">1.46280348300934</t>
   </si>
   <si>
     <t xml:space="preserve">1.48558974266052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48469030857086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45500838756561</t>
+    <t xml:space="preserve">1.48469018936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4550085067749</t>
   </si>
   <si>
     <t xml:space="preserve">1.4572571516037</t>
@@ -4184,19 +4184,19 @@
     <t xml:space="preserve">1.47734463214874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47884380817413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51444697380066</t>
+    <t xml:space="preserve">1.47884392738342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51444709300995</t>
   </si>
   <si>
     <t xml:space="preserve">1.5178200006485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48618948459625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46055495738983</t>
+    <t xml:space="preserve">1.48618936538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46055519580841</t>
   </si>
   <si>
     <t xml:space="preserve">1.43761909008026</t>
@@ -4211,31 +4211,31 @@
     <t xml:space="preserve">1.46520221233368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44091701507568</t>
+    <t xml:space="preserve">1.44091713428497</t>
   </si>
   <si>
     <t xml:space="preserve">1.4692497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44301569461823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44256591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40913653373718</t>
+    <t xml:space="preserve">1.44301581382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44256603717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40913641452789</t>
   </si>
   <si>
     <t xml:space="preserve">1.37165951728821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39534509181976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45410895347595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47074890136719</t>
+    <t xml:space="preserve">1.39534497261047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45410907268524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4707487821579</t>
   </si>
   <si>
     <t xml:space="preserve">1.47839415073395</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">1.49188590049744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49008703231812</t>
+    <t xml:space="preserve">1.49008691310883</t>
   </si>
   <si>
     <t xml:space="preserve">1.48633933067322</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">1.54183995723724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54496228694916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58695840835571</t>
+    <t xml:space="preserve">1.54496216773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.586958527565</t>
   </si>
   <si>
     <t xml:space="preserve">1.60139966011047</t>
@@ -4271,43 +4271,43 @@
     <t xml:space="preserve">1.6076443195343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58500695228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56119883060455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54012250900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59047102928162</t>
+    <t xml:space="preserve">1.58500683307648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56119871139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54012262821198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5904712677002</t>
   </si>
   <si>
     <t xml:space="preserve">1.5631502866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55339276790619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53528273105621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42193984985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3730742931366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38166093826294</t>
+    <t xml:space="preserve">1.5533926486969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5352828502655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42193961143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37307417392731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38166081905365</t>
   </si>
   <si>
     <t xml:space="preserve">1.44520175457001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39961457252502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40788900852203</t>
+    <t xml:space="preserve">1.3996148109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40788888931274</t>
   </si>
   <si>
     <t xml:space="preserve">1.46175038814545</t>
@@ -4322,49 +4322,49 @@
     <t xml:space="preserve">1.43630290031433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46924424171448</t>
+    <t xml:space="preserve">1.4692440032959</t>
   </si>
   <si>
     <t xml:space="preserve">1.47798681259155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48204600811005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46440434455872</t>
+    <t xml:space="preserve">1.48204588890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46440446376801</t>
   </si>
   <si>
     <t xml:space="preserve">1.38946676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37978732585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34669017791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30469357967377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31000185012817</t>
+    <t xml:space="preserve">1.37978756427765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34669005870819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30469369888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31000173091888</t>
   </si>
   <si>
     <t xml:space="preserve">1.36230206489563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37588441371918</t>
+    <t xml:space="preserve">1.37588429450989</t>
   </si>
   <si>
     <t xml:space="preserve">1.35199809074402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33295154571533</t>
+    <t xml:space="preserve">1.33295142650604</t>
   </si>
   <si>
     <t xml:space="preserve">1.32764339447021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25411081314087</t>
+    <t xml:space="preserve">1.25411117076874</t>
   </si>
   <si>
     <t xml:space="preserve">1.27393817901611</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">1.38369047641754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33513724803925</t>
+    <t xml:space="preserve">1.33513712882996</t>
   </si>
   <si>
     <t xml:space="preserve">1.29813671112061</t>
@@ -4391,55 +4391,55 @@
     <t xml:space="preserve">1.29329705238342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3092212677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3315464258194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34934413433075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36542439460754</t>
+    <t xml:space="preserve">1.30922114849091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33154654502869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34934401512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36542427539825</t>
   </si>
   <si>
     <t xml:space="preserve">1.36370706558228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38462722301483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39180874824524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41600728034973</t>
+    <t xml:space="preserve">1.38462710380554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39180862903595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41600739955902</t>
   </si>
   <si>
     <t xml:space="preserve">1.41850507259369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4175683259964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43052637577057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44707524776459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44785559177399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42740404605865</t>
+    <t xml:space="preserve">1.41756856441498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43052649497986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44707500934601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44785583019257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42740392684937</t>
   </si>
   <si>
     <t xml:space="preserve">1.42615509033203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38415884971619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34138178825378</t>
+    <t xml:space="preserve">1.38415896892548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34138190746307</t>
   </si>
   <si>
     <t xml:space="preserve">1.36573660373688</t>
@@ -4448,25 +4448,25 @@
     <t xml:space="preserve">1.37666499614716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35699391365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31530976295471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32811176776886</t>
+    <t xml:space="preserve">1.35699379444122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.315309882164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32811188697815</t>
   </si>
   <si>
     <t xml:space="preserve">1.34996855258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34497261047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32217907905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35683786869049</t>
+    <t xml:space="preserve">1.34497272968292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32217919826508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3568377494812</t>
   </si>
   <si>
     <t xml:space="preserve">1.32467710971832</t>
@@ -4478,16 +4478,16 @@
     <t xml:space="preserve">1.32701897621155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35855519771576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43099462985992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48001635074615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46846342086792</t>
+    <t xml:space="preserve">1.35855507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43099474906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48001646995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4684636592865</t>
   </si>
   <si>
     <t xml:space="preserve">1.48329496383667</t>
@@ -4499,7 +4499,7 @@
     <t xml:space="preserve">1.49484777450562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49516022205353</t>
+    <t xml:space="preserve">1.49515998363495</t>
   </si>
   <si>
     <t xml:space="preserve">1.44348430633545</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">1.43364882469177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44566988945007</t>
+    <t xml:space="preserve">1.44567000865936</t>
   </si>
   <si>
     <t xml:space="preserve">1.37697732448578</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">1.35917961597443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33654236793518</t>
+    <t xml:space="preserve">1.33654224872589</t>
   </si>
   <si>
     <t xml:space="preserve">1.33139026165009</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">1.30781614780426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33201479911804</t>
+    <t xml:space="preserve">1.33201467990875</t>
   </si>
   <si>
     <t xml:space="preserve">1.33669817447662</t>
@@ -4562,40 +4562,40 @@
     <t xml:space="preserve">1.40726459026337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39852178096771</t>
+    <t xml:space="preserve">1.398521900177</t>
   </si>
   <si>
     <t xml:space="preserve">1.42771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42662334442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44863629341125</t>
+    <t xml:space="preserve">1.42662346363068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44863617420197</t>
   </si>
   <si>
     <t xml:space="preserve">1.45550549030304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45644223690033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48766624927521</t>
+    <t xml:space="preserve">1.45644235610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4876663684845</t>
   </si>
   <si>
     <t xml:space="preserve">1.48719787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50577628612518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51842176914215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51810944080353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53746843338013</t>
+    <t xml:space="preserve">1.50577616691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51842188835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51810956001282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53746855258942</t>
   </si>
   <si>
     <t xml:space="preserve">1.61193764209747</t>
@@ -4604,46 +4604,46 @@
     <t xml:space="preserve">1.66189587116241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67672741413116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68141102790833</t>
+    <t xml:space="preserve">1.67672753334045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6814112663269</t>
   </si>
   <si>
     <t xml:space="preserve">1.69936490058899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68648481369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678055286407</t>
+    <t xml:space="preserve">1.68648493289948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678067207336</t>
   </si>
   <si>
     <t xml:space="preserve">1.70951271057129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70990288257599</t>
+    <t xml:space="preserve">1.70990300178528</t>
   </si>
   <si>
     <t xml:space="preserve">1.70014536380768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7301983833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72882580757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74457168579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73165190219879</t>
+    <t xml:space="preserve">1.73019850254059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7288259267807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74457180500031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73165202140808</t>
   </si>
   <si>
     <t xml:space="preserve">1.7441680431366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74295687675476</t>
+    <t xml:space="preserve">1.74295663833618</t>
   </si>
   <si>
     <t xml:space="preserve">1.70863842964172</t>
@@ -4655,13 +4655,13 @@
     <t xml:space="preserve">1.71348345279694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68320286273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69289255142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67835795879364</t>
+    <t xml:space="preserve">1.68320310115814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69289267063141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67835807800293</t>
   </si>
   <si>
     <t xml:space="preserve">1.66866815090179</t>
@@ -4673,37 +4673,37 @@
     <t xml:space="preserve">1.66140079498291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66907179355621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67028319835663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6965264081955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68562543392181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61044859886169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66180455684662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64282846450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67593562602997</t>
+    <t xml:space="preserve">1.6690719127655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67028307914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69652652740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68562531471252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61044836044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66180443763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64282858371735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67593538761139</t>
   </si>
   <si>
     <t xml:space="preserve">1.69612264633179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68279922008514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68966269493103</t>
+    <t xml:space="preserve">1.68279910087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68966257572174</t>
   </si>
   <si>
     <t xml:space="preserve">1.68118417263031</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">1.70137143135071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67795431613922</t>
+    <t xml:space="preserve">1.67795419692993</t>
   </si>
   <si>
     <t xml:space="preserve">1.71429097652435</t>
@@ -4724,10 +4724,10 @@
     <t xml:space="preserve">1.75426137447357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79948055744171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78857946395874</t>
+    <t xml:space="preserve">1.79948079586029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78857958316803</t>
   </si>
   <si>
     <t xml:space="preserve">1.8035181760788</t>
@@ -4739,67 +4739,67 @@
     <t xml:space="preserve">1.82451272010803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84429609775543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8475261926651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84510385990143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82572388648987</t>
+    <t xml:space="preserve">1.84429633617401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84752607345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84510374069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82572400569916</t>
   </si>
   <si>
     <t xml:space="preserve">1.79503953456879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76072132587433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80836319923401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84550726413727</t>
+    <t xml:space="preserve">1.76072156429291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80836308002472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84550738334656</t>
   </si>
   <si>
     <t xml:space="preserve">1.85317850112915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89153397083282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.898397564888</t>
+    <t xml:space="preserve">1.89153373241425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89839780330658</t>
   </si>
   <si>
     <t xml:space="preserve">1.89274549484253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94603931903839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98076105117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98237609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423701286316</t>
+    <t xml:space="preserve">1.94603943824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98076117038727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98237597942352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423725128174</t>
   </si>
   <si>
     <t xml:space="preserve">1.97591614723206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99327719211578</t>
+    <t xml:space="preserve">1.9932769536972</t>
   </si>
   <si>
     <t xml:space="preserve">1.99368095397949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02194285392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00014090538025</t>
+    <t xml:space="preserve">2.02194261550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00014066696167</t>
   </si>
   <si>
     <t xml:space="preserve">2.01790547370911</t>
@@ -4817,13 +4817,13 @@
     <t xml:space="preserve">2.07079601287842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06231713294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06150984764099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99973690509796</t>
+    <t xml:space="preserve">2.06231737136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06150960922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99973702430725</t>
   </si>
   <si>
     <t xml:space="preserve">2.03001761436462</t>
@@ -4832,10 +4832,10 @@
     <t xml:space="preserve">2.04535984992981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06837344169617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04858994483948</t>
+    <t xml:space="preserve">2.06837320327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0485897064209</t>
   </si>
   <si>
     <t xml:space="preserve">2.05262756347656</t>
@@ -4847,52 +4847,52 @@
     <t xml:space="preserve">2.0934054851532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07119965553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0772557258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04414892196655</t>
+    <t xml:space="preserve">2.07119941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07725548744202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04414916038513</t>
   </si>
   <si>
     <t xml:space="preserve">2.00417828559875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88184404373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94482779502869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8115930557251</t>
+    <t xml:space="preserve">1.8818439245224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94482803344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81159293651581</t>
   </si>
   <si>
     <t xml:space="preserve">1.81522655487061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77081501483917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83702874183655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90162754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89193773269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255799770355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82733881473541</t>
+    <t xml:space="preserve">1.77081525325775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83702886104584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90162765979767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89193785190582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87255835533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82733905315399</t>
   </si>
   <si>
     <t xml:space="preserve">1.83420264720917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8519674539566</t>
+    <t xml:space="preserve">1.85196733474731</t>
   </si>
   <si>
     <t xml:space="preserve">1.87982559204102</t>
@@ -4901,106 +4901,106 @@
     <t xml:space="preserve">1.90970242023468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91172111034393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86448335647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90404999256134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91939210891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93433058261871</t>
+    <t xml:space="preserve">1.9117214679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86448323726654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90405023097992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9193924665451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.934330701828</t>
   </si>
   <si>
     <t xml:space="preserve">1.92827463150024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97147512435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00094842910767</t>
+    <t xml:space="preserve">1.97147488594055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00094819068909</t>
   </si>
   <si>
     <t xml:space="preserve">2.01750183105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01023435592651</t>
+    <t xml:space="preserve">2.01023459434509</t>
   </si>
   <si>
     <t xml:space="preserve">2.00619697570801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02436518669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98722100257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9654186964035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98479843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92544853687286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88022899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91293263435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395666122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96380388736725</t>
+    <t xml:space="preserve">2.02436542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98722112178802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96541905403137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98479866981506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.925448179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88022935390472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91293239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89395642280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96380412578583</t>
   </si>
   <si>
     <t xml:space="preserve">1.98883605003357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98358714580536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9504805803299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93917572498322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96057415008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9545179605484</t>
+    <t xml:space="preserve">1.98358738422394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95048034191132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93917560577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96057391166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95451807975769</t>
   </si>
   <si>
     <t xml:space="preserve">1.94038701057434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92948591709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95128798484802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96353387832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96437239646912</t>
+    <t xml:space="preserve">1.9294855594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95128786563873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96353375911713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9643726348877</t>
   </si>
   <si>
     <t xml:space="preserve">1.88888442516327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88804543018341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88301277160645</t>
+    <t xml:space="preserve">1.8880455493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88301301002502</t>
   </si>
   <si>
     <t xml:space="preserve">1.86665725708008</t>
@@ -5009,43 +5009,43 @@
     <t xml:space="preserve">1.85365641117096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80794417858124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87043154239655</t>
+    <t xml:space="preserve">1.80794405937195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87043166160583</t>
   </si>
   <si>
     <t xml:space="preserve">1.90524017810822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89475572109222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91698265075684</t>
+    <t xml:space="preserve">1.89475560188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91698276996613</t>
   </si>
   <si>
     <t xml:space="preserve">1.9316611289978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94927477836609</t>
+    <t xml:space="preserve">1.94927489757538</t>
   </si>
   <si>
     <t xml:space="preserve">1.93711280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93417739868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93920993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97108244895935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97779262065887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99037408828735</t>
+    <t xml:space="preserve">1.93417716026306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93921005725861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97108268737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97779285907745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99037396907806</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840735435486</t>
@@ -5057,22 +5057,22 @@
     <t xml:space="preserve">2.01805305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99540662765503</t>
+    <t xml:space="preserve">1.99540638923645</t>
   </si>
   <si>
     <t xml:space="preserve">1.95850133895874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95598483085632</t>
+    <t xml:space="preserve">1.9559850692749</t>
   </si>
   <si>
     <t xml:space="preserve">1.98072838783264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98240578174591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00127792358398</t>
+    <t xml:space="preserve">1.9824059009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00127768516541</t>
   </si>
   <si>
     <t xml:space="preserve">2.01302075386047</t>
@@ -5081,79 +5081,79 @@
     <t xml:space="preserve">2.04405474662781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03021502494812</t>
+    <t xml:space="preserve">2.0302152633667</t>
   </si>
   <si>
     <t xml:space="preserve">2.02056932449341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96311438083649</t>
+    <t xml:space="preserve">1.96311461925507</t>
   </si>
   <si>
     <t xml:space="preserve">1.97024381160736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97695410251617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99666464328766</t>
+    <t xml:space="preserve">1.97695422172546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99666500091553</t>
   </si>
   <si>
     <t xml:space="preserve">2.01973056793213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04992604255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03860259056091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04237723350525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837892532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09018659591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11534905433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12289786338806</t>
+    <t xml:space="preserve">2.04992628097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03860282897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04237699508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837868690491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09018635749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11534929275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12289762496948</t>
   </si>
   <si>
     <t xml:space="preserve">2.12709164619446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12960815429688</t>
+    <t xml:space="preserve">2.1296079158783</t>
   </si>
   <si>
     <t xml:space="preserve">2.15812587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18874025344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20509648323059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18832087516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14973831176758</t>
+    <t xml:space="preserve">2.18874049186707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20509624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18832111358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.149738073349</t>
   </si>
   <si>
     <t xml:space="preserve">2.13506007194519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13338232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14722180366516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96101760864258</t>
+    <t xml:space="preserve">2.13338255882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14722204208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96101784706116</t>
   </si>
   <si>
     <t xml:space="preserve">2.0067298412323</t>
@@ -5168,10 +5168,10 @@
     <t xml:space="preserve">2.05076456069946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03734421730042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02937650680542</t>
+    <t xml:space="preserve">2.03734469413757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02937626838684</t>
   </si>
   <si>
     <t xml:space="preserve">2.02224707603455</t>
@@ -5180,34 +5180,34 @@
     <t xml:space="preserve">2.04573202133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06292700767517</t>
+    <t xml:space="preserve">2.06292676925659</t>
   </si>
   <si>
     <t xml:space="preserve">2.05915212631226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0532808303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453896522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07760500907898</t>
+    <t xml:space="preserve">2.05328106880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0545392036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0776047706604</t>
   </si>
   <si>
     <t xml:space="preserve">2.09060573577881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09857392311096</t>
+    <t xml:space="preserve">2.09857416152954</t>
   </si>
   <si>
     <t xml:space="preserve">2.073410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05873274803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05202269554138</t>
+    <t xml:space="preserve">2.0587329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05202293395996</t>
   </si>
   <si>
     <t xml:space="preserve">2.00589108467102</t>
@@ -5222,25 +5222,25 @@
     <t xml:space="preserve">2.08012127876282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07634711265564</t>
+    <t xml:space="preserve">2.07634687423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.06544303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07592749595642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07089519500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03818345069885</t>
+    <t xml:space="preserve">2.07592725753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07089495658875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03818321228027</t>
   </si>
   <si>
     <t xml:space="preserve">2.04782891273499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10821962356567</t>
+    <t xml:space="preserve">2.10821938514709</t>
   </si>
   <si>
     <t xml:space="preserve">2.09102535247803</t>
@@ -5249,73 +5249,73 @@
     <t xml:space="preserve">2.06418490409851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03482842445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0323121547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04657101631165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9815673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98282539844513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01427888870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99330973625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03398966789246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04908752441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05286145210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02686023712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03650593757629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99205148220062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96605014801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99079346656799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97611498832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98785769939423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9941486120224</t>
+    <t xml:space="preserve">2.03482818603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03231191635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04657077789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98156702518463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98282551765442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01427865028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99330961704254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03398942947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04908728599548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05286169052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.026859998703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03650569915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99205160140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96605026721954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99079370498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97611510753632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98785781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99414849281311</t>
   </si>
   <si>
     <t xml:space="preserve">2.06041049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08934736251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11702656745911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15015745162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15225458145142</t>
+    <t xml:space="preserve">2.08934760093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11702632904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15015769004822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15225434303284</t>
   </si>
   <si>
     <t xml:space="preserve">2.15057682991028</t>
@@ -5324,22 +5324,22 @@
     <t xml:space="preserve">2.15435147285461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16231966018677</t>
+    <t xml:space="preserve">2.16231942176819</t>
   </si>
   <si>
     <t xml:space="preserve">2.18286919593811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20551538467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21893572807312</t>
+    <t xml:space="preserve">2.20551562309265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21893548965454</t>
   </si>
   <si>
     <t xml:space="preserve">2.21977472305298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25164747238159</t>
+    <t xml:space="preserve">2.25164699554443</t>
   </si>
   <si>
     <t xml:space="preserve">2.27114582061768</t>
@@ -5360,22 +5360,22 @@
     <t xml:space="preserve">2.30438232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.326096534729</t>
+    <t xml:space="preserve">2.32609677314758</t>
   </si>
   <si>
     <t xml:space="preserve">2.34559535980225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34116363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36287784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38858079910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37838840484619</t>
+    <t xml:space="preserve">2.34116387367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36287808418274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3885805606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37838864326477</t>
   </si>
   <si>
     <t xml:space="preserve">2.39788699150085</t>
@@ -5402,7 +5402,7 @@
     <t xml:space="preserve">2.33540272712708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32653951644897</t>
+    <t xml:space="preserve">2.32653975486755</t>
   </si>
   <si>
     <t xml:space="preserve">2.35046982765198</t>
@@ -5411,7 +5411,7 @@
     <t xml:space="preserve">2.3371753692627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33097147941589</t>
+    <t xml:space="preserve">2.33097124099731</t>
   </si>
   <si>
     <t xml:space="preserve">2.3460385799408</t>
@@ -5441,13 +5441,13 @@
     <t xml:space="preserve">2.47765421867371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44353127479553</t>
+    <t xml:space="preserve">2.44353151321411</t>
   </si>
   <si>
     <t xml:space="preserve">2.43599796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41694259643555</t>
+    <t xml:space="preserve">2.41694235801697</t>
   </si>
   <si>
     <t xml:space="preserve">2.41339731216431</t>
@@ -5462,13 +5462,13 @@
     <t xml:space="preserve">2.43732738494873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44220185279846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45328068733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45682597160339</t>
+    <t xml:space="preserve">2.44220209121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45328044891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45682621002197</t>
   </si>
   <si>
     <t xml:space="preserve">2.51221990585327</t>
@@ -5492,7 +5492,7 @@
     <t xml:space="preserve">2.48430132865906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48164248466492</t>
+    <t xml:space="preserve">2.48164224624634</t>
   </si>
   <si>
     <t xml:space="preserve">2.53969502449036</t>
@@ -5516,19 +5516,19 @@
     <t xml:space="preserve">2.4869601726532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49538016319275</t>
+    <t xml:space="preserve">2.49538040161133</t>
   </si>
   <si>
     <t xml:space="preserve">2.50690221786499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50379991531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51620817184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52551436424255</t>
+    <t xml:space="preserve">2.5038001537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5162079334259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52551412582397</t>
   </si>
   <si>
     <t xml:space="preserve">2.55742120742798</t>
@@ -5537,7 +5537,7 @@
     <t xml:space="preserve">2.5671706199646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60483813285828</t>
+    <t xml:space="preserve">2.6048378944397</t>
   </si>
   <si>
     <t xml:space="preserve">2.61857581138611</t>
@@ -5570,16 +5570,16 @@
     <t xml:space="preserve">2.74974846839905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72183012962341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78475737571716</t>
+    <t xml:space="preserve">2.72182989120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78475713729858</t>
   </si>
   <si>
     <t xml:space="preserve">2.82109570503235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81046009063721</t>
+    <t xml:space="preserve">2.81045985221863</t>
   </si>
   <si>
     <t xml:space="preserve">2.86053609848022</t>
@@ -5600,19 +5600,19 @@
     <t xml:space="preserve">2.92036151885986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94384837150574</t>
+    <t xml:space="preserve">2.94384860992432</t>
   </si>
   <si>
     <t xml:space="preserve">2.96511960029602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96733546257019</t>
+    <t xml:space="preserve">2.96733522415161</t>
   </si>
   <si>
     <t xml:space="preserve">2.98062992095947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96689224243164</t>
+    <t xml:space="preserve">2.96689248085022</t>
   </si>
   <si>
     <t xml:space="preserve">3.01608180999756</t>
@@ -5639,16 +5639,16 @@
     <t xml:space="preserve">2.91592979431152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94828009605408</t>
+    <t xml:space="preserve">2.9482798576355</t>
   </si>
   <si>
     <t xml:space="preserve">2.88225054740906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92390656471252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96866488456726</t>
+    <t xml:space="preserve">2.9239068031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96866464614868</t>
   </si>
   <si>
     <t xml:space="preserve">2.99303817749023</t>
@@ -5681,22 +5681,22 @@
     <t xml:space="preserve">3.06837344169617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15789008140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18935370445251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18492221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17251420021057</t>
+    <t xml:space="preserve">3.15788984298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18935394287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18492197990417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17251396179199</t>
   </si>
   <si>
     <t xml:space="preserve">3.19112634658813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21417021751404</t>
+    <t xml:space="preserve">3.21416997909546</t>
   </si>
   <si>
     <t xml:space="preserve">3.2819721698761</t>
@@ -6741,6 +6741,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.38399982452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46999979019165</t>
   </si>
 </sst>
 </file>
@@ -71793,7 +71796,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6513078704</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>44190749</v>
@@ -71814,6 +71817,32 @@
         <v>2242</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6505208333</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>36885509</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>5.46400022506714</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>5.3769998550415</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>5.40899991989136</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>5.46999979019165</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>2243</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISP.MI.xlsx
+++ b/data/ISP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="2245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="2246">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">1.51831996440887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49265539646149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48752248287201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4669908285141</t>
+    <t xml:space="preserve">1.49265515804291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48752224445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46699059009552</t>
   </si>
   <si>
     <t xml:space="preserve">1.49676167964935</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">1.52447950839996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4854691028595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43824625015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36638522148132</t>
+    <t xml:space="preserve">1.48546922206879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43824636936188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36638510227203</t>
   </si>
   <si>
     <t xml:space="preserve">1.38075745105743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30479001998901</t>
+    <t xml:space="preserve">1.3047901391983</t>
   </si>
   <si>
     <t xml:space="preserve">1.36843836307526</t>
@@ -86,94 +86,94 @@
     <t xml:space="preserve">1.39307653903961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35406637191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3725448846817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35919916629791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29041767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380030632019</t>
+    <t xml:space="preserve">1.35406613349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37254464626312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35919892787933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29041814804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380042552948</t>
   </si>
   <si>
     <t xml:space="preserve">1.31505608558655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26988625526428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20315802097321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27296590805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22368991374969</t>
+    <t xml:space="preserve">1.26988613605499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2031581401825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27296614646912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">1.17441380023956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10152614116669</t>
+    <t xml:space="preserve">1.10152626037598</t>
   </si>
   <si>
     <t xml:space="preserve">1.26064693927765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22984945774078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25243437290192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28220522403717</t>
+    <t xml:space="preserve">1.22984933853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25243425369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28220510482788</t>
   </si>
   <si>
     <t xml:space="preserve">1.21958339214325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19494545459747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23395574092865</t>
+    <t xml:space="preserve">1.19494569301605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23395586013794</t>
   </si>
   <si>
     <t xml:space="preserve">1.20110487937927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16004168987274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18057310581207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20007848739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20213162899017</t>
+    <t xml:space="preserve">1.16004145145416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18057322502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20007836818695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20213150978088</t>
   </si>
   <si>
     <t xml:space="preserve">1.22471642494202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27091288566589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32224214076996</t>
+    <t xml:space="preserve">1.27091264724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32224178314209</t>
   </si>
   <si>
     <t xml:space="preserve">1.29555070400238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26475322246552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27604579925537</t>
+    <t xml:space="preserve">1.26475346088409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27604568004608</t>
   </si>
   <si>
     <t xml:space="preserve">1.29144442081451</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">1.30581665039062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40334248542786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37459790706635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36022555828094</t>
+    <t xml:space="preserve">1.40334224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37459778785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36022579669952</t>
   </si>
   <si>
     <t xml:space="preserve">1.33045482635498</t>
@@ -203,31 +203,31 @@
     <t xml:space="preserve">1.29247105121613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25756728649139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23600876331329</t>
+    <t xml:space="preserve">1.2575671672821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23600900173187</t>
   </si>
   <si>
     <t xml:space="preserve">1.24935448169708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24114167690277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18673300743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13540327548981</t>
+    <t xml:space="preserve">1.24114191532135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21753025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18673276901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13540363311768</t>
   </si>
   <si>
     <t xml:space="preserve">1.1487489938736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11076545715332</t>
+    <t xml:space="preserve">1.11076557636261</t>
   </si>
   <si>
     <t xml:space="preserve">1.17749357223511</t>
@@ -236,43 +236,43 @@
     <t xml:space="preserve">1.19802522659302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2442215681076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25038111209869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25654077529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26269996166229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24216830730438</t>
+    <t xml:space="preserve">1.24422144889832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2503809928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25654053688049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26270020008087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24216842651367</t>
   </si>
   <si>
     <t xml:space="preserve">1.2780989408493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2319028377533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26680648326874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26783299446106</t>
+    <t xml:space="preserve">1.23190259933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26680672168732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26783311367035</t>
   </si>
   <si>
     <t xml:space="preserve">1.18878602981567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16209447383881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13950991630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14258968830109</t>
+    <t xml:space="preserve">1.16209483146667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13951003551483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14258980751038</t>
   </si>
   <si>
     <t xml:space="preserve">1.1497757434845</t>
@@ -287,103 +287,103 @@
     <t xml:space="preserve">1.14156305789948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12924420833588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12103152275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15080237388611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17852020263672</t>
+    <t xml:space="preserve">1.12924408912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12103140354156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15080225467682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17852008342743</t>
   </si>
   <si>
     <t xml:space="preserve">1.18775928020477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18666660785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25878429412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28719437122345</t>
+    <t xml:space="preserve">1.18666672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25878465175629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28719460964203</t>
   </si>
   <si>
     <t xml:space="preserve">1.2970290184021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26096987724304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24020886421204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23037445545197</t>
+    <t xml:space="preserve">1.26096975803375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24020862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23037457466125</t>
   </si>
   <si>
     <t xml:space="preserve">1.20852041244507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20414960384369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22491109371185</t>
+    <t xml:space="preserve">1.20414972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22491097450256</t>
   </si>
   <si>
     <t xml:space="preserve">1.21070599555969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1997789144516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15060758590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0828605890274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04516279697418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07466530799866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06537735462189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1145486831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14842224121094</t>
+    <t xml:space="preserve">1.19977915287018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15060782432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08286070823669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04516267776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07466542720795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06537759304047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11454892158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14842236042023</t>
   </si>
   <si>
     <t xml:space="preserve">1.17683231830597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17573964595795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23365247249603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950644671916962</t>
+    <t xml:space="preserve">1.17573952674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23365259170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950644612312317</t>
   </si>
   <si>
     <t xml:space="preserve">0.846838474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887268304824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900380492210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929883360862732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917863667011261</t>
+    <t xml:space="preserve">0.88726806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900380611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929883480072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917863726615906</t>
   </si>
   <si>
     <t xml:space="preserve">0.88999992609024</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">0.870331585407257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868692398071289</t>
+    <t xml:space="preserve">0.868692457675934</t>
   </si>
   <si>
     <t xml:space="preserve">0.874155938625336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961571455001831</t>
+    <t xml:space="preserve">0.961571574211121</t>
   </si>
   <si>
     <t xml:space="preserve">0.983425438404083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04789447784424</t>
+    <t xml:space="preserve">1.04789435863495</t>
   </si>
   <si>
     <t xml:space="preserve">1.03587472438812</t>
@@ -413,22 +413,22 @@
     <t xml:space="preserve">1.05772864818573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05499696731567</t>
+    <t xml:space="preserve">1.05499684810638</t>
   </si>
   <si>
     <t xml:space="preserve">1.05718231201172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05062639713287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06373858451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0670166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06865549087524</t>
+    <t xml:space="preserve">1.05062627792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06373870372772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06701636314392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06865561008453</t>
   </si>
   <si>
     <t xml:space="preserve">1.04898703098297</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">1.05335772037506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0719336271286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03969919681549</t>
+    <t xml:space="preserve">1.07193374633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03969931602478</t>
   </si>
   <si>
     <t xml:space="preserve">1.07630443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03860640525818</t>
+    <t xml:space="preserve">1.03860676288605</t>
   </si>
   <si>
     <t xml:space="preserve">0.999269485473633</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">0.993806004524231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994352519512177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03806018829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05117225646973</t>
+    <t xml:space="preserve">0.994352340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03805994987488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05117249488831</t>
   </si>
   <si>
     <t xml:space="preserve">1.0560896396637</t>
@@ -473,67 +473,67 @@
     <t xml:space="preserve">1.05827498435974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03041124343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00965023040771</t>
+    <t xml:space="preserve">1.03041136264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00964999198914</t>
   </si>
   <si>
     <t xml:space="preserve">1.05991411209106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09214854240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08231437206268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10034358501434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08996319770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11673402786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16372013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19759368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19212996959686</t>
+    <t xml:space="preserve">1.09214842319489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08231449127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10034370422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08996307849884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11673414707184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1637202501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19759345054626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19213008880615</t>
   </si>
   <si>
     <t xml:space="preserve">1.16809093952179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17901790142059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1833883523941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15934920310974</t>
+    <t xml:space="preserve">1.17901802062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18338859081268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15934932231903</t>
   </si>
   <si>
     <t xml:space="preserve">1.13749527931213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1364027261734</t>
+    <t xml:space="preserve">1.13640260696411</t>
   </si>
   <si>
     <t xml:space="preserve">1.12766098976135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09706556797028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11236333847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12656855583191</t>
+    <t xml:space="preserve">1.09706568717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11236321926117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12656843662262</t>
   </si>
   <si>
     <t xml:space="preserve">1.09050953388214</t>
@@ -542,28 +542,28 @@
     <t xml:space="preserve">1.0779435634613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06428468227386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06155288219452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06319200992584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07848989963531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05445039272308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08941686153412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09378755092621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07685077190399</t>
+    <t xml:space="preserve">1.06428480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06155300140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06319212913513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0784900188446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05445051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08941662311554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0937876701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07685089111328</t>
   </si>
   <si>
     <t xml:space="preserve">1.08340704441071</t>
@@ -572,25 +572,25 @@
     <t xml:space="preserve">1.12329030036926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13093912601471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.151700258255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15388596057892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17792499065399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196449756622</t>
+    <t xml:space="preserve">1.130939245224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15170037746429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15388584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17792522907257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196437835693</t>
   </si>
   <si>
     <t xml:space="preserve">1.18229591846466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15279304981232</t>
+    <t xml:space="preserve">1.15279293060303</t>
   </si>
   <si>
     <t xml:space="preserve">1.13858807086945</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">1.09597301483154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16044199466705</t>
+    <t xml:space="preserve">1.16044223308563</t>
   </si>
   <si>
     <t xml:space="preserve">1.16918361186981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22054028511047</t>
+    <t xml:space="preserve">1.22054016590118</t>
   </si>
   <si>
     <t xml:space="preserve">1.21835494041443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15497875213623</t>
+    <t xml:space="preserve">1.15497851371765</t>
   </si>
   <si>
     <t xml:space="preserve">1.1418662071228</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">1.11891949176788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10362184047699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06810939311981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11345624923706</t>
+    <t xml:space="preserve">1.10362195968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06810927391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11345601081848</t>
   </si>
   <si>
     <t xml:space="preserve">1.14514422416687</t>
@@ -638,73 +638,73 @@
     <t xml:space="preserve">1.24567198753357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26643311977386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30904853343964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27845287322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3276242017746</t>
+    <t xml:space="preserve">1.26643347740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30904829502106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27845299243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32762432098389</t>
   </si>
   <si>
     <t xml:space="preserve">1.29265797138214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33636569976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31888294219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33745872974396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3385511636734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34401440620422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964383602142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871687412262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31778991222382</t>
+    <t xml:space="preserve">1.33636605739594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31888258457184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33745861053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855128288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3440146446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964371681213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871699333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31779003143311</t>
   </si>
   <si>
     <t xml:space="preserve">1.32543897628784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36805391311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38772225379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3975567817688</t>
+    <t xml:space="preserve">1.36805415153503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38772249221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39755666255951</t>
   </si>
   <si>
     <t xml:space="preserve">1.38990795612335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35275626182556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34838557243347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34620010852814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34729290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3221607208252</t>
+    <t xml:space="preserve">1.35275638103485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34838545322418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34620034694672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34729266166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32216084003448</t>
   </si>
   <si>
     <t xml:space="preserve">1.34292197227478</t>
@@ -716,28 +716,28 @@
     <t xml:space="preserve">1.31014108657837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25222826004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25659894943237</t>
+    <t xml:space="preserve">1.25222814083099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25659918785095</t>
   </si>
   <si>
     <t xml:space="preserve">1.22928178310394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23911607265472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20087170600891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18557417392731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19103741645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22272527217865</t>
+    <t xml:space="preserve">1.23911583423615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20087158679962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18557405471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19103729724884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22272551059723</t>
   </si>
   <si>
     <t xml:space="preserve">1.19322288036346</t>
@@ -746,145 +746,145 @@
     <t xml:space="preserve">1.17027616500854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1735543012619</t>
+    <t xml:space="preserve">1.17355442047119</t>
   </si>
   <si>
     <t xml:space="preserve">1.16590535640717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17136907577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19650089740753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18120300769806</t>
+    <t xml:space="preserve">1.17136871814728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19650113582611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18120312690735</t>
   </si>
   <si>
     <t xml:space="preserve">1.13421738147736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25113534927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27626764774323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26861870288849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189683914185</t>
+    <t xml:space="preserve">1.25113582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27626752853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26861882209778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189695835114</t>
   </si>
   <si>
     <t xml:space="preserve">1.27408218383789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30577051639557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34182918071747</t>
+    <t xml:space="preserve">1.30577027797699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34182929992676</t>
   </si>
   <si>
     <t xml:space="preserve">1.32325351238251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35057055950165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35603451728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36914682388306</t>
+    <t xml:space="preserve">1.35057103633881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35603439807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36914670467377</t>
   </si>
   <si>
     <t xml:space="preserve">1.39100062847137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38662993907928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38335168361664</t>
+    <t xml:space="preserve">1.38662981987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3833521604538</t>
   </si>
   <si>
     <t xml:space="preserve">1.37679553031921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38007378578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37898087501526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37461006641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36696124076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384893417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33199512958527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30467784404755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35166370868683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36040508747101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37351727485657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47623074054718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50573360919952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49480652809143</t>
+    <t xml:space="preserve">1.38007354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37898075580597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37461018562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36696112155914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384881496429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33199501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30467748641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35166358947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3604052066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37351739406586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47623097896576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50573348999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49480664730072</t>
   </si>
   <si>
     <t xml:space="preserve">1.45984053611755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46093308925629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46311843395233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47076737880707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50791883468628</t>
+    <t xml:space="preserve">1.46093320846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46311855316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47076725959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50791871547699</t>
   </si>
   <si>
     <t xml:space="preserve">1.55271947383881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55818319320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55599737167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5570901632309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54725623130798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54507088661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5516265630722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52868008613586</t>
+    <t xml:space="preserve">1.55818283557892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55599772930145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55709004402161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54725587368011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54507052898407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55162668228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52867996692657</t>
   </si>
   <si>
     <t xml:space="preserve">1.52212405204773</t>
@@ -896,154 +896,154 @@
     <t xml:space="preserve">1.56594586372375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57061362266541</t>
+    <t xml:space="preserve">1.57061350345612</t>
   </si>
   <si>
     <t xml:space="preserve">1.56711292266846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55427730083466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49826753139496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48893249034882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4865984916687</t>
+    <t xml:space="preserve">1.55427742004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49826717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48893237113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659861087799</t>
   </si>
   <si>
     <t xml:space="preserve">1.50060093402863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51110279560089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49126589298248</t>
+    <t xml:space="preserve">1.51110291481018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49126601219177</t>
   </si>
   <si>
     <t xml:space="preserve">1.48426485061646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49943435192108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50876927375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50176775455475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50410175323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49710035324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47843039035797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51460361480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5251053571701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52627217769623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57994854450226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6079535484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64062583446503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61845505237579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61962246894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66279661655426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6592960357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67213177680969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65696203708649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66863095760345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65346121788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66162967681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66396367549896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6709645986557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67446553707123</t>
+    <t xml:space="preserve">1.4994341135025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50876891613007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50176787376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50410163402557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49710023403168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47843050956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51460325717926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52510547637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52627229690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57994842529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60795342922211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64062607288361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61845541000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61962234973907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66279637813568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65929615497589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6721316576004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65696227550507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66863119602203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65346157550812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66162979602814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66396355628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67096495628357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67446517944336</t>
   </si>
   <si>
     <t xml:space="preserve">1.66629719734192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67329859733582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68380045890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69313526153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69546926021576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69430220127106</t>
+    <t xml:space="preserve">1.67329847812653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6838002204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69313538074493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69546902179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69430232048035</t>
   </si>
   <si>
     <t xml:space="preserve">1.69896984100342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70130348205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69196844100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7036372423172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70830452442169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7048043012619</t>
+    <t xml:space="preserve">1.70130336284637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6919686794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70363736152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70830464363098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70480406284332</t>
   </si>
   <si>
     <t xml:space="preserve">1.68263363838196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67796576023102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66046297550201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70713782310486</t>
+    <t xml:space="preserve">1.6779659986496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66046261787415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70713770389557</t>
   </si>
   <si>
     <t xml:space="preserve">1.68963491916656</t>
@@ -1052,37 +1052,37 @@
     <t xml:space="preserve">1.64295959472656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65462863445282</t>
+    <t xml:space="preserve">1.65462851524353</t>
   </si>
   <si>
     <t xml:space="preserve">1.65812921524048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63712549209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66513013839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68146646022797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70013642311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71063828468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71763944625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73280906677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73397600650787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72464084625244</t>
+    <t xml:space="preserve">1.63712537288666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66513061523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68146669864655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70013666152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71063816547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71763956546783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73280930519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73397576808929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72464108467102</t>
   </si>
   <si>
     <t xml:space="preserve">1.73514270782471</t>
@@ -1091,64 +1091,64 @@
     <t xml:space="preserve">1.74447786808014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74214434623718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74564480781555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74681127071381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74097752571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71180522441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71530616283417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70947170257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68496739864349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66746425628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68029963970184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597088336945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6791330575943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65112769603729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63362491130829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63479161262512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61728847026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61495494842529</t>
+    <t xml:space="preserve">1.7421441078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74564456939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74681162834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74097764492035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71180510520935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71530604362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7094714641571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68496716022491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66746413707733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68029987812042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597100257874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67913293838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65112781524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.633624792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63479137420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61728870868683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.614954829216</t>
   </si>
   <si>
     <t xml:space="preserve">1.64412665367126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61378788948059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64529347419739</t>
+    <t xml:space="preserve">1.61378800868988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64529359340668</t>
   </si>
   <si>
     <t xml:space="preserve">1.64646029472351</t>
@@ -1157,139 +1157,139 @@
     <t xml:space="preserve">1.67563211917877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63829231262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62895715236664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62662351131439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62778997421265</t>
+    <t xml:space="preserve">1.63829219341278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62895739078522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62662363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62779033184052</t>
   </si>
   <si>
     <t xml:space="preserve">1.61612164974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60678672790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60445284843445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74331080913544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76548171043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77248287200928</t>
+    <t xml:space="preserve">1.60678648948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60445296764374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74331104755402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76548182964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77248299121857</t>
   </si>
   <si>
     <t xml:space="preserve">1.77598321437836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78415143489838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80515551567078</t>
+    <t xml:space="preserve">1.78415155410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80515539646149</t>
   </si>
   <si>
     <t xml:space="preserve">1.80165481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8238251209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8249922990799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79815423488617</t>
+    <t xml:space="preserve">1.82382524013519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82499217987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79815399646759</t>
   </si>
   <si>
     <t xml:space="preserve">1.82149171829224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8436621427536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824799537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83549392223358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84395384788513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111810684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81769895553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902911186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81098985671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87283384799957</t>
+    <t xml:space="preserve">1.84366238117218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8582478761673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83549380302429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84395396709442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111822605133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81769931316376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902899265289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81098973751068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87283396720886</t>
   </si>
   <si>
     <t xml:space="preserve">1.83636927604675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81157302856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377830028534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80923914909363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80690562725067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83053493499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8130316734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8022381067276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80748903751373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78444337844849</t>
+    <t xml:space="preserve">1.81157326698303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377841949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923938751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80690550804138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83053505420685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81303203105927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223786830902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8074893951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7844432592392</t>
   </si>
   <si>
     <t xml:space="preserve">1.79873740673065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79990470409393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80982315540314</t>
+    <t xml:space="preserve">1.79990434646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80982279777527</t>
   </si>
   <si>
     <t xml:space="preserve">1.80632221698761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79290294647217</t>
+    <t xml:space="preserve">1.79290318489075</t>
   </si>
   <si>
     <t xml:space="preserve">1.75410437583923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72930872440338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74535310268402</t>
+    <t xml:space="preserve">1.72930836677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74535298347473</t>
   </si>
   <si>
     <t xml:space="preserve">1.76518976688385</t>
@@ -1301,46 +1301,46 @@
     <t xml:space="preserve">1.78035938739777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77540004253387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74885332584381</t>
+    <t xml:space="preserve">1.77539992332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74885356426239</t>
   </si>
   <si>
     <t xml:space="preserve">1.7608140707016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79523682594299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77364981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78473508358002</t>
+    <t xml:space="preserve">1.79523718357086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77364993095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78473496437073</t>
   </si>
   <si>
     <t xml:space="preserve">1.77423322200775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74272763729095</t>
+    <t xml:space="preserve">1.74272775650024</t>
   </si>
   <si>
     <t xml:space="preserve">1.72259914875031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70742976665497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72289073467255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72318243980408</t>
+    <t xml:space="preserve">1.70742964744568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72289085388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72318232059479</t>
   </si>
   <si>
     <t xml:space="preserve">1.72522437572479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71909844875336</t>
+    <t xml:space="preserve">1.71909809112549</t>
   </si>
   <si>
     <t xml:space="preserve">1.75206255912781</t>
@@ -1349,91 +1349,91 @@
     <t xml:space="preserve">1.74768686294556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76256430149078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77131593227386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7590639591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77948439121246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78940236568451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79465365409851</t>
+    <t xml:space="preserve">1.76256442070007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77131617069244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75906372070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77948403358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78940260410309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79465341567993</t>
   </si>
   <si>
     <t xml:space="preserve">1.81449043750763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81536531448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82907617092133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84832978248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86437392234802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8398699760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85124707221985</t>
+    <t xml:space="preserve">1.8153657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8290764093399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84832990169525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86437439918518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83987009525299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85124695301056</t>
   </si>
   <si>
     <t xml:space="preserve">1.83957827091217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84191203117371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84862160682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83811974525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84453749656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83403563499451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82674252986908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8378279209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85416388511658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80865585803986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79436194896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031232833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73967373371124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75156390666962</t>
+    <t xml:space="preserve">1.84191238880157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84862124919891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83811962604523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84453737735748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83403551578522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82674264907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83782815933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85416376590729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80865597724915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7943617105484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031244754791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73967397212982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75156378746033</t>
   </si>
   <si>
     <t xml:space="preserve">1.72090029716492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70494294166565</t>
+    <t xml:space="preserve">1.70494282245636</t>
   </si>
   <si>
     <t xml:space="preserve">1.65081286430359</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">1.53191435337067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57759606838226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57352900505066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62546873092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62515580654144</t>
+    <t xml:space="preserve">1.57759618759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57352876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62546861171722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62515556812286</t>
   </si>
   <si>
     <t xml:space="preserve">1.56289064884186</t>
@@ -1466,121 +1466,121 @@
     <t xml:space="preserve">1.53629469871521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51752114295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61827230453491</t>
+    <t xml:space="preserve">1.51752126216888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61827206611633</t>
   </si>
   <si>
     <t xml:space="preserve">1.6173335313797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62578141689301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6232784986496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59417963027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59793412685394</t>
+    <t xml:space="preserve">1.62578153610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62327837944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59417974948883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59793436527252</t>
   </si>
   <si>
     <t xml:space="preserve">1.60575652122498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63548123836517</t>
+    <t xml:space="preserve">1.63548135757446</t>
   </si>
   <si>
     <t xml:space="preserve">1.60325336456299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61952364444733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56695783138275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5506876707077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690815925598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55694544315338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55600690841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54474282264709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57634496688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58416724205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60513067245483</t>
+    <t xml:space="preserve">1.61952376365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56695818901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55068790912628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5269079208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55694556236267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55600678920746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54474294185638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57634484767914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58416712284088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60513079166412</t>
   </si>
   <si>
     <t xml:space="preserve">1.6029406785965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60606968402863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58041226863861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54881048202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53066253662109</t>
+    <t xml:space="preserve">1.60606944561005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58041250705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54881024360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53066289424896</t>
   </si>
   <si>
     <t xml:space="preserve">1.53973650932312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53660774230957</t>
+    <t xml:space="preserve">1.53660762310028</t>
   </si>
   <si>
     <t xml:space="preserve">1.5519392490387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54161393642426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51658260822296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50531876087189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53097569942474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55037486553192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57039988040924</t>
+    <t xml:space="preserve">1.54161381721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51658284664154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50531828403473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250267982483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53097558021545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55037462711334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57039999961853</t>
   </si>
   <si>
     <t xml:space="preserve">1.58322823047638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64830982685089</t>
+    <t xml:space="preserve">1.6483097076416</t>
   </si>
   <si>
     <t xml:space="preserve">1.57259011268616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51188921928406</t>
+    <t xml:space="preserve">1.51188910007477</t>
   </si>
   <si>
     <t xml:space="preserve">1.53003704547882</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">1.50844752788544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49248993396759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43804717063904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41426742076874</t>
+    <t xml:space="preserve">1.49249029159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43804705142975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41426730155945</t>
   </si>
   <si>
     <t xml:space="preserve">1.4017516374588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37640726566315</t>
+    <t xml:space="preserve">1.37640762329102</t>
   </si>
   <si>
     <t xml:space="preserve">1.36576902866364</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">1.35732102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40331614017487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38329100608826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37672054767609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37891066074371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37859785556793</t>
+    <t xml:space="preserve">1.40331625938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38329112529755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37672030925751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37891054153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37859761714935</t>
   </si>
   <si>
     <t xml:space="preserve">1.36357891559601</t>
@@ -1634,115 +1634,115 @@
     <t xml:space="preserve">1.34918582439423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33135116100311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35857260227203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4289733171463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45901083946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43929851055145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4158319234848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47997450828552</t>
+    <t xml:space="preserve">1.3313512802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35857272148132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4590106010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43929862976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41583168506622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47997438907623</t>
   </si>
   <si>
     <t xml:space="preserve">1.456507563591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46432983875275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45744633674622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46683263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50093805789948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49906086921692</t>
+    <t xml:space="preserve">1.46432995796204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45744609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46683299541473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50093793869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49906051158905</t>
   </si>
   <si>
     <t xml:space="preserve">1.51908576488495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51157641410828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53222703933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49999964237213</t>
+    <t xml:space="preserve">1.51157629489899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53222715854645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49999940395355</t>
   </si>
   <si>
     <t xml:space="preserve">1.54568159580231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5222145318985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5043797492981</t>
+    <t xml:space="preserve">1.52221441268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50438010692596</t>
   </si>
   <si>
     <t xml:space="preserve">1.37734615802765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32352888584137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31914842128754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32634484767914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35481810569763</t>
+    <t xml:space="preserve">1.32352876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31914865970612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32634472846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35481786727905</t>
   </si>
   <si>
     <t xml:space="preserve">1.31320333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27033758163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29818475246429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30506837368011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27284049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26783418655396</t>
+    <t xml:space="preserve">1.27033722400665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.298184633255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3050684928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27284061908722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26783430576324</t>
   </si>
   <si>
     <t xml:space="preserve">1.27753400802612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29536867141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28066289424896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23842251300812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24167668819427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23128855228424</t>
+    <t xml:space="preserve">1.29536879062653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28066277503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23842239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24167656898499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23128879070282</t>
   </si>
   <si>
     <t xml:space="preserve">1.23166406154633</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">1.18936121463776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2222775220871</t>
+    <t xml:space="preserve">1.22227740287781</t>
   </si>
   <si>
     <t xml:space="preserve">1.21264040470123</t>
@@ -1760,88 +1760,88 @@
     <t xml:space="preserve">1.24943625926971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24655783176422</t>
+    <t xml:space="preserve">1.24655759334564</t>
   </si>
   <si>
     <t xml:space="preserve">1.22215223312378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24267780780792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25563168525696</t>
+    <t xml:space="preserve">1.24267768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25563156604767</t>
   </si>
   <si>
     <t xml:space="preserve">1.2366703748703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25250244140625</t>
+    <t xml:space="preserve">1.25250267982483</t>
   </si>
   <si>
     <t xml:space="preserve">1.28598201274872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26971173286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25500559806824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22665786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25312852859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23829746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2226527929306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20112586021423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20538115501404</t>
+    <t xml:space="preserve">1.26971161365509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25500583648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22665762901306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25312840938568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23829734325409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22265303134918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20112597942352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20538127422333</t>
   </si>
   <si>
     <t xml:space="preserve">1.17571926116943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20901072025299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20888566970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22165155410767</t>
+    <t xml:space="preserve">1.20901095867157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20888555049896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22165143489838</t>
   </si>
   <si>
     <t xml:space="preserve">1.27690804004669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27628242969513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28535604476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27190208435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28160154819489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32196426391602</t>
+    <t xml:space="preserve">1.27628231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28535616397858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27190184593201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2816014289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32196438312531</t>
   </si>
   <si>
     <t xml:space="preserve">1.29161393642426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30193948745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23491823673248</t>
+    <t xml:space="preserve">1.30193936824799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23491811752319</t>
   </si>
   <si>
     <t xml:space="preserve">1.24029994010925</t>
@@ -1850,43 +1850,43 @@
     <t xml:space="preserve">1.21376669406891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21026253700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25969934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27158904075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26032483577728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23466789722443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24217748641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26345360279083</t>
+    <t xml:space="preserve">1.21026217937469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25969898700714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27158892154694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26032495498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23466801643372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2421772480011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26345384120941</t>
   </si>
   <si>
     <t xml:space="preserve">1.21714603900909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19662022590637</t>
+    <t xml:space="preserve">1.19662034511566</t>
   </si>
   <si>
     <t xml:space="preserve">1.19461786746979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21389174461365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19299077987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18986177444458</t>
+    <t xml:space="preserve">1.21389186382294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19299101829529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18986189365387</t>
   </si>
   <si>
     <t xml:space="preserve">1.25106334686279</t>
@@ -1895,40 +1895,40 @@
     <t xml:space="preserve">1.27221477031708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25750887393951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26470530033112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25844776630402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24017453193665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22465527057648</t>
+    <t xml:space="preserve">1.25750875473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26470541954041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25844752788544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24017465114594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22465538978577</t>
   </si>
   <si>
     <t xml:space="preserve">1.2600120306015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27565670013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27596938610077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26814711093903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26908576488495</t>
+    <t xml:space="preserve">1.27565658092499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27596950531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26814723014832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26908600330353</t>
   </si>
   <si>
     <t xml:space="preserve">1.29192698001862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28003716468811</t>
+    <t xml:space="preserve">1.28003704547882</t>
   </si>
   <si>
     <t xml:space="preserve">1.28191447257996</t>
@@ -1940,25 +1940,25 @@
     <t xml:space="preserve">1.24830985069275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2281596660614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22753381729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24705851078033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2418018579483</t>
+    <t xml:space="preserve">1.22815978527069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22753393650055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24705839157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24180161952972</t>
   </si>
   <si>
     <t xml:space="preserve">1.23616969585419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25131368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25531876087189</t>
+    <t xml:space="preserve">1.25131356716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2553186416626</t>
   </si>
   <si>
     <t xml:space="preserve">1.24155139923096</t>
@@ -1967,28 +1967,28 @@
     <t xml:space="preserve">1.28097569942474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2922397851944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2862948179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28692042827606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27659523487091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2778468132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30444276332855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29943633079529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33385419845581</t>
+    <t xml:space="preserve">1.29223990440369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28629493713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28692054748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2765953540802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27784693241119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30444252490997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.299436211586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3338543176651</t>
   </si>
   <si>
     <t xml:space="preserve">1.3504376411438</t>
@@ -1997,52 +1997,52 @@
     <t xml:space="preserve">1.35513091087341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35262787342072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36545622348785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33510589599609</t>
+    <t xml:space="preserve">1.35262763500214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36545634269714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33510601520538</t>
   </si>
   <si>
     <t xml:space="preserve">1.32603192329407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33760893344879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33667004108429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34824705123901</t>
+    <t xml:space="preserve">1.33760917186737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33667027950287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34824728965759</t>
   </si>
   <si>
     <t xml:space="preserve">1.35794699192047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37609469890594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39737105369568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39924848079681</t>
+    <t xml:space="preserve">1.37609457969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39737129211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3992486000061</t>
   </si>
   <si>
     <t xml:space="preserve">1.39549398422241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38610708713531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34949886798859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480559825897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136378765106</t>
+    <t xml:space="preserve">1.38610696792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34949898719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480547904968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136390686035</t>
   </si>
   <si>
     <t xml:space="preserve">1.3516891002655</t>
@@ -2054,46 +2054,46 @@
     <t xml:space="preserve">1.38016211986542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37546873092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38767158985138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39799702167511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3995612859726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39017474651337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3983097076416</t>
+    <t xml:space="preserve">1.3754688501358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3876713514328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39799690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39956152439117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39017450809479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39830982685089</t>
   </si>
   <si>
     <t xml:space="preserve">1.43992447853088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45337855815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46558141708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45963644981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45243990421295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42365419864655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42490565776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42991173267365</t>
+    <t xml:space="preserve">1.45337879657745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46558153629303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45963656902313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45244014263153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42365407943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42490553855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42991185188293</t>
   </si>
   <si>
     <t xml:space="preserve">1.45932352542877</t>
@@ -2111,25 +2111,25 @@
     <t xml:space="preserve">1.4327278137207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40300345420837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38673305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35450506210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35137605667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32540619373322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34543120861053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36639499664307</t>
+    <t xml:space="preserve">1.40300321578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38673293590546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35450494289398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35137617588043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3254063129425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34543132781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36639475822449</t>
   </si>
   <si>
     <t xml:space="preserve">1.35825979709625</t>
@@ -2141,28 +2141,28 @@
     <t xml:space="preserve">1.36066877841949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33630478382111</t>
+    <t xml:space="preserve">1.33630442619324</t>
   </si>
   <si>
     <t xml:space="preserve">1.30973827838898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32061266899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31331717967987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29872608184814</t>
+    <t xml:space="preserve">1.3206125497818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31331706047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29872632026672</t>
   </si>
   <si>
     <t xml:space="preserve">1.28413534164429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28372228145599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26211130619049</t>
+    <t xml:space="preserve">1.28372240066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26211142539978</t>
   </si>
   <si>
     <t xml:space="preserve">1.25674307346344</t>
@@ -2174,25 +2174,25 @@
     <t xml:space="preserve">1.27326107025146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25701820850372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26142311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27037048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133393287659</t>
+    <t xml:space="preserve">1.2570184469223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26142299175262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27037036418915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2713338136673</t>
   </si>
   <si>
     <t xml:space="preserve">1.25811958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2677549123764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26458919048309</t>
+    <t xml:space="preserve">1.26775503158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2645890712738</t>
   </si>
   <si>
     <t xml:space="preserve">1.2601842880249</t>
@@ -2207,82 +2207,82 @@
     <t xml:space="preserve">1.30134165287018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29046738147736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29032969474792</t>
+    <t xml:space="preserve">1.29046726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29032945632935</t>
   </si>
   <si>
     <t xml:space="preserve">1.28592479228973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29239416122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2929447889328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29528498649597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2853741645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2973495721817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36328411102295</t>
+    <t xml:space="preserve">1.29239439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29294490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29528510570526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28537404537201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29734981060028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36328399181366</t>
   </si>
   <si>
     <t xml:space="preserve">1.39439284801483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39852225780487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38854277133942</t>
+    <t xml:space="preserve">1.39852237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38854265213013</t>
   </si>
   <si>
     <t xml:space="preserve">1.38097202777863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.397833943367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41469633579254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41159927845001</t>
+    <t xml:space="preserve">1.39783406257629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41469621658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41159915924072</t>
   </si>
   <si>
     <t xml:space="preserve">1.40987849235535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41916990280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40609312057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41091096401215</t>
+    <t xml:space="preserve">1.41916978359222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40609288215637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41091072559357</t>
   </si>
   <si>
     <t xml:space="preserve">1.38200438022614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38441300392151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40058720111847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39026343822479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38338100910187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37044191360474</t>
+    <t xml:space="preserve">1.3844131231308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40058732032776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39026355743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38338088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37044179439545</t>
   </si>
   <si>
     <t xml:space="preserve">1.35309791564941</t>
@@ -2300,22 +2300,22 @@
     <t xml:space="preserve">1.35433673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33836936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31455588340759</t>
+    <t xml:space="preserve">1.33836925029755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31455600261688</t>
   </si>
   <si>
     <t xml:space="preserve">1.33891999721527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26362538337708</t>
+    <t xml:space="preserve">1.26362550258636</t>
   </si>
   <si>
     <t xml:space="preserve">1.29886388778687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27023279666901</t>
+    <t xml:space="preserve">1.2702329158783</t>
   </si>
   <si>
     <t xml:space="preserve">1.31744658946991</t>
@@ -2327,37 +2327,37 @@
     <t xml:space="preserve">1.32322800159454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33644223213196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30987584590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33520340919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34084689617157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35488748550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38578963279724</t>
+    <t xml:space="preserve">1.33644211292267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30987572669983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33520352840424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34084713459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35488724708557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38578975200653</t>
   </si>
   <si>
     <t xml:space="preserve">1.37181830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37890732288361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37684261798859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39542531967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41504061222076</t>
+    <t xml:space="preserve">1.37890720367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37684237957001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39542508125305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4150402545929</t>
   </si>
   <si>
     <t xml:space="preserve">1.42261099815369</t>
@@ -2369,28 +2369,28 @@
     <t xml:space="preserve">1.46149718761444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45082926750183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46080887317657</t>
+    <t xml:space="preserve">1.45082938671112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46080899238586</t>
   </si>
   <si>
     <t xml:space="preserve">1.50175964832306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47526240348816</t>
+    <t xml:space="preserve">1.47526228427887</t>
   </si>
   <si>
     <t xml:space="preserve">1.46252942085266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46321785449982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48937153816223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4907478094101</t>
+    <t xml:space="preserve">1.46321761608124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48937141895294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49074757099152</t>
   </si>
   <si>
     <t xml:space="preserve">1.47319734096527</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">1.46597099304199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46941196918488</t>
+    <t xml:space="preserve">1.46941220760345</t>
   </si>
   <si>
     <t xml:space="preserve">1.47491788864136</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">1.48696255683899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49728620052338</t>
+    <t xml:space="preserve">1.49728608131409</t>
   </si>
   <si>
     <t xml:space="preserve">1.4831770658493</t>
@@ -2420,55 +2420,55 @@
     <t xml:space="preserve">1.43912923336029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44222629070282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43568801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4477322101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47939145565033</t>
+    <t xml:space="preserve">1.44222617149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43568766117096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44773232936859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47939157485962</t>
   </si>
   <si>
     <t xml:space="preserve">1.50451278686523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50038313865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52103090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5406459569931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53582811355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53789269924164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55062544345856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56576716899872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56232571601868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56301391124725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56404626369476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56817579269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56370234489441</t>
+    <t xml:space="preserve">1.50038325786591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52103066444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54064583778381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53582787513733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53789281845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55062556266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56576693058014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56232583522797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56301367282867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56404650211334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56817603111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56370210647583</t>
   </si>
   <si>
     <t xml:space="preserve">1.54752850532532</t>
@@ -2477,55 +2477,55 @@
     <t xml:space="preserve">1.54580783843994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56439030170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58710241317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61050319671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60878264904022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62151491641998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256778240204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62220370769501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63665664196014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61394464969635</t>
+    <t xml:space="preserve">1.56439018249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58710253238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6105033159256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60878252983093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62151503562927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256766319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62220346927643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63665652275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61394429206848</t>
   </si>
   <si>
     <t xml:space="preserve">1.60086762905121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60912680625916</t>
+    <t xml:space="preserve">1.60912644863129</t>
   </si>
   <si>
     <t xml:space="preserve">1.61738538742065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61566519737244</t>
+    <t xml:space="preserve">1.61566495895386</t>
   </si>
   <si>
     <t xml:space="preserve">1.62013864517212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61291205883026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61910605430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61187982559204</t>
+    <t xml:space="preserve">1.61291217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61910617351532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61187970638275</t>
   </si>
   <si>
     <t xml:space="preserve">1.60190010070801</t>
@@ -2534,109 +2534,109 @@
     <t xml:space="preserve">1.58985567092896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58331716060638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54511940479279</t>
+    <t xml:space="preserve">1.58331704139709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5451192855835</t>
   </si>
   <si>
     <t xml:space="preserve">1.5767787694931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57471430301666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59226429462433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58090829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58572626113892</t>
+    <t xml:space="preserve">1.57471442222595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59226477146149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58090841770172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58572614192963</t>
   </si>
   <si>
     <t xml:space="preserve">1.59054398536682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60224425792694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6149765253067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62633275985718</t>
+    <t xml:space="preserve">1.60224437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61497676372528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62633299827576</t>
   </si>
   <si>
     <t xml:space="preserve">1.6283974647522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63803315162659</t>
+    <t xml:space="preserve">1.6380330324173</t>
   </si>
   <si>
     <t xml:space="preserve">1.65523934364319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65214240550995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62082719802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61635327339172</t>
+    <t xml:space="preserve">1.65214228630066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62082695960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61635339260101</t>
   </si>
   <si>
     <t xml:space="preserve">1.63872134685516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61704158782959</t>
+    <t xml:space="preserve">1.6170414686203</t>
   </si>
   <si>
     <t xml:space="preserve">1.63390374183655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6111912727356</t>
+    <t xml:space="preserve">1.61119151115417</t>
   </si>
   <si>
     <t xml:space="preserve">1.61532080173492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59673833847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59845876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60809421539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59570574760437</t>
+    <t xml:space="preserve">1.59673821926117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59845888614655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60809433460236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59570586681366</t>
   </si>
   <si>
     <t xml:space="preserve">1.56920790672302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56094908714294</t>
+    <t xml:space="preserve">1.56094896793365</t>
   </si>
   <si>
     <t xml:space="preserve">1.56783175468445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55200183391571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58675873279572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57712316513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5454638004303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57264947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61841809749603</t>
+    <t xml:space="preserve">1.552001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58675837516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57712304592133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54546356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57264935970306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61841797828674</t>
   </si>
   <si>
     <t xml:space="preserve">1.68586647510529</t>
@@ -2648,25 +2648,25 @@
     <t xml:space="preserve">1.7041050195694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69240486621857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70857882499695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72578477859497</t>
+    <t xml:space="preserve">1.69240462779999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70857858657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72578489780426</t>
   </si>
   <si>
     <t xml:space="preserve">1.72750544548035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7481529712677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78944778442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79185676574707</t>
+    <t xml:space="preserve">1.74815285205841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78944790363312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79185664653778</t>
   </si>
   <si>
     <t xml:space="preserve">1.75503551959991</t>
@@ -2675,73 +2675,73 @@
     <t xml:space="preserve">1.73542046546936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63562417030334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60362064838409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5750584602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51311576366425</t>
+    <t xml:space="preserve">1.63562405109406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6036205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57505822181702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51311564445496</t>
   </si>
   <si>
     <t xml:space="preserve">1.47044432163239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45840013027191</t>
+    <t xml:space="preserve">1.45840001106262</t>
   </si>
   <si>
     <t xml:space="preserve">1.46425008773804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40850210189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36080622673035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20443630218506</t>
+    <t xml:space="preserve">1.40850186347961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36080634593964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20443594455719</t>
   </si>
   <si>
     <t xml:space="preserve">1.17608022689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22453308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00677096843719</t>
+    <t xml:space="preserve">1.2245329618454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00677084922791</t>
   </si>
   <si>
     <t xml:space="preserve">1.06981444358826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965476036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998924851417542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969467759132385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980892658233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00856029987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997135400772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08991134166718</t>
+    <t xml:space="preserve">0.965475916862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998925089836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969467639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980892717838287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00856053829193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997135162353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08991158008575</t>
   </si>
   <si>
     <t xml:space="preserve">1.11234831809998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12253451347351</t>
+    <t xml:space="preserve">1.12253439426422</t>
   </si>
   <si>
     <t xml:space="preserve">1.07821118831635</t>
@@ -2750,178 +2750,178 @@
     <t xml:space="preserve">1.01227700710297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0243901014328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987499892711639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989564776420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914820969104767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00360488891602</t>
+    <t xml:space="preserve">1.02438998222351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987500011920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989564538002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914820909500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00360476970673</t>
   </si>
   <si>
     <t xml:space="preserve">1.01103794574738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997410833835602</t>
+    <t xml:space="preserve">0.997410774230957</t>
   </si>
   <si>
     <t xml:space="preserve">0.99452006816864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967816054821014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928035259246826</t>
+    <t xml:space="preserve">0.96781599521637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928035080432892</t>
   </si>
   <si>
     <t xml:space="preserve">0.936156690120697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947168469429016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951848745346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908489108085632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921014904975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952812314033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924869298934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960245311260223</t>
+    <t xml:space="preserve">0.947168588638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951848685741425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908488929271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921015024185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952812135219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924869179725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960245192050934</t>
   </si>
   <si>
     <t xml:space="preserve">0.996034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01888394355774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979378819465637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94703084230423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998649537563324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97745144367218</t>
+    <t xml:space="preserve">1.01888418197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979378521442413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947031021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998649597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97745156288147</t>
   </si>
   <si>
     <t xml:space="preserve">0.966577053070068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973184168338776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97001838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977864384651184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959144175052643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952261388301849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952399432659149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999475598335266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984746813774109</t>
+    <t xml:space="preserve">0.973184406757355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970018446445465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977864444255829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959144294261932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952261626720428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95239919424057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999475419521332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984747052192688</t>
   </si>
   <si>
     <t xml:space="preserve">0.990390598773956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978690445423126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994244873523712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0031920671463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03319954872131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05880272388458</t>
+    <t xml:space="preserve">0.978690385818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994244933128357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00319194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0331996679306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05880260467529</t>
   </si>
   <si>
     <t xml:space="preserve">1.07270526885986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06843793392181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08743381500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11840498447418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15157854557037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16575658321381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2201281785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24118876457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18378853797913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17181301116943</t>
+    <t xml:space="preserve">1.0684380531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08743357658386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11840486526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15157866477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16575646400452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22012805938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24118864536285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18378865718842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17181313037872</t>
   </si>
   <si>
     <t xml:space="preserve">1.11344945430756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11634004116058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11950635910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16947305202484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17263901233673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16025042533875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15956234931946</t>
+    <t xml:space="preserve">1.11634027957916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11950612068176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16947317123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17263877391815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16025066375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15956223011017</t>
   </si>
   <si>
     <t xml:space="preserve">1.15791058540344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17786955833435</t>
+    <t xml:space="preserve">1.17786979675293</t>
   </si>
   <si>
     <t xml:space="preserve">1.14717376232147</t>
@@ -2930,34 +2930,34 @@
     <t xml:space="preserve">1.14249360561371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17140007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1725013256073</t>
+    <t xml:space="preserve">1.17140018939972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17250144481659</t>
   </si>
   <si>
     <t xml:space="preserve">1.16355407238007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20636308193207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20223367214203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23348009586334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22962605953217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21338331699371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19149696826935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21503520011902</t>
+    <t xml:space="preserve">1.20636320114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20223355293274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23348021507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22962594032288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.213383436203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19149708747864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21503508090973</t>
   </si>
   <si>
     <t xml:space="preserve">1.22604715824127</t>
@@ -2966,22 +2966,22 @@
     <t xml:space="preserve">1.2257719039917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24875915050507</t>
+    <t xml:space="preserve">1.24875938892365</t>
   </si>
   <si>
     <t xml:space="preserve">1.26596570014954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26073503494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27628934383392</t>
+    <t xml:space="preserve">1.26073479652405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27628910541534</t>
   </si>
   <si>
     <t xml:space="preserve">1.29721212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29129314422607</t>
+    <t xml:space="preserve">1.29129302501678</t>
   </si>
   <si>
     <t xml:space="preserve">1.27271032333374</t>
@@ -2996,31 +2996,31 @@
     <t xml:space="preserve">1.22935080528259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23155295848846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19411242008209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17497909069061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1756671667099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23444366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26252436637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24834644794464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24256527423859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24848413467407</t>
+    <t xml:space="preserve">1.23155319690704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19411218166351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17497897148132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17566740512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23444354534149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26252448558807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24834609031677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24256503582001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24848401546478</t>
   </si>
   <si>
     <t xml:space="preserve">1.28096950054169</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">1.29583561420441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28399765491486</t>
+    <t xml:space="preserve">1.28399777412415</t>
   </si>
   <si>
     <t xml:space="preserve">1.27436220645905</t>
@@ -3038,73 +3038,73 @@
     <t xml:space="preserve">1.25564169883728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24903476238251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26981973648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24999809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24683237075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26582789421082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26224887371063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2681679725647</t>
+    <t xml:space="preserve">1.24903464317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26981961727142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24999833106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24683225154877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2658280134201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26224899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26816785335541</t>
   </si>
   <si>
     <t xml:space="preserve">1.24146389961243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25605499744415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24242758750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24008750915527</t>
+    <t xml:space="preserve">1.25605487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24242734909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24008738994598</t>
   </si>
   <si>
     <t xml:space="preserve">1.22425758838654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2241199016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2345814704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21269512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23210346698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23967444896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22439527511597</t>
+    <t xml:space="preserve">1.22412014007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23458158969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21269488334656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23210370540619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23967468738556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22439539432526</t>
   </si>
   <si>
     <t xml:space="preserve">1.21737515926361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21145617961884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19989371299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18020975589752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12570035457611</t>
+    <t xml:space="preserve">1.2114565372467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19989347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18020987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1257004737854</t>
   </si>
   <si>
     <t xml:space="preserve">1.12996757030487</t>
@@ -3113,22 +3113,22 @@
     <t xml:space="preserve">1.10959529876709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10670495033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08674550056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11812973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10587871074677</t>
+    <t xml:space="preserve">1.10670483112335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08674538135529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1181298494339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10587882995605</t>
   </si>
   <si>
     <t xml:space="preserve">1.1032634973526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09183859825134</t>
+    <t xml:space="preserve">1.09183847904205</t>
   </si>
   <si>
     <t xml:space="preserve">1.09596788883209</t>
@@ -3137,25 +3137,25 @@
     <t xml:space="preserve">1.1240485906601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14827489852905</t>
+    <t xml:space="preserve">1.14827501773834</t>
   </si>
   <si>
     <t xml:space="preserve">1.13478529453278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15309262275696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15557038784027</t>
+    <t xml:space="preserve">1.15309286117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15557050704956</t>
   </si>
   <si>
     <t xml:space="preserve">1.14978909492493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11317431926727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05825185775757</t>
+    <t xml:space="preserve">1.11317420005798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05825197696686</t>
   </si>
   <si>
     <t xml:space="preserve">1.07077813148499</t>
@@ -3164,10 +3164,10 @@
     <t xml:space="preserve">1.07353103160858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05701303482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05770134925842</t>
+    <t xml:space="preserve">1.05701315402985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05770146846771</t>
   </si>
   <si>
     <t xml:space="preserve">1.07449471950531</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">0.962998270988464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977038562297821</t>
+    <t xml:space="preserve">0.977038621902466</t>
   </si>
   <si>
     <t xml:space="preserve">1.02026045322418</t>
@@ -3194,25 +3194,25 @@
     <t xml:space="preserve">1.06031656265259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09968447685242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12680172920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11276113986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21531045436859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26926922798157</t>
+    <t xml:space="preserve">1.09968459606171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12680160999298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11276137828827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21531057357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26926910877228</t>
   </si>
   <si>
     <t xml:space="preserve">1.25591707229614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2402251958847</t>
+    <t xml:space="preserve">1.24022495746613</t>
   </si>
   <si>
     <t xml:space="preserve">1.25109934806824</t>
@@ -3221,28 +3221,28 @@
     <t xml:space="preserve">1.26637852191925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27615165710449</t>
+    <t xml:space="preserve">1.27615177631378</t>
   </si>
   <si>
     <t xml:space="preserve">1.28730130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28248369693756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31868529319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33671748638153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32777035236359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32515478134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35653901100159</t>
+    <t xml:space="preserve">1.28248357772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31868553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33671760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32777047157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32515501976013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35653913021088</t>
   </si>
   <si>
     <t xml:space="preserve">1.36700046062469</t>
@@ -3251,40 +3251,40 @@
     <t xml:space="preserve">1.37002885341644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35667669773102</t>
+    <t xml:space="preserve">1.35667681694031</t>
   </si>
   <si>
     <t xml:space="preserve">1.35516262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35998034477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34951913356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231270313263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33465278148651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35929226875305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33726823329926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33823156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33189988136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29473447799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3166207075119</t>
+    <t xml:space="preserve">1.35998046398163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3495192527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231282234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3346529006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35929214954376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33726811408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33823192119598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33189964294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29473435878754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31662058830261</t>
   </si>
   <si>
     <t xml:space="preserve">1.32309019565582</t>
@@ -3293,85 +3293,85 @@
     <t xml:space="preserve">1.32130086421967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31634545326233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31125235557556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29693698883057</t>
+    <t xml:space="preserve">1.31634533405304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31125247478485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29693686962128</t>
   </si>
   <si>
     <t xml:space="preserve">1.35447454452515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34552729129791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33713054656982</t>
+    <t xml:space="preserve">1.34552717208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33713066577911</t>
   </si>
   <si>
     <t xml:space="preserve">1.33396458625793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31799721717834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3090500831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31951141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31483137607574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.325843334198</t>
+    <t xml:space="preserve">1.31799709796906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30904972553253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31951129436493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31483125686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32584321498871</t>
   </si>
   <si>
     <t xml:space="preserve">1.29679906368256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25481605529785</t>
+    <t xml:space="preserve">1.25481581687927</t>
   </si>
   <si>
     <t xml:space="preserve">1.26610314846039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24407935142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26197373867035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25399017333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771436214447</t>
+    <t xml:space="preserve">1.24407923221588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26197385787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25399005413055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771424293518</t>
   </si>
   <si>
     <t xml:space="preserve">1.34291183948517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38234853744507</t>
+    <t xml:space="preserve">1.38234865665436</t>
   </si>
   <si>
     <t xml:space="preserve">1.41848170757294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43844079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637597560883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43155837059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43603193759918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44257056713104</t>
+    <t xml:space="preserve">1.43844091892242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637609481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43155825138092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43603181838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44257032871246</t>
   </si>
   <si>
     <t xml:space="preserve">1.4573677778244</t>
@@ -3380,31 +3380,31 @@
     <t xml:space="preserve">1.45392632484436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45117342472076</t>
+    <t xml:space="preserve">1.45117354393005</t>
   </si>
   <si>
     <t xml:space="preserve">1.44532322883606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45358228683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48111212253571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46872401237488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48661839962006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48283302783966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51621294021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50864231586456</t>
+    <t xml:space="preserve">1.45358240604401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.481112241745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4687237739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48661828041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48283278942108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51621282100677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50864207744598</t>
   </si>
   <si>
     <t xml:space="preserve">1.51036274433136</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">1.56198155879974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56507861614227</t>
+    <t xml:space="preserve">1.56507849693298</t>
   </si>
   <si>
     <t xml:space="preserve">1.55991685390472</t>
@@ -3422,25 +3422,25 @@
     <t xml:space="preserve">1.56955230236053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55888450145721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57884383201599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59329700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61669743061066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59260857105255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58194100856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57540249824524</t>
+    <t xml:space="preserve">1.55888438224792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57884347438812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59329676628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61669731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59260845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58194077014923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57540237903595</t>
   </si>
   <si>
     <t xml:space="preserve">1.57987606525421</t>
@@ -3461,16 +3461,16 @@
     <t xml:space="preserve">1.59019958972931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59536147117615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58503782749176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55750787258148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55096960067749</t>
+    <t xml:space="preserve">1.59536170959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58503770828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55750799179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5509694814682</t>
   </si>
   <si>
     <t xml:space="preserve">1.5557873249054</t>
@@ -3479,46 +3479,46 @@
     <t xml:space="preserve">1.56989645957947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52791321277618</t>
+    <t xml:space="preserve">1.5279129743576</t>
   </si>
   <si>
     <t xml:space="preserve">1.53204274177551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52860140800476</t>
+    <t xml:space="preserve">1.52860128879547</t>
   </si>
   <si>
     <t xml:space="preserve">1.5805641412735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59501755237579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59742653369904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60637366771698</t>
+    <t xml:space="preserve">1.59501731395721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59742629528046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60637390613556</t>
   </si>
   <si>
     <t xml:space="preserve">1.58847916126251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62357997894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62564468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64457142353058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63837718963623</t>
+    <t xml:space="preserve">1.62357985973358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62564444541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64457154273987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63837742805481</t>
   </si>
   <si>
     <t xml:space="preserve">1.63975358009338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63287115097046</t>
+    <t xml:space="preserve">1.63287127017975</t>
   </si>
   <si>
     <t xml:space="preserve">1.64319503307343</t>
@@ -3527,10 +3527,10 @@
     <t xml:space="preserve">1.65868079662323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6535187959671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65116286277771</t>
+    <t xml:space="preserve">1.65351855754852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65116310119629</t>
   </si>
   <si>
     <t xml:space="preserve">1.64976537227631</t>
@@ -3545,58 +3545,58 @@
     <t xml:space="preserve">1.68330562114716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68854629993439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70881021022797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72767686843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73012244701385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73326694965363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73676073551178</t>
+    <t xml:space="preserve">1.68854653835297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70881044864655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72767674922943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73012256622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73326706886292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73676061630249</t>
   </si>
   <si>
     <t xml:space="preserve">1.71894216537476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71440052986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70426833629608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69448566436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71195471286774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71265351772308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68749797344208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63788652420044</t>
+    <t xml:space="preserve">1.71440029144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70426845550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69448578357697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71195495128632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71265363693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68749809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63788640499115</t>
   </si>
   <si>
     <t xml:space="preserve">1.65360856056213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63648903369904</t>
+    <t xml:space="preserve">1.63648891448975</t>
   </si>
   <si>
     <t xml:space="preserve">1.61832129955292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65186154842377</t>
+    <t xml:space="preserve">1.65186166763306</t>
   </si>
   <si>
     <t xml:space="preserve">1.66688501834869</t>
@@ -3605,31 +3605,31 @@
     <t xml:space="preserve">1.62775444984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64662075042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64592230319977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6322968006134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65535533428192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62146532535553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60958671569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56242084503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59596121311188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61098456382751</t>
+    <t xml:space="preserve">1.64662063121796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64592218399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63229620456696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65535545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6214656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60958659648895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56242060661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5959609746933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61098420619965</t>
   </si>
   <si>
     <t xml:space="preserve">1.58617854118347</t>
@@ -3638,82 +3638,82 @@
     <t xml:space="preserve">1.59631049633026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57639586925507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55962574481964</t>
+    <t xml:space="preserve">1.57639598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55962586402893</t>
   </si>
   <si>
     <t xml:space="preserve">1.49359321594238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52259135246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56277012825012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59665989875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63334453105927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61657416820526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6211165189743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63998258113861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62915229797363</t>
+    <t xml:space="preserve">1.52259147167206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56277024745941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255280017853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59665977954865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63334465026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61657452583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62111639976501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6399827003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62915217876434</t>
   </si>
   <si>
     <t xml:space="preserve">1.61727333068848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62565803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63509142398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63858532905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67596852779388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68016135692596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68260669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7112557888031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71055734157562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69204020500183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66898119449615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.682257771492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66723430156708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66304183006287</t>
+    <t xml:space="preserve">1.62565815448761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63509154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63858509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67596876621246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68016123771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68260681629181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71125566959381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71055722236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69204008579254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66898131370544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68225765228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6672340631485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66304171085358</t>
   </si>
   <si>
     <t xml:space="preserve">1.67002952098846</t>
@@ -3725,40 +3725,40 @@
     <t xml:space="preserve">1.67526996135712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68365502357483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66828238964081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67911338806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66548752784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6483678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65710234642029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63963329792023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66758370399475</t>
+    <t xml:space="preserve">1.68365478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66828262805939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67911303043365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66548776626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64836776256561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65710258483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63963341712952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66758346557617</t>
   </si>
   <si>
     <t xml:space="preserve">1.66094553470612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65884947776794</t>
+    <t xml:space="preserve">1.65884923934937</t>
   </si>
   <si>
     <t xml:space="preserve">1.6085387468338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62251389026642</t>
+    <t xml:space="preserve">1.62251377105713</t>
   </si>
   <si>
     <t xml:space="preserve">1.65815019607544</t>
@@ -3767,67 +3767,67 @@
     <t xml:space="preserve">1.69623279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69413638114929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732698917389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69763016700745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71824371814728</t>
+    <t xml:space="preserve">1.69413661956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732734680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69763052463531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7182434797287</t>
   </si>
   <si>
     <t xml:space="preserve">1.74898886680603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72942364215851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7538800239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75912058353424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74933850765228</t>
+    <t xml:space="preserve">1.7294237613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75388014316559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75912082195282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74933838844299</t>
   </si>
   <si>
     <t xml:space="preserve">1.75562715530396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74339854717255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76331341266632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7992992401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8110020160675</t>
+    <t xml:space="preserve">1.74339866638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76331329345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79929947853088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81100189685822</t>
   </si>
   <si>
     <t xml:space="preserve">1.78156363964081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79319369792938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77720236778259</t>
+    <t xml:space="preserve">1.79319357872009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77720260620117</t>
   </si>
   <si>
     <t xml:space="preserve">1.78192698955536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79028594493866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80373311042786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78301727771759</t>
+    <t xml:space="preserve">1.79028630256653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80373299121857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78301739692688</t>
   </si>
   <si>
     <t xml:space="preserve">1.77211427688599</t>
@@ -3842,52 +3842,52 @@
     <t xml:space="preserve">1.82590305805206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81863439083099</t>
+    <t xml:space="preserve">1.81863415241241</t>
   </si>
   <si>
     <t xml:space="preserve">1.78556144237518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80518698692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81172895431519</t>
+    <t xml:space="preserve">1.80518710613251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8117288351059</t>
   </si>
   <si>
     <t xml:space="preserve">1.7957376241684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80046248435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79646456241608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80991160869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80446028709412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80409669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7328634262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74418139457703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72544288635254</t>
+    <t xml:space="preserve">1.80046236515045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79682791233063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646480083466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80991172790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80446016788483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8040965795517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73286330699921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74418127536774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72544276714325</t>
   </si>
   <si>
     <t xml:space="preserve">1.7258175611496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71494925022125</t>
+    <t xml:space="preserve">1.71494936943054</t>
   </si>
   <si>
     <t xml:space="preserve">1.61638462543488</t>
@@ -3896,34 +3896,34 @@
     <t xml:space="preserve">1.60626566410065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58565330505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62537920475006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60963881015778</t>
+    <t xml:space="preserve">1.585653424263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62537908554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6096385717392</t>
   </si>
   <si>
     <t xml:space="preserve">1.60888910293579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65873372554779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69246280193329</t>
+    <t xml:space="preserve">1.6587336063385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69246292114258</t>
   </si>
   <si>
     <t xml:space="preserve">1.6722252368927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6677280664444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66060757637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65273725986481</t>
+    <t xml:space="preserve">1.66772818565369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66060745716095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6527373790741</t>
   </si>
   <si>
     <t xml:space="preserve">1.66735327243805</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">1.65011394023895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68084502220154</t>
+    <t xml:space="preserve">1.68084526062012</t>
   </si>
   <si>
     <t xml:space="preserve">1.65311205387115</t>
@@ -3941,13 +3941,13 @@
     <t xml:space="preserve">1.63549780845642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67334961891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67185068130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68721616268158</t>
+    <t xml:space="preserve">1.67334973812103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67185044288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68721628189087</t>
   </si>
   <si>
     <t xml:space="preserve">1.69583594799042</t>
@@ -3956,46 +3956,46 @@
     <t xml:space="preserve">1.71157622337341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70670425891876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7044552564621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75767314434052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79440033435822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8123893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82363283634186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83749890327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84611868858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86036014556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90795576572418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9191986322403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92032325267792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93194150924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9300674200058</t>
+    <t xml:space="preserve">1.70670413970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70445549488068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75767290592194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7944004535675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81238925457001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82363247871399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83749902248383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84611904621124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86036002635956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90795600414276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91919887065887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9203234910965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93194127082825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93006718158722</t>
   </si>
   <si>
     <t xml:space="preserve">1.89933621883392</t>
@@ -4004,22 +4004,22 @@
     <t xml:space="preserve">1.91245305538177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91282820701599</t>
+    <t xml:space="preserve">1.91282784938812</t>
   </si>
   <si>
     <t xml:space="preserve">1.8487423658371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86560666561127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92219734191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95817506313324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94655728340149</t>
+    <t xml:space="preserve">1.86560678482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92219722270966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95817530155182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94655740261078</t>
   </si>
   <si>
     <t xml:space="preserve">1.96342194080353</t>
@@ -4031,25 +4031,25 @@
     <t xml:space="preserve">2.02151131629944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04474711418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99902510643005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03500318527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07585310935974</t>
+    <t xml:space="preserve">2.04474687576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99902522563934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03500294685364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07585334777832</t>
   </si>
   <si>
     <t xml:space="preserve">2.1388144493103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18865847587585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07435369491577</t>
+    <t xml:space="preserve">2.18865895271301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07435393333435</t>
   </si>
   <si>
     <t xml:space="preserve">2.13843965530396</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">2.09196805953979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05299186706543</t>
+    <t xml:space="preserve">2.05299210548401</t>
   </si>
   <si>
     <t xml:space="preserve">2.04024958610535</t>
@@ -4067,37 +4067,37 @@
     <t xml:space="preserve">2.00427198410034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99377822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96417152881622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80789196491241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8569872379303</t>
+    <t xml:space="preserve">1.99377834796906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9641717672348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80789220333099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85698711872101</t>
   </si>
   <si>
     <t xml:space="preserve">1.71907162666321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58640313148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60851418972015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56204283237457</t>
+    <t xml:space="preserve">1.5864030122757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60851442813873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56204295158386</t>
   </si>
   <si>
     <t xml:space="preserve">1.42127907276154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38155329227448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39834308624268</t>
+    <t xml:space="preserve">1.38155341148376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39834320545197</t>
   </si>
   <si>
     <t xml:space="preserve">1.55342316627502</t>
@@ -4106,10 +4106,10 @@
     <t xml:space="preserve">1.4352205991745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43866837024689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49158608913422</t>
+    <t xml:space="preserve">1.43866860866547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49158620834351</t>
   </si>
   <si>
     <t xml:space="preserve">1.50507771968842</t>
@@ -4118,10 +4118,10 @@
     <t xml:space="preserve">1.61001348495483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55304849147797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56354212760925</t>
+    <t xml:space="preserve">1.55304825305939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56354188919067</t>
   </si>
   <si>
     <t xml:space="preserve">1.54892587661743</t>
@@ -4130,40 +4130,40 @@
     <t xml:space="preserve">1.57403540611267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53505945205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5223171710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52381610870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53243601322174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61975729465485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59951996803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56166815757751</t>
+    <t xml:space="preserve">1.53505957126617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52231705188751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52381634712219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53243613243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61975753307343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59951984882355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56166803836823</t>
   </si>
   <si>
     <t xml:space="preserve">1.57778322696686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57028794288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53056228160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48573958873749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46280348300934</t>
+    <t xml:space="preserve">1.57028782367706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53056216239929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48573982715607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46280360221863</t>
   </si>
   <si>
     <t xml:space="preserve">1.48558974266052</t>
@@ -4172,37 +4172,37 @@
     <t xml:space="preserve">1.48469030857086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4550085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45725703239441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47734463214874</t>
+    <t xml:space="preserve">1.45500862598419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4572571516037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47734475135803</t>
   </si>
   <si>
     <t xml:space="preserve">1.47884392738342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51444709300995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5178200006485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48618936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46055519580841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43761909008026</t>
+    <t xml:space="preserve">1.51444697380066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51782011985779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48618948459625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46055507659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43761920928955</t>
   </si>
   <si>
     <t xml:space="preserve">1.4397177696228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44361531734467</t>
+    <t xml:space="preserve">1.44361543655396</t>
   </si>
   <si>
     <t xml:space="preserve">1.46520221233368</t>
@@ -4214,46 +4214,46 @@
     <t xml:space="preserve">1.46924960613251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44301581382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44256591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40913653373718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37165951728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39534497261047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45410895347595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4707487821579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47839391231537</t>
+    <t xml:space="preserve">1.44301569461823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44256603717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40913665294647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3716596364975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39534509181976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45410919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47074902057648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47839403152466</t>
   </si>
   <si>
     <t xml:space="preserve">1.46490240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49188590049744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49008679389954</t>
+    <t xml:space="preserve">1.49188578128815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49008703231812</t>
   </si>
   <si>
     <t xml:space="preserve">1.48633921146393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54183995723724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54496216773987</t>
+    <t xml:space="preserve">1.54183983802795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54496228694916</t>
   </si>
   <si>
     <t xml:space="preserve">1.586958527565</t>
@@ -4265,22 +4265,22 @@
     <t xml:space="preserve">1.59788680076599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60764443874359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58500683307648</t>
+    <t xml:space="preserve">1.6076443195343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58500695228577</t>
   </si>
   <si>
     <t xml:space="preserve">1.56119871139526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54012262821198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5904712677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315016746521</t>
+    <t xml:space="preserve">1.54012250900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59047114849091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5631502866745</t>
   </si>
   <si>
     <t xml:space="preserve">1.55339276790619</t>
@@ -4289,19 +4289,19 @@
     <t xml:space="preserve">1.5352828502655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42193973064423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37307417392731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38166081905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44520175457001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3996148109436</t>
+    <t xml:space="preserve">1.42193984985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3730742931366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38166093826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44520163536072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39961457252502</t>
   </si>
   <si>
     <t xml:space="preserve">1.40788888931274</t>
@@ -4316,25 +4316,25 @@
     <t xml:space="preserve">1.46799516677856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43630290031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4692440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47798681259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48204588890076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46440446376801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38946676254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37978756427765</t>
+    <t xml:space="preserve">1.43630278110504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46924412250519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47798669338226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48204600811005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46440434455872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38946688175201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37978744506836</t>
   </si>
   <si>
     <t xml:space="preserve">1.34669005870819</t>
@@ -4343,91 +4343,91 @@
     <t xml:space="preserve">1.30469369888306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31000173091888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36230206489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3758841753006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35199809074402</t>
+    <t xml:space="preserve">1.31000185012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36230218410492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37588441371918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35199797153473</t>
   </si>
   <si>
     <t xml:space="preserve">1.33295142650604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32764339447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25411105155945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27393805980682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30672347545624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38369047641754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33513712882996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29813671112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29579484462738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31765174865723</t>
+    <t xml:space="preserve">1.3276435136795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25411093235016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27393817901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30672323703766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38369035720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33513724803925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2981368303299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29579496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31765162944794</t>
   </si>
   <si>
     <t xml:space="preserve">1.29329717159271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3092212677002</t>
+    <t xml:space="preserve">1.30922114849091</t>
   </si>
   <si>
     <t xml:space="preserve">1.3315464258194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34934401512146</t>
+    <t xml:space="preserve">1.34934389591217</t>
   </si>
   <si>
     <t xml:space="preserve">1.36542439460754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36370706558228</t>
+    <t xml:space="preserve">1.36370694637299</t>
   </si>
   <si>
     <t xml:space="preserve">1.38462710380554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39180862903595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41600739955902</t>
+    <t xml:space="preserve">1.39180850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41600728034973</t>
   </si>
   <si>
     <t xml:space="preserve">1.41850507259369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41756856441498</t>
+    <t xml:space="preserve">1.41756844520569</t>
   </si>
   <si>
     <t xml:space="preserve">1.43052637577057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4470751285553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44785583019257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42740392684937</t>
+    <t xml:space="preserve">1.44707500934601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44785559177399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42740404605865</t>
   </si>
   <si>
     <t xml:space="preserve">1.42615509033203</t>
@@ -4439,43 +4439,43 @@
     <t xml:space="preserve">1.34138202667236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36573660373688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37666511535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35699391365051</t>
+    <t xml:space="preserve">1.36573672294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37666499614716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3569940328598</t>
   </si>
   <si>
     <t xml:space="preserve">1.315309882164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32811188697815</t>
+    <t xml:space="preserve">1.32811176776886</t>
   </si>
   <si>
     <t xml:space="preserve">1.34996855258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34497261047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32217907905579</t>
+    <t xml:space="preserve">1.34497284889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32217919826508</t>
   </si>
   <si>
     <t xml:space="preserve">1.3568377494812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32467722892761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32998526096344</t>
+    <t xml:space="preserve">1.32467699050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32998514175415</t>
   </si>
   <si>
     <t xml:space="preserve">1.32701897621155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35855507850647</t>
+    <t xml:space="preserve">1.35855519771576</t>
   </si>
   <si>
     <t xml:space="preserve">1.43099474906921</t>
@@ -4487,13 +4487,13 @@
     <t xml:space="preserve">1.46846354007721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48329508304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49875068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4948478937149</t>
+    <t xml:space="preserve">1.48329496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4987508058548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49484765529633</t>
   </si>
   <si>
     <t xml:space="preserve">1.49515998363495</t>
@@ -4502,13 +4502,13 @@
     <t xml:space="preserve">1.44348430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43364882469177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44566988945007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37697720527649</t>
+    <t xml:space="preserve">1.43364870548248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44567000865936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37697744369507</t>
   </si>
   <si>
     <t xml:space="preserve">1.38041174411774</t>
@@ -4517,13 +4517,13 @@
     <t xml:space="preserve">1.34825122356415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32592618465424</t>
+    <t xml:space="preserve">1.32592606544495</t>
   </si>
   <si>
     <t xml:space="preserve">1.29189193248749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32920467853546</t>
+    <t xml:space="preserve">1.32920455932617</t>
   </si>
   <si>
     <t xml:space="preserve">1.35355925559998</t>
@@ -4532,16 +4532,16 @@
     <t xml:space="preserve">1.39571166038513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35917961597443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3365421295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33139026165009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32342791557312</t>
+    <t xml:space="preserve">1.35917949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33654224872589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33139038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3234281539917</t>
   </si>
   <si>
     <t xml:space="preserve">1.30781614780426</t>
@@ -4550,97 +4550,97 @@
     <t xml:space="preserve">1.33201479911804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33669829368591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36058473587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40726459026337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852201938629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42771625518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42662334442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44863617420197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45550549030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45644223690033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4876663684845</t>
+    <t xml:space="preserve">1.3366984128952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36058485507965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40726470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39852178096771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4277161359787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42662346363068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44863629341125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45550560951233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45644235610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48766624927521</t>
   </si>
   <si>
     <t xml:space="preserve">1.48719787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50577616691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51842200756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51810956001282</t>
+    <t xml:space="preserve">1.50577628612518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51842188835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51810967922211</t>
   </si>
   <si>
     <t xml:space="preserve">1.53746843338013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61193764209747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66189587116241</t>
+    <t xml:space="preserve">1.61193752288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66189610958099</t>
   </si>
   <si>
     <t xml:space="preserve">1.67672753334045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68141114711761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6993647813797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68648505210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678043365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.709512591362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70990288257599</t>
+    <t xml:space="preserve">1.68141102790833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69936490058899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68648481369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678067207336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70951271057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70990312099457</t>
   </si>
   <si>
     <t xml:space="preserve">1.70014524459839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73019874095917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72882604598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74457180500031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73165214061737</t>
+    <t xml:space="preserve">1.73019850254059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72882580757141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74457168579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73165202140808</t>
   </si>
   <si>
     <t xml:space="preserve">1.7441680431366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74295675754547</t>
+    <t xml:space="preserve">1.74295663833618</t>
   </si>
   <si>
     <t xml:space="preserve">1.70863854885101</t>
@@ -4649,7 +4649,7 @@
     <t xml:space="preserve">1.72357714176178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71348333358765</t>
+    <t xml:space="preserve">1.71348345279694</t>
   </si>
   <si>
     <t xml:space="preserve">1.68320298194885</t>
@@ -4664,10 +4664,10 @@
     <t xml:space="preserve">1.66866815090179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66463077068329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66140079498291</t>
+    <t xml:space="preserve">1.664630651474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66140067577362</t>
   </si>
   <si>
     <t xml:space="preserve">1.66907179355621</t>
@@ -4676,31 +4676,31 @@
     <t xml:space="preserve">1.67028307914734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6965264081955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68562531471252</t>
+    <t xml:space="preserve">1.69652652740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68562543392181</t>
   </si>
   <si>
     <t xml:space="preserve">1.61044836044312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66180443763733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64282858371735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67593538761139</t>
+    <t xml:space="preserve">1.66180455684662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64282846450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67593550682068</t>
   </si>
   <si>
     <t xml:space="preserve">1.69612264633179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68279922008514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68966257572174</t>
+    <t xml:space="preserve">1.68279933929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68966269493103</t>
   </si>
   <si>
     <t xml:space="preserve">1.68118417263031</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">1.67997288703918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70137143135071</t>
+    <t xml:space="preserve">1.70137131214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.67795419692993</t>
@@ -4718,49 +4718,49 @@
     <t xml:space="preserve">1.71429097652435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75426137447357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79948079586029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78857958316803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8035181760788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81684160232544</t>
+    <t xml:space="preserve">1.75426149368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79948055744171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78857946395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80351805686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81684148311615</t>
   </si>
   <si>
     <t xml:space="preserve">1.82451260089874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84429633617401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84752607345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84510374069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82572376728058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79503965377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76072132587433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80836319923401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84550738334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317850112915</t>
+    <t xml:space="preserve">1.84429597854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8475261926651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84510362148285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82572388648987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79503977298737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76072144508362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80836308002472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84550750255585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85317862033844</t>
   </si>
   <si>
     <t xml:space="preserve">1.89153397083282</t>
@@ -4769,25 +4769,25 @@
     <t xml:space="preserve">1.89839780330658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89274549484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94603943824768</t>
+    <t xml:space="preserve">1.89274537563324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94603931903839</t>
   </si>
   <si>
     <t xml:space="preserve">1.98076117038727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98237597942352</t>
+    <t xml:space="preserve">1.9823762178421</t>
   </si>
   <si>
     <t xml:space="preserve">1.92423725128174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97591638565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9932769536972</t>
+    <t xml:space="preserve">1.97591626644135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99327719211578</t>
   </si>
   <si>
     <t xml:space="preserve">1.99368095397949</t>
@@ -4799,124 +4799,124 @@
     <t xml:space="preserve">2.00014066696167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01790547370911</t>
+    <t xml:space="preserve">2.01790571212769</t>
   </si>
   <si>
     <t xml:space="preserve">2.02073168754578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01467561721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05989456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07079577445984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06231737136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06150960922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99973702430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03001761436462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04535984992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837320327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0485897064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05262756347656</t>
+    <t xml:space="preserve">2.01467537879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05989480018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07079601287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06231689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06150984764099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99973714351654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0300178527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04536008834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837344169617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04858994483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05262732505798</t>
   </si>
   <si>
     <t xml:space="preserve">2.07887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0934054851532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07119965553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07725548744202</t>
+    <t xml:space="preserve">2.09340524673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07119941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.04414892196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00417852401733</t>
+    <t xml:space="preserve">2.00417828559875</t>
   </si>
   <si>
     <t xml:space="preserve">1.88184416294098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94482827186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8115930557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81522643566132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77081513404846</t>
+    <t xml:space="preserve">1.94482815265656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81159317493439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8152266740799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77081525325775</t>
   </si>
   <si>
     <t xml:space="preserve">1.83702886104584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90162765979767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89193785190582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255835533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82733881473541</t>
+    <t xml:space="preserve">1.90162754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89193749427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87255799770355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82733905315399</t>
   </si>
   <si>
     <t xml:space="preserve">1.83420264720917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85196733474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87982559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90970265865326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91172134876251</t>
+    <t xml:space="preserve">1.85196709632874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87982571125031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90970253944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91172122955322</t>
   </si>
   <si>
     <t xml:space="preserve">1.86448323726654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90405023097992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91939222812653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93433046340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92827463150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97147488594055</t>
+    <t xml:space="preserve">1.90405011177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91939234733582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.934330701828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92827475070953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97147500514984</t>
   </si>
   <si>
     <t xml:space="preserve">2.00094819068909</t>
@@ -4928,76 +4928,76 @@
     <t xml:space="preserve">2.01023459434509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00619697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02436542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98722112178802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96541881561279</t>
+    <t xml:space="preserve">2.00619673728943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02436518669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98722088336945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96541893482208</t>
   </si>
   <si>
     <t xml:space="preserve">1.98479866981506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.925448179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88022935390472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91293239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395642280579</t>
+    <t xml:space="preserve">1.92544841766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88022923469543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91293251514435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89395654201508</t>
   </si>
   <si>
     <t xml:space="preserve">1.96380388736725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98883605003357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98358738422394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95048034191132</t>
+    <t xml:space="preserve">1.98883616924286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98358714580536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95048046112061</t>
   </si>
   <si>
     <t xml:space="preserve">1.93917560577393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96057391166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95451807975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94038701057434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9294855594635</t>
+    <t xml:space="preserve">1.96057403087616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9545179605484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94038689136505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92948567867279</t>
   </si>
   <si>
     <t xml:space="preserve">1.95128786563873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96353399753571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96437239646912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88888442516327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8880455493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88301301002502</t>
+    <t xml:space="preserve">1.96353375911713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96437251567841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88888430595398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88804543018341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88301289081573</t>
   </si>
   <si>
     <t xml:space="preserve">1.86665725708008</t>
@@ -5009,22 +5009,22 @@
     <t xml:space="preserve">1.80794405937195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87043166160583</t>
+    <t xml:space="preserve">1.87043154239655</t>
   </si>
   <si>
     <t xml:space="preserve">1.90524017810822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89475584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91698276996613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93166089057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94927489757538</t>
+    <t xml:space="preserve">1.89475572109222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91698288917542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93166100978851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94927477836609</t>
   </si>
   <si>
     <t xml:space="preserve">1.93711280822754</t>
@@ -5033,34 +5033,34 @@
     <t xml:space="preserve">1.93417716026306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93921005725861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97108268737793</t>
+    <t xml:space="preserve">1.93920993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97108244895935</t>
   </si>
   <si>
     <t xml:space="preserve">1.97779285907745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99037396907806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00840735435486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0016975402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01805281639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99540662765503</t>
+    <t xml:space="preserve">1.99037384986877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00840759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00169730186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01805305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99540627002716</t>
   </si>
   <si>
     <t xml:space="preserve">1.95850133895874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9559850692749</t>
+    <t xml:space="preserve">1.95598495006561</t>
   </si>
   <si>
     <t xml:space="preserve">1.98072850704193</t>
@@ -5069,31 +5069,31 @@
     <t xml:space="preserve">1.9824059009552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00127768516541</t>
+    <t xml:space="preserve">2.00127792358398</t>
   </si>
   <si>
     <t xml:space="preserve">2.01302075386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04405474662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0302152633667</t>
+    <t xml:space="preserve">2.04405450820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03021502494812</t>
   </si>
   <si>
     <t xml:space="preserve">2.02056932449341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96311461925507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97024381160736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97695398330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99666476249695</t>
+    <t xml:space="preserve">1.96311450004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97024369239807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97695410251617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99666500091553</t>
   </si>
   <si>
     <t xml:space="preserve">2.01973056793213</t>
@@ -5111,22 +5111,22 @@
     <t xml:space="preserve">2.06837868690491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09018635749817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11534929275513</t>
+    <t xml:space="preserve">2.09018659591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11534905433655</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289762496948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12709188461304</t>
+    <t xml:space="preserve">2.12709164619446</t>
   </si>
   <si>
     <t xml:space="preserve">2.12960815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15812563896179</t>
+    <t xml:space="preserve">2.15812587738037</t>
   </si>
   <si>
     <t xml:space="preserve">2.18874049186707</t>
@@ -5141,34 +5141,34 @@
     <t xml:space="preserve">2.149738073349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13506007194519</t>
+    <t xml:space="preserve">2.13505983352661</t>
   </si>
   <si>
     <t xml:space="preserve">2.13338255882263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14722204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96101760864258</t>
+    <t xml:space="preserve">2.14722180366516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.961017370224</t>
   </si>
   <si>
     <t xml:space="preserve">2.0067298412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04489326477051</t>
+    <t xml:space="preserve">2.04489374160767</t>
   </si>
   <si>
     <t xml:space="preserve">2.04615163803101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05076432228088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03734469413757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02937626838684</t>
+    <t xml:space="preserve">2.05076456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03734445571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02937650680542</t>
   </si>
   <si>
     <t xml:space="preserve">2.02224707603455</t>
@@ -5183,7 +5183,7 @@
     <t xml:space="preserve">2.05915212631226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0532808303833</t>
+    <t xml:space="preserve">2.05328106880188</t>
   </si>
   <si>
     <t xml:space="preserve">2.0545392036438</t>
@@ -5195,16 +5195,16 @@
     <t xml:space="preserve">2.09060573577881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09857392311096</t>
+    <t xml:space="preserve">2.09857416152954</t>
   </si>
   <si>
     <t xml:space="preserve">2.073410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0587329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05202293395996</t>
+    <t xml:space="preserve">2.05873274803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05202269554138</t>
   </si>
   <si>
     <t xml:space="preserve">2.00589108467102</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">2.02434396743774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08012104034424</t>
+    <t xml:space="preserve">2.0801215171814</t>
   </si>
   <si>
     <t xml:space="preserve">2.07634687423706</t>
@@ -5231,7 +5231,7 @@
     <t xml:space="preserve">2.07089495658875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03818321228027</t>
+    <t xml:space="preserve">2.03818345069885</t>
   </si>
   <si>
     <t xml:space="preserve">2.04782891273499</t>
@@ -5240,10 +5240,10 @@
     <t xml:space="preserve">2.10821962356567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09102535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06418490409851</t>
+    <t xml:space="preserve">2.09102511405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06418466567993</t>
   </si>
   <si>
     <t xml:space="preserve">2.03482842445374</t>
@@ -5255,10 +5255,10 @@
     <t xml:space="preserve">2.04657101631165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98156702518463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98282527923584</t>
+    <t xml:space="preserve">1.98156714439392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98282539844513</t>
   </si>
   <si>
     <t xml:space="preserve">2.01427865028381</t>
@@ -5276,37 +5276,37 @@
     <t xml:space="preserve">2.05286169052124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.026859998703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03650569915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99205160140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96605026721954</t>
+    <t xml:space="preserve">2.02686023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03650593757629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9920517206192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96605014801025</t>
   </si>
   <si>
     <t xml:space="preserve">1.99079346656799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97611510753632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98785781860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99414849281311</t>
+    <t xml:space="preserve">1.97611498832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98785769939423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9941486120224</t>
   </si>
   <si>
     <t xml:space="preserve">2.06041049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08934736251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11702632904053</t>
+    <t xml:space="preserve">2.08934760093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11702680587769</t>
   </si>
   <si>
     <t xml:space="preserve">2.15015769004822</t>
@@ -5315,10 +5315,10 @@
     <t xml:space="preserve">2.15225434303284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15057682991028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15435147285461</t>
+    <t xml:space="preserve">2.1505765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15435123443604</t>
   </si>
   <si>
     <t xml:space="preserve">2.16231966018677</t>
@@ -5345,7 +5345,7 @@
     <t xml:space="preserve">2.23835301399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25209045410156</t>
+    <t xml:space="preserve">2.25209021568298</t>
   </si>
   <si>
     <t xml:space="preserve">2.26848697662354</t>
@@ -5354,16 +5354,16 @@
     <t xml:space="preserve">2.3039391040802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30438232421875</t>
+    <t xml:space="preserve">2.30438208580017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32609677314758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34559535980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34116363525391</t>
+    <t xml:space="preserve">2.34559559822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34116387367249</t>
   </si>
   <si>
     <t xml:space="preserve">2.36287808418274</t>
@@ -5375,7 +5375,7 @@
     <t xml:space="preserve">2.37838840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39788675308228</t>
+    <t xml:space="preserve">2.39788699150085</t>
   </si>
   <si>
     <t xml:space="preserve">2.37307071685791</t>
@@ -5384,7 +5384,7 @@
     <t xml:space="preserve">2.39301252365112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38503551483154</t>
+    <t xml:space="preserve">2.38503575325012</t>
   </si>
   <si>
     <t xml:space="preserve">2.37705898284912</t>
@@ -5393,19 +5393,19 @@
     <t xml:space="preserve">2.37572956085205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32343792915344</t>
+    <t xml:space="preserve">2.32343769073486</t>
   </si>
   <si>
     <t xml:space="preserve">2.33540272712708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32653975486755</t>
+    <t xml:space="preserve">2.32653999328613</t>
   </si>
   <si>
     <t xml:space="preserve">2.35046982765198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3371753692627</t>
+    <t xml:space="preserve">2.33717560768127</t>
   </si>
   <si>
     <t xml:space="preserve">2.33097124099731</t>
@@ -5414,7 +5414,7 @@
     <t xml:space="preserve">2.34603834152222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35445857048035</t>
+    <t xml:space="preserve">2.35445833206177</t>
   </si>
   <si>
     <t xml:space="preserve">2.34205007553101</t>
@@ -5441,7 +5441,7 @@
     <t xml:space="preserve">2.44353151321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43599820137024</t>
+    <t xml:space="preserve">2.43599796295166</t>
   </si>
   <si>
     <t xml:space="preserve">2.41694235801697</t>
@@ -5462,7 +5462,7 @@
     <t xml:space="preserve">2.44220209121704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45328044891357</t>
+    <t xml:space="preserve">2.45328068733215</t>
   </si>
   <si>
     <t xml:space="preserve">2.45682597160339</t>
@@ -5474,7 +5474,7 @@
     <t xml:space="preserve">2.48873281478882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49139189720154</t>
+    <t xml:space="preserve">2.49139165878296</t>
   </si>
   <si>
     <t xml:space="preserve">2.46568894386292</t>
@@ -5489,7 +5489,7 @@
     <t xml:space="preserve">2.48430132865906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48164224624634</t>
+    <t xml:space="preserve">2.48164248466492</t>
   </si>
   <si>
     <t xml:space="preserve">2.53969502449036</t>
@@ -5501,7 +5501,7 @@
     <t xml:space="preserve">2.517094373703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49670958518982</t>
+    <t xml:space="preserve">2.49670934677124</t>
   </si>
   <si>
     <t xml:space="preserve">2.46879100799561</t>
@@ -5510,7 +5510,7 @@
     <t xml:space="preserve">2.50247049331665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4869601726532</t>
+    <t xml:space="preserve">2.48696041107178</t>
   </si>
   <si>
     <t xml:space="preserve">2.49538016319275</t>
@@ -5528,10 +5528,10 @@
     <t xml:space="preserve">2.52551436424255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5574209690094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56717038154602</t>
+    <t xml:space="preserve">2.55742120742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5671706199646</t>
   </si>
   <si>
     <t xml:space="preserve">2.6048378944397</t>
@@ -5564,10 +5564,10 @@
     <t xml:space="preserve">2.73601078987122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74974822998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72182989120483</t>
+    <t xml:space="preserve">2.74974846839905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72183012962341</t>
   </si>
   <si>
     <t xml:space="preserve">2.78475713729858</t>
@@ -5579,10 +5579,10 @@
     <t xml:space="preserve">2.81046009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86053609848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86186552047729</t>
+    <t xml:space="preserve">2.86053586006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86186575889587</t>
   </si>
   <si>
     <t xml:space="preserve">2.90352177619934</t>
@@ -5591,16 +5591,16 @@
     <t xml:space="preserve">2.899090051651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91858863830566</t>
+    <t xml:space="preserve">2.91858887672424</t>
   </si>
   <si>
     <t xml:space="preserve">2.92036128044128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94384860992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96511960029602</t>
+    <t xml:space="preserve">2.94384837150574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96511936187744</t>
   </si>
   <si>
     <t xml:space="preserve">2.96733522415161</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">3.01608204841614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00012826919556</t>
+    <t xml:space="preserve">3.00012850761414</t>
   </si>
   <si>
     <t xml:space="preserve">2.95049571990967</t>
@@ -5624,7 +5624,7 @@
     <t xml:space="preserve">2.97442579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93498539924622</t>
+    <t xml:space="preserve">2.93498563766479</t>
   </si>
   <si>
     <t xml:space="preserve">2.96910786628723</t>
@@ -5633,7 +5633,7 @@
     <t xml:space="preserve">2.90883946418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9159300327301</t>
+    <t xml:space="preserve">2.91592979431152</t>
   </si>
   <si>
     <t xml:space="preserve">2.94827961921692</t>
@@ -5648,25 +5648,25 @@
     <t xml:space="preserve">2.96866464614868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99303817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03868246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11933612823486</t>
+    <t xml:space="preserve">2.99303793907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03868269920349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11933588981628</t>
   </si>
   <si>
     <t xml:space="preserve">3.11712002754211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10471224784851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14636778831482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14016366004944</t>
+    <t xml:space="preserve">3.10471200942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1463680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14016389846802</t>
   </si>
   <si>
     <t xml:space="preserve">3.12509679794312</t>
@@ -5681,7 +5681,7 @@
     <t xml:space="preserve">3.15788984298706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18935394287109</t>
+    <t xml:space="preserve">3.18935370445251</t>
   </si>
   <si>
     <t xml:space="preserve">3.18492197990417</t>
@@ -5693,7 +5693,7 @@
     <t xml:space="preserve">3.19112634658813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21416997909546</t>
+    <t xml:space="preserve">3.21417021751404</t>
   </si>
   <si>
     <t xml:space="preserve">3.28197193145752</t>
@@ -5702,7 +5702,7 @@
     <t xml:space="preserve">3.30324339866638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30856132507324</t>
+    <t xml:space="preserve">3.30856108665466</t>
   </si>
   <si>
     <t xml:space="preserve">3.34046792984009</t>
@@ -6747,6 +6747,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.46199989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44899988174438</t>
   </si>
 </sst>
 </file>
@@ -71903,7 +71906,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6514699074</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>30245676</v>
@@ -71924,6 +71927,32 @@
         <v>2222</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6512037037</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>31669731</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>5.41599988937378</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>5.48999977111816</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>5.44899988174438</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>2245</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISP.MI.xlsx
+++ b/data/ISP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="2246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2247" uniqueCount="2247">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53063881397247</t>
+    <t xml:space="preserve">1.53063893318176</t>
   </si>
   <si>
     <t xml:space="preserve">ISP.MI</t>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">1.56040990352631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51831996440887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49265515804291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48752224445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46699059009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49676167964935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52447950839996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48546922206879</t>
+    <t xml:space="preserve">1.51831984519958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4926552772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48752248287201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46699070930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49676132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52447926998138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4854691028595</t>
   </si>
   <si>
     <t xml:space="preserve">1.43824636936188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36638510227203</t>
+    <t xml:space="preserve">1.36638498306274</t>
   </si>
   <si>
     <t xml:space="preserve">1.38075745105743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3047901391983</t>
+    <t xml:space="preserve">1.30479025840759</t>
   </si>
   <si>
     <t xml:space="preserve">1.36843836307526</t>
@@ -89,31 +89,31 @@
     <t xml:space="preserve">1.35406613349915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37254464626312</t>
+    <t xml:space="preserve">1.37254500389099</t>
   </si>
   <si>
     <t xml:space="preserve">1.35919892787933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29041814804077</t>
+    <t xml:space="preserve">1.29041802883148</t>
   </si>
   <si>
     <t xml:space="preserve">1.34380042552948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31505608558655</t>
+    <t xml:space="preserve">1.31505584716797</t>
   </si>
   <si>
     <t xml:space="preserve">1.26988613605499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2031581401825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27296614646912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22368979454041</t>
+    <t xml:space="preserve">1.20315837860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27296602725983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">1.17441380023956</t>
@@ -122,76 +122,76 @@
     <t xml:space="preserve">1.10152626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26064693927765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22984933853149</t>
+    <t xml:space="preserve">1.26064717769623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2298492193222</t>
   </si>
   <si>
     <t xml:space="preserve">1.25243425369263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28220510482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21958339214325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19494569301605</t>
+    <t xml:space="preserve">1.28220534324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21958363056183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19494557380676</t>
   </si>
   <si>
     <t xml:space="preserve">1.23395586013794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20110487937927</t>
+    <t xml:space="preserve">1.20110499858856</t>
   </si>
   <si>
     <t xml:space="preserve">1.16004145145416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18057322502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20007836818695</t>
+    <t xml:space="preserve">1.18057310581207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20007848739624</t>
   </si>
   <si>
     <t xml:space="preserve">1.20213150978088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22471642494202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27091264724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32224178314209</t>
+    <t xml:space="preserve">1.22471630573273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27091300487518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32224202156067</t>
   </si>
   <si>
     <t xml:space="preserve">1.29555070400238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26475346088409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27604568004608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144442081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30581665039062</t>
+    <t xml:space="preserve">1.26475322246552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27604579925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29144465923309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30581676959991</t>
   </si>
   <si>
     <t xml:space="preserve">1.40334224700928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37459778785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36022579669952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33045482635498</t>
+    <t xml:space="preserve">1.37459802627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36022567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33045494556427</t>
   </si>
   <si>
     <t xml:space="preserve">1.29349768161774</t>
@@ -203,25 +203,25 @@
     <t xml:space="preserve">1.29247105121613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2575671672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23600900173187</t>
+    <t xml:space="preserve">1.25756740570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23600876331329</t>
   </si>
   <si>
     <t xml:space="preserve">1.24935448169708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24114191532135</t>
+    <t xml:space="preserve">1.24114167690277</t>
   </si>
   <si>
     <t xml:space="preserve">1.21753025054932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18673276901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13540363311768</t>
+    <t xml:space="preserve">1.18673300743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13540351390839</t>
   </si>
   <si>
     <t xml:space="preserve">1.1487489938736</t>
@@ -230,22 +230,22 @@
     <t xml:space="preserve">1.11076557636261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17749357223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19802522659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24422144889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2503809928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25654053688049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26270020008087</t>
+    <t xml:space="preserve">1.17749345302582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1980254650116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2442215681076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25038123130798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25654065608978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26270008087158</t>
   </si>
   <si>
     <t xml:space="preserve">1.24216842651367</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">1.2780989408493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23190259933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26680672168732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26783311367035</t>
+    <t xml:space="preserve">1.23190271854401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26680636405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26783323287964</t>
   </si>
   <si>
     <t xml:space="preserve">1.18878602981567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16209483146667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13951003551483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14258980751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1497757434845</t>
+    <t xml:space="preserve">1.16209471225739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13950991630554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1425895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14977598190308</t>
   </si>
   <si>
     <t xml:space="preserve">1.15798842906952</t>
@@ -287,22 +287,22 @@
     <t xml:space="preserve">1.14156305789948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12924408912659</t>
+    <t xml:space="preserve">1.1292439699173</t>
   </si>
   <si>
     <t xml:space="preserve">1.12103140354156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15080225467682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17852008342743</t>
+    <t xml:space="preserve">1.15080213546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17852020263672</t>
   </si>
   <si>
     <t xml:space="preserve">1.18775928020477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18666672706604</t>
+    <t xml:space="preserve">1.18666660785675</t>
   </si>
   <si>
     <t xml:space="preserve">1.25878465175629</t>
@@ -314,31 +314,31 @@
     <t xml:space="preserve">1.2970290184021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26096975803375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24020862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23037457466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20852041244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20414972305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22491097450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21070599555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19977915287018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15060782432556</t>
+    <t xml:space="preserve">1.26096999645233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24020874500275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23037433624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20852053165436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20414960384369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22491085529327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2107058763504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1997789144516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15060794353485</t>
   </si>
   <si>
     <t xml:space="preserve">1.08286070823669</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">1.04516267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07466542720795</t>
+    <t xml:space="preserve">1.07466530799866</t>
   </si>
   <si>
     <t xml:space="preserve">1.06537759304047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11454892158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14842236042023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17683231830597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17573952674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23365259170532</t>
+    <t xml:space="preserve">1.11454880237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14842247962952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17683255672455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17573976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23365235328674</t>
   </si>
   <si>
     <t xml:space="preserve">0.950644612312317</t>
@@ -374,58 +374,58 @@
     <t xml:space="preserve">0.846838474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88726806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900380611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929883480072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917863726615906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88999992609024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870331585407257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868692457675934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874155938625336</t>
+    <t xml:space="preserve">0.887268245220184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900380551815033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929883420467377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917863607406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89000004529953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870331525802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868692338466644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874156057834625</t>
   </si>
   <si>
     <t xml:space="preserve">0.961571574211121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983425438404083</t>
+    <t xml:space="preserve">0.983425378799438</t>
   </si>
   <si>
     <t xml:space="preserve">1.04789435863495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03587472438812</t>
+    <t xml:space="preserve">1.0358749628067</t>
   </si>
   <si>
     <t xml:space="preserve">1.05772864818573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05499684810638</t>
+    <t xml:space="preserve">1.05499708652496</t>
   </si>
   <si>
     <t xml:space="preserve">1.05718231201172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05062627792358</t>
+    <t xml:space="preserve">1.05062615871429</t>
   </si>
   <si>
     <t xml:space="preserve">1.06373870372772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06701636314392</t>
+    <t xml:space="preserve">1.06701648235321</t>
   </si>
   <si>
     <t xml:space="preserve">1.06865561008453</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">1.04898703098297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05335772037506</t>
+    <t xml:space="preserve">1.05335783958435</t>
   </si>
   <si>
     <t xml:space="preserve">1.07193374633789</t>
@@ -443,73 +443,73 @@
     <t xml:space="preserve">1.03969931602478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07630443572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03860676288605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999269485473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993806004524231</t>
+    <t xml:space="preserve">1.07630455493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03860652446747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999269425868988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993805944919586</t>
   </si>
   <si>
     <t xml:space="preserve">0.994352340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03805994987488</t>
+    <t xml:space="preserve">1.03806006908417</t>
   </si>
   <si>
     <t xml:space="preserve">1.05117249488831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0560896396637</t>
+    <t xml:space="preserve">1.05608975887299</t>
   </si>
   <si>
     <t xml:space="preserve">1.07958245277405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05827498435974</t>
+    <t xml:space="preserve">1.05827510356903</t>
   </si>
   <si>
     <t xml:space="preserve">1.03041136264801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00964999198914</t>
+    <t xml:space="preserve">1.00965011119843</t>
   </si>
   <si>
     <t xml:space="preserve">1.05991411209106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09214842319489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08231449127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10034370422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08996307849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11673414707184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1637202501297</t>
+    <t xml:space="preserve">1.09214854240417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08231437206268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10034382343292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08996331691742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11673438549042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16372013092041</t>
   </si>
   <si>
     <t xml:space="preserve">1.19759345054626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19213008880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16809093952179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17901802062988</t>
+    <t xml:space="preserve">1.19212996959686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16809105873108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17901790142059</t>
   </si>
   <si>
     <t xml:space="preserve">1.18338859081268</t>
@@ -518,34 +518,34 @@
     <t xml:space="preserve">1.15934932231903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13749527931213</t>
+    <t xml:space="preserve">1.13749551773071</t>
   </si>
   <si>
     <t xml:space="preserve">1.13640260696411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12766098976135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09706568717957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11236321926117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12656843662262</t>
+    <t xml:space="preserve">1.12766110897064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09706556797028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11236345767975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12656855583191</t>
   </si>
   <si>
     <t xml:space="preserve">1.09050953388214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0779435634613</t>
+    <t xml:space="preserve">1.07794344425201</t>
   </si>
   <si>
     <t xml:space="preserve">1.06428480148315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06155300140381</t>
+    <t xml:space="preserve">1.0615531206131</t>
   </si>
   <si>
     <t xml:space="preserve">1.06319212913513</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">1.0784900188446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05445051193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08941662311554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0937876701355</t>
+    <t xml:space="preserve">1.05445063114166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08941686153412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09378778934479</t>
   </si>
   <si>
     <t xml:space="preserve">1.07685089111328</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">1.12329030036926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.130939245224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15170037746429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15388584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17792522907257</t>
+    <t xml:space="preserve">1.13093912601471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15170061588287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15388596057892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17792499065399</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196437835693</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">1.18229591846466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15279293060303</t>
+    <t xml:space="preserve">1.15279304981232</t>
   </si>
   <si>
     <t xml:space="preserve">1.13858807086945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09925103187561</t>
+    <t xml:space="preserve">1.0992511510849</t>
   </si>
   <si>
     <t xml:space="preserve">1.09597301483154</t>
@@ -605,31 +605,31 @@
     <t xml:space="preserve">1.16044223308563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16918361186981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22054016590118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21835494041443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15497851371765</t>
+    <t xml:space="preserve">1.1691837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22054004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21835482120514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15497863292694</t>
   </si>
   <si>
     <t xml:space="preserve">1.1418662071228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11891949176788</t>
+    <t xml:space="preserve">1.11891961097717</t>
   </si>
   <si>
     <t xml:space="preserve">1.10362195968628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06810927391052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11345601081848</t>
+    <t xml:space="preserve">1.0681095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11345613002777</t>
   </si>
   <si>
     <t xml:space="preserve">1.14514422416687</t>
@@ -638,55 +638,55 @@
     <t xml:space="preserve">1.24567198753357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26643347740173</t>
+    <t xml:space="preserve">1.26643371582031</t>
   </si>
   <si>
     <t xml:space="preserve">1.30904829502106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27845299243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32762432098389</t>
+    <t xml:space="preserve">1.27845311164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32762444019318</t>
   </si>
   <si>
     <t xml:space="preserve">1.29265797138214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33636605739594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31888258457184</t>
+    <t xml:space="preserve">1.33636593818665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31888270378113</t>
   </si>
   <si>
     <t xml:space="preserve">1.33745861053467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33855128288269</t>
+    <t xml:space="preserve">1.33855152130127</t>
   </si>
   <si>
     <t xml:space="preserve">1.3440146446228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33964371681213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871699333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31779003143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32543897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36805415153503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38772249221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39755666255951</t>
+    <t xml:space="preserve">1.33964383602142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871687412262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31778991222382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32543921470642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36805391311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38772261142731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39755690097809</t>
   </si>
   <si>
     <t xml:space="preserve">1.38990795612335</t>
@@ -698,40 +698,40 @@
     <t xml:space="preserve">1.34838545322418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34620034694672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34729266166687</t>
+    <t xml:space="preserve">1.34619998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34729290008545</t>
   </si>
   <si>
     <t xml:space="preserve">1.32216084003448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34292197227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34947824478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31014108657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25222814083099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25659918785095</t>
+    <t xml:space="preserve">1.34292185306549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34947836399078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31014132499695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25222849845886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25659894943237</t>
   </si>
   <si>
     <t xml:space="preserve">1.22928178310394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23911583423615</t>
+    <t xml:space="preserve">1.23911571502686</t>
   </si>
   <si>
     <t xml:space="preserve">1.20087158679962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18557405471802</t>
+    <t xml:space="preserve">1.18557393550873</t>
   </si>
   <si>
     <t xml:space="preserve">1.19103729724884</t>
@@ -740,61 +740,61 @@
     <t xml:space="preserve">1.22272551059723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19322288036346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17027616500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17355442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16590535640717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17136871814728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19650113582611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18120312690735</t>
+    <t xml:space="preserve">1.19322276115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17027628421783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1735543012619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16590559482574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17136895656586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19650089740753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18120300769806</t>
   </si>
   <si>
     <t xml:space="preserve">1.13421738147736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25113582611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27626752853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26861882209778</t>
+    <t xml:space="preserve">1.25113558769226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27626764774323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26861894130707</t>
   </si>
   <si>
     <t xml:space="preserve">1.27189695835114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27408218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30577027797699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34182929992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32325351238251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35057103633881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35603439807892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36914670467377</t>
+    <t xml:space="preserve">1.27408242225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30577051639557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34182953834534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3232536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35057079792023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3560346364975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36914682388306</t>
   </si>
   <si>
     <t xml:space="preserve">1.39100062847137</t>
@@ -803,31 +803,31 @@
     <t xml:space="preserve">1.38662981987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3833521604538</t>
+    <t xml:space="preserve">1.38335192203522</t>
   </si>
   <si>
     <t xml:space="preserve">1.37679553031921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38007354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37898075580597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37461018562317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36696112155914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384881496429</t>
+    <t xml:space="preserve">1.38007378578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37898087501526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37461030483246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36696147918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384905338287</t>
   </si>
   <si>
     <t xml:space="preserve">1.33199501037598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30467748641968</t>
+    <t xml:space="preserve">1.30467760562897</t>
   </si>
   <si>
     <t xml:space="preserve">1.35166358947754</t>
@@ -836,28 +836,28 @@
     <t xml:space="preserve">1.3604052066803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37351739406586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47623097896576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50573348999023</t>
+    <t xml:space="preserve">1.37351751327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47623062133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50573372840881</t>
   </si>
   <si>
     <t xml:space="preserve">1.49480664730072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45984053611755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46093320846558</t>
+    <t xml:space="preserve">1.45984017848969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46093332767487</t>
   </si>
   <si>
     <t xml:space="preserve">1.46311855316162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47076725959778</t>
+    <t xml:space="preserve">1.47076737880707</t>
   </si>
   <si>
     <t xml:space="preserve">1.50791871547699</t>
@@ -866,157 +866,157 @@
     <t xml:space="preserve">1.55271947383881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55818283557892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55599772930145</t>
+    <t xml:space="preserve">1.5581830739975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55599761009216</t>
   </si>
   <si>
     <t xml:space="preserve">1.55709004402161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54725587368011</t>
+    <t xml:space="preserve">1.5472559928894</t>
   </si>
   <si>
     <t xml:space="preserve">1.54507052898407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55162668228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52867996692657</t>
+    <t xml:space="preserve">1.55162632465363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52868020534515</t>
   </si>
   <si>
     <t xml:space="preserve">1.52212405204773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52977299690247</t>
+    <t xml:space="preserve">1.52977275848389</t>
   </si>
   <si>
     <t xml:space="preserve">1.56594586372375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57061350345612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56711292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55427742004395</t>
+    <t xml:space="preserve">1.57061338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56711304187775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55427694320679</t>
   </si>
   <si>
     <t xml:space="preserve">1.49826717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48893237113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48659861087799</t>
+    <t xml:space="preserve">1.48893225193024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659873008728</t>
   </si>
   <si>
     <t xml:space="preserve">1.50060093402863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51110291481018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49126601219177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48426485061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4994341135025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50876891613007</t>
+    <t xml:space="preserve">1.51110279560089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49126613140106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48426461219788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49943399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50876903533936</t>
   </si>
   <si>
     <t xml:space="preserve">1.50176787376404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50410163402557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49710023403168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47843050956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51460325717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52510547637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52627229690552</t>
+    <t xml:space="preserve">1.50410151481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49710059165955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47843027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51460349559784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5251053571701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52627241611481</t>
   </si>
   <si>
     <t xml:space="preserve">1.57994842529297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60795342922211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64062607288361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61845541000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61962234973907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66279637813568</t>
+    <t xml:space="preserve">1.60795378684998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64062583446503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61845529079437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6196221113205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66279673576355</t>
   </si>
   <si>
     <t xml:space="preserve">1.65929615497589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6721316576004</t>
+    <t xml:space="preserve">1.67213153839111</t>
   </si>
   <si>
     <t xml:space="preserve">1.65696227550507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66863119602203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65346157550812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66162979602814</t>
+    <t xml:space="preserve">1.66863083839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65346169471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66162967681885</t>
   </si>
   <si>
     <t xml:space="preserve">1.66396355628967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67096495628357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67446517944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66629719734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67329847812653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6838002204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69313538074493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69546902179718</t>
+    <t xml:space="preserve">1.67096471786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67446553707123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66629731655121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67329835891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68380033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69313549995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69546914100647</t>
   </si>
   <si>
     <t xml:space="preserve">1.69430232048035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69896984100342</t>
+    <t xml:space="preserve">1.69896948337555</t>
   </si>
   <si>
     <t xml:space="preserve">1.70130336284637</t>
@@ -1034,118 +1034,118 @@
     <t xml:space="preserve">1.70480406284332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68263363838196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6779659986496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66046261787415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70713770389557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68963491916656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64295959472656</t>
+    <t xml:space="preserve">1.68263351917267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67796611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66046297550201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70713794231415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68963468074799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64295971393585</t>
   </si>
   <si>
     <t xml:space="preserve">1.65462851524353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65812921524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63712537288666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66513061523438</t>
+    <t xml:space="preserve">1.6581289768219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63712513446808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66513049602509</t>
   </si>
   <si>
     <t xml:space="preserve">1.68146669864655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70013666152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71063816547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71763956546783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73280930519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73397576808929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72464108467102</t>
+    <t xml:space="preserve">1.70013654232025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71063840389252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7176399230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73280894756317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73397588729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7246413230896</t>
   </si>
   <si>
     <t xml:space="preserve">1.73514270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74447786808014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7421441078186</t>
+    <t xml:space="preserve">1.74447798728943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74214434623718</t>
   </si>
   <si>
     <t xml:space="preserve">1.74564456939697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74681162834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74097764492035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71180510520935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71530604362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7094714641571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68496716022491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66746413707733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68029987812042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597100257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67913293838501</t>
+    <t xml:space="preserve">1.74681174755096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74097728729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71180534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7153058052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70947158336639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6849672794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66746425628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68029975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597088336945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67913269996643</t>
   </si>
   <si>
     <t xml:space="preserve">1.65112781524658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.633624792099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63479137420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61728870868683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.614954829216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64412665367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61378800868988</t>
+    <t xml:space="preserve">1.63362467288971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6347918510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61728847026825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61495471000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64412677288055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61378788948059</t>
   </si>
   <si>
     <t xml:space="preserve">1.64529359340668</t>
@@ -1157,22 +1157,22 @@
     <t xml:space="preserve">1.67563211917877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63829219341278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62895739078522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62662363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62779033184052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61612164974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60678648948669</t>
+    <t xml:space="preserve">1.63829255104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62895727157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62662351131439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6277904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61612141132355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60678660869598</t>
   </si>
   <si>
     <t xml:space="preserve">1.60445296764374</t>
@@ -1181,10 +1181,10 @@
     <t xml:space="preserve">1.74331104755402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76548182964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77248299121857</t>
+    <t xml:space="preserve">1.76548147201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77248275279999</t>
   </si>
   <si>
     <t xml:space="preserve">1.77598321437836</t>
@@ -1193,31 +1193,31 @@
     <t xml:space="preserve">1.78415155410767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80515539646149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80165481567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82382524013519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82499217987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79815399646759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82149171829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84366238117218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8582478761673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83549380302429</t>
+    <t xml:space="preserve">1.80515563488007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80165493488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82382559776306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8249922990799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79815423488617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82149124145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8436621427536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824811458588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83549427986145</t>
   </si>
   <si>
     <t xml:space="preserve">1.84395396709442</t>
@@ -1226,127 +1226,127 @@
     <t xml:space="preserve">1.83111822605133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81769931316376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902899265289</t>
+    <t xml:space="preserve">1.81769895553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902911186218</t>
   </si>
   <si>
     <t xml:space="preserve">1.81098973751068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87283396720886</t>
+    <t xml:space="preserve">1.87283408641815</t>
   </si>
   <si>
     <t xml:space="preserve">1.83636927604675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81157326698303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377841949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80923938751221</t>
+    <t xml:space="preserve">1.81157302856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377853870392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923962593079</t>
   </si>
   <si>
     <t xml:space="preserve">1.80690550804138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83053505420685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81303203105927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223786830902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8074893951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7844432592392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79873740673065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79990434646606</t>
+    <t xml:space="preserve">1.83053529262543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81303179264069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8022381067276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80748891830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78444314002991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79873752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79990446567535</t>
   </si>
   <si>
     <t xml:space="preserve">1.80982279777527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80632221698761</t>
+    <t xml:space="preserve">1.80632209777832</t>
   </si>
   <si>
     <t xml:space="preserve">1.79290318489075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75410437583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72930836677551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74535298347473</t>
+    <t xml:space="preserve">1.75410461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72930812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74535286426544</t>
   </si>
   <si>
     <t xml:space="preserve">1.76518976688385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77510833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78035938739777</t>
+    <t xml:space="preserve">1.77510821819305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78035926818848</t>
   </si>
   <si>
     <t xml:space="preserve">1.77539992332458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74885356426239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7608140707016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79523718357086</t>
+    <t xml:space="preserve">1.74885380268097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76081395149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79523682594299</t>
   </si>
   <si>
     <t xml:space="preserve">1.77364993095398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78473496437073</t>
+    <t xml:space="preserve">1.78473508358002</t>
   </si>
   <si>
     <t xml:space="preserve">1.77423322200775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74272775650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72259914875031</t>
+    <t xml:space="preserve">1.74272763729095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72259902954102</t>
   </si>
   <si>
     <t xml:space="preserve">1.70742964744568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72289085388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72318232059479</t>
+    <t xml:space="preserve">1.72289073467255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72318267822266</t>
   </si>
   <si>
     <t xml:space="preserve">1.72522437572479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71909809112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75206255912781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74768686294556</t>
+    <t xml:space="preserve">1.71909844875336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75206303596497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74768674373627</t>
   </si>
   <si>
     <t xml:space="preserve">1.76256442070007</t>
@@ -1358,94 +1358,94 @@
     <t xml:space="preserve">1.75906372070312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77948403358459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78940260410309</t>
+    <t xml:space="preserve">1.77948379516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78940236568451</t>
   </si>
   <si>
     <t xml:space="preserve">1.79465341567993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81449043750763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8153657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8290764093399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84832990169525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86437439918518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83987009525299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85124695301056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83957827091217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84191238880157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84862124919891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83811962604523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84453737735748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83403551578522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82674264907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83782815933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85416376590729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80865597724915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7943617105484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031244754791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73967397212982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75156378746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72090029716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70494282245636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65081286430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59730851650238</t>
+    <t xml:space="preserve">1.81449019908905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81536555290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82907593250275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84832978248596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86437451839447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986961841583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85124719142914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83957803249359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84191167354584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84862112998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8381199836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84453749656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83403563499451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8267422914505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83782780170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85416400432587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80865585803986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79436182975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031232833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73967373371124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75156402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7209005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70494294166565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6508127450943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59730863571167</t>
   </si>
   <si>
     <t xml:space="preserve">1.53191435337067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57759618759155</t>
+    <t xml:space="preserve">1.57759606838226</t>
   </si>
   <si>
     <t xml:space="preserve">1.57352876663208</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">1.62546861171722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62515556812286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56289064884186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55475521087646</t>
+    <t xml:space="preserve">1.62515568733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56289052963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55475533008575</t>
   </si>
   <si>
     <t xml:space="preserve">1.53629469871521</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">1.51752126216888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61827206611633</t>
+    <t xml:space="preserve">1.61827230453491</t>
   </si>
   <si>
     <t xml:space="preserve">1.6173335313797</t>
@@ -1478,67 +1478,67 @@
     <t xml:space="preserve">1.62578153610229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62327837944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59417974948883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59793436527252</t>
+    <t xml:space="preserve">1.62327873706818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59417927265167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59793424606323</t>
   </si>
   <si>
     <t xml:space="preserve">1.60575652122498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63548135757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60325336456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61952376365662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56695818901062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55068790912628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5269079208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55694556236267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55600678920746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54474294185638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57634484767914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58416712284088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60513079166412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6029406785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60606944561005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58041250705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54881024360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53066289424896</t>
+    <t xml:space="preserve">1.63548111915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60325348377228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56695795059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55068755149841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690815925598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55694568157196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55600690841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54474246501923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57634472846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58416700363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60513091087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60294079780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60606956481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58041274547577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54881036281586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53066265583038</t>
   </si>
   <si>
     <t xml:space="preserve">1.53973650932312</t>
@@ -1547,25 +1547,25 @@
     <t xml:space="preserve">1.53660762310028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5519392490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54161381721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51658284664154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50531828403473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250267982483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53097558021545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55037462711334</t>
+    <t xml:space="preserve">1.55193948745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54161417484283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51658236980438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5053186416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53097581863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55037498474121</t>
   </si>
   <si>
     <t xml:space="preserve">1.57039999961853</t>
@@ -1580,28 +1580,28 @@
     <t xml:space="preserve">1.57259011268616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51188910007477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53003704547882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50844752788544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49249029159546</t>
+    <t xml:space="preserve">1.51188933849335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53003668785095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50844740867615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4924898147583</t>
   </si>
   <si>
     <t xml:space="preserve">1.43804705142975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41426730155945</t>
+    <t xml:space="preserve">1.41426718235016</t>
   </si>
   <si>
     <t xml:space="preserve">1.4017516374588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37640762329102</t>
+    <t xml:space="preserve">1.37640738487244</t>
   </si>
   <si>
     <t xml:space="preserve">1.36576902866364</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">1.35732102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40331625938416</t>
+    <t xml:space="preserve">1.40331614017487</t>
   </si>
   <si>
     <t xml:space="preserve">1.38329112529755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37672030925751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37891054153442</t>
+    <t xml:space="preserve">1.3767204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37891066074371</t>
   </si>
   <si>
     <t xml:space="preserve">1.37859761714935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36357891559601</t>
+    <t xml:space="preserve">1.3635790348053</t>
   </si>
   <si>
     <t xml:space="preserve">1.38172650337219</t>
@@ -1634,85 +1634,85 @@
     <t xml:space="preserve">1.34918582439423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3313512802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35857272148132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897319793701</t>
+    <t xml:space="preserve">1.33135116100311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3585729598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897295951843</t>
   </si>
   <si>
     <t xml:space="preserve">1.4590106010437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43929862976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41583168506622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47997438907623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.456507563591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46432995796204</t>
+    <t xml:space="preserve">1.43929851055145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41583180427551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47997450828552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45650768280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46432983875275</t>
   </si>
   <si>
     <t xml:space="preserve">1.45744609832764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46683299541473</t>
+    <t xml:space="preserve">1.46683311462402</t>
   </si>
   <si>
     <t xml:space="preserve">1.50093793869019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49906051158905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51908576488495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51157629489899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53222715854645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49999940395355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54568159580231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52221441268921</t>
+    <t xml:space="preserve">1.49906063079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51908564567566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51157641410828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53222703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49999952316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5456817150116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52221465110779</t>
   </si>
   <si>
     <t xml:space="preserve">1.50438010692596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37734615802765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32352876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31914865970612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32634472846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35481786727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31320333480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27033722400665</t>
+    <t xml:space="preserve">1.37734603881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32352900505066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31914854049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32634484767914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35481798648834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31320357322693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27033746242523</t>
   </si>
   <si>
     <t xml:space="preserve">1.298184633255</t>
@@ -1724,40 +1724,40 @@
     <t xml:space="preserve">1.27284061908722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26783430576324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27753400802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29536879062653</t>
+    <t xml:space="preserve">1.26783454418182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27753388881683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29536855220795</t>
   </si>
   <si>
     <t xml:space="preserve">1.28066277503967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23842239379883</t>
+    <t xml:space="preserve">1.23842251300812</t>
   </si>
   <si>
     <t xml:space="preserve">1.24167656898499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23128879070282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23166406154633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18936121463776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22227740287781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21264040470123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24943625926971</t>
+    <t xml:space="preserve">1.23128855228424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23166418075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18936109542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22227728366852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21264028549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.249436378479</t>
   </si>
   <si>
     <t xml:space="preserve">1.24655759334564</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">1.22215223312378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24267768859863</t>
+    <t xml:space="preserve">1.24267792701721</t>
   </si>
   <si>
     <t xml:space="preserve">1.25563156604767</t>
@@ -1775,55 +1775,55 @@
     <t xml:space="preserve">1.2366703748703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25250267982483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28598201274872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26971161365509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25500583648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22665762901306</t>
+    <t xml:space="preserve">1.25250256061554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28598213195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26971173286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25500571727753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22665798664093</t>
   </si>
   <si>
     <t xml:space="preserve">1.25312840938568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23829734325409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22265303134918</t>
+    <t xml:space="preserve">1.23829746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2226527929306</t>
   </si>
   <si>
     <t xml:space="preserve">1.20112597942352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20538127422333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17571926116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20901095867157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20888555049896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22165143489838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27690804004669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27628231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28535616397858</t>
+    <t xml:space="preserve">1.20538115501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17571914196014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20901083946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20888578891754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22165167331696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27690815925598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27628242969513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28535628318787</t>
   </si>
   <si>
     <t xml:space="preserve">1.27190184593201</t>
@@ -1835,13 +1835,13 @@
     <t xml:space="preserve">1.32196438312531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29161393642426</t>
+    <t xml:space="preserve">1.29161381721497</t>
   </si>
   <si>
     <t xml:space="preserve">1.30193936824799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23491811752319</t>
+    <t xml:space="preserve">1.23491823673248</t>
   </si>
   <si>
     <t xml:space="preserve">1.24029994010925</t>
@@ -1850,31 +1850,31 @@
     <t xml:space="preserve">1.21376669406891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21026217937469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25969898700714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27158892154694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26032495498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23466801643372</t>
+    <t xml:space="preserve">1.21026241779327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25969910621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27158904075623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26032483577728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23466777801514</t>
   </si>
   <si>
     <t xml:space="preserve">1.2421772480011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26345384120941</t>
+    <t xml:space="preserve">1.2634539604187</t>
   </si>
   <si>
     <t xml:space="preserve">1.21714603900909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19662034511566</t>
+    <t xml:space="preserve">1.19662010669708</t>
   </si>
   <si>
     <t xml:space="preserve">1.19461786746979</t>
@@ -1883,34 +1883,34 @@
     <t xml:space="preserve">1.21389186382294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19299101829529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18986189365387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25106334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27221477031708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25750875473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26470541954041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25844752788544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24017465114594</t>
+    <t xml:space="preserve">1.19299066066742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18986177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25106346607208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27221488952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25750887393951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26470518112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25844776630402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24017477035522</t>
   </si>
   <si>
     <t xml:space="preserve">1.22465538978577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2600120306015</t>
+    <t xml:space="preserve">1.26001214981079</t>
   </si>
   <si>
     <t xml:space="preserve">1.27565658092499</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">1.27596950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26814723014832</t>
+    <t xml:space="preserve">1.26814711093903</t>
   </si>
   <si>
     <t xml:space="preserve">1.26908600330353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29192698001862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28003704547882</t>
+    <t xml:space="preserve">1.29192709922791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28003692626953</t>
   </si>
   <si>
     <t xml:space="preserve">1.28191447257996</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">1.24830985069275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22815978527069</t>
+    <t xml:space="preserve">1.2281596660614</t>
   </si>
   <si>
     <t xml:space="preserve">1.22753393650055</t>
@@ -1949,73 +1949,73 @@
     <t xml:space="preserve">1.24705839157104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24180161952972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23616969585419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25131356716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2553186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24155139923096</t>
+    <t xml:space="preserve">1.2418018579483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23616981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25131368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25531852245331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24155151844025</t>
   </si>
   <si>
     <t xml:space="preserve">1.28097569942474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29223990440369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28629493713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28692054748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2765953540802</t>
+    <t xml:space="preserve">1.2922397851944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2862948179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28692066669464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27659523487091</t>
   </si>
   <si>
     <t xml:space="preserve">1.27784693241119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30444252490997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.299436211586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3338543176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3504376411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513091087341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35262763500214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36545634269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33510601520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32603192329407</t>
+    <t xml:space="preserve">1.30444276332855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29943633079529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33385443687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35043752193451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513079166412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35262775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36545610427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33510589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32603204250336</t>
   </si>
   <si>
     <t xml:space="preserve">1.33760917186737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33667027950287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34824728965759</t>
+    <t xml:space="preserve">1.33667016029358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34824752807617</t>
   </si>
   <si>
     <t xml:space="preserve">1.35794699192047</t>
@@ -2027,133 +2027,133 @@
     <t xml:space="preserve">1.39737129211426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3992486000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39549398422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38610696792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34949898719788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480547904968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136390686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3516891002655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35419237613678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38016211986542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3754688501358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3876713514328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39799690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39956152439117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39017450809479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39830982685089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43992447853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45337879657745</t>
+    <t xml:space="preserve">1.39924848079681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39549374580383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38610708713531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34949886798859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480535984039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136366844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35168921947479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35419225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38016200065613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37546873092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38767147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39799678325653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39956140518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39017474651337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39830958843231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4399242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45337867736816</t>
   </si>
   <si>
     <t xml:space="preserve">1.46558153629303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45963656902313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45244014263153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42365407943726</t>
+    <t xml:space="preserve">1.45963633060455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45244002342224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42365396022797</t>
   </si>
   <si>
     <t xml:space="preserve">1.42490553855896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42991185188293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45932352542877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46245241165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45619475841522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45306575298309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4327278137207</t>
+    <t xml:space="preserve">1.42991197109222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45932364463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46245217323303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45619451999664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4530656337738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43272769451141</t>
   </si>
   <si>
     <t xml:space="preserve">1.40300321578979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38673293590546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35450494289398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35137617588043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3254063129425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34543132781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36639475822449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35825979709625</t>
+    <t xml:space="preserve">1.38673281669617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35450506210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35137605667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32540619373322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34543120861053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36639511585236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35825991630554</t>
   </si>
   <si>
     <t xml:space="preserve">1.36135697364807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36066877841949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33630442619324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30973827838898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3206125497818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31331706047058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29872632026672</t>
+    <t xml:space="preserve">1.36066865921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3363049030304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30973815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32061243057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31331717967987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29872620105743</t>
   </si>
   <si>
     <t xml:space="preserve">1.28413534164429</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">1.28372240066528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26211142539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25674307346344</t>
+    <t xml:space="preserve">1.26211130619049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25674295425415</t>
   </si>
   <si>
     <t xml:space="preserve">1.28441059589386</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">1.2570184469223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26142299175262</t>
+    <t xml:space="preserve">1.26142311096191</t>
   </si>
   <si>
     <t xml:space="preserve">1.27037036418915</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">1.2713338136673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25811958312988</t>
+    <t xml:space="preserve">1.25811946392059</t>
   </si>
   <si>
     <t xml:space="preserve">1.26775503158569</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">1.2645890712738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2601842880249</t>
+    <t xml:space="preserve">1.26018416881561</t>
   </si>
   <si>
     <t xml:space="preserve">1.2893660068512</t>
@@ -2204,43 +2204,43 @@
     <t xml:space="preserve">1.312628865242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30134165287018</t>
+    <t xml:space="preserve">1.30134153366089</t>
   </si>
   <si>
     <t xml:space="preserve">1.29046726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29032945632935</t>
+    <t xml:space="preserve">1.29032957553864</t>
   </si>
   <si>
     <t xml:space="preserve">1.28592479228973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29239439964294</t>
+    <t xml:space="preserve">1.29239416122437</t>
   </si>
   <si>
     <t xml:space="preserve">1.29294490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29528510570526</t>
+    <t xml:space="preserve">1.29528498649597</t>
   </si>
   <si>
     <t xml:space="preserve">1.28537404537201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29734981060028</t>
+    <t xml:space="preserve">1.29734969139099</t>
   </si>
   <si>
     <t xml:space="preserve">1.36328399181366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39439284801483</t>
+    <t xml:space="preserve">1.39439308643341</t>
   </si>
   <si>
     <t xml:space="preserve">1.39852237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38854265213013</t>
+    <t xml:space="preserve">1.38854277133942</t>
   </si>
   <si>
     <t xml:space="preserve">1.38097202777863</t>
@@ -2252,70 +2252,70 @@
     <t xml:space="preserve">1.41469621658325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41159915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40987849235535</t>
+    <t xml:space="preserve">1.41159927845001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40987861156464</t>
   </si>
   <si>
     <t xml:space="preserve">1.41916978359222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40609288215637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41091072559357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38200438022614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3844131231308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40058732032776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39026355743408</t>
+    <t xml:space="preserve">1.40609312057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41091084480286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38200426101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38441324234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40058720111847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3902633190155</t>
   </si>
   <si>
     <t xml:space="preserve">1.38338088989258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37044179439545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35309791564941</t>
+    <t xml:space="preserve">1.37044191360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3530980348587</t>
   </si>
   <si>
     <t xml:space="preserve">1.34924376010895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37649834156036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34387528896332</t>
+    <t xml:space="preserve">1.37649822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34387516975403</t>
   </si>
   <si>
     <t xml:space="preserve">1.35433673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33836925029755</t>
+    <t xml:space="preserve">1.33836936950684</t>
   </si>
   <si>
     <t xml:space="preserve">1.31455600261688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33891999721527</t>
+    <t xml:space="preserve">1.33891975879669</t>
   </si>
   <si>
     <t xml:space="preserve">1.26362550258636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29886388778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2702329158783</t>
+    <t xml:space="preserve">1.29886400699615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27023279666901</t>
   </si>
   <si>
     <t xml:space="preserve">1.31744658946991</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">1.32322800159454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33644211292267</t>
+    <t xml:space="preserve">1.33644223213196</t>
   </si>
   <si>
     <t xml:space="preserve">1.30987572669983</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">1.33520352840424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34084713459015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35488724708557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38578975200653</t>
+    <t xml:space="preserve">1.34084725379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35488736629486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38578987121582</t>
   </si>
   <si>
     <t xml:space="preserve">1.37181830406189</t>
@@ -2351,85 +2351,85 @@
     <t xml:space="preserve">1.37890720367432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37684237957001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39542508125305</t>
+    <t xml:space="preserve">1.37684273719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39542520046234</t>
   </si>
   <si>
     <t xml:space="preserve">1.4150402545929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42261099815369</t>
+    <t xml:space="preserve">1.42261111736298</t>
   </si>
   <si>
     <t xml:space="preserve">1.44635570049286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46149718761444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45082938671112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46080899238586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50175964832306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47526228427887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46252942085266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46321761608124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48937141895294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49074757099152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319734096527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46597099304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46941220760345</t>
+    <t xml:space="preserve">1.46149730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45082950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46080887317657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50175952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47526216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46252954006195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46321773529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48937129974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4907478094101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319746017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4659708738327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46941196918488</t>
   </si>
   <si>
     <t xml:space="preserve">1.47491788864136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48696255683899</t>
+    <t xml:space="preserve">1.48696231842041</t>
   </si>
   <si>
     <t xml:space="preserve">1.49728608131409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4831770658493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44119393825531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43912923336029</t>
+    <t xml:space="preserve">1.48317694664001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4411940574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43912899494171</t>
   </si>
   <si>
     <t xml:space="preserve">1.44222617149353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43568766117096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44773232936859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47939157485962</t>
+    <t xml:space="preserve">1.43568801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44773209095001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47939169406891</t>
   </si>
   <si>
     <t xml:space="preserve">1.50451278686523</t>
@@ -2438,16 +2438,16 @@
     <t xml:space="preserve">1.50038325786591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52103066444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54064583778381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53582787513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53789281845093</t>
+    <t xml:space="preserve">1.52103078365326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54064571857452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53582799434662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53789258003235</t>
   </si>
   <si>
     <t xml:space="preserve">1.55062556266785</t>
@@ -2456,73 +2456,73 @@
     <t xml:space="preserve">1.56576693058014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56232583522797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56301367282867</t>
+    <t xml:space="preserve">1.56232571601868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56301403045654</t>
   </si>
   <si>
     <t xml:space="preserve">1.56404650211334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56817603111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56370210647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54752850532532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54580783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56439018249512</t>
+    <t xml:space="preserve">1.56817579269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56370222568512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54752838611603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54580760002136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56439030170441</t>
   </si>
   <si>
     <t xml:space="preserve">1.58710253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6105033159256</t>
+    <t xml:space="preserve">1.61050307750702</t>
   </si>
   <si>
     <t xml:space="preserve">1.60878252983093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62151503562927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256766319275</t>
+    <t xml:space="preserve">1.62151515483856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256790161133</t>
   </si>
   <si>
     <t xml:space="preserve">1.62220346927643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63665652275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61394429206848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60086762905121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60912644863129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61738538742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61566495895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62013864517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61291217803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61910617351532</t>
+    <t xml:space="preserve">1.63665676116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61394441127777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60086739063263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60912680625916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61738562583923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61566507816315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62013876438141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61291182041168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61910629272461</t>
   </si>
   <si>
     <t xml:space="preserve">1.61187970638275</t>
@@ -2534,67 +2534,67 @@
     <t xml:space="preserve">1.58985567092896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58331704139709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5451192855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5767787694931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57471442222595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59226477146149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58090841770172</t>
+    <t xml:space="preserve">1.58331739902496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54511940479279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57677900791168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57471418380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5922646522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58090829849243</t>
   </si>
   <si>
     <t xml:space="preserve">1.58572614192963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59054398536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60224437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61497676372528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62633299827576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6283974647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6380330324173</t>
+    <t xml:space="preserve">1.59054410457611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60224413871765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6149765253067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62633311748505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62839734554291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63803315162659</t>
   </si>
   <si>
     <t xml:space="preserve">1.65523934364319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65214228630066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62082695960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61635339260101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63872134685516</t>
+    <t xml:space="preserve">1.65214252471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62082707881927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61635327339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63872122764587</t>
   </si>
   <si>
     <t xml:space="preserve">1.6170414686203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63390374183655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61119151115417</t>
+    <t xml:space="preserve">1.63390362262726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61119115352631</t>
   </si>
   <si>
     <t xml:space="preserve">1.61532080173492</t>
@@ -2603,19 +2603,19 @@
     <t xml:space="preserve">1.59673821926117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59845888614655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60809433460236</t>
+    <t xml:space="preserve">1.59845876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60809421539307</t>
   </si>
   <si>
     <t xml:space="preserve">1.59570586681366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56920790672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56094896793365</t>
+    <t xml:space="preserve">1.56920802593231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56094920635223</t>
   </si>
   <si>
     <t xml:space="preserve">1.56783175468445</t>
@@ -2624,22 +2624,22 @@
     <t xml:space="preserve">1.552001953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58675837516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57712304592133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54546356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57264935970306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61841797828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68586647510529</t>
+    <t xml:space="preserve">1.58675861358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57712292671204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5454638004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57264959812164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61841809749603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.685866355896</t>
   </si>
   <si>
     <t xml:space="preserve">1.70100796222687</t>
@@ -2654,88 +2654,88 @@
     <t xml:space="preserve">1.70857858657837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72578489780426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72750544548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74815285205841</t>
+    <t xml:space="preserve">1.72578501701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72750532627106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7481529712677</t>
   </si>
   <si>
     <t xml:space="preserve">1.78944790363312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79185664653778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75503551959991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73542046546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63562405109406</t>
+    <t xml:space="preserve">1.79185676574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75503528118134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73542034626007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63562393188477</t>
   </si>
   <si>
     <t xml:space="preserve">1.6036205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57505822181702</t>
+    <t xml:space="preserve">1.5750584602356</t>
   </si>
   <si>
     <t xml:space="preserve">1.51311564445496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47044432163239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45840001106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46425008773804</t>
+    <t xml:space="preserve">1.47044444084167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45840013027191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46425020694733</t>
   </si>
   <si>
     <t xml:space="preserve">1.40850186347961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36080634593964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20443594455719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17608022689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2245329618454</t>
+    <t xml:space="preserve">1.36080646514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20443618297577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1760801076889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22453308105469</t>
   </si>
   <si>
     <t xml:space="preserve">1.00677084922791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06981444358826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965475916862488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998925089836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969467639923096</t>
+    <t xml:space="preserve">1.06981456279755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965475857257843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998924911022186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96946793794632</t>
   </si>
   <si>
     <t xml:space="preserve">0.980892717838287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00856053829193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997135162353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08991158008575</t>
+    <t xml:space="preserve">1.00856029987335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997135519981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08991146087646</t>
   </si>
   <si>
     <t xml:space="preserve">1.11234831809998</t>
@@ -2747,58 +2747,58 @@
     <t xml:space="preserve">1.07821118831635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01227700710297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02438998222351</t>
+    <t xml:space="preserve">1.01227676868439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0243901014328</t>
   </si>
   <si>
     <t xml:space="preserve">0.987500011920929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989564538002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914820909500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00360476970673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01103794574738</t>
+    <t xml:space="preserve">0.989564657211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914820730686188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00360488891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01103806495667</t>
   </si>
   <si>
     <t xml:space="preserve">0.997410774230957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99452006816864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96781599521637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928035080432892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936156690120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947168588638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951848685741425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908488929271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921015024185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952812135219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924869179725647</t>
+    <t xml:space="preserve">0.994520127773285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967816114425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928035259246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936156511306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947168409824371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95184862613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908489048480988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921015083789825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952812194824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924869358539581</t>
   </si>
   <si>
     <t xml:space="preserve">0.960245192050934</t>
@@ -2807,58 +2807,58 @@
     <t xml:space="preserve">0.996034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01888418197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979378521442413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947031021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998649597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97745156288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966577053070068</t>
+    <t xml:space="preserve">1.01888406276703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979378581047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947030901908875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998649477958679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977451622486115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966577172279358</t>
   </si>
   <si>
     <t xml:space="preserve">0.973184406757355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970018446445465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977864444255829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959144294261932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952261626720428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95239919424057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999475419521332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984747052192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990390598773956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978690385818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994244933128357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00319194793701</t>
+    <t xml:space="preserve">0.97001838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977864265441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959144175052643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952261686325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95239931344986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999475657939911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984746992588043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990390539169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978690445423126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994244754314423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0031920671463</t>
   </si>
   <si>
     <t xml:space="preserve">1.0331996679306</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">1.05880260467529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07270526885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0684380531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08743357658386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11840486526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15157866477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16575646400452</t>
+    <t xml:space="preserve">1.07270503044128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06843817234039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08743369579315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11840498447418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15157854557037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16575634479523</t>
   </si>
   <si>
     <t xml:space="preserve">1.22012805938721</t>
@@ -2891,76 +2891,76 @@
     <t xml:space="preserve">1.24118864536285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18378865718842</t>
+    <t xml:space="preserve">1.18378853797913</t>
   </si>
   <si>
     <t xml:space="preserve">1.17181313037872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11344945430756</t>
+    <t xml:space="preserve">1.11344933509827</t>
   </si>
   <si>
     <t xml:space="preserve">1.11634027957916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11950612068176</t>
+    <t xml:space="preserve">1.11950623989105</t>
   </si>
   <si>
     <t xml:space="preserve">1.16947317123413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17263877391815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16025066375732</t>
+    <t xml:space="preserve">1.17263913154602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16025042533875</t>
   </si>
   <si>
     <t xml:space="preserve">1.15956223011017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15791058540344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17786979675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14717376232147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14249360561371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17140018939972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17250144481659</t>
+    <t xml:space="preserve">1.15791046619415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17786967754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14717364311218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14249348640442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17140030860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1725013256073</t>
   </si>
   <si>
     <t xml:space="preserve">1.16355407238007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20636320114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20223355293274</t>
+    <t xml:space="preserve">1.20636308193207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20223367214203</t>
   </si>
   <si>
     <t xml:space="preserve">1.23348021507263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22962594032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.213383436203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19149708747864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21503508090973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22604715824127</t>
+    <t xml:space="preserve">1.22962605953217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21338331699371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19149684906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21503496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22604703903198</t>
   </si>
   <si>
     <t xml:space="preserve">1.2257719039917</t>
@@ -2969,58 +2969,58 @@
     <t xml:space="preserve">1.24875938892365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26596570014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26073479652405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27628910541534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29721212387085</t>
+    <t xml:space="preserve">1.26596558094025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26073503494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27628934383392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29721200466156</t>
   </si>
   <si>
     <t xml:space="preserve">1.29129302501678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27271032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24944758415222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23981213569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22935080528259</t>
+    <t xml:space="preserve">1.27271044254303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24944770336151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23981201648712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22935056686401</t>
   </si>
   <si>
     <t xml:space="preserve">1.23155319690704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19411218166351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17497897148132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17566740512848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23444354534149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26252448558807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24834609031677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24256503582001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24848401546478</t>
+    <t xml:space="preserve">1.1941123008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17497909069061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17566728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23444390296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26252436637878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24834620952606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2425651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24848413467407</t>
   </si>
   <si>
     <t xml:space="preserve">1.28096950054169</t>
@@ -3038,16 +3038,16 @@
     <t xml:space="preserve">1.25564169883728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24903464317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26981961727142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24999833106995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24683225154877</t>
+    <t xml:space="preserve">1.24903452396393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26981985569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24999809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24683213233948</t>
   </si>
   <si>
     <t xml:space="preserve">1.2658280134201</t>
@@ -3059,106 +3059,106 @@
     <t xml:space="preserve">1.26816785335541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24146389961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25605487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24242734909058</t>
+    <t xml:space="preserve">1.24146401882172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25605475902557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24242746829987</t>
   </si>
   <si>
     <t xml:space="preserve">1.24008738994598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22425758838654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22412014007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23458158969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21269488334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23210370540619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23967468738556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22439539432526</t>
+    <t xml:space="preserve">1.22425782680511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22412002086639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23458135128021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21269500255585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2321035861969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23967456817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22439527511597</t>
   </si>
   <si>
     <t xml:space="preserve">1.21737515926361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2114565372467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19989347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18020987510681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1257004737854</t>
+    <t xml:space="preserve">1.21145629882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19989371299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18020963668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12570023536682</t>
   </si>
   <si>
     <t xml:space="preserve">1.12996757030487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10959529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10670483112335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08674538135529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1181298494339</t>
+    <t xml:space="preserve">1.10959541797638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10670471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08674550056458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11812961101532</t>
   </si>
   <si>
     <t xml:space="preserve">1.10587882995605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1032634973526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09183847904205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09596788883209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1240485906601</t>
+    <t xml:space="preserve">1.10326337814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09183871746063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09596800804138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12404870986938</t>
   </si>
   <si>
     <t xml:space="preserve">1.14827501773834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13478529453278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15309286117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15557050704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14978909492493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11317420005798</t>
+    <t xml:space="preserve">1.13478517532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15309262275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15557038784027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14978897571564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11317443847656</t>
   </si>
   <si>
     <t xml:space="preserve">1.05825197696686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07077813148499</t>
+    <t xml:space="preserve">1.0707780122757</t>
   </si>
   <si>
     <t xml:space="preserve">1.07353103160858</t>
@@ -3167,52 +3167,52 @@
     <t xml:space="preserve">1.05701315402985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05770146846771</t>
+    <t xml:space="preserve">1.05770134925842</t>
   </si>
   <si>
     <t xml:space="preserve">1.07449471950531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05095648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02590429782867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975937366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962998270988464</t>
+    <t xml:space="preserve">1.05095660686493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0259040594101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975937306880951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96299821138382</t>
   </si>
   <si>
     <t xml:space="preserve">0.977038621902466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02026045322418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06031656265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09968459606171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12680160999298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11276137828827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21531057357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26926910877228</t>
+    <t xml:space="preserve">1.02026057243347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06031668186188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.099684715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12680149078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11276113986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2153103351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26926922798157</t>
   </si>
   <si>
     <t xml:space="preserve">1.25591707229614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24022495746613</t>
+    <t xml:space="preserve">1.24022507667542</t>
   </si>
   <si>
     <t xml:space="preserve">1.25109934806824</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">1.31868553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33671760559082</t>
+    <t xml:space="preserve">1.33671748638153</t>
   </si>
   <si>
     <t xml:space="preserve">1.32777047157288</t>
@@ -3245,10 +3245,10 @@
     <t xml:space="preserve">1.35653913021088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36700046062469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37002885341644</t>
+    <t xml:space="preserve">1.36700057983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37002897262573</t>
   </si>
   <si>
     <t xml:space="preserve">1.35667681694031</t>
@@ -3260,46 +3260,46 @@
     <t xml:space="preserve">1.35998046398163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3495192527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231282234192</t>
+    <t xml:space="preserve">1.34951901435852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231270313263</t>
   </si>
   <si>
     <t xml:space="preserve">1.3346529006958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35929214954376</t>
+    <t xml:space="preserve">1.35929226875305</t>
   </si>
   <si>
     <t xml:space="preserve">1.33726811408997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33823192119598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33189964294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29473435878754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31662058830261</t>
+    <t xml:space="preserve">1.3382316827774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33189976215363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29473447799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31662082672119</t>
   </si>
   <si>
     <t xml:space="preserve">1.32309019565582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32130086421967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31634533405304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31125247478485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29693686962128</t>
+    <t xml:space="preserve">1.32130074501038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31634545326233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31125235557556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29693675041199</t>
   </si>
   <si>
     <t xml:space="preserve">1.35447454452515</t>
@@ -3308,31 +3308,31 @@
     <t xml:space="preserve">1.34552717208862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33713066577911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33396458625793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31799709796906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30904972553253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31951129436493</t>
+    <t xml:space="preserve">1.33713054656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33396446704865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31799721717834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30904984474182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31951141357422</t>
   </si>
   <si>
     <t xml:space="preserve">1.31483125686646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32584321498871</t>
+    <t xml:space="preserve">1.325843334198</t>
   </si>
   <si>
     <t xml:space="preserve">1.29679906368256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25481581687927</t>
+    <t xml:space="preserve">1.25481605529785</t>
   </si>
   <si>
     <t xml:space="preserve">1.26610314846039</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">1.24407923221588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26197385787964</t>
+    <t xml:space="preserve">1.26197373867035</t>
   </si>
   <si>
     <t xml:space="preserve">1.25399005413055</t>
@@ -3350,16 +3350,16 @@
     <t xml:space="preserve">1.28771424293518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34291183948517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38234865665436</t>
+    <t xml:space="preserve">1.34291195869446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38234877586365</t>
   </si>
   <si>
     <t xml:space="preserve">1.41848170757294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43844091892242</t>
+    <t xml:space="preserve">1.43844068050385</t>
   </si>
   <si>
     <t xml:space="preserve">1.43637609481812</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">1.43603181838989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44257032871246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4573677778244</t>
+    <t xml:space="preserve">1.44257020950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45736765861511</t>
   </si>
   <si>
     <t xml:space="preserve">1.45392632484436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45117354393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44532322883606</t>
+    <t xml:space="preserve">1.45117342472076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44532334804535</t>
   </si>
   <si>
     <t xml:space="preserve">1.45358240604401</t>
@@ -3395,61 +3395,61 @@
     <t xml:space="preserve">1.4687237739563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48661828041077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48283278942108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51621282100677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50864207744598</t>
+    <t xml:space="preserve">1.48661839962006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48283314704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51621294021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50864219665527</t>
   </si>
   <si>
     <t xml:space="preserve">1.51036274433136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56198155879974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56507849693298</t>
+    <t xml:space="preserve">1.56198167800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56507861614227</t>
   </si>
   <si>
     <t xml:space="preserve">1.55991685390472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56955230236053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55888438224792</t>
+    <t xml:space="preserve">1.56955218315125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5588846206665</t>
   </si>
   <si>
     <t xml:space="preserve">1.57884347438812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59329676628113</t>
+    <t xml:space="preserve">1.59329688549042</t>
   </si>
   <si>
     <t xml:space="preserve">1.61669731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59260845184326</t>
+    <t xml:space="preserve">1.59260857105255</t>
   </si>
   <si>
     <t xml:space="preserve">1.58194077014923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57540237903595</t>
+    <t xml:space="preserve">1.57540249824524</t>
   </si>
   <si>
     <t xml:space="preserve">1.57987606525421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57918775081635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58125245571136</t>
+    <t xml:space="preserve">1.57918798923492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58125233650208</t>
   </si>
   <si>
     <t xml:space="preserve">1.57333767414093</t>
@@ -3458,46 +3458,46 @@
     <t xml:space="preserve">1.59914684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59019958972931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59536170959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58503770828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55750799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5509694814682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5557873249054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56989645957947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5279129743576</t>
+    <t xml:space="preserve">1.5901997089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59536194801331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58503794670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55750811100006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55096971988678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55578744411469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56989622116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52791333198547</t>
   </si>
   <si>
     <t xml:space="preserve">1.53204274177551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52860128879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5805641412735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59501731395721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59742629528046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60637390613556</t>
+    <t xml:space="preserve">1.52860140800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58056426048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59501779079437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59742641448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60637378692627</t>
   </si>
   <si>
     <t xml:space="preserve">1.58847916126251</t>
@@ -3506,22 +3506,22 @@
     <t xml:space="preserve">1.62357985973358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62564444541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64457154273987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63837742805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63975358009338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63287127017975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64319503307343</t>
+    <t xml:space="preserve">1.6256445646286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64457130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63837730884552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63975346088409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63287115097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.643195271492</t>
   </si>
   <si>
     <t xml:space="preserve">1.65868079662323</t>
@@ -3533,67 +3533,67 @@
     <t xml:space="preserve">1.65116310119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64976537227631</t>
+    <t xml:space="preserve">1.6497654914856</t>
   </si>
   <si>
     <t xml:space="preserve">1.63928401470184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67282450199127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68330562114716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68854653835297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70881044864655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72767674922943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73012256622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73326706886292</t>
+    <t xml:space="preserve">1.67282438278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68330574035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68854641914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70881032943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72767663002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73012244701385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73326671123505</t>
   </si>
   <si>
     <t xml:space="preserve">1.73676061630249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71894216537476</t>
+    <t xml:space="preserve">1.71894252300262</t>
   </si>
   <si>
     <t xml:space="preserve">1.71440029144287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70426845550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69448578357697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71195495128632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71265363693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68749809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63788640499115</t>
+    <t xml:space="preserve">1.7042680978775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69448566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71195471286774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7126532793045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68749845027924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63788676261902</t>
   </si>
   <si>
     <t xml:space="preserve">1.65360856056213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63648891448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61832129955292</t>
+    <t xml:space="preserve">1.63648903369904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61832141876221</t>
   </si>
   <si>
     <t xml:space="preserve">1.65186166763306</t>
@@ -3605,61 +3605,61 @@
     <t xml:space="preserve">1.62775444984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64662063121796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64592218399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63229620456696</t>
+    <t xml:space="preserve">1.64662075042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64592206478119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63229644298553</t>
   </si>
   <si>
     <t xml:space="preserve">1.65535545349121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6214656829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60958659648895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56242060661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5959609746933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61098420619965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58617854118347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59631049633026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57639598846436</t>
+    <t xml:space="preserve">1.62146580219269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60958671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56242072582245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59596109390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61098444461823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58617842197418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59631025791168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57639575004578</t>
   </si>
   <si>
     <t xml:space="preserve">1.55962586402893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49359321594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52259147167206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56277024745941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255280017853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59665977954865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63334465026855</t>
+    <t xml:space="preserve">1.49359345436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52259159088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56277012825012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255256175995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59666001796722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63334453105927</t>
   </si>
   <si>
     <t xml:space="preserve">1.61657452583313</t>
@@ -3671,40 +3671,40 @@
     <t xml:space="preserve">1.6399827003479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62915217876434</t>
+    <t xml:space="preserve">1.62915182113647</t>
   </si>
   <si>
     <t xml:space="preserve">1.61727333068848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62565815448761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63509154319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63858509063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67596876621246</t>
+    <t xml:space="preserve">1.6256582736969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63509130477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63858532905579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67596864700317</t>
   </si>
   <si>
     <t xml:space="preserve">1.68016123771667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68260681629181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71125566959381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71055722236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69204008579254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66898131370544</t>
+    <t xml:space="preserve">1.68260705471039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71125602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71055734157562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69203972816467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66898107528687</t>
   </si>
   <si>
     <t xml:space="preserve">1.68225765228271</t>
@@ -3716,37 +3716,37 @@
     <t xml:space="preserve">1.66304171085358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67002952098846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66164422035217</t>
+    <t xml:space="preserve">1.67002940177917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66164445877075</t>
   </si>
   <si>
     <t xml:space="preserve">1.67526996135712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68365478515625</t>
+    <t xml:space="preserve">1.68365490436554</t>
   </si>
   <si>
     <t xml:space="preserve">1.66828262805939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67911303043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66548776626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64836776256561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65710258483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63963341712952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66758346557617</t>
+    <t xml:space="preserve">1.67911338806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66548752784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6483678817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65710234642029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63963317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66758358478546</t>
   </si>
   <si>
     <t xml:space="preserve">1.66094553470612</t>
@@ -3761,187 +3761,187 @@
     <t xml:space="preserve">1.62251377105713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65815019607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69623279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69413661956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732734680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69763052463531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7182434797287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74898886680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7294237613678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75388014316559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75912082195282</t>
+    <t xml:space="preserve">1.65815007686615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69623255729675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69413638114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732710838318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69763004779816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71824336051941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74898910522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72942352294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7538800239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7591210603714</t>
   </si>
   <si>
     <t xml:space="preserve">1.74933838844299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75562715530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74339866638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76331329345703</t>
+    <t xml:space="preserve">1.75562739372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74339878559113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76331341266632</t>
   </si>
   <si>
     <t xml:space="preserve">1.79929947853088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81100189685822</t>
+    <t xml:space="preserve">1.8110020160675</t>
   </si>
   <si>
     <t xml:space="preserve">1.78156363964081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79319357872009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77720260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78192698955536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79028630256653</t>
+    <t xml:space="preserve">1.79319393634796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7772022485733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78192710876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79028618335724</t>
   </si>
   <si>
     <t xml:space="preserve">1.80373299121857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78301739692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77211427688599</t>
+    <t xml:space="preserve">1.78301763534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77211403846741</t>
   </si>
   <si>
     <t xml:space="preserve">1.78628826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81354594230652</t>
+    <t xml:space="preserve">1.81354606151581</t>
   </si>
   <si>
     <t xml:space="preserve">1.82590305805206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81863415241241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78556144237518</t>
+    <t xml:space="preserve">1.8186342716217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78556168079376</t>
   </si>
   <si>
     <t xml:space="preserve">1.80518710613251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8117288351059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7957376241684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80046236515045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79682791233063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79646480083466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80991172790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80446016788483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8040965795517</t>
+    <t xml:space="preserve">1.81172895431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573750495911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80046212673187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79682779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646444320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80991160869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80446004867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80409669876099</t>
   </si>
   <si>
     <t xml:space="preserve">1.73286330699921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74418127536774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72544276714325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7258175611496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71494936943054</t>
+    <t xml:space="preserve">1.74418103694916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72544288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72581768035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71494925022125</t>
   </si>
   <si>
     <t xml:space="preserve">1.61638462543488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60626566410065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.585653424263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62537908554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6096385717392</t>
+    <t xml:space="preserve">1.60626554489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58565330505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62537896633148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60963869094849</t>
   </si>
   <si>
     <t xml:space="preserve">1.60888910293579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6587336063385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69246292114258</t>
+    <t xml:space="preserve">1.65873384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69246304035187</t>
   </si>
   <si>
     <t xml:space="preserve">1.6722252368927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66772818565369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66060745716095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6527373790741</t>
+    <t xml:space="preserve">1.6677280664444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66060769557953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65273725986481</t>
   </si>
   <si>
     <t xml:space="preserve">1.66735327243805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65011394023895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68084526062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311205387115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63549780845642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67334973812103</t>
+    <t xml:space="preserve">1.65011382102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68084502220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311193466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63549768924713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67334961891174</t>
   </si>
   <si>
     <t xml:space="preserve">1.67185044288635</t>
@@ -3953,76 +3953,76 @@
     <t xml:space="preserve">1.69583594799042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71157622337341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70670413970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70445549488068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75767290592194</t>
+    <t xml:space="preserve">1.71157610416412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70670437812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70445561408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7576732635498</t>
   </si>
   <si>
     <t xml:space="preserve">1.7944004535675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81238925457001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82363247871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83749902248383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84611904621124</t>
+    <t xml:space="preserve">1.8123893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82363271713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83749914169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84611892700195</t>
   </si>
   <si>
     <t xml:space="preserve">1.86036002635956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90795600414276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91919887065887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9203234910965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93194127082825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93006718158722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89933621883392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91245305538177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91282784938812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8487423658371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86560678482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92219722270966</t>
+    <t xml:space="preserve">1.90795624256134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91919898986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92032372951508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93194139003754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93006706237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89933586120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91245353221893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9128280878067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84874224662781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86560702323914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92219734191895</t>
   </si>
   <si>
     <t xml:space="preserve">1.95817530155182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94655740261078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96342194080353</t>
+    <t xml:space="preserve">1.94655692577362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96342182159424</t>
   </si>
   <si>
     <t xml:space="preserve">2.00127387046814</t>
@@ -4031,16 +4031,16 @@
     <t xml:space="preserve">2.02151131629944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04474687576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99902522563934</t>
+    <t xml:space="preserve">2.04474711418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99902534484863</t>
   </si>
   <si>
     <t xml:space="preserve">2.03500294685364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07585334777832</t>
+    <t xml:space="preserve">2.07585310935974</t>
   </si>
   <si>
     <t xml:space="preserve">2.1388144493103</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">2.18865895271301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07435393333435</t>
+    <t xml:space="preserve">2.07435369491577</t>
   </si>
   <si>
     <t xml:space="preserve">2.13843965530396</t>
@@ -4061,40 +4061,40 @@
     <t xml:space="preserve">2.05299210548401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04024958610535</t>
+    <t xml:space="preserve">2.04024982452393</t>
   </si>
   <si>
     <t xml:space="preserve">2.00427198410034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99377834796906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9641717672348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80789220333099</t>
+    <t xml:space="preserve">1.99377846717834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96417140960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8078920841217</t>
   </si>
   <si>
     <t xml:space="preserve">1.85698711872101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71907162666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5864030122757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60851442813873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56204295158386</t>
+    <t xml:space="preserve">1.71907150745392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58640289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60851430892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56204283237457</t>
   </si>
   <si>
     <t xml:space="preserve">1.42127907276154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38155341148376</t>
+    <t xml:space="preserve">1.38155353069305</t>
   </si>
   <si>
     <t xml:space="preserve">1.39834320545197</t>
@@ -4103,13 +4103,13 @@
     <t xml:space="preserve">1.55342316627502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4352205991745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43866860866547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49158620834351</t>
+    <t xml:space="preserve">1.43522047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43866837024689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49158608913422</t>
   </si>
   <si>
     <t xml:space="preserve">1.50507771968842</t>
@@ -4118,37 +4118,37 @@
     <t xml:space="preserve">1.61001348495483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55304825305939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56354188919067</t>
+    <t xml:space="preserve">1.55304837226868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56354200839996</t>
   </si>
   <si>
     <t xml:space="preserve">1.54892587661743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57403540611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53505957126617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52231705188751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52381634712219</t>
+    <t xml:space="preserve">1.57403552532196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53505945205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5223171710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5238162279129</t>
   </si>
   <si>
     <t xml:space="preserve">1.53243613243103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61975753307343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59951984882355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56166803836823</t>
+    <t xml:space="preserve">1.61975765228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59952008724213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56166815757751</t>
   </si>
   <si>
     <t xml:space="preserve">1.57778322696686</t>
@@ -4160,19 +4160,19 @@
     <t xml:space="preserve">1.53056216239929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48573982715607</t>
+    <t xml:space="preserve">1.48573958873749</t>
   </si>
   <si>
     <t xml:space="preserve">1.46280360221863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48558974266052</t>
+    <t xml:space="preserve">1.48558962345123</t>
   </si>
   <si>
     <t xml:space="preserve">1.48469030857086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45500862598419</t>
+    <t xml:space="preserve">1.4550085067749</t>
   </si>
   <si>
     <t xml:space="preserve">1.4572571516037</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">1.47734475135803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47884392738342</t>
+    <t xml:space="preserve">1.47884380817413</t>
   </si>
   <si>
     <t xml:space="preserve">1.51444697380066</t>
@@ -4190,19 +4190,19 @@
     <t xml:space="preserve">1.51782011985779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48618948459625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46055507659912</t>
+    <t xml:space="preserve">1.48618924617767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46055519580841</t>
   </si>
   <si>
     <t xml:space="preserve">1.43761920928955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4397177696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44361543655396</t>
+    <t xml:space="preserve">1.43971788883209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44361531734467</t>
   </si>
   <si>
     <t xml:space="preserve">1.46520221233368</t>
@@ -4211,46 +4211,46 @@
     <t xml:space="preserve">1.44091701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46924960613251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44301569461823</t>
+    <t xml:space="preserve">1.46924984455109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4430159330368</t>
   </si>
   <si>
     <t xml:space="preserve">1.44256603717804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40913665294647</t>
+    <t xml:space="preserve">1.40913653373718</t>
   </si>
   <si>
     <t xml:space="preserve">1.3716596364975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39534509181976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45410919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47074902057648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47839403152466</t>
+    <t xml:space="preserve">1.39534485340118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45410907268524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47074890136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47839415073395</t>
   </si>
   <si>
     <t xml:space="preserve">1.46490240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49188578128815</t>
+    <t xml:space="preserve">1.49188590049744</t>
   </si>
   <si>
     <t xml:space="preserve">1.49008703231812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48633921146393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54183983802795</t>
+    <t xml:space="preserve">1.48633933067322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54184007644653</t>
   </si>
   <si>
     <t xml:space="preserve">1.54496228694916</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">1.60139966011047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59788680076599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6076443195343</t>
+    <t xml:space="preserve">1.59788691997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60764443874359</t>
   </si>
   <si>
     <t xml:space="preserve">1.58500695228577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56119871139526</t>
+    <t xml:space="preserve">1.56119883060455</t>
   </si>
   <si>
     <t xml:space="preserve">1.54012250900269</t>
@@ -4283,16 +4283,16 @@
     <t xml:space="preserve">1.5631502866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55339276790619</t>
+    <t xml:space="preserve">1.5533926486969</t>
   </si>
   <si>
     <t xml:space="preserve">1.5352828502655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42193984985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3730742931366</t>
+    <t xml:space="preserve">1.42193973064423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37307417392731</t>
   </si>
   <si>
     <t xml:space="preserve">1.38166093826294</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">1.44520163536072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39961457252502</t>
+    <t xml:space="preserve">1.3996148109436</t>
   </si>
   <si>
     <t xml:space="preserve">1.40788888931274</t>
@@ -4310,10 +4310,10 @@
     <t xml:space="preserve">1.46175038814545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47221040725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46799516677856</t>
+    <t xml:space="preserve">1.47221052646637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46799504756927</t>
   </si>
   <si>
     <t xml:space="preserve">1.43630278110504</t>
@@ -4322,22 +4322,22 @@
     <t xml:space="preserve">1.46924412250519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47798669338226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48204600811005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46440434455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38946688175201</t>
+    <t xml:space="preserve">1.47798681259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48204588890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46440446376801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38946676254272</t>
   </si>
   <si>
     <t xml:space="preserve">1.37978744506836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34669005870819</t>
+    <t xml:space="preserve">1.34669017791748</t>
   </si>
   <si>
     <t xml:space="preserve">1.30469369888306</t>
@@ -4346,19 +4346,19 @@
     <t xml:space="preserve">1.31000185012817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36230218410492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37588441371918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35199797153473</t>
+    <t xml:space="preserve">1.36230206489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37588429450989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35199809074402</t>
   </si>
   <si>
     <t xml:space="preserve">1.33295142650604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3276435136795</t>
+    <t xml:space="preserve">1.32764339447021</t>
   </si>
   <si>
     <t xml:space="preserve">1.25411093235016</t>
@@ -4367,49 +4367,49 @@
     <t xml:space="preserve">1.27393817901611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30672323703766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38369035720825</t>
+    <t xml:space="preserve">1.30672335624695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38369047641754</t>
   </si>
   <si>
     <t xml:space="preserve">1.33513724803925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2981368303299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29579496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31765162944794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29329717159271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30922114849091</t>
+    <t xml:space="preserve">1.29813671112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29579484462738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31765174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29329705238342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3092212677002</t>
   </si>
   <si>
     <t xml:space="preserve">1.3315464258194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34934389591217</t>
+    <t xml:space="preserve">1.34934401512146</t>
   </si>
   <si>
     <t xml:space="preserve">1.36542439460754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36370694637299</t>
+    <t xml:space="preserve">1.36370718479156</t>
   </si>
   <si>
     <t xml:space="preserve">1.38462710380554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39180850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41600728034973</t>
+    <t xml:space="preserve">1.39180862903595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41600739955902</t>
   </si>
   <si>
     <t xml:space="preserve">1.41850507259369</t>
@@ -4424,10 +4424,10 @@
     <t xml:space="preserve">1.44707500934601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44785559177399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42740404605865</t>
+    <t xml:space="preserve">1.44785571098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42740392684937</t>
   </si>
   <si>
     <t xml:space="preserve">1.42615509033203</t>
@@ -4436,19 +4436,19 @@
     <t xml:space="preserve">1.38415884971619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34138202667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36573672294617</t>
+    <t xml:space="preserve">1.34138190746307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36573660373688</t>
   </si>
   <si>
     <t xml:space="preserve">1.37666499614716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3569940328598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.315309882164</t>
+    <t xml:space="preserve">1.35699379444122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31530976295471</t>
   </si>
   <si>
     <t xml:space="preserve">1.32811176776886</t>
@@ -4457,16 +4457,16 @@
     <t xml:space="preserve">1.34996855258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34497284889221</t>
+    <t xml:space="preserve">1.34497261047363</t>
   </si>
   <si>
     <t xml:space="preserve">1.32217919826508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3568377494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32467699050903</t>
+    <t xml:space="preserve">1.35683786869049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32467710971832</t>
   </si>
   <si>
     <t xml:space="preserve">1.32998514175415</t>
@@ -4475,10 +4475,10 @@
     <t xml:space="preserve">1.32701897621155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35855519771576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43099474906921</t>
+    <t xml:space="preserve">1.35855507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43099462985992</t>
   </si>
   <si>
     <t xml:space="preserve">1.48001635074615</t>
@@ -4490,28 +4490,28 @@
     <t xml:space="preserve">1.48329496383667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4987508058548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49484765529633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49515998363495</t>
+    <t xml:space="preserve">1.49875068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49484777450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49516010284424</t>
   </si>
   <si>
     <t xml:space="preserve">1.44348430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43364870548248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44567000865936</t>
+    <t xml:space="preserve">1.43364882469177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44567012786865</t>
   </si>
   <si>
     <t xml:space="preserve">1.37697744369507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38041174411774</t>
+    <t xml:space="preserve">1.38041186332703</t>
   </si>
   <si>
     <t xml:space="preserve">1.34825122356415</t>
@@ -4520,58 +4520,58 @@
     <t xml:space="preserve">1.32592606544495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29189193248749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32920455932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35355925559998</t>
+    <t xml:space="preserve">1.2918918132782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32920467853546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35355913639069</t>
   </si>
   <si>
     <t xml:space="preserve">1.39571166038513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35917949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33654224872589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33139038085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3234281539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30781614780426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33201479911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3366984128952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36058485507965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40726470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852178096771</t>
+    <t xml:space="preserve">1.35917961597443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3365421295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3313901424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32342803478241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30781602859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33201467990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33669829368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36058473587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40726459026337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.398521900177</t>
   </si>
   <si>
     <t xml:space="preserve">1.4277161359787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42662346363068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44863629341125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45550560951233</t>
+    <t xml:space="preserve">1.42662334442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44863617420197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45550549030304</t>
   </si>
   <si>
     <t xml:space="preserve">1.45644235610962</t>
@@ -4580,70 +4580,70 @@
     <t xml:space="preserve">1.48766624927521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48719787597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50577628612518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51842188835144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51810967922211</t>
+    <t xml:space="preserve">1.48719775676727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50577616691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51842176914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51810956001282</t>
   </si>
   <si>
     <t xml:space="preserve">1.53746843338013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61193752288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66189610958099</t>
+    <t xml:space="preserve">1.61193764209747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66189587116241</t>
   </si>
   <si>
     <t xml:space="preserve">1.67672753334045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68141102790833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69936490058899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68648481369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678067207336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70951271057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70990312099457</t>
+    <t xml:space="preserve">1.6814112663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6993647813797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68648493289948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70951247215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70990288257599</t>
   </si>
   <si>
     <t xml:space="preserve">1.70014524459839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73019850254059</t>
+    <t xml:space="preserve">1.73019862174988</t>
   </si>
   <si>
     <t xml:space="preserve">1.72882580757141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74457168579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73165202140808</t>
+    <t xml:space="preserve">1.74457180500031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73165214061737</t>
   </si>
   <si>
     <t xml:space="preserve">1.7441680431366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74295663833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70863854885101</t>
+    <t xml:space="preserve">1.74295651912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70863842964172</t>
   </si>
   <si>
     <t xml:space="preserve">1.72357714176178</t>
@@ -4661,25 +4661,25 @@
     <t xml:space="preserve">1.67835807800293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66866815090179</t>
+    <t xml:space="preserve">1.6686680316925</t>
   </si>
   <si>
     <t xml:space="preserve">1.664630651474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66140067577362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66907179355621</t>
+    <t xml:space="preserve">1.66140079498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6690719127655</t>
   </si>
   <si>
     <t xml:space="preserve">1.67028307914734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69652652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68562543392181</t>
+    <t xml:space="preserve">1.69652664661407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68562531471252</t>
   </si>
   <si>
     <t xml:space="preserve">1.61044836044312</t>
@@ -4691,13 +4691,13 @@
     <t xml:space="preserve">1.64282846450806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67593550682068</t>
+    <t xml:space="preserve">1.67593538761139</t>
   </si>
   <si>
     <t xml:space="preserve">1.69612264633179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68279933929443</t>
+    <t xml:space="preserve">1.68279910087585</t>
   </si>
   <si>
     <t xml:space="preserve">1.68966269493103</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">1.68118417263031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67997288703918</t>
+    <t xml:space="preserve">1.6799727678299</t>
   </si>
   <si>
     <t xml:space="preserve">1.70137131214142</t>
@@ -4715,91 +4715,91 @@
     <t xml:space="preserve">1.67795419692993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71429097652435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75426149368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79948055744171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78857946395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80351805686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81684148311615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82451260089874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84429597854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8475261926651</t>
+    <t xml:space="preserve">1.71429085731506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75426137447357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.799480676651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78857958316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8035181760788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81684172153473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82451283931732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84429621696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84752607345581</t>
   </si>
   <si>
     <t xml:space="preserve">1.84510362148285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82572388648987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79503977298737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76072144508362</t>
+    <t xml:space="preserve">1.82572400569916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79503953456879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76072156429291</t>
   </si>
   <si>
     <t xml:space="preserve">1.80836308002472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84550750255585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317862033844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89153397083282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89839780330658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89274537563324</t>
+    <t xml:space="preserve">1.84550738334656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85317850112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89153373241425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89839792251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89274549484253</t>
   </si>
   <si>
     <t xml:space="preserve">1.94603931903839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98076117038727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9823762178421</t>
+    <t xml:space="preserve">1.98076128959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98237609863281</t>
   </si>
   <si>
     <t xml:space="preserve">1.92423725128174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97591626644135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99327719211578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99368095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02194285392761</t>
+    <t xml:space="preserve">1.97591614723206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9932769536972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99368107318878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02194261550903</t>
   </si>
   <si>
     <t xml:space="preserve">2.00014066696167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01790571212769</t>
+    <t xml:space="preserve">2.01790547370911</t>
   </si>
   <si>
     <t xml:space="preserve">2.02073168754578</t>
@@ -4808,16 +4808,16 @@
     <t xml:space="preserve">2.01467537879944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05989480018616</t>
+    <t xml:space="preserve">2.05989503860474</t>
   </si>
   <si>
     <t xml:space="preserve">2.07079601287842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06231689453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06150984764099</t>
+    <t xml:space="preserve">2.06231737136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06150960922241</t>
   </si>
   <si>
     <t xml:space="preserve">1.99973714351654</t>
@@ -4826,19 +4826,19 @@
     <t xml:space="preserve">2.0300178527832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04536008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06837344169617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04858994483948</t>
+    <t xml:space="preserve">2.04535984992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06837320327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0485897064209</t>
   </si>
   <si>
     <t xml:space="preserve">2.05262732505798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07887077331543</t>
+    <t xml:space="preserve">2.07887029647827</t>
   </si>
   <si>
     <t xml:space="preserve">2.09340524673462</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">2.07119941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0772557258606</t>
+    <t xml:space="preserve">2.07725548744202</t>
   </si>
   <si>
     <t xml:space="preserve">2.04414892196655</t>
@@ -4856,19 +4856,19 @@
     <t xml:space="preserve">2.00417828559875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88184416294098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94482815265656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81159317493439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8152266740799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77081525325775</t>
+    <t xml:space="preserve">1.8818439245224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94482791423798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81159281730652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81522655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77081513404846</t>
   </si>
   <si>
     <t xml:space="preserve">1.83702886104584</t>
@@ -4877,10 +4877,10 @@
     <t xml:space="preserve">1.90162754058838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89193749427795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255799770355</t>
+    <t xml:space="preserve">1.89193785190582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87255835533142</t>
   </si>
   <si>
     <t xml:space="preserve">1.82733905315399</t>
@@ -4889,31 +4889,31 @@
     <t xml:space="preserve">1.83420264720917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85196709632874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87982571125031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90970253944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91172122955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86448323726654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90405011177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91939234733582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.934330701828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92827475070953</t>
+    <t xml:space="preserve">1.85196733474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87982559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90970242023468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91172158718109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86448335647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90405023097992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91939258575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93433082103729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92827439308167</t>
   </si>
   <si>
     <t xml:space="preserve">1.97147500514984</t>
@@ -4928,13 +4928,13 @@
     <t xml:space="preserve">2.01023459434509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00619673728943</t>
+    <t xml:space="preserve">2.00619697570801</t>
   </si>
   <si>
     <t xml:space="preserve">2.02436518669128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98722088336945</t>
+    <t xml:space="preserve">1.98722100257874</t>
   </si>
   <si>
     <t xml:space="preserve">1.96541893482208</t>
@@ -4943,61 +4943,61 @@
     <t xml:space="preserve">1.98479866981506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92544841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88022923469543</t>
+    <t xml:space="preserve">1.925448179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88022935390472</t>
   </si>
   <si>
     <t xml:space="preserve">1.91293251514435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89395654201508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96380388736725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883616924286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98358714580536</t>
+    <t xml:space="preserve">1.89395642280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96380412578583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883605003357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98358750343323</t>
   </si>
   <si>
     <t xml:space="preserve">1.95048046112061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93917560577393</t>
+    <t xml:space="preserve">1.93917548656464</t>
   </si>
   <si>
     <t xml:space="preserve">1.96057403087616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9545179605484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94038689136505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92948567867279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95128786563873</t>
+    <t xml:space="preserve">1.95451784133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94038712978363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9294855594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95128798484802</t>
   </si>
   <si>
     <t xml:space="preserve">1.96353375911713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96437251567841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88888430595398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88804543018341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88301289081573</t>
+    <t xml:space="preserve">1.9643726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88888442516327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8880455493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88301301002502</t>
   </si>
   <si>
     <t xml:space="preserve">1.86665725708008</t>
@@ -5009,22 +5009,22 @@
     <t xml:space="preserve">1.80794405937195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87043154239655</t>
+    <t xml:space="preserve">1.87043166160583</t>
   </si>
   <si>
     <t xml:space="preserve">1.90524017810822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89475572109222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91698288917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93166100978851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94927477836609</t>
+    <t xml:space="preserve">1.89475560188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91698276996613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9316611289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94927489757538</t>
   </si>
   <si>
     <t xml:space="preserve">1.93711280822754</t>
@@ -5033,64 +5033,64 @@
     <t xml:space="preserve">1.93417716026306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93920993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97108244895935</t>
+    <t xml:space="preserve">1.93921005725861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97108268737793</t>
   </si>
   <si>
     <t xml:space="preserve">1.97779285907745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99037384986877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00840759277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00169730186462</t>
+    <t xml:space="preserve">1.99037396907806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00840735435486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0016975402832</t>
   </si>
   <si>
     <t xml:space="preserve">2.01805305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99540627002716</t>
+    <t xml:space="preserve">1.99540638923645</t>
   </si>
   <si>
     <t xml:space="preserve">1.95850133895874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95598495006561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98072850704193</t>
+    <t xml:space="preserve">1.9559850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98072838783264</t>
   </si>
   <si>
     <t xml:space="preserve">1.9824059009552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00127792358398</t>
+    <t xml:space="preserve">2.00127768516541</t>
   </si>
   <si>
     <t xml:space="preserve">2.01302075386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04405450820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03021502494812</t>
+    <t xml:space="preserve">2.04405474662781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0302152633667</t>
   </si>
   <si>
     <t xml:space="preserve">2.02056932449341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96311450004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97024369239807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97695410251617</t>
+    <t xml:space="preserve">1.96311461925507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97024381160736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97695422172546</t>
   </si>
   <si>
     <t xml:space="preserve">1.99666500091553</t>
@@ -5111,10 +5111,10 @@
     <t xml:space="preserve">2.06837868690491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09018659591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11534905433655</t>
+    <t xml:space="preserve">2.09018635749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11534929275513</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289762496948</t>
@@ -5123,7 +5123,7 @@
     <t xml:space="preserve">2.12709164619446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12960815429688</t>
+    <t xml:space="preserve">2.1296079158783</t>
   </si>
   <si>
     <t xml:space="preserve">2.15812587738037</t>
@@ -5141,22 +5141,22 @@
     <t xml:space="preserve">2.149738073349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13505983352661</t>
+    <t xml:space="preserve">2.13506007194519</t>
   </si>
   <si>
     <t xml:space="preserve">2.13338255882263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14722180366516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.961017370224</t>
+    <t xml:space="preserve">2.14722204208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96101784706116</t>
   </si>
   <si>
     <t xml:space="preserve">2.0067298412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04489374160767</t>
+    <t xml:space="preserve">2.04489326477051</t>
   </si>
   <si>
     <t xml:space="preserve">2.04615163803101</t>
@@ -5165,10 +5165,10 @@
     <t xml:space="preserve">2.05076456069946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03734445571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02937650680542</t>
+    <t xml:space="preserve">2.03734469413757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02937626838684</t>
   </si>
   <si>
     <t xml:space="preserve">2.02224707603455</t>
@@ -5201,10 +5201,10 @@
     <t xml:space="preserve">2.073410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05873274803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05202269554138</t>
+    <t xml:space="preserve">2.0587329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05202293395996</t>
   </si>
   <si>
     <t xml:space="preserve">2.00589108467102</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">2.02434396743774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0801215171814</t>
+    <t xml:space="preserve">2.08012127876282</t>
   </si>
   <si>
     <t xml:space="preserve">2.07634687423706</t>
@@ -5225,40 +5225,40 @@
     <t xml:space="preserve">2.06544303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07592749595642</t>
+    <t xml:space="preserve">2.07592725753784</t>
   </si>
   <si>
     <t xml:space="preserve">2.07089495658875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03818345069885</t>
+    <t xml:space="preserve">2.03818321228027</t>
   </si>
   <si>
     <t xml:space="preserve">2.04782891273499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10821962356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09102511405945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06418466567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03482842445374</t>
+    <t xml:space="preserve">2.10821938514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09102535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06418490409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03482818603516</t>
   </si>
   <si>
     <t xml:space="preserve">2.03231191635132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04657101631165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98156714439392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98282539844513</t>
+    <t xml:space="preserve">2.04657077789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98156702518463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98282551765442</t>
   </si>
   <si>
     <t xml:space="preserve">2.01427865028381</t>
@@ -5276,28 +5276,28 @@
     <t xml:space="preserve">2.05286169052124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02686023712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03650593757629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9920517206192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96605014801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99079346656799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97611498832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98785769939423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9941486120224</t>
+    <t xml:space="preserve">2.026859998703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03650569915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99205160140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96605026721954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99079370498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97611510753632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98785781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99414849281311</t>
   </si>
   <si>
     <t xml:space="preserve">2.06041049957275</t>
@@ -5306,7 +5306,7 @@
     <t xml:space="preserve">2.08934760093689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11702680587769</t>
+    <t xml:space="preserve">2.11702632904053</t>
   </si>
   <si>
     <t xml:space="preserve">2.15015769004822</t>
@@ -5315,13 +5315,13 @@
     <t xml:space="preserve">2.15225434303284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1505765914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15435123443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16231966018677</t>
+    <t xml:space="preserve">2.15057682991028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15435147285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16231942176819</t>
   </si>
   <si>
     <t xml:space="preserve">2.18286919593811</t>
@@ -5330,13 +5330,13 @@
     <t xml:space="preserve">2.20551562309265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21893572807312</t>
+    <t xml:space="preserve">2.21893548965454</t>
   </si>
   <si>
     <t xml:space="preserve">2.21977472305298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25164723396301</t>
+    <t xml:space="preserve">2.25164699554443</t>
   </si>
   <si>
     <t xml:space="preserve">2.27114582061768</t>
@@ -5345,7 +5345,7 @@
     <t xml:space="preserve">2.23835301399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25209021568298</t>
+    <t xml:space="preserve">2.25209045410156</t>
   </si>
   <si>
     <t xml:space="preserve">2.26848697662354</t>
@@ -5354,13 +5354,13 @@
     <t xml:space="preserve">2.3039391040802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30438208580017</t>
+    <t xml:space="preserve">2.30438232421875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32609677314758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34559559822083</t>
+    <t xml:space="preserve">2.34559535980225</t>
   </si>
   <si>
     <t xml:space="preserve">2.34116387367249</t>
@@ -5369,25 +5369,25 @@
     <t xml:space="preserve">2.36287808418274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38858079910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37838840484619</t>
+    <t xml:space="preserve">2.3885805606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37838864326477</t>
   </si>
   <si>
     <t xml:space="preserve">2.39788699150085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37307071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39301252365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38503575325012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37705898284912</t>
+    <t xml:space="preserve">2.37307047843933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39301228523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38503551483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37705874443054</t>
   </si>
   <si>
     <t xml:space="preserve">2.37572956085205</t>
@@ -5399,28 +5399,28 @@
     <t xml:space="preserve">2.33540272712708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32653999328613</t>
+    <t xml:space="preserve">2.32653975486755</t>
   </si>
   <si>
     <t xml:space="preserve">2.35046982765198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33717560768127</t>
+    <t xml:space="preserve">2.3371753692627</t>
   </si>
   <si>
     <t xml:space="preserve">2.33097124099731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34603834152222</t>
+    <t xml:space="preserve">2.3460385799408</t>
   </si>
   <si>
     <t xml:space="preserve">2.35445833206177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34205007553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34293627738953</t>
+    <t xml:space="preserve">2.34204983711243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34293651580811</t>
   </si>
   <si>
     <t xml:space="preserve">2.38813757896423</t>
@@ -5429,7 +5429,7 @@
     <t xml:space="preserve">2.38592195510864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44131565093994</t>
+    <t xml:space="preserve">2.44131588935852</t>
   </si>
   <si>
     <t xml:space="preserve">2.47056365013123</t>
@@ -5462,10 +5462,10 @@
     <t xml:space="preserve">2.44220209121704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45328068733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45682597160339</t>
+    <t xml:space="preserve">2.45328044891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45682621002197</t>
   </si>
   <si>
     <t xml:space="preserve">2.51221990585327</t>
@@ -5474,7 +5474,7 @@
     <t xml:space="preserve">2.48873281478882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49139165878296</t>
+    <t xml:space="preserve">2.49139189720154</t>
   </si>
   <si>
     <t xml:space="preserve">2.46568894386292</t>
@@ -5489,7 +5489,7 @@
     <t xml:space="preserve">2.48430132865906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48164248466492</t>
+    <t xml:space="preserve">2.48164224624634</t>
   </si>
   <si>
     <t xml:space="preserve">2.53969502449036</t>
@@ -5507,25 +5507,25 @@
     <t xml:space="preserve">2.46879100799561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50247049331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48696041107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49538016319275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50690197944641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50379991531372</t>
+    <t xml:space="preserve">2.50247025489807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4869601726532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49538040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50690221786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5038001537323</t>
   </si>
   <si>
     <t xml:space="preserve">2.5162079334259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52551436424255</t>
+    <t xml:space="preserve">2.52551412582397</t>
   </si>
   <si>
     <t xml:space="preserve">2.55742120742798</t>
@@ -5543,7 +5543,7 @@
     <t xml:space="preserve">2.61680340766907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6145875453949</t>
+    <t xml:space="preserve">2.61458778381348</t>
   </si>
   <si>
     <t xml:space="preserve">2.60395193099976</t>
@@ -5552,7 +5552,7 @@
     <t xml:space="preserve">2.66289091110229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65890264511108</t>
+    <t xml:space="preserve">2.6589024066925</t>
   </si>
   <si>
     <t xml:space="preserve">2.71252369880676</t>
@@ -5561,13 +5561,13 @@
     <t xml:space="preserve">2.75019145011902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73601078987122</t>
+    <t xml:space="preserve">2.73601055145264</t>
   </si>
   <si>
     <t xml:space="preserve">2.74974846839905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72183012962341</t>
+    <t xml:space="preserve">2.72182989120483</t>
   </si>
   <si>
     <t xml:space="preserve">2.78475713729858</t>
@@ -5576,13 +5576,13 @@
     <t xml:space="preserve">2.82109570503235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81046009063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86053586006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86186575889587</t>
+    <t xml:space="preserve">2.81045985221863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86053609848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86186552047729</t>
   </si>
   <si>
     <t xml:space="preserve">2.90352177619934</t>
@@ -5591,40 +5591,40 @@
     <t xml:space="preserve">2.899090051651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91858887672424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92036128044128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94384837150574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96511936187744</t>
+    <t xml:space="preserve">2.91858863830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92036151885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94384860992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96511960029602</t>
   </si>
   <si>
     <t xml:space="preserve">2.96733522415161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98062968254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96689224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01608204841614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00012850761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95049571990967</t>
+    <t xml:space="preserve">2.98062992095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96689248085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01608180999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00012826919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95049548149109</t>
   </si>
   <si>
     <t xml:space="preserve">2.97442579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93498563766479</t>
+    <t xml:space="preserve">2.93498539924622</t>
   </si>
   <si>
     <t xml:space="preserve">2.96910786628723</t>
@@ -5636,22 +5636,22 @@
     <t xml:space="preserve">2.91592979431152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94827961921692</t>
+    <t xml:space="preserve">2.9482798576355</t>
   </si>
   <si>
     <t xml:space="preserve">2.88225054740906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92390656471252</t>
+    <t xml:space="preserve">2.9239068031311</t>
   </si>
   <si>
     <t xml:space="preserve">2.96866464614868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99303793907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03868269920349</t>
+    <t xml:space="preserve">2.99303817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03868246078491</t>
   </si>
   <si>
     <t xml:space="preserve">3.11933588981628</t>
@@ -5681,28 +5681,28 @@
     <t xml:space="preserve">3.15788984298706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18935370445251</t>
+    <t xml:space="preserve">3.18935394287109</t>
   </si>
   <si>
     <t xml:space="preserve">3.18492197990417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17251372337341</t>
+    <t xml:space="preserve">3.17251396179199</t>
   </si>
   <si>
     <t xml:space="preserve">3.19112634658813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21417021751404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28197193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30324339866638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30856108665466</t>
+    <t xml:space="preserve">3.21416997909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2819721698761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3032431602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30856132507324</t>
   </si>
   <si>
     <t xml:space="preserve">3.34046792984009</t>
@@ -5735,13 +5735,13 @@
     <t xml:space="preserve">3.33677363395691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33030891418457</t>
+    <t xml:space="preserve">3.33030867576599</t>
   </si>
   <si>
     <t xml:space="preserve">3.36170959472656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27628135681152</t>
+    <t xml:space="preserve">3.27628111839294</t>
   </si>
   <si>
     <t xml:space="preserve">3.2721254825592</t>
@@ -5750,7 +5750,7 @@
     <t xml:space="preserve">3.32569122314453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3127613067627</t>
+    <t xml:space="preserve">3.31276154518127</t>
   </si>
   <si>
     <t xml:space="preserve">3.29521417617798</t>
@@ -5759,7 +5759,7 @@
     <t xml:space="preserve">3.21070957183838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26058101654053</t>
+    <t xml:space="preserve">3.26058125495911</t>
   </si>
   <si>
     <t xml:space="preserve">3.15391159057617</t>
@@ -5774,7 +5774,7 @@
     <t xml:space="preserve">3.15760564804077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19547128677368</t>
+    <t xml:space="preserve">3.1954710483551</t>
   </si>
   <si>
     <t xml:space="preserve">3.22640991210938</t>
@@ -5783,10 +5783,10 @@
     <t xml:space="preserve">3.18900632858276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24765157699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25688672065735</t>
+    <t xml:space="preserve">3.24765133857727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25688695907593</t>
   </si>
   <si>
     <t xml:space="preserve">3.199627161026</t>
@@ -5801,13 +5801,13 @@
     <t xml:space="preserve">3.26011943817139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30583477020264</t>
+    <t xml:space="preserve">3.30583500862122</t>
   </si>
   <si>
     <t xml:space="preserve">3.27812838554382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29336714744568</t>
+    <t xml:space="preserve">3.2933669090271</t>
   </si>
   <si>
     <t xml:space="preserve">3.28136086463928</t>
@@ -5819,7 +5819,7 @@
     <t xml:space="preserve">3.31645584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34277653694153</t>
+    <t xml:space="preserve">3.34277677536011</t>
   </si>
   <si>
     <t xml:space="preserve">3.33215594291687</t>
@@ -5828,7 +5828,7 @@
     <t xml:space="preserve">3.34600901603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36909794807434</t>
+    <t xml:space="preserve">3.36909770965576</t>
   </si>
   <si>
     <t xml:space="preserve">3.38710713386536</t>
@@ -5861,7 +5861,7 @@
     <t xml:space="preserve">3.32800006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18115592002869</t>
+    <t xml:space="preserve">3.18115615844727</t>
   </si>
   <si>
     <t xml:space="preserve">3.15021729469299</t>
@@ -5882,16 +5882,16 @@
     <t xml:space="preserve">3.2051682472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22225379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32199692726135</t>
+    <t xml:space="preserve">3.22225403785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32199668884277</t>
   </si>
   <si>
     <t xml:space="preserve">3.33769726753235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31968808174133</t>
+    <t xml:space="preserve">3.31968832015991</t>
   </si>
   <si>
     <t xml:space="preserve">3.33954429626465</t>
@@ -5909,13 +5909,13 @@
     <t xml:space="preserve">3.41712236404419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41850733757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44344329833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47669076919556</t>
+    <t xml:space="preserve">3.41850757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44344305992126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47669100761414</t>
   </si>
   <si>
     <t xml:space="preserve">3.48500299453735</t>
@@ -5927,7 +5927,7 @@
     <t xml:space="preserve">3.43005180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46422290802002</t>
+    <t xml:space="preserve">3.4642231464386</t>
   </si>
   <si>
     <t xml:space="preserve">3.38618350028992</t>
@@ -5939,7 +5939,7 @@
     <t xml:space="preserve">3.40696310997009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41296601295471</t>
+    <t xml:space="preserve">3.41296625137329</t>
   </si>
   <si>
     <t xml:space="preserve">3.4485228061676</t>
@@ -5948,7 +5948,7 @@
     <t xml:space="preserve">3.46791744232178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45314049720764</t>
+    <t xml:space="preserve">3.45314073562622</t>
   </si>
   <si>
     <t xml:space="preserve">3.47715282440186</t>
@@ -5963,7 +5963,7 @@
     <t xml:space="preserve">3.53256559371948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46607041358948</t>
+    <t xml:space="preserve">3.4660701751709</t>
   </si>
   <si>
     <t xml:space="preserve">3.48869705200195</t>
@@ -5972,7 +5972,7 @@
     <t xml:space="preserve">3.57966637611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57458686828613</t>
+    <t xml:space="preserve">3.57458710670471</t>
   </si>
   <si>
     <t xml:space="preserve">3.54411005973816</t>
@@ -5996,7 +5996,7 @@
     <t xml:space="preserve">3.49654722213745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51686525344849</t>
+    <t xml:space="preserve">3.51686549186707</t>
   </si>
   <si>
     <t xml:space="preserve">3.55565404891968</t>
@@ -6011,10 +6011,10 @@
     <t xml:space="preserve">3.62999987602234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62030243873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66694140434265</t>
+    <t xml:space="preserve">3.62030267715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66694164276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.69418621063232</t>
@@ -6026,7 +6026,7 @@
     <t xml:space="preserve">3.63046145439148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58705496788025</t>
+    <t xml:space="preserve">3.58705472946167</t>
   </si>
   <si>
     <t xml:space="preserve">3.58289885520935</t>
@@ -6044,16 +6044,16 @@
     <t xml:space="preserve">3.63600277900696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7251250743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75744915008545</t>
+    <t xml:space="preserve">3.72512531280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75744938850403</t>
   </si>
   <si>
     <t xml:space="preserve">3.78654074668884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66832685470581</t>
+    <t xml:space="preserve">3.66832661628723</t>
   </si>
   <si>
     <t xml:space="preserve">3.5602719783783</t>
@@ -6062,10 +6062,10 @@
     <t xml:space="preserve">3.54226279258728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60090804100037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51270937919617</t>
+    <t xml:space="preserve">3.60090780258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51270914077759</t>
   </si>
   <si>
     <t xml:space="preserve">3.53071856498718</t>
@@ -6750,6 +6750,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.44899988174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44999980926514</t>
   </si>
 </sst>
 </file>
@@ -71932,7 +71935,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6512037037</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>31669731</v>
@@ -71953,6 +71956,32 @@
         <v>2245</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6523958333</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>28423497</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>5.48400020599365</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>5.4539999961853</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>5.44999980926514</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>2246</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISP.MI.xlsx
+++ b/data/ISP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="2254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="2255">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,100 +38,100 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53063881397247</t>
+    <t xml:space="preserve">1.53063905239105</t>
   </si>
   <si>
     <t xml:space="preserve">ISP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5604100227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51831996440887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49265515804291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48752212524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4669908285141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49676156044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52447926998138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4854691028595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43824648857117</t>
+    <t xml:space="preserve">1.56040990352631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51831984519958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49265503883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48752236366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46699059009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49676144123077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52447950839996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48546922206879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4382461309433</t>
   </si>
   <si>
     <t xml:space="preserve">1.36638522148132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38075745105743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30479025840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36843860149384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39307653903961</t>
+    <t xml:space="preserve">1.38075733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30479001998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36843848228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3930766582489</t>
   </si>
   <si>
     <t xml:space="preserve">1.35406625270844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37254464626312</t>
+    <t xml:space="preserve">1.37254452705383</t>
   </si>
   <si>
     <t xml:space="preserve">1.35919916629791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29041790962219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380042552948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31505596637726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2698860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2031581401825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27296626567841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22368991374969</t>
+    <t xml:space="preserve">1.29041802883148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380006790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31505620479584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26988613605499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20315825939178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27296602725983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22368967533112</t>
   </si>
   <si>
     <t xml:space="preserve">1.17441368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10152637958527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26064705848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2298492193222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25243449211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28220522403717</t>
+    <t xml:space="preserve">1.10152614116669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26064717769623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22984933853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25243425369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28220510482788</t>
   </si>
   <si>
     <t xml:space="preserve">1.21958351135254</t>
@@ -140,136 +140,136 @@
     <t xml:space="preserve">1.19494557380676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23395597934723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20110511779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16004145145416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18057346343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20007836818695</t>
+    <t xml:space="preserve">1.23395574092865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20110499858856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16004168987274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18057310581207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20007824897766</t>
   </si>
   <si>
     <t xml:space="preserve">1.20213174819946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22471630573273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27091288566589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32224202156067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29555058479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26475322246552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27604556083679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144465923309</t>
+    <t xml:space="preserve">1.22471654415131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2709127664566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32224214076996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29555094242096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27604579925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29144442081451</t>
   </si>
   <si>
     <t xml:space="preserve">1.30581676959991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40334212779999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37459790706635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36022579669952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33045482635498</t>
+    <t xml:space="preserve">1.40334260463715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37459802627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36022567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33045470714569</t>
   </si>
   <si>
     <t xml:space="preserve">1.29349756240845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27912545204163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29247105121613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25756704807281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23600900173187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24935472011566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24114191532135</t>
+    <t xml:space="preserve">1.27912569046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29247117042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25756728649139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23600876331329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24935448169708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24114179611206</t>
   </si>
   <si>
     <t xml:space="preserve">1.21753036975861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18673288822174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1354033946991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14874875545502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11076557636261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17749392986298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19802534580231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2442215681076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2503809928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25654053688049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26269996166229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24216830730438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2780989408493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23190248012543</t>
+    <t xml:space="preserve">1.18673276901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13540327548981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1487489938736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1107656955719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17749333381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19802522659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24422168731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25038135051727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25654065608978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26270020008087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24216842651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27809870243073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23190259933472</t>
   </si>
   <si>
     <t xml:space="preserve">1.26680636405945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26783323287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18878614902496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16209483146667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13950991630554</t>
+    <t xml:space="preserve">1.26783299446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18878591060638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16209471225739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13950979709625</t>
   </si>
   <si>
     <t xml:space="preserve">1.1425895690918</t>
@@ -284,52 +284,52 @@
     <t xml:space="preserve">1.14566946029663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14156305789948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1292439699173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12103128433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1508024930954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17851996421814</t>
+    <t xml:space="preserve">1.1415628194809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12924420833588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12103140354156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15080225467682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17852020263672</t>
   </si>
   <si>
     <t xml:space="preserve">1.18775928020477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18666660785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25878441333771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28719460964203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29702889919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26096999645233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24020874500275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23037469387054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20852041244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20414984226227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22491109371185</t>
+    <t xml:space="preserve">1.18666672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25878429412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28719437122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29702877998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26096975803375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24020886421204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23037445545197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20852029323578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20414972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22491097450256</t>
   </si>
   <si>
     <t xml:space="preserve">1.2107058763504</t>
@@ -338,25 +338,25 @@
     <t xml:space="preserve">1.19977903366089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15060758590698</t>
+    <t xml:space="preserve">1.15060782432556</t>
   </si>
   <si>
     <t xml:space="preserve">1.08286046981812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04516279697418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07466530799866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06537759304047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1145486831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14842247962952</t>
+    <t xml:space="preserve">1.0451625585556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07466554641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06537747383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11454880237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14842236042023</t>
   </si>
   <si>
     <t xml:space="preserve">1.17683255672455</t>
@@ -371,76 +371,76 @@
     <t xml:space="preserve">0.950644552707672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846838533878326</t>
+    <t xml:space="preserve">0.846838474273682</t>
   </si>
   <si>
     <t xml:space="preserve">0.887268304824829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900380551815033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929883301258087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917863607406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89000004529953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870331346988678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868692517280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874155938625336</t>
+    <t xml:space="preserve">0.900380492210388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929883420467377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917863667011261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88999992609024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870331525802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868692576885223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874155879020691</t>
   </si>
   <si>
     <t xml:space="preserve">0.961571574211121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983425438404083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04789447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03587472438812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05772852897644</t>
+    <t xml:space="preserve">0.983425259590149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04789435863495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03587484359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">1.05499684810638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05718243122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.050626039505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06373846530914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0670166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06865584850311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04898703098297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05335772037506</t>
+    <t xml:space="preserve">1.05718231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05062615871429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06373834609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06701648235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06865549087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04898715019226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05335783958435</t>
   </si>
   <si>
     <t xml:space="preserve">1.0719336271286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03969931602478</t>
+    <t xml:space="preserve">1.0396990776062</t>
   </si>
   <si>
     <t xml:space="preserve">1.07630455493927</t>
@@ -449,34 +449,34 @@
     <t xml:space="preserve">1.03860652446747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999269485473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993806004524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994352400302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03806030750275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05117237567902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0560896396637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07958257198334</t>
+    <t xml:space="preserve">0.999269425868988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993805944919586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994352340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03806006908417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0511726140976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05608952045441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07958269119263</t>
   </si>
   <si>
     <t xml:space="preserve">1.05827498435974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03041124343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00965023040771</t>
+    <t xml:space="preserve">1.03041136264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00965011119843</t>
   </si>
   <si>
     <t xml:space="preserve">1.05991411209106</t>
@@ -488,76 +488,76 @@
     <t xml:space="preserve">1.08231437206268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10034382343292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08996307849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11673426628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16372001171112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19759368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19213008880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16809070110321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17901766300201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18338859081268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15934932231903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13749516010284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1364027261734</t>
+    <t xml:space="preserve">1.10034370422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08996319770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11673414707184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16372013092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19759321212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19213020801544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16809093952179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17901790142059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18338871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15934908390045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13749539852142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13640260696411</t>
   </si>
   <si>
     <t xml:space="preserve">1.12766110897064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09706544876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11236321926117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12656843662262</t>
+    <t xml:space="preserve">1.09706568717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11236345767975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12656831741333</t>
   </si>
   <si>
     <t xml:space="preserve">1.09050953388214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0779435634613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06428492069244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0615531206131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06319200992584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07848978042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05445051193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08941686153412</t>
+    <t xml:space="preserve">1.07794344425201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06428468227386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06155300140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06319212913513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07848966121674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05445063114166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08941674232483</t>
   </si>
   <si>
     <t xml:space="preserve">1.0937876701355</t>
@@ -566,64 +566,64 @@
     <t xml:space="preserve">1.07685089111328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08340716362</t>
+    <t xml:space="preserve">1.08340680599213</t>
   </si>
   <si>
     <t xml:space="preserve">1.12329041957855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13093912601471</t>
+    <t xml:space="preserve">1.130939245224</t>
   </si>
   <si>
     <t xml:space="preserve">1.15170037746429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15388572216034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17792510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196437835693</t>
+    <t xml:space="preserve">1.15388584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17792499065399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196449756622</t>
   </si>
   <si>
     <t xml:space="preserve">1.18229603767395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15279304981232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13858795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09925091266632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09597289562225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16044199466705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16918337345123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22054004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21835482120514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15497851371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14186608791351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11891973018646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10362184047699</t>
+    <t xml:space="preserve">1.15279293060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13858830928802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0992511510849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09597301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16044211387634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16918349266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22054028511047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21835470199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15497863292694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14186596870422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11891949176788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1036217212677</t>
   </si>
   <si>
     <t xml:space="preserve">1.06810939311981</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">1.11345613002777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14514434337616</t>
+    <t xml:space="preserve">1.14514422416687</t>
   </si>
   <si>
     <t xml:space="preserve">1.24567210674286</t>
@@ -647,88 +647,88 @@
     <t xml:space="preserve">1.27845311164856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3276242017746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29265820980072</t>
+    <t xml:space="preserve">1.32762432098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29265797138214</t>
   </si>
   <si>
     <t xml:space="preserve">1.33636581897736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31888258457184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33745849132538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3385511636734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34401476383209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964407444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871699333191</t>
+    <t xml:space="preserve">1.31888282299042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33745872974396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855140209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3440146446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964395523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3287171125412</t>
   </si>
   <si>
     <t xml:space="preserve">1.31779003143311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32543885707855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36805391311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38772249221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3975567817688</t>
+    <t xml:space="preserve">1.32543897628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36805379390717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38772225379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39755666255951</t>
   </si>
   <si>
     <t xml:space="preserve">1.38990795612335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35275626182556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34838545322418</t>
+    <t xml:space="preserve">1.35275614261627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34838533401489</t>
   </si>
   <si>
     <t xml:space="preserve">1.34619998931885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34729301929474</t>
+    <t xml:space="preserve">1.34729278087616</t>
   </si>
   <si>
     <t xml:space="preserve">1.32216084003448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34292209148407</t>
+    <t xml:space="preserve">1.3429217338562</t>
   </si>
   <si>
     <t xml:space="preserve">1.34947824478149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31014120578766</t>
+    <t xml:space="preserve">1.31014132499695</t>
   </si>
   <si>
     <t xml:space="preserve">1.25222826004028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25659930706024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22928154468536</t>
+    <t xml:space="preserve">1.25659906864166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22928190231323</t>
   </si>
   <si>
     <t xml:space="preserve">1.23911583423615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2008718252182</t>
+    <t xml:space="preserve">1.20087170600891</t>
   </si>
   <si>
     <t xml:space="preserve">1.18557417392731</t>
@@ -737,25 +737,25 @@
     <t xml:space="preserve">1.19103753566742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22272539138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19322264194489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17027628421783</t>
+    <t xml:space="preserve">1.22272562980652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19322276115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17027604579926</t>
   </si>
   <si>
     <t xml:space="preserve">1.1735543012619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16590559482574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17136907577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19650089740753</t>
+    <t xml:space="preserve">1.16590535640717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17136883735657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19650101661682</t>
   </si>
   <si>
     <t xml:space="preserve">1.18120312690735</t>
@@ -767,76 +767,76 @@
     <t xml:space="preserve">1.25113558769226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27626752853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26861894130707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27408242225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30577051639557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34182953834534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32325339317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35057103633881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35603427886963</t>
+    <t xml:space="preserve">1.27626764774323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26861870288849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189695835114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27408230304718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30577039718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34182941913605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32325351238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35057091712952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35603439807892</t>
   </si>
   <si>
     <t xml:space="preserve">1.36914682388306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3910003900528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38662981987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38335180282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37679541110992</t>
+    <t xml:space="preserve">1.39100050926208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38662993907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38335192203522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37679553031921</t>
   </si>
   <si>
     <t xml:space="preserve">1.38007378578186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37898075580597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37461030483246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36696135997772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384917259216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33199501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30467772483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35166347026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3604052066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37351727485657</t>
+    <t xml:space="preserve">1.37898099422455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37461006641388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3669615983963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384893417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33199524879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30467760562897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35166358947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36040508747101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37351751327515</t>
   </si>
   <si>
     <t xml:space="preserve">1.47623085975647</t>
@@ -854,25 +854,25 @@
     <t xml:space="preserve">1.460932970047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46311855316162</t>
+    <t xml:space="preserve">1.46311843395233</t>
   </si>
   <si>
     <t xml:space="preserve">1.47076725959778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50791919231415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55271923542023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55818295478821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55599761009216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55709028244019</t>
+    <t xml:space="preserve">1.50791871547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55271947383881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55818283557892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55599749088287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5570901632309</t>
   </si>
   <si>
     <t xml:space="preserve">1.54725611209869</t>
@@ -881,55 +881,55 @@
     <t xml:space="preserve">1.54507064819336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55162680149078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52868020534515</t>
+    <t xml:space="preserve">1.55162668228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52868008613586</t>
   </si>
   <si>
     <t xml:space="preserve">1.52212405204773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52977252006531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56594610214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57061350345612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56711292266846</t>
+    <t xml:space="preserve">1.52977275848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56594598293304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57061326503754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56711268424988</t>
   </si>
   <si>
     <t xml:space="preserve">1.55427742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52977275848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49826729297638</t>
+    <t xml:space="preserve">1.52977287769318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49826741218567</t>
   </si>
   <si>
     <t xml:space="preserve">1.48893213272095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48659884929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50060093402863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5111026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49126601219177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48426485061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4994341135025</t>
+    <t xml:space="preserve">1.4865984916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50060081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51110291481018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49126589298248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48426473140717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49943423271179</t>
   </si>
   <si>
     <t xml:space="preserve">1.50876915454865</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">1.50176787376404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50410187244415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49710047245026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47843027114868</t>
+    <t xml:space="preserve">1.50410151481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49710035324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47843050956726</t>
   </si>
   <si>
     <t xml:space="preserve">1.51460349559784</t>
@@ -953,91 +953,91 @@
     <t xml:space="preserve">1.52510547637939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52627217769623</t>
+    <t xml:space="preserve">1.52627205848694</t>
   </si>
   <si>
     <t xml:space="preserve">1.57994830608368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6079535484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64062607288361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61845541000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61962234973907</t>
+    <t xml:space="preserve">1.60795342922211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6406261920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61845552921295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6196221113205</t>
   </si>
   <si>
     <t xml:space="preserve">1.66279673576355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65929615497589</t>
+    <t xml:space="preserve">1.65929591655731</t>
   </si>
   <si>
     <t xml:space="preserve">1.67213177680969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65696239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66863095760345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65346193313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66162967681885</t>
+    <t xml:space="preserve">1.65696203708649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66863083839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65346169471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66162979602814</t>
   </si>
   <si>
     <t xml:space="preserve">1.66396355628967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67096471786499</t>
+    <t xml:space="preserve">1.6709645986557</t>
   </si>
   <si>
     <t xml:space="preserve">1.67446541786194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6662974357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67329823970795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68379998207092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69313549995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69546926021576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69430208206177</t>
+    <t xml:space="preserve">1.66629731655121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67329847812653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68380033969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69313538074493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69546914100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69430220127106</t>
   </si>
   <si>
     <t xml:space="preserve">1.69896972179413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70130336284637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69196844100952</t>
+    <t xml:space="preserve">1.70130324363708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6919686794281</t>
   </si>
   <si>
     <t xml:space="preserve">1.7036372423172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70830464363098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70480394363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263363838196</t>
+    <t xml:space="preserve">1.70830452442169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70480418205261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263339996338</t>
   </si>
   <si>
     <t xml:space="preserve">1.67796587944031</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">1.70713806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68963479995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64295971393585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65462827682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6581289768219</t>
+    <t xml:space="preserve">1.68963444232941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64295995235443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65462875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65812909603119</t>
   </si>
   <si>
     <t xml:space="preserve">1.63712525367737</t>
@@ -1067,43 +1067,43 @@
     <t xml:space="preserve">1.6651303768158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68146669864655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70013666152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71063852310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71763968467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73280906677246</t>
+    <t xml:space="preserve">1.68146657943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70013654232025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71063840389252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7176399230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73280894756317</t>
   </si>
   <si>
     <t xml:space="preserve">1.73397576808929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72464108467102</t>
+    <t xml:space="preserve">1.72464096546173</t>
   </si>
   <si>
     <t xml:space="preserve">1.735142827034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74447786808014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74214422702789</t>
+    <t xml:space="preserve">1.74447762966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7421441078186</t>
   </si>
   <si>
     <t xml:space="preserve">1.74564480781555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74681127071381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74097740650177</t>
+    <t xml:space="preserve">1.74681162834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74097716808319</t>
   </si>
   <si>
     <t xml:space="preserve">1.71180546283722</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">1.71530592441559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7094714641571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68496751785278</t>
+    <t xml:space="preserve">1.70947194099426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68496739864349</t>
   </si>
   <si>
     <t xml:space="preserve">1.66746413707733</t>
@@ -1124,202 +1124,202 @@
     <t xml:space="preserve">1.68029975891113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70597112178802</t>
+    <t xml:space="preserve">1.70597100257874</t>
   </si>
   <si>
     <t xml:space="preserve">1.67913293838501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65112769603729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63362443447113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63479197025299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61728870868683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61495435237885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64412665367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61378812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64529371261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6464604139328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67563235759735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63829243183136</t>
+    <t xml:space="preserve">1.65112793445587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63362467288971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63479149341583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61728858947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61495447158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64412689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6137877702713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64529359340668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64646029472351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67563211917877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63829231262207</t>
   </si>
   <si>
     <t xml:space="preserve">1.62895727157593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62662351131439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62779057025909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61612164974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60678672790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60445272922516</t>
+    <t xml:space="preserve">1.62662327289581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62779033184052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61612129211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60678684711456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60445284843445</t>
   </si>
   <si>
     <t xml:space="preserve">1.74331080913544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76548159122467</t>
+    <t xml:space="preserve">1.76548182964325</t>
   </si>
   <si>
     <t xml:space="preserve">1.77248311042786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77598357200623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78415167331696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80515563488007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8016551733017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82382524013519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82499217987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79815447330475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82149159908295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84366226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824859142303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83549427986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.843954205513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111834526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81769907474518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902899265289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81098961830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87283396720886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83636939525604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81157302856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377853870392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80923926830292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80690550804138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83053517341614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81303179264069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223822593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80748891830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78444337844849</t>
+    <t xml:space="preserve">1.77598321437836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78415191173553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80515515804291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80165469646454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8238251209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82499194145203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79815411567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82149136066437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84366238117218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824823379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83549380302429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84395444393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111846446991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81769919395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902946949005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81098997592926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87283432483673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83636927604675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81157350540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377806186676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923938751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80690574645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83053469657898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8130316734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223834514618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80748927593231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78444361686707</t>
   </si>
   <si>
     <t xml:space="preserve">1.79873752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79990434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80982291698456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80632209777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79290306568146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7541047334671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72930836677551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74535310268402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76518976688385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77510821819305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78035938739777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77539992332458</t>
+    <t xml:space="preserve">1.79990446567535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80982303619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80632221698761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79290294647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75410461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72930860519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74535298347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76518988609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77510809898376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7803590297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540004253387</t>
   </si>
   <si>
     <t xml:space="preserve">1.7488534450531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76081395149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79523706436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77364981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78473508358002</t>
+    <t xml:space="preserve">1.7608140707016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79523694515228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77365005016327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78473496437073</t>
   </si>
   <si>
     <t xml:space="preserve">1.77423298358917</t>
@@ -1328,10 +1328,10 @@
     <t xml:space="preserve">1.74272763729095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72259926795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70742976665497</t>
+    <t xml:space="preserve">1.72259902954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70742952823639</t>
   </si>
   <si>
     <t xml:space="preserve">1.72289097309113</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">1.72318243980408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7252242565155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71909844875336</t>
+    <t xml:space="preserve">1.72522449493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71909821033478</t>
   </si>
   <si>
     <t xml:space="preserve">1.7520626783371</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">1.74768686294556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76256442070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77131581306458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75906372070312</t>
+    <t xml:space="preserve">1.76256430149078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77131593227386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7590639591217</t>
   </si>
   <si>
     <t xml:space="preserve">1.77948403358459</t>
@@ -1367,16 +1367,16 @@
     <t xml:space="preserve">1.78940260410309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79465341567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81449019908905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81536555290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82907617092133</t>
+    <t xml:space="preserve">1.79465353488922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81449031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81536567211151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82907629013062</t>
   </si>
   <si>
     <t xml:space="preserve">1.84832978248596</t>
@@ -1385,58 +1385,58 @@
     <t xml:space="preserve">1.86437404155731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8398699760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85124742984772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83957815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84191191196442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84862160682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83811974525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84453725814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83403551578522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82674264907837</t>
+    <t xml:space="preserve">1.83987009525299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85124683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83957827091217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84191179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8486213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83811986446381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84453737735748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83403527736664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82674276828766</t>
   </si>
   <si>
     <t xml:space="preserve">1.83782780170441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85416424274445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80865609645844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79436206817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031197071075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73967373371124</t>
+    <t xml:space="preserve">1.85416436195374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80865585803986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79436182975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031232833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73967385292053</t>
   </si>
   <si>
     <t xml:space="preserve">1.75156366825104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72090041637421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70494294166565</t>
+    <t xml:space="preserve">1.7209005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70494329929352</t>
   </si>
   <si>
     <t xml:space="preserve">1.65081286430359</t>
@@ -1445,73 +1445,73 @@
     <t xml:space="preserve">1.59730851650238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53191411495209</t>
+    <t xml:space="preserve">1.53191447257996</t>
   </si>
   <si>
     <t xml:space="preserve">1.57759630680084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57352864742279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62546873092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62515568733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56289076805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55475521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53629469871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51752126216888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61827206611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62578165531158</t>
+    <t xml:space="preserve">1.57352876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62546861171722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62515580654144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56289041042328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55475533008575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53629457950592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51752114295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61827230453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6173335313797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62578153610229</t>
   </si>
   <si>
     <t xml:space="preserve">1.6232784986496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59417939186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59793436527252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60575675964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63548111915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60325348377228</t>
+    <t xml:space="preserve">1.59417963027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59793412685394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60575652122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63548123836517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60325372219086</t>
   </si>
   <si>
     <t xml:space="preserve">1.61952364444733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56695783138275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55068743228912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690815925598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55694568157196</t>
+    <t xml:space="preserve">1.56695795059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55068755149841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690804004669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55694556236267</t>
   </si>
   <si>
     <t xml:space="preserve">1.55600690841675</t>
@@ -1520,49 +1520,49 @@
     <t xml:space="preserve">1.54474270343781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57634449005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58416724205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60513079166412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60294055938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60606956481934</t>
+    <t xml:space="preserve">1.57634484767914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58416700363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60513091087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6029406785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60606944561005</t>
   </si>
   <si>
     <t xml:space="preserve">1.58041250705719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54881048202515</t>
+    <t xml:space="preserve">1.54881036281586</t>
   </si>
   <si>
     <t xml:space="preserve">1.53066277503967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5397367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53660762310028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55193948745728</t>
+    <t xml:space="preserve">1.53973639011383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53660750389099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5519392490387</t>
   </si>
   <si>
     <t xml:space="preserve">1.54161381721497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51658260822296</t>
+    <t xml:space="preserve">1.51658272743225</t>
   </si>
   <si>
     <t xml:space="preserve">1.50531852245331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50250232219696</t>
+    <t xml:space="preserve">1.50250256061554</t>
   </si>
   <si>
     <t xml:space="preserve">1.53097546100616</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">1.55037498474121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57039976119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58322811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64830958843231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57259011268616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51188921928406</t>
+    <t xml:space="preserve">1.57039988040924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58322846889496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64830982685089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57258987426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51188933849335</t>
   </si>
   <si>
     <t xml:space="preserve">1.53003680706024</t>
@@ -1595,34 +1595,34 @@
     <t xml:space="preserve">1.49249005317688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43804717063904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41426718235016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40175175666809</t>
+    <t xml:space="preserve">1.43804705142975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41426730155945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4017516374588</t>
   </si>
   <si>
     <t xml:space="preserve">1.37640762329102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36576926708221</t>
+    <t xml:space="preserve">1.36576902866364</t>
   </si>
   <si>
     <t xml:space="preserve">1.35732102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40331602096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38329088687897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37672019004822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37891089916229</t>
+    <t xml:space="preserve">1.40331614017487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38329100608826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37672030925751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.378910779953</t>
   </si>
   <si>
     <t xml:space="preserve">1.37859773635864</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">1.36357879638672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38172662258148</t>
+    <t xml:space="preserve">1.38172650337219</t>
   </si>
   <si>
     <t xml:space="preserve">1.34918582439423</t>
@@ -1640,16 +1640,16 @@
     <t xml:space="preserve">1.33135116100311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35857272148132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897295951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45901072025299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43929874897003</t>
+    <t xml:space="preserve">1.35857260227203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45901048183441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43929839134216</t>
   </si>
   <si>
     <t xml:space="preserve">1.41583180427551</t>
@@ -1658,28 +1658,28 @@
     <t xml:space="preserve">1.47997438907623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45650768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46432960033417</t>
+    <t xml:space="preserve">1.45650780200958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46432983875275</t>
   </si>
   <si>
     <t xml:space="preserve">1.45744621753693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46683311462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50093793869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49906063079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51908588409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5115761756897</t>
+    <t xml:space="preserve">1.46683299541473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50093805789948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49906075000763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51908576488495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51157629489899</t>
   </si>
   <si>
     <t xml:space="preserve">1.53222703933716</t>
@@ -1691,34 +1691,34 @@
     <t xml:space="preserve">1.54568147659302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52221465110779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50437998771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37734615802765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32352888584137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31914854049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32634472846985</t>
+    <t xml:space="preserve">1.52221477031708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50437986850739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37734627723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32352900505066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31914842128754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32634484767914</t>
   </si>
   <si>
     <t xml:space="preserve">1.35481786727905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31320345401764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27033734321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29818487167358</t>
+    <t xml:space="preserve">1.31320333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27033746242523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29818475246429</t>
   </si>
   <si>
     <t xml:space="preserve">1.30506837368011</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">1.26783430576324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27753388881683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29536879062653</t>
+    <t xml:space="preserve">1.27753400802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29536867141724</t>
   </si>
   <si>
     <t xml:space="preserve">1.28066277503967</t>
@@ -1742,19 +1742,19 @@
     <t xml:space="preserve">1.23842251300812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24167680740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23128855228424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23166394233704</t>
+    <t xml:space="preserve">1.24167656898499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23128843307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23166418075562</t>
   </si>
   <si>
     <t xml:space="preserve">1.18936109542847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22227740287781</t>
+    <t xml:space="preserve">1.22227728366852</t>
   </si>
   <si>
     <t xml:space="preserve">1.21264040470123</t>
@@ -1763,19 +1763,19 @@
     <t xml:space="preserve">1.249436378479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24655771255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22215223312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2426780462265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25563144683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23667025566101</t>
+    <t xml:space="preserve">1.24655759334564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2221519947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24267792701721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25563156604767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2366703748703</t>
   </si>
   <si>
     <t xml:space="preserve">1.25250267982483</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">1.26971173286438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25500583648682</t>
+    <t xml:space="preserve">1.25500571727753</t>
   </si>
   <si>
     <t xml:space="preserve">1.22665774822235</t>
@@ -1796,19 +1796,19 @@
     <t xml:space="preserve">1.25312852859497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23829746246338</t>
+    <t xml:space="preserve">1.2382972240448</t>
   </si>
   <si>
     <t xml:space="preserve">1.2226527929306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20112597942352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20538103580475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17571914196014</t>
+    <t xml:space="preserve">1.20112586021423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20538127422333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17571926116943</t>
   </si>
   <si>
     <t xml:space="preserve">1.20901095867157</t>
@@ -1817,22 +1817,22 @@
     <t xml:space="preserve">1.20888566970825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22165167331696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27690815925598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27628231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28535616397858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2719019651413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2816014289856</t>
+    <t xml:space="preserve">1.22165143489838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27690804004669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27628242969513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28535628318787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27190184593201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28160154819489</t>
   </si>
   <si>
     <t xml:space="preserve">1.32196438312531</t>
@@ -1844,37 +1844,37 @@
     <t xml:space="preserve">1.30193936824799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2349179983139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24029970169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21376657485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21026229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25969922542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27158892154694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26032495498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23466777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24217712879181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26345372200012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21714603900909</t>
+    <t xml:space="preserve">1.23491823673248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24029982089996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2137668132782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21026241779327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25969898700714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27158880233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26032483577728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23466789722443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24217736721039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26345384120941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2171459197998</t>
   </si>
   <si>
     <t xml:space="preserve">1.19662022590637</t>
@@ -1886,43 +1886,43 @@
     <t xml:space="preserve">1.21389198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19299066066742</t>
+    <t xml:space="preserve">1.192990899086</t>
   </si>
   <si>
     <t xml:space="preserve">1.18986177444458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25106334686279</t>
+    <t xml:space="preserve">1.25106346607208</t>
   </si>
   <si>
     <t xml:space="preserve">1.27221477031708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2575089931488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26470530033112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25844728946686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24017477035522</t>
+    <t xml:space="preserve">1.25750887393951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26470518112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25844752788544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24017465114594</t>
   </si>
   <si>
     <t xml:space="preserve">1.22465538978577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2600120306015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27565670013428</t>
+    <t xml:space="preserve">1.26001214981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27565658092499</t>
   </si>
   <si>
     <t xml:space="preserve">1.27596950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26814723014832</t>
+    <t xml:space="preserve">1.26814711093903</t>
   </si>
   <si>
     <t xml:space="preserve">1.26908600330353</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">1.28003704547882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28191435337067</t>
+    <t xml:space="preserve">1.28191459178925</t>
   </si>
   <si>
     <t xml:space="preserve">1.28973662853241</t>
@@ -1943,22 +1943,22 @@
     <t xml:space="preserve">1.24830996990204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2281596660614</t>
+    <t xml:space="preserve">1.22815978527069</t>
   </si>
   <si>
     <t xml:space="preserve">1.22753393650055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24705827236176</t>
+    <t xml:space="preserve">1.24705839157104</t>
   </si>
   <si>
     <t xml:space="preserve">1.24180161952972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23616981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25131356716156</t>
+    <t xml:space="preserve">1.2361695766449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25131368637085</t>
   </si>
   <si>
     <t xml:space="preserve">1.25531876087189</t>
@@ -1967,64 +1967,64 @@
     <t xml:space="preserve">1.24155139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28097569942474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2922397851944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2862948179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28692042827606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27659499645233</t>
+    <t xml:space="preserve">1.28097546100616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29223990440369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28629469871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28692054748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2765953540802</t>
   </si>
   <si>
     <t xml:space="preserve">1.2778468132019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30444288253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29943633079529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3338543176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3504376411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35513091087341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35262763500214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36545622348785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33510601520538</t>
+    <t xml:space="preserve">1.30444264411926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.299436211586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33385443687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35043752193451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35513079166412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35262775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36545634269714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3351057767868</t>
   </si>
   <si>
     <t xml:space="preserve">1.32603204250336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33760893344879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33667016029358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34824728965759</t>
+    <t xml:space="preserve">1.33760905265808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33667027950287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34824740886688</t>
   </si>
   <si>
     <t xml:space="preserve">1.35794711112976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37609469890594</t>
+    <t xml:space="preserve">1.37609446048737</t>
   </si>
   <si>
     <t xml:space="preserve">1.39737129211426</t>
@@ -2033,148 +2033,148 @@
     <t xml:space="preserve">1.39924848079681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39549386501312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38610684871674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34949886798859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480547904968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136354923248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35168898105621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3541921377182</t>
+    <t xml:space="preserve">1.39549362659454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38610696792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34949910640717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480535984039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136378765106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35168921947479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35419237613678</t>
   </si>
   <si>
     <t xml:space="preserve">1.38016200065613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3754688501358</t>
+    <t xml:space="preserve">1.37546896934509</t>
   </si>
   <si>
     <t xml:space="preserve">1.38767147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39799678325653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39956152439117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39017462730408</t>
+    <t xml:space="preserve">1.39799690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39956140518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39017474651337</t>
   </si>
   <si>
     <t xml:space="preserve">1.39830994606018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43992447853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45337855815887</t>
+    <t xml:space="preserve">1.43992459774017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45337867736816</t>
   </si>
   <si>
     <t xml:space="preserve">1.46558141708374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45963644981384</t>
+    <t xml:space="preserve">1.45963656902313</t>
   </si>
   <si>
     <t xml:space="preserve">1.45244014263153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42365396022797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42490553855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42991197109222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45932328701019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4624525308609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45619451999664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45306587219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4327278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40300333499908</t>
+    <t xml:space="preserve">1.42365419864655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42490541934967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42991173267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45932352542877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46245241165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45619487762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45306575298309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43272793292999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40300321578979</t>
   </si>
   <si>
     <t xml:space="preserve">1.38673281669617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35450518131256</t>
+    <t xml:space="preserve">1.35450506210327</t>
   </si>
   <si>
     <t xml:space="preserve">1.35137605667114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32540655136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34543120861053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36639499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35825979709625</t>
+    <t xml:space="preserve">1.3254063129425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34543144702911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36639475822449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35825967788696</t>
   </si>
   <si>
     <t xml:space="preserve">1.36135697364807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36066877841949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33630466461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30973827838898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32061243057251</t>
+    <t xml:space="preserve">1.36066854000092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33630454540253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30973815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32061266899109</t>
   </si>
   <si>
     <t xml:space="preserve">1.31331717967987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29872620105743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28413534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28372228145599</t>
+    <t xml:space="preserve">1.29872632026672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28413546085358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28372251987457</t>
   </si>
   <si>
     <t xml:space="preserve">1.26211130619049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25674307346344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28441071510315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27326095104218</t>
+    <t xml:space="preserve">1.25674295425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28441059589386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27326107025146</t>
   </si>
   <si>
     <t xml:space="preserve">1.25701832771301</t>
@@ -2183,40 +2183,40 @@
     <t xml:space="preserve">1.26142311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27037036418915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27133393287659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25811946392059</t>
+    <t xml:space="preserve">1.27037024497986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2713338136673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25811958312988</t>
   </si>
   <si>
     <t xml:space="preserve">1.26775503158569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26458919048309</t>
+    <t xml:space="preserve">1.26458895206451</t>
   </si>
   <si>
     <t xml:space="preserve">1.2601842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2893660068512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31262874603271</t>
+    <t xml:space="preserve">1.28936612606049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.312628865242</t>
   </si>
   <si>
     <t xml:space="preserve">1.30134165287018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29046726226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29032933712006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28592479228973</t>
+    <t xml:space="preserve">1.29046714305878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29032969474792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28592491149902</t>
   </si>
   <si>
     <t xml:space="preserve">1.29239439964294</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">1.29294490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29528498649597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28537428379059</t>
+    <t xml:space="preserve">1.29528510570526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2853741645813</t>
   </si>
   <si>
     <t xml:space="preserve">1.29734969139099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36328387260437</t>
+    <t xml:space="preserve">1.36328399181366</t>
   </si>
   <si>
     <t xml:space="preserve">1.39439284801483</t>
@@ -2243,67 +2243,67 @@
     <t xml:space="preserve">1.39852249622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38854289054871</t>
+    <t xml:space="preserve">1.38854277133942</t>
   </si>
   <si>
     <t xml:space="preserve">1.38097202777863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.397833943367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41469621658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41159904003143</t>
+    <t xml:space="preserve">1.39783406257629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41469597816467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41159915924072</t>
   </si>
   <si>
     <t xml:space="preserve">1.40987849235535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41916990280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40609300136566</t>
+    <t xml:space="preserve">1.41916978359222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40609312057495</t>
   </si>
   <si>
     <t xml:space="preserve">1.41091084480286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38200426101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38441324234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40058708190918</t>
+    <t xml:space="preserve">1.38200438022614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3844131231308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40058720111847</t>
   </si>
   <si>
     <t xml:space="preserve">1.39026343822479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38338100910187</t>
+    <t xml:space="preserve">1.38338088989258</t>
   </si>
   <si>
     <t xml:space="preserve">1.37044167518616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35309767723083</t>
+    <t xml:space="preserve">1.35309791564941</t>
   </si>
   <si>
     <t xml:space="preserve">1.34924376010895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37649846076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3438755273819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35433673858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33836936950684</t>
+    <t xml:space="preserve">1.37649834156036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34387528896332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35433661937714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33836925029755</t>
   </si>
   <si>
     <t xml:space="preserve">1.31455588340759</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">1.26362562179565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29886388778687</t>
+    <t xml:space="preserve">1.29886376857758</t>
   </si>
   <si>
     <t xml:space="preserve">1.27023279666901</t>
@@ -2324,193 +2324,193 @@
     <t xml:space="preserve">1.31744647026062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31001341342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32322788238525</t>
+    <t xml:space="preserve">1.31001353263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32322812080383</t>
   </si>
   <si>
     <t xml:space="preserve">1.33644223213196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30987584590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33520352840424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34084701538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35488748550415</t>
+    <t xml:space="preserve">1.30987596511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33520328998566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34084713459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35488736629486</t>
   </si>
   <si>
     <t xml:space="preserve">1.38578987121582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3718181848526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37890720367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37684261798859</t>
+    <t xml:space="preserve">1.37181830406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37890708446503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37684237957001</t>
   </si>
   <si>
     <t xml:space="preserve">1.39542508125305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4150402545929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42261123657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44635593891144</t>
+    <t xml:space="preserve">1.41504037380219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4226108789444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44635581970215</t>
   </si>
   <si>
     <t xml:space="preserve">1.46149730682373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45082938671112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46080887317657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50175988674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47526204586029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46252954006195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46321785449982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48937141895294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4907478094101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319757938385</t>
+    <t xml:space="preserve">1.45082926750183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46080875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50175964832306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47526216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46252965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46321773529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48937153816223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49074769020081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319746017456</t>
   </si>
   <si>
     <t xml:space="preserve">1.46597099304199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46941208839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47491800785065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696231842041</t>
+    <t xml:space="preserve">1.46941196918488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47491788864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4869624376297</t>
   </si>
   <si>
     <t xml:space="preserve">1.49728608131409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48317694664001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44119369983673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43912923336029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44222605228424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43568766117096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44773209095001</t>
+    <t xml:space="preserve">1.48317682743073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44119381904602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43912899494171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44222617149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43568789958954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4477322101593</t>
   </si>
   <si>
     <t xml:space="preserve">1.47939157485962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50451278686523</t>
+    <t xml:space="preserve">1.50451266765594</t>
   </si>
   <si>
     <t xml:space="preserve">1.5003833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52103054523468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5406459569931</t>
+    <t xml:space="preserve">1.52103066444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54064571857452</t>
   </si>
   <si>
     <t xml:space="preserve">1.5358282327652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53789269924164</t>
+    <t xml:space="preserve">1.53789281845093</t>
   </si>
   <si>
     <t xml:space="preserve">1.55062544345856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56576693058014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5623254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56301379203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56404638290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56817579269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56370222568512</t>
+    <t xml:space="preserve">1.56576716899872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56232571601868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56301391124725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56404626369476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5681756734848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56370234489441</t>
   </si>
   <si>
     <t xml:space="preserve">1.54752838611603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54580783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5643904209137</t>
+    <t xml:space="preserve">1.54580771923065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56439030170441</t>
   </si>
   <si>
     <t xml:space="preserve">1.58710277080536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61050295829773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6087828874588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62151527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256778240204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62220346927643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63665652275085</t>
+    <t xml:space="preserve">1.61050319671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60878252983093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62151491641998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256790161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62220358848572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63665664196014</t>
   </si>
   <si>
     <t xml:space="preserve">1.61394441127777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6008677482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60912668704987</t>
+    <t xml:space="preserve">1.60086762905121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60912644863129</t>
   </si>
   <si>
     <t xml:space="preserve">1.61738550662994</t>
@@ -2519,160 +2519,160 @@
     <t xml:space="preserve">1.61566495895386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62013876438141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61291193962097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61910617351532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61187946796417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60190010070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58985567092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58331716060638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5451192855835</t>
+    <t xml:space="preserve">1.62013864517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61291170120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61910605430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61187994480133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6019002199173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58985579013824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58331704139709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54511916637421</t>
   </si>
   <si>
     <t xml:space="preserve">1.5767787694931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57471454143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5922646522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58090841770172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58572602272034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59054386615753</t>
+    <t xml:space="preserve">1.57471418380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59226441383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58090817928314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58572614192963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59054398536682</t>
   </si>
   <si>
     <t xml:space="preserve">1.60224413871765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61497676372528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62633311748505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62839734554291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63803291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65523934364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65214216709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62082695960999</t>
+    <t xml:space="preserve">1.61497664451599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62633264064789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62839770317078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63803339004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6552392244339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65214228630066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6208268404007</t>
   </si>
   <si>
     <t xml:space="preserve">1.61635327339172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63872134685516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6170414686203</t>
+    <t xml:space="preserve">1.63872146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61704123020172</t>
   </si>
   <si>
     <t xml:space="preserve">1.63390374183655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61119151115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61532080173492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59673798084259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59845864772797</t>
+    <t xml:space="preserve">1.61119139194489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61532056331635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59673810005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59845876693726</t>
   </si>
   <si>
     <t xml:space="preserve">1.60809433460236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59570574760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56920826435089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56094896793365</t>
+    <t xml:space="preserve">1.59570586681366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5692081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56094908714294</t>
   </si>
   <si>
     <t xml:space="preserve">1.56783187389374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55200207233429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58675849437714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57712316513062</t>
+    <t xml:space="preserve">1.55200219154358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58675861358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57712292671204</t>
   </si>
   <si>
     <t xml:space="preserve">1.54546368122101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57264947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61841809749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68586623668671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70100772380829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7041050195694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69240486621857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70857870578766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72578477859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72750544548035</t>
+    <t xml:space="preserve">1.57264935970306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61841797828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68586659431458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70100796222687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70410525798798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69240498542786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70857846736908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72578489780426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72750532627106</t>
   </si>
   <si>
     <t xml:space="preserve">1.7481529712677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78944778442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79185664653778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75503551959991</t>
+    <t xml:space="preserve">1.78944754600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79185676574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75503540039062</t>
   </si>
   <si>
     <t xml:space="preserve">1.73542046546936</t>
@@ -2681,16 +2681,16 @@
     <t xml:space="preserve">1.63562417030334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60362076759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57505822181702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51311588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47044432163239</t>
+    <t xml:space="preserve">1.60362064838409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57505834102631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51311576366425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4704442024231</t>
   </si>
   <si>
     <t xml:space="preserve">1.45839989185333</t>
@@ -2699,172 +2699,172 @@
     <t xml:space="preserve">1.46425020694733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40850186347961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36080634593964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20443606376648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17608022689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22453284263611</t>
+    <t xml:space="preserve">1.4085019826889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36080622673035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20443618297577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1760801076889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2245329618454</t>
   </si>
   <si>
     <t xml:space="preserve">1.00677096843719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06981456279755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965475797653198</t>
+    <t xml:space="preserve">1.06981444358826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965475976467133</t>
   </si>
   <si>
     <t xml:space="preserve">0.998924970626831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969467878341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980892658233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00856029987335</t>
+    <t xml:space="preserve">0.96946793794632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980892777442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00856041908264</t>
   </si>
   <si>
     <t xml:space="preserve">0.997135519981384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08991158008575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11234831809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12253451347351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07821130752563</t>
+    <t xml:space="preserve">1.08991134166718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11234819889069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1225346326828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07821106910706</t>
   </si>
   <si>
     <t xml:space="preserve">1.01227688789368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02438998222351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987499952316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989564716815948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914820969104767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00360512733459</t>
+    <t xml:space="preserve">1.0243901014328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987500011920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989564895629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914820909500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00360488891602</t>
   </si>
   <si>
     <t xml:space="preserve">1.01103806495667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997410714626312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994520306587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967816174030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928035199642181</t>
+    <t xml:space="preserve">0.997410774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99452006816864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967815935611725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928035318851471</t>
   </si>
   <si>
     <t xml:space="preserve">0.936156690120697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947168409824371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951848685741425</t>
+    <t xml:space="preserve">0.947168529033661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951848447322845</t>
   </si>
   <si>
     <t xml:space="preserve">0.908488929271698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921015202999115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952812135219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924869298934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960245251655579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99603408575058</t>
+    <t xml:space="preserve">0.921015083789825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952812373638153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924869120121002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960245192050934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996034145355225</t>
   </si>
   <si>
     <t xml:space="preserve">1.01888406276703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979378461837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947031021118164</t>
+    <t xml:space="preserve">0.979378640651703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947030961513519</t>
   </si>
   <si>
     <t xml:space="preserve">0.998649537563324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97745156288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966577172279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973184466362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970018565654755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977864563465118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959144175052643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952261626720428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952399253845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999475538730621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984746813774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990390479564667</t>
+    <t xml:space="preserve">0.97745144367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966577351093292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973184406757355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970018327236176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977864444255829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959144115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952261447906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95239931344986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999475717544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984746754169464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990390598773956</t>
   </si>
   <si>
     <t xml:space="preserve">0.978690326213837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994244754314423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00319194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0331996679306</t>
+    <t xml:space="preserve">0.994244694709778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0031920671463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03319954872131</t>
   </si>
   <si>
     <t xml:space="preserve">1.05880272388458</t>
@@ -2873,13 +2873,13 @@
     <t xml:space="preserve">1.07270514965057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06843817234039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08743369579315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11840498447418</t>
+    <t xml:space="preserve">1.0684380531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08743393421173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11840486526489</t>
   </si>
   <si>
     <t xml:space="preserve">1.15157854557037</t>
@@ -2894,79 +2894,79 @@
     <t xml:space="preserve">1.24118864536285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18378865718842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17181301116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11344945430756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11634016036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11950623989105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16947293281555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17263877391815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16025054454803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15956223011017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15791058540344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17786967754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14717388153076</t>
+    <t xml:space="preserve">1.18378841876984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17181313037872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11344969272614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11634027957916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11950612068176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16947305202484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17263889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16025066375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15956246852875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15791034698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17786955833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14717352390289</t>
   </si>
   <si>
     <t xml:space="preserve">1.14249360561371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17140007019043</t>
+    <t xml:space="preserve">1.17140018939972</t>
   </si>
   <si>
     <t xml:space="preserve">1.1725013256073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16355395317078</t>
+    <t xml:space="preserve">1.16355407238007</t>
   </si>
   <si>
     <t xml:space="preserve">1.20636320114136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20223367214203</t>
+    <t xml:space="preserve">1.20223379135132</t>
   </si>
   <si>
     <t xml:space="preserve">1.23348021507263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22962605953217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.213383436203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19149708747864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21503508090973</t>
+    <t xml:space="preserve">1.22962594032288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21338331699371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19149696826935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21503531932831</t>
   </si>
   <si>
     <t xml:space="preserve">1.22604715824127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22577178478241</t>
+    <t xml:space="preserve">1.22577166557312</t>
   </si>
   <si>
     <t xml:space="preserve">1.24875915050507</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">1.26596570014954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26073479652405</t>
+    <t xml:space="preserve">1.26073491573334</t>
   </si>
   <si>
     <t xml:space="preserve">1.27628934383392</t>
@@ -2984,19 +2984,19 @@
     <t xml:space="preserve">1.29721212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29129302501678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27271044254303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24944746494293</t>
+    <t xml:space="preserve">1.29129314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27271032333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24944758415222</t>
   </si>
   <si>
     <t xml:space="preserve">1.23981201648712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2293506860733</t>
+    <t xml:space="preserve">1.22935080528259</t>
   </si>
   <si>
     <t xml:space="preserve">1.23155307769775</t>
@@ -3005,91 +3005,91 @@
     <t xml:space="preserve">1.19411242008209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1749792098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17566740512848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23444366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26252424716949</t>
+    <t xml:space="preserve">1.17497885227203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1756671667099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23444378376007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26252448558807</t>
   </si>
   <si>
     <t xml:space="preserve">1.24834632873535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24256503582001</t>
+    <t xml:space="preserve">1.2425651550293</t>
   </si>
   <si>
     <t xml:space="preserve">1.24848413467407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2809693813324</t>
+    <t xml:space="preserve">1.28096950054169</t>
   </si>
   <si>
     <t xml:space="preserve">1.29583549499512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28399753570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27436220645905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25564181804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24903452396393</t>
+    <t xml:space="preserve">1.28399765491486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27436244487762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25564169883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24903464317322</t>
   </si>
   <si>
     <t xml:space="preserve">1.26981961727142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24999809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24683213233948</t>
+    <t xml:space="preserve">1.24999833106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24683237075806</t>
   </si>
   <si>
     <t xml:space="preserve">1.26582789421082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26224911212921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26816785335541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24146401882172</t>
+    <t xml:space="preserve">1.26224887371063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26816773414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24146389961243</t>
   </si>
   <si>
     <t xml:space="preserve">1.25605475902557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24242758750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24008727073669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22425758838654</t>
+    <t xml:space="preserve">1.24242746829987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24008750915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22425770759583</t>
   </si>
   <si>
     <t xml:space="preserve">1.22412002086639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2345814704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21269488334656</t>
+    <t xml:space="preserve">1.23458135128021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21269524097443</t>
   </si>
   <si>
     <t xml:space="preserve">1.23210370540619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23967432975769</t>
+    <t xml:space="preserve">1.23967456817627</t>
   </si>
   <si>
     <t xml:space="preserve">1.22439539432526</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">1.12570035457611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12996757030487</t>
+    <t xml:space="preserve">1.12996768951416</t>
   </si>
   <si>
     <t xml:space="preserve">1.10959529876709</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">1.10670483112335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08674561977386</t>
+    <t xml:space="preserve">1.08674550056458</t>
   </si>
   <si>
     <t xml:space="preserve">1.11812973022461</t>
@@ -3128,28 +3128,28 @@
     <t xml:space="preserve">1.10587882995605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10326337814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09183835983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09596812725067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12404870986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14827501773834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13478517532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15309274196625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15557026863098</t>
+    <t xml:space="preserve">1.1032634973526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09183859825134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09596788883209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1240485906601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14827477931976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13478529453278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15309262275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15557038784027</t>
   </si>
   <si>
     <t xml:space="preserve">1.14978921413422</t>
@@ -3158,61 +3158,61 @@
     <t xml:space="preserve">1.11317431926727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05825185775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0707780122757</t>
+    <t xml:space="preserve">1.05825197696686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07077789306641</t>
   </si>
   <si>
     <t xml:space="preserve">1.07353103160858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05701315402985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05770134925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07449471950531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05095660686493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02590441703796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97593742609024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962998270988464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977038562297821</t>
+    <t xml:space="preserve">1.05701303482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05770146846771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07449460029602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05095648765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02590417861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975937247276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962998032569885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977038681507111</t>
   </si>
   <si>
     <t xml:space="preserve">1.02026057243347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06031656265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09968459606171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1268013715744</t>
+    <t xml:space="preserve">1.0603164434433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09968447685242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12680160999298</t>
   </si>
   <si>
     <t xml:space="preserve">1.11276125907898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21531045436859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26926934719086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25591719150543</t>
+    <t xml:space="preserve">1.2153103351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26926910877228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25591707229614</t>
   </si>
   <si>
     <t xml:space="preserve">1.24022507667542</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">1.25109946727753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26637876033783</t>
+    <t xml:space="preserve">1.26637852191925</t>
   </si>
   <si>
     <t xml:space="preserve">1.27615165710449</t>
@@ -3230,19 +3230,19 @@
     <t xml:space="preserve">1.28730130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28248369693756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3186856508255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33671772480011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32777047157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32515501976013</t>
+    <t xml:space="preserve">1.28248357772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31868541240692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33671760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32777035236359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32515490055084</t>
   </si>
   <si>
     <t xml:space="preserve">1.35653901100159</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">1.36700057983398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37002873420715</t>
+    <t xml:space="preserve">1.37002885341644</t>
   </si>
   <si>
     <t xml:space="preserve">1.35667681694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35516262054443</t>
+    <t xml:space="preserve">1.35516273975372</t>
   </si>
   <si>
     <t xml:space="preserve">1.35998046398163</t>
@@ -3269,10 +3269,10 @@
     <t xml:space="preserve">1.33231270313263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3346529006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35929203033447</t>
+    <t xml:space="preserve">1.33465278148651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35929214954376</t>
   </si>
   <si>
     <t xml:space="preserve">1.33726811408997</t>
@@ -3281,28 +3281,28 @@
     <t xml:space="preserve">1.3382316827774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3319000005722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29473435878754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31662058830261</t>
+    <t xml:space="preserve">1.33189988136292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29473423957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3166207075119</t>
   </si>
   <si>
     <t xml:space="preserve">1.32309031486511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32130074501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31634557247162</t>
+    <t xml:space="preserve">1.32130086421967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31634533405304</t>
   </si>
   <si>
     <t xml:space="preserve">1.31125235557556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29693686962128</t>
+    <t xml:space="preserve">1.29693675041199</t>
   </si>
   <si>
     <t xml:space="preserve">1.35447454452515</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">1.34552729129791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33713054656982</t>
+    <t xml:space="preserve">1.3371307849884</t>
   </si>
   <si>
     <t xml:space="preserve">1.33396458625793</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">1.31799733638763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30904984474182</t>
+    <t xml:space="preserve">1.30904996395111</t>
   </si>
   <si>
     <t xml:space="preserve">1.31951129436493</t>
@@ -3329,61 +3329,61 @@
     <t xml:space="preserve">1.31483137607574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.325843334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29679906368256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25481593608856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26610326766968</t>
+    <t xml:space="preserve">1.32584321498871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29679918289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25481581687927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26610314846039</t>
   </si>
   <si>
     <t xml:space="preserve">1.24407923221588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26197373867035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25399005413055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771424293518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34291207790375</t>
+    <t xml:space="preserve">1.26197361946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25398993492126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771436214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34291172027588</t>
   </si>
   <si>
     <t xml:space="preserve">1.38234865665436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41848170757294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43844079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637597560883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43155837059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43603181838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44257009029388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4573677778244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45392620563507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45117342472076</t>
+    <t xml:space="preserve">1.41848182678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43844091892242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637609481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43155825138092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43603193759918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44257020950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45736765861511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45392656326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45117354393005</t>
   </si>
   <si>
     <t xml:space="preserve">1.44532334804535</t>
@@ -3392,73 +3392,73 @@
     <t xml:space="preserve">1.45358240604401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.481112241745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46872389316559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48661816120148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48283290863037</t>
+    <t xml:space="preserve">1.48111236095428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46872365474701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48661839962006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48283302783966</t>
   </si>
   <si>
     <t xml:space="preserve">1.51621305942535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50864195823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51036286354065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56198167800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56507861614227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55991661548615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56955242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5588846206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57884347438812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59329700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61669731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59260869026184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58194100856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57540261745453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57987630367279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57918798923492</t>
+    <t xml:space="preserve">1.50864207744598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51036274433136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56198143959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56507849693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55991685390472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56955230236053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55888438224792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57884359359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59329688549042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61669754981995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59260857105255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58194088935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57540249824524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57987606525421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57918775081635</t>
   </si>
   <si>
     <t xml:space="preserve">1.58125257492065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57333767414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59914672374725</t>
+    <t xml:space="preserve">1.57333755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59914696216583</t>
   </si>
   <si>
     <t xml:space="preserve">1.5901997089386</t>
@@ -3467,28 +3467,28 @@
     <t xml:space="preserve">1.59536182880402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58503770828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55750787258148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55096983909607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55578744411469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56989634037018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52791333198547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53204274177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52860140800476</t>
+    <t xml:space="preserve">1.58503794670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55750799179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5509694814682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5557873249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56989645957947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52791321277618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53204262256622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52860128879547</t>
   </si>
   <si>
     <t xml:space="preserve">1.58056437969208</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">1.59742641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60637366771698</t>
+    <t xml:space="preserve">1.60637378692627</t>
   </si>
   <si>
     <t xml:space="preserve">1.58847916126251</t>
@@ -3509,76 +3509,76 @@
     <t xml:space="preserve">1.62357985973358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62564468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64457130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63837730884552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63975358009338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63287103176117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64319515228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65868055820465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65351867675781</t>
+    <t xml:space="preserve">1.62564444541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.644571185112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63837707042694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63975381851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63287115097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64319491386414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65868079662323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65351843833923</t>
   </si>
   <si>
     <t xml:space="preserve">1.65116310119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64976561069489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63928401470184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67282426357269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68330574035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68854629993439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70881021022797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72767686843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73012232780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73326647281647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73676097393036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71894240379333</t>
+    <t xml:space="preserve">1.64976513385773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63928389549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67282438278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68330562114716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68854641914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70881009101868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72767674922943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73012244701385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73326659202576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73676061630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71894252300262</t>
   </si>
   <si>
     <t xml:space="preserve">1.71440029144287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70426833629608</t>
+    <t xml:space="preserve">1.7042680978775</t>
   </si>
   <si>
     <t xml:space="preserve">1.69448578357697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71195471286774</t>
+    <t xml:space="preserve">1.71195483207703</t>
   </si>
   <si>
     <t xml:space="preserve">1.71265363693237</t>
@@ -3590,22 +3590,22 @@
     <t xml:space="preserve">1.63788664340973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65360844135284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63648891448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61832118034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65186166763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6668848991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62775444984436</t>
+    <t xml:space="preserve">1.65360856056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63648879528046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61832141876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65186154842377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66688477993011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62775456905365</t>
   </si>
   <si>
     <t xml:space="preserve">1.64662075042725</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">1.64592218399048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63229632377625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65535521507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62146556377411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60958683490753</t>
+    <t xml:space="preserve">1.63229644298553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6553555727005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6214656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60958659648895</t>
   </si>
   <si>
     <t xml:space="preserve">1.56242072582245</t>
@@ -3635,61 +3635,61 @@
     <t xml:space="preserve">1.61098432540894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58617830276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59631037712097</t>
+    <t xml:space="preserve">1.58617842197418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59631025791168</t>
   </si>
   <si>
     <t xml:space="preserve">1.57639586925507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55962586402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49359309673309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52259147167206</t>
+    <t xml:space="preserve">1.55962574481964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49359333515167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52259135246277</t>
   </si>
   <si>
     <t xml:space="preserve">1.56277012825012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57255244255066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59665989875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63334488868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61657452583313</t>
+    <t xml:space="preserve">1.57255256175995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59665966033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63334453105927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61657428741455</t>
   </si>
   <si>
     <t xml:space="preserve">1.62111639976501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6399827003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62915182113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6172730922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6256582736969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63509130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63858509063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67596876621246</t>
+    <t xml:space="preserve">1.63998246192932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62915205955505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62565803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63509142398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6385852098465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67596852779388</t>
   </si>
   <si>
     <t xml:space="preserve">1.68016111850739</t>
@@ -3701,10 +3701,10 @@
     <t xml:space="preserve">1.71125590801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71055722236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69204032421112</t>
+    <t xml:space="preserve">1.71055710315704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69204008579254</t>
   </si>
   <si>
     <t xml:space="preserve">1.66898107528687</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">1.68225753307343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6672340631485</t>
+    <t xml:space="preserve">1.66723430156708</t>
   </si>
   <si>
     <t xml:space="preserve">1.66304171085358</t>
@@ -3722,46 +3722,46 @@
     <t xml:space="preserve">1.67002928256989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66164410114288</t>
+    <t xml:space="preserve">1.66164433956146</t>
   </si>
   <si>
     <t xml:space="preserve">1.67526984214783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68365478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6682825088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67911350727081</t>
+    <t xml:space="preserve">1.68365514278412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66828238964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67911326885223</t>
   </si>
   <si>
     <t xml:space="preserve">1.66548752784729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6483678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65710210800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63963353633881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66758382320404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66094553470612</t>
+    <t xml:space="preserve">1.64836800098419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65710246562958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63963317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66758346557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66094541549683</t>
   </si>
   <si>
     <t xml:space="preserve">1.65884935855865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6085387468338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62251400947571</t>
+    <t xml:space="preserve">1.60853862762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62251377105713</t>
   </si>
   <si>
     <t xml:space="preserve">1.65815043449402</t>
@@ -3785,217 +3785,217 @@
     <t xml:space="preserve">1.74898898601532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72942340373993</t>
+    <t xml:space="preserve">1.72942352294922</t>
   </si>
   <si>
     <t xml:space="preserve">1.75388014316559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75912082195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74933815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75562727451324</t>
+    <t xml:space="preserve">1.75912070274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7493382692337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75562715530396</t>
   </si>
   <si>
     <t xml:space="preserve">1.74339878559113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76331341266632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79929947853088</t>
+    <t xml:space="preserve">1.76331317424774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79929935932159</t>
   </si>
   <si>
     <t xml:space="preserve">1.81100189685822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7815637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79319369792938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77720236778259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78192710876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79028618335724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80373299121857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7830171585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77211427688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78628838062286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81354606151581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82590270042419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81863415241241</t>
+    <t xml:space="preserve">1.78156363964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7931934595108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7772022485733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78192698955536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79028606414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80373311042786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78301739692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77211451530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78628849983215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81354582309723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82590281963348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8186342716217</t>
   </si>
   <si>
     <t xml:space="preserve">1.78556132316589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80518698692322</t>
+    <t xml:space="preserve">1.80518710613251</t>
   </si>
   <si>
     <t xml:space="preserve">1.81172895431519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7957376241684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80046200752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79646420478821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80991160869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80446016788483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80409705638885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73286318778992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74418115615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72544276714325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72581779956818</t>
+    <t xml:space="preserve">1.79573786258698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80046224594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79682791233063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646456241608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80991148948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80446028709412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80409669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73286330699921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74418139457703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72544264793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7258175611496</t>
   </si>
   <si>
     <t xml:space="preserve">1.71494936943054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61638462543488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60626578330994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58565330505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62537896633148</t>
+    <t xml:space="preserve">1.61638474464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60626554489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.585653424263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62537884712219</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60888934135437</t>
+    <t xml:space="preserve">1.60888922214508</t>
   </si>
   <si>
     <t xml:space="preserve">1.65873372554779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69246280193329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67222535610199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66772782802582</t>
+    <t xml:space="preserve">1.69246292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67222547531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66772794723511</t>
   </si>
   <si>
     <t xml:space="preserve">1.66060757637024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65273725986481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66735339164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65011382102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68084514141083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311205387115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.635498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67334973812103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67185056209564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68721604347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69583606719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71157610416412</t>
+    <t xml:space="preserve">1.65273714065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66735315322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65011394023895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68084526062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311217308044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63549780845642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67334961891174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67185032367706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68721580505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69583594799042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7115763425827</t>
   </si>
   <si>
     <t xml:space="preserve">1.70670437812805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70445537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75767290592194</t>
+    <t xml:space="preserve">1.70445561408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75767314434052</t>
   </si>
   <si>
     <t xml:space="preserve">1.7944004535675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81238961219788</t>
+    <t xml:space="preserve">1.8123893737793</t>
   </si>
   <si>
     <t xml:space="preserve">1.82363259792328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83749902248383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84611880779266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86036038398743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90795612335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91919898986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9203234910965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93194103240967</t>
+    <t xml:space="preserve">1.83749890327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84611892700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86036014556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90795588493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91919887065887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92032337188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93194127082825</t>
   </si>
   <si>
     <t xml:space="preserve">1.9300674200058</t>
@@ -4004,13 +4004,13 @@
     <t xml:space="preserve">1.89933621883392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91245329380035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91282773017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84874212741852</t>
+    <t xml:space="preserve">1.91245305538177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91282796859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8487423658371</t>
   </si>
   <si>
     <t xml:space="preserve">1.86560690402985</t>
@@ -4019,40 +4019,40 @@
     <t xml:space="preserve">1.92219722270966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95817506313324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94655692577362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96342194080353</t>
+    <t xml:space="preserve">1.95817518234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94655728340149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96342170238495</t>
   </si>
   <si>
     <t xml:space="preserve">2.00127387046814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02151155471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04474687576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99902498722076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03500294685364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07585287094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13881421089172</t>
+    <t xml:space="preserve">2.02151131629944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04474711418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99902510643005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03500318527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07585310935974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13881468772888</t>
   </si>
   <si>
     <t xml:space="preserve">2.18865895271301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07435417175293</t>
+    <t xml:space="preserve">2.07435393333435</t>
   </si>
   <si>
     <t xml:space="preserve">2.13843989372253</t>
@@ -4061,28 +4061,28 @@
     <t xml:space="preserve">2.09196805953979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05299186706543</t>
+    <t xml:space="preserve">2.05299210548401</t>
   </si>
   <si>
     <t xml:space="preserve">2.04024982452393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00427198410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99377834796906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96417164802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80789244174957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8569872379303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71907162666321</t>
+    <t xml:space="preserve">2.00427174568176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99377846717834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9641717672348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80789196491241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85698699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71907150745392</t>
   </si>
   <si>
     <t xml:space="preserve">1.58640289306641</t>
@@ -4091,19 +4091,19 @@
     <t xml:space="preserve">1.60851430892944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56204295158386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42127907276154</t>
+    <t xml:space="preserve">1.56204307079315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42127919197083</t>
   </si>
   <si>
     <t xml:space="preserve">1.38155341148376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39834308624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55342316627502</t>
+    <t xml:space="preserve">1.39834320545197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55342304706573</t>
   </si>
   <si>
     <t xml:space="preserve">1.4352205991745</t>
@@ -4112,34 +4112,34 @@
     <t xml:space="preserve">1.43866848945618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49158585071564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50507748126984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61001348495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55304837226868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56354176998138</t>
+    <t xml:space="preserve">1.49158620834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50507771968842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61001360416412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55304849147797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56354188919067</t>
   </si>
   <si>
     <t xml:space="preserve">1.54892587661743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57403564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53505957126617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52231705188751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52381634712219</t>
+    <t xml:space="preserve">1.57403552532196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53505945205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5223171710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5238162279129</t>
   </si>
   <si>
     <t xml:space="preserve">1.53243613243103</t>
@@ -4151,13 +4151,13 @@
     <t xml:space="preserve">1.59951996803284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56166815757751</t>
+    <t xml:space="preserve">1.56166803836823</t>
   </si>
   <si>
     <t xml:space="preserve">1.57778322696686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57028770446777</t>
+    <t xml:space="preserve">1.57028782367706</t>
   </si>
   <si>
     <t xml:space="preserve">1.53056228160858</t>
@@ -4169,22 +4169,22 @@
     <t xml:space="preserve">1.46280372142792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48558962345123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48469018936157</t>
+    <t xml:space="preserve">1.48558974266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48469054698944</t>
   </si>
   <si>
     <t xml:space="preserve">1.45500838756561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4572571516037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47734463214874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47884404659271</t>
+    <t xml:space="preserve">1.45725727081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47734487056732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47884392738342</t>
   </si>
   <si>
     <t xml:space="preserve">1.51444697380066</t>
@@ -4193,28 +4193,28 @@
     <t xml:space="preserve">1.51782011985779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48618924617767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46055507659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43761920928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4397177696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44361543655396</t>
+    <t xml:space="preserve">1.48618936538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46055519580841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43761909008026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43971788883209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44361555576324</t>
   </si>
   <si>
     <t xml:space="preserve">1.46520221233368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44091713428497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46924960613251</t>
+    <t xml:space="preserve">1.44091701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46924984455109</t>
   </si>
   <si>
     <t xml:space="preserve">1.44301581382751</t>
@@ -4223,52 +4223,52 @@
     <t xml:space="preserve">1.44256603717804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40913641452789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37165951728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39534497261047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45410919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47074890136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47839403152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46490228176117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49188590049744</t>
+    <t xml:space="preserve">1.40913653373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3716596364975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39534509181976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45410907268524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4707487821579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47839391231537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46490240097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49188578128815</t>
   </si>
   <si>
     <t xml:space="preserve">1.49008691310883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48633933067322</t>
+    <t xml:space="preserve">1.48633921146393</t>
   </si>
   <si>
     <t xml:space="preserve">1.54183995723724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54496204853058</t>
+    <t xml:space="preserve">1.54496228694916</t>
   </si>
   <si>
     <t xml:space="preserve">1.586958527565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60139977931976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59788691997528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60764443874359</t>
+    <t xml:space="preserve">1.60139966011047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59788680076599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6076443195343</t>
   </si>
   <si>
     <t xml:space="preserve">1.58500695228577</t>
@@ -4277,55 +4277,55 @@
     <t xml:space="preserve">1.56119871139526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54012274742126</t>
+    <t xml:space="preserve">1.54012262821198</t>
   </si>
   <si>
     <t xml:space="preserve">1.59047114849091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56315016746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55339252948761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53528296947479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42193973064423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37307417392731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38166069984436</t>
+    <t xml:space="preserve">1.5631502866745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55339276790619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5352828502655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42193984985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3730742931366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38166081905365</t>
   </si>
   <si>
     <t xml:space="preserve">1.44520163536072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39961469173431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40788888931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46175026893616</t>
+    <t xml:space="preserve">1.39961457252502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40788900852203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46175038814545</t>
   </si>
   <si>
     <t xml:space="preserve">1.47221040725708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46799504756927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43630290031433</t>
+    <t xml:space="preserve">1.46799516677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43630278110504</t>
   </si>
   <si>
     <t xml:space="preserve">1.4692440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47798681259155</t>
+    <t xml:space="preserve">1.47798669338226</t>
   </si>
   <si>
     <t xml:space="preserve">1.48204600811005</t>
@@ -4340,22 +4340,22 @@
     <t xml:space="preserve">1.37978744506836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34669005870819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30469357967377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31000173091888</t>
+    <t xml:space="preserve">1.34669017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30469369888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31000185012817</t>
   </si>
   <si>
     <t xml:space="preserve">1.36230206489563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3758841753006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35199809074402</t>
+    <t xml:space="preserve">1.37588429450989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35199797153473</t>
   </si>
   <si>
     <t xml:space="preserve">1.33295142650604</t>
@@ -4364,25 +4364,25 @@
     <t xml:space="preserve">1.32764339447021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25411105155945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27393805980682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30672335624695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38369047641754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33513712882996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29813659191132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29579484462738</t>
+    <t xml:space="preserve">1.25411093235016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27393794059753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30672323703766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38369023799896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33513700962067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2981368303299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29579496383667</t>
   </si>
   <si>
     <t xml:space="preserve">1.31765162944794</t>
@@ -4391,67 +4391,67 @@
     <t xml:space="preserve">1.29329717159271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3092212677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33154654502869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34934413433075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36542427539825</t>
+    <t xml:space="preserve">1.30922114849091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3315464258194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34934401512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36542439460754</t>
   </si>
   <si>
     <t xml:space="preserve">1.36370694637299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38462722301483</t>
+    <t xml:space="preserve">1.38462710380554</t>
   </si>
   <si>
     <t xml:space="preserve">1.39180862903595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41600728034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41850507259369</t>
+    <t xml:space="preserve">1.41600716114044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4185049533844</t>
   </si>
   <si>
     <t xml:space="preserve">1.41756856441498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43052649497986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44707500934601</t>
+    <t xml:space="preserve">1.43052637577057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4470751285553</t>
   </si>
   <si>
     <t xml:space="preserve">1.44785559177399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42740392684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42615497112274</t>
+    <t xml:space="preserve">1.42740404605865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42615509033203</t>
   </si>
   <si>
     <t xml:space="preserve">1.38415884971619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34138202667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36573684215546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37666499614716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35699391365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31530976295471</t>
+    <t xml:space="preserve">1.34138190746307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36573672294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37666511535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35699379444122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.315309882164</t>
   </si>
   <si>
     <t xml:space="preserve">1.32811176776886</t>
@@ -4463,43 +4463,43 @@
     <t xml:space="preserve">1.34497272968292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32217919826508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35683786869049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32467710971832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32998502254486</t>
+    <t xml:space="preserve">1.32217907905579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3568377494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32467699050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32998526096344</t>
   </si>
   <si>
     <t xml:space="preserve">1.32701897621155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35855507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43099474906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48001646995544</t>
+    <t xml:space="preserve">1.35855519771576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43099498748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48001635074615</t>
   </si>
   <si>
     <t xml:space="preserve">1.46846354007721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48329484462738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49875092506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4948478937149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49516010284424</t>
+    <t xml:space="preserve">1.48329496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49875056743622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49484765529633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49515998363495</t>
   </si>
   <si>
     <t xml:space="preserve">1.44348430633545</t>
@@ -4511,19 +4511,19 @@
     <t xml:space="preserve">1.44567000865936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37697732448578</t>
+    <t xml:space="preserve">1.37697744369507</t>
   </si>
   <si>
     <t xml:space="preserve">1.38041174411774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34825134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32592606544495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29189193248749</t>
+    <t xml:space="preserve">1.34825122356415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32592618465424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2918918132782</t>
   </si>
   <si>
     <t xml:space="preserve">1.32920455932617</t>
@@ -4535,16 +4535,16 @@
     <t xml:space="preserve">1.39571166038513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35917949676514</t>
+    <t xml:space="preserve">1.35917937755585</t>
   </si>
   <si>
     <t xml:space="preserve">1.33654224872589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33139026165009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32342803478241</t>
+    <t xml:space="preserve">1.33139038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3234281539917</t>
   </si>
   <si>
     <t xml:space="preserve">1.30781626701355</t>
@@ -4553,148 +4553,148 @@
     <t xml:space="preserve">1.33201479911804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33669817447662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36058473587036</t>
+    <t xml:space="preserve">1.33669829368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36058461666107</t>
   </si>
   <si>
     <t xml:space="preserve">1.40726459026337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.398521900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42771625518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4266232252121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44863617420197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45550537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45644223690033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4876663684845</t>
+    <t xml:space="preserve">1.39852178096771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4277161359787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42662334442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44863641262054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45550560951233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45644235610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48766624927521</t>
   </si>
   <si>
     <t xml:space="preserve">1.48719787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5057760477066</t>
+    <t xml:space="preserve">1.50577628612518</t>
   </si>
   <si>
     <t xml:space="preserve">1.51842188835144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51810967922211</t>
+    <t xml:space="preserve">1.5181097984314</t>
   </si>
   <si>
     <t xml:space="preserve">1.53746843338013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61193776130676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66189587116241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67672741413116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68141102790833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69936466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68648493289948</t>
+    <t xml:space="preserve">1.61193764209747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66189610958099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67672753334045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6814112663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69936490058899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68648481369019</t>
   </si>
   <si>
     <t xml:space="preserve">1.70678055286407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.709512591362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70990288257599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70014536380768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73019850254059</t>
+    <t xml:space="preserve">1.70951271057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70990312099457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70014524459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7301983833313</t>
   </si>
   <si>
     <t xml:space="preserve">1.72882580757141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74457180500031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73165190219879</t>
+    <t xml:space="preserve">1.74457168579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73165202140808</t>
   </si>
   <si>
     <t xml:space="preserve">1.7441680431366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74295687675476</t>
+    <t xml:space="preserve">1.74295675754547</t>
   </si>
   <si>
     <t xml:space="preserve">1.70863854885101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72357726097107</t>
+    <t xml:space="preserve">1.72357714176178</t>
   </si>
   <si>
     <t xml:space="preserve">1.71348345279694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68320298194885</t>
+    <t xml:space="preserve">1.68320286273956</t>
   </si>
   <si>
     <t xml:space="preserve">1.69289267063141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67835783958435</t>
+    <t xml:space="preserve">1.67835795879364</t>
   </si>
   <si>
     <t xml:space="preserve">1.66866815090179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66463088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66140067577362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6690719127655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67028307914734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69652652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68562531471252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6104484796524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66180467605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64282846450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67593562602997</t>
+    <t xml:space="preserve">1.66463077068329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66140079498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66907179355621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67028295993805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6965264081955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68562543392181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61044836044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66180455684662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64282858371735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67593550682068</t>
   </si>
   <si>
     <t xml:space="preserve">1.69612264633179</t>
@@ -4709,16 +4709,16 @@
     <t xml:space="preserve">1.68118417263031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6799727678299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70137143135071</t>
+    <t xml:space="preserve">1.67997300624847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70137131214142</t>
   </si>
   <si>
     <t xml:space="preserve">1.67795419692993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71429109573364</t>
+    <t xml:space="preserve">1.71429097652435</t>
   </si>
   <si>
     <t xml:space="preserve">1.75426161289215</t>
@@ -4727,16 +4727,16 @@
     <t xml:space="preserve">1.799480676651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78857970237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80351793766022</t>
+    <t xml:space="preserve">1.78857946395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80351805686951</t>
   </si>
   <si>
     <t xml:space="preserve">1.81684148311615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82451260089874</t>
+    <t xml:space="preserve">1.82451248168945</t>
   </si>
   <si>
     <t xml:space="preserve">1.84429609775543</t>
@@ -4745,61 +4745,61 @@
     <t xml:space="preserve">1.84752631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84510374069214</t>
+    <t xml:space="preserve">1.84510362148285</t>
   </si>
   <si>
     <t xml:space="preserve">1.82572388648987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79503965377808</t>
+    <t xml:space="preserve">1.79503977298737</t>
   </si>
   <si>
     <t xml:space="preserve">1.76072132587433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80836319923401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84550738334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317873954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89153409004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89839780330658</t>
+    <t xml:space="preserve">1.80836308002472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84550750255585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85317862033844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8915342092514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89839792251587</t>
   </si>
   <si>
     <t xml:space="preserve">1.89274537563324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94603943824768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98076105117798</t>
+    <t xml:space="preserve">1.94603931903839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98076128959656</t>
   </si>
   <si>
     <t xml:space="preserve">1.98237597942352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92423701286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97591638565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99327719211578</t>
+    <t xml:space="preserve">1.92423725128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97591614723206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99327707290649</t>
   </si>
   <si>
     <t xml:space="preserve">1.99368119239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02194285392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00014090538025</t>
+    <t xml:space="preserve">2.02194309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00014066696167</t>
   </si>
   <si>
     <t xml:space="preserve">2.01790547370911</t>
@@ -4811,37 +4811,37 @@
     <t xml:space="preserve">2.01467537879944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05989456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07079577445984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06231713294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06150984764099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99973702430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03001737594604</t>
+    <t xml:space="preserve">2.05989480018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07079601287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06231689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06150960922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99973714351654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03001761436462</t>
   </si>
   <si>
     <t xml:space="preserve">2.04535984992981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06837320327759</t>
+    <t xml:space="preserve">2.06837344169617</t>
   </si>
   <si>
     <t xml:space="preserve">2.0485897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05262756347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07887077331543</t>
+    <t xml:space="preserve">2.05262732505798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07887053489685</t>
   </si>
   <si>
     <t xml:space="preserve">2.09340524673462</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">2.07119965553284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0772557258606</t>
+    <t xml:space="preserve">2.07725548744202</t>
   </si>
   <si>
     <t xml:space="preserve">2.04414892196655</t>
@@ -4859,19 +4859,19 @@
     <t xml:space="preserve">2.00417828559875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88184404373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94482827186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81159293651581</t>
+    <t xml:space="preserve">1.88184416294098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94482803344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81159317493439</t>
   </si>
   <si>
     <t xml:space="preserve">1.81522679328918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77081513404846</t>
+    <t xml:space="preserve">1.77081525325775</t>
   </si>
   <si>
     <t xml:space="preserve">1.83702886104584</t>
@@ -4880,25 +4880,25 @@
     <t xml:space="preserve">1.90162765979767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89193785190582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255823612213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8273389339447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83420276641846</t>
+    <t xml:space="preserve">1.89193761348724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87255811691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82733905315399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83420252799988</t>
   </si>
   <si>
     <t xml:space="preserve">1.85196721553802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87982571125031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90970253944397</t>
+    <t xml:space="preserve">1.87982559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90970230102539</t>
   </si>
   <si>
     <t xml:space="preserve">1.91172122955322</t>
@@ -4907,7 +4907,7 @@
     <t xml:space="preserve">1.86448323726654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90404999256134</t>
+    <t xml:space="preserve">1.90405035018921</t>
   </si>
   <si>
     <t xml:space="preserve">1.91939234733582</t>
@@ -4916,7 +4916,7 @@
     <t xml:space="preserve">1.934330701828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92827439308167</t>
+    <t xml:space="preserve">1.92827475070953</t>
   </si>
   <si>
     <t xml:space="preserve">1.97147512435913</t>
@@ -4925,46 +4925,46 @@
     <t xml:space="preserve">2.00094819068909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01750183105469</t>
+    <t xml:space="preserve">2.01750159263611</t>
   </si>
   <si>
     <t xml:space="preserve">2.01023435592651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00619697570801</t>
+    <t xml:space="preserve">2.00619673728943</t>
   </si>
   <si>
     <t xml:space="preserve">2.02436542510986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98722112178802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96541905403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98479843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92544865608215</t>
+    <t xml:space="preserve">1.98722064495087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96541917324066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98479855060577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92544829845428</t>
   </si>
   <si>
     <t xml:space="preserve">1.88022923469543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91293227672577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395642280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96380388736725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883581161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98358738422394</t>
+    <t xml:space="preserve">1.91293251514435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89395654201508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96380376815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883605003357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98358726501465</t>
   </si>
   <si>
     <t xml:space="preserve">1.95048034191132</t>
@@ -4973,19 +4973,19 @@
     <t xml:space="preserve">1.93917560577393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96057415008545</t>
+    <t xml:space="preserve">1.96057403087616</t>
   </si>
   <si>
     <t xml:space="preserve">1.95451784133911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94038724899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92948579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95128810405731</t>
+    <t xml:space="preserve">1.94038689136505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9294855594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95128798484802</t>
   </si>
   <si>
     <t xml:space="preserve">1.96353375911713</t>
@@ -4994,16 +4994,16 @@
     <t xml:space="preserve">1.9643726348877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88888430595398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88804543018341</t>
+    <t xml:space="preserve">1.88888442516327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8880455493927</t>
   </si>
   <si>
     <t xml:space="preserve">1.88301289081573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86665725708008</t>
+    <t xml:space="preserve">1.86665737628937</t>
   </si>
   <si>
     <t xml:space="preserve">1.85365641117096</t>
@@ -5015,13 +5015,13 @@
     <t xml:space="preserve">1.87043154239655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9052402973175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89475548267365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91698276996613</t>
+    <t xml:space="preserve">1.90523993968964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89475572109222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91698288917542</t>
   </si>
   <si>
     <t xml:space="preserve">1.93166077136993</t>
@@ -5030,22 +5030,22 @@
     <t xml:space="preserve">1.94927477836609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93711292743683</t>
+    <t xml:space="preserve">1.93711268901825</t>
   </si>
   <si>
     <t xml:space="preserve">1.93417739868164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93920993804932</t>
+    <t xml:space="preserve">1.93920969963074</t>
   </si>
   <si>
     <t xml:space="preserve">1.97108244895935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97779262065887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99037384986877</t>
+    <t xml:space="preserve">1.97779285907745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99037408828735</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840735435486</t>
@@ -5054,10 +5054,10 @@
     <t xml:space="preserve">2.00169730186462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01805281639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99540686607361</t>
+    <t xml:space="preserve">2.01805305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99540638923645</t>
   </si>
   <si>
     <t xml:space="preserve">1.95850133895874</t>
@@ -5069,13 +5069,13 @@
     <t xml:space="preserve">1.98072838783264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98240578174591</t>
+    <t xml:space="preserve">1.98240602016449</t>
   </si>
   <si>
     <t xml:space="preserve">2.00127792358398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01302051544189</t>
+    <t xml:space="preserve">2.01302075386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.04405450820923</t>
@@ -5090,19 +5090,19 @@
     <t xml:space="preserve">1.96311438083649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97024369239807</t>
+    <t xml:space="preserve">1.97024393081665</t>
   </si>
   <si>
     <t xml:space="preserve">1.97695410251617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99666476249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01973056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04992580413818</t>
+    <t xml:space="preserve">1.99666500091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01973032951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04992604255676</t>
   </si>
   <si>
     <t xml:space="preserve">2.03860282897949</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">2.11534929275513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12289786338806</t>
+    <t xml:space="preserve">2.12289762496948</t>
   </si>
   <si>
     <t xml:space="preserve">2.12709164619446</t>
@@ -5132,13 +5132,13 @@
     <t xml:space="preserve">2.15812587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18874049186707</t>
+    <t xml:space="preserve">2.18874025344849</t>
   </si>
   <si>
     <t xml:space="preserve">2.20509624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18832111358643</t>
+    <t xml:space="preserve">2.188321352005</t>
   </si>
   <si>
     <t xml:space="preserve">2.149738073349</t>
@@ -5156,10 +5156,10 @@
     <t xml:space="preserve">1.96101760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0067298412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04489326477051</t>
+    <t xml:space="preserve">2.00672960281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04489350318909</t>
   </si>
   <si>
     <t xml:space="preserve">2.04615163803101</t>
@@ -5174,13 +5174,13 @@
     <t xml:space="preserve">2.02937650680542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02224683761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04573178291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06292700767517</t>
+    <t xml:space="preserve">2.02224707603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04573202133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06292676925659</t>
   </si>
   <si>
     <t xml:space="preserve">2.05915212631226</t>
@@ -5195,13 +5195,13 @@
     <t xml:space="preserve">2.07760500907898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09060597419739</t>
+    <t xml:space="preserve">2.09060573577881</t>
   </si>
   <si>
     <t xml:space="preserve">2.09857392311096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.073410987854</t>
+    <t xml:space="preserve">2.07341122627258</t>
   </si>
   <si>
     <t xml:space="preserve">2.0587329864502</t>
@@ -5210,28 +5210,28 @@
     <t xml:space="preserve">2.05202293395996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00589108467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00043940544128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02434372901917</t>
+    <t xml:space="preserve">2.0058913230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00043916702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02434396743774</t>
   </si>
   <si>
     <t xml:space="preserve">2.08012127876282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07634687423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06544280052185</t>
+    <t xml:space="preserve">2.07634663581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06544303894043</t>
   </si>
   <si>
     <t xml:space="preserve">2.07592725753784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07089519500732</t>
+    <t xml:space="preserve">2.07089495658875</t>
   </si>
   <si>
     <t xml:space="preserve">2.03818321228027</t>
@@ -5240,34 +5240,34 @@
     <t xml:space="preserve">2.04782915115356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10821938514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09102535247803</t>
+    <t xml:space="preserve">2.10821962356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09102511405945</t>
   </si>
   <si>
     <t xml:space="preserve">2.06418490409851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03482842445374</t>
+    <t xml:space="preserve">2.03482818603516</t>
   </si>
   <si>
     <t xml:space="preserve">2.0323121547699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04657125473022</t>
+    <t xml:space="preserve">2.04657101631165</t>
   </si>
   <si>
     <t xml:space="preserve">1.98156714439392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98282516002655</t>
+    <t xml:space="preserve">1.98282539844513</t>
   </si>
   <si>
     <t xml:space="preserve">2.01427865028381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99330961704254</t>
+    <t xml:space="preserve">1.99330937862396</t>
   </si>
   <si>
     <t xml:space="preserve">2.03398942947388</t>
@@ -5276,10 +5276,10 @@
     <t xml:space="preserve">2.04908728599548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05286145210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02686023712158</t>
+    <t xml:space="preserve">2.05286169052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.026859998703</t>
   </si>
   <si>
     <t xml:space="preserve">2.03650593757629</t>
@@ -5291,13 +5291,13 @@
     <t xml:space="preserve">1.96605014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99079346656799</t>
+    <t xml:space="preserve">1.99079370498657</t>
   </si>
   <si>
     <t xml:space="preserve">1.97611522674561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98785793781281</t>
+    <t xml:space="preserve">1.98785769939423</t>
   </si>
   <si>
     <t xml:space="preserve">1.9941486120224</t>
@@ -5312,7 +5312,7 @@
     <t xml:space="preserve">2.11702656745911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15015745162964</t>
+    <t xml:space="preserve">2.15015769004822</t>
   </si>
   <si>
     <t xml:space="preserve">2.15225458145142</t>
@@ -5321,10 +5321,10 @@
     <t xml:space="preserve">2.15057682991028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15435123443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16231966018677</t>
+    <t xml:space="preserve">2.15435147285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16231942176819</t>
   </si>
   <si>
     <t xml:space="preserve">2.18286919593811</t>
@@ -5342,22 +5342,22 @@
     <t xml:space="preserve">2.25164747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27114605903625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23835301399231</t>
+    <t xml:space="preserve">2.27114582061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23835277557373</t>
   </si>
   <si>
     <t xml:space="preserve">2.25209045410156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26848697662354</t>
+    <t xml:space="preserve">2.26848721504211</t>
   </si>
   <si>
     <t xml:space="preserve">2.3039391040802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30438232421875</t>
+    <t xml:space="preserve">2.30438208580017</t>
   </si>
   <si>
     <t xml:space="preserve">2.326096534729</t>
@@ -5366,13 +5366,13 @@
     <t xml:space="preserve">2.34559535980225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34116363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36287784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38858079910278</t>
+    <t xml:space="preserve">2.34116387367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36287808418274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38858103752136</t>
   </si>
   <si>
     <t xml:space="preserve">2.37838840484619</t>
@@ -5387,10 +5387,10 @@
     <t xml:space="preserve">2.39301228523254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38503551483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37705874443054</t>
+    <t xml:space="preserve">2.38503575325012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37705898284912</t>
   </si>
   <si>
     <t xml:space="preserve">2.37572956085205</t>
@@ -5411,13 +5411,13 @@
     <t xml:space="preserve">2.33717560768127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33097147941589</t>
+    <t xml:space="preserve">2.33097124099731</t>
   </si>
   <si>
     <t xml:space="preserve">2.34603834152222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35445833206177</t>
+    <t xml:space="preserve">2.35445809364319</t>
   </si>
   <si>
     <t xml:space="preserve">2.34204983711243</t>
@@ -5426,16 +5426,16 @@
     <t xml:space="preserve">2.34293627738953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38813781738281</t>
+    <t xml:space="preserve">2.38813757896423</t>
   </si>
   <si>
     <t xml:space="preserve">2.38592171669006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44131588935852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47056365013123</t>
+    <t xml:space="preserve">2.44131565093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47056341171265</t>
   </si>
   <si>
     <t xml:space="preserve">2.47765421867371</t>
@@ -5468,19 +5468,19 @@
     <t xml:space="preserve">2.45328068733215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45682597160339</t>
+    <t xml:space="preserve">2.45682621002197</t>
   </si>
   <si>
     <t xml:space="preserve">2.51221990585327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48873281478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49139189720154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46568918228149</t>
+    <t xml:space="preserve">2.4887330532074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49139165878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46568894386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.54988789558411</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">2.517094373703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49670958518982</t>
+    <t xml:space="preserve">2.49670934677124</t>
   </si>
   <si>
     <t xml:space="preserve">2.46879124641418</t>
@@ -5516,7 +5516,7 @@
     <t xml:space="preserve">2.4869601726532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49537992477417</t>
+    <t xml:space="preserve">2.49538016319275</t>
   </si>
   <si>
     <t xml:space="preserve">2.50690197944641</t>
@@ -5528,13 +5528,13 @@
     <t xml:space="preserve">2.51620817184448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52551436424255</t>
+    <t xml:space="preserve">2.52551412582397</t>
   </si>
   <si>
     <t xml:space="preserve">2.55742120742798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56717038154602</t>
+    <t xml:space="preserve">2.5671706199646</t>
   </si>
   <si>
     <t xml:space="preserve">2.60483813285828</t>
@@ -5546,7 +5546,7 @@
     <t xml:space="preserve">2.61680340766907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61458778381348</t>
+    <t xml:space="preserve">2.6145875453949</t>
   </si>
   <si>
     <t xml:space="preserve">2.60395169258118</t>
@@ -5585,13 +5585,13 @@
     <t xml:space="preserve">2.86053609848022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86186528205872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90352177619934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89908981323242</t>
+    <t xml:space="preserve">2.86186552047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90352153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.899090051651</t>
   </si>
   <si>
     <t xml:space="preserve">2.91858863830566</t>
@@ -5615,10 +5615,10 @@
     <t xml:space="preserve">2.96689224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01608180999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00012826919556</t>
+    <t xml:space="preserve">3.01608204841614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00012850761414</t>
   </si>
   <si>
     <t xml:space="preserve">2.95049548149109</t>
@@ -5627,7 +5627,7 @@
     <t xml:space="preserve">2.97442579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93498516082764</t>
+    <t xml:space="preserve">2.93498539924622</t>
   </si>
   <si>
     <t xml:space="preserve">2.96910786628723</t>
@@ -5639,7 +5639,7 @@
     <t xml:space="preserve">2.91592979431152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9482798576355</t>
+    <t xml:space="preserve">2.94827961921692</t>
   </si>
   <si>
     <t xml:space="preserve">2.88225054740906</t>
@@ -5648,16 +5648,16 @@
     <t xml:space="preserve">2.92390656471252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96866488456726</t>
+    <t xml:space="preserve">2.96866464614868</t>
   </si>
   <si>
     <t xml:space="preserve">2.99303817749023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03868246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11933612823486</t>
+    <t xml:space="preserve">3.03868269920349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11933588981628</t>
   </si>
   <si>
     <t xml:space="preserve">3.11712002754211</t>
@@ -5681,16 +5681,16 @@
     <t xml:space="preserve">3.06837344169617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15789008140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18935346603394</t>
+    <t xml:space="preserve">3.15788984298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18935370445251</t>
   </si>
   <si>
     <t xml:space="preserve">3.18492197990417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17251396179199</t>
+    <t xml:space="preserve">3.17251372337341</t>
   </si>
   <si>
     <t xml:space="preserve">3.19112634658813</t>
@@ -5699,13 +5699,13 @@
     <t xml:space="preserve">3.21416997909546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28197193145752</t>
+    <t xml:space="preserve">3.2819721698761</t>
   </si>
   <si>
     <t xml:space="preserve">3.3032431602478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30856132507324</t>
+    <t xml:space="preserve">3.30856108665466</t>
   </si>
   <si>
     <t xml:space="preserve">3.34046792984009</t>
@@ -5738,13 +5738,13 @@
     <t xml:space="preserve">3.33677363395691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33030867576599</t>
+    <t xml:space="preserve">3.33030891418457</t>
   </si>
   <si>
     <t xml:space="preserve">3.36170959472656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27628111839294</t>
+    <t xml:space="preserve">3.27628135681152</t>
   </si>
   <si>
     <t xml:space="preserve">3.2721254825592</t>
@@ -5753,7 +5753,7 @@
     <t xml:space="preserve">3.32569122314453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31276154518127</t>
+    <t xml:space="preserve">3.3127613067627</t>
   </si>
   <si>
     <t xml:space="preserve">3.29521417617798</t>
@@ -5762,7 +5762,7 @@
     <t xml:space="preserve">3.21070957183838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26058125495911</t>
+    <t xml:space="preserve">3.26058101654053</t>
   </si>
   <si>
     <t xml:space="preserve">3.15391159057617</t>
@@ -5777,7 +5777,7 @@
     <t xml:space="preserve">3.15760564804077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1954710483551</t>
+    <t xml:space="preserve">3.19547128677368</t>
   </si>
   <si>
     <t xml:space="preserve">3.22640991210938</t>
@@ -5786,10 +5786,10 @@
     <t xml:space="preserve">3.18900632858276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24765133857727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25688695907593</t>
+    <t xml:space="preserve">3.24765157699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25688672065735</t>
   </si>
   <si>
     <t xml:space="preserve">3.199627161026</t>
@@ -5804,13 +5804,13 @@
     <t xml:space="preserve">3.26011943817139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30583500862122</t>
+    <t xml:space="preserve">3.30583477020264</t>
   </si>
   <si>
     <t xml:space="preserve">3.27812838554382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2933669090271</t>
+    <t xml:space="preserve">3.29336714744568</t>
   </si>
   <si>
     <t xml:space="preserve">3.28136086463928</t>
@@ -5822,7 +5822,7 @@
     <t xml:space="preserve">3.31645584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34277677536011</t>
+    <t xml:space="preserve">3.34277653694153</t>
   </si>
   <si>
     <t xml:space="preserve">3.33215594291687</t>
@@ -5831,7 +5831,7 @@
     <t xml:space="preserve">3.34600901603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36909770965576</t>
+    <t xml:space="preserve">3.36909794807434</t>
   </si>
   <si>
     <t xml:space="preserve">3.38710713386536</t>
@@ -5864,7 +5864,7 @@
     <t xml:space="preserve">3.32800006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18115615844727</t>
+    <t xml:space="preserve">3.18115592002869</t>
   </si>
   <si>
     <t xml:space="preserve">3.15021729469299</t>
@@ -5885,16 +5885,16 @@
     <t xml:space="preserve">3.2051682472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22225403785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32199668884277</t>
+    <t xml:space="preserve">3.22225379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32199692726135</t>
   </si>
   <si>
     <t xml:space="preserve">3.33769726753235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31968832015991</t>
+    <t xml:space="preserve">3.31968808174133</t>
   </si>
   <si>
     <t xml:space="preserve">3.33954429626465</t>
@@ -5912,13 +5912,13 @@
     <t xml:space="preserve">3.41712236404419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41850757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44344305992126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47669100761414</t>
+    <t xml:space="preserve">3.41850733757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44344329833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47669076919556</t>
   </si>
   <si>
     <t xml:space="preserve">3.48500299453735</t>
@@ -5930,7 +5930,7 @@
     <t xml:space="preserve">3.43005180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4642231464386</t>
+    <t xml:space="preserve">3.46422290802002</t>
   </si>
   <si>
     <t xml:space="preserve">3.38618350028992</t>
@@ -5942,7 +5942,7 @@
     <t xml:space="preserve">3.40696310997009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41296625137329</t>
+    <t xml:space="preserve">3.41296601295471</t>
   </si>
   <si>
     <t xml:space="preserve">3.4485228061676</t>
@@ -5951,7 +5951,7 @@
     <t xml:space="preserve">3.46791744232178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45314073562622</t>
+    <t xml:space="preserve">3.45314049720764</t>
   </si>
   <si>
     <t xml:space="preserve">3.47715282440186</t>
@@ -5966,7 +5966,7 @@
     <t xml:space="preserve">3.53256559371948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4660701751709</t>
+    <t xml:space="preserve">3.46607041358948</t>
   </si>
   <si>
     <t xml:space="preserve">3.48869705200195</t>
@@ -5975,7 +5975,7 @@
     <t xml:space="preserve">3.57966637611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57458710670471</t>
+    <t xml:space="preserve">3.57458686828613</t>
   </si>
   <si>
     <t xml:space="preserve">3.54411005973816</t>
@@ -5999,7 +5999,7 @@
     <t xml:space="preserve">3.49654722213745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51686549186707</t>
+    <t xml:space="preserve">3.51686525344849</t>
   </si>
   <si>
     <t xml:space="preserve">3.55565404891968</t>
@@ -6014,10 +6014,10 @@
     <t xml:space="preserve">3.62999987602234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62030267715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66694164276123</t>
+    <t xml:space="preserve">3.62030243873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66694140434265</t>
   </si>
   <si>
     <t xml:space="preserve">3.69418621063232</t>
@@ -6029,7 +6029,7 @@
     <t xml:space="preserve">3.63046145439148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58705472946167</t>
+    <t xml:space="preserve">3.58705496788025</t>
   </si>
   <si>
     <t xml:space="preserve">3.58289885520935</t>
@@ -6047,16 +6047,16 @@
     <t xml:space="preserve">3.63600277900696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72512531280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75744938850403</t>
+    <t xml:space="preserve">3.7251250743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75744915008545</t>
   </si>
   <si>
     <t xml:space="preserve">3.78654074668884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66832661628723</t>
+    <t xml:space="preserve">3.66832685470581</t>
   </si>
   <si>
     <t xml:space="preserve">3.5602719783783</t>
@@ -6065,10 +6065,10 @@
     <t xml:space="preserve">3.54226279258728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60090780258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51270914077759</t>
+    <t xml:space="preserve">3.60090804100037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51270937919617</t>
   </si>
   <si>
     <t xml:space="preserve">3.53071856498718</t>
@@ -6774,6 +6774,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.54699993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57399988174438</t>
   </si>
 </sst>
 </file>
@@ -72164,7 +72167,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6938541667</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>48908564</v>
@@ -72185,6 +72188,32 @@
         <v>2253</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6938657407</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>44674834</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>5.57499980926514</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>5.46500015258789</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>5.57399988174438</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>2254</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISP.MI.xlsx
+++ b/data/ISP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="2255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="2256">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,64 +44,64 @@
     <t xml:space="preserve">ISP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56040990352631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51831984519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49265503883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48752236366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46699059009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49676144123077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52447950839996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48546922206879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4382461309433</t>
+    <t xml:space="preserve">1.5604100227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51831996440887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4926552772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48752248287201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46699070930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49676156044006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52447926998138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4854691028595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43824625015259</t>
   </si>
   <si>
     <t xml:space="preserve">1.36638522148132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38075733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30479001998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36843848228455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3930766582489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35406625270844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37254452705383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35919916629791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29041802883148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380006790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31505620479584</t>
+    <t xml:space="preserve">1.38075757026672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30478990077972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36843836307526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39307630062103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35406613349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37254476547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35919940471649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2904177904129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31505596637726</t>
   </si>
   <si>
     <t xml:space="preserve">1.26988613605499</t>
@@ -110,25 +110,25 @@
     <t xml:space="preserve">1.20315825939178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27296602725983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22368967533112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17441368103027</t>
+    <t xml:space="preserve">1.27296578884125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22369003295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17441380023956</t>
   </si>
   <si>
     <t xml:space="preserve">1.10152614116669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26064717769623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22984933853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25243425369263</t>
+    <t xml:space="preserve">1.26064705848694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22984910011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25243449211121</t>
   </si>
   <si>
     <t xml:space="preserve">1.28220510482788</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">1.19494557380676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23395574092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20110499858856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16004168987274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18057310581207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20007824897766</t>
+    <t xml:space="preserve">1.23395562171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20110476016998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16004145145416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18057334423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20007848739624</t>
   </si>
   <si>
     <t xml:space="preserve">1.20213174819946</t>
@@ -161,31 +161,31 @@
     <t xml:space="preserve">1.22471654415131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2709127664566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32224214076996</t>
+    <t xml:space="preserve">1.27091264724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32224202156067</t>
   </si>
   <si>
     <t xml:space="preserve">1.29555094242096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26475310325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27604579925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144442081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30581676959991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40334260463715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37459802627563</t>
+    <t xml:space="preserve">1.26475346088409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27604556083679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2914445400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30581653118134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40334236621857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37459778785706</t>
   </si>
   <si>
     <t xml:space="preserve">1.36022567749023</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">1.33045470714569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29349756240845</t>
+    <t xml:space="preserve">1.29349768161774</t>
   </si>
   <si>
     <t xml:space="preserve">1.27912569046021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29247117042542</t>
+    <t xml:space="preserve">1.29247105121613</t>
   </si>
   <si>
     <t xml:space="preserve">1.25756728649139</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">1.23600876331329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24935448169708</t>
+    <t xml:space="preserve">1.24935436248779</t>
   </si>
   <si>
     <t xml:space="preserve">1.24114179611206</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">1.21753036975861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18673276901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13540327548981</t>
+    <t xml:space="preserve">1.18673288822174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1354033946991</t>
   </si>
   <si>
     <t xml:space="preserve">1.1487489938736</t>
@@ -230,19 +230,19 @@
     <t xml:space="preserve">1.1107656955719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17749333381653</t>
+    <t xml:space="preserve">1.17749357223511</t>
   </si>
   <si>
     <t xml:space="preserve">1.19802522659302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24422168731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25038135051727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25654065608978</t>
+    <t xml:space="preserve">1.24422144889832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25038123130798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25654053688049</t>
   </si>
   <si>
     <t xml:space="preserve">1.26270020008087</t>
@@ -251,79 +251,79 @@
     <t xml:space="preserve">1.24216842651367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27809870243073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23190259933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26680636405945</t>
+    <t xml:space="preserve">1.27809882164001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23190248012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26680624485016</t>
   </si>
   <si>
     <t xml:space="preserve">1.26783299446106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18878591060638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16209471225739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13950979709625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1425895690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1497757434845</t>
+    <t xml:space="preserve">1.18878614902496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1620945930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13950991630554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14258980751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14977586269379</t>
   </si>
   <si>
     <t xml:space="preserve">1.15798842906952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14566946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1415628194809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12924420833588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12103140354156</t>
+    <t xml:space="preserve">1.14566934108734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14156293869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1292439699173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12103128433228</t>
   </si>
   <si>
     <t xml:space="preserve">1.15080225467682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17852020263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18775928020477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18666672706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25878429412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28719437122345</t>
+    <t xml:space="preserve">1.17852008342743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18775939941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18666660785675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25878441333771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28719460964203</t>
   </si>
   <si>
     <t xml:space="preserve">1.29702877998352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26096975803375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24020886421204</t>
+    <t xml:space="preserve">1.26097011566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24020862579346</t>
   </si>
   <si>
     <t xml:space="preserve">1.23037445545197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20852029323578</t>
+    <t xml:space="preserve">1.20852053165436</t>
   </si>
   <si>
     <t xml:space="preserve">1.20414972305298</t>
@@ -335,55 +335,55 @@
     <t xml:space="preserve">1.2107058763504</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19977903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15060782432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08286046981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0451625585556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07466554641724</t>
+    <t xml:space="preserve">1.1997789144516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15060770511627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08286082744598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04516267776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07466530799866</t>
   </si>
   <si>
     <t xml:space="preserve">1.06537747383118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11454880237579</t>
+    <t xml:space="preserve">1.1145486831665</t>
   </si>
   <si>
     <t xml:space="preserve">1.14842236042023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17683255672455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17573964595795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23365247249603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950644552707672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846838474273682</t>
+    <t xml:space="preserve">1.17683243751526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17573988437653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23365259170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950644612312317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846838593482971</t>
   </si>
   <si>
     <t xml:space="preserve">0.887268304824829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900380492210388</t>
+    <t xml:space="preserve">0.900380611419678</t>
   </si>
   <si>
     <t xml:space="preserve">0.929883420467377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917863667011261</t>
+    <t xml:space="preserve">0.917863786220551</t>
   </si>
   <si>
     <t xml:space="preserve">0.88999992609024</t>
@@ -392,82 +392,82 @@
     <t xml:space="preserve">0.870331525802612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868692576885223</t>
+    <t xml:space="preserve">0.868692278862</t>
   </si>
   <si>
     <t xml:space="preserve">0.874155879020691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961571574211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983425259590149</t>
+    <t xml:space="preserve">0.96157169342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983425378799438</t>
   </si>
   <si>
     <t xml:space="preserve">1.04789435863495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03587484359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05772876739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05499684810638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05718231201172</t>
+    <t xml:space="preserve">1.03587448596954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05772864818573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05499672889709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05718243122101</t>
   </si>
   <si>
     <t xml:space="preserve">1.05062615871429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06373834609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06701648235321</t>
+    <t xml:space="preserve">1.06373858451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0670166015625</t>
   </si>
   <si>
     <t xml:space="preserve">1.06865549087524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04898715019226</t>
+    <t xml:space="preserve">1.04898703098297</t>
   </si>
   <si>
     <t xml:space="preserve">1.05335783958435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0719336271286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0396990776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07630455493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03860652446747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999269425868988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993805944919586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994352340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03806006908417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0511726140976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05608952045441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07958269119263</t>
+    <t xml:space="preserve">1.07193386554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03969931602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07630467414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03860640525818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999269545078278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993806064128876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994352459907532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03806018829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05117249488831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05608975887299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07958257198334</t>
   </si>
   <si>
     <t xml:space="preserve">1.05827498435974</t>
@@ -476,31 +476,31 @@
     <t xml:space="preserve">1.03041136264801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00965011119843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05991411209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09214854240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08231437206268</t>
+    <t xml:space="preserve">1.00965023040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05991399288177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09214842319489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0823141336441</t>
   </si>
   <si>
     <t xml:space="preserve">1.10034370422363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08996319770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11673414707184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16372013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19759321212769</t>
+    <t xml:space="preserve">1.08996295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11673402786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16372036933899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19759345054626</t>
   </si>
   <si>
     <t xml:space="preserve">1.19213020801544</t>
@@ -512,19 +512,19 @@
     <t xml:space="preserve">1.17901790142059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18338871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15934908390045</t>
+    <t xml:space="preserve">1.18338847160339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15934932231903</t>
   </si>
   <si>
     <t xml:space="preserve">1.13749539852142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13640260696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12766110897064</t>
+    <t xml:space="preserve">1.1364027261734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12766087055206</t>
   </si>
   <si>
     <t xml:space="preserve">1.09706568717957</t>
@@ -533,16 +533,16 @@
     <t xml:space="preserve">1.11236345767975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12656831741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09050953388214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07794344425201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06428468227386</t>
+    <t xml:space="preserve">1.12656843662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09050965309143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0779435634613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06428480148315</t>
   </si>
   <si>
     <t xml:space="preserve">1.06155300140381</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">1.06319212913513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07848966121674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05445063114166</t>
+    <t xml:space="preserve">1.07848989963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05445051193237</t>
   </si>
   <si>
     <t xml:space="preserve">1.08941674232483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0937876701355</t>
+    <t xml:space="preserve">1.09378755092621</t>
   </si>
   <si>
     <t xml:space="preserve">1.07685089111328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08340680599213</t>
+    <t xml:space="preserve">1.08340716362</t>
   </si>
   <si>
     <t xml:space="preserve">1.12329041957855</t>
@@ -581,22 +581,22 @@
     <t xml:space="preserve">1.15388584136963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17792499065399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196449756622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18229603767395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15279293060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13858830928802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0992511510849</t>
+    <t xml:space="preserve">1.1779248714447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196461677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18229591846466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15279304981232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13858819007874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09925138950348</t>
   </si>
   <si>
     <t xml:space="preserve">1.09597301483154</t>
@@ -608,31 +608,31 @@
     <t xml:space="preserve">1.16918349266052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22054028511047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21835470199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15497863292694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14186596870422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11891949176788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1036217212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06810939311981</t>
+    <t xml:space="preserve">1.22054040431976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21835482120514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15497851371765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1418662071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11891973018646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10362184047699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06810927391052</t>
   </si>
   <si>
     <t xml:space="preserve">1.11345613002777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14514422416687</t>
+    <t xml:space="preserve">1.14514434337616</t>
   </si>
   <si>
     <t xml:space="preserve">1.24567210674286</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">1.26643347740173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30904841423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27845311164856</t>
+    <t xml:space="preserve">1.30904829502106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27845299243927</t>
   </si>
   <si>
     <t xml:space="preserve">1.32762432098389</t>
@@ -656,52 +656,52 @@
     <t xml:space="preserve">1.33636581897736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31888282299042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33745872974396</t>
+    <t xml:space="preserve">1.31888258457184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33745861053467</t>
   </si>
   <si>
     <t xml:space="preserve">1.33855140209198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3440146446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964395523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3287171125412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31779003143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32543897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36805379390717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38772225379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39755666255951</t>
+    <t xml:space="preserve">1.34401476383209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964359760284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871687412262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3177901506424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32543885707855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36805403232574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38772261142731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39755690097809</t>
   </si>
   <si>
     <t xml:space="preserve">1.38990795612335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35275614261627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34838533401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34619998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34729278087616</t>
+    <t xml:space="preserve">1.35275661945343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3483852148056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34620010852814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34729313850403</t>
   </si>
   <si>
     <t xml:space="preserve">1.32216084003448</t>
@@ -716,46 +716,46 @@
     <t xml:space="preserve">1.31014132499695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25222826004028</t>
+    <t xml:space="preserve">1.25222837924957</t>
   </si>
   <si>
     <t xml:space="preserve">1.25659906864166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22928190231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23911583423615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20087170600891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18557417392731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19103753566742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22272562980652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19322276115417</t>
+    <t xml:space="preserve">1.22928178310394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23911571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20087158679962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18557405471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19103741645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22272551059723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19322288036346</t>
   </si>
   <si>
     <t xml:space="preserve">1.17027604579926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1735543012619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16590535640717</t>
+    <t xml:space="preserve">1.17355406284332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16590547561646</t>
   </si>
   <si>
     <t xml:space="preserve">1.17136883735657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19650101661682</t>
+    <t xml:space="preserve">1.19650089740753</t>
   </si>
   <si>
     <t xml:space="preserve">1.18120312690735</t>
@@ -764,22 +764,22 @@
     <t xml:space="preserve">1.13421726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25113558769226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27626764774323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26861870288849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189695835114</t>
+    <t xml:space="preserve">1.25113546848297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27626752853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26861882209778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189683914185</t>
   </si>
   <si>
     <t xml:space="preserve">1.27408230304718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30577039718628</t>
+    <t xml:space="preserve">1.30577051639557</t>
   </si>
   <si>
     <t xml:space="preserve">1.34182941913605</t>
@@ -788,25 +788,25 @@
     <t xml:space="preserve">1.32325351238251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35057091712952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35603439807892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36914682388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39100050926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38662993907928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38335192203522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37679553031921</t>
+    <t xml:space="preserve">1.35057079792023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35603451728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36914658546448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39100062847137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38662981987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38335180282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37679588794708</t>
   </si>
   <si>
     <t xml:space="preserve">1.38007378578186</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">1.37898099422455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37461006641388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3669615983963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384893417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33199524879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30467760562897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35166358947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36040508747101</t>
+    <t xml:space="preserve">1.37461018562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36696124076843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384881496429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33199501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30467772483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35166335105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36040496826172</t>
   </si>
   <si>
     <t xml:space="preserve">1.37351751327515</t>
@@ -842,25 +842,25 @@
     <t xml:space="preserve">1.47623085975647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50573360919952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49480676651001</t>
+    <t xml:space="preserve">1.50573372840881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49480652809143</t>
   </si>
   <si>
     <t xml:space="preserve">1.45984041690826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.460932970047</t>
+    <t xml:space="preserve">1.46093320846558</t>
   </si>
   <si>
     <t xml:space="preserve">1.46311843395233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47076725959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50791871547699</t>
+    <t xml:space="preserve">1.47076714038849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50791907310486</t>
   </si>
   <si>
     <t xml:space="preserve">1.55271947383881</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">1.55818283557892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55599749088287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5570901632309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54725611209869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54507064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55162668228149</t>
+    <t xml:space="preserve">1.55599772930145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55709028244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5472559928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54507052898407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55162680149078</t>
   </si>
   <si>
     <t xml:space="preserve">1.52868008613586</t>
@@ -890,43 +890,43 @@
     <t xml:space="preserve">1.52212405204773</t>
   </si>
   <si>
+    <t xml:space="preserve">1.52977287769318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56594610214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57061338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56711268424988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55427718162537</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.52977275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56594598293304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57061326503754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56711268424988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55427742004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52977287769318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49826741218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48893213272095</t>
+    <t xml:space="preserve">1.49826729297638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48893225193024</t>
   </si>
   <si>
     <t xml:space="preserve">1.4865984916687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50060081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51110291481018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49126589298248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48426473140717</t>
+    <t xml:space="preserve">1.50060105323792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51110279560089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49126601219177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48426449298859</t>
   </si>
   <si>
     <t xml:space="preserve">1.49943423271179</t>
@@ -938,397 +938,397 @@
     <t xml:space="preserve">1.50176787376404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50410151481628</t>
+    <t xml:space="preserve">1.50410163402557</t>
   </si>
   <si>
     <t xml:space="preserve">1.49710035324097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47843050956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51460349559784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52510547637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52627205848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57994830608368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60795342922211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6406261920929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61845552921295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6196221113205</t>
+    <t xml:space="preserve">1.47843027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51460361480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5251053571701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52627241611481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57994866371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6079535484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64062607288361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61845529079437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61962223052979</t>
   </si>
   <si>
     <t xml:space="preserve">1.66279673576355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65929591655731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67213177680969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65696203708649</t>
+    <t xml:space="preserve">1.65929627418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67213129997253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65696215629578</t>
   </si>
   <si>
     <t xml:space="preserve">1.66863083839417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65346169471741</t>
+    <t xml:space="preserve">1.6534618139267</t>
   </si>
   <si>
     <t xml:space="preserve">1.66162979602814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66396355628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6709645986557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67446541786194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66629731655121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67329847812653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68380033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69313538074493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69546914100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69430220127106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69896972179413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70130324363708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6919686794281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7036372423172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70830452442169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70480418205261</t>
+    <t xml:space="preserve">1.66396343708038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67096483707428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67446553707123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6662974357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67329835891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6838002204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69313549995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69546926021576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69430208206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69896984100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70130348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69196844100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70363712310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70830476284027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70480394363403</t>
   </si>
   <si>
     <t xml:space="preserve">1.68263339996338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67796587944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66046273708344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70713806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68963444232941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64295995235443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65462875366211</t>
+    <t xml:space="preserve">1.6779659986496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66046285629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70713818073273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6896345615387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64295983314514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65462851524353</t>
   </si>
   <si>
     <t xml:space="preserve">1.65812909603119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63712525367737</t>
+    <t xml:space="preserve">1.63712537288666</t>
   </si>
   <si>
     <t xml:space="preserve">1.6651303768158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68146657943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70013654232025</t>
+    <t xml:space="preserve">1.68146669864655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70013642311096</t>
   </si>
   <si>
     <t xml:space="preserve">1.71063840389252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7176399230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73280894756317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73397576808929</t>
+    <t xml:space="preserve">1.71763956546783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73280930519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73397600650787</t>
   </si>
   <si>
     <t xml:space="preserve">1.72464096546173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.735142827034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447762966156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7421441078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74564480781555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74681162834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74097716808319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71180546283722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71530592441559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70947194099426</t>
+    <t xml:space="preserve">1.73514258861542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447786808014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74214398860931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74564468860626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74681127071381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74097728729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71180522441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71530604362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70947170257568</t>
   </si>
   <si>
     <t xml:space="preserve">1.68496739864349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66746413707733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68029975891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597100257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67913293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65112793445587</t>
+    <t xml:space="preserve">1.66746401786804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68029987812042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597124099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6791330575943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65112769603729</t>
   </si>
   <si>
     <t xml:space="preserve">1.63362467288971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63479149341583</t>
+    <t xml:space="preserve">1.63479173183441</t>
   </si>
   <si>
     <t xml:space="preserve">1.61728858947754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61495447158813</t>
+    <t xml:space="preserve">1.61495471000671</t>
   </si>
   <si>
     <t xml:space="preserve">1.64412689208984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6137877702713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64529359340668</t>
+    <t xml:space="preserve">1.61378788948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64529347419739</t>
   </si>
   <si>
     <t xml:space="preserve">1.64646029472351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67563211917877</t>
+    <t xml:space="preserve">1.67563223838806</t>
   </si>
   <si>
     <t xml:space="preserve">1.63829231262207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62895727157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62662327289581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62779033184052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61612129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60678684711456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60445284843445</t>
+    <t xml:space="preserve">1.62895739078522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62662351131439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62779021263123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61612164974213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60678660869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60445272922516</t>
   </si>
   <si>
     <t xml:space="preserve">1.74331080913544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76548182964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77248311042786</t>
+    <t xml:space="preserve">1.76548159122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77248299121857</t>
   </si>
   <si>
     <t xml:space="preserve">1.77598321437836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78415191173553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80515515804291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80165469646454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8238251209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82499194145203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79815411567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82149136066437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84366238117218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824823379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83549380302429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84395444393158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111846446991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81769919395447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902946949005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81098997592926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87283432483673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83636927604675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81157350540161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377806186676</t>
+    <t xml:space="preserve">1.78415167331696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80515551567078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80165493488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82382535934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82499206066132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79815375804901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82149195671082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84366261959076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8582478761673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.835493683815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84395432472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111822605133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81769907474518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902923107147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81098961830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87283408641815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83636951446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81157314777374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377841949463</t>
   </si>
   <si>
     <t xml:space="preserve">1.80923938751221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80690574645996</t>
+    <t xml:space="preserve">1.80690550804138</t>
   </si>
   <si>
     <t xml:space="preserve">1.83053469657898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8130316734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223834514618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80748927593231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78444361686707</t>
+    <t xml:space="preserve">1.81303179264069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8022381067276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80748891830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78444314002991</t>
   </si>
   <si>
     <t xml:space="preserve">1.79873752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79990446567535</t>
+    <t xml:space="preserve">1.79990434646606</t>
   </si>
   <si>
     <t xml:space="preserve">1.80982303619385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80632221698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79290294647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75410461425781</t>
+    <t xml:space="preserve">1.8063223361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79290342330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75410437583923</t>
   </si>
   <si>
     <t xml:space="preserve">1.72930860519409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74535298347473</t>
+    <t xml:space="preserve">1.74535310268402</t>
   </si>
   <si>
     <t xml:space="preserve">1.76518988609314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77510809898376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7803590297699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540004253387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7488534450531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7608140707016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79523694515228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77365005016327</t>
+    <t xml:space="preserve">1.77510821819305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78035926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77539992332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74885368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76081395149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79523682594299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77364981174469</t>
   </si>
   <si>
     <t xml:space="preserve">1.78473496437073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77423298358917</t>
+    <t xml:space="preserve">1.77423310279846</t>
   </si>
   <si>
     <t xml:space="preserve">1.74272763729095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72259902954102</t>
+    <t xml:space="preserve">1.72259914875031</t>
   </si>
   <si>
     <t xml:space="preserve">1.70742952823639</t>
@@ -1337,55 +1337,55 @@
     <t xml:space="preserve">1.72289097309113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72318243980408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72522449493408</t>
+    <t xml:space="preserve">1.72318255901337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72522437572479</t>
   </si>
   <si>
     <t xml:space="preserve">1.71909821033478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7520626783371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74768686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76256430149078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77131593227386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7590639591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77948403358459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78940260410309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79465353488922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81449031829834</t>
+    <t xml:space="preserve">1.75206243991852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74768698215485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76256418228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77131605148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75906372070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77948439121246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7894024848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79465365409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81449043750763</t>
   </si>
   <si>
     <t xml:space="preserve">1.81536567211151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82907629013062</t>
+    <t xml:space="preserve">1.8290764093399</t>
   </si>
   <si>
     <t xml:space="preserve">1.84832978248596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86437404155731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83987009525299</t>
+    <t xml:space="preserve">1.86437427997589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986985683441</t>
   </si>
   <si>
     <t xml:space="preserve">1.85124683380127</t>
@@ -1394,34 +1394,34 @@
     <t xml:space="preserve">1.83957827091217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84191179275513</t>
+    <t xml:space="preserve">1.84191226959229</t>
   </si>
   <si>
     <t xml:space="preserve">1.8486213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83811986446381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84453737735748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83403527736664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82674276828766</t>
+    <t xml:space="preserve">1.83811950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84453749656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83403539657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8267422914505</t>
   </si>
   <si>
     <t xml:space="preserve">1.83782780170441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85416436195374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80865585803986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79436182975769</t>
+    <t xml:space="preserve">1.85416400432587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80865597724915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79436206817627</t>
   </si>
   <si>
     <t xml:space="preserve">1.75031232833862</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">1.73967385292053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75156366825104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7209005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70494329929352</t>
+    <t xml:space="preserve">1.75156378746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72090017795563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70494318008423</t>
   </si>
   <si>
     <t xml:space="preserve">1.65081286430359</t>
@@ -1445,82 +1445,82 @@
     <t xml:space="preserve">1.59730851650238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53191447257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57759630680084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57352876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62546861171722</t>
+    <t xml:space="preserve">1.53191435337067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57759618759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57352864742279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6254688501358</t>
   </si>
   <si>
     <t xml:space="preserve">1.62515580654144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56289041042328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55475533008575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53629457950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51752114295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61827230453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6173335313797</t>
+    <t xml:space="preserve">1.56289052963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55475556850433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5362948179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51752126216888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61827218532562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61733365058899</t>
   </si>
   <si>
     <t xml:space="preserve">1.62578153610229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6232784986496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59417963027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59793412685394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60575652122498</t>
+    <t xml:space="preserve">1.62327861785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59417939186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59793424606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6057562828064</t>
   </si>
   <si>
     <t xml:space="preserve">1.63548123836517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60325372219086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61952364444733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56695795059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55068755149841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690804004669</t>
+    <t xml:space="preserve">1.60325336456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61952388286591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56695806980133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55068778991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690815925598</t>
   </si>
   <si>
     <t xml:space="preserve">1.55694556236267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55600690841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54474270343781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57634484767914</t>
+    <t xml:space="preserve">1.55600678920746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54474282264709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57634472846985</t>
   </si>
   <si>
     <t xml:space="preserve">1.58416700363159</t>
@@ -1529,28 +1529,28 @@
     <t xml:space="preserve">1.60513091087341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6029406785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60606944561005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58041250705719</t>
+    <t xml:space="preserve">1.60294079780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60606956481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58041226863861</t>
   </si>
   <si>
     <t xml:space="preserve">1.54881036281586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53066277503967</t>
+    <t xml:space="preserve">1.53066289424896</t>
   </si>
   <si>
     <t xml:space="preserve">1.53973639011383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53660750389099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5519392490387</t>
+    <t xml:space="preserve">1.53660762310028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55193948745728</t>
   </si>
   <si>
     <t xml:space="preserve">1.54161381721497</t>
@@ -1568,31 +1568,31 @@
     <t xml:space="preserve">1.53097546100616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55037498474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57039988040924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58322846889496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64830982685089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57258987426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51188933849335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53003680706024</t>
+    <t xml:space="preserve">1.5503751039505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57039964199066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58322834968567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6483097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57259011268616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51188945770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53003692626953</t>
   </si>
   <si>
     <t xml:space="preserve">1.50844752788544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249005317688</t>
+    <t xml:space="preserve">1.4924898147583</t>
   </si>
   <si>
     <t xml:space="preserve">1.43804705142975</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">1.4017516374588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37640762329102</t>
+    <t xml:space="preserve">1.37640750408173</t>
   </si>
   <si>
     <t xml:space="preserve">1.36576902866364</t>
@@ -1613,61 +1613,61 @@
     <t xml:space="preserve">1.35732102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40331614017487</t>
+    <t xml:space="preserve">1.40331602096558</t>
   </si>
   <si>
     <t xml:space="preserve">1.38329100608826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37672030925751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.378910779953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37859773635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36357879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38172650337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34918582439423</t>
+    <t xml:space="preserve">1.3767204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37891066074371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37859761714935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36357891559601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3817263841629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34918570518494</t>
   </si>
   <si>
     <t xml:space="preserve">1.33135116100311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35857260227203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45901048183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43929839134216</t>
+    <t xml:space="preserve">1.35857284069061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897295951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45901072025299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43929851055145</t>
   </si>
   <si>
     <t xml:space="preserve">1.41583180427551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47997438907623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45650780200958</t>
+    <t xml:space="preserve">1.47997450828552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45650768280029</t>
   </si>
   <si>
     <t xml:space="preserve">1.46432983875275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45744621753693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46683299541473</t>
+    <t xml:space="preserve">1.45744633674622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46683287620544</t>
   </si>
   <si>
     <t xml:space="preserve">1.50093805789948</t>
@@ -1679,40 +1679,40 @@
     <t xml:space="preserve">1.51908576488495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51157629489899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53222703933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49999952316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54568147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52221477031708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50437986850739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37734627723694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32352900505066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31914842128754</t>
+    <t xml:space="preserve">1.51157653331757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53222715854645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49999940395355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54568135738373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5222145318985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50438010692596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37734591960907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32352888584137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31914854049683</t>
   </si>
   <si>
     <t xml:space="preserve">1.32634484767914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35481786727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31320333480835</t>
+    <t xml:space="preserve">1.35481798648834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31320357322693</t>
   </si>
   <si>
     <t xml:space="preserve">1.27033746242523</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">1.29818475246429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30506837368011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27284049987793</t>
+    <t xml:space="preserve">1.30506825447083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27284038066864</t>
   </si>
   <si>
     <t xml:space="preserve">1.26783430576324</t>
@@ -1745,46 +1745,46 @@
     <t xml:space="preserve">1.24167656898499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23128843307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23166418075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18936109542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22227728366852</t>
+    <t xml:space="preserve">1.23128855228424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23166406154633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18936121463776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22227740287781</t>
   </si>
   <si>
     <t xml:space="preserve">1.21264040470123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.249436378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24655759334564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2221519947052</t>
+    <t xml:space="preserve">1.24943625926971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24655795097351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22215223312378</t>
   </si>
   <si>
     <t xml:space="preserve">1.24267792701721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25563156604767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2366703748703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25250267982483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28598213195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26971173286438</t>
+    <t xml:space="preserve">1.25563132762909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23667025566101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25250256061554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28598201274872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26971161365509</t>
   </si>
   <si>
     <t xml:space="preserve">1.25500571727753</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">1.22665774822235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25312852859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2382972240448</t>
+    <t xml:space="preserve">1.25312840938568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23829758167267</t>
   </si>
   <si>
     <t xml:space="preserve">1.2226527929306</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">1.20538127422333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17571926116943</t>
+    <t xml:space="preserve">1.17571914196014</t>
   </si>
   <si>
     <t xml:space="preserve">1.20901095867157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20888566970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22165143489838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27690804004669</t>
+    <t xml:space="preserve">1.20888578891754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22165179252625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27690815925598</t>
   </si>
   <si>
     <t xml:space="preserve">1.27628242969513</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">1.28535628318787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27190184593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28160154819489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32196438312531</t>
+    <t xml:space="preserve">1.2719019651413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2816014289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32196450233459</t>
   </si>
   <si>
     <t xml:space="preserve">1.29161393642426</t>
@@ -1844,55 +1844,55 @@
     <t xml:space="preserve">1.30193936824799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23491823673248</t>
+    <t xml:space="preserve">1.23491811752319</t>
   </si>
   <si>
     <t xml:space="preserve">1.24029982089996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2137668132782</t>
+    <t xml:space="preserve">1.21376669406891</t>
   </si>
   <si>
     <t xml:space="preserve">1.21026241779327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25969898700714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27158880233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26032483577728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23466789722443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24217736721039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26345384120941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2171459197998</t>
+    <t xml:space="preserve">1.25969910621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27158904075623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26032495498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23466777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2421772480011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2634539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21714603900909</t>
   </si>
   <si>
     <t xml:space="preserve">1.19662022590637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1946177482605</t>
+    <t xml:space="preserve">1.19461786746979</t>
   </si>
   <si>
     <t xml:space="preserve">1.21389198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.192990899086</t>
+    <t xml:space="preserve">1.19299077987671</t>
   </si>
   <si>
     <t xml:space="preserve">1.18986177444458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25106346607208</t>
+    <t xml:space="preserve">1.25106334686279</t>
   </si>
   <si>
     <t xml:space="preserve">1.27221477031708</t>
@@ -1901,40 +1901,40 @@
     <t xml:space="preserve">1.25750887393951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26470518112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25844752788544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24017465114594</t>
+    <t xml:space="preserve">1.26470530033112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25844764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24017477035522</t>
   </si>
   <si>
     <t xml:space="preserve">1.22465538978577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26001214981079</t>
+    <t xml:space="preserve">1.26001191139221</t>
   </si>
   <si>
     <t xml:space="preserve">1.27565658092499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27596950531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26814711093903</t>
+    <t xml:space="preserve">1.27596938610077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26814723014832</t>
   </si>
   <si>
     <t xml:space="preserve">1.26908600330353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29192698001862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28003704547882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28191459178925</t>
+    <t xml:space="preserve">1.29192686080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28003692626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28191435337067</t>
   </si>
   <si>
     <t xml:space="preserve">1.28973662853241</t>
@@ -1946,49 +1946,49 @@
     <t xml:space="preserve">1.22815978527069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22753393650055</t>
+    <t xml:space="preserve">1.22753405570984</t>
   </si>
   <si>
     <t xml:space="preserve">1.24705839157104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24180161952972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2361695766449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25131368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25531876087189</t>
+    <t xml:space="preserve">1.2418018579483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23616969585419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25131380558014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2553186416626</t>
   </si>
   <si>
     <t xml:space="preserve">1.24155139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28097546100616</t>
+    <t xml:space="preserve">1.28097569942474</t>
   </si>
   <si>
     <t xml:space="preserve">1.29223990440369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28629469871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28692054748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2765953540802</t>
+    <t xml:space="preserve">1.28629493713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28692042827606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27659523487091</t>
   </si>
   <si>
     <t xml:space="preserve">1.2778468132019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30444264411926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.299436211586</t>
+    <t xml:space="preserve">1.30444252490997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29943609237671</t>
   </si>
   <si>
     <t xml:space="preserve">1.33385443687439</t>
@@ -1997,55 +1997,55 @@
     <t xml:space="preserve">1.35043752193451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35513079166412</t>
+    <t xml:space="preserve">1.35513067245483</t>
   </si>
   <si>
     <t xml:space="preserve">1.35262775421143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36545634269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3351057767868</t>
+    <t xml:space="preserve">1.36545646190643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33510601520538</t>
   </si>
   <si>
     <t xml:space="preserve">1.32603204250336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33760905265808</t>
+    <t xml:space="preserve">1.33760917186737</t>
   </si>
   <si>
     <t xml:space="preserve">1.33667027950287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34824740886688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35794711112976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37609446048737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39737129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39924848079681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39549362659454</t>
+    <t xml:space="preserve">1.3482471704483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35794723033905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37609457969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39737105369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39924836158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39549386501312</t>
   </si>
   <si>
     <t xml:space="preserve">1.38610696792603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34949910640717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480535984039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136378765106</t>
+    <t xml:space="preserve">1.34949898719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480547904968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136366844177</t>
   </si>
   <si>
     <t xml:space="preserve">1.35168921947479</t>
@@ -2057,43 +2057,43 @@
     <t xml:space="preserve">1.38016200065613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37546896934509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38767147064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39799690246582</t>
+    <t xml:space="preserve">1.37546873092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3876713514328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3979971408844</t>
   </si>
   <si>
     <t xml:space="preserve">1.39956140518188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39017474651337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39830994606018</t>
+    <t xml:space="preserve">1.39017462730408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39830982685089</t>
   </si>
   <si>
     <t xml:space="preserve">1.43992459774017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45337867736816</t>
+    <t xml:space="preserve">1.45337879657745</t>
   </si>
   <si>
     <t xml:space="preserve">1.46558141708374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45963656902313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45244014263153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42365419864655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42490541934967</t>
+    <t xml:space="preserve">1.45963644981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45243990421295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42365396022797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42490553855896</t>
   </si>
   <si>
     <t xml:space="preserve">1.42991173267365</t>
@@ -2102,43 +2102,43 @@
     <t xml:space="preserve">1.45932352542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46245241165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45619487762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45306575298309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43272793292999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40300321578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38673281669617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35450506210327</t>
+    <t xml:space="preserve">1.46245229244232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45619475841522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45306599140167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43272805213928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40300333499908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38673305511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35450494289398</t>
   </si>
   <si>
     <t xml:space="preserve">1.35137605667114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3254063129425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34543144702911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36639475822449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35825967788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36135697364807</t>
+    <t xml:space="preserve">1.32540619373322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34543132781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36639499664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35825979709625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36135685443878</t>
   </si>
   <si>
     <t xml:space="preserve">1.36066854000092</t>
@@ -2147,22 +2147,22 @@
     <t xml:space="preserve">1.33630454540253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30973815917969</t>
+    <t xml:space="preserve">1.30973827838898</t>
   </si>
   <si>
     <t xml:space="preserve">1.32061266899109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31331717967987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29872632026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28413546085358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28372251987457</t>
+    <t xml:space="preserve">1.31331694126129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29872608184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28413534164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28372240066528</t>
   </si>
   <si>
     <t xml:space="preserve">1.26211130619049</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">1.25674295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28441059589386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27326107025146</t>
+    <t xml:space="preserve">1.28441071510315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27326095104218</t>
   </si>
   <si>
     <t xml:space="preserve">1.25701832771301</t>
@@ -2183,16 +2183,16 @@
     <t xml:space="preserve">1.26142311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27037024497986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2713338136673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25811958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26775503158569</t>
+    <t xml:space="preserve">1.27037036418915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27133393287659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2581193447113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26775515079498</t>
   </si>
   <si>
     <t xml:space="preserve">1.26458895206451</t>
@@ -2201,19 +2201,19 @@
     <t xml:space="preserve">1.2601842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28936612606049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.312628865242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30134165287018</t>
+    <t xml:space="preserve">1.2893660068512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31262874603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30134153366089</t>
   </si>
   <si>
     <t xml:space="preserve">1.29046714305878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29032969474792</t>
+    <t xml:space="preserve">1.29032945632935</t>
   </si>
   <si>
     <t xml:space="preserve">1.28592491149902</t>
@@ -2225,34 +2225,34 @@
     <t xml:space="preserve">1.29294490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29528510570526</t>
+    <t xml:space="preserve">1.29528486728668</t>
   </si>
   <si>
     <t xml:space="preserve">1.2853741645813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29734969139099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36328399181366</t>
+    <t xml:space="preserve">1.29734992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36328411102295</t>
   </si>
   <si>
     <t xml:space="preserve">1.39439284801483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39852249622345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38854277133942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38097202777863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39783406257629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41469597816467</t>
+    <t xml:space="preserve">1.39852237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38854265213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38097178936005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39783418178558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41469633579254</t>
   </si>
   <si>
     <t xml:space="preserve">1.41159915924072</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">1.40987849235535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41916978359222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40609312057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41091084480286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38200438022614</t>
+    <t xml:space="preserve">1.41916990280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40609300136566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41091072559357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38200449943542</t>
   </si>
   <si>
     <t xml:space="preserve">1.3844131231308</t>
@@ -2288,163 +2288,163 @@
     <t xml:space="preserve">1.37044167518616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35309791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34924376010895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37649834156036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34387528896332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35433661937714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33836925029755</t>
+    <t xml:space="preserve">1.35309767723083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34924352169037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37649846076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34387540817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35433673858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33836936950684</t>
   </si>
   <si>
     <t xml:space="preserve">1.31455588340759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33891999721527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26362562179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29886376857758</t>
+    <t xml:space="preserve">1.33892011642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26362550258636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29886400699615</t>
   </si>
   <si>
     <t xml:space="preserve">1.27023279666901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31744647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31001353263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32322812080383</t>
+    <t xml:space="preserve">1.31744658946991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31001341342926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32322800159454</t>
   </si>
   <si>
     <t xml:space="preserve">1.33644223213196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30987596511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33520328998566</t>
+    <t xml:space="preserve">1.30987572669983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33520340919495</t>
   </si>
   <si>
     <t xml:space="preserve">1.34084713459015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35488736629486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38578987121582</t>
+    <t xml:space="preserve">1.35488748550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38578963279724</t>
   </si>
   <si>
     <t xml:space="preserve">1.37181830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37890708446503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37684237957001</t>
+    <t xml:space="preserve">1.37890720367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3768424987793</t>
   </si>
   <si>
     <t xml:space="preserve">1.39542508125305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41504037380219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4226108789444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44635581970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46149730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45082926750183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46080875396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50175964832306</t>
+    <t xml:space="preserve">1.4150402545929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42261099815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44635570049286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46149718761444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45082938671112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46080887317657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50175988674164</t>
   </si>
   <si>
     <t xml:space="preserve">1.47526216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46252965927124</t>
+    <t xml:space="preserve">1.46252942085266</t>
   </si>
   <si>
     <t xml:space="preserve">1.46321773529053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48937153816223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49074769020081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47319746017456</t>
+    <t xml:space="preserve">1.48937141895294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4907478094101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47319734096527</t>
   </si>
   <si>
     <t xml:space="preserve">1.46597099304199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46941196918488</t>
+    <t xml:space="preserve">1.46941208839417</t>
   </si>
   <si>
     <t xml:space="preserve">1.47491788864136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4869624376297</t>
+    <t xml:space="preserve">1.48696219921112</t>
   </si>
   <si>
     <t xml:space="preserve">1.49728608131409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48317682743073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44119381904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43912899494171</t>
+    <t xml:space="preserve">1.48317718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4411940574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43912923336029</t>
   </si>
   <si>
     <t xml:space="preserve">1.44222617149353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43568789958954</t>
+    <t xml:space="preserve">1.43568766117096</t>
   </si>
   <si>
     <t xml:space="preserve">1.4477322101593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47939157485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50451266765594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5003833770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52103066444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54064571857452</t>
+    <t xml:space="preserve">1.47939169406891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50451278686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50038313865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52103078365326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5406459569931</t>
   </si>
   <si>
     <t xml:space="preserve">1.5358282327652</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">1.55062544345856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56576716899872</t>
+    <t xml:space="preserve">1.56576693058014</t>
   </si>
   <si>
     <t xml:space="preserve">1.56232571601868</t>
@@ -2465,37 +2465,37 @@
     <t xml:space="preserve">1.56301391124725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56404626369476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5681756734848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56370234489441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54752838611603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54580771923065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56439030170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58710277080536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61050319671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60878252983093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62151491641998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256790161133</t>
+    <t xml:space="preserve">1.56404638290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56817591190338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56370222568512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54752850532532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54580783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56439054012299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58710265159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61050307750702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60878264904022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62151503562927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256778240204</t>
   </si>
   <si>
     <t xml:space="preserve">1.62220358848572</t>
@@ -2507,55 +2507,55 @@
     <t xml:space="preserve">1.61394441127777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60086762905121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60912644863129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61738550662994</t>
+    <t xml:space="preserve">1.6008677482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60912656784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61738526821136</t>
   </si>
   <si>
     <t xml:space="preserve">1.61566495895386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62013864517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61291170120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61910605430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61187994480133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6019002199173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58985579013824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58331704139709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54511916637421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5767787694931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57471418380737</t>
+    <t xml:space="preserve">1.62013840675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61291193962097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61910617351532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61187958717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60190010070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58985567092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58331727981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54511904716492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57677865028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57471430301666</t>
   </si>
   <si>
     <t xml:space="preserve">1.59226441383362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58090817928314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58572614192963</t>
+    <t xml:space="preserve">1.58090829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58572626113892</t>
   </si>
   <si>
     <t xml:space="preserve">1.59054398536682</t>
@@ -2564,34 +2564,34 @@
     <t xml:space="preserve">1.60224413871765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61497664451599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62633264064789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62839770317078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63803339004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6552392244339</t>
+    <t xml:space="preserve">1.61497640609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62633287906647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62839758396149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63803327083588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65523946285248</t>
   </si>
   <si>
     <t xml:space="preserve">1.65214228630066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6208268404007</t>
+    <t xml:space="preserve">1.62082672119141</t>
   </si>
   <si>
     <t xml:space="preserve">1.61635327339172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63872146606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61704123020172</t>
+    <t xml:space="preserve">1.63872134685516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61704134941101</t>
   </si>
   <si>
     <t xml:space="preserve">1.63390374183655</t>
@@ -2600,40 +2600,40 @@
     <t xml:space="preserve">1.61119139194489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61532056331635</t>
+    <t xml:space="preserve">1.61532068252563</t>
   </si>
   <si>
     <t xml:space="preserve">1.59673810005188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59845876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60809433460236</t>
+    <t xml:space="preserve">1.59845888614655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60809445381165</t>
   </si>
   <si>
     <t xml:space="preserve">1.59570586681366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5692081451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56094908714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56783187389374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55200219154358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58675861358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57712292671204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54546368122101</t>
+    <t xml:space="preserve">1.56920802593231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56094896793365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56783175468445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.552001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58675837516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5771232843399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54546356201172</t>
   </si>
   <si>
     <t xml:space="preserve">1.57264935970306</t>
@@ -2645,55 +2645,55 @@
     <t xml:space="preserve">1.68586659431458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70100796222687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70410525798798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69240498542786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70857846736908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72578489780426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72750532627106</t>
+    <t xml:space="preserve">1.70100784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70410513877869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69240474700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70857894420624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72578501701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72750544548035</t>
   </si>
   <si>
     <t xml:space="preserve">1.7481529712677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78944754600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79185676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75503540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73542046546936</t>
+    <t xml:space="preserve">1.78944778442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7918564081192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75503528118134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73542058467865</t>
   </si>
   <si>
     <t xml:space="preserve">1.63562417030334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60362064838409</t>
+    <t xml:space="preserve">1.6036205291748</t>
   </si>
   <si>
     <t xml:space="preserve">1.57505834102631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51311576366425</t>
+    <t xml:space="preserve">1.51311588287354</t>
   </si>
   <si>
     <t xml:space="preserve">1.4704442024231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45839989185333</t>
+    <t xml:space="preserve">1.45840013027191</t>
   </si>
   <si>
     <t xml:space="preserve">1.46425020694733</t>
@@ -2702,67 +2702,67 @@
     <t xml:space="preserve">1.4085019826889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36080622673035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20443618297577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1760801076889</t>
+    <t xml:space="preserve">1.36080646514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20443594455719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17608022689819</t>
   </si>
   <si>
     <t xml:space="preserve">1.2245329618454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00677096843719</t>
+    <t xml:space="preserve">1.00677108764648</t>
   </si>
   <si>
     <t xml:space="preserve">1.06981444358826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965475976467133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998924970626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96946793794632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980892777442932</t>
+    <t xml:space="preserve">0.965476095676422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998924851417542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969467639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980892598628998</t>
   </si>
   <si>
     <t xml:space="preserve">1.00856041908264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997135519981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08991134166718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11234819889069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1225346326828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07821106910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01227688789368</t>
+    <t xml:space="preserve">0.997135400772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08991146087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11234831809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12253439426422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07821130752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01227700710297</t>
   </si>
   <si>
     <t xml:space="preserve">1.0243901014328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987500011920929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989564895629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914820909500122</t>
+    <t xml:space="preserve">0.987500131130219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989564657211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914820849895477</t>
   </si>
   <si>
     <t xml:space="preserve">1.00360488891602</t>
@@ -2771,40 +2771,40 @@
     <t xml:space="preserve">1.01103806495667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997410774230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99452006816864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967815935611725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928035318851471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936156690120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947168529033661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951848447322845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908488929271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921015083789825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952812373638153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924869120121002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960245192050934</t>
+    <t xml:space="preserve">0.997410655021667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99452018737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967816114425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928035140037537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936156630516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947168409824371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951848685741425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908488988876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921014964580536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952812254428864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924869239330292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960245370864868</t>
   </si>
   <si>
     <t xml:space="preserve">0.996034145355225</t>
@@ -2819,22 +2819,22 @@
     <t xml:space="preserve">0.947030961513519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998649537563324</t>
+    <t xml:space="preserve">0.99864935874939</t>
   </si>
   <si>
     <t xml:space="preserve">0.97745144367218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966577351093292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973184406757355</t>
+    <t xml:space="preserve">0.966577172279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973184287548065</t>
   </si>
   <si>
     <t xml:space="preserve">0.970018327236176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977864444255829</t>
+    <t xml:space="preserve">0.977864325046539</t>
   </si>
   <si>
     <t xml:space="preserve">0.959144115447998</t>
@@ -2843,64 +2843,64 @@
     <t xml:space="preserve">0.952261447906494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95239931344986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999475717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984746754169464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990390598773956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978690326213837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994244694709778</t>
+    <t xml:space="preserve">0.952399492263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999475538730621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984746932983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990390717983246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978690266609192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994244933128357</t>
   </si>
   <si>
     <t xml:space="preserve">1.0031920671463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03319954872131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05880272388458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07270514965057</t>
+    <t xml:space="preserve">1.0331996679306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05880260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07270503044128</t>
   </si>
   <si>
     <t xml:space="preserve">1.0684380531311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08743393421173</t>
+    <t xml:space="preserve">1.08743381500244</t>
   </si>
   <si>
     <t xml:space="preserve">1.11840486526489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15157854557037</t>
+    <t xml:space="preserve">1.15157866477966</t>
   </si>
   <si>
     <t xml:space="preserve">1.16575646400452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2201281785965</t>
+    <t xml:space="preserve">1.22012805938721</t>
   </si>
   <si>
     <t xml:space="preserve">1.24118864536285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18378841876984</t>
+    <t xml:space="preserve">1.18378853797913</t>
   </si>
   <si>
     <t xml:space="preserve">1.17181313037872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11344969272614</t>
+    <t xml:space="preserve">1.11344957351685</t>
   </si>
   <si>
     <t xml:space="preserve">1.11634027957916</t>
@@ -2909,82 +2909,82 @@
     <t xml:space="preserve">1.11950612068176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16947305202484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17263889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16025066375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15956246852875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15791034698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17786955833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14717352390289</t>
+    <t xml:space="preserve">1.16947293281555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17263913154602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16025054454803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15956234931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15791046619415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17786967754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14717364311218</t>
   </si>
   <si>
     <t xml:space="preserve">1.14249360561371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17140018939972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1725013256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16355407238007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20636320114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20223379135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23348021507263</t>
+    <t xml:space="preserve">1.17140030860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17250144481659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16355419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20636332035065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20223367214203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23348033428192</t>
   </si>
   <si>
     <t xml:space="preserve">1.22962594032288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21338331699371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19149696826935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21503531932831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22604715824127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22577166557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24875915050507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26596570014954</t>
+    <t xml:space="preserve">1.213383436203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19149708747864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21503520011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22604703903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2257719039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24875926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26596581935883</t>
   </si>
   <si>
     <t xml:space="preserve">1.26073491573334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27628934383392</t>
+    <t xml:space="preserve">1.27628922462463</t>
   </si>
   <si>
     <t xml:space="preserve">1.29721212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29129314422607</t>
+    <t xml:space="preserve">1.29129302501678</t>
   </si>
   <si>
     <t xml:space="preserve">1.27271032333374</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">1.24944758415222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23981201648712</t>
+    <t xml:space="preserve">1.2398122549057</t>
   </si>
   <si>
     <t xml:space="preserve">1.22935080528259</t>
@@ -3002,76 +3002,76 @@
     <t xml:space="preserve">1.23155307769775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19411242008209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17497885227203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1756671667099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23444378376007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26252448558807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24834632873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2425651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24848413467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28096950054169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29583549499512</t>
+    <t xml:space="preserve">1.1941123008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17497897148132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17566728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23444354534149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26252424716949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24834620952606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24256527423859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24848401546478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2809693813324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29583561420441</t>
   </si>
   <si>
     <t xml:space="preserve">1.28399765491486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27436244487762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25564169883728</t>
+    <t xml:space="preserve">1.27436232566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25564181804657</t>
   </si>
   <si>
     <t xml:space="preserve">1.24903464317322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26981961727142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24999833106995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24683237075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26582789421082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26224887371063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26816773414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24146389961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25605475902557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24242746829987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24008750915527</t>
+    <t xml:space="preserve">1.26981985569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24999809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24683213233948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2658280134201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26224899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2681679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24146401882172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25605463981628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24242734909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24008727073669</t>
   </si>
   <si>
     <t xml:space="preserve">1.22425770759583</t>
@@ -3080,28 +3080,28 @@
     <t xml:space="preserve">1.22412002086639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23458135128021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21269524097443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23210370540619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23967456817627</t>
+    <t xml:space="preserve">1.2345814704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21269512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23210382461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23967444896698</t>
   </si>
   <si>
     <t xml:space="preserve">1.22439539432526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21737504005432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21145617961884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19989371299744</t>
+    <t xml:space="preserve">1.2173752784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21145629882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19989347457886</t>
   </si>
   <si>
     <t xml:space="preserve">1.18020975589752</t>
@@ -3113,40 +3113,40 @@
     <t xml:space="preserve">1.12996768951416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10959529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10670483112335</t>
+    <t xml:space="preserve">1.10959553718567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10670459270477</t>
   </si>
   <si>
     <t xml:space="preserve">1.08674550056458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11812973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10587882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1032634973526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09183859825134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09596788883209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1240485906601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14827477931976</t>
+    <t xml:space="preserve">1.11812961101532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10587871074677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10326337814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09183871746063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09596800804138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12404870986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14827501773834</t>
   </si>
   <si>
     <t xml:space="preserve">1.13478529453278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15309262275696</t>
+    <t xml:space="preserve">1.15309274196625</t>
   </si>
   <si>
     <t xml:space="preserve">1.15557038784027</t>
@@ -3155,94 +3155,94 @@
     <t xml:space="preserve">1.14978921413422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11317431926727</t>
+    <t xml:space="preserve">1.11317443847656</t>
   </si>
   <si>
     <t xml:space="preserve">1.05825197696686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07077789306641</t>
+    <t xml:space="preserve">1.0707780122757</t>
   </si>
   <si>
     <t xml:space="preserve">1.07353103160858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05701303482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05770146846771</t>
+    <t xml:space="preserve">1.05701315402985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05770134925842</t>
   </si>
   <si>
     <t xml:space="preserve">1.07449460029602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05095648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02590417861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975937247276306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962998032569885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977038681507111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02026057243347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0603164434433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09968447685242</t>
+    <t xml:space="preserve">1.05095636844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02590429782867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975937366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962998270988464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977038383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02026033401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06031656265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09968459606171</t>
   </si>
   <si>
     <t xml:space="preserve">1.12680160999298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11276125907898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2153103351593</t>
+    <t xml:space="preserve">1.11276137828827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21531045436859</t>
   </si>
   <si>
     <t xml:space="preserve">1.26926910877228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25591707229614</t>
+    <t xml:space="preserve">1.25591695308685</t>
   </si>
   <si>
     <t xml:space="preserve">1.24022507667542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25109946727753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26637852191925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27615165710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28730130195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28248357772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31868541240692</t>
+    <t xml:space="preserve">1.25109934806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26637864112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27615177631378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28730118274689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28248345851898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3186856508255</t>
   </si>
   <si>
     <t xml:space="preserve">1.33671760559082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32777035236359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32515490055084</t>
+    <t xml:space="preserve">1.32777047157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32515513896942</t>
   </si>
   <si>
     <t xml:space="preserve">1.35653901100159</t>
@@ -3257,16 +3257,16 @@
     <t xml:space="preserve">1.35667681694031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35516273975372</t>
+    <t xml:space="preserve">1.35516262054443</t>
   </si>
   <si>
     <t xml:space="preserve">1.35998046398163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34951889514923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231270313263</t>
+    <t xml:space="preserve">1.34951913356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231258392334</t>
   </si>
   <si>
     <t xml:space="preserve">1.33465278148651</t>
@@ -3278,22 +3278,22 @@
     <t xml:space="preserve">1.33726811408997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3382316827774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33189988136292</t>
+    <t xml:space="preserve">1.33823180198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33189976215363</t>
   </si>
   <si>
     <t xml:space="preserve">1.29473423957825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3166207075119</t>
+    <t xml:space="preserve">1.31662082672119</t>
   </si>
   <si>
     <t xml:space="preserve">1.32309031486511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32130086421967</t>
+    <t xml:space="preserve">1.32130074501038</t>
   </si>
   <si>
     <t xml:space="preserve">1.31634533405304</t>
@@ -3302,43 +3302,43 @@
     <t xml:space="preserve">1.31125235557556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29693675041199</t>
+    <t xml:space="preserve">1.29693686962128</t>
   </si>
   <si>
     <t xml:space="preserve">1.35447454452515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34552729129791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3371307849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33396458625793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31799733638763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30904996395111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31951129436493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31483137607574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32584321498871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29679918289185</t>
+    <t xml:space="preserve">1.34552717208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33713066577911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33396470546722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31799721717834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30904972553253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31951117515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31483125686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32584309577942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29679894447327</t>
   </si>
   <si>
     <t xml:space="preserve">1.25481581687927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26610314846039</t>
+    <t xml:space="preserve">1.2661030292511</t>
   </si>
   <si>
     <t xml:space="preserve">1.24407923221588</t>
@@ -3347,19 +3347,19 @@
     <t xml:space="preserve">1.26197361946106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25398993492126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771436214447</t>
+    <t xml:space="preserve">1.25399005413055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771424293518</t>
   </si>
   <si>
     <t xml:space="preserve">1.34291172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38234865665436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41848182678223</t>
+    <t xml:space="preserve">1.38234853744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41848158836365</t>
   </si>
   <si>
     <t xml:space="preserve">1.43844091892242</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">1.43637609481812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43155825138092</t>
+    <t xml:space="preserve">1.43155837059021</t>
   </si>
   <si>
     <t xml:space="preserve">1.43603193759918</t>
@@ -3380,13 +3380,13 @@
     <t xml:space="preserve">1.45736765861511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45392656326294</t>
+    <t xml:space="preserve">1.45392644405365</t>
   </si>
   <si>
     <t xml:space="preserve">1.45117354393005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44532334804535</t>
+    <t xml:space="preserve">1.44532310962677</t>
   </si>
   <si>
     <t xml:space="preserve">1.45358240604401</t>
@@ -3401,85 +3401,85 @@
     <t xml:space="preserve">1.48661839962006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48283302783966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51621305942535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50864207744598</t>
+    <t xml:space="preserve">1.48283278942108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51621294021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50864195823669</t>
   </si>
   <si>
     <t xml:space="preserve">1.51036274433136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56198143959045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56507849693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55991685390472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56955230236053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55888438224792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57884359359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59329688549042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61669754981995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59260857105255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58194088935852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57540249824524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57987606525421</t>
+    <t xml:space="preserve">1.56198155879974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56507837772369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55991697311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56955218315125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55888450145721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5788437128067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59329676628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61669743061066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59260833263397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58194100856781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57540261745453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5798761844635</t>
   </si>
   <si>
     <t xml:space="preserve">1.57918775081635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58125257492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57333755493164</t>
+    <t xml:space="preserve">1.58125245571136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57333767414093</t>
   </si>
   <si>
     <t xml:space="preserve">1.59914696216583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5901997089386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59536182880402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58503794670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55750799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5509694814682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5557873249054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56989645957947</t>
+    <t xml:space="preserve">1.59019947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59536159038544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58503770828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55750787258148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55096971988678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55578744411469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56989634037018</t>
   </si>
   <si>
     <t xml:space="preserve">1.52791321277618</t>
@@ -3488,157 +3488,157 @@
     <t xml:space="preserve">1.53204262256622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52860128879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58056437969208</t>
+    <t xml:space="preserve">1.52860140800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58056426048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.59501755237579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59742641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60637378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58847916126251</t>
+    <t xml:space="preserve">1.59742629528046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60637366771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5884792804718</t>
   </si>
   <si>
     <t xml:space="preserve">1.62357985973358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62564444541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.644571185112</t>
+    <t xml:space="preserve">1.62564468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64457130432129</t>
   </si>
   <si>
     <t xml:space="preserve">1.63837707042694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63975381851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63287115097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64319491386414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65868079662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65351843833923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65116310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64976513385773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63928389549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67282438278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68330562114716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68854641914368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70881009101868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72767674922943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73012244701385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73326659202576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73676061630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71894252300262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71440029144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7042680978775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69448578357697</t>
+    <t xml:space="preserve">1.63975369930267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63287127017975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64319479465485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65868055820465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65351867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.651162981987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64976537227631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63928377628326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67282450199127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68330574035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68854629993439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70881056785583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72767698764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73012268543243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73326671123505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73676073551178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71894204616547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71440017223358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70426833629608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69448590278625</t>
   </si>
   <si>
     <t xml:space="preserve">1.71195483207703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71265363693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68749809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63788664340973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65360856056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63648879528046</t>
+    <t xml:space="preserve">1.71265351772308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68749833106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63788628578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65360867977142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63648891448975</t>
   </si>
   <si>
     <t xml:space="preserve">1.61832141876221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65186154842377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66688477993011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62775456905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64662075042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64592218399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63229644298553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6553555727005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6214656829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60958659648895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56242072582245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5959609746933</t>
+    <t xml:space="preserve">1.65186178684235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6668848991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62775433063507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64662086963654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64592206478119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63229632377625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65535545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62146532535553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60958683490753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56242060661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59596085548401</t>
   </si>
   <si>
     <t xml:space="preserve">1.61098432540894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58617842197418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59631025791168</t>
+    <t xml:space="preserve">1.58617830276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59631037712097</t>
   </si>
   <si>
     <t xml:space="preserve">1.57639586925507</t>
@@ -3647,31 +3647,31 @@
     <t xml:space="preserve">1.55962574481964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49359333515167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52259135246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56277012825012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255256175995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59665966033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63334453105927</t>
+    <t xml:space="preserve">1.49359321594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52259147167206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56277000904083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255280017853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59665989875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63334465026855</t>
   </si>
   <si>
     <t xml:space="preserve">1.61657428741455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62111639976501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63998246192932</t>
+    <t xml:space="preserve">1.62111628055573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63998258113861</t>
   </si>
   <si>
     <t xml:space="preserve">1.62915205955505</t>
@@ -3680,19 +3680,19 @@
     <t xml:space="preserve">1.61727333068848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62565803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63509142398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6385852098465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67596852779388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68016111850739</t>
+    <t xml:space="preserve">1.6256582736969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63509154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63858509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67596864700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68016147613525</t>
   </si>
   <si>
     <t xml:space="preserve">1.6826069355011</t>
@@ -3701,124 +3701,124 @@
     <t xml:space="preserve">1.71125590801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71055710315704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69204008579254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66898107528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68225753307343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66723430156708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66304171085358</t>
+    <t xml:space="preserve">1.71055722236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69203996658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66898119449615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68225789070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66723418235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66304183006287</t>
   </si>
   <si>
     <t xml:space="preserve">1.67002928256989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66164433956146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67526984214783</t>
+    <t xml:space="preserve">1.66164410114288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6752701997757</t>
   </si>
   <si>
     <t xml:space="preserve">1.68365514278412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66828238964081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67911326885223</t>
+    <t xml:space="preserve">1.66828227043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67911314964294</t>
   </si>
   <si>
     <t xml:space="preserve">1.66548752784729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64836800098419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65710246562958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63963317871094</t>
+    <t xml:space="preserve">1.6483678817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65710234642029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63963329792023</t>
   </si>
   <si>
     <t xml:space="preserve">1.66758346557617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66094541549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65884935855865</t>
+    <t xml:space="preserve">1.66094553470612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65884923934937</t>
   </si>
   <si>
     <t xml:space="preserve">1.60853862762451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62251377105713</t>
+    <t xml:space="preserve">1.62251389026642</t>
   </si>
   <si>
     <t xml:space="preserve">1.65815043449402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69623279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69413650035858</t>
+    <t xml:space="preserve">1.69623267650604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69413638114929</t>
   </si>
   <si>
     <t xml:space="preserve">1.72732722759247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69763028621674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71824359893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74898898601532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72942352294922</t>
+    <t xml:space="preserve">1.69763040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7182434797287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74898910522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72942364215851</t>
   </si>
   <si>
     <t xml:space="preserve">1.75388014316559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75912070274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7493382692337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75562715530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74339878559113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76331317424774</t>
+    <t xml:space="preserve">1.75912094116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74933815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75562739372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74339854717255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76331353187561</t>
   </si>
   <si>
     <t xml:space="preserve">1.79929935932159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81100189685822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78156363964081</t>
+    <t xml:space="preserve">1.81100177764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7815637588501</t>
   </si>
   <si>
     <t xml:space="preserve">1.7931934595108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7772022485733</t>
+    <t xml:space="preserve">1.77720236778259</t>
   </si>
   <si>
     <t xml:space="preserve">1.78192698955536</t>
@@ -3827,52 +3827,52 @@
     <t xml:space="preserve">1.79028606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80373311042786</t>
+    <t xml:space="preserve">1.80373322963715</t>
   </si>
   <si>
     <t xml:space="preserve">1.78301739692688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77211451530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78628849983215</t>
+    <t xml:space="preserve">1.77211427688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78628826141357</t>
   </si>
   <si>
     <t xml:space="preserve">1.81354582309723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82590281963348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8186342716217</t>
+    <t xml:space="preserve">1.82590305805206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81863403320312</t>
   </si>
   <si>
     <t xml:space="preserve">1.78556132316589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80518710613251</t>
+    <t xml:space="preserve">1.80518698692322</t>
   </si>
   <si>
     <t xml:space="preserve">1.81172895431519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79573786258698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80046224594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79682791233063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79646456241608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80991148948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80446028709412</t>
+    <t xml:space="preserve">1.79573774337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80046212673187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79682767391205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646444320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80991160869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80446040630341</t>
   </si>
   <si>
     <t xml:space="preserve">1.80409669876099</t>
@@ -3884,160 +3884,160 @@
     <t xml:space="preserve">1.74418139457703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72544264793396</t>
+    <t xml:space="preserve">1.72544276714325</t>
   </si>
   <si>
     <t xml:space="preserve">1.7258175611496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71494936943054</t>
+    <t xml:space="preserve">1.71494925022125</t>
   </si>
   <si>
     <t xml:space="preserve">1.61638474464417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60626554489136</t>
+    <t xml:space="preserve">1.60626578330994</t>
   </si>
   <si>
     <t xml:space="preserve">1.585653424263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62537884712219</t>
+    <t xml:space="preserve">1.62537896633148</t>
   </si>
   <si>
     <t xml:space="preserve">1.60963869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60888922214508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65873372554779</t>
+    <t xml:space="preserve">1.60888910293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65873348712921</t>
   </si>
   <si>
     <t xml:space="preserve">1.69246292114258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67222547531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66772794723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66060757637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65273714065552</t>
+    <t xml:space="preserve">1.6722252368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6677280664444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66060769557953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6527373790741</t>
   </si>
   <si>
     <t xml:space="preserve">1.66735315322876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65011394023895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68084526062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311217308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63549780845642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67334961891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67185032367706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68721580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69583594799042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7115763425827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70670437812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70445561408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75767314434052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7944004535675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8123893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82363259792328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83749890327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84611892700195</t>
+    <t xml:space="preserve">1.65011382102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68084514141083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311205387115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63549792766571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67334985733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67185044288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68721604347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69583606719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71157622337341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70670402050018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70445537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75767302513123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79440069198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81238949298859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82363271713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83749902248383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84611880779266</t>
   </si>
   <si>
     <t xml:space="preserve">1.86036014556885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90795588493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91919887065887</t>
+    <t xml:space="preserve">1.90795564651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91919898986816</t>
   </si>
   <si>
     <t xml:space="preserve">1.92032337188721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93194127082825</t>
+    <t xml:space="preserve">1.93194150924683</t>
   </si>
   <si>
     <t xml:space="preserve">1.9300674200058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89933621883392</t>
+    <t xml:space="preserve">1.89933586120605</t>
   </si>
   <si>
     <t xml:space="preserve">1.91245305538177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91282796859741</t>
+    <t xml:space="preserve">1.91282784938812</t>
   </si>
   <si>
     <t xml:space="preserve">1.8487423658371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86560690402985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92219722270966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95817518234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94655728340149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96342170238495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00127387046814</t>
+    <t xml:space="preserve">1.86560714244843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92219710350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95817506313324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9465571641922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96342194080353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00127363204956</t>
   </si>
   <si>
     <t xml:space="preserve">2.02151131629944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04474711418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99902510643005</t>
+    <t xml:space="preserve">2.04474687576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99902522563934</t>
   </si>
   <si>
     <t xml:space="preserve">2.03500318527222</t>
@@ -4046,19 +4046,19 @@
     <t xml:space="preserve">2.07585310935974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13881468772888</t>
+    <t xml:space="preserve">2.1388144493103</t>
   </si>
   <si>
     <t xml:space="preserve">2.18865895271301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07435393333435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13843989372253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09196805953979</t>
+    <t xml:space="preserve">2.07435417175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13843965530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09196829795837</t>
   </si>
   <si>
     <t xml:space="preserve">2.05299210548401</t>
@@ -4070,19 +4070,19 @@
     <t xml:space="preserve">2.00427174568176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99377846717834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9641717672348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80789196491241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85698699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71907150745392</t>
+    <t xml:space="preserve">1.99377834796906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96417152881622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80789220333099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85698747634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71907162666321</t>
   </si>
   <si>
     <t xml:space="preserve">1.58640289306641</t>
@@ -4091,43 +4091,43 @@
     <t xml:space="preserve">1.60851430892944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56204307079315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42127919197083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38155341148376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39834320545197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55342304706573</t>
+    <t xml:space="preserve">1.56204295158386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42127907276154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38155353069305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39834308624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55342316627502</t>
   </si>
   <si>
     <t xml:space="preserve">1.4352205991745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43866848945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49158620834351</t>
+    <t xml:space="preserve">1.43866837024689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49158608913422</t>
   </si>
   <si>
     <t xml:space="preserve">1.50507771968842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61001360416412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55304849147797</t>
+    <t xml:space="preserve">1.61001348495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55304837226868</t>
   </si>
   <si>
     <t xml:space="preserve">1.56354188919067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54892587661743</t>
+    <t xml:space="preserve">1.54892611503601</t>
   </si>
   <si>
     <t xml:space="preserve">1.57403552532196</t>
@@ -4136,73 +4136,73 @@
     <t xml:space="preserve">1.53505945205688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5223171710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5238162279129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53243613243103</t>
+    <t xml:space="preserve">1.52231729030609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52381634712219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53243625164032</t>
   </si>
   <si>
     <t xml:space="preserve">1.61975753307343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59951996803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56166803836823</t>
+    <t xml:space="preserve">1.59951984882355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56166815757751</t>
   </si>
   <si>
     <t xml:space="preserve">1.57778322696686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57028782367706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53056228160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48573958873749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46280372142792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48558974266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48469054698944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45500838756561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45725727081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47734487056732</t>
+    <t xml:space="preserve">1.57028794288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53056204319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48573970794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46280360221863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48558986186981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48469030857086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4550085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4572571516037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47734463214874</t>
   </si>
   <si>
     <t xml:space="preserve">1.47884392738342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51444697380066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51782011985779</t>
+    <t xml:space="preserve">1.51444709300995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5178200006485</t>
   </si>
   <si>
     <t xml:space="preserve">1.48618936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46055519580841</t>
+    <t xml:space="preserve">1.46055507659912</t>
   </si>
   <si>
     <t xml:space="preserve">1.43761909008026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43971788883209</t>
+    <t xml:space="preserve">1.43971765041351</t>
   </si>
   <si>
     <t xml:space="preserve">1.44361555576324</t>
@@ -4211,16 +4211,16 @@
     <t xml:space="preserve">1.46520221233368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44091701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46924984455109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44301581382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44256603717804</t>
+    <t xml:space="preserve">1.44091713428497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46924960613251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44301569461823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44256615638733</t>
   </si>
   <si>
     <t xml:space="preserve">1.40913653373718</t>
@@ -4229,103 +4229,103 @@
     <t xml:space="preserve">1.3716596364975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39534509181976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45410907268524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4707487821579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47839391231537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46490240097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49188578128815</t>
+    <t xml:space="preserve">1.39534497261047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45410895347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47074902057648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47839403152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46490252017975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49188566207886</t>
   </si>
   <si>
     <t xml:space="preserve">1.49008691310883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48633921146393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54183995723724</t>
+    <t xml:space="preserve">1.48633933067322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54184007644653</t>
   </si>
   <si>
     <t xml:space="preserve">1.54496228694916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.586958527565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60139966011047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59788680076599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6076443195343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58500695228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56119871139526</t>
+    <t xml:space="preserve">1.58695840835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60139954090118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59788691997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60764420032501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58500683307648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56119883060455</t>
   </si>
   <si>
     <t xml:space="preserve">1.54012262821198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59047114849091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5631502866745</t>
+    <t xml:space="preserve">1.59047102928162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315040588379</t>
   </si>
   <si>
     <t xml:space="preserve">1.55339276790619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5352828502655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42193984985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3730742931366</t>
+    <t xml:space="preserve">1.53528273105621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42193973064423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37307417392731</t>
   </si>
   <si>
     <t xml:space="preserve">1.38166081905365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44520163536072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39961457252502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40788900852203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46175038814545</t>
+    <t xml:space="preserve">1.44520151615143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39961469173431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40788888931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46175050735474</t>
   </si>
   <si>
     <t xml:space="preserve">1.47221040725708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46799516677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43630278110504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4692440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47798669338226</t>
+    <t xml:space="preserve">1.46799528598785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43630290031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46924412250519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47798681259155</t>
   </si>
   <si>
     <t xml:space="preserve">1.48204600811005</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">1.46440446376801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38946688175201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37978744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34669017791748</t>
+    <t xml:space="preserve">1.38946676254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37978756427765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34669005870819</t>
   </si>
   <si>
     <t xml:space="preserve">1.30469369888306</t>
@@ -4352,10 +4352,10 @@
     <t xml:space="preserve">1.36230206489563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37588429450989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35199797153473</t>
+    <t xml:space="preserve">1.37588441371918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35199809074402</t>
   </si>
   <si>
     <t xml:space="preserve">1.33295142650604</t>
@@ -4367,31 +4367,31 @@
     <t xml:space="preserve">1.25411093235016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27393794059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30672323703766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38369023799896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33513700962067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2981368303299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29579496383667</t>
+    <t xml:space="preserve">1.27393817901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30672335624695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38369047641754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33513712882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29813694953918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29579508304596</t>
   </si>
   <si>
     <t xml:space="preserve">1.31765162944794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29329717159271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30922114849091</t>
+    <t xml:space="preserve">1.29329705238342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30922102928162</t>
   </si>
   <si>
     <t xml:space="preserve">1.3315464258194</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">1.36542439460754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36370694637299</t>
+    <t xml:space="preserve">1.36370706558228</t>
   </si>
   <si>
     <t xml:space="preserve">1.38462710380554</t>
@@ -4412,13 +4412,13 @@
     <t xml:space="preserve">1.39180862903595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41600716114044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4185049533844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41756856441498</t>
+    <t xml:space="preserve">1.41600728034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41850507259369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41756844520569</t>
   </si>
   <si>
     <t xml:space="preserve">1.43052637577057</t>
@@ -4439,16 +4439,16 @@
     <t xml:space="preserve">1.38415884971619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34138190746307</t>
+    <t xml:space="preserve">1.34138202667236</t>
   </si>
   <si>
     <t xml:space="preserve">1.36573672294617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37666511535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35699379444122</t>
+    <t xml:space="preserve">1.37666499614716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35699391365051</t>
   </si>
   <si>
     <t xml:space="preserve">1.315309882164</t>
@@ -4463,28 +4463,28 @@
     <t xml:space="preserve">1.34497272968292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32217907905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3568377494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32467699050903</t>
+    <t xml:space="preserve">1.32217919826508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35683763027191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32467710971832</t>
   </si>
   <si>
     <t xml:space="preserve">1.32998526096344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32701897621155</t>
+    <t xml:space="preserve">1.32701885700226</t>
   </si>
   <si>
     <t xml:space="preserve">1.35855519771576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43099498748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48001635074615</t>
+    <t xml:space="preserve">1.43099462985992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48001623153687</t>
   </si>
   <si>
     <t xml:space="preserve">1.46846354007721</t>
@@ -4493,13 +4493,13 @@
     <t xml:space="preserve">1.48329496383667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49875056743622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49484765529633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49515998363495</t>
+    <t xml:space="preserve">1.4987508058548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49484777450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49516010284424</t>
   </si>
   <si>
     <t xml:space="preserve">1.44348430633545</t>
@@ -4508,34 +4508,34 @@
     <t xml:space="preserve">1.43364870548248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44567000865936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37697744369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38041174411774</t>
+    <t xml:space="preserve">1.44567012786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37697732448578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38041186332703</t>
   </si>
   <si>
     <t xml:space="preserve">1.34825122356415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32592618465424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2918918132782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32920455932617</t>
+    <t xml:space="preserve">1.32592606544495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29189205169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32920467853546</t>
   </si>
   <si>
     <t xml:space="preserve">1.35355925559998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39571166038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35917937755585</t>
+    <t xml:space="preserve">1.39571154117584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35917949676514</t>
   </si>
   <si>
     <t xml:space="preserve">1.33654224872589</t>
@@ -4547,7 +4547,7 @@
     <t xml:space="preserve">1.3234281539917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30781626701355</t>
+    <t xml:space="preserve">1.30781602859497</t>
   </si>
   <si>
     <t xml:space="preserve">1.33201479911804</t>
@@ -4559,13 +4559,13 @@
     <t xml:space="preserve">1.36058461666107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40726459026337</t>
+    <t xml:space="preserve">1.40726470947266</t>
   </si>
   <si>
     <t xml:space="preserve">1.39852178096771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4277161359787</t>
+    <t xml:space="preserve">1.42771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">1.42662334442139</t>
@@ -4580,19 +4580,19 @@
     <t xml:space="preserve">1.45644235610962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48766624927521</t>
+    <t xml:space="preserve">1.48766613006592</t>
   </si>
   <si>
     <t xml:space="preserve">1.48719787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50577628612518</t>
+    <t xml:space="preserve">1.50577616691589</t>
   </si>
   <si>
     <t xml:space="preserve">1.51842188835144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5181097984314</t>
+    <t xml:space="preserve">1.51810956001282</t>
   </si>
   <si>
     <t xml:space="preserve">1.53746843338013</t>
@@ -4604,10 +4604,10 @@
     <t xml:space="preserve">1.66189610958099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67672753334045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6814112663269</t>
+    <t xml:space="preserve">1.67672741413116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68141114711761</t>
   </si>
   <si>
     <t xml:space="preserve">1.69936490058899</t>
@@ -4619,7 +4619,7 @@
     <t xml:space="preserve">1.70678055286407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70951271057129</t>
+    <t xml:space="preserve">1.70951247215271</t>
   </si>
   <si>
     <t xml:space="preserve">1.70990312099457</t>
@@ -4631,19 +4631,19 @@
     <t xml:space="preserve">1.7301983833313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72882580757141</t>
+    <t xml:space="preserve">1.7288259267807</t>
   </si>
   <si>
     <t xml:space="preserve">1.74457168579102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73165202140808</t>
+    <t xml:space="preserve">1.73165190219879</t>
   </si>
   <si>
     <t xml:space="preserve">1.7441680431366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74295675754547</t>
+    <t xml:space="preserve">1.74295663833618</t>
   </si>
   <si>
     <t xml:space="preserve">1.70863854885101</t>
@@ -4652,13 +4652,13 @@
     <t xml:space="preserve">1.72357714176178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71348345279694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68320286273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69289267063141</t>
+    <t xml:space="preserve">1.71348357200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68320298194885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6928927898407</t>
   </si>
   <si>
     <t xml:space="preserve">1.67835795879364</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">1.66866815090179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66463077068329</t>
+    <t xml:space="preserve">1.664630651474</t>
   </si>
   <si>
     <t xml:space="preserve">1.66140079498291</t>
@@ -4676,22 +4676,22 @@
     <t xml:space="preserve">1.66907179355621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67028295993805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6965264081955</t>
+    <t xml:space="preserve">1.67028307914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69652652740479</t>
   </si>
   <si>
     <t xml:space="preserve">1.68562543392181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61044836044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66180455684662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64282858371735</t>
+    <t xml:space="preserve">1.61044859886169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66180467605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64282846450806</t>
   </si>
   <si>
     <t xml:space="preserve">1.67593550682068</t>
@@ -4703,28 +4703,28 @@
     <t xml:space="preserve">1.68279922008514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68966281414032</t>
+    <t xml:space="preserve">1.68966269493103</t>
   </si>
   <si>
     <t xml:space="preserve">1.68118417263031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67997300624847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70137131214142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67795419692993</t>
+    <t xml:space="preserve">1.67997288703918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70137143135071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67795431613922</t>
   </si>
   <si>
     <t xml:space="preserve">1.71429097652435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75426161289215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.799480676651</t>
+    <t xml:space="preserve">1.75426149368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79948055744171</t>
   </si>
   <si>
     <t xml:space="preserve">1.78857946395874</t>
@@ -4733,10 +4733,10 @@
     <t xml:space="preserve">1.80351805686951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81684148311615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82451248168945</t>
+    <t xml:space="preserve">1.81684160232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82451260089874</t>
   </si>
   <si>
     <t xml:space="preserve">1.84429609775543</t>
@@ -4748,13 +4748,13 @@
     <t xml:space="preserve">1.84510362148285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82572388648987</t>
+    <t xml:space="preserve">1.82572400569916</t>
   </si>
   <si>
     <t xml:space="preserve">1.79503977298737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76072132587433</t>
+    <t xml:space="preserve">1.76072144508362</t>
   </si>
   <si>
     <t xml:space="preserve">1.80836308002472</t>
@@ -4763,13 +4763,13 @@
     <t xml:space="preserve">1.84550750255585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85317862033844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8915342092514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89839792251587</t>
+    <t xml:space="preserve">1.85317873954773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89153397083282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89839768409729</t>
   </si>
   <si>
     <t xml:space="preserve">1.89274537563324</t>
@@ -4778,31 +4778,31 @@
     <t xml:space="preserve">1.94603931903839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98076128959656</t>
+    <t xml:space="preserve">1.98076117038727</t>
   </si>
   <si>
     <t xml:space="preserve">1.98237597942352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92423725128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97591614723206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99327707290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99368119239807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02194309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00014066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01790547370911</t>
+    <t xml:space="preserve">1.92423713207245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97591626644135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99327719211578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99368095397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02194285392761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00014090538025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01790571212769</t>
   </si>
   <si>
     <t xml:space="preserve">2.02073168754578</t>
@@ -4814,10 +4814,10 @@
     <t xml:space="preserve">2.05989480018616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07079601287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06231689453125</t>
+    <t xml:space="preserve">2.07079577445984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06231713294983</t>
   </si>
   <si>
     <t xml:space="preserve">2.06150960922241</t>
@@ -4826,31 +4826,31 @@
     <t xml:space="preserve">1.99973714351654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03001761436462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04535984992981</t>
+    <t xml:space="preserve">2.0300178527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04536008834839</t>
   </si>
   <si>
     <t xml:space="preserve">2.06837344169617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0485897064209</t>
+    <t xml:space="preserve">2.04858994483948</t>
   </si>
   <si>
     <t xml:space="preserve">2.05262732505798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07887053489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09340524673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07119965553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07725548744202</t>
+    <t xml:space="preserve">2.07887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09340500831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07119941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.04414892196655</t>
@@ -4859,19 +4859,19 @@
     <t xml:space="preserve">2.00417828559875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88184416294098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94482803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81159317493439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81522679328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77081525325775</t>
+    <t xml:space="preserve">1.88184440135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94482815265656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81159293651581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81522655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77081513404846</t>
   </si>
   <si>
     <t xml:space="preserve">1.83702886104584</t>
@@ -4880,10 +4880,10 @@
     <t xml:space="preserve">1.90162765979767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89193761348724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255811691284</t>
+    <t xml:space="preserve">1.89193773269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87255823612213</t>
   </si>
   <si>
     <t xml:space="preserve">1.82733905315399</t>
@@ -4892,25 +4892,25 @@
     <t xml:space="preserve">1.83420252799988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85196721553802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87982559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90970230102539</t>
+    <t xml:space="preserve">1.85196709632874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87982583045959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90970253944397</t>
   </si>
   <si>
     <t xml:space="preserve">1.91172122955322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86448323726654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90405035018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91939234733582</t>
+    <t xml:space="preserve">1.86448335647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90405011177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91939258575439</t>
   </si>
   <si>
     <t xml:space="preserve">1.934330701828</t>
@@ -4919,82 +4919,82 @@
     <t xml:space="preserve">1.92827475070953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97147512435913</t>
+    <t xml:space="preserve">1.97147524356842</t>
   </si>
   <si>
     <t xml:space="preserve">2.00094819068909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01750159263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01023435592651</t>
+    <t xml:space="preserve">2.01750183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01023459434509</t>
   </si>
   <si>
     <t xml:space="preserve">2.00619673728943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02436542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98722064495087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96541917324066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98479855060577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92544829845428</t>
+    <t xml:space="preserve">2.02436518669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98722088336945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96541893482208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98479866981506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92544841766357</t>
   </si>
   <si>
     <t xml:space="preserve">1.88022923469543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91293251514435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395654201508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96380376815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883605003357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98358726501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95048034191132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93917560577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96057403087616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95451784133911</t>
+    <t xml:space="preserve">1.91293227672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8939563035965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96380388736725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883616924286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98358738422394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95048022270203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9391758441925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96057426929474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9545179605484</t>
   </si>
   <si>
     <t xml:space="preserve">1.94038689136505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9294855594635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95128798484802</t>
+    <t xml:space="preserve">1.92948591709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95128786563873</t>
   </si>
   <si>
     <t xml:space="preserve">1.96353375911713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9643726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88888442516327</t>
+    <t xml:space="preserve">1.96437251567841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88888430595398</t>
   </si>
   <si>
     <t xml:space="preserve">1.8880455493927</t>
@@ -5003,7 +5003,7 @@
     <t xml:space="preserve">1.88301289081573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86665737628937</t>
+    <t xml:space="preserve">1.86665749549866</t>
   </si>
   <si>
     <t xml:space="preserve">1.85365641117096</t>
@@ -5015,7 +5015,7 @@
     <t xml:space="preserve">1.87043154239655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90523993968964</t>
+    <t xml:space="preserve">1.90524005889893</t>
   </si>
   <si>
     <t xml:space="preserve">1.89475572109222</t>
@@ -5030,7 +5030,7 @@
     <t xml:space="preserve">1.94927477836609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93711268901825</t>
+    <t xml:space="preserve">1.93711280822754</t>
   </si>
   <si>
     <t xml:space="preserve">1.93417739868164</t>
@@ -5045,7 +5045,7 @@
     <t xml:space="preserve">1.97779285907745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99037408828735</t>
+    <t xml:space="preserve">1.99037396907806</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840735435486</t>
@@ -5054,10 +5054,10 @@
     <t xml:space="preserve">2.00169730186462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01805305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99540638923645</t>
+    <t xml:space="preserve">2.01805329322815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99540627002716</t>
   </si>
   <si>
     <t xml:space="preserve">1.95850133895874</t>
@@ -5066,10 +5066,10 @@
     <t xml:space="preserve">1.95598495006561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98072838783264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98240602016449</t>
+    <t xml:space="preserve">1.98072850704193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9824059009552</t>
   </si>
   <si>
     <t xml:space="preserve">2.00127792358398</t>
@@ -5078,19 +5078,19 @@
     <t xml:space="preserve">2.01302075386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04405450820923</t>
+    <t xml:space="preserve">2.04405474662781</t>
   </si>
   <si>
     <t xml:space="preserve">2.03021502494812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02056956291199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96311438083649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97024393081665</t>
+    <t xml:space="preserve">2.02056932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96311450004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97024369239807</t>
   </si>
   <si>
     <t xml:space="preserve">1.97695410251617</t>
@@ -5099,13 +5099,13 @@
     <t xml:space="preserve">1.99666500091553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01973032951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04992604255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03860282897949</t>
+    <t xml:space="preserve">2.01973056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04992628097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03860306739807</t>
   </si>
   <si>
     <t xml:space="preserve">2.04237699508667</t>
@@ -5135,10 +5135,10 @@
     <t xml:space="preserve">2.18874025344849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20509624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.188321352005</t>
+    <t xml:space="preserve">2.20509600639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18832111358643</t>
   </si>
   <si>
     <t xml:space="preserve">2.149738073349</t>
@@ -5156,7 +5156,7 @@
     <t xml:space="preserve">1.96101760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00672960281372</t>
+    <t xml:space="preserve">2.0067298412323</t>
   </si>
   <si>
     <t xml:space="preserve">2.04489350318909</t>
@@ -5168,10 +5168,10 @@
     <t xml:space="preserve">2.05076456069946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03734445571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02937650680542</t>
+    <t xml:space="preserve">2.03734421730042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.029376745224</t>
   </si>
   <si>
     <t xml:space="preserve">2.02224707603455</t>
@@ -5186,7 +5186,7 @@
     <t xml:space="preserve">2.05915212631226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0532808303833</t>
+    <t xml:space="preserve">2.05328106880188</t>
   </si>
   <si>
     <t xml:space="preserve">2.0545392036438</t>
@@ -5201,10 +5201,10 @@
     <t xml:space="preserve">2.09857392311096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07341122627258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0587329864502</t>
+    <t xml:space="preserve">2.073410987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05873274803162</t>
   </si>
   <si>
     <t xml:space="preserve">2.05202293395996</t>
@@ -5225,10 +5225,10 @@
     <t xml:space="preserve">2.07634663581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06544303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07592725753784</t>
+    <t xml:space="preserve">2.06544327735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07592749595642</t>
   </si>
   <si>
     <t xml:space="preserve">2.07089495658875</t>
@@ -5246,16 +5246,16 @@
     <t xml:space="preserve">2.09102511405945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06418490409851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03482818603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0323121547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04657101631165</t>
+    <t xml:space="preserve">2.06418466567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03482842445374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03231191635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04657077789307</t>
   </si>
   <si>
     <t xml:space="preserve">1.98156714439392</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">1.98282539844513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01427865028381</t>
+    <t xml:space="preserve">2.01427888870239</t>
   </si>
   <si>
     <t xml:space="preserve">1.99330937862396</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">2.04908728599548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05286169052124</t>
+    <t xml:space="preserve">2.05286145210266</t>
   </si>
   <si>
     <t xml:space="preserve">2.026859998703</t>
@@ -5285,13 +5285,13 @@
     <t xml:space="preserve">2.03650593757629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99205160140991</t>
+    <t xml:space="preserve">1.9920517206192</t>
   </si>
   <si>
     <t xml:space="preserve">1.96605014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99079370498657</t>
+    <t xml:space="preserve">1.99079346656799</t>
   </si>
   <si>
     <t xml:space="preserve">1.97611522674561</t>
@@ -5330,28 +5330,28 @@
     <t xml:space="preserve">2.18286919593811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20551562309265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21893572807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21977496147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25164747238159</t>
+    <t xml:space="preserve">2.20551586151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2189359664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21977472305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25164723396301</t>
   </si>
   <si>
     <t xml:space="preserve">2.27114582061768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23835277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25209045410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26848721504211</t>
+    <t xml:space="preserve">2.23835301399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25209021568298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26848697662354</t>
   </si>
   <si>
     <t xml:space="preserve">2.3039391040802</t>
@@ -5360,10 +5360,10 @@
     <t xml:space="preserve">2.30438208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.326096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34559535980225</t>
+    <t xml:space="preserve">2.32609677314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34559559822083</t>
   </si>
   <si>
     <t xml:space="preserve">2.34116387367249</t>
@@ -5372,19 +5372,19 @@
     <t xml:space="preserve">2.36287808418274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38858103752136</t>
+    <t xml:space="preserve">2.38858079910278</t>
   </si>
   <si>
     <t xml:space="preserve">2.37838840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39788675308228</t>
+    <t xml:space="preserve">2.39788699150085</t>
   </si>
   <si>
     <t xml:space="preserve">2.37307071685791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39301228523254</t>
+    <t xml:space="preserve">2.39301252365112</t>
   </si>
   <si>
     <t xml:space="preserve">2.38503575325012</t>
@@ -5402,7 +5402,7 @@
     <t xml:space="preserve">2.33540272712708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32653975486755</t>
+    <t xml:space="preserve">2.32653999328613</t>
   </si>
   <si>
     <t xml:space="preserve">2.35046982765198</t>
@@ -5417,10 +5417,10 @@
     <t xml:space="preserve">2.34603834152222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35445809364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34204983711243</t>
+    <t xml:space="preserve">2.35445833206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34205007553101</t>
   </si>
   <si>
     <t xml:space="preserve">2.34293627738953</t>
@@ -5429,25 +5429,25 @@
     <t xml:space="preserve">2.38813757896423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38592171669006</t>
+    <t xml:space="preserve">2.38592195510864</t>
   </si>
   <si>
     <t xml:space="preserve">2.44131565093994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47056341171265</t>
+    <t xml:space="preserve">2.47056365013123</t>
   </si>
   <si>
     <t xml:space="preserve">2.47765421867371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44353127479553</t>
+    <t xml:space="preserve">2.44353151321411</t>
   </si>
   <si>
     <t xml:space="preserve">2.43599796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41694259643555</t>
+    <t xml:space="preserve">2.41694235801697</t>
   </si>
   <si>
     <t xml:space="preserve">2.41339731216431</t>
@@ -5456,25 +5456,25 @@
     <t xml:space="preserve">2.40719318389893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41827178001404</t>
+    <t xml:space="preserve">2.41827201843262</t>
   </si>
   <si>
     <t xml:space="preserve">2.43732738494873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44220185279846</t>
+    <t xml:space="preserve">2.44220209121704</t>
   </si>
   <si>
     <t xml:space="preserve">2.45328068733215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45682621002197</t>
+    <t xml:space="preserve">2.45682597160339</t>
   </si>
   <si>
     <t xml:space="preserve">2.51221990585327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4887330532074</t>
+    <t xml:space="preserve">2.48873281478882</t>
   </si>
   <si>
     <t xml:space="preserve">2.49139165878296</t>
@@ -5486,7 +5486,7 @@
     <t xml:space="preserve">2.54988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53747916221619</t>
+    <t xml:space="preserve">2.53747940063477</t>
   </si>
   <si>
     <t xml:space="preserve">2.48430132865906</t>
@@ -5507,13 +5507,13 @@
     <t xml:space="preserve">2.49670934677124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46879124641418</t>
+    <t xml:space="preserve">2.46879100799561</t>
   </si>
   <si>
     <t xml:space="preserve">2.50247049331665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4869601726532</t>
+    <t xml:space="preserve">2.48696041107178</t>
   </si>
   <si>
     <t xml:space="preserve">2.49538016319275</t>
@@ -5525,10 +5525,10 @@
     <t xml:space="preserve">2.50379991531372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51620817184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52551412582397</t>
+    <t xml:space="preserve">2.5162079334259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52551436424255</t>
   </si>
   <si>
     <t xml:space="preserve">2.55742120742798</t>
@@ -5537,7 +5537,7 @@
     <t xml:space="preserve">2.5671706199646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60483813285828</t>
+    <t xml:space="preserve">2.6048378944397</t>
   </si>
   <si>
     <t xml:space="preserve">2.61857581138611</t>
@@ -5549,7 +5549,7 @@
     <t xml:space="preserve">2.6145875453949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60395169258118</t>
+    <t xml:space="preserve">2.60395193099976</t>
   </si>
   <si>
     <t xml:space="preserve">2.66289091110229</t>
@@ -5573,28 +5573,28 @@
     <t xml:space="preserve">2.72183012962341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78475737571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82109594345093</t>
+    <t xml:space="preserve">2.78475713729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82109570503235</t>
   </si>
   <si>
     <t xml:space="preserve">2.81046009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86053609848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86186552047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90352153778076</t>
+    <t xml:space="preserve">2.86053586006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86186575889587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90352177619934</t>
   </si>
   <si>
     <t xml:space="preserve">2.899090051651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91858863830566</t>
+    <t xml:space="preserve">2.91858887672424</t>
   </si>
   <si>
     <t xml:space="preserve">2.92036128044128</t>
@@ -5603,7 +5603,7 @@
     <t xml:space="preserve">2.94384837150574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96511960029602</t>
+    <t xml:space="preserve">2.96511936187744</t>
   </si>
   <si>
     <t xml:space="preserve">2.96733522415161</t>
@@ -5621,13 +5621,13 @@
     <t xml:space="preserve">3.00012850761414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95049548149109</t>
+    <t xml:space="preserve">2.95049571990967</t>
   </si>
   <si>
     <t xml:space="preserve">2.97442579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93498539924622</t>
+    <t xml:space="preserve">2.93498563766479</t>
   </si>
   <si>
     <t xml:space="preserve">2.96910786628723</t>
@@ -5651,7 +5651,7 @@
     <t xml:space="preserve">2.96866464614868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99303817749023</t>
+    <t xml:space="preserve">2.99303793907166</t>
   </si>
   <si>
     <t xml:space="preserve">3.03868269920349</t>
@@ -5696,13 +5696,13 @@
     <t xml:space="preserve">3.19112634658813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21416997909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2819721698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3032431602478</t>
+    <t xml:space="preserve">3.21417021751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28197193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30324339866638</t>
   </si>
   <si>
     <t xml:space="preserve">3.30856108665466</t>
@@ -6777,6 +6777,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.57399988174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60699987411499</t>
   </si>
 </sst>
 </file>
@@ -72193,7 +72196,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6938657407</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>44674834</v>
@@ -72214,6 +72217,32 @@
         <v>2254</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6939699074</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>42965378</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>5.61199998855591</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>5.51300001144409</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>5.51300001144409</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>5.60699987411499</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>2255</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISP.MI.xlsx
+++ b/data/ISP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="2254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="2255">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,106 +38,106 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53063917160034</t>
+    <t xml:space="preserve">1.53063893318176</t>
   </si>
   <si>
     <t xml:space="preserve">ISP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56040990352631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51831996440887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49265551567078</t>
+    <t xml:space="preserve">1.56040978431702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5183197259903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49265515804291</t>
   </si>
   <si>
     <t xml:space="preserve">1.48752224445343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46699059009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49676156044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52447950839996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4854691028595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4382461309433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36638510227203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38075745105743</t>
+    <t xml:space="preserve">1.46699070930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49676167964935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52447938919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48546922206879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43824636936188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3663854598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38075757026672</t>
   </si>
   <si>
     <t xml:space="preserve">1.30479001998901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36843836307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39307641983032</t>
+    <t xml:space="preserve">1.36843848228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39307653903961</t>
   </si>
   <si>
     <t xml:space="preserve">1.35406613349915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37254476547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35919904708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29041767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380066394806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31505608558655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26988613605499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20315837860107</t>
+    <t xml:space="preserve">1.37254464626312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3591992855072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29041790962219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380030632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31505572795868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26988625526428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20315825939178</t>
   </si>
   <si>
     <t xml:space="preserve">1.27296602725983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22368991374969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17441380023956</t>
+    <t xml:space="preserve">1.22369003295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17441391944885</t>
   </si>
   <si>
     <t xml:space="preserve">1.10152626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26064693927765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22984945774078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25243449211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28220510482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21958351135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19494569301605</t>
+    <t xml:space="preserve">1.26064705848694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22984933853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25243413448334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28220522403717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21958363056183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19494557380676</t>
   </si>
   <si>
     <t xml:space="preserve">1.23395574092865</t>
@@ -149,16 +149,16 @@
     <t xml:space="preserve">1.16004168987274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18057346343994</t>
+    <t xml:space="preserve">1.18057322502136</t>
   </si>
   <si>
     <t xml:space="preserve">1.20007848739624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20213150978088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22471630573273</t>
+    <t xml:space="preserve">1.20213162899017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2247166633606</t>
   </si>
   <si>
     <t xml:space="preserve">1.27091288566589</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">1.32224202156067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29555058479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2647533416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27604579925537</t>
+    <t xml:space="preserve">1.29555082321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26475346088409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27604568004608</t>
   </si>
   <si>
     <t xml:space="preserve">1.2914445400238</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">1.30581676959991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40334224700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37459778785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36022579669952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3304545879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29349756240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27912545204163</t>
+    <t xml:space="preserve">1.40334248542786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37459790706635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36022567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33045494556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29349780082703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27912569046021</t>
   </si>
   <si>
     <t xml:space="preserve">1.29247093200684</t>
@@ -206,43 +206,43 @@
     <t xml:space="preserve">1.2575671672821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23600876331329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24935460090637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24114191532135</t>
+    <t xml:space="preserve">1.23600900173187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24935448169708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24114179611206</t>
   </si>
   <si>
     <t xml:space="preserve">1.2175304889679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18673276901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13540351390839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14874911308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1107656955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1774936914444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19802498817444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24422144889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25038111209869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25654065608978</t>
+    <t xml:space="preserve">1.18673264980316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13540375232697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1487489938736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11076545715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17749333381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19802522659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24422168731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25038123130798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2565404176712</t>
   </si>
   <si>
     <t xml:space="preserve">1.26270020008087</t>
@@ -257,40 +257,40 @@
     <t xml:space="preserve">1.23190259933472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26680648326874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26783311367035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18878602981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16209471225739</t>
+    <t xml:space="preserve">1.26680624485016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26783299446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18878591060638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1620945930481</t>
   </si>
   <si>
     <t xml:space="preserve">1.13950979709625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1425895690918</t>
+    <t xml:space="preserve">1.14258968830109</t>
   </si>
   <si>
     <t xml:space="preserve">1.1497757434845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15798830986023</t>
+    <t xml:space="preserve">1.15798842906952</t>
   </si>
   <si>
     <t xml:space="preserve">1.14566946029663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14156305789948</t>
+    <t xml:space="preserve">1.1415628194809</t>
   </si>
   <si>
     <t xml:space="preserve">1.1292439699173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12103140354156</t>
+    <t xml:space="preserve">1.12103128433228</t>
   </si>
   <si>
     <t xml:space="preserve">1.15080237388611</t>
@@ -302,10 +302,10 @@
     <t xml:space="preserve">1.18775928020477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18666636943817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.258784532547</t>
+    <t xml:space="preserve">1.18666660785675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25878417491913</t>
   </si>
   <si>
     <t xml:space="preserve">1.28719460964203</t>
@@ -320,40 +320,40 @@
     <t xml:space="preserve">1.24020874500275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23037457466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20852041244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20414984226227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22491097450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21070599555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19977915287018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15060770511627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08286070823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04516267776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07466530799866</t>
+    <t xml:space="preserve">1.23037421703339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20852065086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20414972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22491109371185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2107058763504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1997789144516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15060782432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08286046981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0451625585556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07466542720795</t>
   </si>
   <si>
     <t xml:space="preserve">1.06537759304047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11454880237579</t>
+    <t xml:space="preserve">1.1145486831665</t>
   </si>
   <si>
     <t xml:space="preserve">1.14842236042023</t>
@@ -365,49 +365,49 @@
     <t xml:space="preserve">1.17573976516724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23365259170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950644373893738</t>
+    <t xml:space="preserve">1.23365235328674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950644552707672</t>
   </si>
   <si>
     <t xml:space="preserve">0.846838474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887268126010895</t>
+    <t xml:space="preserve">0.887268304824829</t>
   </si>
   <si>
     <t xml:space="preserve">0.900380611419678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929883420467377</t>
+    <t xml:space="preserve">0.929883360862732</t>
   </si>
   <si>
     <t xml:space="preserve">0.917863667011261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890000104904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870331585407257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868692576885223</t>
+    <t xml:space="preserve">0.88999992609024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870331466197968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868692517280579</t>
   </si>
   <si>
     <t xml:space="preserve">0.87415599822998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961571455001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983425378799438</t>
+    <t xml:space="preserve">0.961571574211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983425259590149</t>
   </si>
   <si>
     <t xml:space="preserve">1.04789435863495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03587472438812</t>
+    <t xml:space="preserve">1.0358749628067</t>
   </si>
   <si>
     <t xml:space="preserve">1.05772864818573</t>
@@ -425,10 +425,10 @@
     <t xml:space="preserve">1.06373858451843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0670166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06865549087524</t>
+    <t xml:space="preserve">1.06701648235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06865561008453</t>
   </si>
   <si>
     <t xml:space="preserve">1.04898703098297</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">1.03969931602478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07630443572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03860664367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999269545078278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993805825710297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994352221488953</t>
+    <t xml:space="preserve">1.07630431652069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03860652446747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999269366264343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993805944919586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994352459907532</t>
   </si>
   <si>
     <t xml:space="preserve">1.03806018829346</t>
@@ -467,31 +467,31 @@
     <t xml:space="preserve">1.0560896396637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07958257198334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05827510356903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03041124343872</t>
+    <t xml:space="preserve">1.07958269119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05827486515045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03041136264801</t>
   </si>
   <si>
     <t xml:space="preserve">1.00964999198914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05991399288177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09214854240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08231437206268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10034370422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08996319770813</t>
+    <t xml:space="preserve">1.05991411209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09214866161346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08231425285339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10034358501434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08996307849884</t>
   </si>
   <si>
     <t xml:space="preserve">1.11673414707184</t>
@@ -503,85 +503,85 @@
     <t xml:space="preserve">1.19759368896484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19213008880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1680908203125</t>
+    <t xml:space="preserve">1.19213020801544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16809105873108</t>
   </si>
   <si>
     <t xml:space="preserve">1.1790177822113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18338847160339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15934920310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13749539852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13640248775482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12766087055206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09706580638885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11236321926117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12656843662262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09050977230072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07794368267059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06428492069244</t>
+    <t xml:space="preserve">1.18338859081268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15934932231903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13749527931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13640260696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12766098976135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09706568717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11236333847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12656819820404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09050953388214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07794344425201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06428468227386</t>
   </si>
   <si>
     <t xml:space="preserve">1.06155300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06319212913513</t>
+    <t xml:space="preserve">1.06319224834442</t>
   </si>
   <si>
     <t xml:space="preserve">1.07848978042603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05445063114166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08941686153412</t>
+    <t xml:space="preserve">1.05445051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08941698074341</t>
   </si>
   <si>
     <t xml:space="preserve">1.09378755092621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0768506526947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08340692520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12329018115997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.130939245224</t>
+    <t xml:space="preserve">1.07685101032257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08340704441071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12329053878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13093912601471</t>
   </si>
   <si>
     <t xml:space="preserve">1.15170037746429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15388584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17792510986328</t>
+    <t xml:space="preserve">1.15388572216034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1779248714447</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196437835693</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">1.13858807086945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09925103187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09597313404083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16044199466705</t>
+    <t xml:space="preserve">1.0992511510849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09597301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16044211387634</t>
   </si>
   <si>
     <t xml:space="preserve">1.16918361186981</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">1.22054028511047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21835482120514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15497863292694</t>
+    <t xml:space="preserve">1.21835494041443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15497851371765</t>
   </si>
   <si>
     <t xml:space="preserve">1.14186608791351</t>
@@ -623,91 +623,91 @@
     <t xml:space="preserve">1.11891961097717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10362184047699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06810939311981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11345601081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14514446258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24567210674286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26643323898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30904865264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27845323085785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32762432098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29265809059143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33636581897736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31888282299042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33745872974396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33855140209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3440146446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964383602142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871687412262</t>
+    <t xml:space="preserve">1.1036217212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06810915470123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11345613002777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14514422416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24567234516144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26643335819244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30904853343964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27845311164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32762444019318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29265820980072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33636593818665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31888258457184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33745837211609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3385511636734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34401488304138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964407444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871699333191</t>
   </si>
   <si>
     <t xml:space="preserve">1.31779003143311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32543921470642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36805415153503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3877227306366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39755702018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38990795612335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35275638103485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34838557243347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34619998931885</t>
+    <t xml:space="preserve">1.32543897628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36805403232574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38772237300873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3975567817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38990783691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35275626182556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34838545322418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34620010852814</t>
   </si>
   <si>
     <t xml:space="preserve">1.34729290008545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3221607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34292197227478</t>
+    <t xml:space="preserve">1.32216095924377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34292185306549</t>
   </si>
   <si>
     <t xml:space="preserve">1.34947824478149</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">1.31014120578766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25222849845886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25659906864166</t>
+    <t xml:space="preserve">1.25222826004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25659930706024</t>
   </si>
   <si>
     <t xml:space="preserve">1.22928178310394</t>
@@ -731,19 +731,19 @@
     <t xml:space="preserve">1.20087170600891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18557393550873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19103741645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22272562980652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19322264194489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17027628421783</t>
+    <t xml:space="preserve">1.18557405471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19103753566742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22272539138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19322288036346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17027592658997</t>
   </si>
   <si>
     <t xml:space="preserve">1.17355442047119</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">1.19650101661682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18120324611664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13421714305878</t>
+    <t xml:space="preserve">1.18120312690735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13421726226807</t>
   </si>
   <si>
     <t xml:space="preserve">1.25113558769226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27626729011536</t>
+    <t xml:space="preserve">1.27626764774323</t>
   </si>
   <si>
     <t xml:space="preserve">1.26861882209778</t>
@@ -776,73 +776,73 @@
     <t xml:space="preserve">1.27189695835114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27408230304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30577027797699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34182929992676</t>
+    <t xml:space="preserve">1.27408218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30577051639557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34182941913605</t>
   </si>
   <si>
     <t xml:space="preserve">1.32325339317322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35057067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35603415966034</t>
+    <t xml:space="preserve">1.35057079792023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35603451728821</t>
   </si>
   <si>
     <t xml:space="preserve">1.36914658546448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39100062847137</t>
+    <t xml:space="preserve">1.39100050926208</t>
   </si>
   <si>
     <t xml:space="preserve">1.38662981987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38335180282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37679553031921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38007366657257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37898075580597</t>
+    <t xml:space="preserve">1.38335204124451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3767956495285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38007342815399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37898087501526</t>
   </si>
   <si>
     <t xml:space="preserve">1.37461030483246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36696147918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384893417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33199501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30467760562897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35166347026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36040496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37351739406586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47623074054718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50573325157166</t>
+    <t xml:space="preserve">1.36696135997772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384881496429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33199536800385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30467772483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35166358947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36040484905243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37351751327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4762305021286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50573348999023</t>
   </si>
   <si>
     <t xml:space="preserve">1.49480664730072</t>
@@ -851,49 +851,49 @@
     <t xml:space="preserve">1.45984029769897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46093308925629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46311807632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47076725959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50791883468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55271935462952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55818283557892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55599761009216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5570901632309</t>
+    <t xml:space="preserve">1.46093320846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46311819553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47076737880707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50791895389557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55271971225739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55818271636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55599749088287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55709028244019</t>
   </si>
   <si>
     <t xml:space="preserve">1.5472559928894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54507052898407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5516265630722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52868020534515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52212381362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52977299690247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56594622135162</t>
+    <t xml:space="preserve">1.54507076740265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55162668228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52868008613586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52212417125702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52977287769318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56594586372375</t>
   </si>
   <si>
     <t xml:space="preserve">1.57061350345612</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">1.56711304187775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55427706241608</t>
+    <t xml:space="preserve">1.55427718162537</t>
   </si>
   <si>
     <t xml:space="preserve">1.49826729297638</t>
@@ -911,109 +911,109 @@
     <t xml:space="preserve">1.48893225193024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48659861087799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50060093402863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51110279560089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49126625061035</t>
+    <t xml:space="preserve">1.48659884929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5006011724472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5111026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49126601219177</t>
   </si>
   <si>
     <t xml:space="preserve">1.48426473140717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49943399429321</t>
+    <t xml:space="preserve">1.4994341135025</t>
   </si>
   <si>
     <t xml:space="preserve">1.50876915454865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50176775455475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50410151481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49710023403168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47843039035797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51460325717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52510547637939</t>
+    <t xml:space="preserve">1.50176787376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50410163402557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49710047245026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47843050956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51460349559784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5251053571701</t>
   </si>
   <si>
     <t xml:space="preserve">1.52627229690552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57994842529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60795342922211</t>
+    <t xml:space="preserve">1.57994830608368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6079535484314</t>
   </si>
   <si>
     <t xml:space="preserve">1.64062607288361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61845529079437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61962223052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66279661655426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6592960357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67213129997253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65696203708649</t>
+    <t xml:space="preserve">1.61845541000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6196221113205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66279625892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65929627418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67213177680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65696227550507</t>
   </si>
   <si>
     <t xml:space="preserve">1.66863083839417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65346193313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66162979602814</t>
+    <t xml:space="preserve">1.6534618139267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66163003444672</t>
   </si>
   <si>
     <t xml:space="preserve">1.66396343708038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67096471786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67446529865265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66629731655121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67329835891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68380033969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6931357383728</t>
+    <t xml:space="preserve">1.67096483707428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67446517944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66629719734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67329859733582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6838002204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69313526153564</t>
   </si>
   <si>
     <t xml:space="preserve">1.69546902179718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69430255889893</t>
+    <t xml:space="preserve">1.69430232048035</t>
   </si>
   <si>
     <t xml:space="preserve">1.69896972179413</t>
@@ -1022,40 +1022,40 @@
     <t xml:space="preserve">1.70130324363708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69196856021881</t>
+    <t xml:space="preserve">1.69196844100952</t>
   </si>
   <si>
     <t xml:space="preserve">1.7036372423172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7083044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70480382442474</t>
+    <t xml:space="preserve">1.70830476284027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70480406284332</t>
   </si>
   <si>
     <t xml:space="preserve">1.68263351917267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67796611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66046273708344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70713782310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68963479995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64295995235443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65462851524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6581289768219</t>
+    <t xml:space="preserve">1.6779659986496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6604630947113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70713794231415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6896345615387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64295983314514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65462827682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65812909603119</t>
   </si>
   <si>
     <t xml:space="preserve">1.63712549209595</t>
@@ -1067,79 +1067,79 @@
     <t xml:space="preserve">1.68146657943726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70013654232025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71063840389252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71763980388641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73280930519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73397612571716</t>
+    <t xml:space="preserve">1.70013666152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71063876152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71763968467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73280894756317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73397588729858</t>
   </si>
   <si>
     <t xml:space="preserve">1.72464108467102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73514258861542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447786808014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7421441078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74564480781555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7468113899231</t>
+    <t xml:space="preserve">1.73514306545258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447810649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74214422702789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74564468860626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74681162834167</t>
   </si>
   <si>
     <t xml:space="preserve">1.74097728729248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71180510520935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71530604362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70947158336639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68496751785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66746413707733</t>
+    <t xml:space="preserve">1.71180534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71530592441559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70947170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6849672794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66746437549591</t>
   </si>
   <si>
     <t xml:space="preserve">1.68029963970184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70597100257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67913281917572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.651127576828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63362455368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6347918510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61728858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.614954829216</t>
+    <t xml:space="preserve">1.70597076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67913269996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65112793445587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.633624792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63479173183441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61728847026825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61495447158813</t>
   </si>
   <si>
     <t xml:space="preserve">1.64412689208984</t>
@@ -1148,436 +1148,436 @@
     <t xml:space="preserve">1.61378800868988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64529359340668</t>
+    <t xml:space="preserve">1.64529347419739</t>
   </si>
   <si>
     <t xml:space="preserve">1.6464604139328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67563247680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63829255104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62895715236664</t>
+    <t xml:space="preserve">1.67563235759735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63829231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62895727157593</t>
   </si>
   <si>
     <t xml:space="preserve">1.62662363052368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62779033184052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61612153053284</t>
+    <t xml:space="preserve">1.62779057025909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61612164974213</t>
   </si>
   <si>
     <t xml:space="preserve">1.60678660869598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60445308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74331104755402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76548194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77248322963715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77598321437836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78415155410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80515563488007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80165457725525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8238251209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8249922990799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79815399646759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82149171829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84366261959076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824835300446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83549427986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84395432472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111798763275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81769943237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79902911186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81098973751068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87283432483673</t>
+    <t xml:space="preserve">1.60445272922516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74331092834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76548159122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77248299121857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77598357200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78415191173553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80515551567078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80165505409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82382535934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82499217987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79815423488617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82149159908295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84366238117218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824811458588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83549392223358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84395372867584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111846446991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81769907474518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79902935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81098997592926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87283384799957</t>
   </si>
   <si>
     <t xml:space="preserve">1.83636951446533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81157302856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377865791321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8092395067215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80690550804138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83053505420685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8130316734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223798751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80748891830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78444349765778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79873728752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79990434646606</t>
+    <t xml:space="preserve">1.81157338619232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377818107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923926830292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80690562725067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83053481578827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81303179264069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223822593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8074893951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78444337844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79873764514923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79990422725677</t>
   </si>
   <si>
     <t xml:space="preserve">1.80982279777527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80632197856903</t>
+    <t xml:space="preserve">1.8063223361969</t>
   </si>
   <si>
     <t xml:space="preserve">1.79290282726288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75410461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7293084859848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74535322189331</t>
+    <t xml:space="preserve">1.75410497188568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72930824756622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74535310268402</t>
   </si>
   <si>
     <t xml:space="preserve">1.76519000530243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77510833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78035962581635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540016174316</t>
+    <t xml:space="preserve">1.77510809898376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7803590297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77540004253387</t>
   </si>
   <si>
     <t xml:space="preserve">1.74885356426239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76081383228302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79523694515228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77364981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78473496437073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77423334121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74272763729095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72259891033173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70742952823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72289097309113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72318232059479</t>
+    <t xml:space="preserve">1.76081418991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79523682594299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7736496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78473508358002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77423310279846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74272739887238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72259914875031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70742976665497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72289049625397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72318208217621</t>
   </si>
   <si>
     <t xml:space="preserve">1.72522449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71909832954407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7520626783371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74768674373627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76256453990936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77131581306458</t>
+    <t xml:space="preserve">1.71909821033478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75206232070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74768686294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76256418228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77131617069244</t>
   </si>
   <si>
     <t xml:space="preserve">1.75906372070312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77948403358459</t>
+    <t xml:space="preserve">1.77948415279388</t>
   </si>
   <si>
     <t xml:space="preserve">1.78940236568451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7946537733078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81449043750763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81536555290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82907617092133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84832978248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86437451839447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83986985683441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85124719142914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83957803249359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84191191196442</t>
+    <t xml:space="preserve">1.79465389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81449031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81536543369293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82907652854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84832942485809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86437439918518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986973762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85124707221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83957827091217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.841912150383</t>
   </si>
   <si>
     <t xml:space="preserve">1.8486213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83811974525452</t>
+    <t xml:space="preserve">1.83811950683594</t>
   </si>
   <si>
     <t xml:space="preserve">1.84453725814819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83403587341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82674252986908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83782780170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85416400432587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80865573883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79436182975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75031220912933</t>
+    <t xml:space="preserve">1.83403539657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82674241065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8378279209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85416412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80865609645844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7943617105484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75031232833862</t>
   </si>
   <si>
     <t xml:space="preserve">1.73967385292053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75156331062317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7209005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70494282245636</t>
+    <t xml:space="preserve">1.75156366825104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72090065479279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70494306087494</t>
   </si>
   <si>
     <t xml:space="preserve">1.65081298351288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59730839729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5319139957428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57759618759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57352900505066</t>
+    <t xml:space="preserve">1.59730851650238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53191435337067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57759642601013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5735285282135</t>
   </si>
   <si>
     <t xml:space="preserve">1.62546873092651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62515556812286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56289052963257</t>
+    <t xml:space="preserve">1.62515568733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56289041042328</t>
   </si>
   <si>
     <t xml:space="preserve">1.55475509166718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53629457950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51752138137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61827218532562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733365058899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62578165531158</t>
+    <t xml:space="preserve">1.5362948179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51752126216888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61827206611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61733341217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62578177452087</t>
   </si>
   <si>
     <t xml:space="preserve">1.62327861785889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59417939186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59793412685394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6057562828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63548111915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60325360298157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61952388286591</t>
+    <t xml:space="preserve">1.59417951107025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59793424606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60575664043427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63548147678375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60325336456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61952364444733</t>
   </si>
   <si>
     <t xml:space="preserve">1.56695795059204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5506876707077</t>
+    <t xml:space="preserve">1.55068778991699</t>
   </si>
   <si>
     <t xml:space="preserve">1.52690804004669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55694532394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55600690841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54474270343781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57634508609772</t>
+    <t xml:space="preserve">1.55694556236267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55600678920746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54474282264709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57634472846985</t>
   </si>
   <si>
     <t xml:space="preserve">1.58416712284088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60513055324554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60294044017792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60606944561005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58041250705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54881024360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53066265583038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973662853241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53660774230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5519392490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54161357879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51658272743225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50531852245331</t>
+    <t xml:space="preserve">1.60513091087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60294055938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60606956481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58041262626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54881048202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53066289424896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973650932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53660762310028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55193912982941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54161405563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51658260822296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5053186416626</t>
   </si>
   <si>
     <t xml:space="preserve">1.50250267982483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53097569942474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55037474632263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57039976119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58322834968567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64830994606018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57259011268616</t>
+    <t xml:space="preserve">1.53097558021545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55037486553192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57039988040924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5832279920578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64830982685089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57258987426758</t>
   </si>
   <si>
     <t xml:space="preserve">1.51188921928406</t>
@@ -1586,127 +1586,127 @@
     <t xml:space="preserve">1.53003692626953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50844740867615</t>
+    <t xml:space="preserve">1.50844752788544</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249005317688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43804693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41426742076874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4017516374588</t>
+    <t xml:space="preserve">1.43804705142975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41426718235016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40175151824951</t>
   </si>
   <si>
     <t xml:space="preserve">1.37640750408173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36576914787292</t>
+    <t xml:space="preserve">1.36576890945435</t>
   </si>
   <si>
     <t xml:space="preserve">1.35732114315033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40331625938416</t>
+    <t xml:space="preserve">1.40331602096558</t>
   </si>
   <si>
     <t xml:space="preserve">1.38329100608826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37672054767609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37891066074371</t>
+    <t xml:space="preserve">1.37672019004822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37891054153442</t>
   </si>
   <si>
     <t xml:space="preserve">1.37859785556793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36357891559601</t>
+    <t xml:space="preserve">1.36357879638672</t>
   </si>
   <si>
     <t xml:space="preserve">1.38172662258148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34918606281281</t>
+    <t xml:space="preserve">1.34918582439423</t>
   </si>
   <si>
     <t xml:space="preserve">1.33135116100311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35857260227203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4590106010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43929851055145</t>
+    <t xml:space="preserve">1.35857248306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897307872772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45901072025299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43929839134216</t>
   </si>
   <si>
     <t xml:space="preserve">1.41583168506622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47997438907623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.456507563591</t>
+    <t xml:space="preserve">1.47997450828552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45650768280029</t>
   </si>
   <si>
     <t xml:space="preserve">1.46432983875275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45744633674622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46683311462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50093805789948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49906075000763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51908564567566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51157641410828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53222692012787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49999952316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54568159580231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5222145318985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50437998771667</t>
+    <t xml:space="preserve">1.45744609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46683323383331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5009378194809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49906063079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51908588409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5115761756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53222703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49999928474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54568147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52221465110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50437986850739</t>
   </si>
   <si>
     <t xml:space="preserve">1.37734615802765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32352912425995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31914842128754</t>
+    <t xml:space="preserve">1.32352888584137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31914854049683</t>
   </si>
   <si>
     <t xml:space="preserve">1.32634496688843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35481798648834</t>
+    <t xml:space="preserve">1.35481786727905</t>
   </si>
   <si>
     <t xml:space="preserve">1.31320345401764</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">1.29818475246429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30506825447083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27284061908722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26783442497253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27753388881683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29536867141724</t>
+    <t xml:space="preserve">1.30506837368011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27284049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26783430576324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27753400802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29536879062653</t>
   </si>
   <si>
     <t xml:space="preserve">1.28066277503967</t>
@@ -1739,22 +1739,22 @@
     <t xml:space="preserve">1.23842239379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24167656898499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23128867149353</t>
+    <t xml:space="preserve">1.24167680740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23128855228424</t>
   </si>
   <si>
     <t xml:space="preserve">1.23166406154633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18936109542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22227728366852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21264040470123</t>
+    <t xml:space="preserve">1.18936121463776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2222775220871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21264028549194</t>
   </si>
   <si>
     <t xml:space="preserve">1.24943625926971</t>
@@ -1763,28 +1763,28 @@
     <t xml:space="preserve">1.24655771255493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22215211391449</t>
+    <t xml:space="preserve">1.2221519947052</t>
   </si>
   <si>
     <t xml:space="preserve">1.24267780780792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25563168525696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2366703748703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25250256061554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28598189353943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26971173286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25500595569611</t>
+    <t xml:space="preserve">1.25563156604767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23667049407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25250267982483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28598213195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2697114944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25500571727753</t>
   </si>
   <si>
     <t xml:space="preserve">1.22665786743164</t>
@@ -1793,61 +1793,61 @@
     <t xml:space="preserve">1.25312852859497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23829734325409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2226527929306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20112597942352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20538139343262</t>
+    <t xml:space="preserve">1.2382972240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22265267372131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20112586021423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20538151264191</t>
   </si>
   <si>
     <t xml:space="preserve">1.17571914196014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20901072025299</t>
+    <t xml:space="preserve">1.20901083946228</t>
   </si>
   <si>
     <t xml:space="preserve">1.20888555049896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22165155410767</t>
+    <t xml:space="preserve">1.22165179252625</t>
   </si>
   <si>
     <t xml:space="preserve">1.27690815925598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27628242969513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28535604476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2719019651413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2816014289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32196450233459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29161393642426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30193936824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23491823673248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24029994010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21376669406891</t>
+    <t xml:space="preserve">1.27628219127655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28535616397858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27190172672272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28160166740417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32196438312531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29161405563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3019392490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23491811752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24029982089996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21376657485962</t>
   </si>
   <si>
     <t xml:space="preserve">1.21026229858398</t>
@@ -1856,37 +1856,37 @@
     <t xml:space="preserve">1.25969910621643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27158915996552</t>
+    <t xml:space="preserve">1.27158904075623</t>
   </si>
   <si>
     <t xml:space="preserve">1.26032483577728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23466789722443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24217712879181</t>
+    <t xml:space="preserve">1.23466801643372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24217736721039</t>
   </si>
   <si>
     <t xml:space="preserve">1.26345384120941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2171459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19662034511566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19461786746979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21389198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19299066066742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18986189365387</t>
+    <t xml:space="preserve">1.21714603900909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19662022590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1946177482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21389186382294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19299077987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18986201286316</t>
   </si>
   <si>
     <t xml:space="preserve">1.25106334686279</t>
@@ -1895,58 +1895,58 @@
     <t xml:space="preserve">1.27221488952637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2575089931488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26470541954041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25844740867615</t>
+    <t xml:space="preserve">1.25750911235809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26470530033112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25844752788544</t>
   </si>
   <si>
     <t xml:space="preserve">1.24017453193665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22465527057648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26001191139221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27565658092499</t>
+    <t xml:space="preserve">1.22465538978577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26001214981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27565670013428</t>
   </si>
   <si>
     <t xml:space="preserve">1.27596950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26814746856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26908612251282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29192698001862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28003692626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28191435337067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28973686695099</t>
+    <t xml:space="preserve">1.26814723014832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26908588409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29192674160004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28003704547882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28191447257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2897367477417</t>
   </si>
   <si>
     <t xml:space="preserve">1.24830996990204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22815954685211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22753393650055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24705827236176</t>
+    <t xml:space="preserve">1.2281596660614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22753381729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24705839157104</t>
   </si>
   <si>
     <t xml:space="preserve">1.24180173873901</t>
@@ -1964,55 +1964,55 @@
     <t xml:space="preserve">1.24155139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28097558021545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29223966598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28629469871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28692054748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27659511566162</t>
+    <t xml:space="preserve">1.28097569942474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2922397851944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28629493713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28692066669464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27659523487091</t>
   </si>
   <si>
     <t xml:space="preserve">1.2778468132019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30444264411926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.299436211586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33385407924652</t>
+    <t xml:space="preserve">1.30444252490997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29943633079529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33385443687439</t>
   </si>
   <si>
     <t xml:space="preserve">1.35043752193451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35513067245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35262787342072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36545622348785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33510601520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32603204250336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33760905265808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33667027950287</t>
+    <t xml:space="preserve">1.35513079166412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35262763500214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36545610427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33510589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32603192329407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33760893344879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33667016029358</t>
   </si>
   <si>
     <t xml:space="preserve">1.3482471704483</t>
@@ -2021,22 +2021,22 @@
     <t xml:space="preserve">1.35794687271118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37609457969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39737117290497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39924871921539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39549374580383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38610684871674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34949886798859</t>
+    <t xml:space="preserve">1.37609446048737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39737105369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3992486000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39549386501312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38610696792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34949898719788</t>
   </si>
   <si>
     <t xml:space="preserve">1.34480547904968</t>
@@ -2045,34 +2045,34 @@
     <t xml:space="preserve">1.34136378765106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3516891002655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3541921377182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38016200065613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37546873092651</t>
+    <t xml:space="preserve">1.35168921947479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35419225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38016188144684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3754688501358</t>
   </si>
   <si>
     <t xml:space="preserve">1.38767147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39799702167511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39956152439117</t>
+    <t xml:space="preserve">1.39799678325653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39956140518188</t>
   </si>
   <si>
     <t xml:space="preserve">1.39017462730408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3983097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43992435932159</t>
+    <t xml:space="preserve">1.39830958843231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43992459774017</t>
   </si>
   <si>
     <t xml:space="preserve">1.45337855815887</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">1.46558153629303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45963644981384</t>
+    <t xml:space="preserve">1.45963656902313</t>
   </si>
   <si>
     <t xml:space="preserve">1.45244014263153</t>
@@ -2096,43 +2096,43 @@
     <t xml:space="preserve">1.42991185188293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45932364463806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46245265007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45619451999664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45306587219238</t>
+    <t xml:space="preserve">1.45932352542877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46245229244232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45619475841522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45306575298309</t>
   </si>
   <si>
     <t xml:space="preserve">1.4327278137207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40300309658051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38673281669617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35450506210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35137617588043</t>
+    <t xml:space="preserve">1.40300321578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38673293590546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35450482368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35137593746185</t>
   </si>
   <si>
     <t xml:space="preserve">1.3254063129425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34543120861053</t>
+    <t xml:space="preserve">1.34543132781982</t>
   </si>
   <si>
     <t xml:space="preserve">1.36639499664307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35825979709625</t>
+    <t xml:space="preserve">1.35825967788696</t>
   </si>
   <si>
     <t xml:space="preserve">1.36135697364807</t>
@@ -2141,31 +2141,31 @@
     <t xml:space="preserve">1.36066865921021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33630466461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30973827838898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32061243057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31331717967987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29872632026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28413546085358</t>
+    <t xml:space="preserve">1.33630442619324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30973815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32061266899109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31331706047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29872620105743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28413534164429</t>
   </si>
   <si>
     <t xml:space="preserve">1.28372240066528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26211142539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25674319267273</t>
+    <t xml:space="preserve">1.26211130619049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25674307346344</t>
   </si>
   <si>
     <t xml:space="preserve">1.28441059589386</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">1.27326107025146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25701832771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26142311096191</t>
+    <t xml:space="preserve">1.2570184469223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2614232301712</t>
   </si>
   <si>
     <t xml:space="preserve">1.27037048339844</t>
@@ -2186,37 +2186,37 @@
     <t xml:space="preserve">1.27133393287659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25811946392059</t>
+    <t xml:space="preserve">1.25811958312988</t>
   </si>
   <si>
     <t xml:space="preserve">1.26775503158569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2645890712738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26018416881561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2893660068512</t>
+    <t xml:space="preserve">1.26458919048309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26018440723419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28936612606049</t>
   </si>
   <si>
     <t xml:space="preserve">1.312628865242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30134165287018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29046738147736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29032969474792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28592467308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29239451885223</t>
+    <t xml:space="preserve">1.30134153366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29046714305878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29032981395721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28592479228973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29239428043365</t>
   </si>
   <si>
     <t xml:space="preserve">1.29294490814209</t>
@@ -2225,22 +2225,22 @@
     <t xml:space="preserve">1.29528510570526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2853741645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29734981060028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36328387260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39439296722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852249622345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38854265213013</t>
+    <t xml:space="preserve">1.28537428379059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29734969139099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36328423023224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39439284801483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39852237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38854277133942</t>
   </si>
   <si>
     <t xml:space="preserve">1.38097214698792</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">1.39783418178558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41469609737396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41159904003143</t>
+    <t xml:space="preserve">1.41469645500183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41159915924072</t>
   </si>
   <si>
     <t xml:space="preserve">1.40987849235535</t>
@@ -2261,43 +2261,43 @@
     <t xml:space="preserve">1.41916978359222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40609323978424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41091072559357</t>
+    <t xml:space="preserve">1.40609312057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41091096401215</t>
   </si>
   <si>
     <t xml:space="preserve">1.38200438022614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3844131231308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40058696269989</t>
+    <t xml:space="preserve">1.38441324234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40058708190918</t>
   </si>
   <si>
     <t xml:space="preserve">1.3902633190155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38338100910187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37044167518616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35309791564941</t>
+    <t xml:space="preserve">1.38338088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37044179439545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35309779644012</t>
   </si>
   <si>
     <t xml:space="preserve">1.34924364089966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37649834156036</t>
+    <t xml:space="preserve">1.37649857997894</t>
   </si>
   <si>
     <t xml:space="preserve">1.34387540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35433685779572</t>
+    <t xml:space="preserve">1.35433673858643</t>
   </si>
   <si>
     <t xml:space="preserve">1.33836948871613</t>
@@ -2306,124 +2306,124 @@
     <t xml:space="preserve">1.31455600261688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33892023563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26362538337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29886376857758</t>
+    <t xml:space="preserve">1.33892011642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26362562179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29886400699615</t>
   </si>
   <si>
     <t xml:space="preserve">1.27023267745972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31744658946991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31001341342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32322776317596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33644223213196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30987596511841</t>
+    <t xml:space="preserve">1.3174467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31001353263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32322800159454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33644235134125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30987584590912</t>
   </si>
   <si>
     <t xml:space="preserve">1.33520352840424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34084701538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35488748550415</t>
+    <t xml:space="preserve">1.34084713459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35488736629486</t>
   </si>
   <si>
     <t xml:space="preserve">1.38578963279724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3718181848526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37890732288361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37684261798859</t>
+    <t xml:space="preserve">1.37181830406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37890720367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3768424987793</t>
   </si>
   <si>
     <t xml:space="preserve">1.39542531967163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4150402545929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4226108789444</t>
+    <t xml:space="preserve">1.41504037380219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42261099815369</t>
   </si>
   <si>
     <t xml:space="preserve">1.44635570049286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46149718761444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45082926750183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46080875396729</t>
+    <t xml:space="preserve">1.46149742603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45082938671112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46080887317657</t>
   </si>
   <si>
     <t xml:space="preserve">1.50175964832306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47526228427887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46252965927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46321773529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48937118053436</t>
+    <t xml:space="preserve">1.47526216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46252930164337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46321785449982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48937129974365</t>
   </si>
   <si>
     <t xml:space="preserve">1.49074769020081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47319757938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46597063541412</t>
+    <t xml:space="preserve">1.47319746017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46597075462341</t>
   </si>
   <si>
     <t xml:space="preserve">1.46941208839417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47491776943207</t>
+    <t xml:space="preserve">1.47491812705994</t>
   </si>
   <si>
     <t xml:space="preserve">1.48696255683899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49728620052338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48317718505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44119393825531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43912899494171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44222617149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43568789958954</t>
+    <t xml:space="preserve">1.49728608131409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4831770658493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4411940574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43912923336029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44222605228424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43568778038025</t>
   </si>
   <si>
     <t xml:space="preserve">1.44773209095001</t>
@@ -2435,130 +2435,130 @@
     <t xml:space="preserve">1.50451278686523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50038361549377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52103078365326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5406459569931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53582787513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53789269924164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55062544345856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56576704978943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56232559680939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56301391124725</t>
+    <t xml:space="preserve">1.5003833770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52103090286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54064583778381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53582811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53789293766022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55062556266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56576716899872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56232571601868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56301379203796</t>
   </si>
   <si>
     <t xml:space="preserve">1.56404626369476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56817591190338</t>
+    <t xml:space="preserve">1.56817603111267</t>
   </si>
   <si>
     <t xml:space="preserve">1.56370222568512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54752826690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54580783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5643904209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58710253238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61050307750702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60878264904022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62151527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256790161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6222038269043</t>
+    <t xml:space="preserve">1.54752814769745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54580771923065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56439054012299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58710265159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61050283908844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60878252983093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62151503562927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256778240204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62220335006714</t>
   </si>
   <si>
     <t xml:space="preserve">1.63665652275085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61394429206848</t>
+    <t xml:space="preserve">1.61394441127777</t>
   </si>
   <si>
     <t xml:space="preserve">1.60086762905121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60912668704987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61738538742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61566495895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62013876438141</t>
+    <t xml:space="preserve">1.60912656784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61738550662994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61566507816315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62013852596283</t>
   </si>
   <si>
     <t xml:space="preserve">1.61291193962097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61910629272461</t>
+    <t xml:space="preserve">1.61910617351532</t>
   </si>
   <si>
     <t xml:space="preserve">1.61187970638275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60189998149872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58985555171967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58331716060638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54511952400208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57677900791168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57471430301666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59226441383362</t>
+    <t xml:space="preserve">1.60190033912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58985579013824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58331739902496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54511940479279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5767787694931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57471418380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5922646522522</t>
   </si>
   <si>
     <t xml:space="preserve">1.58090841770172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58572614192963</t>
+    <t xml:space="preserve">1.58572626113892</t>
   </si>
   <si>
     <t xml:space="preserve">1.59054398536682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60224425792694</t>
+    <t xml:space="preserve">1.60224413871765</t>
   </si>
   <si>
     <t xml:space="preserve">1.61497676372528</t>
@@ -2573,31 +2573,31 @@
     <t xml:space="preserve">1.63803327083588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65523934364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65214252471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62082695960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61635327339172</t>
+    <t xml:space="preserve">1.6552392244339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65214216709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6208268404007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61635303497314</t>
   </si>
   <si>
     <t xml:space="preserve">1.63872122764587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6170414686203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63390374183655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61119151115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61532068252563</t>
+    <t xml:space="preserve">1.61704123020172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63390362262726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61119139194489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61532092094421</t>
   </si>
   <si>
     <t xml:space="preserve">1.59673798084259</t>
@@ -2609,94 +2609,94 @@
     <t xml:space="preserve">1.60809421539307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59570598602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56920802593231</t>
+    <t xml:space="preserve">1.59570586681366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5692081451416</t>
   </si>
   <si>
     <t xml:space="preserve">1.56094920635223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56783175468445</t>
+    <t xml:space="preserve">1.56783187389374</t>
   </si>
   <si>
     <t xml:space="preserve">1.552001953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58675837516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57712304592133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54546368122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57264947891235</t>
+    <t xml:space="preserve">1.58675873279572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57712316513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54546356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57264935970306</t>
   </si>
   <si>
     <t xml:space="preserve">1.61841797828674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.685866355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70100796222687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70410513877869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69240486621857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70857846736908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72578465938568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72750556468964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74815273284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78944766521454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79185676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75503540039062</t>
+    <t xml:space="preserve">1.68586659431458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70100784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7041050195694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69240474700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70857870578766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72578477859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72750520706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74815309047699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78944802284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79185664653778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75503551959991</t>
   </si>
   <si>
     <t xml:space="preserve">1.73542034626007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63562393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60362040996552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57505834102631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51311576366425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4704442024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45840013027191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46425020694733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40850186347961</t>
+    <t xml:space="preserve">1.63562417030334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60362064838409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57505822181702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51311588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47044432163239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45839989185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46425008773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4085019826889</t>
   </si>
   <si>
     <t xml:space="preserve">1.36080634593964</t>
@@ -2705,40 +2705,40 @@
     <t xml:space="preserve">1.20443606376648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17608034610748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2245329618454</t>
+    <t xml:space="preserve">1.17608022689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22453308105469</t>
   </si>
   <si>
     <t xml:space="preserve">1.00677096843719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06981456279755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965476036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998924791812897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96946781873703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980892837047577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00856041908264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99713534116745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08991146087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11234831809998</t>
+    <t xml:space="preserve">1.06981432437897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965476095676422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998924851417542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96946769952774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980892777442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00856029987335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997135400772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08991158008575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11234819889069</t>
   </si>
   <si>
     <t xml:space="preserve">1.12253451347351</t>
@@ -2747,73 +2747,73 @@
     <t xml:space="preserve">1.07821106910706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01227700710297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02439022064209</t>
+    <t xml:space="preserve">1.01227688789368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02438998222351</t>
   </si>
   <si>
     <t xml:space="preserve">0.987499892711639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989564776420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914820730686188</t>
+    <t xml:space="preserve">0.989564657211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914820909500122</t>
   </si>
   <si>
     <t xml:space="preserve">1.00360488891602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01103806495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997410774230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994520127773285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96781599521637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928035140037537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936156570911407</t>
+    <t xml:space="preserve">1.01103782653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997410893440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99452006816864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967815935611725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928035259246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936156690120697</t>
   </si>
   <si>
     <t xml:space="preserve">0.947168469429016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.951848685741425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908489048480988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921015083789825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952812254428864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924869239330292</t>
+    <t xml:space="preserve">0.95184862613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908488988876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921015202999115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952812314033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924869179725647</t>
   </si>
   <si>
     <t xml:space="preserve">0.960245192050934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996034264564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01888406276703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979378581047058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947030961513519</t>
+    <t xml:space="preserve">0.996034145355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01888418197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979378640651703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947031021118164</t>
   </si>
   <si>
     <t xml:space="preserve">0.998649597167969</t>
@@ -2822,28 +2822,28 @@
     <t xml:space="preserve">0.97745144367218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966577172279358</t>
+    <t xml:space="preserve">0.966577112674713</t>
   </si>
   <si>
     <t xml:space="preserve">0.973184406757355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970018327236176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977864444255829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959144055843353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952261805534363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95239931344986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999475538730621</t>
+    <t xml:space="preserve">0.970018446445465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977864325046539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959144115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952261567115784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952399492263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999475359916687</t>
   </si>
   <si>
     <t xml:space="preserve">0.984746932983398</t>
@@ -2852,16 +2852,16 @@
     <t xml:space="preserve">0.990390598773956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978690385818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994244813919067</t>
+    <t xml:space="preserve">0.978690207004547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994244694709778</t>
   </si>
   <si>
     <t xml:space="preserve">1.0031920671463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0331996679306</t>
+    <t xml:space="preserve">1.03319978713989</t>
   </si>
   <si>
     <t xml:space="preserve">1.05880260467529</t>
@@ -2870,94 +2870,94 @@
     <t xml:space="preserve">1.07270526885986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0684380531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08743381500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11840510368347</t>
+    <t xml:space="preserve">1.06843817234039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08743369579315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1184047460556</t>
   </si>
   <si>
     <t xml:space="preserve">1.15157854557037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16575646400452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2201281785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24118864536285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18378841876984</t>
+    <t xml:space="preserve">1.16575658321381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22012805938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24118852615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18378865718842</t>
   </si>
   <si>
     <t xml:space="preserve">1.17181301116943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11344969272614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11634004116058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11950600147247</t>
+    <t xml:space="preserve">1.11344945430756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11634027957916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11950612068176</t>
   </si>
   <si>
     <t xml:space="preserve">1.16947305202484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17263877391815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16025030612946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15956223011017</t>
+    <t xml:space="preserve">1.17263889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16025054454803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15956211090088</t>
   </si>
   <si>
     <t xml:space="preserve">1.15791046619415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17786967754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14717364311218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14249360561371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17140007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17250144481659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16355407238007</t>
+    <t xml:space="preserve">1.17786955833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14717376232147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.142493724823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17140018939972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1725013256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16355419158936</t>
   </si>
   <si>
     <t xml:space="preserve">1.20636332035065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20223367214203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23348021507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22962605953217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.213383436203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19149696826935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21503508090973</t>
+    <t xml:space="preserve">1.20223355293274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23348033428192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22962594032288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21338331699371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19149708747864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21503531932831</t>
   </si>
   <si>
     <t xml:space="preserve">1.22604703903198</t>
@@ -2972,19 +2972,19 @@
     <t xml:space="preserve">1.26596558094025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26073491573334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27628946304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29721212387085</t>
+    <t xml:space="preserve">1.26073479652405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27628922462463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29721224308014</t>
   </si>
   <si>
     <t xml:space="preserve">1.29129314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27271044254303</t>
+    <t xml:space="preserve">1.27271032333374</t>
   </si>
   <si>
     <t xml:space="preserve">1.24944770336151</t>
@@ -2993,13 +2993,13 @@
     <t xml:space="preserve">1.23981201648712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22935080528259</t>
+    <t xml:space="preserve">1.22935056686401</t>
   </si>
   <si>
     <t xml:space="preserve">1.23155319690704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1941123008728</t>
+    <t xml:space="preserve">1.19411242008209</t>
   </si>
   <si>
     <t xml:space="preserve">1.17497909069061</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">1.23444378376007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26252448558807</t>
+    <t xml:space="preserve">1.26252436637878</t>
   </si>
   <si>
     <t xml:space="preserve">1.24834644794464</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">1.24256503582001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24848389625549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2809693813324</t>
+    <t xml:space="preserve">1.24848401546478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28096950054169</t>
   </si>
   <si>
     <t xml:space="preserve">1.29583561420441</t>
@@ -3032,58 +3032,58 @@
     <t xml:space="preserve">1.28399765491486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27436244487762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25564193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24903464317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26981985569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24999821186066</t>
+    <t xml:space="preserve">1.27436220645905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25564181804657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24903476238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26981973648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24999809265137</t>
   </si>
   <si>
     <t xml:space="preserve">1.24683225154877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26582789421082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26224887371063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26816809177399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24146378040314</t>
+    <t xml:space="preserve">1.2658280134201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26224911212921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26816785335541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24146401882172</t>
   </si>
   <si>
     <t xml:space="preserve">1.25605475902557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24242746829987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24008727073669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22425758838654</t>
+    <t xml:space="preserve">1.24242734909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24008750915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22425770759583</t>
   </si>
   <si>
     <t xml:space="preserve">1.22412002086639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23458158969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21269512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23210382461548</t>
+    <t xml:space="preserve">1.23458123207092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21269524097443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23210370540619</t>
   </si>
   <si>
     <t xml:space="preserve">1.23967456817627</t>
@@ -3095,31 +3095,31 @@
     <t xml:space="preserve">1.21737515926361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21145629882812</t>
+    <t xml:space="preserve">1.21145617961884</t>
   </si>
   <si>
     <t xml:space="preserve">1.19989371299744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18020963668823</t>
+    <t xml:space="preserve">1.18020975589752</t>
   </si>
   <si>
     <t xml:space="preserve">1.1257004737854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12996768951416</t>
+    <t xml:space="preserve">1.12996757030487</t>
   </si>
   <si>
     <t xml:space="preserve">1.10959541797638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10670471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08674550056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11812973022461</t>
+    <t xml:space="preserve">1.10670495033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08674538135529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11812961101532</t>
   </si>
   <si>
     <t xml:space="preserve">1.10587871074677</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">1.10326337814331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09183871746063</t>
+    <t xml:space="preserve">1.09183859825134</t>
   </si>
   <si>
     <t xml:space="preserve">1.09596788883209</t>
@@ -3140,22 +3140,22 @@
     <t xml:space="preserve">1.14827513694763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13478541374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15309274196625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15557026863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14978909492493</t>
+    <t xml:space="preserve">1.13478529453278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15309262275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15557050704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14978921413422</t>
   </si>
   <si>
     <t xml:space="preserve">1.11317431926727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05825197696686</t>
+    <t xml:space="preserve">1.05825185775757</t>
   </si>
   <si>
     <t xml:space="preserve">1.0707780122757</t>
@@ -3164,28 +3164,28 @@
     <t xml:space="preserve">1.07353115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05701315402985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05770146846771</t>
+    <t xml:space="preserve">1.05701303482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05770123004913</t>
   </si>
   <si>
     <t xml:space="preserve">1.07449471950531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05095660686493</t>
+    <t xml:space="preserve">1.05095648765564</t>
   </si>
   <si>
     <t xml:space="preserve">1.02590429782867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97593742609024</t>
+    <t xml:space="preserve">0.97593754529953</t>
   </si>
   <si>
     <t xml:space="preserve">0.962998270988464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977038621902466</t>
+    <t xml:space="preserve">0.977038562297821</t>
   </si>
   <si>
     <t xml:space="preserve">1.02026057243347</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">1.11276137828827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21531045436859</t>
+    <t xml:space="preserve">1.2153103351593</t>
   </si>
   <si>
     <t xml:space="preserve">1.26926910877228</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">1.24022507667542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25109934806824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26637864112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2761515378952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28730118274689</t>
+    <t xml:space="preserve">1.25109922885895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26637852191925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27615177631378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28730130195618</t>
   </si>
   <si>
     <t xml:space="preserve">1.28248345851898</t>
@@ -3236,112 +3236,112 @@
     <t xml:space="preserve">1.33671748638153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32777047157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32515513896942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35653913021088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36700046062469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37002885341644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35667669773102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35516273975372</t>
+    <t xml:space="preserve">1.3277702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32515490055084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35653924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36700034141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37002873420715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3566769361496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516262054443</t>
   </si>
   <si>
     <t xml:space="preserve">1.35998046398163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34951889514923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231282234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3346529006958</t>
+    <t xml:space="preserve">1.34951901435852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231294155121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33465266227722</t>
   </si>
   <si>
     <t xml:space="preserve">1.35929214954376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33726811408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3382316827774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33189988136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29473435878754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3166207075119</t>
+    <t xml:space="preserve">1.33726823329926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33823180198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3319000005722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29473423957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31662082672119</t>
   </si>
   <si>
     <t xml:space="preserve">1.32309031486511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32130074501038</t>
+    <t xml:space="preserve">1.32130086421967</t>
   </si>
   <si>
     <t xml:space="preserve">1.31634545326233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31125235557556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29693675041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35447442531586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34552717208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33713066577911</t>
+    <t xml:space="preserve">1.31125223636627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29693698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35447454452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34552729129791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33713054656982</t>
   </si>
   <si>
     <t xml:space="preserve">1.33396470546722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31799721717834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30904996395111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31951129436493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31483125686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32584309577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29679918289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25481605529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26610314846039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24407935142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26197385787964</t>
+    <t xml:space="preserve">1.31799733638763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3090500831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31951117515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31483137607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.325843334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29679906368256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25481581687927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26610326766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24407923221588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26197373867035</t>
   </si>
   <si>
     <t xml:space="preserve">1.25399005413055</t>
@@ -3350,16 +3350,16 @@
     <t xml:space="preserve">1.28771436214447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34291160106659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38234865665436</t>
+    <t xml:space="preserve">1.34291183948517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38234841823578</t>
   </si>
   <si>
     <t xml:space="preserve">1.41848182678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43844079971313</t>
+    <t xml:space="preserve">1.43844068050385</t>
   </si>
   <si>
     <t xml:space="preserve">1.43637597560883</t>
@@ -3371,58 +3371,58 @@
     <t xml:space="preserve">1.43603193759918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44257009029388</t>
+    <t xml:space="preserve">1.44257020950317</t>
   </si>
   <si>
     <t xml:space="preserve">1.4573677778244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45392644405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45117342472076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44532334804535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45358240604401</t>
+    <t xml:space="preserve">1.45392656326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45117354393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44532322883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45358228683472</t>
   </si>
   <si>
     <t xml:space="preserve">1.481112241745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46872389316559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48661828041077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48283278942108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51621317863464</t>
+    <t xml:space="preserve">1.4687237739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48661851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48283302783966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51621305942535</t>
   </si>
   <si>
     <t xml:space="preserve">1.50864219665527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51036274433136</t>
+    <t xml:space="preserve">1.51036286354065</t>
   </si>
   <si>
     <t xml:space="preserve">1.56198167800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56507873535156</t>
+    <t xml:space="preserve">1.56507837772369</t>
   </si>
   <si>
     <t xml:space="preserve">1.55991697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56955230236053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55888450145721</t>
+    <t xml:space="preserve">1.56955206394196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5588846206665</t>
   </si>
   <si>
     <t xml:space="preserve">1.5788437128067</t>
@@ -3431,199 +3431,199 @@
     <t xml:space="preserve">1.59329688549042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61669731140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59260880947113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58194100856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57540249824524</t>
+    <t xml:space="preserve">1.61669743061066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59260869026184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58194077014923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57540225982666</t>
   </si>
   <si>
     <t xml:space="preserve">1.57987606525421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57918775081635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58125245571136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57333755493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59914720058441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59019982814789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59536182880402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58503794670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55750811100006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5509694814682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55578744411469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56989622116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52791333198547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53204274177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52860140800476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58056437969208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59501755237579</t>
+    <t xml:space="preserve">1.57918787002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58125233650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57333767414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59914684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5901997089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59536170959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58503782749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55750787258148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55096936225891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55578720569611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56989657878876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52791309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53204298019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52860164642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58056426048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5950174331665</t>
   </si>
   <si>
     <t xml:space="preserve">1.59742653369904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60637378692627</t>
+    <t xml:space="preserve">1.60637390613556</t>
   </si>
   <si>
     <t xml:space="preserve">1.58847916126251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62358009815216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62564480304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64457130432129</t>
+    <t xml:space="preserve">1.623579621315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6256445646286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64457142353058</t>
   </si>
   <si>
     <t xml:space="preserve">1.63837730884552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63975346088409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63287115097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64319479465485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65868055820465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65351855754852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65116286277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6497654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63928413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67282462120056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68330585956573</t>
+    <t xml:space="preserve">1.63975369930267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63287091255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64319503307343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65868067741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65351891517639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65116274356842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64976537227631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63928389549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67282438278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68330562114716</t>
   </si>
   <si>
     <t xml:space="preserve">1.68854653835297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70881044864655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72767674922943</t>
+    <t xml:space="preserve">1.70881009101868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72767686843872</t>
   </si>
   <si>
     <t xml:space="preserve">1.73012232780457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73326683044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73676085472107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71894252300262</t>
+    <t xml:space="preserve">1.73326671123505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73676073551178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71894216537476</t>
   </si>
   <si>
     <t xml:space="preserve">1.71440029144287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7042680978775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69448578357697</t>
+    <t xml:space="preserve">1.70426833629608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69448566436768</t>
   </si>
   <si>
     <t xml:space="preserve">1.71195483207703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71265351772308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68749845027924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63788664340973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65360856056213</t>
+    <t xml:space="preserve">1.71265339851379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68749821186066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63788652420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65360844135284</t>
   </si>
   <si>
     <t xml:space="preserve">1.63648903369904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61832118034363</t>
+    <t xml:space="preserve">1.61832141876221</t>
   </si>
   <si>
     <t xml:space="preserve">1.65186166763306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66688477993011</t>
+    <t xml:space="preserve">1.66688501834869</t>
   </si>
   <si>
     <t xml:space="preserve">1.62775456905365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64662086963654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64592218399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63229632377625</t>
+    <t xml:space="preserve">1.64662110805511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64592230319977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63229644298553</t>
   </si>
   <si>
     <t xml:space="preserve">1.65535533428192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6214656829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60958695411682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56242084503174</t>
+    <t xml:space="preserve">1.62146556377411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60958659648895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56242072582245</t>
   </si>
   <si>
     <t xml:space="preserve">1.5959609746933</t>
@@ -3635,109 +3635,109 @@
     <t xml:space="preserve">1.58617842197418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59631037712097</t>
+    <t xml:space="preserve">1.59631013870239</t>
   </si>
   <si>
     <t xml:space="preserve">1.57639598846436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55962598323822</t>
+    <t xml:space="preserve">1.55962562561035</t>
   </si>
   <si>
     <t xml:space="preserve">1.49359321594238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52259171009064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56277012825012</t>
+    <t xml:space="preserve">1.52259159088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56277000904083</t>
   </si>
   <si>
     <t xml:space="preserve">1.57255268096924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59665977954865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63334465026855</t>
+    <t xml:space="preserve">1.59665989875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63334453105927</t>
   </si>
   <si>
     <t xml:space="preserve">1.61657440662384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62111616134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63998258113861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62915205955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6172730922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6256582736969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63509130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63858532905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67596852779388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68016111850739</t>
+    <t xml:space="preserve">1.62111628055573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63998281955719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62915194034576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727321147919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62565791606903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63509118556976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63858544826508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67596876621246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68016123771667</t>
   </si>
   <si>
     <t xml:space="preserve">1.6826069355011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71125590801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71055722236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69204008579254</t>
+    <t xml:space="preserve">1.7112557888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71055710315704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69203996658325</t>
   </si>
   <si>
     <t xml:space="preserve">1.66898107528687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68225741386414</t>
+    <t xml:space="preserve">1.68225765228271</t>
   </si>
   <si>
     <t xml:space="preserve">1.66723418235779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66304183006287</t>
+    <t xml:space="preserve">1.66304194927216</t>
   </si>
   <si>
     <t xml:space="preserve">1.67002940177917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66164433956146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67527008056641</t>
+    <t xml:space="preserve">1.66164422035217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67526996135712</t>
   </si>
   <si>
     <t xml:space="preserve">1.68365502357483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66828227043152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67911338806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66548728942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64836764335632</t>
+    <t xml:space="preserve">1.6682825088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67911326885223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.665487408638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64836776256561</t>
   </si>
   <si>
     <t xml:space="preserve">1.657102227211</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">1.63963341712952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66758370399475</t>
+    <t xml:space="preserve">1.66758346557617</t>
   </si>
   <si>
     <t xml:space="preserve">1.66094553470612</t>
@@ -3755,121 +3755,121 @@
     <t xml:space="preserve">1.65884923934937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60853862762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62251365184784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65815007686615</t>
+    <t xml:space="preserve">1.6085387468338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62251400947571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65815043449402</t>
   </si>
   <si>
     <t xml:space="preserve">1.69623291492462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69413614273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732722759247</t>
+    <t xml:space="preserve">1.69413673877716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732710838318</t>
   </si>
   <si>
     <t xml:space="preserve">1.69763028621674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71824359893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74898886680603</t>
+    <t xml:space="preserve">1.7182434797287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74898874759674</t>
   </si>
   <si>
     <t xml:space="preserve">1.72942352294922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7538800239563</t>
+    <t xml:space="preserve">1.75387990474701</t>
   </si>
   <si>
     <t xml:space="preserve">1.75912082195282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7493382692337</t>
+    <t xml:space="preserve">1.74933815002441</t>
   </si>
   <si>
     <t xml:space="preserve">1.75562691688538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74339878559113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76331329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7992992401123</t>
+    <t xml:space="preserve">1.74339866638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76331317424774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79929947853088</t>
   </si>
   <si>
     <t xml:space="preserve">1.81100177764893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7815637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79319381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77720236778259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78192722797394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79028594493866</t>
+    <t xml:space="preserve">1.78156363964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79319369792938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77720248699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78192710876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79028630256653</t>
   </si>
   <si>
     <t xml:space="preserve">1.80373311042786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78301739692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7721141576767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78628861904144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81354606151581</t>
+    <t xml:space="preserve">1.78301751613617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77211427688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78628814220428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81354594230652</t>
   </si>
   <si>
     <t xml:space="preserve">1.82590281963348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81863403320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78556156158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80518686771393</t>
+    <t xml:space="preserve">1.8186342716217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78556132316589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80518710613251</t>
   </si>
   <si>
     <t xml:space="preserve">1.81172895431519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79573750495911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80046224594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79682803153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7964643239975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80991184711456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80446028709412</t>
+    <t xml:space="preserve">1.79573774337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80046236515045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79682779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79646456241608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80991160869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80446016788483</t>
   </si>
   <si>
     <t xml:space="preserve">1.80409669876099</t>
@@ -3884,52 +3884,52 @@
     <t xml:space="preserve">1.72544276714325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72581744194031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71494936943054</t>
+    <t xml:space="preserve">1.72581732273102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71494925022125</t>
   </si>
   <si>
     <t xml:space="preserve">1.61638462543488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60626566410065</t>
+    <t xml:space="preserve">1.60626590251923</t>
   </si>
   <si>
     <t xml:space="preserve">1.58565330505371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62537896633148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60963869094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60888934135437</t>
+    <t xml:space="preserve">1.62537908554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60963881015778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60888922214508</t>
   </si>
   <si>
     <t xml:space="preserve">1.6587336063385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.692462682724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67222535610199</t>
+    <t xml:space="preserve">1.69246304035187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67222511768341</t>
   </si>
   <si>
     <t xml:space="preserve">1.6677280664444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66060769557953</t>
+    <t xml:space="preserve">1.66060757637024</t>
   </si>
   <si>
     <t xml:space="preserve">1.65273725986481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66735339164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65011382102966</t>
+    <t xml:space="preserve">1.66735327243805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65011394023895</t>
   </si>
   <si>
     <t xml:space="preserve">1.68084514141083</t>
@@ -3938,52 +3938,52 @@
     <t xml:space="preserve">1.65311193466187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63549792766571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67334961891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67185068130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.687215924263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69583582878113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71157622337341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70670425891876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70445549488068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75767290592194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79440081119537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81238949298859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82363283634186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8374992609024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84611880779266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86036026477814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90795576572418</t>
+    <t xml:space="preserve">1.63549757003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67334973812103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67185056209564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68721604347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69583594799042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7115763425827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70670413970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70445537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75767314434052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7944004535675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81238913536072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82363259792328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83749902248383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84611904621124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86036014556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90795612335205</t>
   </si>
   <si>
     <t xml:space="preserve">1.91919887065887</t>
@@ -3992,112 +3992,112 @@
     <t xml:space="preserve">1.92032337188721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93194139003754</t>
+    <t xml:space="preserve">1.93194127082825</t>
   </si>
   <si>
     <t xml:space="preserve">1.9300674200058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89933633804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91245317459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91282773017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8487423658371</t>
+    <t xml:space="preserve">1.89933598041534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91245329380035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91282796859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84874248504639</t>
   </si>
   <si>
     <t xml:space="preserve">1.86560714244843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92219698429108</t>
+    <t xml:space="preserve">1.92219722270966</t>
   </si>
   <si>
     <t xml:space="preserve">1.95817518234253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9465571641922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96342182159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00127387046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02151131629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04474687576294</t>
+    <t xml:space="preserve">1.94655704498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96342170238495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00127410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02151155471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04474711418152</t>
   </si>
   <si>
     <t xml:space="preserve">1.99902510643005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03500294685364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07585310935974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13881421089172</t>
+    <t xml:space="preserve">2.03500270843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07585287094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13881468772888</t>
   </si>
   <si>
     <t xml:space="preserve">2.18865895271301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07435393333435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13843965530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09196829795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05299234390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04024958610535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00427198410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99377822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96417164802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80789244174957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8569872379303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71907150745392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5864030122757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60851442813873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56204307079315</t>
+    <t xml:space="preserve">2.07435417175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13843941688538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09196805953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05299210548401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04024982452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00427174568176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99377846717834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96417129039764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80789220333099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85698699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71907162666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58640265464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60851430892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56204283237457</t>
   </si>
   <si>
     <t xml:space="preserve">1.42127919197083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38155353069305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39834308624268</t>
+    <t xml:space="preserve">1.38155341148376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39834332466125</t>
   </si>
   <si>
     <t xml:space="preserve">1.55342304706573</t>
@@ -4106,37 +4106,37 @@
     <t xml:space="preserve">1.43522047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43866848945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49158596992493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50507760047913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61001360416412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55304837226868</t>
+    <t xml:space="preserve">1.43866837024689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49158608913422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50507783889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61001336574554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55304849147797</t>
   </si>
   <si>
     <t xml:space="preserve">1.56354188919067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54892587661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57403540611267</t>
+    <t xml:space="preserve">1.54892575740814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57403552532196</t>
   </si>
   <si>
     <t xml:space="preserve">1.53505957126617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52231705188751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52381634712219</t>
+    <t xml:space="preserve">1.52231729030609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5238162279129</t>
   </si>
   <si>
     <t xml:space="preserve">1.53243613243103</t>
@@ -4160,25 +4160,25 @@
     <t xml:space="preserve">1.53056216239929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48573970794678</t>
+    <t xml:space="preserve">1.48573982715607</t>
   </si>
   <si>
     <t xml:space="preserve">1.46280360221863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48558986186981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48469018936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4550085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45725703239441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47734463214874</t>
+    <t xml:space="preserve">1.48558962345123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48469054698944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45500838756561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4572571516037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47734475135803</t>
   </si>
   <si>
     <t xml:space="preserve">1.47884392738342</t>
@@ -4187,22 +4187,22 @@
     <t xml:space="preserve">1.51444697380066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5178200006485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48618924617767</t>
+    <t xml:space="preserve">1.51782011985779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48618936538696</t>
   </si>
   <si>
     <t xml:space="preserve">1.46055507659912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43761920928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4397177696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44361543655396</t>
+    <t xml:space="preserve">1.43761909008026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43971788883209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44361555576324</t>
   </si>
   <si>
     <t xml:space="preserve">1.46520221233368</t>
@@ -4217,13 +4217,13 @@
     <t xml:space="preserve">1.44301581382751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44256627559662</t>
+    <t xml:space="preserve">1.44256603717804</t>
   </si>
   <si>
     <t xml:space="preserve">1.40913665294647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3716596364975</t>
+    <t xml:space="preserve">1.37165951728821</t>
   </si>
   <si>
     <t xml:space="preserve">1.39534509181976</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">1.45410907268524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47074890136719</t>
+    <t xml:space="preserve">1.47074866294861</t>
   </si>
   <si>
     <t xml:space="preserve">1.47839403152466</t>
@@ -4253,10 +4253,10 @@
     <t xml:space="preserve">1.54183983802795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54496216773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58695840835571</t>
+    <t xml:space="preserve">1.54496228694916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.586958527565</t>
   </si>
   <si>
     <t xml:space="preserve">1.60139966011047</t>
@@ -4268,43 +4268,43 @@
     <t xml:space="preserve">1.6076443195343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58500707149506</t>
+    <t xml:space="preserve">1.58500683307648</t>
   </si>
   <si>
     <t xml:space="preserve">1.56119871139526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54012262821198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59047114849091</t>
+    <t xml:space="preserve">1.54012250900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59047102928162</t>
   </si>
   <si>
     <t xml:space="preserve">1.5631502866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5533926486969</t>
+    <t xml:space="preserve">1.55339276790619</t>
   </si>
   <si>
     <t xml:space="preserve">1.53528273105621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42193984985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3730742931366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38166093826294</t>
+    <t xml:space="preserve">1.42193973064423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37307417392731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38166081905365</t>
   </si>
   <si>
     <t xml:space="preserve">1.44520163536072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39961457252502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40788900852203</t>
+    <t xml:space="preserve">1.39961469173431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40788912773132</t>
   </si>
   <si>
     <t xml:space="preserve">1.46175038814545</t>
@@ -4316,10 +4316,10 @@
     <t xml:space="preserve">1.46799516677856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43630278110504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46924412250519</t>
+    <t xml:space="preserve">1.43630290031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46924424171448</t>
   </si>
   <si>
     <t xml:space="preserve">1.47798681259155</t>
@@ -4328,13 +4328,13 @@
     <t xml:space="preserve">1.48204600811005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46440434455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38946676254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37978744506836</t>
+    <t xml:space="preserve">1.46440446376801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38946688175201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37978732585907</t>
   </si>
   <si>
     <t xml:space="preserve">1.34669017791748</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">1.30469357967377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31000185012817</t>
+    <t xml:space="preserve">1.31000173091888</t>
   </si>
   <si>
     <t xml:space="preserve">1.36230206489563</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">1.37588429450989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35199809074402</t>
+    <t xml:space="preserve">1.35199820995331</t>
   </si>
   <si>
     <t xml:space="preserve">1.33295154571533</t>
@@ -4361,40 +4361,40 @@
     <t xml:space="preserve">1.32764339447021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25411093235016</t>
+    <t xml:space="preserve">1.25411105155945</t>
   </si>
   <si>
     <t xml:space="preserve">1.27393805980682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30672347545624</t>
+    <t xml:space="preserve">1.30672335624695</t>
   </si>
   <si>
     <t xml:space="preserve">1.38369047641754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33513724803925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2981368303299</t>
+    <t xml:space="preserve">1.33513700962067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29813671112061</t>
   </si>
   <si>
     <t xml:space="preserve">1.29579484462738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31765174865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29329717159271</t>
+    <t xml:space="preserve">1.31765162944794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29329693317413</t>
   </si>
   <si>
     <t xml:space="preserve">1.30922114849091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3315464258194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34934413433075</t>
+    <t xml:space="preserve">1.33154654502869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34934401512146</t>
   </si>
   <si>
     <t xml:space="preserve">1.36542439460754</t>
@@ -4406,22 +4406,22 @@
     <t xml:space="preserve">1.38462710380554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39180874824524</t>
+    <t xml:space="preserve">1.39180862903595</t>
   </si>
   <si>
     <t xml:space="preserve">1.41600728034973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41850507259369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4175683259964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43052625656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44707524776459</t>
+    <t xml:space="preserve">1.4185049533844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41756844520569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43052649497986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4470751285553</t>
   </si>
   <si>
     <t xml:space="preserve">1.44785559177399</t>
@@ -4430,13 +4430,13 @@
     <t xml:space="preserve">1.42740404605865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42615497112274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38415884971619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34138178825378</t>
+    <t xml:space="preserve">1.42615509033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3841587305069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34138190746307</t>
   </si>
   <si>
     <t xml:space="preserve">1.36573672294617</t>
@@ -4445,67 +4445,67 @@
     <t xml:space="preserve">1.37666499614716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3569940328598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31530976295471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32811188697815</t>
+    <t xml:space="preserve">1.35699391365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.315309882164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32811176776886</t>
   </si>
   <si>
     <t xml:space="preserve">1.34996855258942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34497261047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32217919826508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35683798789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32467710971832</t>
+    <t xml:space="preserve">1.34497272968292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32217907905579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35683763027191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32467699050903</t>
   </si>
   <si>
     <t xml:space="preserve">1.32998514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32701897621155</t>
+    <t xml:space="preserve">1.32701885700226</t>
   </si>
   <si>
     <t xml:space="preserve">1.35855507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43099462985992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48001635074615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46846354007721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48329496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49875068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49484765529633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49516010284424</t>
+    <t xml:space="preserve">1.43099474906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48001646995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46846342086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48329484462738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49875056743622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49484777450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49515998363495</t>
   </si>
   <si>
     <t xml:space="preserve">1.44348430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43364882469177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44566988945007</t>
+    <t xml:space="preserve">1.43364870548248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44567000865936</t>
   </si>
   <si>
     <t xml:space="preserve">1.37697744369507</t>
@@ -4514,16 +4514,16 @@
     <t xml:space="preserve">1.38041186332703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34825122356415</t>
+    <t xml:space="preserve">1.34825110435486</t>
   </si>
   <si>
     <t xml:space="preserve">1.32592606544495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29189193248749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32920467853546</t>
+    <t xml:space="preserve">1.2918918132782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32920455932617</t>
   </si>
   <si>
     <t xml:space="preserve">1.35355925559998</t>
@@ -4538,85 +4538,85 @@
     <t xml:space="preserve">1.33654236793518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33139026165009</t>
+    <t xml:space="preserve">1.3313901424408</t>
   </si>
   <si>
     <t xml:space="preserve">1.3234281539917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30781602859497</t>
+    <t xml:space="preserve">1.30781614780426</t>
   </si>
   <si>
     <t xml:space="preserve">1.33201479911804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33669829368591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36058473587036</t>
+    <t xml:space="preserve">1.33669817447662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36058461666107</t>
   </si>
   <si>
     <t xml:space="preserve">1.40726447105408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39852178096771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42771625518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42662334442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44863629341125</t>
+    <t xml:space="preserve">1.39852166175842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4277161359787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42662346363068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44863641262054</t>
   </si>
   <si>
     <t xml:space="preserve">1.45550549030304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45644211769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48766624927521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48719799518585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5057760477066</t>
+    <t xml:space="preserve">1.45644235610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4876663684845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48719787597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50577628612518</t>
   </si>
   <si>
     <t xml:space="preserve">1.51842188835144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51810956001282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53746855258942</t>
+    <t xml:space="preserve">1.5181097984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53746843338013</t>
   </si>
   <si>
     <t xml:space="preserve">1.61193764209747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6618959903717</t>
+    <t xml:space="preserve">1.66189587116241</t>
   </si>
   <si>
     <t xml:space="preserve">1.67672741413116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68141102790833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6993647813797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68648481369019</t>
+    <t xml:space="preserve">1.68141114711761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69936490058899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68648505210876</t>
   </si>
   <si>
     <t xml:space="preserve">1.70678055286407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70951271057129</t>
+    <t xml:space="preserve">1.709512591362</t>
   </si>
   <si>
     <t xml:space="preserve">1.70990288257599</t>
@@ -4628,13 +4628,13 @@
     <t xml:space="preserve">1.73019850254059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72882568836212</t>
+    <t xml:space="preserve">1.7288259267807</t>
   </si>
   <si>
     <t xml:space="preserve">1.74457168579102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73165190219879</t>
+    <t xml:space="preserve">1.73165214061737</t>
   </si>
   <si>
     <t xml:space="preserve">1.74416792392731</t>
@@ -4643,25 +4643,25 @@
     <t xml:space="preserve">1.74295675754547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70863854885101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72357726097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71348345279694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68320298194885</t>
+    <t xml:space="preserve">1.70863842964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72357702255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71348333358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68320286273956</t>
   </si>
   <si>
     <t xml:space="preserve">1.69289255142212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67835795879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66866815090179</t>
+    <t xml:space="preserve">1.67835807800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66866827011108</t>
   </si>
   <si>
     <t xml:space="preserve">1.66463077068329</t>
@@ -4670,67 +4670,67 @@
     <t xml:space="preserve">1.66140067577362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6690719127655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67028319835663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69652652740479</t>
+    <t xml:space="preserve">1.66907179355621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67028307914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6965264081955</t>
   </si>
   <si>
     <t xml:space="preserve">1.68562543392181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6104484796524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66180455684662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64282858371735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67593562602997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69612276554108</t>
+    <t xml:space="preserve">1.61044836044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66180443763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64282846450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67593550682068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69612264633179</t>
   </si>
   <si>
     <t xml:space="preserve">1.68279922008514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68966269493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6811842918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67997288703918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70137143135071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67795407772064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71429085731506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75426161289215</t>
+    <t xml:space="preserve">1.68966281414032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68118417263031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67997300624847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70137131214142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67795419692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71429097652435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75426149368286</t>
   </si>
   <si>
     <t xml:space="preserve">1.799480676651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78857982158661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8035181760788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81684160232544</t>
+    <t xml:space="preserve">1.78857946395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80351805686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81684148311615</t>
   </si>
   <si>
     <t xml:space="preserve">1.82451272010803</t>
@@ -4739,13 +4739,13 @@
     <t xml:space="preserve">1.84429597854614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8475261926651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84510385990143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82572388648987</t>
+    <t xml:space="preserve">1.84752643108368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84510374069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82572376728058</t>
   </si>
   <si>
     <t xml:space="preserve">1.79503965377808</t>
@@ -4754,31 +4754,31 @@
     <t xml:space="preserve">1.76072144508362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80836319923401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84550726413727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317850112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89153409004211</t>
+    <t xml:space="preserve">1.80836308002472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84550738334656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85317873954773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89153397083282</t>
   </si>
   <si>
     <t xml:space="preserve">1.89839768409729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89274537563324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94603955745697</t>
+    <t xml:space="preserve">1.89274525642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94603931903839</t>
   </si>
   <si>
     <t xml:space="preserve">1.98076128959656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98237586021423</t>
+    <t xml:space="preserve">1.9823762178421</t>
   </si>
   <si>
     <t xml:space="preserve">1.92423701286316</t>
@@ -4787,22 +4787,22 @@
     <t xml:space="preserve">1.97591614723206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99327719211578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99368095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02194285392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00014090538025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01790547370911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0207314491272</t>
+    <t xml:space="preserve">1.99327707290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99368119239807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02194309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00014066696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01790571212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02073168754578</t>
   </si>
   <si>
     <t xml:space="preserve">2.01467537879944</t>
@@ -4811,25 +4811,25 @@
     <t xml:space="preserve">2.05989480018616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07079577445984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06231713294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06150984764099</t>
+    <t xml:space="preserve">2.07079601287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06231689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06150960922241</t>
   </si>
   <si>
     <t xml:space="preserve">1.99973714351654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0300178527832</t>
+    <t xml:space="preserve">2.03001761436462</t>
   </si>
   <si>
     <t xml:space="preserve">2.04536008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06837320327759</t>
+    <t xml:space="preserve">2.06837344169617</t>
   </si>
   <si>
     <t xml:space="preserve">2.0485897064209</t>
@@ -4838,22 +4838,22 @@
     <t xml:space="preserve">2.05262732505798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07887077331543</t>
+    <t xml:space="preserve">2.07887053489685</t>
   </si>
   <si>
     <t xml:space="preserve">2.09340524673462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07119965553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0772557258606</t>
+    <t xml:space="preserve">2.07119941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07725548744202</t>
   </si>
   <si>
     <t xml:space="preserve">2.04414892196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00417828559875</t>
+    <t xml:space="preserve">2.00417852401733</t>
   </si>
   <si>
     <t xml:space="preserve">1.88184428215027</t>
@@ -4862,28 +4862,28 @@
     <t xml:space="preserve">1.94482803344727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81159293651581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81522655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77081489562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83702874183655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90162765979767</t>
+    <t xml:space="preserve">1.81159317493439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8152266740799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77081525325775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83702898025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90162777900696</t>
   </si>
   <si>
     <t xml:space="preserve">1.89193761348724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87255799770355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8273389339447</t>
+    <t xml:space="preserve">1.87255811691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82733905315399</t>
   </si>
   <si>
     <t xml:space="preserve">1.83420264720917</t>
@@ -4892,10 +4892,10 @@
     <t xml:space="preserve">1.85196721553802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87982559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90970242023468</t>
+    <t xml:space="preserve">1.87982547283173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90970253944397</t>
   </si>
   <si>
     <t xml:space="preserve">1.91172122955322</t>
@@ -4910,10 +4910,10 @@
     <t xml:space="preserve">1.91939234733582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93433082103729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92827463150024</t>
+    <t xml:space="preserve">1.934330701828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92827451229095</t>
   </si>
   <si>
     <t xml:space="preserve">1.97147512435913</t>
@@ -4922,85 +4922,85 @@
     <t xml:space="preserve">2.00094819068909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01750183105469</t>
+    <t xml:space="preserve">2.01750159263611</t>
   </si>
   <si>
     <t xml:space="preserve">2.01023435592651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00619697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02436518669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98722124099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9654186964035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98479843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92544853687286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88022947311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91293215751648</t>
+    <t xml:space="preserve">2.00619673728943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02436542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98722064495087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96541893482208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98479855060577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92544829845428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88022911548615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91293251514435</t>
   </si>
   <si>
     <t xml:space="preserve">1.89395654201508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96380388736725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883593082428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98358738422394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9504805803299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93917572498322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96057415008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95451772212982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94038724899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92948567867279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9512882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96353387832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96437251567841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88888430595398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88804531097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88301277160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86665725708008</t>
+    <t xml:space="preserve">1.96380400657654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883605003357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98358726501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95048034191132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9391758441925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96057403087616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95451807975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94038689136505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9294855594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95128774642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96353375911713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9643726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88888454437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88804543018341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88301289081573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86665737628937</t>
   </si>
   <si>
     <t xml:space="preserve">1.85365641117096</t>
@@ -5012,16 +5012,16 @@
     <t xml:space="preserve">1.87043154239655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9052402973175</t>
+    <t xml:space="preserve">1.90524005889893</t>
   </si>
   <si>
     <t xml:space="preserve">1.89475572109222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91698265075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9316611289978</t>
+    <t xml:space="preserve">1.91698276996613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93166077136993</t>
   </si>
   <si>
     <t xml:space="preserve">1.94927477836609</t>
@@ -5030,28 +5030,28 @@
     <t xml:space="preserve">1.93711292743683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93417739868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93920993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97108268737793</t>
+    <t xml:space="preserve">1.93417716026306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93920969963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97108221054077</t>
   </si>
   <si>
     <t xml:space="preserve">1.97779285907745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99037396907806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00840735435486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00169730186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01805305480957</t>
+    <t xml:space="preserve">1.99037384986877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00840759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00169706344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01805281639099</t>
   </si>
   <si>
     <t xml:space="preserve">1.99540662765503</t>
@@ -5060,7 +5060,7 @@
     <t xml:space="preserve">1.95850133895874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95598483085632</t>
+    <t xml:space="preserve">1.95598495006561</t>
   </si>
   <si>
     <t xml:space="preserve">1.98072838783264</t>
@@ -5069,10 +5069,10 @@
     <t xml:space="preserve">1.98240602016449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00127816200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01302075386047</t>
+    <t xml:space="preserve">2.00127792358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.04405450820923</t>
@@ -5081,25 +5081,25 @@
     <t xml:space="preserve">2.03021502494812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02056932449341</t>
+    <t xml:space="preserve">2.02056956291199</t>
   </si>
   <si>
     <t xml:space="preserve">1.96311438083649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97024381160736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9769538640976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99666464328766</t>
+    <t xml:space="preserve">1.97024369239807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97695422172546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99666476249695</t>
   </si>
   <si>
     <t xml:space="preserve">2.01973056793213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04992604255676</t>
+    <t xml:space="preserve">2.04992580413818</t>
   </si>
   <si>
     <t xml:space="preserve">2.03860282897949</t>
@@ -5111,13 +5111,13 @@
     <t xml:space="preserve">2.06837868690491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09018635749817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11534905433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12289786338806</t>
+    <t xml:space="preserve">2.09018659591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11534929275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12289762496948</t>
   </si>
   <si>
     <t xml:space="preserve">2.12709164619446</t>
@@ -5129,22 +5129,22 @@
     <t xml:space="preserve">2.15812587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18874025344849</t>
+    <t xml:space="preserve">2.18874049186707</t>
   </si>
   <si>
     <t xml:space="preserve">2.20509624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18832087516785</t>
+    <t xml:space="preserve">2.188321352005</t>
   </si>
   <si>
     <t xml:space="preserve">2.149738073349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13506007194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13338255882263</t>
+    <t xml:space="preserve">2.13505983352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13338232040405</t>
   </si>
   <si>
     <t xml:space="preserve">2.14722180366516</t>
@@ -5153,7 +5153,7 @@
     <t xml:space="preserve">1.96101760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0067298412323</t>
+    <t xml:space="preserve">2.00672960281372</t>
   </si>
   <si>
     <t xml:space="preserve">2.04489326477051</t>
@@ -5162,10 +5162,10 @@
     <t xml:space="preserve">2.04615163803101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05076456069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03734421730042</t>
+    <t xml:space="preserve">2.05076479911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03734445571899</t>
   </si>
   <si>
     <t xml:space="preserve">2.02937650680542</t>
@@ -5177,22 +5177,22 @@
     <t xml:space="preserve">2.04573202133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06292676925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05915236473083</t>
+    <t xml:space="preserve">2.06292700767517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05915212631226</t>
   </si>
   <si>
     <t xml:space="preserve">2.0532808303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05453896522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07760524749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09060597419739</t>
+    <t xml:space="preserve">2.0545392036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07760500907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09060573577881</t>
   </si>
   <si>
     <t xml:space="preserve">2.09857392311096</t>
@@ -5204,7 +5204,7 @@
     <t xml:space="preserve">2.0587329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05202269554138</t>
+    <t xml:space="preserve">2.05202293395996</t>
   </si>
   <si>
     <t xml:space="preserve">2.00589108467102</t>
@@ -5219,61 +5219,61 @@
     <t xml:space="preserve">2.08012127876282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07634711265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06544303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07592749595642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07089519500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03818345069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04782891273499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10821986198425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09102535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06418490409851</t>
+    <t xml:space="preserve">2.07634687423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06544280052185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07592725753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07089495658875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03818321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04782915115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10821962356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09102511405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06418466567993</t>
   </si>
   <si>
     <t xml:space="preserve">2.03482842445374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03231191635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04657101631165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98156714439392</t>
+    <t xml:space="preserve">2.0323121547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04657125473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98156690597534</t>
   </si>
   <si>
     <t xml:space="preserve">1.98282539844513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01427888870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99330949783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03398942947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04908728599548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05286145210266</t>
+    <t xml:space="preserve">2.01427865028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99330961704254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0339891910553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0490870475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05286169052124</t>
   </si>
   <si>
     <t xml:space="preserve">2.02686023712158</t>
@@ -5282,25 +5282,25 @@
     <t xml:space="preserve">2.03650593757629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99205148220062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96605014801025</t>
+    <t xml:space="preserve">1.99205160140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96604990959167</t>
   </si>
   <si>
     <t xml:space="preserve">1.99079346656799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97611522674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98785781860352</t>
+    <t xml:space="preserve">1.97611498832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98785793781281</t>
   </si>
   <si>
     <t xml:space="preserve">1.9941486120224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06041049957275</t>
+    <t xml:space="preserve">2.06041026115417</t>
   </si>
   <si>
     <t xml:space="preserve">2.08934760093689</t>
@@ -5312,10 +5312,10 @@
     <t xml:space="preserve">2.15015769004822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15225458145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15057706832886</t>
+    <t xml:space="preserve">2.15225434303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15057682991028</t>
   </si>
   <si>
     <t xml:space="preserve">2.15435123443604</t>
@@ -5327,13 +5327,13 @@
     <t xml:space="preserve">2.18286919593811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20551538467407</t>
+    <t xml:space="preserve">2.20551562309265</t>
   </si>
   <si>
     <t xml:space="preserve">2.21893572807312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21977472305298</t>
+    <t xml:space="preserve">2.21977496147156</t>
   </si>
   <si>
     <t xml:space="preserve">2.25164747238159</t>
@@ -5342,19 +5342,19 @@
     <t xml:space="preserve">2.27114582061768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23835301399231</t>
+    <t xml:space="preserve">2.23835277557373</t>
   </si>
   <si>
     <t xml:space="preserve">2.25209045410156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26848697662354</t>
+    <t xml:space="preserve">2.26848721504211</t>
   </si>
   <si>
     <t xml:space="preserve">2.3039391040802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30438232421875</t>
+    <t xml:space="preserve">2.30438208580017</t>
   </si>
   <si>
     <t xml:space="preserve">2.326096534729</t>
@@ -5363,31 +5363,31 @@
     <t xml:space="preserve">2.34559535980225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34116363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36287784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38858079910278</t>
+    <t xml:space="preserve">2.34116387367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36287808418274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38858103752136</t>
   </si>
   <si>
     <t xml:space="preserve">2.37838840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39788699150085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37307047843933</t>
+    <t xml:space="preserve">2.39788675308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37307071685791</t>
   </si>
   <si>
     <t xml:space="preserve">2.39301228523254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38503551483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37705874443054</t>
+    <t xml:space="preserve">2.38503575325012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37705898284912</t>
   </si>
   <si>
     <t xml:space="preserve">2.37572956085205</t>
@@ -5399,40 +5399,40 @@
     <t xml:space="preserve">2.33540272712708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32653951644897</t>
+    <t xml:space="preserve">2.32653975486755</t>
   </si>
   <si>
     <t xml:space="preserve">2.35046982765198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3371753692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33097147941589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3460385799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35445833206177</t>
+    <t xml:space="preserve">2.33717560768127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33097124099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34603834152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35445809364319</t>
   </si>
   <si>
     <t xml:space="preserve">2.34204983711243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34293651580811</t>
+    <t xml:space="preserve">2.34293627738953</t>
   </si>
   <si>
     <t xml:space="preserve">2.38813757896423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38592195510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44131588935852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47056365013123</t>
+    <t xml:space="preserve">2.38592171669006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44131565093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47056341171265</t>
   </si>
   <si>
     <t xml:space="preserve">2.47765421867371</t>
@@ -5453,7 +5453,7 @@
     <t xml:space="preserve">2.40719318389893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41827201843262</t>
+    <t xml:space="preserve">2.41827178001404</t>
   </si>
   <si>
     <t xml:space="preserve">2.43732738494873</t>
@@ -5465,16 +5465,16 @@
     <t xml:space="preserve">2.45328068733215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45682597160339</t>
+    <t xml:space="preserve">2.45682621002197</t>
   </si>
   <si>
     <t xml:space="preserve">2.51221990585327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48873281478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49139189720154</t>
+    <t xml:space="preserve">2.4887330532074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49139165878296</t>
   </si>
   <si>
     <t xml:space="preserve">2.46568894386292</t>
@@ -5483,7 +5483,7 @@
     <t xml:space="preserve">2.54988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53747940063477</t>
+    <t xml:space="preserve">2.53747916221619</t>
   </si>
   <si>
     <t xml:space="preserve">2.48430132865906</t>
@@ -5504,10 +5504,10 @@
     <t xml:space="preserve">2.49670934677124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46879100799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50247025489807</t>
+    <t xml:space="preserve">2.46879124641418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50247049331665</t>
   </si>
   <si>
     <t xml:space="preserve">2.4869601726532</t>
@@ -5516,7 +5516,7 @@
     <t xml:space="preserve">2.49538016319275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50690221786499</t>
+    <t xml:space="preserve">2.50690197944641</t>
   </si>
   <si>
     <t xml:space="preserve">2.50379991531372</t>
@@ -5525,7 +5525,7 @@
     <t xml:space="preserve">2.51620817184448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52551436424255</t>
+    <t xml:space="preserve">2.52551412582397</t>
   </si>
   <si>
     <t xml:space="preserve">2.55742120742798</t>
@@ -5543,16 +5543,16 @@
     <t xml:space="preserve">2.61680340766907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61458778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60395193099976</t>
+    <t xml:space="preserve">2.6145875453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60395169258118</t>
   </si>
   <si>
     <t xml:space="preserve">2.66289091110229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6589024066925</t>
+    <t xml:space="preserve">2.65890264511108</t>
   </si>
   <si>
     <t xml:space="preserve">2.71252369880676</t>
@@ -5561,7 +5561,7 @@
     <t xml:space="preserve">2.75019145011902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73601055145264</t>
+    <t xml:space="preserve">2.73601078987122</t>
   </si>
   <si>
     <t xml:space="preserve">2.74974846839905</t>
@@ -5573,7 +5573,7 @@
     <t xml:space="preserve">2.78475737571716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82109570503235</t>
+    <t xml:space="preserve">2.82109594345093</t>
   </si>
   <si>
     <t xml:space="preserve">2.81046009063721</t>
@@ -5585,7 +5585,7 @@
     <t xml:space="preserve">2.86186552047729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90352177619934</t>
+    <t xml:space="preserve">2.90352153778076</t>
   </si>
   <si>
     <t xml:space="preserve">2.899090051651</t>
@@ -5594,7 +5594,7 @@
     <t xml:space="preserve">2.91858863830566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92036151885986</t>
+    <t xml:space="preserve">2.92036128044128</t>
   </si>
   <si>
     <t xml:space="preserve">2.94384837150574</t>
@@ -5603,19 +5603,19 @@
     <t xml:space="preserve">2.96511960029602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96733546257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98062992095947</t>
+    <t xml:space="preserve">2.96733522415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98062968254089</t>
   </si>
   <si>
     <t xml:space="preserve">2.96689224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01608180999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00012826919556</t>
+    <t xml:space="preserve">3.01608204841614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00012850761414</t>
   </si>
   <si>
     <t xml:space="preserve">2.95049548149109</t>
@@ -5636,7 +5636,7 @@
     <t xml:space="preserve">2.91592979431152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94828009605408</t>
+    <t xml:space="preserve">2.94827961921692</t>
   </si>
   <si>
     <t xml:space="preserve">2.88225054740906</t>
@@ -5645,13 +5645,13 @@
     <t xml:space="preserve">2.92390656471252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96866488456726</t>
+    <t xml:space="preserve">2.96866464614868</t>
   </si>
   <si>
     <t xml:space="preserve">2.99303817749023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03868246078491</t>
+    <t xml:space="preserve">3.03868269920349</t>
   </si>
   <si>
     <t xml:space="preserve">3.11933588981628</t>
@@ -5678,22 +5678,22 @@
     <t xml:space="preserve">3.06837344169617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15789008140564</t>
+    <t xml:space="preserve">3.15788984298706</t>
   </si>
   <si>
     <t xml:space="preserve">3.18935370445251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18492221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17251420021057</t>
+    <t xml:space="preserve">3.18492197990417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17251372337341</t>
   </si>
   <si>
     <t xml:space="preserve">3.19112634658813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21417021751404</t>
+    <t xml:space="preserve">3.21416997909546</t>
   </si>
   <si>
     <t xml:space="preserve">3.2819721698761</t>
@@ -5702,7 +5702,7 @@
     <t xml:space="preserve">3.3032431602478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30856132507324</t>
+    <t xml:space="preserve">3.30856108665466</t>
   </si>
   <si>
     <t xml:space="preserve">3.34046792984009</t>
@@ -5735,13 +5735,13 @@
     <t xml:space="preserve">3.33677363395691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33030867576599</t>
+    <t xml:space="preserve">3.33030891418457</t>
   </si>
   <si>
     <t xml:space="preserve">3.36170959472656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27628111839294</t>
+    <t xml:space="preserve">3.27628135681152</t>
   </si>
   <si>
     <t xml:space="preserve">3.2721254825592</t>
@@ -5750,7 +5750,7 @@
     <t xml:space="preserve">3.32569122314453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31276154518127</t>
+    <t xml:space="preserve">3.3127613067627</t>
   </si>
   <si>
     <t xml:space="preserve">3.29521417617798</t>
@@ -5759,7 +5759,7 @@
     <t xml:space="preserve">3.21070957183838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26058125495911</t>
+    <t xml:space="preserve">3.26058101654053</t>
   </si>
   <si>
     <t xml:space="preserve">3.15391159057617</t>
@@ -5774,7 +5774,7 @@
     <t xml:space="preserve">3.15760564804077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1954710483551</t>
+    <t xml:space="preserve">3.19547128677368</t>
   </si>
   <si>
     <t xml:space="preserve">3.22640991210938</t>
@@ -5783,10 +5783,10 @@
     <t xml:space="preserve">3.18900632858276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24765133857727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25688695907593</t>
+    <t xml:space="preserve">3.24765157699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25688672065735</t>
   </si>
   <si>
     <t xml:space="preserve">3.199627161026</t>
@@ -5801,13 +5801,13 @@
     <t xml:space="preserve">3.26011943817139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30583500862122</t>
+    <t xml:space="preserve">3.30583477020264</t>
   </si>
   <si>
     <t xml:space="preserve">3.27812838554382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2933669090271</t>
+    <t xml:space="preserve">3.29336714744568</t>
   </si>
   <si>
     <t xml:space="preserve">3.28136086463928</t>
@@ -5819,7 +5819,7 @@
     <t xml:space="preserve">3.31645584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34277677536011</t>
+    <t xml:space="preserve">3.34277653694153</t>
   </si>
   <si>
     <t xml:space="preserve">3.33215594291687</t>
@@ -5828,7 +5828,7 @@
     <t xml:space="preserve">3.34600901603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36909770965576</t>
+    <t xml:space="preserve">3.36909794807434</t>
   </si>
   <si>
     <t xml:space="preserve">3.38710713386536</t>
@@ -5861,7 +5861,7 @@
     <t xml:space="preserve">3.32800006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18115615844727</t>
+    <t xml:space="preserve">3.18115592002869</t>
   </si>
   <si>
     <t xml:space="preserve">3.15021729469299</t>
@@ -5882,16 +5882,16 @@
     <t xml:space="preserve">3.2051682472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22225403785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32199668884277</t>
+    <t xml:space="preserve">3.22225379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32199692726135</t>
   </si>
   <si>
     <t xml:space="preserve">3.33769726753235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31968832015991</t>
+    <t xml:space="preserve">3.31968808174133</t>
   </si>
   <si>
     <t xml:space="preserve">3.33954429626465</t>
@@ -5909,13 +5909,13 @@
     <t xml:space="preserve">3.41712236404419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41850757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44344305992126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47669100761414</t>
+    <t xml:space="preserve">3.41850733757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44344329833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47669076919556</t>
   </si>
   <si>
     <t xml:space="preserve">3.48500299453735</t>
@@ -5927,7 +5927,7 @@
     <t xml:space="preserve">3.43005180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4642231464386</t>
+    <t xml:space="preserve">3.46422290802002</t>
   </si>
   <si>
     <t xml:space="preserve">3.38618350028992</t>
@@ -5939,7 +5939,7 @@
     <t xml:space="preserve">3.40696310997009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41296625137329</t>
+    <t xml:space="preserve">3.41296601295471</t>
   </si>
   <si>
     <t xml:space="preserve">3.4485228061676</t>
@@ -5948,7 +5948,7 @@
     <t xml:space="preserve">3.46791744232178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45314073562622</t>
+    <t xml:space="preserve">3.45314049720764</t>
   </si>
   <si>
     <t xml:space="preserve">3.47715282440186</t>
@@ -5963,7 +5963,7 @@
     <t xml:space="preserve">3.53256559371948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4660701751709</t>
+    <t xml:space="preserve">3.46607041358948</t>
   </si>
   <si>
     <t xml:space="preserve">3.48869705200195</t>
@@ -5972,7 +5972,7 @@
     <t xml:space="preserve">3.57966637611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57458710670471</t>
+    <t xml:space="preserve">3.57458686828613</t>
   </si>
   <si>
     <t xml:space="preserve">3.54411005973816</t>
@@ -5996,7 +5996,7 @@
     <t xml:space="preserve">3.49654722213745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51686549186707</t>
+    <t xml:space="preserve">3.51686525344849</t>
   </si>
   <si>
     <t xml:space="preserve">3.55565404891968</t>
@@ -6011,10 +6011,10 @@
     <t xml:space="preserve">3.62999987602234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62030267715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66694164276123</t>
+    <t xml:space="preserve">3.62030243873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66694140434265</t>
   </si>
   <si>
     <t xml:space="preserve">3.69418621063232</t>
@@ -6026,7 +6026,7 @@
     <t xml:space="preserve">3.63046145439148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58705472946167</t>
+    <t xml:space="preserve">3.58705496788025</t>
   </si>
   <si>
     <t xml:space="preserve">3.58289885520935</t>
@@ -6044,16 +6044,16 @@
     <t xml:space="preserve">3.63600277900696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72512531280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75744938850403</t>
+    <t xml:space="preserve">3.7251250743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75744915008545</t>
   </si>
   <si>
     <t xml:space="preserve">3.78654074668884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66832661628723</t>
+    <t xml:space="preserve">3.66832685470581</t>
   </si>
   <si>
     <t xml:space="preserve">3.5602719783783</t>
@@ -6062,10 +6062,10 @@
     <t xml:space="preserve">3.54226279258728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60090780258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51270914077759</t>
+    <t xml:space="preserve">3.60090804100037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51270937919617</t>
   </si>
   <si>
     <t xml:space="preserve">3.53071856498718</t>
@@ -6774,6 +6774,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.57399988174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57200002670288</t>
   </si>
 </sst>
 </file>
@@ -72216,25 +72219,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.693587963</v>
+        <v>45968.6918171296</v>
       </c>
       <c r="B2505" t="n">
-        <v>44411626</v>
+        <v>37773875</v>
       </c>
       <c r="C2505" t="n">
-        <v>5.63700008392334</v>
+        <v>5.62599992752075</v>
       </c>
       <c r="D2505" t="n">
-        <v>5.56500005722046</v>
+        <v>5.54500007629395</v>
       </c>
       <c r="E2505" t="n">
-        <v>5.63000011444092</v>
+        <v>5.61100006103516</v>
       </c>
       <c r="F2505" t="n">
-        <v>5.57600021362305</v>
+        <v>5.57200002670288</v>
       </c>
       <c r="G2505" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/ISP.MI.xlsx
+++ b/data/ISP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="2255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="2257">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ISP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56040978431702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5183197259903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49265515804291</t>
+    <t xml:space="preserve">1.56040990352631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51831984519958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4926552772522</t>
   </si>
   <si>
     <t xml:space="preserve">1.48752224445343</t>
@@ -59,73 +59,73 @@
     <t xml:space="preserve">1.46699070930481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49676167964935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52447938919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48546922206879</t>
+    <t xml:space="preserve">1.49676156044006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52447950839996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4854691028595</t>
   </si>
   <si>
     <t xml:space="preserve">1.43824636936188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3663854598999</t>
+    <t xml:space="preserve">1.36638522148132</t>
   </si>
   <si>
     <t xml:space="preserve">1.38075757026672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30479001998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36843848228455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39307653903961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35406613349915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37254464626312</t>
+    <t xml:space="preserve">1.3047901391983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36843860149384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3930766582489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35406625270844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3725448846817</t>
   </si>
   <si>
     <t xml:space="preserve">1.3591992855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29041790962219</t>
+    <t xml:space="preserve">1.2904177904129</t>
   </si>
   <si>
     <t xml:space="preserve">1.34380030632019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31505572795868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26988625526428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20315825939178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27296602725983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22369003295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17441391944885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10152626037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26064705848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22984933853149</t>
+    <t xml:space="preserve">1.31505584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26988637447357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2031581401825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27296590805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22368991374969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17441380023956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1015260219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26064693927765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2298492193222</t>
   </si>
   <si>
     <t xml:space="preserve">1.25243413448334</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">1.21958363056183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19494557380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23395574092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20110499858856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16004168987274</t>
+    <t xml:space="preserve">1.19494569301605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23395562171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20110476016998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16004157066345</t>
   </si>
   <si>
     <t xml:space="preserve">1.18057322502136</t>
@@ -155,25 +155,25 @@
     <t xml:space="preserve">1.20007848739624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20213162899017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2247166633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27091288566589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32224202156067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29555082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26475346088409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27604568004608</t>
+    <t xml:space="preserve">1.20213139057159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22471642494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27091264724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32224178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29555070400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26475310325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27604579925537</t>
   </si>
   <si>
     <t xml:space="preserve">1.2914445400238</t>
@@ -182,55 +182,55 @@
     <t xml:space="preserve">1.30581676959991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40334248542786</t>
+    <t xml:space="preserve">1.40334236621857</t>
   </si>
   <si>
     <t xml:space="preserve">1.37459790706635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36022567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33045494556427</t>
+    <t xml:space="preserve">1.36022591590881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33045446872711</t>
   </si>
   <si>
     <t xml:space="preserve">1.29349780082703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27912569046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29247093200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2575671672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23600900173187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24935448169708</t>
+    <t xml:space="preserve">1.27912557125092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29247105121613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25756728649139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23600888252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24935460090637</t>
   </si>
   <si>
     <t xml:space="preserve">1.24114179611206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2175304889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18673264980316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13540375232697</t>
+    <t xml:space="preserve">1.21753036975861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18673312664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13540351390839</t>
   </si>
   <si>
     <t xml:space="preserve">1.1487489938736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11076545715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17749333381653</t>
+    <t xml:space="preserve">1.11076557636261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17749345302582</t>
   </si>
   <si>
     <t xml:space="preserve">1.19802522659302</t>
@@ -239,10 +239,10 @@
     <t xml:space="preserve">1.24422168731689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25038123130798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2565404176712</t>
+    <t xml:space="preserve">1.25038111209869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25654077529907</t>
   </si>
   <si>
     <t xml:space="preserve">1.26270020008087</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">1.24216842651367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27809870243073</t>
+    <t xml:space="preserve">1.27809882164001</t>
   </si>
   <si>
     <t xml:space="preserve">1.23190259933472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26680624485016</t>
+    <t xml:space="preserve">1.26680660247803</t>
   </si>
   <si>
     <t xml:space="preserve">1.26783299446106</t>
@@ -272,25 +272,25 @@
     <t xml:space="preserve">1.13950979709625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14258968830109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1497757434845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15798842906952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14566946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1415628194809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1292439699173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12103128433228</t>
+    <t xml:space="preserve">1.1425895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14977562427521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15798830986023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14566922187805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14156305789948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12924420833588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12103152275085</t>
   </si>
   <si>
     <t xml:space="preserve">1.15080237388611</t>
@@ -302,10 +302,10 @@
     <t xml:space="preserve">1.18775928020477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18666660785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25878417491913</t>
+    <t xml:space="preserve">1.18666648864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25878441333771</t>
   </si>
   <si>
     <t xml:space="preserve">1.28719460964203</t>
@@ -320,34 +320,34 @@
     <t xml:space="preserve">1.24020874500275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23037421703339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20852065086365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20414972305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22491109371185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2107058763504</t>
+    <t xml:space="preserve">1.23037445545197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20852053165436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20414984226227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22491085529327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21070599555969</t>
   </si>
   <si>
     <t xml:space="preserve">1.1997789144516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15060782432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08286046981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0451625585556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07466542720795</t>
+    <t xml:space="preserve">1.15060770511627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0828605890274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04516279697418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07466530799866</t>
   </si>
   <si>
     <t xml:space="preserve">1.06537759304047</t>
@@ -359,43 +359,43 @@
     <t xml:space="preserve">1.14842236042023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17683243751526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17573976516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23365235328674</t>
+    <t xml:space="preserve">1.17683255672455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17573964595795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23365247249603</t>
   </si>
   <si>
     <t xml:space="preserve">0.950644552707672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846838474273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887268304824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900380611419678</t>
+    <t xml:space="preserve">0.846838593482971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887268364429474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900380492210388</t>
   </si>
   <si>
     <t xml:space="preserve">0.929883360862732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917863667011261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88999992609024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870331466197968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868692517280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87415599822998</t>
+    <t xml:space="preserve">0.917863726615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889999985694885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870331585407257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868692457675934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874155938625336</t>
   </si>
   <si>
     <t xml:space="preserve">0.961571574211121</t>
@@ -404,28 +404,28 @@
     <t xml:space="preserve">0.983425259590149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04789435863495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0358749628067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05772864818573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05499696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05718207359314</t>
+    <t xml:space="preserve">1.04789423942566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03587472438812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05772876739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05499684810638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05718243122101</t>
   </si>
   <si>
     <t xml:space="preserve">1.05062615871429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06373858451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06701648235321</t>
+    <t xml:space="preserve">1.06373846530914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06701636314392</t>
   </si>
   <si>
     <t xml:space="preserve">1.06865561008453</t>
@@ -437,25 +437,25 @@
     <t xml:space="preserve">1.05335783958435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07193374633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03969931602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07630431652069</t>
+    <t xml:space="preserve">1.0719336271286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03969919681549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07630443572998</t>
   </si>
   <si>
     <t xml:space="preserve">1.03860652446747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999269366264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993805944919586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994352459907532</t>
+    <t xml:space="preserve">0.999269425868988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993806123733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994352340698242</t>
   </si>
   <si>
     <t xml:space="preserve">1.03806018829346</t>
@@ -467,49 +467,49 @@
     <t xml:space="preserve">1.0560896396637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07958269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05827486515045</t>
+    <t xml:space="preserve">1.07958257198334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05827510356903</t>
   </si>
   <si>
     <t xml:space="preserve">1.03041136264801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00964999198914</t>
+    <t xml:space="preserve">1.00965011119843</t>
   </si>
   <si>
     <t xml:space="preserve">1.05991411209106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09214866161346</t>
+    <t xml:space="preserve">1.09214854240417</t>
   </si>
   <si>
     <t xml:space="preserve">1.08231425285339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10034358501434</t>
+    <t xml:space="preserve">1.10034370422363</t>
   </si>
   <si>
     <t xml:space="preserve">1.08996307849884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11673414707184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16372001171112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19759368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19213020801544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16809105873108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1790177822113</t>
+    <t xml:space="preserve">1.11673402786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16372013092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19759356975555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19213008880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16809093952179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17901766300201</t>
   </si>
   <si>
     <t xml:space="preserve">1.18338859081268</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">1.15934932231903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13749527931213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13640260696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12766098976135</t>
+    <t xml:space="preserve">1.13749539852142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1364027261734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12766110897064</t>
   </si>
   <si>
     <t xml:space="preserve">1.09706568717957</t>
@@ -533,82 +533,82 @@
     <t xml:space="preserve">1.11236333847046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12656819820404</t>
+    <t xml:space="preserve">1.12656855583191</t>
   </si>
   <si>
     <t xml:space="preserve">1.09050953388214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07794344425201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06428468227386</t>
+    <t xml:space="preserve">1.0779435634613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06428492069244</t>
   </si>
   <si>
     <t xml:space="preserve">1.06155300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06319224834442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07848978042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05445051193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08941698074341</t>
+    <t xml:space="preserve">1.06319200992584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07848989963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05445063114166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08941674232483</t>
   </si>
   <si>
     <t xml:space="preserve">1.09378755092621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07685101032257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08340704441071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12329053878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13093912601471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15170037746429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15388572216034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1779248714447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196437835693</t>
+    <t xml:space="preserve">1.0768506526947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08340692520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12329041957855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.130939245224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15170049667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15388596057892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17792522907257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196449756622</t>
   </si>
   <si>
     <t xml:space="preserve">1.18229591846466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15279304981232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13858807086945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0992511510849</t>
+    <t xml:space="preserve">1.15279293060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13858819007874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09925103187561</t>
   </si>
   <si>
     <t xml:space="preserve">1.09597301483154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16044211387634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16918361186981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22054028511047</t>
+    <t xml:space="preserve">1.16044199466705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16918349266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22054004669189</t>
   </si>
   <si>
     <t xml:space="preserve">1.21835494041443</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">1.15497851371765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14186608791351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11891961097717</t>
+    <t xml:space="preserve">1.1418662071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11891949176788</t>
   </si>
   <si>
     <t xml:space="preserve">1.1036217212677</t>
@@ -629,67 +629,67 @@
     <t xml:space="preserve">1.06810915470123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11345613002777</t>
+    <t xml:space="preserve">1.11345601081848</t>
   </si>
   <si>
     <t xml:space="preserve">1.14514422416687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24567234516144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26643335819244</t>
+    <t xml:space="preserve">1.24567198753357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26643323898315</t>
   </si>
   <si>
     <t xml:space="preserve">1.30904853343964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27845311164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32762444019318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29265820980072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33636593818665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31888258457184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33745837211609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3385511636734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34401488304138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964407444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871699333191</t>
+    <t xml:space="preserve">1.27845275402069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32762432098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29265809059143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33636569976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31888294219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33745861053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33855152130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34401452541351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964395523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871687412262</t>
   </si>
   <si>
     <t xml:space="preserve">1.31779003143311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32543897628784</t>
+    <t xml:space="preserve">1.32543885707855</t>
   </si>
   <si>
     <t xml:space="preserve">1.36805403232574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38772237300873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3975567817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38990783691406</t>
+    <t xml:space="preserve">1.38772249221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39755666255951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38990807533264</t>
   </si>
   <si>
     <t xml:space="preserve">1.35275626182556</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">1.34838545322418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34620010852814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34729290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32216095924377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34292185306549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34947824478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31014120578766</t>
+    <t xml:space="preserve">1.34619998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34729278087616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3221607208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34292232990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3494781255722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31014132499695</t>
   </si>
   <si>
     <t xml:space="preserve">1.25222826004028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25659930706024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22928178310394</t>
+    <t xml:space="preserve">1.25659918785095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22928202152252</t>
   </si>
   <si>
     <t xml:space="preserve">1.23911595344543</t>
@@ -731,31 +731,31 @@
     <t xml:space="preserve">1.20087170600891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18557405471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19103753566742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22272539138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19322288036346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17027592658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17355442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16590547561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17136895656586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19650101661682</t>
+    <t xml:space="preserve">1.18557393550873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19103741645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22272551059723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19322299957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17027616500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1735543012619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16590535640717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17136883735657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19650089740753</t>
   </si>
   <si>
     <t xml:space="preserve">1.18120312690735</t>
@@ -767,82 +767,82 @@
     <t xml:space="preserve">1.25113558769226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27626764774323</t>
+    <t xml:space="preserve">1.2762678861618</t>
   </si>
   <si>
     <t xml:space="preserve">1.26861882209778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27189695835114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27408218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30577051639557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34182941913605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32325339317322</t>
+    <t xml:space="preserve">1.27189707756042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2740820646286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30577027797699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34182918071747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3232536315918</t>
   </si>
   <si>
     <t xml:space="preserve">1.35057079792023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35603451728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36914658546448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39100050926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38662981987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38335204124451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3767956495285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38007342815399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37898087501526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37461030483246</t>
+    <t xml:space="preserve">1.35603439807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36914670467377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39100062847137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38662993907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38335156440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37679576873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38007378578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37898099422455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37461006641388</t>
   </si>
   <si>
     <t xml:space="preserve">1.36696135997772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35384881496429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33199536800385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30467772483826</t>
+    <t xml:space="preserve">1.35384893417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33199501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30467784404755</t>
   </si>
   <si>
     <t xml:space="preserve">1.35166358947754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36040484905243</t>
+    <t xml:space="preserve">1.36040508747101</t>
   </si>
   <si>
     <t xml:space="preserve">1.37351751327515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4762305021286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50573348999023</t>
+    <t xml:space="preserve">1.47623074054718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50573372840881</t>
   </si>
   <si>
     <t xml:space="preserve">1.49480664730072</t>
@@ -851,52 +851,52 @@
     <t xml:space="preserve">1.45984029769897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46093320846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46311819553375</t>
+    <t xml:space="preserve">1.46093308925629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46311831474304</t>
   </si>
   <si>
     <t xml:space="preserve">1.47076737880707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50791895389557</t>
+    <t xml:space="preserve">1.50791883468628</t>
   </si>
   <si>
     <t xml:space="preserve">1.55271971225739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55818271636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55599749088287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55709028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5472559928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54507076740265</t>
+    <t xml:space="preserve">1.55818331241608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55599784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55709004402161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54725587368011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54507052898407</t>
   </si>
   <si>
     <t xml:space="preserve">1.55162668228149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52868008613586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52212417125702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52977287769318</t>
+    <t xml:space="preserve">1.52868044376373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52212405204773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52977299690247</t>
   </si>
   <si>
     <t xml:space="preserve">1.56594586372375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57061350345612</t>
+    <t xml:space="preserve">1.57061362266541</t>
   </si>
   <si>
     <t xml:space="preserve">1.56711304187775</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">1.55427718162537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49826729297638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48893225193024</t>
+    <t xml:space="preserve">1.49826741218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48893237113953</t>
   </si>
   <si>
     <t xml:space="preserve">1.48659884929657</t>
@@ -917,94 +917,94 @@
     <t xml:space="preserve">1.5006011724472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5111026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49126601219177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48426473140717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4994341135025</t>
+    <t xml:space="preserve">1.51110291481018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49126589298248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48426496982574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49943399429321</t>
   </si>
   <si>
     <t xml:space="preserve">1.50876915454865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50176787376404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50410163402557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49710047245026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47843050956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51460349559784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5251053571701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52627229690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57994830608368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6079535484314</t>
+    <t xml:space="preserve">1.50176763534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50410151481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49710035324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47843062877655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51460373401642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52510559558868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52627217769623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57994854450226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60795342922211</t>
   </si>
   <si>
     <t xml:space="preserve">1.64062607288361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61845541000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6196221113205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66279625892639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65929627418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67213177680969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65696227550507</t>
+    <t xml:space="preserve">1.61845517158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61962246894836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66279637813568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6592960357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6721316576004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65696203708649</t>
   </si>
   <si>
     <t xml:space="preserve">1.66863083839417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6534618139267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66163003444672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66396343708038</t>
+    <t xml:space="preserve">1.65346157550812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66162979602814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66396379470825</t>
   </si>
   <si>
     <t xml:space="preserve">1.67096483707428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67446517944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66629719734192</t>
+    <t xml:space="preserve">1.67446529865265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66629695892334</t>
   </si>
   <si>
     <t xml:space="preserve">1.67329859733582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6838002204895</t>
+    <t xml:space="preserve">1.68380033969879</t>
   </si>
   <si>
     <t xml:space="preserve">1.69313526153564</t>
@@ -1016,40 +1016,40 @@
     <t xml:space="preserve">1.69430232048035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69896972179413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70130324363708</t>
+    <t xml:space="preserve">1.69896960258484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70130336284637</t>
   </si>
   <si>
     <t xml:space="preserve">1.69196844100952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7036372423172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70830476284027</t>
+    <t xml:space="preserve">1.70363700389862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70830488204956</t>
   </si>
   <si>
     <t xml:space="preserve">1.70480406284332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68263351917267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6779659986496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6604630947113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70713794231415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6896345615387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64295983314514</t>
+    <t xml:space="preserve">1.6826331615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67796564102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66046297550201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70713758468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68963491916656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64295947551727</t>
   </si>
   <si>
     <t xml:space="preserve">1.65462827682495</t>
@@ -1061,88 +1061,88 @@
     <t xml:space="preserve">1.63712549209595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66513049602509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68146657943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70013666152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71063876152039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71763968467712</t>
+    <t xml:space="preserve">1.66513073444366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68146693706512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70013678073883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7106386423111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71764004230499</t>
   </si>
   <si>
     <t xml:space="preserve">1.73280894756317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73397588729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72464108467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73514306545258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447810649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74214422702789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74564468860626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74681162834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74097728729248</t>
+    <t xml:space="preserve">1.73397624492645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72464120388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73514270782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447786808014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7421441078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74564480781555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74681174755096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7409770488739</t>
   </si>
   <si>
     <t xml:space="preserve">1.71180534362793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71530592441559</t>
+    <t xml:space="preserve">1.71530604362488</t>
   </si>
   <si>
     <t xml:space="preserve">1.70947170257568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6849672794342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66746437549591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68029963970184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597076416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67913269996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65112793445587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.633624792099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63479173183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61728847026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61495447158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64412689208984</t>
+    <t xml:space="preserve">1.68496739864349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66746413707733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68029987812042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597100257874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67913317680359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65112781524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63362467288971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6347918510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61728835105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61495471000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64412677288055</t>
   </si>
   <si>
     <t xml:space="preserve">1.61378800868988</t>
@@ -1154,76 +1154,76 @@
     <t xml:space="preserve">1.6464604139328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67563235759735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63829231262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62895727157593</t>
+    <t xml:space="preserve">1.67563247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63829219341278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62895739078522</t>
   </si>
   <si>
     <t xml:space="preserve">1.62662363052368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62779057025909</t>
+    <t xml:space="preserve">1.6277904510498</t>
   </si>
   <si>
     <t xml:space="preserve">1.61612164974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60678660869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60445272922516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74331092834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76548159122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77248299121857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77598357200623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78415191173553</t>
+    <t xml:space="preserve">1.6067863702774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60445284843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74331068992615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76548171043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77248311042786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77598345279694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78415143489838</t>
   </si>
   <si>
     <t xml:space="preserve">1.80515551567078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80165505409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82382535934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82499217987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79815423488617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82149159908295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84366238117218</t>
+    <t xml:space="preserve">1.80165469646454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82382524013519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8249922990799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79815375804901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82149183750153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8436621427536</t>
   </si>
   <si>
     <t xml:space="preserve">1.85824811458588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83549392223358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84395372867584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111846446991</t>
+    <t xml:space="preserve">1.83549416065216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84395384788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111834526062</t>
   </si>
   <si>
     <t xml:space="preserve">1.81769907474518</t>
@@ -1232,88 +1232,88 @@
     <t xml:space="preserve">1.79902935028076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81098997592926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87283384799957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83636951446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81157338619232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377818107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80923926830292</t>
+    <t xml:space="preserve">1.81099009513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87283396720886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83636927604675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81157326698303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377865791321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923938751221</t>
   </si>
   <si>
     <t xml:space="preserve">1.80690562725067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83053481578827</t>
+    <t xml:space="preserve">1.83053469657898</t>
   </si>
   <si>
     <t xml:space="preserve">1.81303179264069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80223822593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8074893951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78444337844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79873764514923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79990422725677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80982279777527</t>
+    <t xml:space="preserve">1.80223798751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80748879909515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78444349765778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79873740673065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79990446567535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80982291698456</t>
   </si>
   <si>
     <t xml:space="preserve">1.8063223361969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79290282726288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75410497188568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72930824756622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74535310268402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76519000530243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77510809898376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7803590297699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77540004253387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74885356426239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76081418991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79523682594299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7736496925354</t>
+    <t xml:space="preserve">1.79290318489075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75410425662994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72930872440338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74535274505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76518976688385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77510845661163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78035926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7753998041153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74885380268097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7608140707016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79523706436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77364945411682</t>
   </si>
   <si>
     <t xml:space="preserve">1.78473508358002</t>
@@ -1322,73 +1322,73 @@
     <t xml:space="preserve">1.77423310279846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74272739887238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72259914875031</t>
+    <t xml:space="preserve">1.74272763729095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72259902954102</t>
   </si>
   <si>
     <t xml:space="preserve">1.70742976665497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72289049625397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72318208217621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72522449493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71909821033478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75206232070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74768686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76256418228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77131617069244</t>
+    <t xml:space="preserve">1.72289073467255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72318255901337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72522437572479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71909832954407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75206243991852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74768674373627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76256442070007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77131581306458</t>
   </si>
   <si>
     <t xml:space="preserve">1.75906372070312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77948415279388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78940236568451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79465389251709</t>
+    <t xml:space="preserve">1.77948403358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78940260410309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79465353488922</t>
   </si>
   <si>
     <t xml:space="preserve">1.81449031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81536543369293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82907652854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84832942485809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86437439918518</t>
+    <t xml:space="preserve">1.81536567211151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82907617092133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84832954406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8643741607666</t>
   </si>
   <si>
     <t xml:space="preserve">1.83986973762512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85124707221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83957827091217</t>
+    <t xml:space="preserve">1.85124719142914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83957839012146</t>
   </si>
   <si>
     <t xml:space="preserve">1.841912150383</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">1.8486213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83811950683594</t>
+    <t xml:space="preserve">1.83811962604523</t>
   </si>
   <si>
     <t xml:space="preserve">1.84453725814819</t>
@@ -1406,16 +1406,16 @@
     <t xml:space="preserve">1.83403539657593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82674241065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8378279209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85416412353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80865609645844</t>
+    <t xml:space="preserve">1.82674252986908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83782756328583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85416376590729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80865621566772</t>
   </si>
   <si>
     <t xml:space="preserve">1.7943617105484</t>
@@ -1427,16 +1427,16 @@
     <t xml:space="preserve">1.73967385292053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75156366825104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72090065479279</t>
+    <t xml:space="preserve">1.75156342983246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72090041637421</t>
   </si>
   <si>
     <t xml:space="preserve">1.70494306087494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65081298351288</t>
+    <t xml:space="preserve">1.65081310272217</t>
   </si>
   <si>
     <t xml:space="preserve">1.59730851650238</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">1.53191435337067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57759642601013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5735285282135</t>
+    <t xml:space="preserve">1.57759606838226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57352888584137</t>
   </si>
   <si>
     <t xml:space="preserve">1.62546873092651</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">1.56289041042328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55475509166718</t>
+    <t xml:space="preserve">1.55475521087646</t>
   </si>
   <si>
     <t xml:space="preserve">1.5362948179245</t>
@@ -1469,37 +1469,37 @@
     <t xml:space="preserve">1.51752126216888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61827206611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62578177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62327861785889</t>
+    <t xml:space="preserve">1.61827218532562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61733365058899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62578165531158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62327873706818</t>
   </si>
   <si>
     <t xml:space="preserve">1.59417951107025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59793424606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60575664043427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63548147678375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60325336456299</t>
+    <t xml:space="preserve">1.59793412685394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60575652122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63548123836517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60325348377228</t>
   </si>
   <si>
     <t xml:space="preserve">1.61952364444733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56695795059204</t>
+    <t xml:space="preserve">1.56695806980133</t>
   </si>
   <si>
     <t xml:space="preserve">1.55068778991699</t>
@@ -1508,16 +1508,16 @@
     <t xml:space="preserve">1.52690804004669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55694556236267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55600678920746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54474282264709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57634472846985</t>
+    <t xml:space="preserve">1.55694544315338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55600690841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54474270343781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57634484767914</t>
   </si>
   <si>
     <t xml:space="preserve">1.58416712284088</t>
@@ -1526,103 +1526,103 @@
     <t xml:space="preserve">1.60513091087341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60294055938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60606956481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58041262626648</t>
+    <t xml:space="preserve">1.60294044017792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60606932640076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5804123878479</t>
   </si>
   <si>
     <t xml:space="preserve">1.54881048202515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53066289424896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53973650932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53660762310028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55193912982941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54161405563354</t>
+    <t xml:space="preserve">1.53066265583038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53973662853241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53660750389099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55193901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54161393642426</t>
   </si>
   <si>
     <t xml:space="preserve">1.51658260822296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5053186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250267982483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53097558021545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55037486553192</t>
+    <t xml:space="preserve">1.50531840324402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53097569942474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55037498474121</t>
   </si>
   <si>
     <t xml:space="preserve">1.57039988040924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5832279920578</t>
+    <t xml:space="preserve">1.58322834968567</t>
   </si>
   <si>
     <t xml:space="preserve">1.64830982685089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57258987426758</t>
+    <t xml:space="preserve">1.57259011268616</t>
   </si>
   <si>
     <t xml:space="preserve">1.51188921928406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53003692626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50844752788544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49249005317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43804705142975</t>
+    <t xml:space="preserve">1.53003680706024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50844728946686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49249017238617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43804681301117</t>
   </si>
   <si>
     <t xml:space="preserve">1.41426718235016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40175151824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37640750408173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36576890945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35732114315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40331602096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38329100608826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37672019004822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37891054153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37859785556793</t>
+    <t xml:space="preserve">1.4017516374588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37640762329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36576902866364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35732102394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40331614017487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38329112529755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37672054767609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37891066074371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37859773635864</t>
   </si>
   <si>
     <t xml:space="preserve">1.36357879638672</t>
@@ -1634,37 +1634,37 @@
     <t xml:space="preserve">1.34918582439423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33135116100311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35857248306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897307872772</t>
+    <t xml:space="preserve">1.33135139942169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35857260227203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897319793701</t>
   </si>
   <si>
     <t xml:space="preserve">1.45901072025299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43929839134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41583168506622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47997450828552</t>
+    <t xml:space="preserve">1.43929874897003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4158319234848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47997426986694</t>
   </si>
   <si>
     <t xml:space="preserve">1.45650768280029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46432983875275</t>
+    <t xml:space="preserve">1.46432971954346</t>
   </si>
   <si>
     <t xml:space="preserve">1.45744609832764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46683323383331</t>
+    <t xml:space="preserve">1.46683287620544</t>
   </si>
   <si>
     <t xml:space="preserve">1.5009378194809</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">1.49906063079834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51908588409424</t>
+    <t xml:space="preserve">1.51908576488495</t>
   </si>
   <si>
     <t xml:space="preserve">1.5115761756897</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">1.53222703933716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49999928474426</t>
+    <t xml:space="preserve">1.49999964237213</t>
   </si>
   <si>
     <t xml:space="preserve">1.54568147659302</t>
@@ -1697,22 +1697,22 @@
     <t xml:space="preserve">1.37734615802765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32352888584137</t>
+    <t xml:space="preserve">1.32352900505066</t>
   </si>
   <si>
     <t xml:space="preserve">1.31914854049683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32634496688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35481786727905</t>
+    <t xml:space="preserve">1.32634472846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35481798648834</t>
   </si>
   <si>
     <t xml:space="preserve">1.31320345401764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27033758163452</t>
+    <t xml:space="preserve">1.27033734321594</t>
   </si>
   <si>
     <t xml:space="preserve">1.29818475246429</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">1.27284049987793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26783430576324</t>
+    <t xml:space="preserve">1.26783418655396</t>
   </si>
   <si>
     <t xml:space="preserve">1.27753400802612</t>
@@ -1733,37 +1733,37 @@
     <t xml:space="preserve">1.29536879062653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28066277503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23842239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24167680740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23128855228424</t>
+    <t xml:space="preserve">1.28066289424896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23842263221741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24167668819427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23128867149353</t>
   </si>
   <si>
     <t xml:space="preserve">1.23166406154633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18936121463776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2222775220871</t>
+    <t xml:space="preserve">1.18936133384705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22227728366852</t>
   </si>
   <si>
     <t xml:space="preserve">1.21264028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24943625926971</t>
+    <t xml:space="preserve">1.249436378479</t>
   </si>
   <si>
     <t xml:space="preserve">1.24655771255493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2221519947052</t>
+    <t xml:space="preserve">1.22215223312378</t>
   </si>
   <si>
     <t xml:space="preserve">1.24267780780792</t>
@@ -1772,37 +1772,37 @@
     <t xml:space="preserve">1.25563156604767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23667049407959</t>
+    <t xml:space="preserve">1.2366703748703</t>
   </si>
   <si>
     <t xml:space="preserve">1.25250267982483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28598213195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2697114944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25500571727753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22665786743164</t>
+    <t xml:space="preserve">1.28598201274872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26971185207367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25500583648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22665798664093</t>
   </si>
   <si>
     <t xml:space="preserve">1.25312852859497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2382972240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22265267372131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20112586021423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20538151264191</t>
+    <t xml:space="preserve">1.23829746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22265291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20112597942352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20538115501404</t>
   </si>
   <si>
     <t xml:space="preserve">1.17571914196014</t>
@@ -1814,22 +1814,22 @@
     <t xml:space="preserve">1.20888555049896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22165179252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27690815925598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27628219127655</t>
+    <t xml:space="preserve">1.22165155410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27690804004669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27628242969513</t>
   </si>
   <si>
     <t xml:space="preserve">1.28535616397858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27190172672272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28160166740417</t>
+    <t xml:space="preserve">1.2719019651413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2816014289856</t>
   </si>
   <si>
     <t xml:space="preserve">1.32196438312531</t>
@@ -1838,16 +1838,16 @@
     <t xml:space="preserve">1.29161405563354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3019392490387</t>
+    <t xml:space="preserve">1.30193936824799</t>
   </si>
   <si>
     <t xml:space="preserve">1.23491811752319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24029982089996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21376657485962</t>
+    <t xml:space="preserve">1.24029994010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2137668132782</t>
   </si>
   <si>
     <t xml:space="preserve">1.21026229858398</t>
@@ -1862,10 +1862,10 @@
     <t xml:space="preserve">1.26032483577728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23466801643372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24217736721039</t>
+    <t xml:space="preserve">1.23466789722443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2421772480011</t>
   </si>
   <si>
     <t xml:space="preserve">1.26345384120941</t>
@@ -1886,58 +1886,58 @@
     <t xml:space="preserve">1.19299077987671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18986201286316</t>
+    <t xml:space="preserve">1.18986189365387</t>
   </si>
   <si>
     <t xml:space="preserve">1.25106334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27221488952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25750911235809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26470530033112</t>
+    <t xml:space="preserve">1.27221465110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25750887393951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26470553874969</t>
   </si>
   <si>
     <t xml:space="preserve">1.25844752788544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24017453193665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22465538978577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26001214981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27565670013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27596950531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26814723014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26908588409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29192674160004</t>
+    <t xml:space="preserve">1.24017465114594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22465527057648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2600120306015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27565658092499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27596962451935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26814711093903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26908576488495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29192686080933</t>
   </si>
   <si>
     <t xml:space="preserve">1.28003704547882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28191447257996</t>
+    <t xml:space="preserve">1.28191435337067</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897367477417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24830996990204</t>
+    <t xml:space="preserve">1.24831008911133</t>
   </si>
   <si>
     <t xml:space="preserve">1.2281596660614</t>
@@ -1949,34 +1949,34 @@
     <t xml:space="preserve">1.24705839157104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24180173873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2361695766449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25131368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25531876087189</t>
+    <t xml:space="preserve">1.24180197715759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23616969585419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25131344795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2553186416626</t>
   </si>
   <si>
     <t xml:space="preserve">1.24155139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28097569942474</t>
+    <t xml:space="preserve">1.28097546100616</t>
   </si>
   <si>
     <t xml:space="preserve">1.2922397851944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28629493713379</t>
+    <t xml:space="preserve">1.28629469871521</t>
   </si>
   <si>
     <t xml:space="preserve">1.28692066669464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27659523487091</t>
+    <t xml:space="preserve">1.27659499645233</t>
   </si>
   <si>
     <t xml:space="preserve">1.2778468132019</t>
@@ -1985,46 +1985,46 @@
     <t xml:space="preserve">1.30444252490997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29943633079529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33385443687439</t>
+    <t xml:space="preserve">1.299436211586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3338543176651</t>
   </si>
   <si>
     <t xml:space="preserve">1.35043752193451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35513079166412</t>
+    <t xml:space="preserve">1.35513091087341</t>
   </si>
   <si>
     <t xml:space="preserve">1.35262763500214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36545610427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33510589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32603192329407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33760893344879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33667016029358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3482471704483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35794687271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37609446048737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39737105369568</t>
+    <t xml:space="preserve">1.36545634269714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33510613441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32603204250336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33760917186737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33667004108429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34824728965759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35794699192047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37609469890594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39737141132355</t>
   </si>
   <si>
     <t xml:space="preserve">1.3992486000061</t>
@@ -2033,82 +2033,82 @@
     <t xml:space="preserve">1.39549386501312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38610696792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34949898719788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480547904968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136378765106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35168921947479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35419225692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38016188144684</t>
+    <t xml:space="preserve">1.3861072063446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3494987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480559825897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136366844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3516891002655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35419237613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38016211986542</t>
   </si>
   <si>
     <t xml:space="preserve">1.3754688501358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38767147064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39799678325653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39956140518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39017462730408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39830958843231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43992459774017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45337855815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46558153629303</t>
+    <t xml:space="preserve">1.38767158985138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39799690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3995612859726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39017474651337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39830994606018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4399242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45337867736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46558129787445</t>
   </si>
   <si>
     <t xml:space="preserve">1.45963656902313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45244014263153</t>
+    <t xml:space="preserve">1.45244026184082</t>
   </si>
   <si>
     <t xml:space="preserve">1.42365407943726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42490565776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42991185188293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45932352542877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46245229244232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45619475841522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45306575298309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4327278137207</t>
+    <t xml:space="preserve">1.42490553855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42991197109222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45932364463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46245241165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45619463920593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45306587219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43272769451141</t>
   </si>
   <si>
     <t xml:space="preserve">1.40300321578979</t>
@@ -2117,34 +2117,34 @@
     <t xml:space="preserve">1.38673293590546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35450482368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35137593746185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3254063129425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34543132781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36639499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35825967788696</t>
+    <t xml:space="preserve">1.35450506210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35137629508972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32540619373322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3454315662384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36639475822449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35825991630554</t>
   </si>
   <si>
     <t xml:space="preserve">1.36135697364807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36066865921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33630442619324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30973815917969</t>
+    <t xml:space="preserve">1.36066877841949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33630454540253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30973839759827</t>
   </si>
   <si>
     <t xml:space="preserve">1.32061266899109</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">1.31331706047058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29872620105743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28413534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28372240066528</t>
+    <t xml:space="preserve">1.29872632026672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28413546085358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28372228145599</t>
   </si>
   <si>
     <t xml:space="preserve">1.26211130619049</t>
@@ -2174,31 +2174,31 @@
     <t xml:space="preserve">1.27326107025146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2570184469223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2614232301712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27037048339844</t>
+    <t xml:space="preserve">1.25701832771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26142311096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27037036418915</t>
   </si>
   <si>
     <t xml:space="preserve">1.27133393287659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25811958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26775503158569</t>
+    <t xml:space="preserve">1.2581193447113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2677549123764</t>
   </si>
   <si>
     <t xml:space="preserve">1.26458919048309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26018440723419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28936612606049</t>
+    <t xml:space="preserve">1.2601842880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2893660068512</t>
   </si>
   <si>
     <t xml:space="preserve">1.312628865242</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">1.30134153366089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29046714305878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29032981395721</t>
+    <t xml:space="preserve">1.29046726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29032957553864</t>
   </si>
   <si>
     <t xml:space="preserve">1.28592479228973</t>
@@ -2219,28 +2219,28 @@
     <t xml:space="preserve">1.29239428043365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29294490814209</t>
+    <t xml:space="preserve">1.29294466972351</t>
   </si>
   <si>
     <t xml:space="preserve">1.29528510570526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28537428379059</t>
+    <t xml:space="preserve">1.2853741645813</t>
   </si>
   <si>
     <t xml:space="preserve">1.29734969139099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36328423023224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39439284801483</t>
+    <t xml:space="preserve">1.36328387260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39439272880554</t>
   </si>
   <si>
     <t xml:space="preserve">1.39852237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38854277133942</t>
+    <t xml:space="preserve">1.38854265213013</t>
   </si>
   <si>
     <t xml:space="preserve">1.38097214698792</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">1.39783418178558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41469645500183</t>
+    <t xml:space="preserve">1.41469597816467</t>
   </si>
   <si>
     <t xml:space="preserve">1.41159915924072</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">1.40987849235535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41916978359222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40609312057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41091096401215</t>
+    <t xml:space="preserve">1.4191700220108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40609300136566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41091084480286</t>
   </si>
   <si>
     <t xml:space="preserve">1.38200438022614</t>
@@ -2273,61 +2273,61 @@
     <t xml:space="preserve">1.38441324234009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40058708190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3902633190155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38338088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37044179439545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35309779644012</t>
+    <t xml:space="preserve">1.40058720111847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39026343822479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38338077068329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37044167518616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35309791564941</t>
   </si>
   <si>
     <t xml:space="preserve">1.34924364089966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37649857997894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34387540817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35433673858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33836948871613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31455600261688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33892011642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26362562179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29886400699615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27023267745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3174467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31001353263855</t>
+    <t xml:space="preserve">1.37649846076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3438755273819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35433685779572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33836936950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31455588340759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33891999721527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26362538337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29886388778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27023279666901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31744658946991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31001341342926</t>
   </si>
   <si>
     <t xml:space="preserve">1.32322800159454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33644235134125</t>
+    <t xml:space="preserve">1.33644211292267</t>
   </si>
   <si>
     <t xml:space="preserve">1.30987584590912</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">1.33520352840424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34084713459015</t>
+    <t xml:space="preserve">1.34084701538086</t>
   </si>
   <si>
     <t xml:space="preserve">1.35488736629486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38578963279724</t>
+    <t xml:space="preserve">1.38578975200653</t>
   </si>
   <si>
     <t xml:space="preserve">1.37181830406189</t>
@@ -2351,76 +2351,76 @@
     <t xml:space="preserve">1.37890720367432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3768424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39542531967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41504037380219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42261099815369</t>
+    <t xml:space="preserve">1.37684261798859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39542520046234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41504049301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42261123657227</t>
   </si>
   <si>
     <t xml:space="preserve">1.44635570049286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46149742603302</t>
+    <t xml:space="preserve">1.46149706840515</t>
   </si>
   <si>
     <t xml:space="preserve">1.45082938671112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46080887317657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50175964832306</t>
+    <t xml:space="preserve">1.46080875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50175976753235</t>
   </si>
   <si>
     <t xml:space="preserve">1.47526216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46252930164337</t>
+    <t xml:space="preserve">1.46252954006195</t>
   </si>
   <si>
     <t xml:space="preserve">1.46321785449982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48937129974365</t>
+    <t xml:space="preserve">1.48937141895294</t>
   </si>
   <si>
     <t xml:space="preserve">1.49074769020081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47319746017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46597075462341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46941208839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47491812705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696255683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49728608131409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4831770658493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4411940574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43912923336029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44222605228424</t>
+    <t xml:space="preserve">1.47319734096527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46597099304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46941184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47491788864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4869624376297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4972859621048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48317730426788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44119381904602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.439129114151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44222617149353</t>
   </si>
   <si>
     <t xml:space="preserve">1.43568778038025</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">1.44773209095001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47939169406891</t>
+    <t xml:space="preserve">1.47939157485962</t>
   </si>
   <si>
     <t xml:space="preserve">1.50451278686523</t>
@@ -2438,100 +2438,100 @@
     <t xml:space="preserve">1.5003833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52103090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54064583778381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53582811355591</t>
+    <t xml:space="preserve">1.52103066444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5406459569931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53582799434662</t>
   </si>
   <si>
     <t xml:space="preserve">1.53789293766022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55062556266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56576716899872</t>
+    <t xml:space="preserve">1.55062532424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56576704978943</t>
   </si>
   <si>
     <t xml:space="preserve">1.56232571601868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56301379203796</t>
+    <t xml:space="preserve">1.56301391124725</t>
   </si>
   <si>
     <t xml:space="preserve">1.56404626369476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56817603111267</t>
+    <t xml:space="preserve">1.56817555427551</t>
   </si>
   <si>
     <t xml:space="preserve">1.56370222568512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54752814769745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54580771923065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56439054012299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58710265159607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61050283908844</t>
+    <t xml:space="preserve">1.54752838611603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54580783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56439018249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58710253238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61050295829773</t>
   </si>
   <si>
     <t xml:space="preserve">1.60878252983093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62151503562927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61256778240204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62220335006714</t>
+    <t xml:space="preserve">1.62151515483856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61256790161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62220370769501</t>
   </si>
   <si>
     <t xml:space="preserve">1.63665652275085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61394441127777</t>
+    <t xml:space="preserve">1.61394417285919</t>
   </si>
   <si>
     <t xml:space="preserve">1.60086762905121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60912656784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61738550662994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61566507816315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62013852596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61291193962097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61910617351532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61187970638275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60190033912659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58985579013824</t>
+    <t xml:space="preserve">1.60912668704987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61738526821136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61566519737244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62013864517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61291205883026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61910629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61187958717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60190010070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58985567092896</t>
   </si>
   <si>
     <t xml:space="preserve">1.58331739902496</t>
@@ -2546,52 +2546,52 @@
     <t xml:space="preserve">1.57471418380737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5922646522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58090841770172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58572626113892</t>
+    <t xml:space="preserve">1.59226417541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58090853691101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58572614192963</t>
   </si>
   <si>
     <t xml:space="preserve">1.59054398536682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60224413871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61497676372528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62633275985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6283974647522</t>
+    <t xml:space="preserve">1.60224449634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6149765253067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62633287906647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62839758396149</t>
   </si>
   <si>
     <t xml:space="preserve">1.63803327083588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6552392244339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65214216709137</t>
+    <t xml:space="preserve">1.65523946285248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65214240550995</t>
   </si>
   <si>
     <t xml:space="preserve">1.6208268404007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61635303497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63872122764587</t>
+    <t xml:space="preserve">1.61635339260101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63872146606445</t>
   </si>
   <si>
     <t xml:space="preserve">1.61704123020172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63390362262726</t>
+    <t xml:space="preserve">1.63390374183655</t>
   </si>
   <si>
     <t xml:space="preserve">1.61119139194489</t>
@@ -2600,100 +2600,100 @@
     <t xml:space="preserve">1.61532092094421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59673798084259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59845864772797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60809421539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59570586681366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5692081451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56094920635223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56783187389374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.552001953125</t>
+    <t xml:space="preserve">1.59673821926117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59845876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60809433460236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59570574760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56920802593231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56094908714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56783175468445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55200207233429</t>
   </si>
   <si>
     <t xml:space="preserve">1.58675873279572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57712316513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54546356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57264935970306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61841797828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68586659431458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70100784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7041050195694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69240474700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70857870578766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72578477859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72750520706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74815309047699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78944802284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79185664653778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75503551959991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73542034626007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63562417030334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60362064838409</t>
+    <t xml:space="preserve">1.5771232843399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5454638004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57264959812164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61841821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.685866355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70100808143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70410478115082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69240510463715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70857894420624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72578501701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72750556468964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7481529712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78944790363312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79185676574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75503516197205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73542058467865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63562440872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6036205291748</t>
   </si>
   <si>
     <t xml:space="preserve">1.57505822181702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51311588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47044432163239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45839989185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46425008773804</t>
+    <t xml:space="preserve">1.51311564445496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4704442024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45840013027191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46425032615662</t>
   </si>
   <si>
     <t xml:space="preserve">1.4085019826889</t>
@@ -2708,25 +2708,25 @@
     <t xml:space="preserve">1.17608022689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22453308105469</t>
+    <t xml:space="preserve">1.2245329618454</t>
   </si>
   <si>
     <t xml:space="preserve">1.00677096843719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06981432437897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965476095676422</t>
+    <t xml:space="preserve">1.06981456279755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965476036071777</t>
   </si>
   <si>
     <t xml:space="preserve">0.998924851417542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96946769952774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980892777442932</t>
+    <t xml:space="preserve">0.969467639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980892717838287</t>
   </si>
   <si>
     <t xml:space="preserve">1.00856029987335</t>
@@ -2735,76 +2735,76 @@
     <t xml:space="preserve">0.997135400772095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08991158008575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11234819889069</t>
+    <t xml:space="preserve">1.08991134166718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11234831809998</t>
   </si>
   <si>
     <t xml:space="preserve">1.12253451347351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07821106910706</t>
+    <t xml:space="preserve">1.07821118831635</t>
   </si>
   <si>
     <t xml:space="preserve">1.01227688789368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02438998222351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987499892711639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989564657211304</t>
+    <t xml:space="preserve">1.02439022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987500011920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989564895629883</t>
   </si>
   <si>
     <t xml:space="preserve">0.914820909500122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00360488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01103782653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997410893440247</t>
+    <t xml:space="preserve">1.00360500812531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01103830337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997410774230957</t>
   </si>
   <si>
     <t xml:space="preserve">0.99452006816864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967815935611725</t>
+    <t xml:space="preserve">0.96781599521637</t>
   </si>
   <si>
     <t xml:space="preserve">0.928035259246826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.936156690120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947168469429016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95184862613678</t>
+    <t xml:space="preserve">0.936156630516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947168588638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951848804950714</t>
   </si>
   <si>
     <t xml:space="preserve">0.908488988876343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921015202999115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952812314033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924869179725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960245192050934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996034145355225</t>
+    <t xml:space="preserve">0.921014964580536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952812016010284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924869239330292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960245311260223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996034264564514</t>
   </si>
   <si>
     <t xml:space="preserve">1.01888418197632</t>
@@ -2813,82 +2813,82 @@
     <t xml:space="preserve">0.979378640651703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947031021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998649597167969</t>
+    <t xml:space="preserve">0.947030961513519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998649477958679</t>
   </si>
   <si>
     <t xml:space="preserve">0.97745144367218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966577112674713</t>
+    <t xml:space="preserve">0.966577291488647</t>
   </si>
   <si>
     <t xml:space="preserve">0.973184406757355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970018446445465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977864325046539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959144115447998</t>
+    <t xml:space="preserve">0.970018208026886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977864444255829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959143996238708</t>
   </si>
   <si>
     <t xml:space="preserve">0.952261567115784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952399492263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999475359916687</t>
+    <t xml:space="preserve">0.952399373054504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999475538730621</t>
   </si>
   <si>
     <t xml:space="preserve">0.984746932983398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990390598773956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978690207004547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994244694709778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0031920671463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03319978713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05880260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07270526885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06843817234039</t>
+    <t xml:space="preserve">0.990390717983246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978690385818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994244813919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00319194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03319954872131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.058802485466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07270514965057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06843793392181</t>
   </si>
   <si>
     <t xml:space="preserve">1.08743369579315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1184047460556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15157854557037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16575658321381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22012805938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24118852615356</t>
+    <t xml:space="preserve">1.11840498447418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15157866477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16575646400452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22012794017792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24118864536285</t>
   </si>
   <si>
     <t xml:space="preserve">1.18378865718842</t>
@@ -2900,28 +2900,28 @@
     <t xml:space="preserve">1.11344945430756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11634027957916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11950612068176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16947305202484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17263889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16025054454803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15956211090088</t>
+    <t xml:space="preserve">1.11634004116058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11950623989105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16947293281555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17263901233673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16025042533875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15956234931946</t>
   </si>
   <si>
     <t xml:space="preserve">1.15791046619415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17786955833435</t>
+    <t xml:space="preserve">1.17786967754364</t>
   </si>
   <si>
     <t xml:space="preserve">1.14717376232147</t>
@@ -2930,34 +2930,34 @@
     <t xml:space="preserve">1.142493724823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17140018939972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1725013256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16355419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20636332035065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20223355293274</t>
+    <t xml:space="preserve">1.17140030860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17250144481659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16355407238007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20636320114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20223367214203</t>
   </si>
   <si>
     <t xml:space="preserve">1.23348033428192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22962594032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21338331699371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19149708747864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21503531932831</t>
+    <t xml:space="preserve">1.22962605953217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.213383436203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19149696826935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21503520011902</t>
   </si>
   <si>
     <t xml:space="preserve">1.22604703903198</t>
@@ -2969,25 +2969,25 @@
     <t xml:space="preserve">1.24875938892365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26596558094025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26073479652405</t>
+    <t xml:space="preserve">1.26596570014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26073491573334</t>
   </si>
   <si>
     <t xml:space="preserve">1.27628922462463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29721224308014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29129314422607</t>
+    <t xml:space="preserve">1.29721200466156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29129302501678</t>
   </si>
   <si>
     <t xml:space="preserve">1.27271032333374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24944770336151</t>
+    <t xml:space="preserve">1.24944758415222</t>
   </si>
   <si>
     <t xml:space="preserve">1.23981201648712</t>
@@ -2996,16 +2996,16 @@
     <t xml:space="preserve">1.22935056686401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23155319690704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19411242008209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17497909069061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17566728591919</t>
+    <t xml:space="preserve">1.23155307769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1941123008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17497897148132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17566740512848</t>
   </si>
   <si>
     <t xml:space="preserve">1.23444378376007</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">1.26252436637878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24834644794464</t>
+    <t xml:space="preserve">1.24834632873535</t>
   </si>
   <si>
     <t xml:space="preserve">1.24256503582001</t>
@@ -3038,28 +3038,28 @@
     <t xml:space="preserve">1.25564181804657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24903476238251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26981973648071</t>
+    <t xml:space="preserve">1.24903464317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26981961727142</t>
   </si>
   <si>
     <t xml:space="preserve">1.24999809265137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24683225154877</t>
+    <t xml:space="preserve">1.24683213233948</t>
   </si>
   <si>
     <t xml:space="preserve">1.2658280134201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26224911212921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26816785335541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24146401882172</t>
+    <t xml:space="preserve">1.26224899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2681679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24146389961243</t>
   </si>
   <si>
     <t xml:space="preserve">1.25605475902557</t>
@@ -3068,22 +3068,22 @@
     <t xml:space="preserve">1.24242734909058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24008750915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22425770759583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22412002086639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23458123207092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21269524097443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23210370540619</t>
+    <t xml:space="preserve">1.24008738994598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22425758838654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22412014007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2345814704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21269512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23210382461548</t>
   </si>
   <si>
     <t xml:space="preserve">1.23967456817627</t>
@@ -3095,25 +3095,25 @@
     <t xml:space="preserve">1.21737515926361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21145617961884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19989371299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18020975589752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1257004737854</t>
+    <t xml:space="preserve">1.21145629882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19989347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18020963668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12570035457611</t>
   </si>
   <si>
     <t xml:space="preserve">1.12996757030487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10959541797638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10670495033264</t>
+    <t xml:space="preserve">1.10959529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10670471191406</t>
   </si>
   <si>
     <t xml:space="preserve">1.08674538135529</t>
@@ -3122,55 +3122,55 @@
     <t xml:space="preserve">1.11812961101532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10587871074677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10326337814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09183859825134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09596788883209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1240485906601</t>
+    <t xml:space="preserve">1.10587882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10326373577118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09183835983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09596800804138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12404870986938</t>
   </si>
   <si>
     <t xml:space="preserve">1.14827513694763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13478529453278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15309262275696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15557050704956</t>
+    <t xml:space="preserve">1.1347850561142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15309286117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15557026863098</t>
   </si>
   <si>
     <t xml:space="preserve">1.14978921413422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11317431926727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05825185775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0707780122757</t>
+    <t xml:space="preserve">1.11317420005798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05825209617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07077813148499</t>
   </si>
   <si>
     <t xml:space="preserve">1.07353115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05701303482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05770123004913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07449471950531</t>
+    <t xml:space="preserve">1.05701315402985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05770134925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07449460029602</t>
   </si>
   <si>
     <t xml:space="preserve">1.05095648765564</t>
@@ -3179,25 +3179,25 @@
     <t xml:space="preserve">1.02590429782867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97593754529953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962998270988464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977038562297821</t>
+    <t xml:space="preserve">0.975937247276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962998151779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977038621902466</t>
   </si>
   <si>
     <t xml:space="preserve">1.02026057243347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06031668186188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09968459606171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12680149078369</t>
+    <t xml:space="preserve">1.06031656265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09968447685242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12680160999298</t>
   </si>
   <si>
     <t xml:space="preserve">1.11276137828827</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">1.2153103351593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26926910877228</t>
+    <t xml:space="preserve">1.26926922798157</t>
   </si>
   <si>
     <t xml:space="preserve">1.25591707229614</t>
@@ -3224,67 +3224,67 @@
     <t xml:space="preserve">1.27615177631378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28730130195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28248345851898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31868553161621</t>
+    <t xml:space="preserve">1.28730142116547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28248369693756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31868541240692</t>
   </si>
   <si>
     <t xml:space="preserve">1.33671748638153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3277702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32515490055084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35653924942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36700034141541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37002873420715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3566769361496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35516262054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35998046398163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34951901435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231294155121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33465266227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35929214954376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33726823329926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33823180198669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3319000005722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29473423957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31662082672119</t>
+    <t xml:space="preserve">1.32777059078217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32515501976013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35653901100159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36700057983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37002897262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35667681694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516250133514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35998022556305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34951913356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231282234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3346529006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35929226875305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33726811408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3382316827774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33189976215363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29473435878754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3166207075119</t>
   </si>
   <si>
     <t xml:space="preserve">1.32309031486511</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">1.31634545326233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31125223636627</t>
+    <t xml:space="preserve">1.31125247478485</t>
   </si>
   <si>
     <t xml:space="preserve">1.29693698883057</t>
@@ -3305,34 +3305,34 @@
     <t xml:space="preserve">1.35447454452515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34552729129791</t>
+    <t xml:space="preserve">1.34552717208862</t>
   </si>
   <si>
     <t xml:space="preserve">1.33713054656982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33396470546722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31799733638763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3090500831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31951117515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31483137607574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.325843334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29679906368256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25481581687927</t>
+    <t xml:space="preserve">1.33396446704865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31799721717834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30904984474182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31951141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31483125686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32584321498871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29679918289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25481593608856</t>
   </si>
   <si>
     <t xml:space="preserve">1.26610326766968</t>
@@ -3341,34 +3341,34 @@
     <t xml:space="preserve">1.24407923221588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26197373867035</t>
+    <t xml:space="preserve">1.26197361946106</t>
   </si>
   <si>
     <t xml:space="preserve">1.25399005413055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28771436214447</t>
+    <t xml:space="preserve">1.28771424293518</t>
   </si>
   <si>
     <t xml:space="preserve">1.34291183948517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38234841823578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41848182678223</t>
+    <t xml:space="preserve">1.38234865665436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41848158836365</t>
   </si>
   <si>
     <t xml:space="preserve">1.43844068050385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43637597560883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43155825138092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43603193759918</t>
+    <t xml:space="preserve">1.43637609481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43155837059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43603205680847</t>
   </si>
   <si>
     <t xml:space="preserve">1.44257020950317</t>
@@ -3377,16 +3377,16 @@
     <t xml:space="preserve">1.4573677778244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45392656326294</t>
+    <t xml:space="preserve">1.45392632484436</t>
   </si>
   <si>
     <t xml:space="preserve">1.45117354393005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44532322883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45358228683472</t>
+    <t xml:space="preserve">1.44532310962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4535825252533</t>
   </si>
   <si>
     <t xml:space="preserve">1.481112241745</t>
@@ -3395,37 +3395,37 @@
     <t xml:space="preserve">1.4687237739563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48661851882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48283302783966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51621305942535</t>
+    <t xml:space="preserve">1.48661828041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48283278942108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51621294021606</t>
   </si>
   <si>
     <t xml:space="preserve">1.50864219665527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51036286354065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56198167800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56507837772369</t>
+    <t xml:space="preserve">1.51036298274994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56198143959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56507849693298</t>
   </si>
   <si>
     <t xml:space="preserve">1.55991697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56955206394196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5588846206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5788437128067</t>
+    <t xml:space="preserve">1.56955242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55888450145721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57884335517883</t>
   </si>
   <si>
     <t xml:space="preserve">1.59329688549042</t>
@@ -3437,73 +3437,73 @@
     <t xml:space="preserve">1.59260869026184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58194077014923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57540225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57987606525421</t>
+    <t xml:space="preserve">1.58194100856781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57540237903595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5798761844635</t>
   </si>
   <si>
     <t xml:space="preserve">1.57918787002563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58125233650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57333767414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59914684295654</t>
+    <t xml:space="preserve">1.58125257492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57333791255951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59914696216583</t>
   </si>
   <si>
     <t xml:space="preserve">1.5901997089386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59536170959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58503782749176</t>
+    <t xml:space="preserve">1.59536159038544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58503794670105</t>
   </si>
   <si>
     <t xml:space="preserve">1.55750787258148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55096936225891</t>
+    <t xml:space="preserve">1.5509694814682</t>
   </si>
   <si>
     <t xml:space="preserve">1.55578720569611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56989657878876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52791309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53204298019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52860164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58056426048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5950174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59742653369904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60637390613556</t>
+    <t xml:space="preserve">1.56989634037018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52791321277618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5320428609848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52860140800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5805641412735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59501755237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59742665290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60637354850769</t>
   </si>
   <si>
     <t xml:space="preserve">1.58847916126251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.623579621315</t>
+    <t xml:space="preserve">1.62357974052429</t>
   </si>
   <si>
     <t xml:space="preserve">1.6256445646286</t>
@@ -3512,13 +3512,13 @@
     <t xml:space="preserve">1.64457142353058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63837730884552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63975369930267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63287091255188</t>
+    <t xml:space="preserve">1.63837718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63975346088409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63287138938904</t>
   </si>
   <si>
     <t xml:space="preserve">1.64319503307343</t>
@@ -3527,37 +3527,37 @@
     <t xml:space="preserve">1.65868067741394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65351891517639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65116274356842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64976537227631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63928389549255</t>
+    <t xml:space="preserve">1.65351843833923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.651162981987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6497654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63928401470184</t>
   </si>
   <si>
     <t xml:space="preserve">1.67282438278198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68330562114716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68854653835297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70881009101868</t>
+    <t xml:space="preserve">1.68330574035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68854629993439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70881032943726</t>
   </si>
   <si>
     <t xml:space="preserve">1.72767686843872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73012232780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73326671123505</t>
+    <t xml:space="preserve">1.73012220859528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73326659202576</t>
   </si>
   <si>
     <t xml:space="preserve">1.73676073551178</t>
@@ -3566,61 +3566,61 @@
     <t xml:space="preserve">1.71894216537476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71440029144287</t>
+    <t xml:space="preserve">1.71440041065216</t>
   </si>
   <si>
     <t xml:space="preserve">1.70426833629608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69448566436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71195483207703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71265339851379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68749821186066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63788652420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65360844135284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63648903369904</t>
+    <t xml:space="preserve">1.69448578357697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71195495128632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71265351772308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68749809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63788640499115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65360867977142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63648891448975</t>
   </si>
   <si>
     <t xml:space="preserve">1.61832141876221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65186166763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66688501834869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62775456905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64662110805511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64592230319977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63229644298553</t>
+    <t xml:space="preserve">1.65186178684235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66688477993011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62775433063507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64662086963654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64592218399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63229656219482</t>
   </si>
   <si>
     <t xml:space="preserve">1.65535533428192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62146556377411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60958659648895</t>
+    <t xml:space="preserve">1.6214656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60958671569824</t>
   </si>
   <si>
     <t xml:space="preserve">1.56242072582245</t>
@@ -3629,25 +3629,25 @@
     <t xml:space="preserve">1.5959609746933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61098432540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58617842197418</t>
+    <t xml:space="preserve">1.61098456382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58617854118347</t>
   </si>
   <si>
     <t xml:space="preserve">1.59631013870239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57639598846436</t>
+    <t xml:space="preserve">1.57639575004578</t>
   </si>
   <si>
     <t xml:space="preserve">1.55962562561035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49359321594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52259159088135</t>
+    <t xml:space="preserve">1.49359333515167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52259135246277</t>
   </si>
   <si>
     <t xml:space="preserve">1.56277000904083</t>
@@ -3656,37 +3656,37 @@
     <t xml:space="preserve">1.57255268096924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59665989875793</t>
+    <t xml:space="preserve">1.59666001796722</t>
   </si>
   <si>
     <t xml:space="preserve">1.63334453105927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61657440662384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62111628055573</t>
+    <t xml:space="preserve">1.61657404899597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62111639976501</t>
   </si>
   <si>
     <t xml:space="preserve">1.63998281955719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62915194034576</t>
+    <t xml:space="preserve">1.62915217876434</t>
   </si>
   <si>
     <t xml:space="preserve">1.61727321147919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62565791606903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63509118556976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63858544826508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67596876621246</t>
+    <t xml:space="preserve">1.6256582736969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63509130477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63858509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67596852779388</t>
   </si>
   <si>
     <t xml:space="preserve">1.68016123771667</t>
@@ -3695,46 +3695,46 @@
     <t xml:space="preserve">1.6826069355011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7112557888031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71055710315704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69203996658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66898107528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68225765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66723418235779</t>
+    <t xml:space="preserve">1.71125590801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71055722236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69204020500183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66898119449615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68225753307343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6672340631485</t>
   </si>
   <si>
     <t xml:space="preserve">1.66304194927216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67002940177917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66164422035217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67526996135712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68365502357483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6682825088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67911326885223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.665487408638</t>
+    <t xml:space="preserve">1.6700291633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66164410114288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67527031898499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68365514278412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66828238964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67911303043365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66548764705658</t>
   </si>
   <si>
     <t xml:space="preserve">1.64836776256561</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">1.657102227211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63963341712952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66758346557617</t>
+    <t xml:space="preserve">1.63963317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66758370399475</t>
   </si>
   <si>
     <t xml:space="preserve">1.66094553470612</t>
@@ -3758,34 +3758,34 @@
     <t xml:space="preserve">1.6085387468338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62251400947571</t>
+    <t xml:space="preserve">1.62251389026642</t>
   </si>
   <si>
     <t xml:space="preserve">1.65815043449402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69623291492462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69413673877716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732710838318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69763028621674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7182434797287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74898874759674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72942352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75387990474701</t>
+    <t xml:space="preserve">1.69623267650604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69413638114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732722759247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69763040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71824383735657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74898910522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72942388057709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75388026237488</t>
   </si>
   <si>
     <t xml:space="preserve">1.75912082195282</t>
@@ -3794,16 +3794,16 @@
     <t xml:space="preserve">1.74933815002441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75562691688538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74339866638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76331317424774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79929947853088</t>
+    <t xml:space="preserve">1.75562715530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74339878559113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76331341266632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79929935932159</t>
   </si>
   <si>
     <t xml:space="preserve">1.81100177764893</t>
@@ -3812,88 +3812,88 @@
     <t xml:space="preserve">1.78156363964081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79319369792938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77720248699188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78192710876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79028630256653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80373311042786</t>
+    <t xml:space="preserve">1.79319381713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77720236778259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78192675113678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79028606414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80373322963715</t>
   </si>
   <si>
     <t xml:space="preserve">1.78301751613617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77211427688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78628814220428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81354594230652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82590281963348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8186342716217</t>
+    <t xml:space="preserve">1.7721141576767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78628838062286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81354606151581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82590293884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81863415241241</t>
   </si>
   <si>
     <t xml:space="preserve">1.78556132316589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80518710613251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81172895431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79573774337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80046236515045</t>
+    <t xml:space="preserve">1.80518698692322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8117288351059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79573786258698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80046212673187</t>
   </si>
   <si>
     <t xml:space="preserve">1.79682779312134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79646456241608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80991160869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80446016788483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80409669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73286330699921</t>
+    <t xml:space="preserve">1.79646468162537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80991148948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80446040630341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80409681797028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73286318778992</t>
   </si>
   <si>
     <t xml:space="preserve">1.74418127536774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72544276714325</t>
+    <t xml:space="preserve">1.72544288635254</t>
   </si>
   <si>
     <t xml:space="preserve">1.72581732273102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71494925022125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61638462543488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60626590251923</t>
+    <t xml:space="preserve">1.71494936943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61638474464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60626554489136</t>
   </si>
   <si>
     <t xml:space="preserve">1.58565330505371</t>
@@ -3902,43 +3902,43 @@
     <t xml:space="preserve">1.62537908554077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60963881015778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60888922214508</t>
+    <t xml:space="preserve">1.60963869094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60888910293579</t>
   </si>
   <si>
     <t xml:space="preserve">1.6587336063385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69246304035187</t>
+    <t xml:space="preserve">1.69246292114258</t>
   </si>
   <si>
     <t xml:space="preserve">1.67222511768341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6677280664444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66060757637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65273725986481</t>
+    <t xml:space="preserve">1.66772818565369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66060745716095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6527373790741</t>
   </si>
   <si>
     <t xml:space="preserve">1.66735327243805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65011394023895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68084514141083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311193466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63549757003784</t>
+    <t xml:space="preserve">1.65011382102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68084490299225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311205387115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63549780845642</t>
   </si>
   <si>
     <t xml:space="preserve">1.67334973812103</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">1.67185056209564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68721604347229</t>
+    <t xml:space="preserve">1.68721628189087</t>
   </si>
   <si>
     <t xml:space="preserve">1.69583594799042</t>
@@ -3956,19 +3956,19 @@
     <t xml:space="preserve">1.7115763425827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70670413970947</t>
+    <t xml:space="preserve">1.70670437812805</t>
   </si>
   <si>
     <t xml:space="preserve">1.70445537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75767314434052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7944004535675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81238913536072</t>
+    <t xml:space="preserve">1.75767290592194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79440057277679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8123893737793</t>
   </si>
   <si>
     <t xml:space="preserve">1.82363259792328</t>
@@ -3977,19 +3977,19 @@
     <t xml:space="preserve">1.83749902248383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84611904621124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86036014556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90795612335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91919887065887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92032337188721</t>
+    <t xml:space="preserve">1.84611880779266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86036050319672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90795576572418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9191986322403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9203234910965</t>
   </si>
   <si>
     <t xml:space="preserve">1.93194127082825</t>
@@ -3998,61 +3998,61 @@
     <t xml:space="preserve">1.9300674200058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89933598041534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91245329380035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91282796859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84874248504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86560714244843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92219722270966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95817518234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94655704498291</t>
+    <t xml:space="preserve">1.89933621883392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91245305538177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9128280878067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84874200820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86560690402985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92219746112823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95817506313324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9465571641922</t>
   </si>
   <si>
     <t xml:space="preserve">1.96342170238495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00127410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02151155471802</t>
+    <t xml:space="preserve">2.00127363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02151131629944</t>
   </si>
   <si>
     <t xml:space="preserve">2.04474711418152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99902510643005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03500270843506</t>
+    <t xml:space="preserve">1.99902522563934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03500318527222</t>
   </si>
   <si>
     <t xml:space="preserve">2.07585287094116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13881468772888</t>
+    <t xml:space="preserve">2.1388144493103</t>
   </si>
   <si>
     <t xml:space="preserve">2.18865895271301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07435417175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13843941688538</t>
+    <t xml:space="preserve">2.07435393333435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13843989372253</t>
   </si>
   <si>
     <t xml:space="preserve">2.09196805953979</t>
@@ -4064,25 +4064,25 @@
     <t xml:space="preserve">2.04024982452393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00427174568176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99377846717834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96417129039764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80789220333099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85698699951172</t>
+    <t xml:space="preserve">2.00427198410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99377834796906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96417152881622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80789232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85698735713959</t>
   </si>
   <si>
     <t xml:space="preserve">1.71907162666321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58640265464783</t>
+    <t xml:space="preserve">1.5864030122757</t>
   </si>
   <si>
     <t xml:space="preserve">1.60851430892944</t>
@@ -4091,52 +4091,52 @@
     <t xml:space="preserve">1.56204283237457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42127919197083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38155341148376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39834332466125</t>
+    <t xml:space="preserve">1.42127907276154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38155364990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39834320545197</t>
   </si>
   <si>
     <t xml:space="preserve">1.55342304706573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43522047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43866837024689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49158608913422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50507783889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61001336574554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55304849147797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56354188919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54892575740814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57403552532196</t>
+    <t xml:space="preserve">1.4352205991745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43866860866547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49158620834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50507771968842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61001348495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55304837226868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56354212760925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54892587661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57403540611267</t>
   </si>
   <si>
     <t xml:space="preserve">1.53505957126617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52231729030609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5238162279129</t>
+    <t xml:space="preserve">1.52231693267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52381634712219</t>
   </si>
   <si>
     <t xml:space="preserve">1.53243613243103</t>
@@ -4145,76 +4145,76 @@
     <t xml:space="preserve">1.61975753307343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59951996803284</t>
+    <t xml:space="preserve">1.59951984882355</t>
   </si>
   <si>
     <t xml:space="preserve">1.56166803836823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57778322696686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57028782367706</t>
+    <t xml:space="preserve">1.57778334617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57028794288635</t>
   </si>
   <si>
     <t xml:space="preserve">1.53056216239929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48573982715607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46280360221863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48558962345123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48469054698944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45500838756561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4572571516037</t>
+    <t xml:space="preserve">1.48573970794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46280348300934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48558974266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48469030857086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45500862598419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45725727081299</t>
   </si>
   <si>
     <t xml:space="preserve">1.47734475135803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47884392738342</t>
+    <t xml:space="preserve">1.47884404659271</t>
   </si>
   <si>
     <t xml:space="preserve">1.51444697380066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51782011985779</t>
+    <t xml:space="preserve">1.51782023906708</t>
   </si>
   <si>
     <t xml:space="preserve">1.48618936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46055507659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43761909008026</t>
+    <t xml:space="preserve">1.46055519580841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43761920928955</t>
   </si>
   <si>
     <t xml:space="preserve">1.43971788883209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44361555576324</t>
+    <t xml:space="preserve">1.44361543655396</t>
   </si>
   <si>
     <t xml:space="preserve">1.46520221233368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44091713428497</t>
+    <t xml:space="preserve">1.44091701507568</t>
   </si>
   <si>
     <t xml:space="preserve">1.4692497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44301581382751</t>
+    <t xml:space="preserve">1.4430159330368</t>
   </si>
   <si>
     <t xml:space="preserve">1.44256603717804</t>
@@ -4223,16 +4223,16 @@
     <t xml:space="preserve">1.40913665294647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37165951728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39534509181976</t>
+    <t xml:space="preserve">1.37165939807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39534497261047</t>
   </si>
   <si>
     <t xml:space="preserve">1.45410907268524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47074866294861</t>
+    <t xml:space="preserve">1.47074902057648</t>
   </si>
   <si>
     <t xml:space="preserve">1.47839403152466</t>
@@ -4241,13 +4241,13 @@
     <t xml:space="preserve">1.46490240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49188590049744</t>
+    <t xml:space="preserve">1.49188578128815</t>
   </si>
   <si>
     <t xml:space="preserve">1.49008703231812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48633921146393</t>
+    <t xml:space="preserve">1.48633933067322</t>
   </si>
   <si>
     <t xml:space="preserve">1.54183983802795</t>
@@ -4265,7 +4265,7 @@
     <t xml:space="preserve">1.59788691997528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6076443195343</t>
+    <t xml:space="preserve">1.60764443874359</t>
   </si>
   <si>
     <t xml:space="preserve">1.58500683307648</t>
@@ -4286,16 +4286,16 @@
     <t xml:space="preserve">1.55339276790619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53528273105621</t>
+    <t xml:space="preserve">1.5352828502655</t>
   </si>
   <si>
     <t xml:space="preserve">1.42193973064423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37307417392731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38166081905365</t>
+    <t xml:space="preserve">1.3730742931366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38166093826294</t>
   </si>
   <si>
     <t xml:space="preserve">1.44520163536072</t>
@@ -4304,103 +4304,103 @@
     <t xml:space="preserve">1.39961469173431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40788912773132</t>
+    <t xml:space="preserve">1.40788888931274</t>
   </si>
   <si>
     <t xml:space="preserve">1.46175038814545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47221052646637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46799516677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43630290031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46924424171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47798681259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48204600811005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46440446376801</t>
+    <t xml:space="preserve">1.47221040725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46799528598785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43630278110504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46924412250519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47798669338226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48204588890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46440434455872</t>
   </si>
   <si>
     <t xml:space="preserve">1.38946688175201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37978732585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34669017791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30469357967377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31000173091888</t>
+    <t xml:space="preserve">1.37978756427765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34669005870819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30469369888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31000185012817</t>
   </si>
   <si>
     <t xml:space="preserve">1.36230206489563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37588429450989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35199820995331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33295154571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32764339447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25411105155945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27393805980682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30672335624695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38369047641754</t>
+    <t xml:space="preserve">1.37588441371918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35199809074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33295130729675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3276435136795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25411093235016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27393817901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30672323703766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38369035720825</t>
   </si>
   <si>
     <t xml:space="preserve">1.33513700962067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29813671112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29579484462738</t>
+    <t xml:space="preserve">1.2981368303299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29579496383667</t>
   </si>
   <si>
     <t xml:space="preserve">1.31765162944794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29329693317413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30922114849091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33154654502869</t>
+    <t xml:space="preserve">1.29329705238342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3092212677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3315464258194</t>
   </si>
   <si>
     <t xml:space="preserve">1.34934401512146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36542439460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36370706558228</t>
+    <t xml:space="preserve">1.36542427539825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36370694637299</t>
   </si>
   <si>
     <t xml:space="preserve">1.38462710380554</t>
@@ -4412,25 +4412,25 @@
     <t xml:space="preserve">1.41600728034973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4185049533844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41756844520569</t>
+    <t xml:space="preserve">1.41850519180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41756856441498</t>
   </si>
   <si>
     <t xml:space="preserve">1.43052649497986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4470751285553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44785559177399</t>
+    <t xml:space="preserve">1.44707500934601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44785571098328</t>
   </si>
   <si>
     <t xml:space="preserve">1.42740404605865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42615509033203</t>
+    <t xml:space="preserve">1.42615520954132</t>
   </si>
   <si>
     <t xml:space="preserve">1.3841587305069</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">1.36573672294617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37666499614716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35699391365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.315309882164</t>
+    <t xml:space="preserve">1.37666487693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3569940328598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31530976295471</t>
   </si>
   <si>
     <t xml:space="preserve">1.32811176776886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34996855258942</t>
+    <t xml:space="preserve">1.34996867179871</t>
   </si>
   <si>
     <t xml:space="preserve">1.34497272968292</t>
@@ -4463,43 +4463,43 @@
     <t xml:space="preserve">1.32217907905579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35683763027191</t>
+    <t xml:space="preserve">1.3568377494812</t>
   </si>
   <si>
     <t xml:space="preserve">1.32467699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32998514175415</t>
+    <t xml:space="preserve">1.32998526096344</t>
   </si>
   <si>
     <t xml:space="preserve">1.32701885700226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35855507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43099474906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48001646995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46846342086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48329484462738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49875056743622</t>
+    <t xml:space="preserve">1.35855519771576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4309948682785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48001635074615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46846354007721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48329496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4987508058548</t>
   </si>
   <si>
     <t xml:space="preserve">1.49484777450562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49515998363495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44348430633545</t>
+    <t xml:space="preserve">1.49516010284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44348442554474</t>
   </si>
   <si>
     <t xml:space="preserve">1.43364870548248</t>
@@ -4511,16 +4511,16 @@
     <t xml:space="preserve">1.37697744369507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38041186332703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34825110435486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32592606544495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2918918132782</t>
+    <t xml:space="preserve">1.38041174411774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34825122356415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32592594623566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29189193248749</t>
   </si>
   <si>
     <t xml:space="preserve">1.32920455932617</t>
@@ -4529,55 +4529,55 @@
     <t xml:space="preserve">1.35355925559998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39571166038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35917961597443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33654236793518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3313901424408</t>
+    <t xml:space="preserve">1.39571154117584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35917949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33654224872589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33139026165009</t>
   </si>
   <si>
     <t xml:space="preserve">1.3234281539917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30781614780426</t>
+    <t xml:space="preserve">1.30781602859497</t>
   </si>
   <si>
     <t xml:space="preserve">1.33201479911804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33669817447662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36058461666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40726447105408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852166175842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4277161359787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42662346363068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44863641262054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45550549030304</t>
+    <t xml:space="preserve">1.33669829368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36058473587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40726470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39852178096771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42771637439728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42662334442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44863629341125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45550560951233</t>
   </si>
   <si>
     <t xml:space="preserve">1.45644235610962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4876663684845</t>
+    <t xml:space="preserve">1.48766624927521</t>
   </si>
   <si>
     <t xml:space="preserve">1.48719787597656</t>
@@ -4586,88 +4586,88 @@
     <t xml:space="preserve">1.50577628612518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51842188835144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5181097984314</t>
+    <t xml:space="preserve">1.51842176914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51810967922211</t>
   </si>
   <si>
     <t xml:space="preserve">1.53746843338013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61193764209747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66189587116241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67672741413116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68141114711761</t>
+    <t xml:space="preserve">1.61193752288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66189610958099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67672753334045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68141102790833</t>
   </si>
   <si>
     <t xml:space="preserve">1.69936490058899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68648505210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70678055286407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.709512591362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70990288257599</t>
+    <t xml:space="preserve">1.6864846944809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70678067207336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70951271057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70990312099457</t>
   </si>
   <si>
     <t xml:space="preserve">1.70014536380768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73019850254059</t>
+    <t xml:space="preserve">1.73019862174988</t>
   </si>
   <si>
     <t xml:space="preserve">1.7288259267807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74457168579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73165214061737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74416792392731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74295675754547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70863842964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72357702255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71348333358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68320286273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69289255142212</t>
+    <t xml:space="preserve">1.74457156658173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73165190219879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7441680431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74295663833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70863854885101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72357714176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71348345279694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68320310115814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6928927898407</t>
   </si>
   <si>
     <t xml:space="preserve">1.67835807800293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66866827011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66463077068329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66140067577362</t>
+    <t xml:space="preserve">1.66866815090179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.664630651474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66140079498291</t>
   </si>
   <si>
     <t xml:space="preserve">1.66907179355621</t>
@@ -4676,52 +4676,52 @@
     <t xml:space="preserve">1.67028307914734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6965264081955</t>
+    <t xml:space="preserve">1.69652652740479</t>
   </si>
   <si>
     <t xml:space="preserve">1.68562543392181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61044836044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66180443763733</t>
+    <t xml:space="preserve">1.61044859886169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66180455684662</t>
   </si>
   <si>
     <t xml:space="preserve">1.64282846450806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67593550682068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69612264633179</t>
+    <t xml:space="preserve">1.67593562602997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69612276554108</t>
   </si>
   <si>
     <t xml:space="preserve">1.68279922008514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68966281414032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68118417263031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67997300624847</t>
+    <t xml:space="preserve">1.68966269493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68118405342102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67997288703918</t>
   </si>
   <si>
     <t xml:space="preserve">1.70137131214142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67795419692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71429097652435</t>
+    <t xml:space="preserve">1.67795431613922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71429109573364</t>
   </si>
   <si>
     <t xml:space="preserve">1.75426149368286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.799480676651</t>
+    <t xml:space="preserve">1.79948055744171</t>
   </si>
   <si>
     <t xml:space="preserve">1.78857946395874</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">1.84429597854614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84752643108368</t>
+    <t xml:space="preserve">1.8475261926651</t>
   </si>
   <si>
     <t xml:space="preserve">1.84510374069214</t>
@@ -4748,19 +4748,19 @@
     <t xml:space="preserve">1.82572376728058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79503965377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76072144508362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80836308002472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84550738334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85317873954773</t>
+    <t xml:space="preserve">1.79503977298737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76072156429291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80836319923401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84550750255585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85317862033844</t>
   </si>
   <si>
     <t xml:space="preserve">1.89153397083282</t>
@@ -4769,31 +4769,31 @@
     <t xml:space="preserve">1.89839768409729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89274525642395</t>
+    <t xml:space="preserve">1.89274537563324</t>
   </si>
   <si>
     <t xml:space="preserve">1.94603931903839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98076128959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9823762178421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92423701286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97591614723206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99327707290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99368119239807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02194309234619</t>
+    <t xml:space="preserve">1.98076117038727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98237597942352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92423689365387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97591626644135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9932769536972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99368095397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02194285392761</t>
   </si>
   <si>
     <t xml:space="preserve">2.00014066696167</t>
@@ -4808,10 +4808,10 @@
     <t xml:space="preserve">2.01467537879944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05989480018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07079601287842</t>
+    <t xml:space="preserve">2.05989503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07079577445984</t>
   </si>
   <si>
     <t xml:space="preserve">2.06231689453125</t>
@@ -4823,7 +4823,7 @@
     <t xml:space="preserve">1.99973714351654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03001761436462</t>
+    <t xml:space="preserve">2.0300178527832</t>
   </si>
   <si>
     <t xml:space="preserve">2.04536008834839</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">2.05262732505798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07887053489685</t>
+    <t xml:space="preserve">2.07887077331543</t>
   </si>
   <si>
     <t xml:space="preserve">2.09340524673462</t>
@@ -4847,55 +4847,55 @@
     <t xml:space="preserve">2.07119941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07725548744202</t>
+    <t xml:space="preserve">2.0772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.04414892196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00417852401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88184428215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94482803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81159317493439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8152266740799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77081525325775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83702898025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90162777900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89193761348724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255811691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82733905315399</t>
+    <t xml:space="preserve">2.00417828559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88184440135956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94482815265656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81159293651581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81522655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77081513404846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83702886104584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90162742137909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89193773269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87255823612213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82733917236328</t>
   </si>
   <si>
     <t xml:space="preserve">1.83420264720917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85196721553802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87982547283173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90970253944397</t>
+    <t xml:space="preserve">1.85196733474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87982559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90970230102539</t>
   </si>
   <si>
     <t xml:space="preserve">1.91172122955322</t>
@@ -4916,82 +4916,82 @@
     <t xml:space="preserve">1.92827451229095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97147512435913</t>
+    <t xml:space="preserve">1.97147500514984</t>
   </si>
   <si>
     <t xml:space="preserve">2.00094819068909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01750159263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01023435592651</t>
+    <t xml:space="preserve">2.01750183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01023459434509</t>
   </si>
   <si>
     <t xml:space="preserve">2.00619673728943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02436542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98722064495087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96541893482208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98479855060577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92544829845428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88022911548615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91293251514435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89395654201508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96380400657654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98883605003357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98358726501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95048034191132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9391758441925</t>
+    <t xml:space="preserve">2.02436518669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98722088336945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96541917324066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98479866981506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92544865608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88022923469543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91293227672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8939563035965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96380388736725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98883616924286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98358738422394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95048046112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93917560577393</t>
   </si>
   <si>
     <t xml:space="preserve">1.96057403087616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95451807975769</t>
+    <t xml:space="preserve">1.9545179605484</t>
   </si>
   <si>
     <t xml:space="preserve">1.94038689136505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9294855594635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95128774642944</t>
+    <t xml:space="preserve">1.92948591709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95128810405731</t>
   </si>
   <si>
     <t xml:space="preserve">1.96353375911713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9643726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88888454437256</t>
+    <t xml:space="preserve">1.96437251567841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88888430595398</t>
   </si>
   <si>
     <t xml:space="preserve">1.88804543018341</t>
@@ -5000,43 +5000,43 @@
     <t xml:space="preserve">1.88301289081573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86665737628937</t>
+    <t xml:space="preserve">1.86665725708008</t>
   </si>
   <si>
     <t xml:space="preserve">1.85365641117096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80794417858124</t>
+    <t xml:space="preserve">1.80794405937195</t>
   </si>
   <si>
     <t xml:space="preserve">1.87043154239655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90524005889893</t>
+    <t xml:space="preserve">1.90524017810822</t>
   </si>
   <si>
     <t xml:space="preserve">1.89475572109222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91698276996613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93166077136993</t>
+    <t xml:space="preserve">1.91698288917542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93166100978851</t>
   </si>
   <si>
     <t xml:space="preserve">1.94927477836609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93711292743683</t>
+    <t xml:space="preserve">1.93711280822754</t>
   </si>
   <si>
     <t xml:space="preserve">1.93417716026306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93920969963074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97108221054077</t>
+    <t xml:space="preserve">1.93920993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97108244895935</t>
   </si>
   <si>
     <t xml:space="preserve">1.97779285907745</t>
@@ -5048,13 +5048,13 @@
     <t xml:space="preserve">2.00840759277344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00169706344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01805281639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99540662765503</t>
+    <t xml:space="preserve">2.00169730186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01805305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99540627002716</t>
   </si>
   <si>
     <t xml:space="preserve">1.95850133895874</t>
@@ -5063,16 +5063,16 @@
     <t xml:space="preserve">1.95598495006561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98072838783264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98240602016449</t>
+    <t xml:space="preserve">1.98072850704193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9824059009552</t>
   </si>
   <si>
     <t xml:space="preserve">2.00127792358398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01302051544189</t>
+    <t xml:space="preserve">2.01302075386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.04405450820923</t>
@@ -5081,25 +5081,25 @@
     <t xml:space="preserve">2.03021502494812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02056956291199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96311438083649</t>
+    <t xml:space="preserve">2.02056932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96311450004578</t>
   </si>
   <si>
     <t xml:space="preserve">1.97024369239807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97695422172546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99666476249695</t>
+    <t xml:space="preserve">1.97695410251617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99666500091553</t>
   </si>
   <si>
     <t xml:space="preserve">2.01973056793213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04992580413818</t>
+    <t xml:space="preserve">2.04992628097534</t>
   </si>
   <si>
     <t xml:space="preserve">2.03860282897949</t>
@@ -5114,7 +5114,7 @@
     <t xml:space="preserve">2.09018659591675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11534929275513</t>
+    <t xml:space="preserve">2.11534905433655</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289762496948</t>
@@ -5135,7 +5135,7 @@
     <t xml:space="preserve">2.20509624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.188321352005</t>
+    <t xml:space="preserve">2.18832111358643</t>
   </si>
   <si>
     <t xml:space="preserve">2.149738073349</t>
@@ -5144,25 +5144,25 @@
     <t xml:space="preserve">2.13505983352661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13338232040405</t>
+    <t xml:space="preserve">2.13338255882263</t>
   </si>
   <si>
     <t xml:space="preserve">2.14722180366516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96101760864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00672960281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04489326477051</t>
+    <t xml:space="preserve">1.961017370224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0067298412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04489374160767</t>
   </si>
   <si>
     <t xml:space="preserve">2.04615163803101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05076479911804</t>
+    <t xml:space="preserve">2.05076456069946</t>
   </si>
   <si>
     <t xml:space="preserve">2.03734445571899</t>
@@ -5171,40 +5171,40 @@
     <t xml:space="preserve">2.02937650680542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02224683761597</t>
+    <t xml:space="preserve">2.02224707603455</t>
   </si>
   <si>
     <t xml:space="preserve">2.04573202133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06292700767517</t>
+    <t xml:space="preserve">2.06292676925659</t>
   </si>
   <si>
     <t xml:space="preserve">2.05915212631226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0532808303833</t>
+    <t xml:space="preserve">2.05328106880188</t>
   </si>
   <si>
     <t xml:space="preserve">2.0545392036438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07760500907898</t>
+    <t xml:space="preserve">2.0776047706604</t>
   </si>
   <si>
     <t xml:space="preserve">2.09060573577881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09857392311096</t>
+    <t xml:space="preserve">2.09857416152954</t>
   </si>
   <si>
     <t xml:space="preserve">2.073410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0587329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05202293395996</t>
+    <t xml:space="preserve">2.05873274803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05202269554138</t>
   </si>
   <si>
     <t xml:space="preserve">2.00589108467102</t>
@@ -5216,25 +5216,25 @@
     <t xml:space="preserve">2.02434396743774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08012127876282</t>
+    <t xml:space="preserve">2.0801215171814</t>
   </si>
   <si>
     <t xml:space="preserve">2.07634687423706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06544280052185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07592725753784</t>
+    <t xml:space="preserve">2.06544303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07592749595642</t>
   </si>
   <si>
     <t xml:space="preserve">2.07089495658875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03818321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04782915115356</t>
+    <t xml:space="preserve">2.03818345069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04782891273499</t>
   </si>
   <si>
     <t xml:space="preserve">2.10821962356567</t>
@@ -5249,13 +5249,13 @@
     <t xml:space="preserve">2.03482842445374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0323121547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04657125473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98156690597534</t>
+    <t xml:space="preserve">2.03231191635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04657101631165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98156714439392</t>
   </si>
   <si>
     <t xml:space="preserve">1.98282539844513</t>
@@ -5267,10 +5267,10 @@
     <t xml:space="preserve">1.99330961704254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0339891910553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0490870475769</t>
+    <t xml:space="preserve">2.03398942947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04908728599548</t>
   </si>
   <si>
     <t xml:space="preserve">2.05286169052124</t>
@@ -5282,10 +5282,10 @@
     <t xml:space="preserve">2.03650593757629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99205160140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96604990959167</t>
+    <t xml:space="preserve">1.9920517206192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96605014801025</t>
   </si>
   <si>
     <t xml:space="preserve">1.99079346656799</t>
@@ -5294,19 +5294,19 @@
     <t xml:space="preserve">1.97611498832703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98785793781281</t>
+    <t xml:space="preserve">1.98785769939423</t>
   </si>
   <si>
     <t xml:space="preserve">1.9941486120224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06041026115417</t>
+    <t xml:space="preserve">2.06041049957275</t>
   </si>
   <si>
     <t xml:space="preserve">2.08934760093689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11702656745911</t>
+    <t xml:space="preserve">2.11702680587769</t>
   </si>
   <si>
     <t xml:space="preserve">2.15015769004822</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">2.15225434303284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15057682991028</t>
+    <t xml:space="preserve">2.1505765914917</t>
   </si>
   <si>
     <t xml:space="preserve">2.15435123443604</t>
@@ -5333,22 +5333,22 @@
     <t xml:space="preserve">2.21893572807312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21977496147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25164747238159</t>
+    <t xml:space="preserve">2.21977472305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25164723396301</t>
   </si>
   <si>
     <t xml:space="preserve">2.27114582061768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23835277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25209045410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26848721504211</t>
+    <t xml:space="preserve">2.23835301399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25209021568298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26848697662354</t>
   </si>
   <si>
     <t xml:space="preserve">2.3039391040802</t>
@@ -5357,10 +5357,10 @@
     <t xml:space="preserve">2.30438208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.326096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34559535980225</t>
+    <t xml:space="preserve">2.32609677314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34559559822083</t>
   </si>
   <si>
     <t xml:space="preserve">2.34116387367249</t>
@@ -5369,19 +5369,19 @@
     <t xml:space="preserve">2.36287808418274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38858103752136</t>
+    <t xml:space="preserve">2.38858079910278</t>
   </si>
   <si>
     <t xml:space="preserve">2.37838840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39788675308228</t>
+    <t xml:space="preserve">2.39788699150085</t>
   </si>
   <si>
     <t xml:space="preserve">2.37307071685791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39301228523254</t>
+    <t xml:space="preserve">2.39301252365112</t>
   </si>
   <si>
     <t xml:space="preserve">2.38503575325012</t>
@@ -5399,7 +5399,7 @@
     <t xml:space="preserve">2.33540272712708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32653975486755</t>
+    <t xml:space="preserve">2.32653999328613</t>
   </si>
   <si>
     <t xml:space="preserve">2.35046982765198</t>
@@ -5414,10 +5414,10 @@
     <t xml:space="preserve">2.34603834152222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35445809364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34204983711243</t>
+    <t xml:space="preserve">2.35445833206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34205007553101</t>
   </si>
   <si>
     <t xml:space="preserve">2.34293627738953</t>
@@ -5426,25 +5426,25 @@
     <t xml:space="preserve">2.38813757896423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38592171669006</t>
+    <t xml:space="preserve">2.38592195510864</t>
   </si>
   <si>
     <t xml:space="preserve">2.44131565093994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47056341171265</t>
+    <t xml:space="preserve">2.47056365013123</t>
   </si>
   <si>
     <t xml:space="preserve">2.47765421867371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44353127479553</t>
+    <t xml:space="preserve">2.44353151321411</t>
   </si>
   <si>
     <t xml:space="preserve">2.43599796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41694259643555</t>
+    <t xml:space="preserve">2.41694235801697</t>
   </si>
   <si>
     <t xml:space="preserve">2.41339731216431</t>
@@ -5453,25 +5453,25 @@
     <t xml:space="preserve">2.40719318389893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41827178001404</t>
+    <t xml:space="preserve">2.41827201843262</t>
   </si>
   <si>
     <t xml:space="preserve">2.43732738494873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44220185279846</t>
+    <t xml:space="preserve">2.44220209121704</t>
   </si>
   <si>
     <t xml:space="preserve">2.45328068733215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45682621002197</t>
+    <t xml:space="preserve">2.45682597160339</t>
   </si>
   <si>
     <t xml:space="preserve">2.51221990585327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4887330532074</t>
+    <t xml:space="preserve">2.48873281478882</t>
   </si>
   <si>
     <t xml:space="preserve">2.49139165878296</t>
@@ -5483,7 +5483,7 @@
     <t xml:space="preserve">2.54988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53747916221619</t>
+    <t xml:space="preserve">2.53747940063477</t>
   </si>
   <si>
     <t xml:space="preserve">2.48430132865906</t>
@@ -5504,13 +5504,13 @@
     <t xml:space="preserve">2.49670934677124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46879124641418</t>
+    <t xml:space="preserve">2.46879100799561</t>
   </si>
   <si>
     <t xml:space="preserve">2.50247049331665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4869601726532</t>
+    <t xml:space="preserve">2.48696041107178</t>
   </si>
   <si>
     <t xml:space="preserve">2.49538016319275</t>
@@ -5522,10 +5522,10 @@
     <t xml:space="preserve">2.50379991531372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51620817184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52551412582397</t>
+    <t xml:space="preserve">2.5162079334259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52551436424255</t>
   </si>
   <si>
     <t xml:space="preserve">2.55742120742798</t>
@@ -5534,7 +5534,7 @@
     <t xml:space="preserve">2.5671706199646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60483813285828</t>
+    <t xml:space="preserve">2.6048378944397</t>
   </si>
   <si>
     <t xml:space="preserve">2.61857581138611</t>
@@ -5546,7 +5546,7 @@
     <t xml:space="preserve">2.6145875453949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60395169258118</t>
+    <t xml:space="preserve">2.60395193099976</t>
   </si>
   <si>
     <t xml:space="preserve">2.66289091110229</t>
@@ -5570,28 +5570,28 @@
     <t xml:space="preserve">2.72183012962341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78475737571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82109594345093</t>
+    <t xml:space="preserve">2.78475713729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82109570503235</t>
   </si>
   <si>
     <t xml:space="preserve">2.81046009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86053609848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86186552047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90352153778076</t>
+    <t xml:space="preserve">2.86053586006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86186575889587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90352177619934</t>
   </si>
   <si>
     <t xml:space="preserve">2.899090051651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91858863830566</t>
+    <t xml:space="preserve">2.91858887672424</t>
   </si>
   <si>
     <t xml:space="preserve">2.92036128044128</t>
@@ -5600,7 +5600,7 @@
     <t xml:space="preserve">2.94384837150574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96511960029602</t>
+    <t xml:space="preserve">2.96511936187744</t>
   </si>
   <si>
     <t xml:space="preserve">2.96733522415161</t>
@@ -5618,13 +5618,13 @@
     <t xml:space="preserve">3.00012850761414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95049548149109</t>
+    <t xml:space="preserve">2.95049571990967</t>
   </si>
   <si>
     <t xml:space="preserve">2.97442579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93498539924622</t>
+    <t xml:space="preserve">2.93498563766479</t>
   </si>
   <si>
     <t xml:space="preserve">2.96910786628723</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">2.96866464614868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99303817749023</t>
+    <t xml:space="preserve">2.99303793907166</t>
   </si>
   <si>
     <t xml:space="preserve">3.03868269920349</t>
@@ -5693,13 +5693,13 @@
     <t xml:space="preserve">3.19112634658813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21416997909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2819721698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3032431602478</t>
+    <t xml:space="preserve">3.21417021751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28197193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30324339866638</t>
   </si>
   <si>
     <t xml:space="preserve">3.30856108665466</t>
@@ -6776,7 +6776,13 @@
     <t xml:space="preserve">5.57399988174438</t>
   </si>
   <si>
+    <t xml:space="preserve">5.60699987411499</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.57200002670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76999998092651</t>
   </si>
 </sst>
 </file>
@@ -72219,27 +72225,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6918171296</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>37773875</v>
+        <v>42965378</v>
       </c>
       <c r="C2505" t="n">
-        <v>5.62599992752075</v>
+        <v>5.61199998855591</v>
       </c>
       <c r="D2505" t="n">
-        <v>5.54500007629395</v>
+        <v>5.51300001144409</v>
       </c>
       <c r="E2505" t="n">
-        <v>5.61100006103516</v>
+        <v>5.51300001144409</v>
       </c>
       <c r="F2505" t="n">
-        <v>5.57200002670288</v>
+        <v>5.60699987411499</v>
       </c>
       <c r="G2505" t="s">
         <v>2254</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>44411626</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>5.63700008392334</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>5.56500005722046</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>5.63000011444092</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>5.57600021362305</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>2251</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>37773875</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>5.62599992752075</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>5.54500007629395</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>5.61100006103516</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>5.57200002670288</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>2255</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6938541667</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>93258145</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>5.78299999237061</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>5.67000007629395</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>5.76999998092651</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>2256</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISP.MI.xlsx
+++ b/data/ISP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="2257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="2258">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>